--- a/three_gate/analysis/ES_weekly.xlsx
+++ b/three_gate/analysis/ES_weekly.xlsx
@@ -487,7 +487,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X58"/>
+  <dimension ref="A1:X59"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -5307,31 +5307,115 @@
       <c r="X57" t="inlineStr"/>
     </row>
     <row r="58">
-      <c r="A58" s="12" t="inlineStr">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="B58" t="n">
+        <v>7609.25</v>
+      </c>
+      <c r="C58" t="n">
+        <v>7719.75</v>
+      </c>
+      <c r="D58" t="n">
+        <v>7661.25</v>
+      </c>
+      <c r="E58" t="n">
+        <v>7700</v>
+      </c>
+      <c r="F58" t="n">
+        <v>40.5</v>
+      </c>
+      <c r="G58" s="5" t="n">
+        <v>0.0053</v>
+      </c>
+      <c r="H58" t="n">
+        <v>58.5</v>
+      </c>
+      <c r="I58" t="n">
+        <v>7442.5</v>
+      </c>
+      <c r="J58" t="n">
+        <v>7517.75</v>
+      </c>
+      <c r="K58" t="n">
+        <v>7588</v>
+      </c>
+      <c r="L58" t="n">
+        <v>7658.25</v>
+      </c>
+      <c r="M58" t="n">
+        <v>7731</v>
+      </c>
+      <c r="N58" t="n">
+        <v>7803.75</v>
+      </c>
+      <c r="O58" t="n">
+        <v>7871.5</v>
+      </c>
+      <c r="P58" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q58" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R58" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S58" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T58" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="U58" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V58" s="8" t="n">
+        <v/>
+      </c>
+      <c r="W58" s="11" t="inlineStr">
+        <is>
+          <t>空方</t>
+        </is>
+      </c>
+      <c r="X58" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="12" t="inlineStr">
         <is>
           <t>下週預測</t>
         </is>
       </c>
-      <c r="I58" s="13" t="n">
-        <v>7442.5</v>
-      </c>
-      <c r="J58" s="13" t="n">
-        <v>7517.75</v>
-      </c>
-      <c r="K58" s="13" t="n">
-        <v>7588</v>
-      </c>
-      <c r="L58" s="13" t="n">
-        <v>7658.25</v>
-      </c>
-      <c r="M58" s="13" t="n">
-        <v>7731</v>
-      </c>
-      <c r="N58" s="13" t="n">
-        <v>7803.75</v>
-      </c>
-      <c r="O58" s="13" t="n">
-        <v>7871.5</v>
+      <c r="I59" s="13" t="n">
+        <v>7602.75</v>
+      </c>
+      <c r="J59" s="13" t="n">
+        <v>7646.25</v>
+      </c>
+      <c r="K59" s="13" t="n">
+        <v>7670.75</v>
+      </c>
+      <c r="L59" s="13" t="n">
+        <v>7695.25</v>
+      </c>
+      <c r="M59" s="13" t="n">
+        <v>7729.25</v>
+      </c>
+      <c r="N59" s="13" t="n">
+        <v>7763.25</v>
+      </c>
+      <c r="O59" s="13" t="n">
+        <v>7778.25</v>
       </c>
     </row>
   </sheetData>

--- a/three_gate/analysis/ES_weekly.xlsx
+++ b/three_gate/analysis/ES_weekly.xlsx
@@ -91,7 +91,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="15">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -120,6 +120,9 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="6" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="6" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
@@ -666,31 +669,33 @@
         <v>133.5</v>
       </c>
       <c r="I2" t="n">
-        <v>6266.25</v>
+        <v>6273.75</v>
       </c>
       <c r="J2" t="n">
-        <v>6361.94</v>
+        <v>6364.75</v>
       </c>
       <c r="K2" t="n">
-        <v>6410.88</v>
+        <v>6412.75</v>
       </c>
       <c r="L2" t="n">
-        <v>6459.81</v>
+        <v>6460.75</v>
       </c>
       <c r="M2" t="n">
-        <v>6532.12</v>
+        <v>6530.25</v>
       </c>
       <c r="N2" t="n">
-        <v>6604.44</v>
+        <v>6599.75</v>
       </c>
       <c r="O2" t="n">
-        <v>6630</v>
+        <v>6626.25</v>
       </c>
       <c r="P2" s="6" t="n">
         <v/>
       </c>
-      <c r="Q2" s="6" t="n">
-        <v/>
+      <c r="Q2" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="R2" s="6" t="inlineStr">
         <is>
@@ -5313,25 +5318,25 @@
         </is>
       </c>
       <c r="B58" t="n">
-        <v>7609.25</v>
+        <v>7699.25</v>
       </c>
       <c r="C58" t="n">
-        <v>7719.75</v>
+        <v>7701</v>
       </c>
       <c r="D58" t="n">
-        <v>7661.25</v>
+        <v>7692</v>
       </c>
       <c r="E58" t="n">
-        <v>7700</v>
+        <v/>
       </c>
       <c r="F58" t="n">
-        <v>40.5</v>
+        <v/>
       </c>
       <c r="G58" s="5" t="n">
-        <v>0.0053</v>
+        <v/>
       </c>
       <c r="H58" t="n">
-        <v>58.5</v>
+        <v>9</v>
       </c>
       <c r="I58" t="n">
         <v>7442.5</v>
@@ -5354,8 +5359,10 @@
       <c r="O58" t="n">
         <v>7871.5</v>
       </c>
-      <c r="P58" s="6" t="n">
-        <v/>
+      <c r="P58" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="Q58" s="6" t="n">
         <v/>
@@ -5363,15 +5370,13 @@
       <c r="R58" s="6" t="n">
         <v/>
       </c>
-      <c r="S58" s="7" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T58" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+      <c r="S58" s="12" t="inlineStr">
+        <is>
+          <t>=</t>
+        </is>
+      </c>
+      <c r="T58" s="8" t="n">
+        <v/>
       </c>
       <c r="U58" s="8" t="n">
         <v/>
@@ -5386,36 +5391,36 @@
       </c>
       <c r="X58" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="59">
-      <c r="A59" s="12" t="inlineStr">
+      <c r="A59" s="13" t="inlineStr">
         <is>
           <t>下週預測</t>
         </is>
       </c>
-      <c r="I59" s="13" t="n">
-        <v>7602.75</v>
-      </c>
-      <c r="J59" s="13" t="n">
-        <v>7646.25</v>
-      </c>
-      <c r="K59" s="13" t="n">
-        <v>7670.75</v>
-      </c>
-      <c r="L59" s="13" t="n">
-        <v>7695.25</v>
-      </c>
-      <c r="M59" s="13" t="n">
-        <v>7729.25</v>
-      </c>
-      <c r="N59" s="13" t="n">
-        <v>7763.25</v>
-      </c>
-      <c r="O59" s="13" t="n">
-        <v>7778.25</v>
+      <c r="I59" s="14" t="n">
+        <v>7683</v>
+      </c>
+      <c r="J59" s="14" t="n">
+        <v/>
+      </c>
+      <c r="K59" s="14" t="n">
+        <v/>
+      </c>
+      <c r="L59" s="14" t="n">
+        <v/>
+      </c>
+      <c r="M59" s="14" t="n">
+        <v/>
+      </c>
+      <c r="N59" s="14" t="n">
+        <v/>
+      </c>
+      <c r="O59" s="14" t="n">
+        <v>7710</v>
       </c>
     </row>
   </sheetData>

--- a/three_gate/analysis/ES_weekly.xlsx
+++ b/three_gate/analysis/ES_weekly.xlsx
@@ -5324,7 +5324,7 @@
         <v>7701</v>
       </c>
       <c r="D58" t="n">
-        <v>7692</v>
+        <v>7690</v>
       </c>
       <c r="E58" t="n">
         <v/>
@@ -5336,7 +5336,7 @@
         <v/>
       </c>
       <c r="H58" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="I58" t="n">
         <v>7442.5</v>
@@ -5402,7 +5402,7 @@
         </is>
       </c>
       <c r="I59" s="14" t="n">
-        <v>7683</v>
+        <v>7679</v>
       </c>
       <c r="J59" s="14" t="n">
         <v/>
@@ -5420,7 +5420,7 @@
         <v/>
       </c>
       <c r="O59" s="14" t="n">
-        <v>7710</v>
+        <v>7712</v>
       </c>
     </row>
   </sheetData>

--- a/three_gate/analysis/ES_weekly.xlsx
+++ b/three_gate/analysis/ES_weekly.xlsx
@@ -91,7 +91,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="15">
+  <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -120,9 +120,6 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="6" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="6" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
@@ -5318,25 +5315,25 @@
         </is>
       </c>
       <c r="B58" t="n">
-        <v>7699.25</v>
+        <v>7609.25</v>
       </c>
       <c r="C58" t="n">
-        <v>7701</v>
+        <v>7652</v>
       </c>
       <c r="D58" t="n">
-        <v>7690</v>
+        <v>7593.75</v>
       </c>
       <c r="E58" t="n">
-        <v/>
+        <v>7625</v>
       </c>
       <c r="F58" t="n">
-        <v/>
+        <v>-34.5</v>
       </c>
       <c r="G58" s="5" t="n">
-        <v/>
+        <v>-0.0045</v>
       </c>
       <c r="H58" t="n">
-        <v>11</v>
+        <v>58.25</v>
       </c>
       <c r="I58" t="n">
         <v>7442.5</v>
@@ -5359,10 +5356,8 @@
       <c r="O58" t="n">
         <v>7871.5</v>
       </c>
-      <c r="P58" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+      <c r="P58" s="6" t="n">
+        <v/>
       </c>
       <c r="Q58" s="6" t="n">
         <v/>
@@ -5370,9 +5365,9 @@
       <c r="R58" s="6" t="n">
         <v/>
       </c>
-      <c r="S58" s="12" t="inlineStr">
-        <is>
-          <t>=</t>
+      <c r="S58" s="10" t="inlineStr">
+        <is>
+          <t>↓C</t>
         </is>
       </c>
       <c r="T58" s="8" t="n">
@@ -5396,31 +5391,31 @@
       </c>
     </row>
     <row r="59">
-      <c r="A59" s="13" t="inlineStr">
+      <c r="A59" s="12" t="inlineStr">
         <is>
           <t>下週預測</t>
         </is>
       </c>
-      <c r="I59" s="14" t="n">
-        <v>7679</v>
-      </c>
-      <c r="J59" s="14" t="n">
-        <v/>
-      </c>
-      <c r="K59" s="14" t="n">
-        <v/>
-      </c>
-      <c r="L59" s="14" t="n">
-        <v/>
-      </c>
-      <c r="M59" s="14" t="n">
-        <v/>
-      </c>
-      <c r="N59" s="14" t="n">
-        <v/>
-      </c>
-      <c r="O59" s="14" t="n">
-        <v>7712</v>
+      <c r="I59" s="13" t="n">
+        <v>7535.5</v>
+      </c>
+      <c r="J59" s="13" t="n">
+        <v>7567.81</v>
+      </c>
+      <c r="K59" s="13" t="n">
+        <v>7595.88</v>
+      </c>
+      <c r="L59" s="13" t="n">
+        <v>7623.94</v>
+      </c>
+      <c r="M59" s="13" t="n">
+        <v>7654.12</v>
+      </c>
+      <c r="N59" s="13" t="n">
+        <v>7684.31</v>
+      </c>
+      <c r="O59" s="13" t="n">
+        <v>7710.25</v>
       </c>
     </row>
   </sheetData>

--- a/three_gate/analysis/ES_weekly.xlsx
+++ b/three_gate/analysis/ES_weekly.xlsx
@@ -5318,22 +5318,22 @@
         <v>7609.25</v>
       </c>
       <c r="C58" t="n">
-        <v>7652</v>
+        <v>7701</v>
       </c>
       <c r="D58" t="n">
         <v>7593.75</v>
       </c>
       <c r="E58" t="n">
-        <v>7625</v>
+        <v>7663.75</v>
       </c>
       <c r="F58" t="n">
-        <v>-34.5</v>
+        <v>4.25</v>
       </c>
       <c r="G58" s="5" t="n">
-        <v>-0.0045</v>
+        <v>0.0005999999999999999</v>
       </c>
       <c r="H58" t="n">
-        <v>58.25</v>
+        <v>107.25</v>
       </c>
       <c r="I58" t="n">
         <v>7442.5</v>
@@ -5365,9 +5365,9 @@
       <c r="R58" s="6" t="n">
         <v/>
       </c>
-      <c r="S58" s="10" t="inlineStr">
-        <is>
-          <t>↓C</t>
+      <c r="S58" s="7" t="inlineStr">
+        <is>
+          <t>↑C</t>
         </is>
       </c>
       <c r="T58" s="8" t="n">
@@ -5386,7 +5386,7 @@
       </c>
       <c r="X58" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>
@@ -5397,25 +5397,25 @@
         </is>
       </c>
       <c r="I59" s="13" t="n">
-        <v>7535.5</v>
+        <v>7486.5</v>
       </c>
       <c r="J59" s="13" t="n">
-        <v>7567.81</v>
+        <v>7564.69</v>
       </c>
       <c r="K59" s="13" t="n">
-        <v>7595.88</v>
+        <v>7610.12</v>
       </c>
       <c r="L59" s="13" t="n">
-        <v>7623.94</v>
+        <v>7655.56</v>
       </c>
       <c r="M59" s="13" t="n">
-        <v>7654.12</v>
+        <v>7717.38</v>
       </c>
       <c r="N59" s="13" t="n">
-        <v>7684.31</v>
+        <v>7779.19</v>
       </c>
       <c r="O59" s="13" t="n">
-        <v>7710.25</v>
+        <v>7808.25</v>
       </c>
     </row>
   </sheetData>

--- a/three_gate/analysis/ES_weekly.xlsx
+++ b/three_gate/analysis/ES_weekly.xlsx
@@ -666,28 +666,30 @@
         <v>133.5</v>
       </c>
       <c r="I2" t="n">
-        <v>6273.75</v>
+        <v>6397.75</v>
       </c>
       <c r="J2" t="n">
-        <v>6364.75</v>
+        <v>6411.25</v>
       </c>
       <c r="K2" t="n">
-        <v>6412.75</v>
+        <v>6443.75</v>
       </c>
       <c r="L2" t="n">
-        <v>6460.75</v>
+        <v>6476.25</v>
       </c>
       <c r="M2" t="n">
-        <v>6530.25</v>
+        <v>6499.25</v>
       </c>
       <c r="N2" t="n">
-        <v>6599.75</v>
+        <v>6522.25</v>
       </c>
       <c r="O2" t="n">
-        <v>6626.25</v>
-      </c>
-      <c r="P2" s="6" t="n">
-        <v/>
+        <v>6564.25</v>
+      </c>
+      <c r="P2" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="Q2" s="6" t="inlineStr">
         <is>
@@ -5318,22 +5320,22 @@
         <v>7609.25</v>
       </c>
       <c r="C58" t="n">
-        <v>7701</v>
+        <v>7667.75</v>
       </c>
       <c r="D58" t="n">
         <v>7593.75</v>
       </c>
       <c r="E58" t="n">
-        <v>7663.75</v>
+        <v>7662.25</v>
       </c>
       <c r="F58" t="n">
-        <v>4.25</v>
+        <v>2.75</v>
       </c>
       <c r="G58" s="5" t="n">
-        <v>0.0005999999999999999</v>
+        <v>0.0004</v>
       </c>
       <c r="H58" t="n">
-        <v>107.25</v>
+        <v>74</v>
       </c>
       <c r="I58" t="n">
         <v>7442.5</v>
@@ -5397,25 +5399,25 @@
         </is>
       </c>
       <c r="I59" s="13" t="n">
-        <v>7486.5</v>
+        <v>7519.75</v>
       </c>
       <c r="J59" s="13" t="n">
-        <v>7564.69</v>
+        <v>7604</v>
       </c>
       <c r="K59" s="13" t="n">
-        <v>7610.12</v>
+        <v>7625.25</v>
       </c>
       <c r="L59" s="13" t="n">
-        <v>7655.56</v>
+        <v>7646.5</v>
       </c>
       <c r="M59" s="13" t="n">
-        <v>7717.38</v>
+        <v>7699.25</v>
       </c>
       <c r="N59" s="13" t="n">
-        <v>7779.19</v>
+        <v>7752</v>
       </c>
       <c r="O59" s="13" t="n">
-        <v>7808.25</v>
+        <v>7741.75</v>
       </c>
     </row>
   </sheetData>

--- a/three_gate/analysis/ES_weekly.xlsx
+++ b/three_gate/analysis/ES_weekly.xlsx
@@ -5320,22 +5320,22 @@
         <v>7609.25</v>
       </c>
       <c r="C58" t="n">
-        <v>7667.75</v>
+        <v>7678</v>
       </c>
       <c r="D58" t="n">
-        <v>7593.75</v>
+        <v>7576.75</v>
       </c>
       <c r="E58" t="n">
-        <v>7662.25</v>
+        <v>7670.5</v>
       </c>
       <c r="F58" t="n">
-        <v>2.75</v>
+        <v>11</v>
       </c>
       <c r="G58" s="5" t="n">
-        <v>0.0004</v>
+        <v>0.0014</v>
       </c>
       <c r="H58" t="n">
-        <v>74</v>
+        <v>101.25</v>
       </c>
       <c r="I58" t="n">
         <v>7442.5</v>
@@ -5364,8 +5364,10 @@
       <c r="Q58" s="6" t="n">
         <v/>
       </c>
-      <c r="R58" s="6" t="n">
-        <v/>
+      <c r="R58" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S58" s="7" t="inlineStr">
         <is>
@@ -5388,7 +5390,7 @@
       </c>
       <c r="X58" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
@@ -5399,25 +5401,25 @@
         </is>
       </c>
       <c r="I59" s="13" t="n">
-        <v>7519.75</v>
+        <v>7475.5</v>
       </c>
       <c r="J59" s="13" t="n">
-        <v>7604</v>
+        <v>7590.81</v>
       </c>
       <c r="K59" s="13" t="n">
-        <v>7625.25</v>
+        <v>7619.88</v>
       </c>
       <c r="L59" s="13" t="n">
-        <v>7646.5</v>
+        <v>7648.94</v>
       </c>
       <c r="M59" s="13" t="n">
-        <v>7699.25</v>
+        <v>7721.12</v>
       </c>
       <c r="N59" s="13" t="n">
-        <v>7752</v>
+        <v>7793.31</v>
       </c>
       <c r="O59" s="13" t="n">
-        <v>7741.75</v>
+        <v>7779.25</v>
       </c>
     </row>
   </sheetData>

--- a/three_gate/analysis/ES_weekly.xlsx
+++ b/three_gate/analysis/ES_weekly.xlsx
@@ -5320,22 +5320,22 @@
         <v>7609.25</v>
       </c>
       <c r="C58" t="n">
-        <v>7678</v>
+        <v>7681.5</v>
       </c>
       <c r="D58" t="n">
         <v>7576.75</v>
       </c>
       <c r="E58" t="n">
-        <v>7670.5</v>
+        <v>7675.75</v>
       </c>
       <c r="F58" t="n">
-        <v>11</v>
+        <v>16.25</v>
       </c>
       <c r="G58" s="5" t="n">
-        <v>0.0014</v>
+        <v>0.0021</v>
       </c>
       <c r="H58" t="n">
-        <v>101.25</v>
+        <v>104.75</v>
       </c>
       <c r="I58" t="n">
         <v>7442.5</v>
@@ -5401,25 +5401,25 @@
         </is>
       </c>
       <c r="I59" s="13" t="n">
-        <v>7475.5</v>
+        <v>7472</v>
       </c>
       <c r="J59" s="13" t="n">
-        <v>7590.81</v>
+        <v>7594.31</v>
       </c>
       <c r="K59" s="13" t="n">
-        <v>7619.88</v>
+        <v>7623.38</v>
       </c>
       <c r="L59" s="13" t="n">
-        <v>7648.94</v>
+        <v>7652.44</v>
       </c>
       <c r="M59" s="13" t="n">
-        <v>7721.12</v>
+        <v>7728.12</v>
       </c>
       <c r="N59" s="13" t="n">
-        <v>7793.31</v>
+        <v>7803.81</v>
       </c>
       <c r="O59" s="13" t="n">
-        <v>7779.25</v>
+        <v>7786.25</v>
       </c>
     </row>
   </sheetData>

--- a/three_gate/analysis/ES_weekly.xlsx
+++ b/three_gate/analysis/ES_weekly.xlsx
@@ -5320,22 +5320,22 @@
         <v>7609.25</v>
       </c>
       <c r="C58" t="n">
-        <v>7681.5</v>
+        <v>7683.5</v>
       </c>
       <c r="D58" t="n">
         <v>7576.75</v>
       </c>
       <c r="E58" t="n">
-        <v>7675.75</v>
+        <v>7683.25</v>
       </c>
       <c r="F58" t="n">
-        <v>16.25</v>
+        <v>23.75</v>
       </c>
       <c r="G58" s="5" t="n">
-        <v>0.0021</v>
+        <v>0.0031</v>
       </c>
       <c r="H58" t="n">
-        <v>104.75</v>
+        <v>106.75</v>
       </c>
       <c r="I58" t="n">
         <v>7442.5</v>
@@ -5401,25 +5401,25 @@
         </is>
       </c>
       <c r="I59" s="13" t="n">
-        <v>7472</v>
+        <v>7470</v>
       </c>
       <c r="J59" s="13" t="n">
-        <v>7594.31</v>
+        <v>7603.06</v>
       </c>
       <c r="K59" s="13" t="n">
-        <v>7623.38</v>
+        <v>7629.88</v>
       </c>
       <c r="L59" s="13" t="n">
-        <v>7652.44</v>
+        <v>7656.69</v>
       </c>
       <c r="M59" s="13" t="n">
-        <v>7728.12</v>
+        <v>7736.62</v>
       </c>
       <c r="N59" s="13" t="n">
-        <v>7803.81</v>
+        <v>7816.56</v>
       </c>
       <c r="O59" s="13" t="n">
-        <v>7786.25</v>
+        <v>7790.25</v>
       </c>
     </row>
   </sheetData>

--- a/three_gate/analysis/ES_weekly.xlsx
+++ b/three_gate/analysis/ES_weekly.xlsx
@@ -5320,22 +5320,22 @@
         <v>7609.25</v>
       </c>
       <c r="C58" t="n">
-        <v>7683.5</v>
+        <v>7689.25</v>
       </c>
       <c r="D58" t="n">
         <v>7576.75</v>
       </c>
       <c r="E58" t="n">
-        <v>7683.25</v>
+        <v>7685.5</v>
       </c>
       <c r="F58" t="n">
-        <v>23.75</v>
+        <v>26</v>
       </c>
       <c r="G58" s="5" t="n">
-        <v>0.0031</v>
+        <v>0.0034</v>
       </c>
       <c r="H58" t="n">
-        <v>106.75</v>
+        <v>112.5</v>
       </c>
       <c r="I58" t="n">
         <v>7442.5</v>
@@ -5401,25 +5401,25 @@
         </is>
       </c>
       <c r="I59" s="13" t="n">
-        <v>7470</v>
+        <v>7464.25</v>
       </c>
       <c r="J59" s="13" t="n">
-        <v>7603.06</v>
+        <v>7599.25</v>
       </c>
       <c r="K59" s="13" t="n">
-        <v>7629.88</v>
+        <v>7629.25</v>
       </c>
       <c r="L59" s="13" t="n">
-        <v>7656.69</v>
+        <v>7659.25</v>
       </c>
       <c r="M59" s="13" t="n">
-        <v>7736.62</v>
+        <v>7741.75</v>
       </c>
       <c r="N59" s="13" t="n">
-        <v>7816.56</v>
+        <v>7824.25</v>
       </c>
       <c r="O59" s="13" t="n">
-        <v>7790.25</v>
+        <v>7801.75</v>
       </c>
     </row>
   </sheetData>

--- a/three_gate/analysis/ES_weekly.xlsx
+++ b/three_gate/analysis/ES_weekly.xlsx
@@ -5320,22 +5320,22 @@
         <v>7609.25</v>
       </c>
       <c r="C58" t="n">
-        <v>7689.25</v>
+        <v>7652</v>
       </c>
       <c r="D58" t="n">
         <v>7576.75</v>
       </c>
       <c r="E58" t="n">
-        <v>7685.5</v>
+        <v>7620.25</v>
       </c>
       <c r="F58" t="n">
-        <v>26</v>
+        <v>-39.25</v>
       </c>
       <c r="G58" s="5" t="n">
-        <v>0.0034</v>
+        <v>-0.0051</v>
       </c>
       <c r="H58" t="n">
-        <v>112.5</v>
+        <v>75.25</v>
       </c>
       <c r="I58" t="n">
         <v>7442.5</v>
@@ -5366,12 +5366,12 @@
       </c>
       <c r="R58" s="6" t="inlineStr">
         <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S58" s="7" t="inlineStr">
-        <is>
-          <t>↑C</t>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="S58" s="10" t="inlineStr">
+        <is>
+          <t>↓</t>
         </is>
       </c>
       <c r="T58" s="8" t="n">
@@ -5388,11 +5388,7 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X58" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="X58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" s="12" t="inlineStr">
@@ -5401,25 +5397,25 @@
         </is>
       </c>
       <c r="I59" s="13" t="n">
-        <v>7464.25</v>
+        <v>7501.5</v>
       </c>
       <c r="J59" s="13" t="n">
-        <v>7599.25</v>
+        <v>7547.94</v>
       </c>
       <c r="K59" s="13" t="n">
-        <v>7629.25</v>
+        <v>7582.62</v>
       </c>
       <c r="L59" s="13" t="n">
-        <v>7659.25</v>
+        <v>7617.31</v>
       </c>
       <c r="M59" s="13" t="n">
-        <v>7741.75</v>
+        <v>7657.88</v>
       </c>
       <c r="N59" s="13" t="n">
-        <v>7824.25</v>
+        <v>7698.44</v>
       </c>
       <c r="O59" s="13" t="n">
-        <v>7801.75</v>
+        <v>7727.25</v>
       </c>
     </row>
   </sheetData>

--- a/three_gate/analysis/ES_weekly.xlsx
+++ b/three_gate/analysis/ES_weekly.xlsx
@@ -5320,22 +5320,22 @@
         <v>7609.25</v>
       </c>
       <c r="C58" t="n">
-        <v>7652</v>
+        <v>7667.75</v>
       </c>
       <c r="D58" t="n">
         <v>7576.75</v>
       </c>
       <c r="E58" t="n">
-        <v>7620.25</v>
+        <v>7661.75</v>
       </c>
       <c r="F58" t="n">
-        <v>-39.25</v>
+        <v>2.25</v>
       </c>
       <c r="G58" s="5" t="n">
-        <v>-0.0051</v>
+        <v>0.0003</v>
       </c>
       <c r="H58" t="n">
-        <v>75.25</v>
+        <v>91</v>
       </c>
       <c r="I58" t="n">
         <v>7442.5</v>
@@ -5366,12 +5366,12 @@
       </c>
       <c r="R58" s="6" t="inlineStr">
         <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="S58" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S58" s="7" t="inlineStr">
+        <is>
+          <t>↑C</t>
         </is>
       </c>
       <c r="T58" s="8" t="n">
@@ -5388,7 +5388,11 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X58" t="inlineStr"/>
+      <c r="X58" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" s="12" t="inlineStr">
@@ -5397,25 +5401,25 @@
         </is>
       </c>
       <c r="I59" s="13" t="n">
-        <v>7501.5</v>
+        <v>7485.75</v>
       </c>
       <c r="J59" s="13" t="n">
-        <v>7547.94</v>
+        <v>7590.5</v>
       </c>
       <c r="K59" s="13" t="n">
-        <v>7582.62</v>
+        <v>7616.25</v>
       </c>
       <c r="L59" s="13" t="n">
-        <v>7617.31</v>
+        <v>7642</v>
       </c>
       <c r="M59" s="13" t="n">
-        <v>7657.88</v>
+        <v>7707.25</v>
       </c>
       <c r="N59" s="13" t="n">
-        <v>7698.44</v>
+        <v>7772.5</v>
       </c>
       <c r="O59" s="13" t="n">
-        <v>7727.25</v>
+        <v>7758.75</v>
       </c>
     </row>
   </sheetData>

--- a/three_gate/analysis/ES_weekly.xlsx
+++ b/three_gate/analysis/ES_weekly.xlsx
@@ -5320,22 +5320,22 @@
         <v>7609.25</v>
       </c>
       <c r="C58" t="n">
-        <v>7667.75</v>
+        <v>7704.25</v>
       </c>
       <c r="D58" t="n">
-        <v>7576.75</v>
+        <v>7509.25</v>
       </c>
       <c r="E58" t="n">
-        <v>7661.75</v>
+        <v>7701.75</v>
       </c>
       <c r="F58" t="n">
-        <v>2.25</v>
+        <v>42.25</v>
       </c>
       <c r="G58" s="5" t="n">
-        <v>0.0003</v>
+        <v>0.0055</v>
       </c>
       <c r="H58" t="n">
-        <v>91</v>
+        <v>195</v>
       </c>
       <c r="I58" t="n">
         <v>7442.5</v>
@@ -5361,8 +5361,10 @@
       <c r="P58" s="6" t="n">
         <v/>
       </c>
-      <c r="Q58" s="6" t="n">
-        <v/>
+      <c r="Q58" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="R58" s="6" t="inlineStr">
         <is>
@@ -5371,11 +5373,13 @@
       </c>
       <c r="S58" s="7" t="inlineStr">
         <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T58" s="8" t="n">
-        <v/>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T58" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="U58" s="8" t="n">
         <v/>
@@ -5401,25 +5405,25 @@
         </is>
       </c>
       <c r="I59" s="13" t="n">
-        <v>7485.75</v>
+        <v>7314.25</v>
       </c>
       <c r="J59" s="13" t="n">
-        <v>7590.5</v>
+        <v>7554.25</v>
       </c>
       <c r="K59" s="13" t="n">
-        <v>7616.25</v>
+        <v>7604.25</v>
       </c>
       <c r="L59" s="13" t="n">
-        <v>7642</v>
+        <v>7654.25</v>
       </c>
       <c r="M59" s="13" t="n">
-        <v>7707.25</v>
+        <v>7799.25</v>
       </c>
       <c r="N59" s="13" t="n">
-        <v>7772.5</v>
+        <v>7944.25</v>
       </c>
       <c r="O59" s="13" t="n">
-        <v>7758.75</v>
+        <v>7899.25</v>
       </c>
     </row>
   </sheetData>

--- a/three_gate/analysis/ES_weekly.xlsx
+++ b/three_gate/analysis/ES_weekly.xlsx
@@ -5326,13 +5326,13 @@
         <v>7509.25</v>
       </c>
       <c r="E58" t="n">
-        <v>7701.75</v>
+        <v>7700.25</v>
       </c>
       <c r="F58" t="n">
-        <v>42.25</v>
+        <v>40.75</v>
       </c>
       <c r="G58" s="5" t="n">
-        <v>0.0055</v>
+        <v>0.0053</v>
       </c>
       <c r="H58" t="n">
         <v>195</v>
@@ -5408,19 +5408,19 @@
         <v>7314.25</v>
       </c>
       <c r="J59" s="13" t="n">
-        <v>7554.25</v>
+        <v>7552</v>
       </c>
       <c r="K59" s="13" t="n">
-        <v>7604.25</v>
+        <v>7602.75</v>
       </c>
       <c r="L59" s="13" t="n">
-        <v>7654.25</v>
+        <v>7653.5</v>
       </c>
       <c r="M59" s="13" t="n">
-        <v>7799.25</v>
+        <v>7797.75</v>
       </c>
       <c r="N59" s="13" t="n">
-        <v>7944.25</v>
+        <v>7942</v>
       </c>
       <c r="O59" s="13" t="n">
         <v>7899.25</v>

--- a/three_gate/analysis/ES_weekly.xlsx
+++ b/three_gate/analysis/ES_weekly.xlsx
@@ -46,7 +46,7 @@
       <sz val="10"/>
     </font>
   </fonts>
-  <fills count="7">
+  <fills count="6">
     <fill>
       <patternFill/>
     </fill>
@@ -73,11 +73,6 @@
         <fgColor rgb="00FFC7CE"/>
       </patternFill>
     </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00FFE699"/>
-      </patternFill>
-    </fill>
   </fills>
   <borders count="1">
     <border>
@@ -91,7 +86,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -120,8 +115,6 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="6" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -487,7 +480,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X59"/>
+  <dimension ref="A1:X58"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -666,25 +659,25 @@
         <v>133.5</v>
       </c>
       <c r="I2" t="n">
-        <v>6397.75</v>
+        <v>6414.25</v>
       </c>
       <c r="J2" t="n">
-        <v>6411.25</v>
+        <v>6417.44</v>
       </c>
       <c r="K2" t="n">
-        <v>6443.75</v>
+        <v>6447.88</v>
       </c>
       <c r="L2" t="n">
-        <v>6476.25</v>
+        <v>6478.31</v>
       </c>
       <c r="M2" t="n">
-        <v>6499.25</v>
+        <v>6495.12</v>
       </c>
       <c r="N2" t="n">
-        <v>6522.25</v>
+        <v>6511.94</v>
       </c>
       <c r="O2" t="n">
-        <v>6564.25</v>
+        <v>6556</v>
       </c>
       <c r="P2" s="6" t="inlineStr">
         <is>
@@ -706,8 +699,10 @@
           <t>↑C</t>
         </is>
       </c>
-      <c r="T2" s="8" t="n">
-        <v/>
+      <c r="T2" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="U2" s="8" t="n">
         <v/>
@@ -5326,13 +5321,13 @@
         <v>7509.25</v>
       </c>
       <c r="E58" t="n">
-        <v>7700.25</v>
+        <v>7700.5</v>
       </c>
       <c r="F58" t="n">
-        <v>40.75</v>
+        <v>41</v>
       </c>
       <c r="G58" s="5" t="n">
-        <v>0.0053</v>
+        <v>0.0054</v>
       </c>
       <c r="H58" t="n">
         <v>195</v>
@@ -5396,34 +5391,6 @@
         <is>
           <t>弱警訊</t>
         </is>
-      </c>
-    </row>
-    <row r="59">
-      <c r="A59" s="12" t="inlineStr">
-        <is>
-          <t>下週預測</t>
-        </is>
-      </c>
-      <c r="I59" s="13" t="n">
-        <v>7314.25</v>
-      </c>
-      <c r="J59" s="13" t="n">
-        <v>7552</v>
-      </c>
-      <c r="K59" s="13" t="n">
-        <v>7602.75</v>
-      </c>
-      <c r="L59" s="13" t="n">
-        <v>7653.5</v>
-      </c>
-      <c r="M59" s="13" t="n">
-        <v>7797.75</v>
-      </c>
-      <c r="N59" s="13" t="n">
-        <v>7942</v>
-      </c>
-      <c r="O59" s="13" t="n">
-        <v>7899.25</v>
       </c>
     </row>
   </sheetData>

--- a/three_gate/analysis/ES_weekly.xlsx
+++ b/three_gate/analysis/ES_weekly.xlsx
@@ -480,7 +480,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X58"/>
+  <dimension ref="A1:X57"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -634,75 +634,67 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2025-08-18</t>
+          <t>2025-08-25</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>6467</v>
+        <v>6493</v>
       </c>
       <c r="C2" t="n">
-        <v>6496.25</v>
+        <v>6523</v>
       </c>
       <c r="D2" t="n">
-        <v>6362.75</v>
+        <v>6430.75</v>
       </c>
       <c r="E2" t="n">
-        <v>6483.25</v>
+        <v>6472.75</v>
       </c>
       <c r="F2" t="n">
-        <v>11.75</v>
+        <v>-10.5</v>
       </c>
       <c r="G2" s="5" t="n">
-        <v>0.0018</v>
+        <v>-0.0016</v>
       </c>
       <c r="H2" t="n">
-        <v>133.5</v>
+        <v>92.25</v>
       </c>
       <c r="I2" t="n">
-        <v>6414.25</v>
+        <v>6229.25</v>
       </c>
       <c r="J2" t="n">
-        <v>6417.44</v>
+        <v>6376.62</v>
       </c>
       <c r="K2" t="n">
-        <v>6447.88</v>
+        <v>6416.5</v>
       </c>
       <c r="L2" t="n">
-        <v>6478.31</v>
+        <v>6456.38</v>
       </c>
       <c r="M2" t="n">
-        <v>6495.12</v>
+        <v>6550</v>
       </c>
       <c r="N2" t="n">
-        <v>6511.94</v>
+        <v>6643.62</v>
       </c>
       <c r="O2" t="n">
-        <v>6556</v>
-      </c>
-      <c r="P2" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="Q2" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="R2" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+        <v>6629.75</v>
+      </c>
+      <c r="P2" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q2" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R2" s="6" t="n">
+        <v/>
       </c>
       <c r="S2" s="7" t="inlineStr">
         <is>
           <t>↑C</t>
         </is>
       </c>
-      <c r="T2" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="T2" s="8" t="n">
+        <v/>
       </c>
       <c r="U2" s="8" t="n">
         <v/>
@@ -717,74 +709,80 @@
       </c>
       <c r="X2" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2025-08-25</t>
+          <t>2025-09-01</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>6493</v>
+        <v>6478.75</v>
       </c>
       <c r="C3" t="n">
-        <v>6523</v>
+        <v>6541.75</v>
       </c>
       <c r="D3" t="n">
-        <v>6430.75</v>
+        <v>6371.75</v>
       </c>
       <c r="E3" t="n">
-        <v>6472.75</v>
+        <v>6489.75</v>
       </c>
       <c r="F3" t="n">
-        <v>-10.5</v>
+        <v>17</v>
       </c>
       <c r="G3" s="5" t="n">
-        <v>-0.0016</v>
+        <v>0.0026</v>
       </c>
       <c r="H3" t="n">
-        <v>92.25</v>
+        <v>170</v>
       </c>
       <c r="I3" t="n">
-        <v>6229.25</v>
+        <v>6338.5</v>
       </c>
       <c r="J3" t="n">
-        <v>6376.62</v>
+        <v>6378.44</v>
       </c>
       <c r="K3" t="n">
-        <v>6416.5</v>
+        <v>6426.62</v>
       </c>
       <c r="L3" t="n">
-        <v>6456.38</v>
+        <v>6474.81</v>
       </c>
       <c r="M3" t="n">
-        <v>6550</v>
+        <v>6518.88</v>
       </c>
       <c r="N3" t="n">
-        <v>6643.62</v>
+        <v>6562.94</v>
       </c>
       <c r="O3" t="n">
-        <v>6629.75</v>
+        <v>6615.25</v>
       </c>
       <c r="P3" s="6" t="n">
         <v/>
       </c>
-      <c r="Q3" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R3" s="6" t="n">
-        <v/>
+      <c r="Q3" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="R3" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S3" s="7" t="inlineStr">
         <is>
           <t>↑C</t>
         </is>
       </c>
-      <c r="T3" s="8" t="n">
-        <v/>
+      <c r="T3" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="U3" s="8" t="n">
         <v/>
@@ -806,72 +804,68 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2025-09-01</t>
+          <t>2025-09-08</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>6478.75</v>
+        <v>6483.75</v>
       </c>
       <c r="C4" t="n">
-        <v>6541.75</v>
+        <v>6606</v>
       </c>
       <c r="D4" t="n">
-        <v>6371.75</v>
+        <v>6480.25</v>
       </c>
       <c r="E4" t="n">
-        <v>6489.75</v>
+        <v>6588.25</v>
       </c>
       <c r="F4" t="n">
-        <v>17</v>
+        <v>98.5</v>
       </c>
       <c r="G4" s="5" t="n">
-        <v>0.0026</v>
+        <v>0.0152</v>
       </c>
       <c r="H4" t="n">
-        <v>170</v>
+        <v>125.75</v>
       </c>
       <c r="I4" t="n">
-        <v>6338.5</v>
+        <v>6201.75</v>
       </c>
       <c r="J4" t="n">
-        <v>6378.44</v>
+        <v>6336.25</v>
       </c>
       <c r="K4" t="n">
-        <v>6426.62</v>
+        <v>6404.75</v>
       </c>
       <c r="L4" t="n">
-        <v>6474.81</v>
+        <v>6473.25</v>
       </c>
       <c r="M4" t="n">
-        <v>6518.88</v>
+        <v>6574.75</v>
       </c>
       <c r="N4" t="n">
-        <v>6562.94</v>
+        <v>6676.25</v>
       </c>
       <c r="O4" t="n">
-        <v>6615.25</v>
+        <v>6711.75</v>
       </c>
       <c r="P4" s="6" t="n">
         <v/>
       </c>
-      <c r="Q4" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="R4" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="Q4" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R4" s="6" t="n">
+        <v/>
       </c>
       <c r="S4" s="7" t="inlineStr">
         <is>
-          <t>↑C</t>
+          <t>↑</t>
         </is>
       </c>
       <c r="T4" s="8" t="inlineStr">
         <is>
-          <t>✓</t>
+          <t>△C</t>
         </is>
       </c>
       <c r="U4" s="8" t="n">
@@ -885,59 +879,55 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X4" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="X4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2025-09-08</t>
+          <t>2025-09-15</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>6483.75</v>
+        <v>6588.25</v>
       </c>
       <c r="C5" t="n">
-        <v>6606</v>
+        <v>6662</v>
       </c>
       <c r="D5" t="n">
-        <v>6480.25</v>
+        <v>6554</v>
       </c>
       <c r="E5" t="n">
-        <v>6588.25</v>
+        <v>6658.77</v>
       </c>
       <c r="F5" t="n">
-        <v>98.5</v>
+        <v>70.52</v>
       </c>
       <c r="G5" s="5" t="n">
-        <v>0.0152</v>
+        <v>0.0107</v>
       </c>
       <c r="H5" t="n">
-        <v>125.75</v>
+        <v>108</v>
       </c>
       <c r="I5" t="n">
-        <v>6201.75</v>
+        <v>6354.5</v>
       </c>
       <c r="J5" t="n">
-        <v>6336.25</v>
+        <v>6485.06</v>
       </c>
       <c r="K5" t="n">
-        <v>6404.75</v>
+        <v>6525.38</v>
       </c>
       <c r="L5" t="n">
-        <v>6473.25</v>
+        <v>6565.69</v>
       </c>
       <c r="M5" t="n">
-        <v>6574.75</v>
+        <v>6651.12</v>
       </c>
       <c r="N5" t="n">
-        <v>6676.25</v>
+        <v>6736.56</v>
       </c>
       <c r="O5" t="n">
-        <v>6711.75</v>
+        <v>6731.75</v>
       </c>
       <c r="P5" s="6" t="n">
         <v/>
@@ -974,50 +964,50 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2025-09-15</t>
+          <t>2025-09-22</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>6588.25</v>
+        <v>6716</v>
       </c>
       <c r="C6" t="n">
-        <v>6662</v>
+        <v>6756.75</v>
       </c>
       <c r="D6" t="n">
-        <v>6554</v>
+        <v>6624.25</v>
       </c>
       <c r="E6" t="n">
-        <v>6658.77</v>
+        <v>6696.5</v>
       </c>
       <c r="F6" t="n">
-        <v>70.52</v>
+        <v>37.73</v>
       </c>
       <c r="G6" s="5" t="n">
-        <v>0.0107</v>
+        <v>0.0057</v>
       </c>
       <c r="H6" t="n">
-        <v>108</v>
+        <v>132.5</v>
       </c>
       <c r="I6" t="n">
-        <v>6354.5</v>
+        <v>6446</v>
       </c>
       <c r="J6" t="n">
-        <v>6485.06</v>
+        <v>6576.16</v>
       </c>
       <c r="K6" t="n">
-        <v>6525.38</v>
+        <v>6604.77</v>
       </c>
       <c r="L6" t="n">
-        <v>6565.69</v>
+        <v>6633.39</v>
       </c>
       <c r="M6" t="n">
-        <v>6651.12</v>
+        <v>6712.77</v>
       </c>
       <c r="N6" t="n">
-        <v>6736.56</v>
+        <v>6792.16</v>
       </c>
       <c r="O6" t="n">
-        <v>6731.75</v>
+        <v>6770</v>
       </c>
       <c r="P6" s="6" t="n">
         <v/>
@@ -1054,50 +1044,50 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2025-09-22</t>
+          <t>2025-09-29</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>6716</v>
+        <v>6697</v>
       </c>
       <c r="C7" t="n">
-        <v>6756.75</v>
+        <v>6800</v>
       </c>
       <c r="D7" t="n">
-        <v>6624.25</v>
+        <v>6680</v>
       </c>
       <c r="E7" t="n">
-        <v>6696.5</v>
+        <v>6764</v>
       </c>
       <c r="F7" t="n">
-        <v>37.73</v>
+        <v>67.5</v>
       </c>
       <c r="G7" s="5" t="n">
-        <v>0.0057</v>
+        <v>0.0101</v>
       </c>
       <c r="H7" t="n">
-        <v>132.5</v>
+        <v>120</v>
       </c>
       <c r="I7" t="n">
-        <v>6446</v>
+        <v>6491.75</v>
       </c>
       <c r="J7" t="n">
-        <v>6576.16</v>
+        <v>6567</v>
       </c>
       <c r="K7" t="n">
-        <v>6604.77</v>
+        <v>6630.25</v>
       </c>
       <c r="L7" t="n">
-        <v>6633.39</v>
+        <v>6693.5</v>
       </c>
       <c r="M7" t="n">
-        <v>6712.77</v>
+        <v>6762.75</v>
       </c>
       <c r="N7" t="n">
-        <v>6792.16</v>
+        <v>6832</v>
       </c>
       <c r="O7" t="n">
-        <v>6770</v>
+        <v>6889.25</v>
       </c>
       <c r="P7" s="6" t="n">
         <v/>
@@ -1134,154 +1124,158 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2025-09-29</t>
+          <t>2025-10-06</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>6697</v>
+        <v>6768</v>
       </c>
       <c r="C8" t="n">
-        <v>6800</v>
+        <v>6812.25</v>
       </c>
       <c r="D8" t="n">
-        <v>6680</v>
+        <v>6540.25</v>
       </c>
       <c r="E8" t="n">
-        <v>6764</v>
+        <v>6595.25</v>
       </c>
       <c r="F8" t="n">
-        <v>67.5</v>
+        <v>-168.75</v>
       </c>
       <c r="G8" s="5" t="n">
-        <v>0.0101</v>
+        <v>-0.0249</v>
       </c>
       <c r="H8" t="n">
-        <v>120</v>
+        <v>272</v>
       </c>
       <c r="I8" t="n">
-        <v>6491.75</v>
+        <v>6560</v>
       </c>
       <c r="J8" t="n">
-        <v>6567</v>
+        <v>6656</v>
       </c>
       <c r="K8" t="n">
-        <v>6630.25</v>
+        <v>6704</v>
       </c>
       <c r="L8" t="n">
-        <v>6693.5</v>
+        <v>6752</v>
       </c>
       <c r="M8" t="n">
-        <v>6762.75</v>
+        <v>6824</v>
       </c>
       <c r="N8" t="n">
-        <v>6832</v>
+        <v>6896</v>
       </c>
       <c r="O8" t="n">
-        <v>6889.25</v>
-      </c>
-      <c r="P8" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q8" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R8" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S8" s="7" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T8" s="8" t="inlineStr">
+        <v>6920</v>
+      </c>
+      <c r="P8" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
+      <c r="Q8" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="R8" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S8" s="10" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T8" s="8" t="n">
+        <v/>
+      </c>
       <c r="U8" s="8" t="n">
         <v/>
       </c>
       <c r="V8" s="8" t="n">
         <v/>
       </c>
-      <c r="W8" s="9" t="inlineStr">
-        <is>
-          <t>多方</t>
-        </is>
-      </c>
-      <c r="X8" t="inlineStr"/>
+      <c r="W8" s="11" t="inlineStr">
+        <is>
+          <t>空方</t>
+        </is>
+      </c>
+      <c r="X8" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2025-10-06</t>
+          <t>2025-10-13</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>6768</v>
+        <v>6632</v>
       </c>
       <c r="C9" t="n">
-        <v>6812.25</v>
+        <v>6766.75</v>
       </c>
       <c r="D9" t="n">
-        <v>6540.25</v>
+        <v>6571.25</v>
       </c>
       <c r="E9" t="n">
-        <v>6595.25</v>
+        <v>6702.5</v>
       </c>
       <c r="F9" t="n">
-        <v>-168.75</v>
+        <v>107.25</v>
       </c>
       <c r="G9" s="5" t="n">
-        <v>-0.0249</v>
+        <v>0.0163</v>
       </c>
       <c r="H9" t="n">
-        <v>272</v>
+        <v>195.5</v>
       </c>
       <c r="I9" t="n">
-        <v>6560</v>
+        <v>6268.25</v>
       </c>
       <c r="J9" t="n">
-        <v>6656</v>
+        <v>6282.75</v>
       </c>
       <c r="K9" t="n">
-        <v>6704</v>
+        <v>6459.25</v>
       </c>
       <c r="L9" t="n">
-        <v>6752</v>
+        <v>6635.75</v>
       </c>
       <c r="M9" t="n">
-        <v>6824</v>
+        <v>6731.25</v>
       </c>
       <c r="N9" t="n">
-        <v>6896</v>
+        <v>6826.75</v>
       </c>
       <c r="O9" t="n">
-        <v>6920</v>
-      </c>
-      <c r="P9" s="6" t="inlineStr">
+        <v>7084.25</v>
+      </c>
+      <c r="P9" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q9" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R9" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S9" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T9" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="Q9" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="R9" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S9" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T9" s="8" t="n">
-        <v/>
-      </c>
       <c r="U9" s="8" t="n">
         <v/>
       </c>
@@ -1295,57 +1289,57 @@
       </c>
       <c r="X9" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2025-10-13</t>
+          <t>2025-10-20</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>6632</v>
+        <v>6721</v>
       </c>
       <c r="C10" t="n">
-        <v>6766.75</v>
+        <v>6841.25</v>
       </c>
       <c r="D10" t="n">
-        <v>6571.25</v>
+        <v>6690.75</v>
       </c>
       <c r="E10" t="n">
-        <v>6702.5</v>
+        <v>6827</v>
       </c>
       <c r="F10" t="n">
-        <v>107.25</v>
+        <v>124.5</v>
       </c>
       <c r="G10" s="5" t="n">
-        <v>0.0163</v>
+        <v>0.0186</v>
       </c>
       <c r="H10" t="n">
-        <v>195.5</v>
+        <v>150.5</v>
       </c>
       <c r="I10" t="n">
-        <v>6268.25</v>
+        <v>6375.75</v>
       </c>
       <c r="J10" t="n">
-        <v>6282.75</v>
+        <v>6523.75</v>
       </c>
       <c r="K10" t="n">
-        <v>6459.25</v>
+        <v>6604.75</v>
       </c>
       <c r="L10" t="n">
-        <v>6635.75</v>
+        <v>6685.75</v>
       </c>
       <c r="M10" t="n">
-        <v>6731.25</v>
+        <v>6800.25</v>
       </c>
       <c r="N10" t="n">
-        <v>6826.75</v>
+        <v>6914.75</v>
       </c>
       <c r="O10" t="n">
-        <v>7084.25</v>
+        <v>6962.25</v>
       </c>
       <c r="P10" s="6" t="n">
         <v/>
@@ -1379,57 +1373,57 @@
       </c>
       <c r="X10" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2025-10-20</t>
+          <t>2025-10-27</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>6721</v>
+        <v>6881</v>
       </c>
       <c r="C11" t="n">
-        <v>6841.25</v>
+        <v>6953.75</v>
       </c>
       <c r="D11" t="n">
-        <v>6690.75</v>
+        <v>6843.5</v>
       </c>
       <c r="E11" t="n">
-        <v>6827</v>
+        <v>6874</v>
       </c>
       <c r="F11" t="n">
-        <v>124.5</v>
+        <v>47</v>
       </c>
       <c r="G11" s="5" t="n">
-        <v>0.0186</v>
+        <v>0.0069</v>
       </c>
       <c r="H11" t="n">
-        <v>150.5</v>
+        <v>110.25</v>
       </c>
       <c r="I11" t="n">
-        <v>6375.75</v>
+        <v>6540.25</v>
       </c>
       <c r="J11" t="n">
-        <v>6523.75</v>
+        <v>6707</v>
       </c>
       <c r="K11" t="n">
-        <v>6604.75</v>
+        <v>6751.75</v>
       </c>
       <c r="L11" t="n">
-        <v>6685.75</v>
+        <v>6796.5</v>
       </c>
       <c r="M11" t="n">
-        <v>6800.25</v>
+        <v>6902.25</v>
       </c>
       <c r="N11" t="n">
-        <v>6914.75</v>
+        <v>7008</v>
       </c>
       <c r="O11" t="n">
-        <v>6962.25</v>
+        <v>6991.75</v>
       </c>
       <c r="P11" s="6" t="n">
         <v/>
@@ -1470,70 +1464,74 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2025-10-27</t>
+          <t>2025-11-03</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>6881</v>
+        <v>6878</v>
       </c>
       <c r="C12" t="n">
-        <v>6953.75</v>
+        <v>6909.5</v>
       </c>
       <c r="D12" t="n">
-        <v>6843.5</v>
+        <v>6655.5</v>
       </c>
       <c r="E12" t="n">
-        <v>6874</v>
+        <v>6753.75</v>
       </c>
       <c r="F12" t="n">
-        <v>47</v>
+        <v>-120.25</v>
       </c>
       <c r="G12" s="5" t="n">
-        <v>0.0069</v>
+        <v>-0.0175</v>
       </c>
       <c r="H12" t="n">
-        <v>110.25</v>
+        <v>254</v>
       </c>
       <c r="I12" t="n">
-        <v>6540.25</v>
+        <v>6733.25</v>
       </c>
       <c r="J12" t="n">
-        <v>6707</v>
+        <v>6751.44</v>
       </c>
       <c r="K12" t="n">
-        <v>6751.75</v>
+        <v>6818.88</v>
       </c>
       <c r="L12" t="n">
-        <v>6796.5</v>
+        <v>6886.31</v>
       </c>
       <c r="M12" t="n">
-        <v>6902.25</v>
+        <v>6929.12</v>
       </c>
       <c r="N12" t="n">
-        <v>7008</v>
+        <v>6971.94</v>
       </c>
       <c r="O12" t="n">
-        <v>6991.75</v>
-      </c>
-      <c r="P12" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q12" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R12" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S12" s="7" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T12" s="8" t="inlineStr">
+        <v>7064</v>
+      </c>
+      <c r="P12" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="Q12" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
+      <c r="R12" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S12" s="10" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T12" s="8" t="n">
+        <v/>
+      </c>
       <c r="U12" s="8" t="n">
         <v/>
       </c>
@@ -1545,83 +1543,75 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X12" t="inlineStr">
-        <is>
-          <t>強警訊</t>
-        </is>
-      </c>
+      <c r="X12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2025-11-03</t>
+          <t>2025-11-10</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>6878</v>
+        <v>6788</v>
       </c>
       <c r="C13" t="n">
-        <v>6909.5</v>
+        <v>6900.5</v>
       </c>
       <c r="D13" t="n">
-        <v>6655.5</v>
+        <v>6670.5</v>
       </c>
       <c r="E13" t="n">
-        <v>6753.75</v>
+        <v>6755.25</v>
       </c>
       <c r="F13" t="n">
-        <v>-120.25</v>
+        <v>1.5</v>
       </c>
       <c r="G13" s="5" t="n">
-        <v>-0.0175</v>
+        <v>0.0002</v>
       </c>
       <c r="H13" t="n">
-        <v>254</v>
+        <v>230</v>
       </c>
       <c r="I13" t="n">
-        <v>6733.25</v>
+        <v>6401.5</v>
       </c>
       <c r="J13" t="n">
-        <v>6751.44</v>
+        <v>6485.38</v>
       </c>
       <c r="K13" t="n">
-        <v>6818.88</v>
+        <v>6626.75</v>
       </c>
       <c r="L13" t="n">
-        <v>6886.31</v>
+        <v>6768.12</v>
       </c>
       <c r="M13" t="n">
-        <v>6929.12</v>
+        <v>6880.75</v>
       </c>
       <c r="N13" t="n">
-        <v>6971.94</v>
+        <v>6993.38</v>
       </c>
       <c r="O13" t="n">
-        <v>7064</v>
-      </c>
-      <c r="P13" s="6" t="inlineStr">
+        <v>7163.5</v>
+      </c>
+      <c r="P13" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q13" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R13" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S13" s="10" t="inlineStr">
+        <is>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T13" s="8" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="Q13" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="R13" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S13" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T13" s="8" t="n">
-        <v/>
-      </c>
       <c r="U13" s="8" t="n">
         <v/>
       </c>
@@ -1633,55 +1623,59 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X13" t="inlineStr"/>
+      <c r="X13" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2025-11-10</t>
+          <t>2025-11-17</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>6788</v>
+        <v>6764.75</v>
       </c>
       <c r="C14" t="n">
-        <v>6900.5</v>
+        <v>6801.5</v>
       </c>
       <c r="D14" t="n">
-        <v>6670.5</v>
+        <v>6525</v>
       </c>
       <c r="E14" t="n">
-        <v>6755.25</v>
+        <v>6620.25</v>
       </c>
       <c r="F14" t="n">
-        <v>1.5</v>
+        <v>-135</v>
       </c>
       <c r="G14" s="5" t="n">
-        <v>0.0002</v>
+        <v>-0.02</v>
       </c>
       <c r="H14" t="n">
-        <v>230</v>
+        <v>276.5</v>
       </c>
       <c r="I14" t="n">
-        <v>6401.5</v>
+        <v>6440.5</v>
       </c>
       <c r="J14" t="n">
-        <v>6485.38</v>
+        <v>6510.12</v>
       </c>
       <c r="K14" t="n">
-        <v>6626.75</v>
+        <v>6640.25</v>
       </c>
       <c r="L14" t="n">
-        <v>6768.12</v>
+        <v>6770.38</v>
       </c>
       <c r="M14" t="n">
-        <v>6880.75</v>
+        <v>6870.25</v>
       </c>
       <c r="N14" t="n">
-        <v>6993.38</v>
+        <v>6970.12</v>
       </c>
       <c r="O14" t="n">
-        <v>7163.5</v>
+        <v>7130.5</v>
       </c>
       <c r="P14" s="6" t="n">
         <v/>
@@ -1689,18 +1683,18 @@
       <c r="Q14" s="6" t="n">
         <v/>
       </c>
-      <c r="R14" s="6" t="n">
-        <v/>
+      <c r="R14" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="S14" s="10" t="inlineStr">
         <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T14" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T14" s="8" t="n">
+        <v/>
       </c>
       <c r="U14" s="8" t="n">
         <v/>
@@ -1713,59 +1707,55 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X14" t="inlineStr">
-        <is>
-          <t>中警訊</t>
-        </is>
-      </c>
+      <c r="X14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2025-11-17</t>
+          <t>2025-11-24</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>6764.75</v>
+        <v>6654.75</v>
       </c>
       <c r="C15" t="n">
-        <v>6801.5</v>
+        <v>6863.75</v>
       </c>
       <c r="D15" t="n">
-        <v>6525</v>
+        <v>6625</v>
       </c>
       <c r="E15" t="n">
-        <v>6620.25</v>
+        <v>6859.5</v>
       </c>
       <c r="F15" t="n">
-        <v>-135</v>
+        <v>239.25</v>
       </c>
       <c r="G15" s="5" t="n">
-        <v>-0.02</v>
+        <v>0.0361</v>
       </c>
       <c r="H15" t="n">
-        <v>276.5</v>
+        <v>238.75</v>
       </c>
       <c r="I15" t="n">
-        <v>6440.5</v>
+        <v>6248.5</v>
       </c>
       <c r="J15" t="n">
-        <v>6510.12</v>
+        <v>6322.25</v>
       </c>
       <c r="K15" t="n">
-        <v>6640.25</v>
+        <v>6482</v>
       </c>
       <c r="L15" t="n">
-        <v>6770.38</v>
+        <v>6641.75</v>
       </c>
       <c r="M15" t="n">
-        <v>6870.25</v>
+        <v>6758.5</v>
       </c>
       <c r="N15" t="n">
-        <v>6970.12</v>
+        <v>6875.25</v>
       </c>
       <c r="O15" t="n">
-        <v>7130.5</v>
+        <v>7078</v>
       </c>
       <c r="P15" s="6" t="n">
         <v/>
@@ -1773,22 +1763,24 @@
       <c r="Q15" s="6" t="n">
         <v/>
       </c>
-      <c r="R15" s="6" t="inlineStr">
+      <c r="R15" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S15" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T15" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U15" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="S15" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T15" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U15" s="8" t="n">
-        <v/>
-      </c>
       <c r="V15" s="8" t="n">
         <v/>
       </c>
@@ -1797,55 +1789,59 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X15" t="inlineStr"/>
+      <c r="X15" t="inlineStr">
+        <is>
+          <t>強警訊</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2025-11-24</t>
+          <t>2025-12-01</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>6654.75</v>
+        <v>6854.75</v>
       </c>
       <c r="C16" t="n">
-        <v>6863.75</v>
+        <v>6905</v>
       </c>
       <c r="D16" t="n">
-        <v>6625</v>
+        <v>6802</v>
       </c>
       <c r="E16" t="n">
-        <v>6859.5</v>
+        <v>6878.25</v>
       </c>
       <c r="F16" t="n">
-        <v>239.25</v>
+        <v>18.75</v>
       </c>
       <c r="G16" s="5" t="n">
-        <v>0.0361</v>
+        <v>0.0027</v>
       </c>
       <c r="H16" t="n">
-        <v>238.75</v>
+        <v>103</v>
       </c>
       <c r="I16" t="n">
-        <v>6248.5</v>
+        <v>6386.25</v>
       </c>
       <c r="J16" t="n">
-        <v>6322.25</v>
+        <v>6678.31</v>
       </c>
       <c r="K16" t="n">
-        <v>6482</v>
+        <v>6740.12</v>
       </c>
       <c r="L16" t="n">
-        <v>6641.75</v>
+        <v>6801.94</v>
       </c>
       <c r="M16" t="n">
-        <v>6758.5</v>
+        <v>6978.88</v>
       </c>
       <c r="N16" t="n">
-        <v>6875.25</v>
+        <v>7155.81</v>
       </c>
       <c r="O16" t="n">
-        <v>7078</v>
+        <v>7102.5</v>
       </c>
       <c r="P16" s="6" t="n">
         <v/>
@@ -1858,18 +1854,14 @@
       </c>
       <c r="S16" s="7" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T16" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U16" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T16" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U16" s="8" t="n">
+        <v/>
       </c>
       <c r="V16" s="8" t="n">
         <v/>
@@ -1888,50 +1880,50 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2025-12-01</t>
+          <t>2025-12-08</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>6854.75</v>
+        <v>6883</v>
       </c>
       <c r="C17" t="n">
-        <v>6905</v>
+        <v>6928.75</v>
       </c>
       <c r="D17" t="n">
-        <v>6802</v>
+        <v>6805</v>
       </c>
       <c r="E17" t="n">
-        <v>6878.25</v>
+        <v>6830.75</v>
       </c>
       <c r="F17" t="n">
-        <v>18.75</v>
+        <v>-47.5</v>
       </c>
       <c r="G17" s="5" t="n">
-        <v>0.0027</v>
+        <v>-0.0069</v>
       </c>
       <c r="H17" t="n">
-        <v>103</v>
+        <v>123.75</v>
       </c>
       <c r="I17" t="n">
-        <v>6386.25</v>
+        <v>6699</v>
       </c>
       <c r="J17" t="n">
-        <v>6678.31</v>
+        <v>6787.62</v>
       </c>
       <c r="K17" t="n">
-        <v>6740.12</v>
+        <v>6826.75</v>
       </c>
       <c r="L17" t="n">
-        <v>6801.94</v>
+        <v>6865.88</v>
       </c>
       <c r="M17" t="n">
-        <v>6978.88</v>
+        <v>6929.75</v>
       </c>
       <c r="N17" t="n">
-        <v>7155.81</v>
+        <v>6993.62</v>
       </c>
       <c r="O17" t="n">
-        <v>7102.5</v>
+        <v>7008</v>
       </c>
       <c r="P17" s="6" t="n">
         <v/>
@@ -1939,12 +1931,14 @@
       <c r="Q17" s="6" t="n">
         <v/>
       </c>
-      <c r="R17" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S17" s="7" t="inlineStr">
-        <is>
-          <t>↑C</t>
+      <c r="R17" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="S17" s="10" t="inlineStr">
+        <is>
+          <t>↓</t>
         </is>
       </c>
       <c r="T17" s="8" t="n">
@@ -1963,57 +1957,57 @@
       </c>
       <c r="X17" t="inlineStr">
         <is>
-          <t>強警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2025-12-08</t>
+          <t>2025-12-15</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>6883</v>
+        <v>6831</v>
       </c>
       <c r="C18" t="n">
-        <v>6928.75</v>
+        <v>6872.5</v>
       </c>
       <c r="D18" t="n">
-        <v>6805</v>
+        <v>6720.25</v>
       </c>
       <c r="E18" t="n">
-        <v>6830.75</v>
+        <v>6796.54</v>
       </c>
       <c r="F18" t="n">
-        <v>-47.5</v>
+        <v>-34.21</v>
       </c>
       <c r="G18" s="5" t="n">
-        <v>-0.0069</v>
+        <v>-0.005</v>
       </c>
       <c r="H18" t="n">
-        <v>123.75</v>
+        <v>152.25</v>
       </c>
       <c r="I18" t="n">
-        <v>6699</v>
+        <v>6681.25</v>
       </c>
       <c r="J18" t="n">
-        <v>6787.62</v>
+        <v>6688.94</v>
       </c>
       <c r="K18" t="n">
-        <v>6826.75</v>
+        <v>6768.88</v>
       </c>
       <c r="L18" t="n">
-        <v>6865.88</v>
+        <v>6848.81</v>
       </c>
       <c r="M18" t="n">
-        <v>6929.75</v>
+        <v>6892.62</v>
       </c>
       <c r="N18" t="n">
-        <v>6993.62</v>
+        <v>6936.44</v>
       </c>
       <c r="O18" t="n">
-        <v>7008</v>
+        <v>7052.5</v>
       </c>
       <c r="P18" s="6" t="n">
         <v/>
@@ -2045,59 +2039,55 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X18" t="inlineStr">
-        <is>
-          <t>中警訊</t>
-        </is>
-      </c>
+      <c r="X18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2025-12-15</t>
+          <t>2025-12-22</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>6831</v>
+        <v>6906.25</v>
       </c>
       <c r="C19" t="n">
-        <v>6872.5</v>
+        <v>6994</v>
       </c>
       <c r="D19" t="n">
-        <v>6720.25</v>
+        <v>6900.5</v>
       </c>
       <c r="E19" t="n">
-        <v>6796.54</v>
+        <v>6979.25</v>
       </c>
       <c r="F19" t="n">
-        <v>-34.21</v>
+        <v>182.71</v>
       </c>
       <c r="G19" s="5" t="n">
-        <v>-0.005</v>
+        <v>0.0269</v>
       </c>
       <c r="H19" t="n">
-        <v>152.25</v>
+        <v>93.5</v>
       </c>
       <c r="I19" t="n">
-        <v>6681.25</v>
+        <v>6568</v>
       </c>
       <c r="J19" t="n">
-        <v>6688.94</v>
+        <v>6644.37</v>
       </c>
       <c r="K19" t="n">
-        <v>6768.88</v>
+        <v>6720.42</v>
       </c>
       <c r="L19" t="n">
-        <v>6848.81</v>
+        <v>6796.46</v>
       </c>
       <c r="M19" t="n">
-        <v>6892.62</v>
+        <v>6872.67</v>
       </c>
       <c r="N19" t="n">
-        <v>6936.44</v>
+        <v>6948.87</v>
       </c>
       <c r="O19" t="n">
-        <v>7052.5</v>
+        <v>7024.75</v>
       </c>
       <c r="P19" s="6" t="n">
         <v/>
@@ -2105,28 +2095,30 @@
       <c r="Q19" s="6" t="n">
         <v/>
       </c>
-      <c r="R19" s="6" t="inlineStr">
+      <c r="R19" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S19" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T19" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U19" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="S19" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T19" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U19" s="8" t="n">
-        <v/>
-      </c>
       <c r="V19" s="8" t="n">
         <v/>
       </c>
-      <c r="W19" s="11" t="inlineStr">
-        <is>
-          <t>空方</t>
+      <c r="W19" s="9" t="inlineStr">
+        <is>
+          <t>多方</t>
         </is>
       </c>
       <c r="X19" t="inlineStr"/>
@@ -2134,81 +2126,81 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2025-12-22</t>
+          <t>2025-12-29</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>6906.25</v>
+        <v>6980.5</v>
       </c>
       <c r="C20" t="n">
-        <v>6994</v>
+        <v>6984.75</v>
       </c>
       <c r="D20" t="n">
+        <v>6866.75</v>
+      </c>
+      <c r="E20" t="n">
         <v>6900.5</v>
       </c>
-      <c r="E20" t="n">
-        <v>6979.25</v>
-      </c>
       <c r="F20" t="n">
-        <v>182.71</v>
+        <v>-78.75</v>
       </c>
       <c r="G20" s="5" t="n">
-        <v>0.0269</v>
+        <v>-0.0113</v>
       </c>
       <c r="H20" t="n">
-        <v>93.5</v>
+        <v>118</v>
       </c>
       <c r="I20" t="n">
-        <v>6568</v>
+        <v>6807</v>
       </c>
       <c r="J20" t="n">
-        <v>6644.37</v>
+        <v>6901.75</v>
       </c>
       <c r="K20" t="n">
-        <v>6720.42</v>
+        <v>6932.5</v>
       </c>
       <c r="L20" t="n">
-        <v>6796.46</v>
+        <v>6963.25</v>
       </c>
       <c r="M20" t="n">
-        <v>6872.67</v>
+        <v>7026</v>
       </c>
       <c r="N20" t="n">
-        <v>6948.87</v>
+        <v>7088.75</v>
       </c>
       <c r="O20" t="n">
-        <v>7024.75</v>
+        <v>7087.5</v>
       </c>
       <c r="P20" s="6" t="n">
         <v/>
       </c>
-      <c r="Q20" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R20" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S20" s="7" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T20" s="8" t="inlineStr">
+      <c r="Q20" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="R20" s="6" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="U20" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+      <c r="S20" s="10" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T20" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U20" s="8" t="n">
+        <v/>
       </c>
       <c r="V20" s="8" t="n">
         <v/>
       </c>
-      <c r="W20" s="9" t="inlineStr">
-        <is>
-          <t>多方</t>
+      <c r="W20" s="11" t="inlineStr">
+        <is>
+          <t>空方</t>
         </is>
       </c>
       <c r="X20" t="inlineStr"/>
@@ -2216,75 +2208,75 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2025-12-29</t>
+          <t>2026-01-05</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>6980.5</v>
+        <v>6911.5</v>
       </c>
       <c r="C21" t="n">
-        <v>6984.75</v>
+        <v>7017.5</v>
       </c>
       <c r="D21" t="n">
-        <v>6866.75</v>
+        <v>6899.5</v>
       </c>
       <c r="E21" t="n">
-        <v>6900.5</v>
+        <v>7005</v>
       </c>
       <c r="F21" t="n">
-        <v>-78.75</v>
+        <v>104.5</v>
       </c>
       <c r="G21" s="5" t="n">
-        <v>-0.0113</v>
+        <v>0.0151</v>
       </c>
       <c r="H21" t="n">
         <v>118</v>
       </c>
       <c r="I21" t="n">
-        <v>6807</v>
+        <v>6748.75</v>
       </c>
       <c r="J21" t="n">
-        <v>6901.75</v>
+        <v>6769.88</v>
       </c>
       <c r="K21" t="n">
-        <v>6932.5</v>
+        <v>6841.5</v>
       </c>
       <c r="L21" t="n">
-        <v>6963.25</v>
+        <v>6913.12</v>
       </c>
       <c r="M21" t="n">
-        <v>7026</v>
+        <v>6959.5</v>
       </c>
       <c r="N21" t="n">
-        <v>7088.75</v>
+        <v>7005.88</v>
       </c>
       <c r="O21" t="n">
-        <v>7087.5</v>
+        <v>7102.75</v>
       </c>
       <c r="P21" s="6" t="n">
         <v/>
       </c>
-      <c r="Q21" s="6" t="inlineStr">
+      <c r="Q21" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R21" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S21" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T21" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U21" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="R21" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S21" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T21" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U21" s="8" t="n">
-        <v/>
-      </c>
       <c r="V21" s="8" t="n">
         <v/>
       </c>
@@ -2293,55 +2285,59 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X21" t="inlineStr"/>
+      <c r="X21" t="inlineStr">
+        <is>
+          <t>強警訊</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2026-01-05</t>
+          <t>2026-01-12</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>6911.5</v>
+        <v>7007</v>
       </c>
       <c r="C22" t="n">
-        <v>7017.5</v>
+        <v>7036.25</v>
       </c>
       <c r="D22" t="n">
-        <v>6899.5</v>
+        <v>6923.25</v>
       </c>
       <c r="E22" t="n">
-        <v>7005</v>
+        <v>6976.75</v>
       </c>
       <c r="F22" t="n">
-        <v>104.5</v>
+        <v>-28.25</v>
       </c>
       <c r="G22" s="5" t="n">
-        <v>0.0151</v>
+        <v>-0.004</v>
       </c>
       <c r="H22" t="n">
-        <v>118</v>
+        <v>113</v>
       </c>
       <c r="I22" t="n">
-        <v>6748.75</v>
+        <v>6781.5</v>
       </c>
       <c r="J22" t="n">
-        <v>6769.88</v>
+        <v>6910.25</v>
       </c>
       <c r="K22" t="n">
-        <v>6841.5</v>
+        <v>6946</v>
       </c>
       <c r="L22" t="n">
-        <v>6913.12</v>
+        <v>6981.75</v>
       </c>
       <c r="M22" t="n">
-        <v>6959.5</v>
+        <v>7064</v>
       </c>
       <c r="N22" t="n">
-        <v>7005.88</v>
+        <v>7146.25</v>
       </c>
       <c r="O22" t="n">
-        <v>7102.75</v>
+        <v>7135.5</v>
       </c>
       <c r="P22" s="6" t="n">
         <v/>
@@ -2349,23 +2345,21 @@
       <c r="Q22" s="6" t="n">
         <v/>
       </c>
-      <c r="R22" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S22" s="7" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T22" s="8" t="inlineStr">
+      <c r="R22" s="6" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="U22" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+      <c r="S22" s="10" t="inlineStr">
+        <is>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T22" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U22" s="8" t="n">
+        <v/>
       </c>
       <c r="V22" s="8" t="n">
         <v/>
@@ -2377,72 +2371,74 @@
       </c>
       <c r="X22" t="inlineStr">
         <is>
-          <t>強警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-01-12</t>
+          <t>2026-01-19</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>7007</v>
+        <v>6918.25</v>
       </c>
       <c r="C23" t="n">
-        <v>7036.25</v>
+        <v>6969</v>
       </c>
       <c r="D23" t="n">
-        <v>6923.25</v>
+        <v>6814.5</v>
       </c>
       <c r="E23" t="n">
-        <v>6976.75</v>
+        <v>6945.75</v>
       </c>
       <c r="F23" t="n">
-        <v>-28.25</v>
+        <v>-31</v>
       </c>
       <c r="G23" s="5" t="n">
-        <v>-0.004</v>
+        <v>-0.0044</v>
       </c>
       <c r="H23" t="n">
-        <v>113</v>
+        <v>154.5</v>
       </c>
       <c r="I23" t="n">
-        <v>6781.5</v>
+        <v>6810.25</v>
       </c>
       <c r="J23" t="n">
-        <v>6910.25</v>
+        <v>6862.25</v>
       </c>
       <c r="K23" t="n">
-        <v>6946</v>
+        <v>6920.25</v>
       </c>
       <c r="L23" t="n">
-        <v>6981.75</v>
+        <v>6978.25</v>
       </c>
       <c r="M23" t="n">
-        <v>7064</v>
+        <v>7033.25</v>
       </c>
       <c r="N23" t="n">
-        <v>7146.25</v>
+        <v>7088.25</v>
       </c>
       <c r="O23" t="n">
-        <v>7135.5</v>
+        <v>7149.25</v>
       </c>
       <c r="P23" s="6" t="n">
         <v/>
       </c>
-      <c r="Q23" s="6" t="n">
-        <v/>
+      <c r="Q23" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="R23" s="6" t="inlineStr">
         <is>
-          <t>✓</t>
+          <t>△C</t>
         </is>
       </c>
       <c r="S23" s="10" t="inlineStr">
         <is>
-          <t>↓C</t>
+          <t>↓</t>
         </is>
       </c>
       <c r="T23" s="8" t="n">
@@ -2459,81 +2455,75 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X23" t="inlineStr">
-        <is>
-          <t>中警訊</t>
-        </is>
-      </c>
+      <c r="X23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2026-01-19</t>
+          <t>2026-01-26</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>6918.25</v>
+        <v>6904</v>
       </c>
       <c r="C24" t="n">
-        <v>6969</v>
+        <v>7043</v>
       </c>
       <c r="D24" t="n">
-        <v>6814.5</v>
+        <v>6879</v>
       </c>
       <c r="E24" t="n">
-        <v>6945.75</v>
+        <v>6965.75</v>
       </c>
       <c r="F24" t="n">
-        <v>-31</v>
+        <v>20</v>
       </c>
       <c r="G24" s="5" t="n">
-        <v>-0.0044</v>
+        <v>0.0029</v>
       </c>
       <c r="H24" t="n">
-        <v>154.5</v>
+        <v>164</v>
       </c>
       <c r="I24" t="n">
-        <v>6810.25</v>
+        <v>6660</v>
       </c>
       <c r="J24" t="n">
-        <v>6862.25</v>
+        <v>6818.25</v>
       </c>
       <c r="K24" t="n">
-        <v>6920.25</v>
+        <v>6868.5</v>
       </c>
       <c r="L24" t="n">
-        <v>6978.25</v>
+        <v>6918.75</v>
       </c>
       <c r="M24" t="n">
-        <v>7033.25</v>
+        <v>7023</v>
       </c>
       <c r="N24" t="n">
-        <v>7088.25</v>
+        <v>7127.25</v>
       </c>
       <c r="O24" t="n">
-        <v>7149.25</v>
+        <v>7123.5</v>
       </c>
       <c r="P24" s="6" t="n">
         <v/>
       </c>
-      <c r="Q24" s="6" t="inlineStr">
+      <c r="Q24" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R24" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S24" s="7" t="inlineStr">
+        <is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T24" s="8" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="R24" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="S24" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T24" s="8" t="n">
-        <v/>
-      </c>
       <c r="U24" s="8" t="n">
         <v/>
       </c>
@@ -2545,75 +2535,81 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X24" t="inlineStr"/>
+      <c r="X24" t="inlineStr">
+        <is>
+          <t>強警訊</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-01-26</t>
+          <t>2026-02-02</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>6904</v>
+        <v>6938.5</v>
       </c>
       <c r="C25" t="n">
-        <v>7043</v>
+        <v>7027.25</v>
       </c>
       <c r="D25" t="n">
-        <v>6879</v>
+        <v>6751.5</v>
       </c>
       <c r="E25" t="n">
-        <v>6965.75</v>
+        <v>6952.75</v>
       </c>
       <c r="F25" t="n">
-        <v>20</v>
+        <v>-13</v>
       </c>
       <c r="G25" s="5" t="n">
-        <v>0.0029</v>
+        <v>-0.0019</v>
       </c>
       <c r="H25" t="n">
-        <v>164</v>
+        <v>275.75</v>
       </c>
       <c r="I25" t="n">
-        <v>6660</v>
+        <v>6715</v>
       </c>
       <c r="J25" t="n">
-        <v>6818.25</v>
+        <v>6804.12</v>
       </c>
       <c r="K25" t="n">
-        <v>6868.5</v>
+        <v>6883.75</v>
       </c>
       <c r="L25" t="n">
-        <v>6918.75</v>
+        <v>6963.38</v>
       </c>
       <c r="M25" t="n">
-        <v>7023</v>
+        <v>7047.75</v>
       </c>
       <c r="N25" t="n">
-        <v>7127.25</v>
+        <v>7132.12</v>
       </c>
       <c r="O25" t="n">
-        <v>7123.5</v>
+        <v>7207</v>
       </c>
       <c r="P25" s="6" t="n">
         <v/>
       </c>
-      <c r="Q25" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R25" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S25" s="7" t="inlineStr">
-        <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T25" s="8" t="inlineStr">
+      <c r="Q25" s="6" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
+      <c r="R25" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S25" s="10" t="inlineStr">
+        <is>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T25" s="8" t="n">
+        <v/>
+      </c>
       <c r="U25" s="8" t="n">
         <v/>
       </c>
@@ -2625,76 +2621,70 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X25" t="inlineStr">
-        <is>
-          <t>強警訊</t>
-        </is>
-      </c>
+      <c r="X25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2026-02-02</t>
+          <t>2026-02-09</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>6938.5</v>
+        <v>6960.25</v>
       </c>
       <c r="C26" t="n">
-        <v>7027.25</v>
+        <v>7011.5</v>
       </c>
       <c r="D26" t="n">
-        <v>6751.5</v>
+        <v>6808.75</v>
       </c>
       <c r="E26" t="n">
-        <v>6952.75</v>
+        <v>6850.5</v>
       </c>
       <c r="F26" t="n">
-        <v>-13</v>
+        <v>-102.25</v>
       </c>
       <c r="G26" s="5" t="n">
-        <v>-0.0019</v>
+        <v>-0.0147</v>
       </c>
       <c r="H26" t="n">
-        <v>275.75</v>
+        <v>202.75</v>
       </c>
       <c r="I26" t="n">
-        <v>6715</v>
+        <v>6475.75</v>
       </c>
       <c r="J26" t="n">
-        <v>6804.12</v>
+        <v>6708.69</v>
       </c>
       <c r="K26" t="n">
-        <v>6883.75</v>
+        <v>6814.88</v>
       </c>
       <c r="L26" t="n">
-        <v>6963.38</v>
+        <v>6921.06</v>
       </c>
       <c r="M26" t="n">
-        <v>7047.75</v>
+        <v>7090.62</v>
       </c>
       <c r="N26" t="n">
-        <v>7132.12</v>
+        <v>7260.19</v>
       </c>
       <c r="O26" t="n">
-        <v>7207</v>
+        <v>7303</v>
       </c>
       <c r="P26" s="6" t="n">
         <v/>
       </c>
-      <c r="Q26" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="Q26" s="6" t="n">
+        <v/>
       </c>
       <c r="R26" s="6" t="inlineStr">
         <is>
-          <t>✓</t>
+          <t>△C</t>
         </is>
       </c>
       <c r="S26" s="10" t="inlineStr">
         <is>
-          <t>↓C</t>
+          <t>↓</t>
         </is>
       </c>
       <c r="T26" s="8" t="n">
@@ -2711,55 +2701,59 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X26" t="inlineStr"/>
+      <c r="X26" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-02-09</t>
+          <t>2026-02-16</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>6960.25</v>
+        <v>6852.5</v>
       </c>
       <c r="C27" t="n">
-        <v>7011.5</v>
+        <v>6931.5</v>
       </c>
       <c r="D27" t="n">
-        <v>6808.75</v>
+        <v>6791</v>
       </c>
       <c r="E27" t="n">
-        <v>6850.5</v>
+        <v>6923.25</v>
       </c>
       <c r="F27" t="n">
-        <v>-102.25</v>
+        <v>72.75</v>
       </c>
       <c r="G27" s="5" t="n">
-        <v>-0.0147</v>
+        <v>0.0106</v>
       </c>
       <c r="H27" t="n">
-        <v>202.75</v>
+        <v>140.5</v>
       </c>
       <c r="I27" t="n">
-        <v>6475.75</v>
+        <v>6606</v>
       </c>
       <c r="J27" t="n">
-        <v>6708.69</v>
+        <v>6617.94</v>
       </c>
       <c r="K27" t="n">
-        <v>6814.88</v>
+        <v>6749.12</v>
       </c>
       <c r="L27" t="n">
-        <v>6921.06</v>
+        <v>6880.31</v>
       </c>
       <c r="M27" t="n">
-        <v>7090.62</v>
+        <v>6951.88</v>
       </c>
       <c r="N27" t="n">
-        <v>7260.19</v>
+        <v>7023.44</v>
       </c>
       <c r="O27" t="n">
-        <v>7303</v>
+        <v>7214.25</v>
       </c>
       <c r="P27" s="6" t="n">
         <v/>
@@ -2767,18 +2761,18 @@
       <c r="Q27" s="6" t="n">
         <v/>
       </c>
-      <c r="R27" s="6" t="inlineStr">
+      <c r="R27" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S27" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T27" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
-      </c>
-      <c r="S27" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T27" s="8" t="n">
-        <v/>
       </c>
       <c r="U27" s="8" t="n">
         <v/>
@@ -2800,50 +2794,50 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2026-02-16</t>
+          <t>2026-02-23</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>6852.5</v>
+        <v>6918</v>
       </c>
       <c r="C28" t="n">
-        <v>6931.5</v>
+        <v>6983.75</v>
       </c>
       <c r="D28" t="n">
-        <v>6791</v>
+        <v>6828.5</v>
       </c>
       <c r="E28" t="n">
-        <v>6923.25</v>
+        <v>6889</v>
       </c>
       <c r="F28" t="n">
-        <v>72.75</v>
+        <v>-34.25</v>
       </c>
       <c r="G28" s="5" t="n">
-        <v>0.0106</v>
+        <v>-0.0049</v>
       </c>
       <c r="H28" t="n">
-        <v>140.5</v>
+        <v>155.25</v>
       </c>
       <c r="I28" t="n">
-        <v>6606</v>
+        <v>6650.5</v>
       </c>
       <c r="J28" t="n">
-        <v>6617.94</v>
+        <v>6813.75</v>
       </c>
       <c r="K28" t="n">
-        <v>6749.12</v>
+        <v>6853</v>
       </c>
       <c r="L28" t="n">
-        <v>6880.31</v>
+        <v>6892.25</v>
       </c>
       <c r="M28" t="n">
-        <v>6951.88</v>
+        <v>6993.5</v>
       </c>
       <c r="N28" t="n">
-        <v>7023.44</v>
+        <v>7094.75</v>
       </c>
       <c r="O28" t="n">
-        <v>7214.25</v>
+        <v>7072</v>
       </c>
       <c r="P28" s="6" t="n">
         <v/>
@@ -2851,18 +2845,18 @@
       <c r="Q28" s="6" t="n">
         <v/>
       </c>
-      <c r="R28" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S28" s="7" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T28" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+      <c r="R28" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S28" s="10" t="inlineStr">
+        <is>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T28" s="8" t="n">
+        <v/>
       </c>
       <c r="U28" s="8" t="n">
         <v/>
@@ -2877,63 +2871,65 @@
       </c>
       <c r="X28" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-02-23</t>
+          <t>2026-03-02</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>6918</v>
+        <v>6820</v>
       </c>
       <c r="C29" t="n">
-        <v>6983.75</v>
+        <v>6911.25</v>
       </c>
       <c r="D29" t="n">
-        <v>6828.5</v>
+        <v>6715.75</v>
       </c>
       <c r="E29" t="n">
-        <v>6889</v>
+        <v>6743.75</v>
       </c>
       <c r="F29" t="n">
-        <v>-34.25</v>
+        <v>-145.25</v>
       </c>
       <c r="G29" s="5" t="n">
-        <v>-0.0049</v>
+        <v>-0.0211</v>
       </c>
       <c r="H29" t="n">
-        <v>155.25</v>
+        <v>195.5</v>
       </c>
       <c r="I29" t="n">
-        <v>6650.5</v>
+        <v>6673.25</v>
       </c>
       <c r="J29" t="n">
-        <v>6813.75</v>
+        <v>6725.19</v>
       </c>
       <c r="K29" t="n">
-        <v>6853</v>
+        <v>6811.38</v>
       </c>
       <c r="L29" t="n">
-        <v>6892.25</v>
+        <v>6897.56</v>
       </c>
       <c r="M29" t="n">
-        <v>6993.5</v>
+        <v>6966.62</v>
       </c>
       <c r="N29" t="n">
-        <v>7094.75</v>
+        <v>7035.69</v>
       </c>
       <c r="O29" t="n">
-        <v>7072</v>
+        <v>7139</v>
       </c>
       <c r="P29" s="6" t="n">
         <v/>
       </c>
-      <c r="Q29" s="6" t="n">
-        <v/>
+      <c r="Q29" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="R29" s="6" t="inlineStr">
         <is>
@@ -2942,7 +2938,7 @@
       </c>
       <c r="S29" s="10" t="inlineStr">
         <is>
-          <t>↓C</t>
+          <t>↓</t>
         </is>
       </c>
       <c r="T29" s="8" t="n">
@@ -2959,80 +2955,76 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X29" t="inlineStr">
-        <is>
-          <t>中警訊</t>
-        </is>
-      </c>
+      <c r="X29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-09</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>6820</v>
+        <v>6685.5</v>
       </c>
       <c r="C30" t="n">
-        <v>6911.25</v>
+        <v>6852</v>
       </c>
       <c r="D30" t="n">
-        <v>6715.75</v>
+        <v>6584.5</v>
       </c>
       <c r="E30" t="n">
-        <v>6743.75</v>
+        <v>6636</v>
       </c>
       <c r="F30" t="n">
-        <v>-145.25</v>
+        <v>-107.75</v>
       </c>
       <c r="G30" s="5" t="n">
-        <v>-0.0211</v>
+        <v>-0.016</v>
       </c>
       <c r="H30" t="n">
-        <v>195.5</v>
+        <v>267.5</v>
       </c>
       <c r="I30" t="n">
-        <v>6673.25</v>
+        <v>6520.25</v>
       </c>
       <c r="J30" t="n">
-        <v>6725.19</v>
+        <v>6513.38</v>
       </c>
       <c r="K30" t="n">
-        <v>6811.38</v>
+        <v>6646</v>
       </c>
       <c r="L30" t="n">
-        <v>6897.56</v>
+        <v>6778.62</v>
       </c>
       <c r="M30" t="n">
-        <v>6966.62</v>
+        <v>6841.5</v>
       </c>
       <c r="N30" t="n">
-        <v>7035.69</v>
+        <v>6904.38</v>
       </c>
       <c r="O30" t="n">
-        <v>7139</v>
+        <v>7106.75</v>
       </c>
       <c r="P30" s="6" t="n">
         <v/>
       </c>
-      <c r="Q30" s="6" t="inlineStr">
+      <c r="Q30" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R30" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="R30" s="6" t="inlineStr">
+      <c r="S30" s="10" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T30" s="8" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
-      </c>
-      <c r="S30" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T30" s="8" t="n">
-        <v/>
       </c>
       <c r="U30" s="8" t="n">
         <v/>
@@ -3050,50 +3042,50 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-03-16</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>6685.5</v>
+        <v>6608.5</v>
       </c>
       <c r="C31" t="n">
-        <v>6852</v>
+        <v>6762.25</v>
       </c>
       <c r="D31" t="n">
-        <v>6584.5</v>
+        <v>6558</v>
       </c>
       <c r="E31" t="n">
-        <v>6636</v>
+        <v>6594.63</v>
       </c>
       <c r="F31" t="n">
-        <v>-107.75</v>
+        <v>-41.37</v>
       </c>
       <c r="G31" s="5" t="n">
-        <v>-0.016</v>
+        <v>-0.0062</v>
       </c>
       <c r="H31" t="n">
-        <v>267.5</v>
+        <v>204.25</v>
       </c>
       <c r="I31" t="n">
-        <v>6520.25</v>
+        <v>6317</v>
       </c>
       <c r="J31" t="n">
-        <v>6513.38</v>
+        <v>6327.38</v>
       </c>
       <c r="K31" t="n">
-        <v>6646</v>
+        <v>6502.25</v>
       </c>
       <c r="L31" t="n">
-        <v>6778.62</v>
+        <v>6677.12</v>
       </c>
       <c r="M31" t="n">
-        <v>6841.5</v>
+        <v>6769.75</v>
       </c>
       <c r="N31" t="n">
-        <v>6904.38</v>
+        <v>6862.38</v>
       </c>
       <c r="O31" t="n">
-        <v>7106.75</v>
+        <v>7119.5</v>
       </c>
       <c r="P31" s="6" t="n">
         <v/>
@@ -3101,20 +3093,16 @@
       <c r="Q31" s="6" t="n">
         <v/>
       </c>
-      <c r="R31" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+      <c r="R31" s="6" t="n">
+        <v/>
       </c>
       <c r="S31" s="10" t="inlineStr">
         <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T31" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T31" s="8" t="n">
+        <v/>
       </c>
       <c r="U31" s="8" t="n">
         <v/>
@@ -3132,67 +3120,73 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-23</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>6608.5</v>
+        <v>6510</v>
       </c>
       <c r="C32" t="n">
-        <v>6762.25</v>
+        <v>6748</v>
       </c>
       <c r="D32" t="n">
-        <v>6558</v>
+        <v>6389</v>
       </c>
       <c r="E32" t="n">
-        <v>6594.63</v>
+        <v>6412.25</v>
       </c>
       <c r="F32" t="n">
-        <v>-41.37</v>
+        <v>-182.38</v>
       </c>
       <c r="G32" s="5" t="n">
-        <v>-0.0062</v>
+        <v>-0.0277</v>
       </c>
       <c r="H32" t="n">
-        <v>204.25</v>
+        <v>359</v>
       </c>
       <c r="I32" t="n">
-        <v>6317</v>
+        <v>6353.75</v>
       </c>
       <c r="J32" t="n">
-        <v>6327.38</v>
+        <v>6357.63</v>
       </c>
       <c r="K32" t="n">
-        <v>6502.25</v>
+        <v>6492.5</v>
       </c>
       <c r="L32" t="n">
-        <v>6677.12</v>
+        <v>6627.38</v>
       </c>
       <c r="M32" t="n">
-        <v>6769.75</v>
+        <v>6696.75</v>
       </c>
       <c r="N32" t="n">
-        <v>6862.38</v>
+        <v>6766.13</v>
       </c>
       <c r="O32" t="n">
-        <v>7119.5</v>
+        <v>6966.5</v>
       </c>
       <c r="P32" s="6" t="n">
         <v/>
       </c>
-      <c r="Q32" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R32" s="6" t="n">
-        <v/>
+      <c r="Q32" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="R32" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S32" s="10" t="inlineStr">
         <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T32" s="8" t="n">
-        <v/>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T32" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="U32" s="8" t="n">
         <v/>
@@ -3210,74 +3204,70 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2026-03-23</t>
+          <t>2026-03-30</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>6510</v>
+        <v>6380</v>
       </c>
       <c r="C33" t="n">
-        <v>6748</v>
+        <v>6653.75</v>
       </c>
       <c r="D33" t="n">
-        <v>6389</v>
+        <v>6353.25</v>
       </c>
       <c r="E33" t="n">
-        <v>6412.25</v>
+        <v>6603.75</v>
       </c>
       <c r="F33" t="n">
-        <v>-182.38</v>
+        <v>191.5</v>
       </c>
       <c r="G33" s="5" t="n">
-        <v>-0.0277</v>
+        <v>0.0299</v>
       </c>
       <c r="H33" t="n">
-        <v>359</v>
+        <v>300.5</v>
       </c>
       <c r="I33" t="n">
-        <v>6353.75</v>
+        <v>6030</v>
       </c>
       <c r="J33" t="n">
-        <v>6357.63</v>
+        <v>5975.12</v>
       </c>
       <c r="K33" t="n">
-        <v>6492.5</v>
+        <v>6232.75</v>
       </c>
       <c r="L33" t="n">
-        <v>6627.38</v>
+        <v>6490.38</v>
       </c>
       <c r="M33" t="n">
-        <v>6696.75</v>
+        <v>6591.75</v>
       </c>
       <c r="N33" t="n">
-        <v>6766.13</v>
+        <v>6693.12</v>
       </c>
       <c r="O33" t="n">
-        <v>6966.5</v>
+        <v>7107</v>
       </c>
       <c r="P33" s="6" t="n">
         <v/>
       </c>
-      <c r="Q33" s="6" t="inlineStr">
+      <c r="Q33" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R33" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S33" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T33" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="R33" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S33" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T33" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
       <c r="U33" s="8" t="n">
         <v/>
       </c>
@@ -3289,55 +3279,59 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X33" t="inlineStr"/>
+      <c r="X33" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-04-06</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>6380</v>
+        <v>6590</v>
       </c>
       <c r="C34" t="n">
-        <v>6653.75</v>
+        <v>6888</v>
       </c>
       <c r="D34" t="n">
-        <v>6353.25</v>
+        <v>6567</v>
       </c>
       <c r="E34" t="n">
-        <v>6603.75</v>
+        <v>6855.25</v>
       </c>
       <c r="F34" t="n">
-        <v>191.5</v>
+        <v>251.5</v>
       </c>
       <c r="G34" s="5" t="n">
-        <v>0.0299</v>
+        <v>0.0381</v>
       </c>
       <c r="H34" t="n">
-        <v>300.5</v>
+        <v>321</v>
       </c>
       <c r="I34" t="n">
-        <v>6030</v>
+        <v>6052.75</v>
       </c>
       <c r="J34" t="n">
-        <v>5975.12</v>
+        <v>6353.38</v>
       </c>
       <c r="K34" t="n">
-        <v>6232.75</v>
+        <v>6453.5</v>
       </c>
       <c r="L34" t="n">
-        <v>6490.38</v>
+        <v>6553.62</v>
       </c>
       <c r="M34" t="n">
-        <v>6591.75</v>
+        <v>6754</v>
       </c>
       <c r="N34" t="n">
-        <v>6693.12</v>
+        <v>6954.38</v>
       </c>
       <c r="O34" t="n">
-        <v>7107</v>
+        <v>6954.25</v>
       </c>
       <c r="P34" s="6" t="n">
         <v/>
@@ -3355,15 +3349,17 @@
       </c>
       <c r="T34" s="8" t="inlineStr">
         <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U34" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V34" s="8" t="inlineStr">
+        <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="U34" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V34" s="8" t="n">
-        <v/>
-      </c>
       <c r="W34" s="11" t="inlineStr">
         <is>
           <t>空方</t>
@@ -3371,57 +3367,57 @@
       </c>
       <c r="X34" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2026-04-06</t>
+          <t>2026-04-13</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>6590</v>
+        <v>6780</v>
       </c>
       <c r="C35" t="n">
-        <v>6888</v>
+        <v>7185.75</v>
       </c>
       <c r="D35" t="n">
-        <v>6567</v>
+        <v>6767</v>
       </c>
       <c r="E35" t="n">
-        <v>6855.25</v>
+        <v>7161.5</v>
       </c>
       <c r="F35" t="n">
-        <v>251.5</v>
+        <v>306.25</v>
       </c>
       <c r="G35" s="5" t="n">
-        <v>0.0381</v>
+        <v>0.0447</v>
       </c>
       <c r="H35" t="n">
-        <v>321</v>
+        <v>418.75</v>
       </c>
       <c r="I35" t="n">
-        <v>6052.75</v>
+        <v>6246</v>
       </c>
       <c r="J35" t="n">
-        <v>6353.38</v>
+        <v>6598.12</v>
       </c>
       <c r="K35" t="n">
-        <v>6453.5</v>
+        <v>6694.75</v>
       </c>
       <c r="L35" t="n">
-        <v>6553.62</v>
+        <v>6791.38</v>
       </c>
       <c r="M35" t="n">
-        <v>6754</v>
+        <v>7015.75</v>
       </c>
       <c r="N35" t="n">
-        <v>6954.38</v>
+        <v>7240.12</v>
       </c>
       <c r="O35" t="n">
-        <v>6954.25</v>
+        <v>7209</v>
       </c>
       <c r="P35" s="6" t="n">
         <v/>
@@ -3464,50 +3460,50 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2026-04-13</t>
+          <t>2026-04-20</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>6780</v>
+        <v>7102.5</v>
       </c>
       <c r="C36" t="n">
-        <v>7185.75</v>
+        <v>7200.5</v>
       </c>
       <c r="D36" t="n">
-        <v>6767</v>
+        <v>7079.25</v>
       </c>
       <c r="E36" t="n">
-        <v>7161.5</v>
+        <v>7194.75</v>
       </c>
       <c r="F36" t="n">
-        <v>306.25</v>
+        <v>33.25</v>
       </c>
       <c r="G36" s="5" t="n">
-        <v>0.0447</v>
+        <v>0.0046</v>
       </c>
       <c r="H36" t="n">
-        <v>418.75</v>
+        <v>121.25</v>
       </c>
       <c r="I36" t="n">
-        <v>6246</v>
+        <v>6348.25</v>
       </c>
       <c r="J36" t="n">
-        <v>6598.12</v>
+        <v>6835.31</v>
       </c>
       <c r="K36" t="n">
-        <v>6694.75</v>
+        <v>6952.12</v>
       </c>
       <c r="L36" t="n">
-        <v>6791.38</v>
+        <v>7068.94</v>
       </c>
       <c r="M36" t="n">
-        <v>7015.75</v>
+        <v>7370.88</v>
       </c>
       <c r="N36" t="n">
-        <v>7240.12</v>
+        <v>7672.81</v>
       </c>
       <c r="O36" t="n">
-        <v>7209</v>
+        <v>7604.5</v>
       </c>
       <c r="P36" s="6" t="n">
         <v/>
@@ -3520,21 +3516,17 @@
       </c>
       <c r="S36" s="7" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T36" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T36" s="8" t="n">
+        <v/>
       </c>
       <c r="U36" s="8" t="n">
         <v/>
       </c>
-      <c r="V36" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+      <c r="V36" s="8" t="n">
+        <v/>
       </c>
       <c r="W36" s="11" t="inlineStr">
         <is>
@@ -3550,50 +3542,50 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
+          <t>2026-04-27</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>7102.5</v>
+        <v>7185</v>
       </c>
       <c r="C37" t="n">
-        <v>7200.5</v>
+        <v>7300.75</v>
       </c>
       <c r="D37" t="n">
-        <v>7079.25</v>
+        <v>7131.25</v>
       </c>
       <c r="E37" t="n">
-        <v>7194.75</v>
+        <v>7258</v>
       </c>
       <c r="F37" t="n">
-        <v>33.25</v>
+        <v>63.25</v>
       </c>
       <c r="G37" s="5" t="n">
-        <v>0.0046</v>
+        <v>0.008800000000000001</v>
       </c>
       <c r="H37" t="n">
-        <v>121.25</v>
+        <v>169.5</v>
       </c>
       <c r="I37" t="n">
-        <v>6348.25</v>
+        <v>6958</v>
       </c>
       <c r="J37" t="n">
-        <v>6835.31</v>
+        <v>7100.94</v>
       </c>
       <c r="K37" t="n">
-        <v>6952.12</v>
+        <v>7134.12</v>
       </c>
       <c r="L37" t="n">
-        <v>7068.94</v>
+        <v>7167.31</v>
       </c>
       <c r="M37" t="n">
-        <v>7370.88</v>
+        <v>7255.38</v>
       </c>
       <c r="N37" t="n">
-        <v>7672.81</v>
+        <v>7343.44</v>
       </c>
       <c r="O37" t="n">
-        <v>7604.5</v>
+        <v>7321.75</v>
       </c>
       <c r="P37" s="6" t="n">
         <v/>
@@ -3601,16 +3593,20 @@
       <c r="Q37" s="6" t="n">
         <v/>
       </c>
-      <c r="R37" s="6" t="n">
-        <v/>
+      <c r="R37" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S37" s="7" t="inlineStr">
         <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T37" s="8" t="n">
-        <v/>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T37" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="U37" s="8" t="n">
         <v/>
@@ -3632,50 +3628,50 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-05-04</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>7185</v>
+        <v>7276.25</v>
       </c>
       <c r="C38" t="n">
-        <v>7300.75</v>
+        <v>7427.75</v>
       </c>
       <c r="D38" t="n">
-        <v>7131.25</v>
+        <v>7199.5</v>
       </c>
       <c r="E38" t="n">
-        <v>7258</v>
+        <v>7419</v>
       </c>
       <c r="F38" t="n">
-        <v>63.25</v>
+        <v>161</v>
       </c>
       <c r="G38" s="5" t="n">
-        <v>0.008800000000000001</v>
+        <v>0.0222</v>
       </c>
       <c r="H38" t="n">
-        <v>169.5</v>
+        <v>228.25</v>
       </c>
       <c r="I38" t="n">
-        <v>6958</v>
+        <v>6961.75</v>
       </c>
       <c r="J38" t="n">
-        <v>7100.94</v>
+        <v>7109.5</v>
       </c>
       <c r="K38" t="n">
-        <v>7134.12</v>
+        <v>7173.25</v>
       </c>
       <c r="L38" t="n">
-        <v>7167.31</v>
+        <v>7237</v>
       </c>
       <c r="M38" t="n">
-        <v>7255.38</v>
+        <v>7342.75</v>
       </c>
       <c r="N38" t="n">
-        <v>7343.44</v>
+        <v>7448.5</v>
       </c>
       <c r="O38" t="n">
-        <v>7321.75</v>
+        <v>7470.25</v>
       </c>
       <c r="P38" s="6" t="n">
         <v/>
@@ -3683,23 +3679,23 @@
       <c r="Q38" s="6" t="n">
         <v/>
       </c>
-      <c r="R38" s="6" t="inlineStr">
+      <c r="R38" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S38" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T38" s="8" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="S38" s="7" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T38" s="8" t="inlineStr">
+      <c r="U38" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
-      </c>
-      <c r="U38" s="8" t="n">
-        <v/>
       </c>
       <c r="V38" s="8" t="n">
         <v/>
@@ -3718,50 +3714,50 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2026-05-04</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>7276.25</v>
+        <v>7403.5</v>
       </c>
       <c r="C39" t="n">
-        <v>7427.75</v>
+        <v>7540</v>
       </c>
       <c r="D39" t="n">
-        <v>7199.5</v>
+        <v>7363.25</v>
       </c>
       <c r="E39" t="n">
-        <v>7419</v>
+        <v>7432.25</v>
       </c>
       <c r="F39" t="n">
-        <v>161</v>
+        <v>13.25</v>
       </c>
       <c r="G39" s="5" t="n">
-        <v>0.0222</v>
+        <v>0.0018</v>
       </c>
       <c r="H39" t="n">
-        <v>228.25</v>
+        <v>176.75</v>
       </c>
       <c r="I39" t="n">
-        <v>6961.75</v>
+        <v>6971.25</v>
       </c>
       <c r="J39" t="n">
-        <v>7109.5</v>
+        <v>7243.44</v>
       </c>
       <c r="K39" t="n">
-        <v>7173.25</v>
+        <v>7304.88</v>
       </c>
       <c r="L39" t="n">
-        <v>7237</v>
+        <v>7366.31</v>
       </c>
       <c r="M39" t="n">
-        <v>7342.75</v>
+        <v>7533.12</v>
       </c>
       <c r="N39" t="n">
-        <v>7448.5</v>
+        <v>7699.94</v>
       </c>
       <c r="O39" t="n">
-        <v>7470.25</v>
+        <v>7656</v>
       </c>
       <c r="P39" s="6" t="n">
         <v/>
@@ -3774,7 +3770,7 @@
       </c>
       <c r="S39" s="7" t="inlineStr">
         <is>
-          <t>↑</t>
+          <t>↑C</t>
         </is>
       </c>
       <c r="T39" s="8" t="inlineStr">
@@ -3782,10 +3778,8 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="U39" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+      <c r="U39" s="8" t="n">
+        <v/>
       </c>
       <c r="V39" s="8" t="n">
         <v/>
@@ -3804,50 +3798,50 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-05-18</t>
         </is>
       </c>
       <c r="B40" t="n">
-        <v>7403.5</v>
+        <v>7410</v>
       </c>
       <c r="C40" t="n">
-        <v>7540</v>
+        <v>7524</v>
       </c>
       <c r="D40" t="n">
-        <v>7363.25</v>
+        <v>7354.25</v>
       </c>
       <c r="E40" t="n">
-        <v>7432.25</v>
+        <v>7491</v>
       </c>
       <c r="F40" t="n">
-        <v>13.25</v>
+        <v>58.75</v>
       </c>
       <c r="G40" s="5" t="n">
-        <v>0.0018</v>
+        <v>0.007900000000000001</v>
       </c>
       <c r="H40" t="n">
-        <v>176.75</v>
+        <v>169.75</v>
       </c>
       <c r="I40" t="n">
-        <v>6971.25</v>
+        <v>7186.5</v>
       </c>
       <c r="J40" t="n">
-        <v>7243.44</v>
+        <v>7245.81</v>
       </c>
       <c r="K40" t="n">
-        <v>7304.88</v>
+        <v>7343.88</v>
       </c>
       <c r="L40" t="n">
-        <v>7366.31</v>
+        <v>7441.94</v>
       </c>
       <c r="M40" t="n">
-        <v>7533.12</v>
+        <v>7520.62</v>
       </c>
       <c r="N40" t="n">
-        <v>7699.94</v>
+        <v>7599.31</v>
       </c>
       <c r="O40" t="n">
-        <v>7656</v>
+        <v>7716.75</v>
       </c>
       <c r="P40" s="6" t="n">
         <v/>
@@ -3860,12 +3854,12 @@
       </c>
       <c r="S40" s="7" t="inlineStr">
         <is>
-          <t>↑C</t>
+          <t>↑</t>
         </is>
       </c>
       <c r="T40" s="8" t="inlineStr">
         <is>
-          <t>✓</t>
+          <t>△C</t>
         </is>
       </c>
       <c r="U40" s="8" t="n">
@@ -3881,57 +3875,57 @@
       </c>
       <c r="X40" t="inlineStr">
         <is>
-          <t>強警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-05-25</t>
         </is>
       </c>
       <c r="B41" t="n">
-        <v>7410</v>
+        <v>7519</v>
       </c>
       <c r="C41" t="n">
-        <v>7524</v>
+        <v>7611.5</v>
       </c>
       <c r="D41" t="n">
-        <v>7354.25</v>
+        <v>7505.75</v>
       </c>
       <c r="E41" t="n">
-        <v>7491</v>
+        <v>7595.75</v>
       </c>
       <c r="F41" t="n">
-        <v>58.75</v>
+        <v>104.75</v>
       </c>
       <c r="G41" s="5" t="n">
-        <v>0.007900000000000001</v>
+        <v>0.014</v>
       </c>
       <c r="H41" t="n">
-        <v>169.75</v>
+        <v>105.75</v>
       </c>
       <c r="I41" t="n">
-        <v>7186.5</v>
+        <v>7184.5</v>
       </c>
       <c r="J41" t="n">
-        <v>7245.81</v>
+        <v>7347.19</v>
       </c>
       <c r="K41" t="n">
-        <v>7343.88</v>
+        <v>7406.12</v>
       </c>
       <c r="L41" t="n">
-        <v>7441.94</v>
+        <v>7465.06</v>
       </c>
       <c r="M41" t="n">
-        <v>7520.62</v>
+        <v>7575.88</v>
       </c>
       <c r="N41" t="n">
-        <v>7599.31</v>
+        <v>7686.69</v>
       </c>
       <c r="O41" t="n">
-        <v>7716.75</v>
+        <v>7693.75</v>
       </c>
       <c r="P41" s="6" t="n">
         <v/>
@@ -3965,77 +3959,81 @@
       </c>
       <c r="X41" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>2026-05-25</t>
+          <t>2026-06-01</t>
         </is>
       </c>
       <c r="B42" t="n">
-        <v>7519</v>
+        <v>7595</v>
       </c>
       <c r="C42" t="n">
-        <v>7611.5</v>
+        <v>7632.25</v>
       </c>
       <c r="D42" t="n">
-        <v>7505.75</v>
+        <v>7359</v>
       </c>
       <c r="E42" t="n">
-        <v>7595.75</v>
+        <v>7400.5</v>
       </c>
       <c r="F42" t="n">
-        <v>104.75</v>
+        <v>-195.25</v>
       </c>
       <c r="G42" s="5" t="n">
-        <v>0.014</v>
+        <v>-0.0257</v>
       </c>
       <c r="H42" t="n">
-        <v>105.75</v>
+        <v>273.25</v>
       </c>
       <c r="I42" t="n">
-        <v>7184.5</v>
+        <v>7400</v>
       </c>
       <c r="J42" t="n">
-        <v>7347.19</v>
+        <v>7508.56</v>
       </c>
       <c r="K42" t="n">
-        <v>7406.12</v>
+        <v>7542.88</v>
       </c>
       <c r="L42" t="n">
-        <v>7465.06</v>
+        <v>7577.19</v>
       </c>
       <c r="M42" t="n">
-        <v>7575.88</v>
+        <v>7648.62</v>
       </c>
       <c r="N42" t="n">
-        <v>7686.69</v>
+        <v>7720.06</v>
       </c>
       <c r="O42" t="n">
-        <v>7693.75</v>
-      </c>
-      <c r="P42" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q42" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R42" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S42" s="7" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T42" s="8" t="inlineStr">
+        <v>7717.25</v>
+      </c>
+      <c r="P42" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
+      <c r="Q42" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="R42" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S42" s="10" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T42" s="8" t="n">
+        <v/>
+      </c>
       <c r="U42" s="8" t="n">
         <v/>
       </c>
@@ -4049,76 +4047,72 @@
       </c>
       <c r="X42" t="inlineStr">
         <is>
-          <t>強警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-06-08</t>
         </is>
       </c>
       <c r="B43" t="n">
-        <v>7595</v>
+        <v>7368</v>
       </c>
       <c r="C43" t="n">
-        <v>7632.25</v>
+        <v>7491</v>
       </c>
       <c r="D43" t="n">
-        <v>7359</v>
+        <v>7232.25</v>
       </c>
       <c r="E43" t="n">
-        <v>7400.5</v>
+        <v>7435</v>
       </c>
       <c r="F43" t="n">
-        <v>-195.25</v>
+        <v>34.5</v>
       </c>
       <c r="G43" s="5" t="n">
-        <v>-0.0257</v>
+        <v>0.0047</v>
       </c>
       <c r="H43" t="n">
-        <v>273.25</v>
+        <v>258.75</v>
       </c>
       <c r="I43" t="n">
-        <v>7400</v>
+        <v>7085.75</v>
       </c>
       <c r="J43" t="n">
-        <v>7508.56</v>
+        <v>7079.69</v>
       </c>
       <c r="K43" t="n">
-        <v>7542.88</v>
+        <v>7263.88</v>
       </c>
       <c r="L43" t="n">
-        <v>7577.19</v>
+        <v>7448.06</v>
       </c>
       <c r="M43" t="n">
-        <v>7648.62</v>
+        <v>7537.12</v>
       </c>
       <c r="N43" t="n">
-        <v>7720.06</v>
+        <v>7626.19</v>
       </c>
       <c r="O43" t="n">
-        <v>7717.25</v>
-      </c>
-      <c r="P43" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="Q43" s="6" t="inlineStr">
+        <v>7905.5</v>
+      </c>
+      <c r="P43" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q43" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R43" s="6" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="R43" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
       <c r="S43" s="10" t="inlineStr">
         <is>
-          <t>↓</t>
+          <t>↓C</t>
         </is>
       </c>
       <c r="T43" s="8" t="n">
@@ -4144,50 +4138,50 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="B44" t="n">
-        <v>7368</v>
+        <v>7480</v>
       </c>
       <c r="C44" t="n">
-        <v>7491</v>
+        <v>7584.5</v>
       </c>
       <c r="D44" t="n">
-        <v>7232.25</v>
+        <v>7405</v>
       </c>
       <c r="E44" t="n">
-        <v>7435</v>
+        <v>7556.25</v>
       </c>
       <c r="F44" t="n">
-        <v>34.5</v>
+        <v>121.25</v>
       </c>
       <c r="G44" s="5" t="n">
-        <v>0.0047</v>
+        <v>0.0163</v>
       </c>
       <c r="H44" t="n">
-        <v>258.75</v>
+        <v>179.5</v>
       </c>
       <c r="I44" t="n">
-        <v>7085.75</v>
+        <v>6973.5</v>
       </c>
       <c r="J44" t="n">
-        <v>7079.69</v>
+        <v>7212.94</v>
       </c>
       <c r="K44" t="n">
-        <v>7263.88</v>
+        <v>7305.62</v>
       </c>
       <c r="L44" t="n">
-        <v>7448.06</v>
+        <v>7398.31</v>
       </c>
       <c r="M44" t="n">
-        <v>7537.12</v>
+        <v>7564.38</v>
       </c>
       <c r="N44" t="n">
-        <v>7626.19</v>
+        <v>7730.44</v>
       </c>
       <c r="O44" t="n">
-        <v>7905.5</v>
+        <v>7749.75</v>
       </c>
       <c r="P44" s="6" t="n">
         <v/>
@@ -4195,18 +4189,18 @@
       <c r="Q44" s="6" t="n">
         <v/>
       </c>
-      <c r="R44" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S44" s="10" t="inlineStr">
-        <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T44" s="8" t="n">
-        <v/>
+      <c r="R44" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S44" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T44" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="U44" s="8" t="n">
         <v/>
@@ -4221,77 +4215,79 @@
       </c>
       <c r="X44" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="B45" t="n">
-        <v>7480</v>
+        <v>7543.25</v>
       </c>
       <c r="C45" t="n">
-        <v>7584.5</v>
+        <v>7599.25</v>
       </c>
       <c r="D45" t="n">
-        <v>7405</v>
+        <v>7357.25</v>
       </c>
       <c r="E45" t="n">
-        <v>7556.25</v>
+        <v>7401.75</v>
       </c>
       <c r="F45" t="n">
-        <v>121.25</v>
+        <v>-154.5</v>
       </c>
       <c r="G45" s="5" t="n">
-        <v>0.0163</v>
+        <v>-0.0204</v>
       </c>
       <c r="H45" t="n">
-        <v>179.5</v>
+        <v>242</v>
       </c>
       <c r="I45" t="n">
-        <v>6973.5</v>
+        <v>7225.5</v>
       </c>
       <c r="J45" t="n">
-        <v>7212.94</v>
+        <v>7407.5</v>
       </c>
       <c r="K45" t="n">
-        <v>7305.62</v>
+        <v>7466.5</v>
       </c>
       <c r="L45" t="n">
-        <v>7398.31</v>
+        <v>7525.5</v>
       </c>
       <c r="M45" t="n">
-        <v>7564.38</v>
+        <v>7646</v>
       </c>
       <c r="N45" t="n">
-        <v>7730.44</v>
+        <v>7766.5</v>
       </c>
       <c r="O45" t="n">
-        <v>7749.75</v>
+        <v>7764</v>
       </c>
       <c r="P45" s="6" t="n">
         <v/>
       </c>
-      <c r="Q45" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R45" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S45" s="7" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T45" s="8" t="inlineStr">
+      <c r="Q45" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
+      <c r="R45" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S45" s="10" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T45" s="8" t="n">
+        <v/>
+      </c>
       <c r="U45" s="8" t="n">
         <v/>
       </c>
@@ -4305,79 +4301,77 @@
       </c>
       <c r="X45" t="inlineStr">
         <is>
-          <t>強警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="B46" t="n">
-        <v>7543.25</v>
+        <v>7398</v>
       </c>
       <c r="C46" t="n">
-        <v>7599.25</v>
+        <v>7593.75</v>
       </c>
       <c r="D46" t="n">
-        <v>7357.25</v>
+        <v>7398</v>
       </c>
       <c r="E46" t="n">
-        <v>7401.75</v>
+        <v>7557</v>
       </c>
       <c r="F46" t="n">
-        <v>-154.5</v>
+        <v>155.25</v>
       </c>
       <c r="G46" s="5" t="n">
-        <v>-0.0204</v>
+        <v>0.021</v>
       </c>
       <c r="H46" t="n">
-        <v>242</v>
+        <v>195.75</v>
       </c>
       <c r="I46" t="n">
-        <v>7225.5</v>
+        <v>7115.25</v>
       </c>
       <c r="J46" t="n">
-        <v>7407.5</v>
+        <v>7121.5</v>
       </c>
       <c r="K46" t="n">
-        <v>7466.5</v>
+        <v>7280.75</v>
       </c>
       <c r="L46" t="n">
-        <v>7525.5</v>
+        <v>7440</v>
       </c>
       <c r="M46" t="n">
-        <v>7646</v>
+        <v>7522.75</v>
       </c>
       <c r="N46" t="n">
-        <v>7766.5</v>
+        <v>7605.5</v>
       </c>
       <c r="O46" t="n">
-        <v>7764</v>
+        <v>7841.25</v>
       </c>
       <c r="P46" s="6" t="n">
         <v/>
       </c>
-      <c r="Q46" s="6" t="inlineStr">
+      <c r="Q46" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R46" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S46" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T46" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="R46" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S46" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T46" s="8" t="n">
-        <v/>
-      </c>
       <c r="U46" s="8" t="n">
         <v/>
       </c>
@@ -4391,57 +4385,57 @@
       </c>
       <c r="X46" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="B47" t="n">
-        <v>7398</v>
+        <v>7562.25</v>
       </c>
       <c r="C47" t="n">
-        <v>7593.75</v>
+        <v>7628.75</v>
       </c>
       <c r="D47" t="n">
-        <v>7398</v>
+        <v>7468.5</v>
       </c>
       <c r="E47" t="n">
-        <v>7557</v>
+        <v>7620.25</v>
       </c>
       <c r="F47" t="n">
-        <v>155.25</v>
+        <v>63.25</v>
       </c>
       <c r="G47" s="5" t="n">
-        <v>0.021</v>
+        <v>0.008399999999999999</v>
       </c>
       <c r="H47" t="n">
-        <v>195.75</v>
+        <v>160.25</v>
       </c>
       <c r="I47" t="n">
-        <v>7115.25</v>
+        <v>7202.25</v>
       </c>
       <c r="J47" t="n">
-        <v>7121.5</v>
+        <v>7391.81</v>
       </c>
       <c r="K47" t="n">
-        <v>7280.75</v>
+        <v>7459.12</v>
       </c>
       <c r="L47" t="n">
-        <v>7440</v>
+        <v>7526.44</v>
       </c>
       <c r="M47" t="n">
-        <v>7522.75</v>
+        <v>7654.88</v>
       </c>
       <c r="N47" t="n">
-        <v>7605.5</v>
+        <v>7783.31</v>
       </c>
       <c r="O47" t="n">
-        <v>7841.25</v>
+        <v>7789.5</v>
       </c>
       <c r="P47" s="6" t="n">
         <v/>
@@ -4475,77 +4469,79 @@
       </c>
       <c r="X47" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="B48" t="n">
-        <v>7562.25</v>
+        <v>7607</v>
       </c>
       <c r="C48" t="n">
-        <v>7628.75</v>
+        <v>7632</v>
       </c>
       <c r="D48" t="n">
-        <v>7468.5</v>
+        <v>7473</v>
       </c>
       <c r="E48" t="n">
-        <v>7620.25</v>
+        <v>7497.75</v>
       </c>
       <c r="F48" t="n">
-        <v>63.25</v>
+        <v>-122.5</v>
       </c>
       <c r="G48" s="5" t="n">
-        <v>0.008399999999999999</v>
+        <v>-0.0161</v>
       </c>
       <c r="H48" t="n">
-        <v>160.25</v>
+        <v>159</v>
       </c>
       <c r="I48" t="n">
-        <v>7202.25</v>
+        <v>7308.25</v>
       </c>
       <c r="J48" t="n">
-        <v>7391.81</v>
+        <v>7495.81</v>
       </c>
       <c r="K48" t="n">
-        <v>7459.12</v>
+        <v>7540.12</v>
       </c>
       <c r="L48" t="n">
-        <v>7526.44</v>
+        <v>7584.44</v>
       </c>
       <c r="M48" t="n">
-        <v>7654.88</v>
+        <v>7700.38</v>
       </c>
       <c r="N48" t="n">
-        <v>7783.31</v>
+        <v>7816.31</v>
       </c>
       <c r="O48" t="n">
-        <v>7789.5</v>
+        <v>7789</v>
       </c>
       <c r="P48" s="6" t="n">
         <v/>
       </c>
-      <c r="Q48" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R48" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S48" s="7" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T48" s="8" t="inlineStr">
+      <c r="Q48" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
+      <c r="R48" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S48" s="10" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T48" s="8" t="n">
+        <v/>
+      </c>
       <c r="U48" s="8" t="n">
         <v/>
       </c>
@@ -4559,71 +4555,69 @@
       </c>
       <c r="X48" t="inlineStr">
         <is>
-          <t>強警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="B49" t="n">
-        <v>7607</v>
+        <v>7485</v>
       </c>
       <c r="C49" t="n">
-        <v>7632</v>
+        <v>7563.5</v>
       </c>
       <c r="D49" t="n">
-        <v>7473</v>
+        <v>7411.75</v>
       </c>
       <c r="E49" t="n">
-        <v>7497.75</v>
+        <v>7447.5</v>
       </c>
       <c r="F49" t="n">
-        <v>-122.5</v>
+        <v>-50.25</v>
       </c>
       <c r="G49" s="5" t="n">
-        <v>-0.0161</v>
+        <v>-0.0067</v>
       </c>
       <c r="H49" t="n">
-        <v>159</v>
+        <v>151.75</v>
       </c>
       <c r="I49" t="n">
-        <v>7308.25</v>
+        <v>7314</v>
       </c>
       <c r="J49" t="n">
-        <v>7495.81</v>
+        <v>7311.38</v>
       </c>
       <c r="K49" t="n">
-        <v>7540.12</v>
+        <v>7418.25</v>
       </c>
       <c r="L49" t="n">
-        <v>7584.44</v>
+        <v>7525.12</v>
       </c>
       <c r="M49" t="n">
-        <v>7700.38</v>
+        <v>7577.25</v>
       </c>
       <c r="N49" t="n">
-        <v>7816.31</v>
+        <v>7629.38</v>
       </c>
       <c r="O49" t="n">
-        <v>7789</v>
+        <v>7791</v>
       </c>
       <c r="P49" s="6" t="n">
         <v/>
       </c>
-      <c r="Q49" s="6" t="inlineStr">
+      <c r="Q49" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R49" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="R49" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
       <c r="S49" s="10" t="inlineStr">
         <is>
           <t>↓</t>
@@ -4643,59 +4637,55 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X49" t="inlineStr">
-        <is>
-          <t>中警訊</t>
-        </is>
-      </c>
+      <c r="X49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="B50" t="n">
-        <v>7485</v>
+        <v>7490</v>
       </c>
       <c r="C50" t="n">
-        <v>7563.5</v>
+        <v>7541</v>
       </c>
       <c r="D50" t="n">
-        <v>7411.75</v>
+        <v>7324</v>
       </c>
       <c r="E50" t="n">
-        <v>7447.5</v>
+        <v>7519.25</v>
       </c>
       <c r="F50" t="n">
-        <v>-50.25</v>
+        <v>71.75</v>
       </c>
       <c r="G50" s="5" t="n">
-        <v>-0.0067</v>
+        <v>0.009599999999999999</v>
       </c>
       <c r="H50" t="n">
-        <v>151.75</v>
+        <v>217</v>
       </c>
       <c r="I50" t="n">
-        <v>7314</v>
+        <v>7260</v>
       </c>
       <c r="J50" t="n">
-        <v>7311.38</v>
+        <v>7275.69</v>
       </c>
       <c r="K50" t="n">
-        <v>7418.25</v>
+        <v>7371.62</v>
       </c>
       <c r="L50" t="n">
-        <v>7525.12</v>
+        <v>7467.56</v>
       </c>
       <c r="M50" t="n">
-        <v>7577.25</v>
+        <v>7523.38</v>
       </c>
       <c r="N50" t="n">
-        <v>7629.38</v>
+        <v>7579.19</v>
       </c>
       <c r="O50" t="n">
-        <v>7791</v>
+        <v>7715.25</v>
       </c>
       <c r="P50" s="6" t="n">
         <v/>
@@ -4705,17 +4695,19 @@
       </c>
       <c r="R50" s="6" t="inlineStr">
         <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S50" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T50" s="8" t="inlineStr">
+        <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="S50" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T50" s="8" t="n">
-        <v/>
-      </c>
       <c r="U50" s="8" t="n">
         <v/>
       </c>
@@ -4727,55 +4719,59 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X50" t="inlineStr"/>
+      <c r="X50" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="B51" t="n">
-        <v>7490</v>
+        <v>7550</v>
       </c>
       <c r="C51" t="n">
-        <v>7541</v>
+        <v>7820.25</v>
       </c>
       <c r="D51" t="n">
-        <v>7324</v>
+        <v>7542.75</v>
       </c>
       <c r="E51" t="n">
-        <v>7519.25</v>
+        <v>7779.75</v>
       </c>
       <c r="F51" t="n">
-        <v>71.75</v>
+        <v>260.5</v>
       </c>
       <c r="G51" s="5" t="n">
-        <v>0.009599999999999999</v>
+        <v>0.0346</v>
       </c>
       <c r="H51" t="n">
-        <v>217</v>
+        <v>277.5</v>
       </c>
       <c r="I51" t="n">
-        <v>7260</v>
+        <v>7107</v>
       </c>
       <c r="J51" t="n">
-        <v>7275.69</v>
+        <v>7345.62</v>
       </c>
       <c r="K51" t="n">
-        <v>7371.62</v>
+        <v>7410.75</v>
       </c>
       <c r="L51" t="n">
-        <v>7467.56</v>
+        <v>7475.88</v>
       </c>
       <c r="M51" t="n">
-        <v>7523.38</v>
+        <v>7627.75</v>
       </c>
       <c r="N51" t="n">
-        <v>7579.19</v>
+        <v>7779.62</v>
       </c>
       <c r="O51" t="n">
-        <v>7715.25</v>
+        <v>7758</v>
       </c>
       <c r="P51" s="6" t="n">
         <v/>
@@ -4783,85 +4779,83 @@
       <c r="Q51" s="6" t="n">
         <v/>
       </c>
-      <c r="R51" s="6" t="inlineStr">
+      <c r="R51" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S51" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T51" s="8" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="S51" s="7" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T51" s="8" t="inlineStr">
+      <c r="U51" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="U51" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V51" s="8" t="n">
-        <v/>
-      </c>
-      <c r="W51" s="11" t="inlineStr">
-        <is>
-          <t>空方</t>
-        </is>
-      </c>
-      <c r="X51" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="V51" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="W51" s="9" t="inlineStr">
+        <is>
+          <t>多方</t>
+        </is>
+      </c>
+      <c r="X51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="B52" t="n">
-        <v>7550</v>
+        <v>7776.75</v>
       </c>
       <c r="C52" t="n">
-        <v>7820.25</v>
+        <v>7838.5</v>
       </c>
       <c r="D52" t="n">
-        <v>7542.75</v>
+        <v>7738</v>
       </c>
       <c r="E52" t="n">
-        <v>7779.75</v>
+        <v>7805</v>
       </c>
       <c r="F52" t="n">
-        <v>260.5</v>
+        <v>25.25</v>
       </c>
       <c r="G52" s="5" t="n">
-        <v>0.0346</v>
+        <v>0.0032</v>
       </c>
       <c r="H52" t="n">
-        <v>277.5</v>
+        <v>100.5</v>
       </c>
       <c r="I52" t="n">
-        <v>7107</v>
+        <v>7265.25</v>
       </c>
       <c r="J52" t="n">
-        <v>7345.62</v>
+        <v>7551.38</v>
       </c>
       <c r="K52" t="n">
-        <v>7410.75</v>
+        <v>7641</v>
       </c>
       <c r="L52" t="n">
-        <v>7475.88</v>
+        <v>7730.62</v>
       </c>
       <c r="M52" t="n">
-        <v>7627.75</v>
+        <v>7918.5</v>
       </c>
       <c r="N52" t="n">
-        <v>7779.62</v>
+        <v>8106.38</v>
       </c>
       <c r="O52" t="n">
-        <v>7758</v>
+        <v>8097.75</v>
       </c>
       <c r="P52" s="6" t="n">
         <v/>
@@ -4874,23 +4868,17 @@
       </c>
       <c r="S52" s="7" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T52" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U52" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="V52" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T52" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U52" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V52" s="8" t="n">
+        <v/>
       </c>
       <c r="W52" s="9" t="inlineStr">
         <is>
@@ -4902,63 +4890,67 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="B53" t="n">
-        <v>7776.75</v>
+        <v>7809.25</v>
       </c>
       <c r="C53" t="n">
-        <v>7838.5</v>
+        <v>7824.5</v>
       </c>
       <c r="D53" t="n">
-        <v>7738</v>
+        <v>7657.75</v>
       </c>
       <c r="E53" t="n">
-        <v>7805</v>
+        <v>7691.25</v>
       </c>
       <c r="F53" t="n">
-        <v>25.25</v>
+        <v>-113.75</v>
       </c>
       <c r="G53" s="5" t="n">
-        <v>0.0032</v>
+        <v>-0.0146</v>
       </c>
       <c r="H53" t="n">
-        <v>100.5</v>
+        <v>166.75</v>
       </c>
       <c r="I53" t="n">
-        <v>7265.25</v>
+        <v>7637.5</v>
       </c>
       <c r="J53" t="n">
-        <v>7551.38</v>
+        <v>7712.88</v>
       </c>
       <c r="K53" t="n">
-        <v>7641</v>
+        <v>7754.75</v>
       </c>
       <c r="L53" t="n">
-        <v>7730.62</v>
+        <v>7796.62</v>
       </c>
       <c r="M53" t="n">
-        <v>7918.5</v>
+        <v>7855.25</v>
       </c>
       <c r="N53" t="n">
-        <v>8106.38</v>
+        <v>7913.88</v>
       </c>
       <c r="O53" t="n">
-        <v>8097.75</v>
+        <v>7939</v>
       </c>
       <c r="P53" s="6" t="n">
         <v/>
       </c>
-      <c r="Q53" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R53" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S53" s="7" t="inlineStr">
-        <is>
-          <t>↑C</t>
+      <c r="Q53" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="R53" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S53" s="10" t="inlineStr">
+        <is>
+          <t>↓</t>
         </is>
       </c>
       <c r="T53" s="8" t="n">
@@ -4970,9 +4962,9 @@
       <c r="V53" s="8" t="n">
         <v/>
       </c>
-      <c r="W53" s="9" t="inlineStr">
-        <is>
-          <t>多方</t>
+      <c r="W53" s="11" t="inlineStr">
+        <is>
+          <t>空方</t>
         </is>
       </c>
       <c r="X53" t="inlineStr"/>
@@ -4980,72 +4972,70 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="B54" t="n">
-        <v>7809.25</v>
+        <v>7693.5</v>
       </c>
       <c r="C54" t="n">
-        <v>7824.5</v>
+        <v>7782.5</v>
       </c>
       <c r="D54" t="n">
-        <v>7657.75</v>
+        <v>7655</v>
       </c>
       <c r="E54" t="n">
-        <v>7691.25</v>
+        <v>7722</v>
       </c>
       <c r="F54" t="n">
-        <v>-113.75</v>
+        <v>30.75</v>
       </c>
       <c r="G54" s="5" t="n">
-        <v>-0.0146</v>
+        <v>0.004</v>
       </c>
       <c r="H54" t="n">
-        <v>166.75</v>
+        <v>127.5</v>
       </c>
       <c r="I54" t="n">
-        <v>7637.5</v>
+        <v>7491</v>
       </c>
       <c r="J54" t="n">
-        <v>7712.88</v>
+        <v>7499.56</v>
       </c>
       <c r="K54" t="n">
-        <v>7754.75</v>
+        <v>7607.88</v>
       </c>
       <c r="L54" t="n">
-        <v>7796.62</v>
+        <v>7716.19</v>
       </c>
       <c r="M54" t="n">
-        <v>7855.25</v>
+        <v>7774.62</v>
       </c>
       <c r="N54" t="n">
-        <v>7913.88</v>
+        <v>7833.06</v>
       </c>
       <c r="O54" t="n">
-        <v>7939</v>
+        <v>7991.25</v>
       </c>
       <c r="P54" s="6" t="n">
         <v/>
       </c>
-      <c r="Q54" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="R54" s="6" t="inlineStr">
+      <c r="Q54" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R54" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S54" s="7" t="inlineStr">
+        <is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T54" s="8" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="S54" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T54" s="8" t="n">
-        <v/>
-      </c>
       <c r="U54" s="8" t="n">
         <v/>
       </c>
@@ -5057,55 +5047,59 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X54" t="inlineStr"/>
+      <c r="X54" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="B55" t="n">
-        <v>7693.5</v>
+        <v>7723.5</v>
       </c>
       <c r="C55" t="n">
-        <v>7782.5</v>
+        <v>7766.5</v>
       </c>
       <c r="D55" t="n">
-        <v>7655</v>
+        <v>7618.5</v>
       </c>
       <c r="E55" t="n">
         <v>7722</v>
       </c>
       <c r="F55" t="n">
-        <v>30.75</v>
+        <v>0</v>
       </c>
       <c r="G55" s="5" t="n">
-        <v>0.004</v>
+        <v>0</v>
       </c>
       <c r="H55" t="n">
-        <v>127.5</v>
+        <v>148</v>
       </c>
       <c r="I55" t="n">
-        <v>7491</v>
+        <v>7527.5</v>
       </c>
       <c r="J55" t="n">
-        <v>7499.56</v>
+        <v>7596.12</v>
       </c>
       <c r="K55" t="n">
-        <v>7607.88</v>
+        <v>7658.25</v>
       </c>
       <c r="L55" t="n">
-        <v>7716.19</v>
+        <v>7720.38</v>
       </c>
       <c r="M55" t="n">
-        <v>7774.62</v>
+        <v>7785.75</v>
       </c>
       <c r="N55" t="n">
-        <v>7833.06</v>
+        <v>7851.12</v>
       </c>
       <c r="O55" t="n">
-        <v>7991.25</v>
+        <v>7910</v>
       </c>
       <c r="P55" s="6" t="n">
         <v/>
@@ -5113,18 +5107,18 @@
       <c r="Q55" s="6" t="n">
         <v/>
       </c>
-      <c r="R55" s="6" t="n">
-        <v/>
+      <c r="R55" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S55" s="7" t="inlineStr">
         <is>
           <t>↑C</t>
         </is>
       </c>
-      <c r="T55" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="T55" s="8" t="n">
+        <v/>
       </c>
       <c r="U55" s="8" t="n">
         <v/>
@@ -5137,74 +5131,72 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X55" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="X55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="B56" t="n">
-        <v>7723.5</v>
+        <v>7715.5</v>
       </c>
       <c r="C56" t="n">
-        <v>7766.5</v>
+        <v>7728.5</v>
       </c>
       <c r="D56" t="n">
-        <v>7618.5</v>
+        <v>7585.5</v>
       </c>
       <c r="E56" t="n">
-        <v>7722</v>
+        <v>7659.5</v>
       </c>
       <c r="F56" t="n">
-        <v>0</v>
+        <v>-62.5</v>
       </c>
       <c r="G56" s="5" t="n">
-        <v>0</v>
+        <v>-0.0081</v>
       </c>
       <c r="H56" t="n">
-        <v>148</v>
+        <v>143</v>
       </c>
       <c r="I56" t="n">
-        <v>7527.5</v>
+        <v>7470.5</v>
       </c>
       <c r="J56" t="n">
-        <v>7596.12</v>
+        <v>7588.75</v>
       </c>
       <c r="K56" t="n">
-        <v>7658.25</v>
+        <v>7648</v>
       </c>
       <c r="L56" t="n">
-        <v>7720.38</v>
+        <v>7707.25</v>
       </c>
       <c r="M56" t="n">
-        <v>7785.75</v>
+        <v>7796</v>
       </c>
       <c r="N56" t="n">
-        <v>7851.12</v>
+        <v>7884.75</v>
       </c>
       <c r="O56" t="n">
-        <v>7910</v>
+        <v>7914.5</v>
       </c>
       <c r="P56" s="6" t="n">
         <v/>
       </c>
-      <c r="Q56" s="6" t="n">
-        <v/>
+      <c r="Q56" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="R56" s="6" t="inlineStr">
         <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S56" s="7" t="inlineStr">
-        <is>
-          <t>↑C</t>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="S56" s="10" t="inlineStr">
+        <is>
+          <t>↓</t>
         </is>
       </c>
       <c r="T56" s="8" t="n">
@@ -5226,50 +5218,50 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="B57" t="n">
-        <v>7715.5</v>
+        <v>7609.25</v>
       </c>
       <c r="C57" t="n">
-        <v>7728.5</v>
+        <v>7724.25</v>
       </c>
       <c r="D57" t="n">
-        <v>7585.5</v>
+        <v>7509.25</v>
       </c>
       <c r="E57" t="n">
-        <v>7659.5</v>
+        <v>7712.5</v>
       </c>
       <c r="F57" t="n">
-        <v>-62.5</v>
+        <v>53</v>
       </c>
       <c r="G57" s="5" t="n">
-        <v>-0.0081</v>
+        <v>0.0069</v>
       </c>
       <c r="H57" t="n">
-        <v>143</v>
+        <v>215</v>
       </c>
       <c r="I57" t="n">
-        <v>7470.5</v>
+        <v>7442.5</v>
       </c>
       <c r="J57" t="n">
-        <v>7588.75</v>
+        <v>7517.75</v>
       </c>
       <c r="K57" t="n">
-        <v>7648</v>
+        <v>7588</v>
       </c>
       <c r="L57" t="n">
-        <v>7707.25</v>
+        <v>7658.25</v>
       </c>
       <c r="M57" t="n">
-        <v>7796</v>
+        <v>7731</v>
       </c>
       <c r="N57" t="n">
-        <v>7884.75</v>
+        <v>7803.75</v>
       </c>
       <c r="O57" t="n">
-        <v>7914.5</v>
+        <v>7871.5</v>
       </c>
       <c r="P57" s="6" t="n">
         <v/>
@@ -5281,17 +5273,19 @@
       </c>
       <c r="R57" s="6" t="inlineStr">
         <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S57" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T57" s="8" t="inlineStr">
+        <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="S57" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T57" s="8" t="n">
-        <v/>
-      </c>
       <c r="U57" s="8" t="n">
         <v/>
       </c>
@@ -5303,91 +5297,7 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X57" t="inlineStr"/>
-    </row>
-    <row r="58">
-      <c r="A58" t="inlineStr">
-        <is>
-          <t>2026-09-14</t>
-        </is>
-      </c>
-      <c r="B58" t="n">
-        <v>7609.25</v>
-      </c>
-      <c r="C58" t="n">
-        <v>7704.25</v>
-      </c>
-      <c r="D58" t="n">
-        <v>7509.25</v>
-      </c>
-      <c r="E58" t="n">
-        <v>7700.5</v>
-      </c>
-      <c r="F58" t="n">
-        <v>41</v>
-      </c>
-      <c r="G58" s="5" t="n">
-        <v>0.0054</v>
-      </c>
-      <c r="H58" t="n">
-        <v>195</v>
-      </c>
-      <c r="I58" t="n">
-        <v>7442.5</v>
-      </c>
-      <c r="J58" t="n">
-        <v>7517.75</v>
-      </c>
-      <c r="K58" t="n">
-        <v>7588</v>
-      </c>
-      <c r="L58" t="n">
-        <v>7658.25</v>
-      </c>
-      <c r="M58" t="n">
-        <v>7731</v>
-      </c>
-      <c r="N58" t="n">
-        <v>7803.75</v>
-      </c>
-      <c r="O58" t="n">
-        <v>7871.5</v>
-      </c>
-      <c r="P58" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q58" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="R58" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S58" s="7" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T58" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="U58" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V58" s="8" t="n">
-        <v/>
-      </c>
-      <c r="W58" s="11" t="inlineStr">
-        <is>
-          <t>空方</t>
-        </is>
-      </c>
-      <c r="X58" t="inlineStr">
+      <c r="X57" t="inlineStr">
         <is>
           <t>弱警訊</t>
         </is>

--- a/three_gate/analysis/ES_weekly.xlsx
+++ b/three_gate/analysis/ES_weekly.xlsx
@@ -480,7 +480,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X57"/>
+  <dimension ref="A1:X58"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -5225,22 +5225,22 @@
         <v>7609.25</v>
       </c>
       <c r="C57" t="n">
-        <v>7724.25</v>
+        <v>7670.25</v>
       </c>
       <c r="D57" t="n">
         <v>7509.25</v>
       </c>
       <c r="E57" t="n">
-        <v>7712.5</v>
+        <v>7657.35</v>
       </c>
       <c r="F57" t="n">
-        <v>53</v>
+        <v>-2.15</v>
       </c>
       <c r="G57" s="5" t="n">
-        <v>0.0069</v>
+        <v>-0.0003</v>
       </c>
       <c r="H57" t="n">
-        <v>215</v>
+        <v>161</v>
       </c>
       <c r="I57" t="n">
         <v>7442.5</v>
@@ -5276,30 +5276,110 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="S57" s="7" t="inlineStr">
+      <c r="S57" s="10" t="inlineStr">
+        <is>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T57" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U57" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V57" s="8" t="n">
+        <v/>
+      </c>
+      <c r="W57" s="11" t="inlineStr">
+        <is>
+          <t>空方</t>
+        </is>
+      </c>
+      <c r="X57" t="inlineStr"/>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="B58" t="n">
+        <v>7830</v>
+      </c>
+      <c r="C58" t="n">
+        <v>7833</v>
+      </c>
+      <c r="D58" t="n">
+        <v>7829</v>
+      </c>
+      <c r="E58" t="n">
+        <v>7832.5</v>
+      </c>
+      <c r="F58" t="n">
+        <v>175.15</v>
+      </c>
+      <c r="G58" s="5" t="n">
+        <v>0.0229</v>
+      </c>
+      <c r="H58" t="n">
+        <v>4</v>
+      </c>
+      <c r="I58" t="n">
+        <v>7348.25</v>
+      </c>
+      <c r="J58" t="n">
+        <v>7530.15</v>
+      </c>
+      <c r="K58" t="n">
+        <v>7576.85</v>
+      </c>
+      <c r="L58" t="n">
+        <v>7623.55</v>
+      </c>
+      <c r="M58" t="n">
+        <v>7737.85</v>
+      </c>
+      <c r="N58" t="n">
+        <v>7852.15</v>
+      </c>
+      <c r="O58" t="n">
+        <v>7831.25</v>
+      </c>
+      <c r="P58" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q58" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R58" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S58" s="7" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
       </c>
-      <c r="T57" s="8" t="inlineStr">
+      <c r="T58" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U58" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V58" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="U57" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V57" s="8" t="n">
-        <v/>
-      </c>
-      <c r="W57" s="11" t="inlineStr">
+      <c r="W58" s="11" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
       </c>
-      <c r="X57" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
+      <c r="X58" t="inlineStr">
+        <is>
+          <t>強警訊</t>
         </is>
       </c>
     </row>

--- a/three_gate/analysis/ES_weekly.xlsx
+++ b/three_gate/analysis/ES_weekly.xlsx
@@ -5304,25 +5304,25 @@
         </is>
       </c>
       <c r="B58" t="n">
-        <v>7830</v>
+        <v>7722</v>
       </c>
       <c r="C58" t="n">
-        <v>7833</v>
+        <v>7848.5</v>
       </c>
       <c r="D58" t="n">
-        <v>7829</v>
+        <v>7713.75</v>
       </c>
       <c r="E58" t="n">
-        <v>7832.5</v>
+        <v>7837.5</v>
       </c>
       <c r="F58" t="n">
-        <v>175.15</v>
+        <v>180.15</v>
       </c>
       <c r="G58" s="5" t="n">
-        <v>0.0229</v>
+        <v>0.0235</v>
       </c>
       <c r="H58" t="n">
-        <v>4</v>
+        <v>134.75</v>
       </c>
       <c r="I58" t="n">
         <v>7348.25</v>

--- a/three_gate/analysis/ES_weekly.xlsx
+++ b/three_gate/analysis/ES_weekly.xlsx
@@ -5313,13 +5313,13 @@
         <v>7713.75</v>
       </c>
       <c r="E58" t="n">
-        <v>7837.5</v>
+        <v>7829.75</v>
       </c>
       <c r="F58" t="n">
-        <v>180.15</v>
+        <v>172.4</v>
       </c>
       <c r="G58" s="5" t="n">
-        <v>0.0235</v>
+        <v>0.0225</v>
       </c>
       <c r="H58" t="n">
         <v>134.75</v>

--- a/three_gate/analysis/ES_weekly.xlsx
+++ b/three_gate/analysis/ES_weekly.xlsx
@@ -5307,22 +5307,22 @@
         <v>7722</v>
       </c>
       <c r="C58" t="n">
-        <v>7848.5</v>
+        <v>7847.25</v>
       </c>
       <c r="D58" t="n">
         <v>7713.75</v>
       </c>
       <c r="E58" t="n">
-        <v>7829.75</v>
+        <v>7830.75</v>
       </c>
       <c r="F58" t="n">
-        <v>172.4</v>
+        <v>173.4</v>
       </c>
       <c r="G58" s="5" t="n">
-        <v>0.0225</v>
+        <v>0.0226</v>
       </c>
       <c r="H58" t="n">
-        <v>134.75</v>
+        <v>133.5</v>
       </c>
       <c r="I58" t="n">
         <v>7348.25</v>

--- a/three_gate/analysis/ES_weekly.xlsx
+++ b/three_gate/analysis/ES_weekly.xlsx
@@ -5313,13 +5313,13 @@
         <v>7713.75</v>
       </c>
       <c r="E58" t="n">
-        <v>7830.75</v>
+        <v>7832.75</v>
       </c>
       <c r="F58" t="n">
-        <v>173.4</v>
+        <v>175.4</v>
       </c>
       <c r="G58" s="5" t="n">
-        <v>0.0226</v>
+        <v>0.0229</v>
       </c>
       <c r="H58" t="n">
         <v>133.5</v>

--- a/three_gate/analysis/ES_weekly.xlsx
+++ b/three_gate/analysis/ES_weekly.xlsx
@@ -5313,13 +5313,13 @@
         <v>7713.75</v>
       </c>
       <c r="E58" t="n">
-        <v>7832.75</v>
+        <v>7831.25</v>
       </c>
       <c r="F58" t="n">
-        <v>175.4</v>
+        <v>173.9</v>
       </c>
       <c r="G58" s="5" t="n">
-        <v>0.0229</v>
+        <v>0.0227</v>
       </c>
       <c r="H58" t="n">
         <v>133.5</v>

--- a/three_gate/analysis/ES_weekly.xlsx
+++ b/three_gate/analysis/ES_weekly.xlsx
@@ -5307,22 +5307,22 @@
         <v>7722</v>
       </c>
       <c r="C58" t="n">
-        <v>7847.25</v>
+        <v>7848.5</v>
       </c>
       <c r="D58" t="n">
         <v>7713.75</v>
       </c>
       <c r="E58" t="n">
-        <v>7831.25</v>
+        <v>7831.5</v>
       </c>
       <c r="F58" t="n">
-        <v>173.9</v>
+        <v>174.15</v>
       </c>
       <c r="G58" s="5" t="n">
         <v>0.0227</v>
       </c>
       <c r="H58" t="n">
-        <v>133.5</v>
+        <v>134.75</v>
       </c>
       <c r="I58" t="n">
         <v>7348.25</v>

--- a/three_gate/analysis/ES_weekly.xlsx
+++ b/three_gate/analysis/ES_weekly.xlsx
@@ -5313,13 +5313,13 @@
         <v>7713.75</v>
       </c>
       <c r="E58" t="n">
-        <v>7831.5</v>
+        <v>7834.25</v>
       </c>
       <c r="F58" t="n">
-        <v>174.15</v>
+        <v>176.9</v>
       </c>
       <c r="G58" s="5" t="n">
-        <v>0.0227</v>
+        <v>0.0231</v>
       </c>
       <c r="H58" t="n">
         <v>134.75</v>

--- a/three_gate/analysis/ES_weekly.xlsx
+++ b/three_gate/analysis/ES_weekly.xlsx
@@ -5313,13 +5313,13 @@
         <v>7713.75</v>
       </c>
       <c r="E58" t="n">
-        <v>7834.25</v>
+        <v>7820.75</v>
       </c>
       <c r="F58" t="n">
-        <v>176.9</v>
+        <v>163.4</v>
       </c>
       <c r="G58" s="5" t="n">
-        <v>0.0231</v>
+        <v>0.0213</v>
       </c>
       <c r="H58" t="n">
         <v>134.75</v>

--- a/three_gate/analysis/ES_weekly.xlsx
+++ b/three_gate/analysis/ES_weekly.xlsx
@@ -5313,13 +5313,13 @@
         <v>7713.75</v>
       </c>
       <c r="E58" t="n">
-        <v>7820.75</v>
+        <v>7777.25</v>
       </c>
       <c r="F58" t="n">
-        <v>163.4</v>
+        <v>119.9</v>
       </c>
       <c r="G58" s="5" t="n">
-        <v>0.0213</v>
+        <v>0.0157</v>
       </c>
       <c r="H58" t="n">
         <v>134.75</v>
@@ -5361,15 +5361,15 @@
       </c>
       <c r="T58" s="8" t="inlineStr">
         <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="U58" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V58" s="8" t="inlineStr">
+        <is>
           <t>✓</t>
-        </is>
-      </c>
-      <c r="U58" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V58" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
         </is>
       </c>
       <c r="W58" s="11" t="inlineStr">

--- a/three_gate/analysis/ES_weekly.xlsx
+++ b/three_gate/analysis/ES_weekly.xlsx
@@ -659,25 +659,25 @@
         <v>92.25</v>
       </c>
       <c r="I2" t="n">
-        <v>6229.25</v>
+        <v>6231.75</v>
       </c>
       <c r="J2" t="n">
-        <v>6376.62</v>
+        <v>6377.56</v>
       </c>
       <c r="K2" t="n">
-        <v>6416.5</v>
+        <v>6417.12</v>
       </c>
       <c r="L2" t="n">
-        <v>6456.38</v>
+        <v>6456.69</v>
       </c>
       <c r="M2" t="n">
-        <v>6550</v>
+        <v>6549.38</v>
       </c>
       <c r="N2" t="n">
-        <v>6643.62</v>
+        <v>6642.06</v>
       </c>
       <c r="O2" t="n">
-        <v>6629.75</v>
+        <v>6628.5</v>
       </c>
       <c r="P2" s="6" t="n">
         <v/>
@@ -5313,13 +5313,13 @@
         <v>7713.75</v>
       </c>
       <c r="E58" t="n">
-        <v>7777.25</v>
+        <v>7759</v>
       </c>
       <c r="F58" t="n">
-        <v>119.9</v>
+        <v>101.65</v>
       </c>
       <c r="G58" s="5" t="n">
-        <v>0.0157</v>
+        <v>0.0133</v>
       </c>
       <c r="H58" t="n">
         <v>134.75</v>

--- a/three_gate/analysis/ES_weekly.xlsx
+++ b/three_gate/analysis/ES_weekly.xlsx
@@ -480,7 +480,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X58"/>
+  <dimension ref="A1:X57"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -634,67 +634,73 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2025-08-25</t>
+          <t>2025-09-01</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>6493</v>
+        <v>6478.75</v>
       </c>
       <c r="C2" t="n">
-        <v>6523</v>
+        <v>6541.75</v>
       </c>
       <c r="D2" t="n">
-        <v>6430.75</v>
+        <v>6371.75</v>
       </c>
       <c r="E2" t="n">
-        <v>6472.75</v>
+        <v>6489.75</v>
       </c>
       <c r="F2" t="n">
-        <v>-10.5</v>
+        <v>17</v>
       </c>
       <c r="G2" s="5" t="n">
-        <v>-0.0016</v>
+        <v>0.0026</v>
       </c>
       <c r="H2" t="n">
-        <v>92.25</v>
+        <v>170</v>
       </c>
       <c r="I2" t="n">
-        <v>6231.75</v>
+        <v>6338.5</v>
       </c>
       <c r="J2" t="n">
-        <v>6377.56</v>
+        <v>6378.44</v>
       </c>
       <c r="K2" t="n">
-        <v>6417.12</v>
+        <v>6426.62</v>
       </c>
       <c r="L2" t="n">
-        <v>6456.69</v>
+        <v>6474.81</v>
       </c>
       <c r="M2" t="n">
-        <v>6549.38</v>
+        <v>6518.88</v>
       </c>
       <c r="N2" t="n">
-        <v>6642.06</v>
+        <v>6562.94</v>
       </c>
       <c r="O2" t="n">
-        <v>6628.5</v>
+        <v>6615.25</v>
       </c>
       <c r="P2" s="6" t="n">
         <v/>
       </c>
-      <c r="Q2" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R2" s="6" t="n">
-        <v/>
+      <c r="Q2" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="R2" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S2" s="7" t="inlineStr">
         <is>
           <t>↑C</t>
         </is>
       </c>
-      <c r="T2" s="8" t="n">
-        <v/>
+      <c r="T2" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="U2" s="8" t="n">
         <v/>
@@ -716,72 +722,68 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2025-09-01</t>
+          <t>2025-09-08</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>6478.75</v>
+        <v>6483.75</v>
       </c>
       <c r="C3" t="n">
-        <v>6541.75</v>
+        <v>6606</v>
       </c>
       <c r="D3" t="n">
-        <v>6371.75</v>
+        <v>6480.25</v>
       </c>
       <c r="E3" t="n">
-        <v>6489.75</v>
+        <v>6588.25</v>
       </c>
       <c r="F3" t="n">
-        <v>17</v>
+        <v>98.5</v>
       </c>
       <c r="G3" s="5" t="n">
-        <v>0.0026</v>
+        <v>0.0152</v>
       </c>
       <c r="H3" t="n">
-        <v>170</v>
+        <v>125.75</v>
       </c>
       <c r="I3" t="n">
-        <v>6338.5</v>
+        <v>6201.75</v>
       </c>
       <c r="J3" t="n">
-        <v>6378.44</v>
+        <v>6336.25</v>
       </c>
       <c r="K3" t="n">
-        <v>6426.62</v>
+        <v>6404.75</v>
       </c>
       <c r="L3" t="n">
-        <v>6474.81</v>
+        <v>6473.25</v>
       </c>
       <c r="M3" t="n">
-        <v>6518.88</v>
+        <v>6574.75</v>
       </c>
       <c r="N3" t="n">
-        <v>6562.94</v>
+        <v>6676.25</v>
       </c>
       <c r="O3" t="n">
-        <v>6615.25</v>
+        <v>6711.75</v>
       </c>
       <c r="P3" s="6" t="n">
         <v/>
       </c>
-      <c r="Q3" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="R3" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="Q3" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R3" s="6" t="n">
+        <v/>
       </c>
       <c r="S3" s="7" t="inlineStr">
         <is>
-          <t>↑C</t>
+          <t>↑</t>
         </is>
       </c>
       <c r="T3" s="8" t="inlineStr">
         <is>
-          <t>✓</t>
+          <t>△C</t>
         </is>
       </c>
       <c r="U3" s="8" t="n">
@@ -795,59 +797,55 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X3" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="X3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2025-09-08</t>
+          <t>2025-09-15</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>6483.75</v>
+        <v>6588.25</v>
       </c>
       <c r="C4" t="n">
-        <v>6606</v>
+        <v>6662</v>
       </c>
       <c r="D4" t="n">
-        <v>6480.25</v>
+        <v>6554</v>
       </c>
       <c r="E4" t="n">
-        <v>6588.25</v>
+        <v>6658.77</v>
       </c>
       <c r="F4" t="n">
-        <v>98.5</v>
+        <v>70.52</v>
       </c>
       <c r="G4" s="5" t="n">
-        <v>0.0152</v>
+        <v>0.0107</v>
       </c>
       <c r="H4" t="n">
-        <v>125.75</v>
+        <v>108</v>
       </c>
       <c r="I4" t="n">
-        <v>6201.75</v>
+        <v>6354.5</v>
       </c>
       <c r="J4" t="n">
-        <v>6336.25</v>
+        <v>6485.06</v>
       </c>
       <c r="K4" t="n">
-        <v>6404.75</v>
+        <v>6525.38</v>
       </c>
       <c r="L4" t="n">
-        <v>6473.25</v>
+        <v>6565.69</v>
       </c>
       <c r="M4" t="n">
-        <v>6574.75</v>
+        <v>6651.12</v>
       </c>
       <c r="N4" t="n">
-        <v>6676.25</v>
+        <v>6736.56</v>
       </c>
       <c r="O4" t="n">
-        <v>6711.75</v>
+        <v>6731.75</v>
       </c>
       <c r="P4" s="6" t="n">
         <v/>
@@ -884,50 +882,50 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2025-09-15</t>
+          <t>2025-09-22</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>6588.25</v>
+        <v>6716</v>
       </c>
       <c r="C5" t="n">
-        <v>6662</v>
+        <v>6756.75</v>
       </c>
       <c r="D5" t="n">
-        <v>6554</v>
+        <v>6624.25</v>
       </c>
       <c r="E5" t="n">
-        <v>6658.77</v>
+        <v>6696.5</v>
       </c>
       <c r="F5" t="n">
-        <v>70.52</v>
+        <v>37.73</v>
       </c>
       <c r="G5" s="5" t="n">
-        <v>0.0107</v>
+        <v>0.0057</v>
       </c>
       <c r="H5" t="n">
-        <v>108</v>
+        <v>132.5</v>
       </c>
       <c r="I5" t="n">
-        <v>6354.5</v>
+        <v>6446</v>
       </c>
       <c r="J5" t="n">
-        <v>6485.06</v>
+        <v>6576.16</v>
       </c>
       <c r="K5" t="n">
-        <v>6525.38</v>
+        <v>6604.77</v>
       </c>
       <c r="L5" t="n">
-        <v>6565.69</v>
+        <v>6633.39</v>
       </c>
       <c r="M5" t="n">
-        <v>6651.12</v>
+        <v>6712.77</v>
       </c>
       <c r="N5" t="n">
-        <v>6736.56</v>
+        <v>6792.16</v>
       </c>
       <c r="O5" t="n">
-        <v>6731.75</v>
+        <v>6770</v>
       </c>
       <c r="P5" s="6" t="n">
         <v/>
@@ -964,50 +962,50 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2025-09-22</t>
+          <t>2025-09-29</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>6716</v>
+        <v>6697</v>
       </c>
       <c r="C6" t="n">
-        <v>6756.75</v>
+        <v>6800</v>
       </c>
       <c r="D6" t="n">
-        <v>6624.25</v>
+        <v>6680</v>
       </c>
       <c r="E6" t="n">
-        <v>6696.5</v>
+        <v>6764</v>
       </c>
       <c r="F6" t="n">
-        <v>37.73</v>
+        <v>67.5</v>
       </c>
       <c r="G6" s="5" t="n">
-        <v>0.0057</v>
+        <v>0.0101</v>
       </c>
       <c r="H6" t="n">
-        <v>132.5</v>
+        <v>120</v>
       </c>
       <c r="I6" t="n">
-        <v>6446</v>
+        <v>6491.75</v>
       </c>
       <c r="J6" t="n">
-        <v>6576.16</v>
+        <v>6567</v>
       </c>
       <c r="K6" t="n">
-        <v>6604.77</v>
+        <v>6630.25</v>
       </c>
       <c r="L6" t="n">
-        <v>6633.39</v>
+        <v>6693.5</v>
       </c>
       <c r="M6" t="n">
-        <v>6712.77</v>
+        <v>6762.75</v>
       </c>
       <c r="N6" t="n">
-        <v>6792.16</v>
+        <v>6832</v>
       </c>
       <c r="O6" t="n">
-        <v>6770</v>
+        <v>6889.25</v>
       </c>
       <c r="P6" s="6" t="n">
         <v/>
@@ -1044,154 +1042,158 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2025-09-29</t>
+          <t>2025-10-06</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>6697</v>
+        <v>6768</v>
       </c>
       <c r="C7" t="n">
-        <v>6800</v>
+        <v>6812.25</v>
       </c>
       <c r="D7" t="n">
-        <v>6680</v>
+        <v>6540.25</v>
       </c>
       <c r="E7" t="n">
-        <v>6764</v>
+        <v>6595.25</v>
       </c>
       <c r="F7" t="n">
-        <v>67.5</v>
+        <v>-168.75</v>
       </c>
       <c r="G7" s="5" t="n">
-        <v>0.0101</v>
+        <v>-0.0249</v>
       </c>
       <c r="H7" t="n">
-        <v>120</v>
+        <v>272</v>
       </c>
       <c r="I7" t="n">
-        <v>6491.75</v>
+        <v>6560</v>
       </c>
       <c r="J7" t="n">
-        <v>6567</v>
+        <v>6656</v>
       </c>
       <c r="K7" t="n">
-        <v>6630.25</v>
+        <v>6704</v>
       </c>
       <c r="L7" t="n">
-        <v>6693.5</v>
+        <v>6752</v>
       </c>
       <c r="M7" t="n">
-        <v>6762.75</v>
+        <v>6824</v>
       </c>
       <c r="N7" t="n">
-        <v>6832</v>
+        <v>6896</v>
       </c>
       <c r="O7" t="n">
-        <v>6889.25</v>
-      </c>
-      <c r="P7" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q7" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R7" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S7" s="7" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T7" s="8" t="inlineStr">
+        <v>6920</v>
+      </c>
+      <c r="P7" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
+      <c r="Q7" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="R7" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S7" s="10" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T7" s="8" t="n">
+        <v/>
+      </c>
       <c r="U7" s="8" t="n">
         <v/>
       </c>
       <c r="V7" s="8" t="n">
         <v/>
       </c>
-      <c r="W7" s="9" t="inlineStr">
-        <is>
-          <t>多方</t>
-        </is>
-      </c>
-      <c r="X7" t="inlineStr"/>
+      <c r="W7" s="11" t="inlineStr">
+        <is>
+          <t>空方</t>
+        </is>
+      </c>
+      <c r="X7" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2025-10-06</t>
+          <t>2025-10-13</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>6768</v>
+        <v>6632</v>
       </c>
       <c r="C8" t="n">
-        <v>6812.25</v>
+        <v>6766.75</v>
       </c>
       <c r="D8" t="n">
-        <v>6540.25</v>
+        <v>6571.25</v>
       </c>
       <c r="E8" t="n">
-        <v>6595.25</v>
+        <v>6702.5</v>
       </c>
       <c r="F8" t="n">
-        <v>-168.75</v>
+        <v>107.25</v>
       </c>
       <c r="G8" s="5" t="n">
-        <v>-0.0249</v>
+        <v>0.0163</v>
       </c>
       <c r="H8" t="n">
-        <v>272</v>
+        <v>195.5</v>
       </c>
       <c r="I8" t="n">
-        <v>6560</v>
+        <v>6268.25</v>
       </c>
       <c r="J8" t="n">
-        <v>6656</v>
+        <v>6282.75</v>
       </c>
       <c r="K8" t="n">
-        <v>6704</v>
+        <v>6459.25</v>
       </c>
       <c r="L8" t="n">
-        <v>6752</v>
+        <v>6635.75</v>
       </c>
       <c r="M8" t="n">
-        <v>6824</v>
+        <v>6731.25</v>
       </c>
       <c r="N8" t="n">
-        <v>6896</v>
+        <v>6826.75</v>
       </c>
       <c r="O8" t="n">
-        <v>6920</v>
-      </c>
-      <c r="P8" s="6" t="inlineStr">
+        <v>7084.25</v>
+      </c>
+      <c r="P8" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q8" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R8" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S8" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T8" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="Q8" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="R8" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S8" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T8" s="8" t="n">
-        <v/>
-      </c>
       <c r="U8" s="8" t="n">
         <v/>
       </c>
@@ -1205,57 +1207,57 @@
       </c>
       <c r="X8" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2025-10-13</t>
+          <t>2025-10-20</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>6632</v>
+        <v>6721</v>
       </c>
       <c r="C9" t="n">
-        <v>6766.75</v>
+        <v>6841.25</v>
       </c>
       <c r="D9" t="n">
-        <v>6571.25</v>
+        <v>6690.75</v>
       </c>
       <c r="E9" t="n">
-        <v>6702.5</v>
+        <v>6827</v>
       </c>
       <c r="F9" t="n">
-        <v>107.25</v>
+        <v>124.5</v>
       </c>
       <c r="G9" s="5" t="n">
-        <v>0.0163</v>
+        <v>0.0186</v>
       </c>
       <c r="H9" t="n">
-        <v>195.5</v>
+        <v>150.5</v>
       </c>
       <c r="I9" t="n">
-        <v>6268.25</v>
+        <v>6375.75</v>
       </c>
       <c r="J9" t="n">
-        <v>6282.75</v>
+        <v>6523.75</v>
       </c>
       <c r="K9" t="n">
-        <v>6459.25</v>
+        <v>6604.75</v>
       </c>
       <c r="L9" t="n">
-        <v>6635.75</v>
+        <v>6685.75</v>
       </c>
       <c r="M9" t="n">
-        <v>6731.25</v>
+        <v>6800.25</v>
       </c>
       <c r="N9" t="n">
-        <v>6826.75</v>
+        <v>6914.75</v>
       </c>
       <c r="O9" t="n">
-        <v>7084.25</v>
+        <v>6962.25</v>
       </c>
       <c r="P9" s="6" t="n">
         <v/>
@@ -1289,57 +1291,57 @@
       </c>
       <c r="X9" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2025-10-20</t>
+          <t>2025-10-27</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>6721</v>
+        <v>6881</v>
       </c>
       <c r="C10" t="n">
-        <v>6841.25</v>
+        <v>6953.75</v>
       </c>
       <c r="D10" t="n">
-        <v>6690.75</v>
+        <v>6843.5</v>
       </c>
       <c r="E10" t="n">
-        <v>6827</v>
+        <v>6874</v>
       </c>
       <c r="F10" t="n">
-        <v>124.5</v>
+        <v>47</v>
       </c>
       <c r="G10" s="5" t="n">
-        <v>0.0186</v>
+        <v>0.0069</v>
       </c>
       <c r="H10" t="n">
-        <v>150.5</v>
+        <v>110.25</v>
       </c>
       <c r="I10" t="n">
-        <v>6375.75</v>
+        <v>6540.25</v>
       </c>
       <c r="J10" t="n">
-        <v>6523.75</v>
+        <v>6707</v>
       </c>
       <c r="K10" t="n">
-        <v>6604.75</v>
+        <v>6751.75</v>
       </c>
       <c r="L10" t="n">
-        <v>6685.75</v>
+        <v>6796.5</v>
       </c>
       <c r="M10" t="n">
-        <v>6800.25</v>
+        <v>6902.25</v>
       </c>
       <c r="N10" t="n">
-        <v>6914.75</v>
+        <v>7008</v>
       </c>
       <c r="O10" t="n">
-        <v>6962.25</v>
+        <v>6991.75</v>
       </c>
       <c r="P10" s="6" t="n">
         <v/>
@@ -1380,70 +1382,74 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2025-10-27</t>
+          <t>2025-11-03</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>6881</v>
+        <v>6878</v>
       </c>
       <c r="C11" t="n">
-        <v>6953.75</v>
+        <v>6909.5</v>
       </c>
       <c r="D11" t="n">
-        <v>6843.5</v>
+        <v>6655.5</v>
       </c>
       <c r="E11" t="n">
-        <v>6874</v>
+        <v>6753.75</v>
       </c>
       <c r="F11" t="n">
-        <v>47</v>
+        <v>-120.25</v>
       </c>
       <c r="G11" s="5" t="n">
-        <v>0.0069</v>
+        <v>-0.0175</v>
       </c>
       <c r="H11" t="n">
-        <v>110.25</v>
+        <v>254</v>
       </c>
       <c r="I11" t="n">
-        <v>6540.25</v>
+        <v>6733.25</v>
       </c>
       <c r="J11" t="n">
-        <v>6707</v>
+        <v>6751.44</v>
       </c>
       <c r="K11" t="n">
-        <v>6751.75</v>
+        <v>6818.88</v>
       </c>
       <c r="L11" t="n">
-        <v>6796.5</v>
+        <v>6886.31</v>
       </c>
       <c r="M11" t="n">
-        <v>6902.25</v>
+        <v>6929.12</v>
       </c>
       <c r="N11" t="n">
-        <v>7008</v>
+        <v>6971.94</v>
       </c>
       <c r="O11" t="n">
-        <v>6991.75</v>
-      </c>
-      <c r="P11" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q11" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R11" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S11" s="7" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T11" s="8" t="inlineStr">
+        <v>7064</v>
+      </c>
+      <c r="P11" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="Q11" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
+      <c r="R11" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S11" s="10" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T11" s="8" t="n">
+        <v/>
+      </c>
       <c r="U11" s="8" t="n">
         <v/>
       </c>
@@ -1455,83 +1461,75 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X11" t="inlineStr">
-        <is>
-          <t>強警訊</t>
-        </is>
-      </c>
+      <c r="X11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2025-11-03</t>
+          <t>2025-11-10</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>6878</v>
+        <v>6788</v>
       </c>
       <c r="C12" t="n">
-        <v>6909.5</v>
+        <v>6900.5</v>
       </c>
       <c r="D12" t="n">
-        <v>6655.5</v>
+        <v>6670.5</v>
       </c>
       <c r="E12" t="n">
-        <v>6753.75</v>
+        <v>6755.25</v>
       </c>
       <c r="F12" t="n">
-        <v>-120.25</v>
+        <v>1.5</v>
       </c>
       <c r="G12" s="5" t="n">
-        <v>-0.0175</v>
+        <v>0.0002</v>
       </c>
       <c r="H12" t="n">
-        <v>254</v>
+        <v>230</v>
       </c>
       <c r="I12" t="n">
-        <v>6733.25</v>
+        <v>6401.5</v>
       </c>
       <c r="J12" t="n">
-        <v>6751.44</v>
+        <v>6485.38</v>
       </c>
       <c r="K12" t="n">
-        <v>6818.88</v>
+        <v>6626.75</v>
       </c>
       <c r="L12" t="n">
-        <v>6886.31</v>
+        <v>6768.12</v>
       </c>
       <c r="M12" t="n">
-        <v>6929.12</v>
+        <v>6880.75</v>
       </c>
       <c r="N12" t="n">
-        <v>6971.94</v>
+        <v>6993.38</v>
       </c>
       <c r="O12" t="n">
-        <v>7064</v>
-      </c>
-      <c r="P12" s="6" t="inlineStr">
+        <v>7163.5</v>
+      </c>
+      <c r="P12" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q12" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R12" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S12" s="10" t="inlineStr">
+        <is>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T12" s="8" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="Q12" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="R12" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S12" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T12" s="8" t="n">
-        <v/>
-      </c>
       <c r="U12" s="8" t="n">
         <v/>
       </c>
@@ -1543,55 +1541,59 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X12" t="inlineStr"/>
+      <c r="X12" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2025-11-10</t>
+          <t>2025-11-17</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>6788</v>
+        <v>6764.75</v>
       </c>
       <c r="C13" t="n">
-        <v>6900.5</v>
+        <v>6801.5</v>
       </c>
       <c r="D13" t="n">
-        <v>6670.5</v>
+        <v>6525</v>
       </c>
       <c r="E13" t="n">
-        <v>6755.25</v>
+        <v>6620.25</v>
       </c>
       <c r="F13" t="n">
-        <v>1.5</v>
+        <v>-135</v>
       </c>
       <c r="G13" s="5" t="n">
-        <v>0.0002</v>
+        <v>-0.02</v>
       </c>
       <c r="H13" t="n">
-        <v>230</v>
+        <v>276.5</v>
       </c>
       <c r="I13" t="n">
-        <v>6401.5</v>
+        <v>6440.5</v>
       </c>
       <c r="J13" t="n">
-        <v>6485.38</v>
+        <v>6510.12</v>
       </c>
       <c r="K13" t="n">
-        <v>6626.75</v>
+        <v>6640.25</v>
       </c>
       <c r="L13" t="n">
-        <v>6768.12</v>
+        <v>6770.38</v>
       </c>
       <c r="M13" t="n">
-        <v>6880.75</v>
+        <v>6870.25</v>
       </c>
       <c r="N13" t="n">
-        <v>6993.38</v>
+        <v>6970.12</v>
       </c>
       <c r="O13" t="n">
-        <v>7163.5</v>
+        <v>7130.5</v>
       </c>
       <c r="P13" s="6" t="n">
         <v/>
@@ -1599,18 +1601,18 @@
       <c r="Q13" s="6" t="n">
         <v/>
       </c>
-      <c r="R13" s="6" t="n">
-        <v/>
+      <c r="R13" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="S13" s="10" t="inlineStr">
         <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T13" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T13" s="8" t="n">
+        <v/>
       </c>
       <c r="U13" s="8" t="n">
         <v/>
@@ -1623,59 +1625,55 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X13" t="inlineStr">
-        <is>
-          <t>中警訊</t>
-        </is>
-      </c>
+      <c r="X13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2025-11-17</t>
+          <t>2025-11-24</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>6764.75</v>
+        <v>6654.75</v>
       </c>
       <c r="C14" t="n">
-        <v>6801.5</v>
+        <v>6863.75</v>
       </c>
       <c r="D14" t="n">
-        <v>6525</v>
+        <v>6625</v>
       </c>
       <c r="E14" t="n">
-        <v>6620.25</v>
+        <v>6859.5</v>
       </c>
       <c r="F14" t="n">
-        <v>-135</v>
+        <v>239.25</v>
       </c>
       <c r="G14" s="5" t="n">
-        <v>-0.02</v>
+        <v>0.0361</v>
       </c>
       <c r="H14" t="n">
-        <v>276.5</v>
+        <v>238.75</v>
       </c>
       <c r="I14" t="n">
-        <v>6440.5</v>
+        <v>6248.5</v>
       </c>
       <c r="J14" t="n">
-        <v>6510.12</v>
+        <v>6322.25</v>
       </c>
       <c r="K14" t="n">
-        <v>6640.25</v>
+        <v>6482</v>
       </c>
       <c r="L14" t="n">
-        <v>6770.38</v>
+        <v>6641.75</v>
       </c>
       <c r="M14" t="n">
-        <v>6870.25</v>
+        <v>6758.5</v>
       </c>
       <c r="N14" t="n">
-        <v>6970.12</v>
+        <v>6875.25</v>
       </c>
       <c r="O14" t="n">
-        <v>7130.5</v>
+        <v>7078</v>
       </c>
       <c r="P14" s="6" t="n">
         <v/>
@@ -1683,22 +1681,24 @@
       <c r="Q14" s="6" t="n">
         <v/>
       </c>
-      <c r="R14" s="6" t="inlineStr">
+      <c r="R14" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S14" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T14" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U14" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="S14" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T14" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U14" s="8" t="n">
-        <v/>
-      </c>
       <c r="V14" s="8" t="n">
         <v/>
       </c>
@@ -1707,55 +1707,59 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X14" t="inlineStr"/>
+      <c r="X14" t="inlineStr">
+        <is>
+          <t>強警訊</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2025-11-24</t>
+          <t>2025-12-01</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>6654.75</v>
+        <v>6854.75</v>
       </c>
       <c r="C15" t="n">
-        <v>6863.75</v>
+        <v>6905</v>
       </c>
       <c r="D15" t="n">
-        <v>6625</v>
+        <v>6802</v>
       </c>
       <c r="E15" t="n">
-        <v>6859.5</v>
+        <v>6878.25</v>
       </c>
       <c r="F15" t="n">
-        <v>239.25</v>
+        <v>18.75</v>
       </c>
       <c r="G15" s="5" t="n">
-        <v>0.0361</v>
+        <v>0.0027</v>
       </c>
       <c r="H15" t="n">
-        <v>238.75</v>
+        <v>103</v>
       </c>
       <c r="I15" t="n">
-        <v>6248.5</v>
+        <v>6386.25</v>
       </c>
       <c r="J15" t="n">
-        <v>6322.25</v>
+        <v>6678.31</v>
       </c>
       <c r="K15" t="n">
-        <v>6482</v>
+        <v>6740.12</v>
       </c>
       <c r="L15" t="n">
-        <v>6641.75</v>
+        <v>6801.94</v>
       </c>
       <c r="M15" t="n">
-        <v>6758.5</v>
+        <v>6978.88</v>
       </c>
       <c r="N15" t="n">
-        <v>6875.25</v>
+        <v>7155.81</v>
       </c>
       <c r="O15" t="n">
-        <v>7078</v>
+        <v>7102.5</v>
       </c>
       <c r="P15" s="6" t="n">
         <v/>
@@ -1768,18 +1772,14 @@
       </c>
       <c r="S15" s="7" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T15" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U15" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T15" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U15" s="8" t="n">
+        <v/>
       </c>
       <c r="V15" s="8" t="n">
         <v/>
@@ -1798,50 +1798,50 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2025-12-01</t>
+          <t>2025-12-08</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>6854.75</v>
+        <v>6883</v>
       </c>
       <c r="C16" t="n">
-        <v>6905</v>
+        <v>6928.75</v>
       </c>
       <c r="D16" t="n">
-        <v>6802</v>
+        <v>6805</v>
       </c>
       <c r="E16" t="n">
-        <v>6878.25</v>
+        <v>6830.75</v>
       </c>
       <c r="F16" t="n">
-        <v>18.75</v>
+        <v>-47.5</v>
       </c>
       <c r="G16" s="5" t="n">
-        <v>0.0027</v>
+        <v>-0.0069</v>
       </c>
       <c r="H16" t="n">
-        <v>103</v>
+        <v>123.75</v>
       </c>
       <c r="I16" t="n">
-        <v>6386.25</v>
+        <v>6699</v>
       </c>
       <c r="J16" t="n">
-        <v>6678.31</v>
+        <v>6787.62</v>
       </c>
       <c r="K16" t="n">
-        <v>6740.12</v>
+        <v>6826.75</v>
       </c>
       <c r="L16" t="n">
-        <v>6801.94</v>
+        <v>6865.88</v>
       </c>
       <c r="M16" t="n">
-        <v>6978.88</v>
+        <v>6929.75</v>
       </c>
       <c r="N16" t="n">
-        <v>7155.81</v>
+        <v>6993.62</v>
       </c>
       <c r="O16" t="n">
-        <v>7102.5</v>
+        <v>7008</v>
       </c>
       <c r="P16" s="6" t="n">
         <v/>
@@ -1849,12 +1849,14 @@
       <c r="Q16" s="6" t="n">
         <v/>
       </c>
-      <c r="R16" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S16" s="7" t="inlineStr">
-        <is>
-          <t>↑C</t>
+      <c r="R16" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="S16" s="10" t="inlineStr">
+        <is>
+          <t>↓</t>
         </is>
       </c>
       <c r="T16" s="8" t="n">
@@ -1873,57 +1875,57 @@
       </c>
       <c r="X16" t="inlineStr">
         <is>
-          <t>強警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2025-12-08</t>
+          <t>2025-12-15</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>6883</v>
+        <v>6831</v>
       </c>
       <c r="C17" t="n">
-        <v>6928.75</v>
+        <v>6872.5</v>
       </c>
       <c r="D17" t="n">
-        <v>6805</v>
+        <v>6720.25</v>
       </c>
       <c r="E17" t="n">
-        <v>6830.75</v>
+        <v>6796.54</v>
       </c>
       <c r="F17" t="n">
-        <v>-47.5</v>
+        <v>-34.21</v>
       </c>
       <c r="G17" s="5" t="n">
-        <v>-0.0069</v>
+        <v>-0.005</v>
       </c>
       <c r="H17" t="n">
-        <v>123.75</v>
+        <v>152.25</v>
       </c>
       <c r="I17" t="n">
-        <v>6699</v>
+        <v>6681.25</v>
       </c>
       <c r="J17" t="n">
-        <v>6787.62</v>
+        <v>6688.94</v>
       </c>
       <c r="K17" t="n">
-        <v>6826.75</v>
+        <v>6768.88</v>
       </c>
       <c r="L17" t="n">
-        <v>6865.88</v>
+        <v>6848.81</v>
       </c>
       <c r="M17" t="n">
-        <v>6929.75</v>
+        <v>6892.62</v>
       </c>
       <c r="N17" t="n">
-        <v>6993.62</v>
+        <v>6936.44</v>
       </c>
       <c r="O17" t="n">
-        <v>7008</v>
+        <v>7052.5</v>
       </c>
       <c r="P17" s="6" t="n">
         <v/>
@@ -1955,59 +1957,55 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X17" t="inlineStr">
-        <is>
-          <t>中警訊</t>
-        </is>
-      </c>
+      <c r="X17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2025-12-15</t>
+          <t>2025-12-22</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>6831</v>
+        <v>6906.25</v>
       </c>
       <c r="C18" t="n">
-        <v>6872.5</v>
+        <v>6994</v>
       </c>
       <c r="D18" t="n">
-        <v>6720.25</v>
+        <v>6900.5</v>
       </c>
       <c r="E18" t="n">
-        <v>6796.54</v>
+        <v>6979.25</v>
       </c>
       <c r="F18" t="n">
-        <v>-34.21</v>
+        <v>182.71</v>
       </c>
       <c r="G18" s="5" t="n">
-        <v>-0.005</v>
+        <v>0.0269</v>
       </c>
       <c r="H18" t="n">
-        <v>152.25</v>
+        <v>93.5</v>
       </c>
       <c r="I18" t="n">
-        <v>6681.25</v>
+        <v>6568</v>
       </c>
       <c r="J18" t="n">
-        <v>6688.94</v>
+        <v>6644.37</v>
       </c>
       <c r="K18" t="n">
-        <v>6768.88</v>
+        <v>6720.42</v>
       </c>
       <c r="L18" t="n">
-        <v>6848.81</v>
+        <v>6796.46</v>
       </c>
       <c r="M18" t="n">
-        <v>6892.62</v>
+        <v>6872.67</v>
       </c>
       <c r="N18" t="n">
-        <v>6936.44</v>
+        <v>6948.87</v>
       </c>
       <c r="O18" t="n">
-        <v>7052.5</v>
+        <v>7024.75</v>
       </c>
       <c r="P18" s="6" t="n">
         <v/>
@@ -2015,28 +2013,30 @@
       <c r="Q18" s="6" t="n">
         <v/>
       </c>
-      <c r="R18" s="6" t="inlineStr">
+      <c r="R18" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S18" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T18" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U18" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="S18" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T18" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U18" s="8" t="n">
-        <v/>
-      </c>
       <c r="V18" s="8" t="n">
         <v/>
       </c>
-      <c r="W18" s="11" t="inlineStr">
-        <is>
-          <t>空方</t>
+      <c r="W18" s="9" t="inlineStr">
+        <is>
+          <t>多方</t>
         </is>
       </c>
       <c r="X18" t="inlineStr"/>
@@ -2044,81 +2044,81 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2025-12-22</t>
+          <t>2025-12-29</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>6906.25</v>
+        <v>6980.5</v>
       </c>
       <c r="C19" t="n">
-        <v>6994</v>
+        <v>6984.75</v>
       </c>
       <c r="D19" t="n">
+        <v>6866.75</v>
+      </c>
+      <c r="E19" t="n">
         <v>6900.5</v>
       </c>
-      <c r="E19" t="n">
-        <v>6979.25</v>
-      </c>
       <c r="F19" t="n">
-        <v>182.71</v>
+        <v>-78.75</v>
       </c>
       <c r="G19" s="5" t="n">
-        <v>0.0269</v>
+        <v>-0.0113</v>
       </c>
       <c r="H19" t="n">
-        <v>93.5</v>
+        <v>118</v>
       </c>
       <c r="I19" t="n">
-        <v>6568</v>
+        <v>6807</v>
       </c>
       <c r="J19" t="n">
-        <v>6644.37</v>
+        <v>6901.75</v>
       </c>
       <c r="K19" t="n">
-        <v>6720.42</v>
+        <v>6932.5</v>
       </c>
       <c r="L19" t="n">
-        <v>6796.46</v>
+        <v>6963.25</v>
       </c>
       <c r="M19" t="n">
-        <v>6872.67</v>
+        <v>7026</v>
       </c>
       <c r="N19" t="n">
-        <v>6948.87</v>
+        <v>7088.75</v>
       </c>
       <c r="O19" t="n">
-        <v>7024.75</v>
+        <v>7087.5</v>
       </c>
       <c r="P19" s="6" t="n">
         <v/>
       </c>
-      <c r="Q19" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R19" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S19" s="7" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T19" s="8" t="inlineStr">
+      <c r="Q19" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="R19" s="6" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="U19" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+      <c r="S19" s="10" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T19" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U19" s="8" t="n">
+        <v/>
       </c>
       <c r="V19" s="8" t="n">
         <v/>
       </c>
-      <c r="W19" s="9" t="inlineStr">
-        <is>
-          <t>多方</t>
+      <c r="W19" s="11" t="inlineStr">
+        <is>
+          <t>空方</t>
         </is>
       </c>
       <c r="X19" t="inlineStr"/>
@@ -2126,75 +2126,75 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2025-12-29</t>
+          <t>2026-01-05</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>6980.5</v>
+        <v>6911.5</v>
       </c>
       <c r="C20" t="n">
-        <v>6984.75</v>
+        <v>7017.5</v>
       </c>
       <c r="D20" t="n">
-        <v>6866.75</v>
+        <v>6899.5</v>
       </c>
       <c r="E20" t="n">
-        <v>6900.5</v>
+        <v>7005</v>
       </c>
       <c r="F20" t="n">
-        <v>-78.75</v>
+        <v>104.5</v>
       </c>
       <c r="G20" s="5" t="n">
-        <v>-0.0113</v>
+        <v>0.0151</v>
       </c>
       <c r="H20" t="n">
         <v>118</v>
       </c>
       <c r="I20" t="n">
-        <v>6807</v>
+        <v>6748.75</v>
       </c>
       <c r="J20" t="n">
-        <v>6901.75</v>
+        <v>6769.88</v>
       </c>
       <c r="K20" t="n">
-        <v>6932.5</v>
+        <v>6841.5</v>
       </c>
       <c r="L20" t="n">
-        <v>6963.25</v>
+        <v>6913.12</v>
       </c>
       <c r="M20" t="n">
-        <v>7026</v>
+        <v>6959.5</v>
       </c>
       <c r="N20" t="n">
-        <v>7088.75</v>
+        <v>7005.88</v>
       </c>
       <c r="O20" t="n">
-        <v>7087.5</v>
+        <v>7102.75</v>
       </c>
       <c r="P20" s="6" t="n">
         <v/>
       </c>
-      <c r="Q20" s="6" t="inlineStr">
+      <c r="Q20" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R20" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S20" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T20" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U20" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="R20" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S20" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T20" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U20" s="8" t="n">
-        <v/>
-      </c>
       <c r="V20" s="8" t="n">
         <v/>
       </c>
@@ -2203,55 +2203,59 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X20" t="inlineStr"/>
+      <c r="X20" t="inlineStr">
+        <is>
+          <t>強警訊</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-01-05</t>
+          <t>2026-01-12</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>6911.5</v>
+        <v>7007</v>
       </c>
       <c r="C21" t="n">
-        <v>7017.5</v>
+        <v>7036.25</v>
       </c>
       <c r="D21" t="n">
-        <v>6899.5</v>
+        <v>6923.25</v>
       </c>
       <c r="E21" t="n">
-        <v>7005</v>
+        <v>6976.75</v>
       </c>
       <c r="F21" t="n">
-        <v>104.5</v>
+        <v>-28.25</v>
       </c>
       <c r="G21" s="5" t="n">
-        <v>0.0151</v>
+        <v>-0.004</v>
       </c>
       <c r="H21" t="n">
-        <v>118</v>
+        <v>113</v>
       </c>
       <c r="I21" t="n">
-        <v>6748.75</v>
+        <v>6781.5</v>
       </c>
       <c r="J21" t="n">
-        <v>6769.88</v>
+        <v>6910.25</v>
       </c>
       <c r="K21" t="n">
-        <v>6841.5</v>
+        <v>6946</v>
       </c>
       <c r="L21" t="n">
-        <v>6913.12</v>
+        <v>6981.75</v>
       </c>
       <c r="M21" t="n">
-        <v>6959.5</v>
+        <v>7064</v>
       </c>
       <c r="N21" t="n">
-        <v>7005.88</v>
+        <v>7146.25</v>
       </c>
       <c r="O21" t="n">
-        <v>7102.75</v>
+        <v>7135.5</v>
       </c>
       <c r="P21" s="6" t="n">
         <v/>
@@ -2259,23 +2263,21 @@
       <c r="Q21" s="6" t="n">
         <v/>
       </c>
-      <c r="R21" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S21" s="7" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T21" s="8" t="inlineStr">
+      <c r="R21" s="6" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="U21" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+      <c r="S21" s="10" t="inlineStr">
+        <is>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T21" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U21" s="8" t="n">
+        <v/>
       </c>
       <c r="V21" s="8" t="n">
         <v/>
@@ -2287,72 +2289,74 @@
       </c>
       <c r="X21" t="inlineStr">
         <is>
-          <t>強警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2026-01-12</t>
+          <t>2026-01-19</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>7007</v>
+        <v>6918.25</v>
       </c>
       <c r="C22" t="n">
-        <v>7036.25</v>
+        <v>6969</v>
       </c>
       <c r="D22" t="n">
-        <v>6923.25</v>
+        <v>6814.5</v>
       </c>
       <c r="E22" t="n">
-        <v>6976.75</v>
+        <v>6945.75</v>
       </c>
       <c r="F22" t="n">
-        <v>-28.25</v>
+        <v>-31</v>
       </c>
       <c r="G22" s="5" t="n">
-        <v>-0.004</v>
+        <v>-0.0044</v>
       </c>
       <c r="H22" t="n">
-        <v>113</v>
+        <v>154.5</v>
       </c>
       <c r="I22" t="n">
-        <v>6781.5</v>
+        <v>6810.25</v>
       </c>
       <c r="J22" t="n">
-        <v>6910.25</v>
+        <v>6862.25</v>
       </c>
       <c r="K22" t="n">
-        <v>6946</v>
+        <v>6920.25</v>
       </c>
       <c r="L22" t="n">
-        <v>6981.75</v>
+        <v>6978.25</v>
       </c>
       <c r="M22" t="n">
-        <v>7064</v>
+        <v>7033.25</v>
       </c>
       <c r="N22" t="n">
-        <v>7146.25</v>
+        <v>7088.25</v>
       </c>
       <c r="O22" t="n">
-        <v>7135.5</v>
+        <v>7149.25</v>
       </c>
       <c r="P22" s="6" t="n">
         <v/>
       </c>
-      <c r="Q22" s="6" t="n">
-        <v/>
+      <c r="Q22" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="R22" s="6" t="inlineStr">
         <is>
-          <t>✓</t>
+          <t>△C</t>
         </is>
       </c>
       <c r="S22" s="10" t="inlineStr">
         <is>
-          <t>↓C</t>
+          <t>↓</t>
         </is>
       </c>
       <c r="T22" s="8" t="n">
@@ -2369,81 +2373,75 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X22" t="inlineStr">
-        <is>
-          <t>中警訊</t>
-        </is>
-      </c>
+      <c r="X22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-01-19</t>
+          <t>2026-01-26</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>6918.25</v>
+        <v>6904</v>
       </c>
       <c r="C23" t="n">
-        <v>6969</v>
+        <v>7043</v>
       </c>
       <c r="D23" t="n">
-        <v>6814.5</v>
+        <v>6879</v>
       </c>
       <c r="E23" t="n">
-        <v>6945.75</v>
+        <v>6965.75</v>
       </c>
       <c r="F23" t="n">
-        <v>-31</v>
+        <v>20</v>
       </c>
       <c r="G23" s="5" t="n">
-        <v>-0.0044</v>
+        <v>0.0029</v>
       </c>
       <c r="H23" t="n">
-        <v>154.5</v>
+        <v>164</v>
       </c>
       <c r="I23" t="n">
-        <v>6810.25</v>
+        <v>6660</v>
       </c>
       <c r="J23" t="n">
-        <v>6862.25</v>
+        <v>6818.25</v>
       </c>
       <c r="K23" t="n">
-        <v>6920.25</v>
+        <v>6868.5</v>
       </c>
       <c r="L23" t="n">
-        <v>6978.25</v>
+        <v>6918.75</v>
       </c>
       <c r="M23" t="n">
-        <v>7033.25</v>
+        <v>7023</v>
       </c>
       <c r="N23" t="n">
-        <v>7088.25</v>
+        <v>7127.25</v>
       </c>
       <c r="O23" t="n">
-        <v>7149.25</v>
+        <v>7123.5</v>
       </c>
       <c r="P23" s="6" t="n">
         <v/>
       </c>
-      <c r="Q23" s="6" t="inlineStr">
+      <c r="Q23" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R23" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S23" s="7" t="inlineStr">
+        <is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T23" s="8" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="R23" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="S23" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T23" s="8" t="n">
-        <v/>
-      </c>
       <c r="U23" s="8" t="n">
         <v/>
       </c>
@@ -2455,75 +2453,81 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X23" t="inlineStr"/>
+      <c r="X23" t="inlineStr">
+        <is>
+          <t>強警訊</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2026-01-26</t>
+          <t>2026-02-02</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>6904</v>
+        <v>6938.5</v>
       </c>
       <c r="C24" t="n">
-        <v>7043</v>
+        <v>7027.25</v>
       </c>
       <c r="D24" t="n">
-        <v>6879</v>
+        <v>6751.5</v>
       </c>
       <c r="E24" t="n">
-        <v>6965.75</v>
+        <v>6952.75</v>
       </c>
       <c r="F24" t="n">
-        <v>20</v>
+        <v>-13</v>
       </c>
       <c r="G24" s="5" t="n">
-        <v>0.0029</v>
+        <v>-0.0019</v>
       </c>
       <c r="H24" t="n">
-        <v>164</v>
+        <v>275.75</v>
       </c>
       <c r="I24" t="n">
-        <v>6660</v>
+        <v>6715</v>
       </c>
       <c r="J24" t="n">
-        <v>6818.25</v>
+        <v>6804.12</v>
       </c>
       <c r="K24" t="n">
-        <v>6868.5</v>
+        <v>6883.75</v>
       </c>
       <c r="L24" t="n">
-        <v>6918.75</v>
+        <v>6963.38</v>
       </c>
       <c r="M24" t="n">
-        <v>7023</v>
+        <v>7047.75</v>
       </c>
       <c r="N24" t="n">
-        <v>7127.25</v>
+        <v>7132.12</v>
       </c>
       <c r="O24" t="n">
-        <v>7123.5</v>
+        <v>7207</v>
       </c>
       <c r="P24" s="6" t="n">
         <v/>
       </c>
-      <c r="Q24" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R24" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S24" s="7" t="inlineStr">
-        <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T24" s="8" t="inlineStr">
+      <c r="Q24" s="6" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
+      <c r="R24" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S24" s="10" t="inlineStr">
+        <is>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T24" s="8" t="n">
+        <v/>
+      </c>
       <c r="U24" s="8" t="n">
         <v/>
       </c>
@@ -2535,76 +2539,70 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X24" t="inlineStr">
-        <is>
-          <t>強警訊</t>
-        </is>
-      </c>
+      <c r="X24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-02-02</t>
+          <t>2026-02-09</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>6938.5</v>
+        <v>6960.25</v>
       </c>
       <c r="C25" t="n">
-        <v>7027.25</v>
+        <v>7011.5</v>
       </c>
       <c r="D25" t="n">
-        <v>6751.5</v>
+        <v>6808.75</v>
       </c>
       <c r="E25" t="n">
-        <v>6952.75</v>
+        <v>6850.5</v>
       </c>
       <c r="F25" t="n">
-        <v>-13</v>
+        <v>-102.25</v>
       </c>
       <c r="G25" s="5" t="n">
-        <v>-0.0019</v>
+        <v>-0.0147</v>
       </c>
       <c r="H25" t="n">
-        <v>275.75</v>
+        <v>202.75</v>
       </c>
       <c r="I25" t="n">
-        <v>6715</v>
+        <v>6475.75</v>
       </c>
       <c r="J25" t="n">
-        <v>6804.12</v>
+        <v>6708.69</v>
       </c>
       <c r="K25" t="n">
-        <v>6883.75</v>
+        <v>6814.88</v>
       </c>
       <c r="L25" t="n">
-        <v>6963.38</v>
+        <v>6921.06</v>
       </c>
       <c r="M25" t="n">
-        <v>7047.75</v>
+        <v>7090.62</v>
       </c>
       <c r="N25" t="n">
-        <v>7132.12</v>
+        <v>7260.19</v>
       </c>
       <c r="O25" t="n">
-        <v>7207</v>
+        <v>7303</v>
       </c>
       <c r="P25" s="6" t="n">
         <v/>
       </c>
-      <c r="Q25" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="Q25" s="6" t="n">
+        <v/>
       </c>
       <c r="R25" s="6" t="inlineStr">
         <is>
-          <t>✓</t>
+          <t>△C</t>
         </is>
       </c>
       <c r="S25" s="10" t="inlineStr">
         <is>
-          <t>↓C</t>
+          <t>↓</t>
         </is>
       </c>
       <c r="T25" s="8" t="n">
@@ -2621,55 +2619,59 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X25" t="inlineStr"/>
+      <c r="X25" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2026-02-09</t>
+          <t>2026-02-16</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>6960.25</v>
+        <v>6852.5</v>
       </c>
       <c r="C26" t="n">
-        <v>7011.5</v>
+        <v>6931.5</v>
       </c>
       <c r="D26" t="n">
-        <v>6808.75</v>
+        <v>6791</v>
       </c>
       <c r="E26" t="n">
-        <v>6850.5</v>
+        <v>6923.25</v>
       </c>
       <c r="F26" t="n">
-        <v>-102.25</v>
+        <v>72.75</v>
       </c>
       <c r="G26" s="5" t="n">
-        <v>-0.0147</v>
+        <v>0.0106</v>
       </c>
       <c r="H26" t="n">
-        <v>202.75</v>
+        <v>140.5</v>
       </c>
       <c r="I26" t="n">
-        <v>6475.75</v>
+        <v>6606</v>
       </c>
       <c r="J26" t="n">
-        <v>6708.69</v>
+        <v>6617.94</v>
       </c>
       <c r="K26" t="n">
-        <v>6814.88</v>
+        <v>6749.12</v>
       </c>
       <c r="L26" t="n">
-        <v>6921.06</v>
+        <v>6880.31</v>
       </c>
       <c r="M26" t="n">
-        <v>7090.62</v>
+        <v>6951.88</v>
       </c>
       <c r="N26" t="n">
-        <v>7260.19</v>
+        <v>7023.44</v>
       </c>
       <c r="O26" t="n">
-        <v>7303</v>
+        <v>7214.25</v>
       </c>
       <c r="P26" s="6" t="n">
         <v/>
@@ -2677,18 +2679,18 @@
       <c r="Q26" s="6" t="n">
         <v/>
       </c>
-      <c r="R26" s="6" t="inlineStr">
+      <c r="R26" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S26" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T26" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
-      </c>
-      <c r="S26" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T26" s="8" t="n">
-        <v/>
       </c>
       <c r="U26" s="8" t="n">
         <v/>
@@ -2710,50 +2712,50 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-02-16</t>
+          <t>2026-02-23</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>6852.5</v>
+        <v>6918</v>
       </c>
       <c r="C27" t="n">
-        <v>6931.5</v>
+        <v>6983.75</v>
       </c>
       <c r="D27" t="n">
-        <v>6791</v>
+        <v>6828.5</v>
       </c>
       <c r="E27" t="n">
-        <v>6923.25</v>
+        <v>6889</v>
       </c>
       <c r="F27" t="n">
-        <v>72.75</v>
+        <v>-34.25</v>
       </c>
       <c r="G27" s="5" t="n">
-        <v>0.0106</v>
+        <v>-0.0049</v>
       </c>
       <c r="H27" t="n">
-        <v>140.5</v>
+        <v>155.25</v>
       </c>
       <c r="I27" t="n">
-        <v>6606</v>
+        <v>6650.5</v>
       </c>
       <c r="J27" t="n">
-        <v>6617.94</v>
+        <v>6813.75</v>
       </c>
       <c r="K27" t="n">
-        <v>6749.12</v>
+        <v>6853</v>
       </c>
       <c r="L27" t="n">
-        <v>6880.31</v>
+        <v>6892.25</v>
       </c>
       <c r="M27" t="n">
-        <v>6951.88</v>
+        <v>6993.5</v>
       </c>
       <c r="N27" t="n">
-        <v>7023.44</v>
+        <v>7094.75</v>
       </c>
       <c r="O27" t="n">
-        <v>7214.25</v>
+        <v>7072</v>
       </c>
       <c r="P27" s="6" t="n">
         <v/>
@@ -2761,18 +2763,18 @@
       <c r="Q27" s="6" t="n">
         <v/>
       </c>
-      <c r="R27" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S27" s="7" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T27" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+      <c r="R27" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S27" s="10" t="inlineStr">
+        <is>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T27" s="8" t="n">
+        <v/>
       </c>
       <c r="U27" s="8" t="n">
         <v/>
@@ -2787,63 +2789,65 @@
       </c>
       <c r="X27" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2026-02-23</t>
+          <t>2026-03-02</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>6918</v>
+        <v>6820</v>
       </c>
       <c r="C28" t="n">
-        <v>6983.75</v>
+        <v>6911.25</v>
       </c>
       <c r="D28" t="n">
-        <v>6828.5</v>
+        <v>6715.75</v>
       </c>
       <c r="E28" t="n">
-        <v>6889</v>
+        <v>6743.75</v>
       </c>
       <c r="F28" t="n">
-        <v>-34.25</v>
+        <v>-145.25</v>
       </c>
       <c r="G28" s="5" t="n">
-        <v>-0.0049</v>
+        <v>-0.0211</v>
       </c>
       <c r="H28" t="n">
-        <v>155.25</v>
+        <v>195.5</v>
       </c>
       <c r="I28" t="n">
-        <v>6650.5</v>
+        <v>6673.25</v>
       </c>
       <c r="J28" t="n">
-        <v>6813.75</v>
+        <v>6725.19</v>
       </c>
       <c r="K28" t="n">
-        <v>6853</v>
+        <v>6811.38</v>
       </c>
       <c r="L28" t="n">
-        <v>6892.25</v>
+        <v>6897.56</v>
       </c>
       <c r="M28" t="n">
-        <v>6993.5</v>
+        <v>6966.62</v>
       </c>
       <c r="N28" t="n">
-        <v>7094.75</v>
+        <v>7035.69</v>
       </c>
       <c r="O28" t="n">
-        <v>7072</v>
+        <v>7139</v>
       </c>
       <c r="P28" s="6" t="n">
         <v/>
       </c>
-      <c r="Q28" s="6" t="n">
-        <v/>
+      <c r="Q28" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="R28" s="6" t="inlineStr">
         <is>
@@ -2852,7 +2856,7 @@
       </c>
       <c r="S28" s="10" t="inlineStr">
         <is>
-          <t>↓C</t>
+          <t>↓</t>
         </is>
       </c>
       <c r="T28" s="8" t="n">
@@ -2869,80 +2873,76 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X28" t="inlineStr">
-        <is>
-          <t>中警訊</t>
-        </is>
-      </c>
+      <c r="X28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-09</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>6820</v>
+        <v>6685.5</v>
       </c>
       <c r="C29" t="n">
-        <v>6911.25</v>
+        <v>6852</v>
       </c>
       <c r="D29" t="n">
-        <v>6715.75</v>
+        <v>6584.5</v>
       </c>
       <c r="E29" t="n">
-        <v>6743.75</v>
+        <v>6636</v>
       </c>
       <c r="F29" t="n">
-        <v>-145.25</v>
+        <v>-107.75</v>
       </c>
       <c r="G29" s="5" t="n">
-        <v>-0.0211</v>
+        <v>-0.016</v>
       </c>
       <c r="H29" t="n">
-        <v>195.5</v>
+        <v>267.5</v>
       </c>
       <c r="I29" t="n">
-        <v>6673.25</v>
+        <v>6520.25</v>
       </c>
       <c r="J29" t="n">
-        <v>6725.19</v>
+        <v>6513.38</v>
       </c>
       <c r="K29" t="n">
-        <v>6811.38</v>
+        <v>6646</v>
       </c>
       <c r="L29" t="n">
-        <v>6897.56</v>
+        <v>6778.62</v>
       </c>
       <c r="M29" t="n">
-        <v>6966.62</v>
+        <v>6841.5</v>
       </c>
       <c r="N29" t="n">
-        <v>7035.69</v>
+        <v>6904.38</v>
       </c>
       <c r="O29" t="n">
-        <v>7139</v>
+        <v>7106.75</v>
       </c>
       <c r="P29" s="6" t="n">
         <v/>
       </c>
-      <c r="Q29" s="6" t="inlineStr">
+      <c r="Q29" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R29" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="R29" s="6" t="inlineStr">
+      <c r="S29" s="10" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T29" s="8" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
-      </c>
-      <c r="S29" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T29" s="8" t="n">
-        <v/>
       </c>
       <c r="U29" s="8" t="n">
         <v/>
@@ -2960,50 +2960,50 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-03-16</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>6685.5</v>
+        <v>6608.5</v>
       </c>
       <c r="C30" t="n">
-        <v>6852</v>
+        <v>6762.25</v>
       </c>
       <c r="D30" t="n">
-        <v>6584.5</v>
+        <v>6558</v>
       </c>
       <c r="E30" t="n">
-        <v>6636</v>
+        <v>6594.63</v>
       </c>
       <c r="F30" t="n">
-        <v>-107.75</v>
+        <v>-41.37</v>
       </c>
       <c r="G30" s="5" t="n">
-        <v>-0.016</v>
+        <v>-0.0062</v>
       </c>
       <c r="H30" t="n">
-        <v>267.5</v>
+        <v>204.25</v>
       </c>
       <c r="I30" t="n">
-        <v>6520.25</v>
+        <v>6317</v>
       </c>
       <c r="J30" t="n">
-        <v>6513.38</v>
+        <v>6327.38</v>
       </c>
       <c r="K30" t="n">
-        <v>6646</v>
+        <v>6502.25</v>
       </c>
       <c r="L30" t="n">
-        <v>6778.62</v>
+        <v>6677.12</v>
       </c>
       <c r="M30" t="n">
-        <v>6841.5</v>
+        <v>6769.75</v>
       </c>
       <c r="N30" t="n">
-        <v>6904.38</v>
+        <v>6862.38</v>
       </c>
       <c r="O30" t="n">
-        <v>7106.75</v>
+        <v>7119.5</v>
       </c>
       <c r="P30" s="6" t="n">
         <v/>
@@ -3011,20 +3011,16 @@
       <c r="Q30" s="6" t="n">
         <v/>
       </c>
-      <c r="R30" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+      <c r="R30" s="6" t="n">
+        <v/>
       </c>
       <c r="S30" s="10" t="inlineStr">
         <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T30" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T30" s="8" t="n">
+        <v/>
       </c>
       <c r="U30" s="8" t="n">
         <v/>
@@ -3042,67 +3038,73 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-23</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>6608.5</v>
+        <v>6510</v>
       </c>
       <c r="C31" t="n">
-        <v>6762.25</v>
+        <v>6748</v>
       </c>
       <c r="D31" t="n">
-        <v>6558</v>
+        <v>6389</v>
       </c>
       <c r="E31" t="n">
-        <v>6594.63</v>
+        <v>6412.25</v>
       </c>
       <c r="F31" t="n">
-        <v>-41.37</v>
+        <v>-182.38</v>
       </c>
       <c r="G31" s="5" t="n">
-        <v>-0.0062</v>
+        <v>-0.0277</v>
       </c>
       <c r="H31" t="n">
-        <v>204.25</v>
+        <v>359</v>
       </c>
       <c r="I31" t="n">
-        <v>6317</v>
+        <v>6353.75</v>
       </c>
       <c r="J31" t="n">
-        <v>6327.38</v>
+        <v>6357.63</v>
       </c>
       <c r="K31" t="n">
-        <v>6502.25</v>
+        <v>6492.5</v>
       </c>
       <c r="L31" t="n">
-        <v>6677.12</v>
+        <v>6627.38</v>
       </c>
       <c r="M31" t="n">
-        <v>6769.75</v>
+        <v>6696.75</v>
       </c>
       <c r="N31" t="n">
-        <v>6862.38</v>
+        <v>6766.13</v>
       </c>
       <c r="O31" t="n">
-        <v>7119.5</v>
+        <v>6966.5</v>
       </c>
       <c r="P31" s="6" t="n">
         <v/>
       </c>
-      <c r="Q31" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R31" s="6" t="n">
-        <v/>
+      <c r="Q31" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="R31" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S31" s="10" t="inlineStr">
         <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T31" s="8" t="n">
-        <v/>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T31" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="U31" s="8" t="n">
         <v/>
@@ -3120,74 +3122,70 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2026-03-23</t>
+          <t>2026-03-30</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>6510</v>
+        <v>6380</v>
       </c>
       <c r="C32" t="n">
-        <v>6748</v>
+        <v>6653.75</v>
       </c>
       <c r="D32" t="n">
-        <v>6389</v>
+        <v>6353.25</v>
       </c>
       <c r="E32" t="n">
-        <v>6412.25</v>
+        <v>6603.75</v>
       </c>
       <c r="F32" t="n">
-        <v>-182.38</v>
+        <v>191.5</v>
       </c>
       <c r="G32" s="5" t="n">
-        <v>-0.0277</v>
+        <v>0.0299</v>
       </c>
       <c r="H32" t="n">
-        <v>359</v>
+        <v>300.5</v>
       </c>
       <c r="I32" t="n">
-        <v>6353.75</v>
+        <v>6030</v>
       </c>
       <c r="J32" t="n">
-        <v>6357.63</v>
+        <v>5975.12</v>
       </c>
       <c r="K32" t="n">
-        <v>6492.5</v>
+        <v>6232.75</v>
       </c>
       <c r="L32" t="n">
-        <v>6627.38</v>
+        <v>6490.38</v>
       </c>
       <c r="M32" t="n">
-        <v>6696.75</v>
+        <v>6591.75</v>
       </c>
       <c r="N32" t="n">
-        <v>6766.13</v>
+        <v>6693.12</v>
       </c>
       <c r="O32" t="n">
-        <v>6966.5</v>
+        <v>7107</v>
       </c>
       <c r="P32" s="6" t="n">
         <v/>
       </c>
-      <c r="Q32" s="6" t="inlineStr">
+      <c r="Q32" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R32" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S32" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T32" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="R32" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S32" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T32" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
       <c r="U32" s="8" t="n">
         <v/>
       </c>
@@ -3199,55 +3197,59 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X32" t="inlineStr"/>
+      <c r="X32" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-04-06</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>6380</v>
+        <v>6590</v>
       </c>
       <c r="C33" t="n">
-        <v>6653.75</v>
+        <v>6888</v>
       </c>
       <c r="D33" t="n">
-        <v>6353.25</v>
+        <v>6567</v>
       </c>
       <c r="E33" t="n">
-        <v>6603.75</v>
+        <v>6855.25</v>
       </c>
       <c r="F33" t="n">
-        <v>191.5</v>
+        <v>251.5</v>
       </c>
       <c r="G33" s="5" t="n">
-        <v>0.0299</v>
+        <v>0.0381</v>
       </c>
       <c r="H33" t="n">
-        <v>300.5</v>
+        <v>321</v>
       </c>
       <c r="I33" t="n">
-        <v>6030</v>
+        <v>6052.75</v>
       </c>
       <c r="J33" t="n">
-        <v>5975.12</v>
+        <v>6353.38</v>
       </c>
       <c r="K33" t="n">
-        <v>6232.75</v>
+        <v>6453.5</v>
       </c>
       <c r="L33" t="n">
-        <v>6490.38</v>
+        <v>6553.62</v>
       </c>
       <c r="M33" t="n">
-        <v>6591.75</v>
+        <v>6754</v>
       </c>
       <c r="N33" t="n">
-        <v>6693.12</v>
+        <v>6954.38</v>
       </c>
       <c r="O33" t="n">
-        <v>7107</v>
+        <v>6954.25</v>
       </c>
       <c r="P33" s="6" t="n">
         <v/>
@@ -3265,15 +3267,17 @@
       </c>
       <c r="T33" s="8" t="inlineStr">
         <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U33" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V33" s="8" t="inlineStr">
+        <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="U33" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V33" s="8" t="n">
-        <v/>
-      </c>
       <c r="W33" s="11" t="inlineStr">
         <is>
           <t>空方</t>
@@ -3281,57 +3285,57 @@
       </c>
       <c r="X33" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2026-04-06</t>
+          <t>2026-04-13</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>6590</v>
+        <v>6780</v>
       </c>
       <c r="C34" t="n">
-        <v>6888</v>
+        <v>7185.75</v>
       </c>
       <c r="D34" t="n">
-        <v>6567</v>
+        <v>6767</v>
       </c>
       <c r="E34" t="n">
-        <v>6855.25</v>
+        <v>7161.5</v>
       </c>
       <c r="F34" t="n">
-        <v>251.5</v>
+        <v>306.25</v>
       </c>
       <c r="G34" s="5" t="n">
-        <v>0.0381</v>
+        <v>0.0447</v>
       </c>
       <c r="H34" t="n">
-        <v>321</v>
+        <v>418.75</v>
       </c>
       <c r="I34" t="n">
-        <v>6052.75</v>
+        <v>6246</v>
       </c>
       <c r="J34" t="n">
-        <v>6353.38</v>
+        <v>6598.12</v>
       </c>
       <c r="K34" t="n">
-        <v>6453.5</v>
+        <v>6694.75</v>
       </c>
       <c r="L34" t="n">
-        <v>6553.62</v>
+        <v>6791.38</v>
       </c>
       <c r="M34" t="n">
-        <v>6754</v>
+        <v>7015.75</v>
       </c>
       <c r="N34" t="n">
-        <v>6954.38</v>
+        <v>7240.12</v>
       </c>
       <c r="O34" t="n">
-        <v>6954.25</v>
+        <v>7209</v>
       </c>
       <c r="P34" s="6" t="n">
         <v/>
@@ -3374,50 +3378,50 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2026-04-13</t>
+          <t>2026-04-20</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>6780</v>
+        <v>7102.5</v>
       </c>
       <c r="C35" t="n">
-        <v>7185.75</v>
+        <v>7200.5</v>
       </c>
       <c r="D35" t="n">
-        <v>6767</v>
+        <v>7079.25</v>
       </c>
       <c r="E35" t="n">
-        <v>7161.5</v>
+        <v>7194.75</v>
       </c>
       <c r="F35" t="n">
-        <v>306.25</v>
+        <v>33.25</v>
       </c>
       <c r="G35" s="5" t="n">
-        <v>0.0447</v>
+        <v>0.0046</v>
       </c>
       <c r="H35" t="n">
-        <v>418.75</v>
+        <v>121.25</v>
       </c>
       <c r="I35" t="n">
-        <v>6246</v>
+        <v>6348.25</v>
       </c>
       <c r="J35" t="n">
-        <v>6598.12</v>
+        <v>6835.31</v>
       </c>
       <c r="K35" t="n">
-        <v>6694.75</v>
+        <v>6952.12</v>
       </c>
       <c r="L35" t="n">
-        <v>6791.38</v>
+        <v>7068.94</v>
       </c>
       <c r="M35" t="n">
-        <v>7015.75</v>
+        <v>7370.88</v>
       </c>
       <c r="N35" t="n">
-        <v>7240.12</v>
+        <v>7672.81</v>
       </c>
       <c r="O35" t="n">
-        <v>7209</v>
+        <v>7604.5</v>
       </c>
       <c r="P35" s="6" t="n">
         <v/>
@@ -3430,21 +3434,17 @@
       </c>
       <c r="S35" s="7" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T35" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T35" s="8" t="n">
+        <v/>
       </c>
       <c r="U35" s="8" t="n">
         <v/>
       </c>
-      <c r="V35" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+      <c r="V35" s="8" t="n">
+        <v/>
       </c>
       <c r="W35" s="11" t="inlineStr">
         <is>
@@ -3460,50 +3460,50 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
+          <t>2026-04-27</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>7102.5</v>
+        <v>7185</v>
       </c>
       <c r="C36" t="n">
-        <v>7200.5</v>
+        <v>7300.75</v>
       </c>
       <c r="D36" t="n">
-        <v>7079.25</v>
+        <v>7131.25</v>
       </c>
       <c r="E36" t="n">
-        <v>7194.75</v>
+        <v>7258</v>
       </c>
       <c r="F36" t="n">
-        <v>33.25</v>
+        <v>63.25</v>
       </c>
       <c r="G36" s="5" t="n">
-        <v>0.0046</v>
+        <v>0.008800000000000001</v>
       </c>
       <c r="H36" t="n">
-        <v>121.25</v>
+        <v>169.5</v>
       </c>
       <c r="I36" t="n">
-        <v>6348.25</v>
+        <v>6958</v>
       </c>
       <c r="J36" t="n">
-        <v>6835.31</v>
+        <v>7100.94</v>
       </c>
       <c r="K36" t="n">
-        <v>6952.12</v>
+        <v>7134.12</v>
       </c>
       <c r="L36" t="n">
-        <v>7068.94</v>
+        <v>7167.31</v>
       </c>
       <c r="M36" t="n">
-        <v>7370.88</v>
+        <v>7255.38</v>
       </c>
       <c r="N36" t="n">
-        <v>7672.81</v>
+        <v>7343.44</v>
       </c>
       <c r="O36" t="n">
-        <v>7604.5</v>
+        <v>7321.75</v>
       </c>
       <c r="P36" s="6" t="n">
         <v/>
@@ -3511,16 +3511,20 @@
       <c r="Q36" s="6" t="n">
         <v/>
       </c>
-      <c r="R36" s="6" t="n">
-        <v/>
+      <c r="R36" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S36" s="7" t="inlineStr">
         <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T36" s="8" t="n">
-        <v/>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T36" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="U36" s="8" t="n">
         <v/>
@@ -3542,50 +3546,50 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-05-04</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>7185</v>
+        <v>7276.25</v>
       </c>
       <c r="C37" t="n">
-        <v>7300.75</v>
+        <v>7427.75</v>
       </c>
       <c r="D37" t="n">
-        <v>7131.25</v>
+        <v>7199.5</v>
       </c>
       <c r="E37" t="n">
-        <v>7258</v>
+        <v>7419</v>
       </c>
       <c r="F37" t="n">
-        <v>63.25</v>
+        <v>161</v>
       </c>
       <c r="G37" s="5" t="n">
-        <v>0.008800000000000001</v>
+        <v>0.0222</v>
       </c>
       <c r="H37" t="n">
-        <v>169.5</v>
+        <v>228.25</v>
       </c>
       <c r="I37" t="n">
-        <v>6958</v>
+        <v>6961.75</v>
       </c>
       <c r="J37" t="n">
-        <v>7100.94</v>
+        <v>7109.5</v>
       </c>
       <c r="K37" t="n">
-        <v>7134.12</v>
+        <v>7173.25</v>
       </c>
       <c r="L37" t="n">
-        <v>7167.31</v>
+        <v>7237</v>
       </c>
       <c r="M37" t="n">
-        <v>7255.38</v>
+        <v>7342.75</v>
       </c>
       <c r="N37" t="n">
-        <v>7343.44</v>
+        <v>7448.5</v>
       </c>
       <c r="O37" t="n">
-        <v>7321.75</v>
+        <v>7470.25</v>
       </c>
       <c r="P37" s="6" t="n">
         <v/>
@@ -3593,23 +3597,23 @@
       <c r="Q37" s="6" t="n">
         <v/>
       </c>
-      <c r="R37" s="6" t="inlineStr">
+      <c r="R37" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S37" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T37" s="8" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="S37" s="7" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T37" s="8" t="inlineStr">
+      <c r="U37" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
-      </c>
-      <c r="U37" s="8" t="n">
-        <v/>
       </c>
       <c r="V37" s="8" t="n">
         <v/>
@@ -3628,50 +3632,50 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>2026-05-04</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>7276.25</v>
+        <v>7403.5</v>
       </c>
       <c r="C38" t="n">
-        <v>7427.75</v>
+        <v>7540</v>
       </c>
       <c r="D38" t="n">
-        <v>7199.5</v>
+        <v>7363.25</v>
       </c>
       <c r="E38" t="n">
-        <v>7419</v>
+        <v>7432.25</v>
       </c>
       <c r="F38" t="n">
-        <v>161</v>
+        <v>13.25</v>
       </c>
       <c r="G38" s="5" t="n">
-        <v>0.0222</v>
+        <v>0.0018</v>
       </c>
       <c r="H38" t="n">
-        <v>228.25</v>
+        <v>176.75</v>
       </c>
       <c r="I38" t="n">
-        <v>6961.75</v>
+        <v>6971.25</v>
       </c>
       <c r="J38" t="n">
-        <v>7109.5</v>
+        <v>7243.44</v>
       </c>
       <c r="K38" t="n">
-        <v>7173.25</v>
+        <v>7304.88</v>
       </c>
       <c r="L38" t="n">
-        <v>7237</v>
+        <v>7366.31</v>
       </c>
       <c r="M38" t="n">
-        <v>7342.75</v>
+        <v>7533.12</v>
       </c>
       <c r="N38" t="n">
-        <v>7448.5</v>
+        <v>7699.94</v>
       </c>
       <c r="O38" t="n">
-        <v>7470.25</v>
+        <v>7656</v>
       </c>
       <c r="P38" s="6" t="n">
         <v/>
@@ -3684,7 +3688,7 @@
       </c>
       <c r="S38" s="7" t="inlineStr">
         <is>
-          <t>↑</t>
+          <t>↑C</t>
         </is>
       </c>
       <c r="T38" s="8" t="inlineStr">
@@ -3692,10 +3696,8 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="U38" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+      <c r="U38" s="8" t="n">
+        <v/>
       </c>
       <c r="V38" s="8" t="n">
         <v/>
@@ -3714,50 +3716,50 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-05-18</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>7403.5</v>
+        <v>7410</v>
       </c>
       <c r="C39" t="n">
-        <v>7540</v>
+        <v>7524</v>
       </c>
       <c r="D39" t="n">
-        <v>7363.25</v>
+        <v>7354.25</v>
       </c>
       <c r="E39" t="n">
-        <v>7432.25</v>
+        <v>7491</v>
       </c>
       <c r="F39" t="n">
-        <v>13.25</v>
+        <v>58.75</v>
       </c>
       <c r="G39" s="5" t="n">
-        <v>0.0018</v>
+        <v>0.007900000000000001</v>
       </c>
       <c r="H39" t="n">
-        <v>176.75</v>
+        <v>169.75</v>
       </c>
       <c r="I39" t="n">
-        <v>6971.25</v>
+        <v>7186.5</v>
       </c>
       <c r="J39" t="n">
-        <v>7243.44</v>
+        <v>7245.81</v>
       </c>
       <c r="K39" t="n">
-        <v>7304.88</v>
+        <v>7343.88</v>
       </c>
       <c r="L39" t="n">
-        <v>7366.31</v>
+        <v>7441.94</v>
       </c>
       <c r="M39" t="n">
-        <v>7533.12</v>
+        <v>7520.62</v>
       </c>
       <c r="N39" t="n">
-        <v>7699.94</v>
+        <v>7599.31</v>
       </c>
       <c r="O39" t="n">
-        <v>7656</v>
+        <v>7716.75</v>
       </c>
       <c r="P39" s="6" t="n">
         <v/>
@@ -3770,12 +3772,12 @@
       </c>
       <c r="S39" s="7" t="inlineStr">
         <is>
-          <t>↑C</t>
+          <t>↑</t>
         </is>
       </c>
       <c r="T39" s="8" t="inlineStr">
         <is>
-          <t>✓</t>
+          <t>△C</t>
         </is>
       </c>
       <c r="U39" s="8" t="n">
@@ -3791,57 +3793,57 @@
       </c>
       <c r="X39" t="inlineStr">
         <is>
-          <t>強警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-05-25</t>
         </is>
       </c>
       <c r="B40" t="n">
-        <v>7410</v>
+        <v>7519</v>
       </c>
       <c r="C40" t="n">
-        <v>7524</v>
+        <v>7611.5</v>
       </c>
       <c r="D40" t="n">
-        <v>7354.25</v>
+        <v>7505.75</v>
       </c>
       <c r="E40" t="n">
-        <v>7491</v>
+        <v>7595.75</v>
       </c>
       <c r="F40" t="n">
-        <v>58.75</v>
+        <v>104.75</v>
       </c>
       <c r="G40" s="5" t="n">
-        <v>0.007900000000000001</v>
+        <v>0.014</v>
       </c>
       <c r="H40" t="n">
-        <v>169.75</v>
+        <v>105.75</v>
       </c>
       <c r="I40" t="n">
-        <v>7186.5</v>
+        <v>7184.5</v>
       </c>
       <c r="J40" t="n">
-        <v>7245.81</v>
+        <v>7347.19</v>
       </c>
       <c r="K40" t="n">
-        <v>7343.88</v>
+        <v>7406.12</v>
       </c>
       <c r="L40" t="n">
-        <v>7441.94</v>
+        <v>7465.06</v>
       </c>
       <c r="M40" t="n">
-        <v>7520.62</v>
+        <v>7575.88</v>
       </c>
       <c r="N40" t="n">
-        <v>7599.31</v>
+        <v>7686.69</v>
       </c>
       <c r="O40" t="n">
-        <v>7716.75</v>
+        <v>7693.75</v>
       </c>
       <c r="P40" s="6" t="n">
         <v/>
@@ -3875,77 +3877,81 @@
       </c>
       <c r="X40" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2026-05-25</t>
+          <t>2026-06-01</t>
         </is>
       </c>
       <c r="B41" t="n">
-        <v>7519</v>
+        <v>7595</v>
       </c>
       <c r="C41" t="n">
-        <v>7611.5</v>
+        <v>7632.25</v>
       </c>
       <c r="D41" t="n">
-        <v>7505.75</v>
+        <v>7359</v>
       </c>
       <c r="E41" t="n">
-        <v>7595.75</v>
+        <v>7400.5</v>
       </c>
       <c r="F41" t="n">
-        <v>104.75</v>
+        <v>-195.25</v>
       </c>
       <c r="G41" s="5" t="n">
-        <v>0.014</v>
+        <v>-0.0257</v>
       </c>
       <c r="H41" t="n">
-        <v>105.75</v>
+        <v>273.25</v>
       </c>
       <c r="I41" t="n">
-        <v>7184.5</v>
+        <v>7400</v>
       </c>
       <c r="J41" t="n">
-        <v>7347.19</v>
+        <v>7508.56</v>
       </c>
       <c r="K41" t="n">
-        <v>7406.12</v>
+        <v>7542.88</v>
       </c>
       <c r="L41" t="n">
-        <v>7465.06</v>
+        <v>7577.19</v>
       </c>
       <c r="M41" t="n">
-        <v>7575.88</v>
+        <v>7648.62</v>
       </c>
       <c r="N41" t="n">
-        <v>7686.69</v>
+        <v>7720.06</v>
       </c>
       <c r="O41" t="n">
-        <v>7693.75</v>
-      </c>
-      <c r="P41" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q41" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R41" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S41" s="7" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T41" s="8" t="inlineStr">
+        <v>7717.25</v>
+      </c>
+      <c r="P41" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
+      <c r="Q41" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="R41" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S41" s="10" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T41" s="8" t="n">
+        <v/>
+      </c>
       <c r="U41" s="8" t="n">
         <v/>
       </c>
@@ -3959,76 +3965,72 @@
       </c>
       <c r="X41" t="inlineStr">
         <is>
-          <t>強警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-06-08</t>
         </is>
       </c>
       <c r="B42" t="n">
-        <v>7595</v>
+        <v>7368</v>
       </c>
       <c r="C42" t="n">
-        <v>7632.25</v>
+        <v>7491</v>
       </c>
       <c r="D42" t="n">
-        <v>7359</v>
+        <v>7232.25</v>
       </c>
       <c r="E42" t="n">
-        <v>7400.5</v>
+        <v>7435</v>
       </c>
       <c r="F42" t="n">
-        <v>-195.25</v>
+        <v>34.5</v>
       </c>
       <c r="G42" s="5" t="n">
-        <v>-0.0257</v>
+        <v>0.0047</v>
       </c>
       <c r="H42" t="n">
-        <v>273.25</v>
+        <v>258.75</v>
       </c>
       <c r="I42" t="n">
-        <v>7400</v>
+        <v>7085.75</v>
       </c>
       <c r="J42" t="n">
-        <v>7508.56</v>
+        <v>7079.69</v>
       </c>
       <c r="K42" t="n">
-        <v>7542.88</v>
+        <v>7263.88</v>
       </c>
       <c r="L42" t="n">
-        <v>7577.19</v>
+        <v>7448.06</v>
       </c>
       <c r="M42" t="n">
-        <v>7648.62</v>
+        <v>7537.12</v>
       </c>
       <c r="N42" t="n">
-        <v>7720.06</v>
+        <v>7626.19</v>
       </c>
       <c r="O42" t="n">
-        <v>7717.25</v>
-      </c>
-      <c r="P42" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="Q42" s="6" t="inlineStr">
+        <v>7905.5</v>
+      </c>
+      <c r="P42" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q42" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R42" s="6" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="R42" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
       <c r="S42" s="10" t="inlineStr">
         <is>
-          <t>↓</t>
+          <t>↓C</t>
         </is>
       </c>
       <c r="T42" s="8" t="n">
@@ -4054,50 +4056,50 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="B43" t="n">
-        <v>7368</v>
+        <v>7480</v>
       </c>
       <c r="C43" t="n">
-        <v>7491</v>
+        <v>7584.5</v>
       </c>
       <c r="D43" t="n">
-        <v>7232.25</v>
+        <v>7405</v>
       </c>
       <c r="E43" t="n">
-        <v>7435</v>
+        <v>7556.25</v>
       </c>
       <c r="F43" t="n">
-        <v>34.5</v>
+        <v>121.25</v>
       </c>
       <c r="G43" s="5" t="n">
-        <v>0.0047</v>
+        <v>0.0163</v>
       </c>
       <c r="H43" t="n">
-        <v>258.75</v>
+        <v>179.5</v>
       </c>
       <c r="I43" t="n">
-        <v>7085.75</v>
+        <v>6973.5</v>
       </c>
       <c r="J43" t="n">
-        <v>7079.69</v>
+        <v>7212.94</v>
       </c>
       <c r="K43" t="n">
-        <v>7263.88</v>
+        <v>7305.62</v>
       </c>
       <c r="L43" t="n">
-        <v>7448.06</v>
+        <v>7398.31</v>
       </c>
       <c r="M43" t="n">
-        <v>7537.12</v>
+        <v>7564.38</v>
       </c>
       <c r="N43" t="n">
-        <v>7626.19</v>
+        <v>7730.44</v>
       </c>
       <c r="O43" t="n">
-        <v>7905.5</v>
+        <v>7749.75</v>
       </c>
       <c r="P43" s="6" t="n">
         <v/>
@@ -4105,18 +4107,18 @@
       <c r="Q43" s="6" t="n">
         <v/>
       </c>
-      <c r="R43" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S43" s="10" t="inlineStr">
-        <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T43" s="8" t="n">
-        <v/>
+      <c r="R43" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S43" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T43" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="U43" s="8" t="n">
         <v/>
@@ -4131,77 +4133,79 @@
       </c>
       <c r="X43" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="B44" t="n">
-        <v>7480</v>
+        <v>7543.25</v>
       </c>
       <c r="C44" t="n">
-        <v>7584.5</v>
+        <v>7599.25</v>
       </c>
       <c r="D44" t="n">
-        <v>7405</v>
+        <v>7357.25</v>
       </c>
       <c r="E44" t="n">
-        <v>7556.25</v>
+        <v>7401.75</v>
       </c>
       <c r="F44" t="n">
-        <v>121.25</v>
+        <v>-154.5</v>
       </c>
       <c r="G44" s="5" t="n">
-        <v>0.0163</v>
+        <v>-0.0204</v>
       </c>
       <c r="H44" t="n">
-        <v>179.5</v>
+        <v>242</v>
       </c>
       <c r="I44" t="n">
-        <v>6973.5</v>
+        <v>7225.5</v>
       </c>
       <c r="J44" t="n">
-        <v>7212.94</v>
+        <v>7407.5</v>
       </c>
       <c r="K44" t="n">
-        <v>7305.62</v>
+        <v>7466.5</v>
       </c>
       <c r="L44" t="n">
-        <v>7398.31</v>
+        <v>7525.5</v>
       </c>
       <c r="M44" t="n">
-        <v>7564.38</v>
+        <v>7646</v>
       </c>
       <c r="N44" t="n">
-        <v>7730.44</v>
+        <v>7766.5</v>
       </c>
       <c r="O44" t="n">
-        <v>7749.75</v>
+        <v>7764</v>
       </c>
       <c r="P44" s="6" t="n">
         <v/>
       </c>
-      <c r="Q44" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R44" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S44" s="7" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T44" s="8" t="inlineStr">
+      <c r="Q44" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
+      <c r="R44" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S44" s="10" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T44" s="8" t="n">
+        <v/>
+      </c>
       <c r="U44" s="8" t="n">
         <v/>
       </c>
@@ -4215,79 +4219,77 @@
       </c>
       <c r="X44" t="inlineStr">
         <is>
-          <t>強警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="B45" t="n">
-        <v>7543.25</v>
+        <v>7398</v>
       </c>
       <c r="C45" t="n">
-        <v>7599.25</v>
+        <v>7593.75</v>
       </c>
       <c r="D45" t="n">
-        <v>7357.25</v>
+        <v>7398</v>
       </c>
       <c r="E45" t="n">
-        <v>7401.75</v>
+        <v>7557</v>
       </c>
       <c r="F45" t="n">
-        <v>-154.5</v>
+        <v>155.25</v>
       </c>
       <c r="G45" s="5" t="n">
-        <v>-0.0204</v>
+        <v>0.021</v>
       </c>
       <c r="H45" t="n">
-        <v>242</v>
+        <v>195.75</v>
       </c>
       <c r="I45" t="n">
-        <v>7225.5</v>
+        <v>7115.25</v>
       </c>
       <c r="J45" t="n">
-        <v>7407.5</v>
+        <v>7121.5</v>
       </c>
       <c r="K45" t="n">
-        <v>7466.5</v>
+        <v>7280.75</v>
       </c>
       <c r="L45" t="n">
-        <v>7525.5</v>
+        <v>7440</v>
       </c>
       <c r="M45" t="n">
-        <v>7646</v>
+        <v>7522.75</v>
       </c>
       <c r="N45" t="n">
-        <v>7766.5</v>
+        <v>7605.5</v>
       </c>
       <c r="O45" t="n">
-        <v>7764</v>
+        <v>7841.25</v>
       </c>
       <c r="P45" s="6" t="n">
         <v/>
       </c>
-      <c r="Q45" s="6" t="inlineStr">
+      <c r="Q45" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R45" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S45" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T45" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="R45" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S45" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T45" s="8" t="n">
-        <v/>
-      </c>
       <c r="U45" s="8" t="n">
         <v/>
       </c>
@@ -4301,57 +4303,57 @@
       </c>
       <c r="X45" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="B46" t="n">
-        <v>7398</v>
+        <v>7562.25</v>
       </c>
       <c r="C46" t="n">
-        <v>7593.75</v>
+        <v>7628.75</v>
       </c>
       <c r="D46" t="n">
-        <v>7398</v>
+        <v>7468.5</v>
       </c>
       <c r="E46" t="n">
-        <v>7557</v>
+        <v>7620.25</v>
       </c>
       <c r="F46" t="n">
-        <v>155.25</v>
+        <v>63.25</v>
       </c>
       <c r="G46" s="5" t="n">
-        <v>0.021</v>
+        <v>0.008399999999999999</v>
       </c>
       <c r="H46" t="n">
-        <v>195.75</v>
+        <v>160.25</v>
       </c>
       <c r="I46" t="n">
-        <v>7115.25</v>
+        <v>7202.25</v>
       </c>
       <c r="J46" t="n">
-        <v>7121.5</v>
+        <v>7391.81</v>
       </c>
       <c r="K46" t="n">
-        <v>7280.75</v>
+        <v>7459.12</v>
       </c>
       <c r="L46" t="n">
-        <v>7440</v>
+        <v>7526.44</v>
       </c>
       <c r="M46" t="n">
-        <v>7522.75</v>
+        <v>7654.88</v>
       </c>
       <c r="N46" t="n">
-        <v>7605.5</v>
+        <v>7783.31</v>
       </c>
       <c r="O46" t="n">
-        <v>7841.25</v>
+        <v>7789.5</v>
       </c>
       <c r="P46" s="6" t="n">
         <v/>
@@ -4385,77 +4387,79 @@
       </c>
       <c r="X46" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="B47" t="n">
-        <v>7562.25</v>
+        <v>7607</v>
       </c>
       <c r="C47" t="n">
-        <v>7628.75</v>
+        <v>7632</v>
       </c>
       <c r="D47" t="n">
-        <v>7468.5</v>
+        <v>7473</v>
       </c>
       <c r="E47" t="n">
-        <v>7620.25</v>
+        <v>7497.75</v>
       </c>
       <c r="F47" t="n">
-        <v>63.25</v>
+        <v>-122.5</v>
       </c>
       <c r="G47" s="5" t="n">
-        <v>0.008399999999999999</v>
+        <v>-0.0161</v>
       </c>
       <c r="H47" t="n">
-        <v>160.25</v>
+        <v>159</v>
       </c>
       <c r="I47" t="n">
-        <v>7202.25</v>
+        <v>7308.25</v>
       </c>
       <c r="J47" t="n">
-        <v>7391.81</v>
+        <v>7495.81</v>
       </c>
       <c r="K47" t="n">
-        <v>7459.12</v>
+        <v>7540.12</v>
       </c>
       <c r="L47" t="n">
-        <v>7526.44</v>
+        <v>7584.44</v>
       </c>
       <c r="M47" t="n">
-        <v>7654.88</v>
+        <v>7700.38</v>
       </c>
       <c r="N47" t="n">
-        <v>7783.31</v>
+        <v>7816.31</v>
       </c>
       <c r="O47" t="n">
-        <v>7789.5</v>
+        <v>7789</v>
       </c>
       <c r="P47" s="6" t="n">
         <v/>
       </c>
-      <c r="Q47" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R47" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S47" s="7" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T47" s="8" t="inlineStr">
+      <c r="Q47" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
+      <c r="R47" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S47" s="10" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T47" s="8" t="n">
+        <v/>
+      </c>
       <c r="U47" s="8" t="n">
         <v/>
       </c>
@@ -4469,71 +4473,69 @@
       </c>
       <c r="X47" t="inlineStr">
         <is>
-          <t>強警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="B48" t="n">
-        <v>7607</v>
+        <v>7485</v>
       </c>
       <c r="C48" t="n">
-        <v>7632</v>
+        <v>7563.5</v>
       </c>
       <c r="D48" t="n">
-        <v>7473</v>
+        <v>7411.75</v>
       </c>
       <c r="E48" t="n">
-        <v>7497.75</v>
+        <v>7447.5</v>
       </c>
       <c r="F48" t="n">
-        <v>-122.5</v>
+        <v>-50.25</v>
       </c>
       <c r="G48" s="5" t="n">
-        <v>-0.0161</v>
+        <v>-0.0067</v>
       </c>
       <c r="H48" t="n">
-        <v>159</v>
+        <v>151.75</v>
       </c>
       <c r="I48" t="n">
-        <v>7308.25</v>
+        <v>7314</v>
       </c>
       <c r="J48" t="n">
-        <v>7495.81</v>
+        <v>7311.38</v>
       </c>
       <c r="K48" t="n">
-        <v>7540.12</v>
+        <v>7418.25</v>
       </c>
       <c r="L48" t="n">
-        <v>7584.44</v>
+        <v>7525.12</v>
       </c>
       <c r="M48" t="n">
-        <v>7700.38</v>
+        <v>7577.25</v>
       </c>
       <c r="N48" t="n">
-        <v>7816.31</v>
+        <v>7629.38</v>
       </c>
       <c r="O48" t="n">
-        <v>7789</v>
+        <v>7791</v>
       </c>
       <c r="P48" s="6" t="n">
         <v/>
       </c>
-      <c r="Q48" s="6" t="inlineStr">
+      <c r="Q48" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R48" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="R48" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
       <c r="S48" s="10" t="inlineStr">
         <is>
           <t>↓</t>
@@ -4553,59 +4555,55 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X48" t="inlineStr">
-        <is>
-          <t>中警訊</t>
-        </is>
-      </c>
+      <c r="X48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="B49" t="n">
-        <v>7485</v>
+        <v>7490</v>
       </c>
       <c r="C49" t="n">
-        <v>7563.5</v>
+        <v>7541</v>
       </c>
       <c r="D49" t="n">
-        <v>7411.75</v>
+        <v>7324</v>
       </c>
       <c r="E49" t="n">
-        <v>7447.5</v>
+        <v>7519.25</v>
       </c>
       <c r="F49" t="n">
-        <v>-50.25</v>
+        <v>71.75</v>
       </c>
       <c r="G49" s="5" t="n">
-        <v>-0.0067</v>
+        <v>0.009599999999999999</v>
       </c>
       <c r="H49" t="n">
-        <v>151.75</v>
+        <v>217</v>
       </c>
       <c r="I49" t="n">
-        <v>7314</v>
+        <v>7260</v>
       </c>
       <c r="J49" t="n">
-        <v>7311.38</v>
+        <v>7275.69</v>
       </c>
       <c r="K49" t="n">
-        <v>7418.25</v>
+        <v>7371.62</v>
       </c>
       <c r="L49" t="n">
-        <v>7525.12</v>
+        <v>7467.56</v>
       </c>
       <c r="M49" t="n">
-        <v>7577.25</v>
+        <v>7523.38</v>
       </c>
       <c r="N49" t="n">
-        <v>7629.38</v>
+        <v>7579.19</v>
       </c>
       <c r="O49" t="n">
-        <v>7791</v>
+        <v>7715.25</v>
       </c>
       <c r="P49" s="6" t="n">
         <v/>
@@ -4615,17 +4613,19 @@
       </c>
       <c r="R49" s="6" t="inlineStr">
         <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S49" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T49" s="8" t="inlineStr">
+        <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="S49" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T49" s="8" t="n">
-        <v/>
-      </c>
       <c r="U49" s="8" t="n">
         <v/>
       </c>
@@ -4637,55 +4637,59 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X49" t="inlineStr"/>
+      <c r="X49" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="B50" t="n">
-        <v>7490</v>
+        <v>7550</v>
       </c>
       <c r="C50" t="n">
-        <v>7541</v>
+        <v>7820.25</v>
       </c>
       <c r="D50" t="n">
-        <v>7324</v>
+        <v>7542.75</v>
       </c>
       <c r="E50" t="n">
-        <v>7519.25</v>
+        <v>7779.75</v>
       </c>
       <c r="F50" t="n">
-        <v>71.75</v>
+        <v>260.5</v>
       </c>
       <c r="G50" s="5" t="n">
-        <v>0.009599999999999999</v>
+        <v>0.0346</v>
       </c>
       <c r="H50" t="n">
-        <v>217</v>
+        <v>277.5</v>
       </c>
       <c r="I50" t="n">
-        <v>7260</v>
+        <v>7107</v>
       </c>
       <c r="J50" t="n">
-        <v>7275.69</v>
+        <v>7345.62</v>
       </c>
       <c r="K50" t="n">
-        <v>7371.62</v>
+        <v>7410.75</v>
       </c>
       <c r="L50" t="n">
-        <v>7467.56</v>
+        <v>7475.88</v>
       </c>
       <c r="M50" t="n">
-        <v>7523.38</v>
+        <v>7627.75</v>
       </c>
       <c r="N50" t="n">
-        <v>7579.19</v>
+        <v>7779.62</v>
       </c>
       <c r="O50" t="n">
-        <v>7715.25</v>
+        <v>7758</v>
       </c>
       <c r="P50" s="6" t="n">
         <v/>
@@ -4693,85 +4697,83 @@
       <c r="Q50" s="6" t="n">
         <v/>
       </c>
-      <c r="R50" s="6" t="inlineStr">
+      <c r="R50" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S50" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T50" s="8" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="S50" s="7" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T50" s="8" t="inlineStr">
+      <c r="U50" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="U50" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V50" s="8" t="n">
-        <v/>
-      </c>
-      <c r="W50" s="11" t="inlineStr">
-        <is>
-          <t>空方</t>
-        </is>
-      </c>
-      <c r="X50" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="V50" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="W50" s="9" t="inlineStr">
+        <is>
+          <t>多方</t>
+        </is>
+      </c>
+      <c r="X50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="B51" t="n">
-        <v>7550</v>
+        <v>7776.75</v>
       </c>
       <c r="C51" t="n">
-        <v>7820.25</v>
+        <v>7838.5</v>
       </c>
       <c r="D51" t="n">
-        <v>7542.75</v>
+        <v>7738</v>
       </c>
       <c r="E51" t="n">
-        <v>7779.75</v>
+        <v>7805</v>
       </c>
       <c r="F51" t="n">
-        <v>260.5</v>
+        <v>25.25</v>
       </c>
       <c r="G51" s="5" t="n">
-        <v>0.0346</v>
+        <v>0.0032</v>
       </c>
       <c r="H51" t="n">
-        <v>277.5</v>
+        <v>100.5</v>
       </c>
       <c r="I51" t="n">
-        <v>7107</v>
+        <v>7265.25</v>
       </c>
       <c r="J51" t="n">
-        <v>7345.62</v>
+        <v>7551.38</v>
       </c>
       <c r="K51" t="n">
-        <v>7410.75</v>
+        <v>7641</v>
       </c>
       <c r="L51" t="n">
-        <v>7475.88</v>
+        <v>7730.62</v>
       </c>
       <c r="M51" t="n">
-        <v>7627.75</v>
+        <v>7918.5</v>
       </c>
       <c r="N51" t="n">
-        <v>7779.62</v>
+        <v>8106.38</v>
       </c>
       <c r="O51" t="n">
-        <v>7758</v>
+        <v>8097.75</v>
       </c>
       <c r="P51" s="6" t="n">
         <v/>
@@ -4784,23 +4786,17 @@
       </c>
       <c r="S51" s="7" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T51" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U51" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="V51" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T51" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U51" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V51" s="8" t="n">
+        <v/>
       </c>
       <c r="W51" s="9" t="inlineStr">
         <is>
@@ -4812,63 +4808,67 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="B52" t="n">
-        <v>7776.75</v>
+        <v>7809.25</v>
       </c>
       <c r="C52" t="n">
-        <v>7838.5</v>
+        <v>7824.5</v>
       </c>
       <c r="D52" t="n">
-        <v>7738</v>
+        <v>7657.75</v>
       </c>
       <c r="E52" t="n">
-        <v>7805</v>
+        <v>7691.25</v>
       </c>
       <c r="F52" t="n">
-        <v>25.25</v>
+        <v>-113.75</v>
       </c>
       <c r="G52" s="5" t="n">
-        <v>0.0032</v>
+        <v>-0.0146</v>
       </c>
       <c r="H52" t="n">
-        <v>100.5</v>
+        <v>166.75</v>
       </c>
       <c r="I52" t="n">
-        <v>7265.25</v>
+        <v>7637.5</v>
       </c>
       <c r="J52" t="n">
-        <v>7551.38</v>
+        <v>7712.88</v>
       </c>
       <c r="K52" t="n">
-        <v>7641</v>
+        <v>7754.75</v>
       </c>
       <c r="L52" t="n">
-        <v>7730.62</v>
+        <v>7796.62</v>
       </c>
       <c r="M52" t="n">
-        <v>7918.5</v>
+        <v>7855.25</v>
       </c>
       <c r="N52" t="n">
-        <v>8106.38</v>
+        <v>7913.88</v>
       </c>
       <c r="O52" t="n">
-        <v>8097.75</v>
+        <v>7939</v>
       </c>
       <c r="P52" s="6" t="n">
         <v/>
       </c>
-      <c r="Q52" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R52" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S52" s="7" t="inlineStr">
-        <is>
-          <t>↑C</t>
+      <c r="Q52" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="R52" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S52" s="10" t="inlineStr">
+        <is>
+          <t>↓</t>
         </is>
       </c>
       <c r="T52" s="8" t="n">
@@ -4880,9 +4880,9 @@
       <c r="V52" s="8" t="n">
         <v/>
       </c>
-      <c r="W52" s="9" t="inlineStr">
-        <is>
-          <t>多方</t>
+      <c r="W52" s="11" t="inlineStr">
+        <is>
+          <t>空方</t>
         </is>
       </c>
       <c r="X52" t="inlineStr"/>
@@ -4890,72 +4890,70 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="B53" t="n">
-        <v>7809.25</v>
+        <v>7693.5</v>
       </c>
       <c r="C53" t="n">
-        <v>7824.5</v>
+        <v>7782.5</v>
       </c>
       <c r="D53" t="n">
-        <v>7657.75</v>
+        <v>7655</v>
       </c>
       <c r="E53" t="n">
-        <v>7691.25</v>
+        <v>7722</v>
       </c>
       <c r="F53" t="n">
-        <v>-113.75</v>
+        <v>30.75</v>
       </c>
       <c r="G53" s="5" t="n">
-        <v>-0.0146</v>
+        <v>0.004</v>
       </c>
       <c r="H53" t="n">
-        <v>166.75</v>
+        <v>127.5</v>
       </c>
       <c r="I53" t="n">
-        <v>7637.5</v>
+        <v>7491</v>
       </c>
       <c r="J53" t="n">
-        <v>7712.88</v>
+        <v>7499.56</v>
       </c>
       <c r="K53" t="n">
-        <v>7754.75</v>
+        <v>7607.88</v>
       </c>
       <c r="L53" t="n">
-        <v>7796.62</v>
+        <v>7716.19</v>
       </c>
       <c r="M53" t="n">
-        <v>7855.25</v>
+        <v>7774.62</v>
       </c>
       <c r="N53" t="n">
-        <v>7913.88</v>
+        <v>7833.06</v>
       </c>
       <c r="O53" t="n">
-        <v>7939</v>
+        <v>7991.25</v>
       </c>
       <c r="P53" s="6" t="n">
         <v/>
       </c>
-      <c r="Q53" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="R53" s="6" t="inlineStr">
+      <c r="Q53" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R53" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S53" s="7" t="inlineStr">
+        <is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T53" s="8" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="S53" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T53" s="8" t="n">
-        <v/>
-      </c>
       <c r="U53" s="8" t="n">
         <v/>
       </c>
@@ -4967,55 +4965,59 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X53" t="inlineStr"/>
+      <c r="X53" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="B54" t="n">
-        <v>7693.5</v>
+        <v>7723.5</v>
       </c>
       <c r="C54" t="n">
-        <v>7782.5</v>
+        <v>7766.5</v>
       </c>
       <c r="D54" t="n">
-        <v>7655</v>
+        <v>7618.5</v>
       </c>
       <c r="E54" t="n">
         <v>7722</v>
       </c>
       <c r="F54" t="n">
-        <v>30.75</v>
+        <v>0</v>
       </c>
       <c r="G54" s="5" t="n">
-        <v>0.004</v>
+        <v>0</v>
       </c>
       <c r="H54" t="n">
-        <v>127.5</v>
+        <v>148</v>
       </c>
       <c r="I54" t="n">
-        <v>7491</v>
+        <v>7527.5</v>
       </c>
       <c r="J54" t="n">
-        <v>7499.56</v>
+        <v>7596.12</v>
       </c>
       <c r="K54" t="n">
-        <v>7607.88</v>
+        <v>7658.25</v>
       </c>
       <c r="L54" t="n">
-        <v>7716.19</v>
+        <v>7720.38</v>
       </c>
       <c r="M54" t="n">
-        <v>7774.62</v>
+        <v>7785.75</v>
       </c>
       <c r="N54" t="n">
-        <v>7833.06</v>
+        <v>7851.12</v>
       </c>
       <c r="O54" t="n">
-        <v>7991.25</v>
+        <v>7910</v>
       </c>
       <c r="P54" s="6" t="n">
         <v/>
@@ -5023,18 +5025,18 @@
       <c r="Q54" s="6" t="n">
         <v/>
       </c>
-      <c r="R54" s="6" t="n">
-        <v/>
+      <c r="R54" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S54" s="7" t="inlineStr">
         <is>
           <t>↑C</t>
         </is>
       </c>
-      <c r="T54" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="T54" s="8" t="n">
+        <v/>
       </c>
       <c r="U54" s="8" t="n">
         <v/>
@@ -5047,74 +5049,72 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X54" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="X54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="B55" t="n">
-        <v>7723.5</v>
+        <v>7715.5</v>
       </c>
       <c r="C55" t="n">
-        <v>7766.5</v>
+        <v>7728.5</v>
       </c>
       <c r="D55" t="n">
-        <v>7618.5</v>
+        <v>7585.5</v>
       </c>
       <c r="E55" t="n">
-        <v>7722</v>
+        <v>7659.5</v>
       </c>
       <c r="F55" t="n">
-        <v>0</v>
+        <v>-62.5</v>
       </c>
       <c r="G55" s="5" t="n">
-        <v>0</v>
+        <v>-0.0081</v>
       </c>
       <c r="H55" t="n">
-        <v>148</v>
+        <v>143</v>
       </c>
       <c r="I55" t="n">
-        <v>7527.5</v>
+        <v>7470.5</v>
       </c>
       <c r="J55" t="n">
-        <v>7596.12</v>
+        <v>7588.75</v>
       </c>
       <c r="K55" t="n">
-        <v>7658.25</v>
+        <v>7648</v>
       </c>
       <c r="L55" t="n">
-        <v>7720.38</v>
+        <v>7707.25</v>
       </c>
       <c r="M55" t="n">
-        <v>7785.75</v>
+        <v>7796</v>
       </c>
       <c r="N55" t="n">
-        <v>7851.12</v>
+        <v>7884.75</v>
       </c>
       <c r="O55" t="n">
-        <v>7910</v>
+        <v>7914.5</v>
       </c>
       <c r="P55" s="6" t="n">
         <v/>
       </c>
-      <c r="Q55" s="6" t="n">
-        <v/>
+      <c r="Q55" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="R55" s="6" t="inlineStr">
         <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S55" s="7" t="inlineStr">
-        <is>
-          <t>↑C</t>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="S55" s="10" t="inlineStr">
+        <is>
+          <t>↓</t>
         </is>
       </c>
       <c r="T55" s="8" t="n">
@@ -5136,50 +5136,50 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="B56" t="n">
-        <v>7715.5</v>
+        <v>7609.25</v>
       </c>
       <c r="C56" t="n">
-        <v>7728.5</v>
+        <v>7670.25</v>
       </c>
       <c r="D56" t="n">
-        <v>7585.5</v>
+        <v>7509.25</v>
       </c>
       <c r="E56" t="n">
-        <v>7659.5</v>
+        <v>7657.35</v>
       </c>
       <c r="F56" t="n">
-        <v>-62.5</v>
+        <v>-2.15</v>
       </c>
       <c r="G56" s="5" t="n">
-        <v>-0.0081</v>
+        <v>-0.0003</v>
       </c>
       <c r="H56" t="n">
-        <v>143</v>
+        <v>161</v>
       </c>
       <c r="I56" t="n">
-        <v>7470.5</v>
+        <v>7442.5</v>
       </c>
       <c r="J56" t="n">
-        <v>7588.75</v>
+        <v>7517.75</v>
       </c>
       <c r="K56" t="n">
-        <v>7648</v>
+        <v>7588</v>
       </c>
       <c r="L56" t="n">
-        <v>7707.25</v>
+        <v>7658.25</v>
       </c>
       <c r="M56" t="n">
-        <v>7796</v>
+        <v>7731</v>
       </c>
       <c r="N56" t="n">
-        <v>7884.75</v>
+        <v>7803.75</v>
       </c>
       <c r="O56" t="n">
-        <v>7914.5</v>
+        <v>7871.5</v>
       </c>
       <c r="P56" s="6" t="n">
         <v/>
@@ -5191,12 +5191,12 @@
       </c>
       <c r="R56" s="6" t="inlineStr">
         <is>
-          <t>△C</t>
+          <t>✓</t>
         </is>
       </c>
       <c r="S56" s="10" t="inlineStr">
         <is>
-          <t>↓</t>
+          <t>↓C</t>
         </is>
       </c>
       <c r="T56" s="8" t="n">
@@ -5218,166 +5218,84 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="B57" t="n">
-        <v>7609.25</v>
+        <v>7722</v>
       </c>
       <c r="C57" t="n">
-        <v>7670.25</v>
+        <v>7848.5</v>
       </c>
       <c r="D57" t="n">
-        <v>7509.25</v>
+        <v>7707.25</v>
       </c>
       <c r="E57" t="n">
-        <v>7657.35</v>
+        <v>7803.75</v>
       </c>
       <c r="F57" t="n">
-        <v>-2.15</v>
+        <v>146.4</v>
       </c>
       <c r="G57" s="5" t="n">
-        <v>-0.0003</v>
+        <v>0.0191</v>
       </c>
       <c r="H57" t="n">
-        <v>161</v>
+        <v>141.25</v>
       </c>
       <c r="I57" t="n">
-        <v>7442.5</v>
+        <v>7348.25</v>
       </c>
       <c r="J57" t="n">
-        <v>7517.75</v>
+        <v>7530.15</v>
       </c>
       <c r="K57" t="n">
-        <v>7588</v>
+        <v>7576.85</v>
       </c>
       <c r="L57" t="n">
-        <v>7658.25</v>
+        <v>7623.55</v>
       </c>
       <c r="M57" t="n">
-        <v>7731</v>
+        <v>7737.85</v>
       </c>
       <c r="N57" t="n">
-        <v>7803.75</v>
+        <v>7852.15</v>
       </c>
       <c r="O57" t="n">
-        <v>7871.5</v>
+        <v>7831.25</v>
       </c>
       <c r="P57" s="6" t="n">
         <v/>
       </c>
-      <c r="Q57" s="6" t="inlineStr">
+      <c r="Q57" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R57" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S57" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T57" s="8" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="R57" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S57" s="10" t="inlineStr">
-        <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T57" s="8" t="n">
-        <v/>
-      </c>
       <c r="U57" s="8" t="n">
         <v/>
       </c>
-      <c r="V57" s="8" t="n">
-        <v/>
+      <c r="V57" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="W57" s="11" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
       </c>
-      <c r="X57" t="inlineStr"/>
-    </row>
-    <row r="58">
-      <c r="A58" t="inlineStr">
-        <is>
-          <t>2026-09-21</t>
-        </is>
-      </c>
-      <c r="B58" t="n">
-        <v>7722</v>
-      </c>
-      <c r="C58" t="n">
-        <v>7848.5</v>
-      </c>
-      <c r="D58" t="n">
-        <v>7713.75</v>
-      </c>
-      <c r="E58" t="n">
-        <v>7759</v>
-      </c>
-      <c r="F58" t="n">
-        <v>101.65</v>
-      </c>
-      <c r="G58" s="5" t="n">
-        <v>0.0133</v>
-      </c>
-      <c r="H58" t="n">
-        <v>134.75</v>
-      </c>
-      <c r="I58" t="n">
-        <v>7348.25</v>
-      </c>
-      <c r="J58" t="n">
-        <v>7530.15</v>
-      </c>
-      <c r="K58" t="n">
-        <v>7576.85</v>
-      </c>
-      <c r="L58" t="n">
-        <v>7623.55</v>
-      </c>
-      <c r="M58" t="n">
-        <v>7737.85</v>
-      </c>
-      <c r="N58" t="n">
-        <v>7852.15</v>
-      </c>
-      <c r="O58" t="n">
-        <v>7831.25</v>
-      </c>
-      <c r="P58" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q58" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R58" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S58" s="7" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T58" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="U58" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V58" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="W58" s="11" t="inlineStr">
-        <is>
-          <t>空方</t>
-        </is>
-      </c>
-      <c r="X58" t="inlineStr">
+      <c r="X57" t="inlineStr">
         <is>
           <t>強警訊</t>
         </is>

--- a/three_gate/analysis/ES_weekly.xlsx
+++ b/three_gate/analysis/ES_weekly.xlsx
@@ -480,7 +480,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X57"/>
+  <dimension ref="A1:X58"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -5301,6 +5301,90 @@
         </is>
       </c>
     </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="B58" t="n">
+        <v>7746.5</v>
+      </c>
+      <c r="C58" t="n">
+        <v>7748.25</v>
+      </c>
+      <c r="D58" t="n">
+        <v>7741</v>
+      </c>
+      <c r="E58" t="n">
+        <v>7742.5</v>
+      </c>
+      <c r="F58" t="n">
+        <v>-61.25</v>
+      </c>
+      <c r="G58" s="5" t="n">
+        <v>-0.0078</v>
+      </c>
+      <c r="H58" t="n">
+        <v>7.25</v>
+      </c>
+      <c r="I58" t="n">
+        <v>7566</v>
+      </c>
+      <c r="J58" t="n">
+        <v>7675.44</v>
+      </c>
+      <c r="K58" t="n">
+        <v>7733.12</v>
+      </c>
+      <c r="L58" t="n">
+        <v>7790.81</v>
+      </c>
+      <c r="M58" t="n">
+        <v>7874.38</v>
+      </c>
+      <c r="N58" t="n">
+        <v>7957.94</v>
+      </c>
+      <c r="O58" t="n">
+        <v>7989.75</v>
+      </c>
+      <c r="P58" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q58" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R58" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="S58" s="10" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T58" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U58" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V58" s="8" t="n">
+        <v/>
+      </c>
+      <c r="W58" s="11" t="inlineStr">
+        <is>
+          <t>空方</t>
+        </is>
+      </c>
+      <c r="X58" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/three_gate/analysis/ES_weekly.xlsx
+++ b/three_gate/analysis/ES_weekly.xlsx
@@ -5308,25 +5308,25 @@
         </is>
       </c>
       <c r="B58" t="n">
-        <v>7746.5</v>
+        <v>7796</v>
       </c>
       <c r="C58" t="n">
-        <v>7748.25</v>
+        <v>7803</v>
       </c>
       <c r="D58" t="n">
-        <v>7741</v>
+        <v>7726</v>
       </c>
       <c r="E58" t="n">
-        <v>7742.5</v>
+        <v>7745</v>
       </c>
       <c r="F58" t="n">
-        <v>-61.25</v>
+        <v>-58.75</v>
       </c>
       <c r="G58" s="5" t="n">
-        <v>-0.0078</v>
+        <v>-0.0075</v>
       </c>
       <c r="H58" t="n">
-        <v>7.25</v>
+        <v>77</v>
       </c>
       <c r="I58" t="n">
         <v>7566</v>

--- a/three_gate/analysis/ES_weekly.xlsx
+++ b/three_gate/analysis/ES_weekly.xlsx
@@ -659,28 +659,30 @@
         <v>170</v>
       </c>
       <c r="I2" t="n">
-        <v>6338.5</v>
+        <v>6388</v>
       </c>
       <c r="J2" t="n">
-        <v>6378.44</v>
+        <v>6397</v>
       </c>
       <c r="K2" t="n">
-        <v>6426.62</v>
+        <v>6439</v>
       </c>
       <c r="L2" t="n">
-        <v>6474.81</v>
+        <v>6481</v>
       </c>
       <c r="M2" t="n">
-        <v>6518.88</v>
+        <v>6506.5</v>
       </c>
       <c r="N2" t="n">
-        <v>6562.94</v>
+        <v>6532</v>
       </c>
       <c r="O2" t="n">
-        <v>6615.25</v>
-      </c>
-      <c r="P2" s="6" t="n">
-        <v/>
+        <v>6590.5</v>
+      </c>
+      <c r="P2" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="Q2" s="6" t="inlineStr">
         <is>
@@ -702,8 +704,10 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="U2" s="8" t="n">
-        <v/>
+      <c r="U2" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="V2" s="8" t="n">
         <v/>
@@ -5314,19 +5318,19 @@
         <v>7803</v>
       </c>
       <c r="D58" t="n">
-        <v>7726</v>
+        <v>7712.25</v>
       </c>
       <c r="E58" t="n">
-        <v>7745</v>
+        <v>7725.25</v>
       </c>
       <c r="F58" t="n">
-        <v>-58.75</v>
+        <v>-78.5</v>
       </c>
       <c r="G58" s="5" t="n">
-        <v>-0.0075</v>
+        <v>-0.0101</v>
       </c>
       <c r="H58" t="n">
-        <v>77</v>
+        <v>90.75</v>
       </c>
       <c r="I58" t="n">
         <v>7566</v>

--- a/three_gate/analysis/ES_weekly.xlsx
+++ b/three_gate/analysis/ES_weekly.xlsx
@@ -5318,19 +5318,19 @@
         <v>7803</v>
       </c>
       <c r="D58" t="n">
-        <v>7712.25</v>
+        <v>7705.5</v>
       </c>
       <c r="E58" t="n">
-        <v>7725.25</v>
+        <v>7726</v>
       </c>
       <c r="F58" t="n">
-        <v>-78.5</v>
+        <v>-77.75</v>
       </c>
       <c r="G58" s="5" t="n">
-        <v>-0.0101</v>
+        <v>-0.01</v>
       </c>
       <c r="H58" t="n">
-        <v>90.75</v>
+        <v>97.5</v>
       </c>
       <c r="I58" t="n">
         <v>7566</v>
@@ -5383,11 +5383,7 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X58" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="X58" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/three_gate/analysis/ES_weekly.xlsx
+++ b/three_gate/analysis/ES_weekly.xlsx
@@ -480,7 +480,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X58"/>
+  <dimension ref="A1:X57"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -634,80 +634,72 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2025-09-01</t>
+          <t>2025-09-08</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>6478.75</v>
+        <v>6483.75</v>
       </c>
       <c r="C2" t="n">
-        <v>6541.75</v>
+        <v>6606</v>
       </c>
       <c r="D2" t="n">
-        <v>6371.75</v>
+        <v>6480.25</v>
       </c>
       <c r="E2" t="n">
-        <v>6489.75</v>
+        <v>6588.25</v>
       </c>
       <c r="F2" t="n">
-        <v>17</v>
+        <v>98.5</v>
       </c>
       <c r="G2" s="5" t="n">
-        <v>0.0026</v>
+        <v>0.0152</v>
       </c>
       <c r="H2" t="n">
-        <v>170</v>
+        <v>125.75</v>
       </c>
       <c r="I2" t="n">
-        <v>6388</v>
+        <v>6201.75</v>
       </c>
       <c r="J2" t="n">
-        <v>6397</v>
+        <v>6336.25</v>
       </c>
       <c r="K2" t="n">
-        <v>6439</v>
+        <v>6404.75</v>
       </c>
       <c r="L2" t="n">
-        <v>6481</v>
+        <v>6473.25</v>
       </c>
       <c r="M2" t="n">
-        <v>6506.5</v>
+        <v>6574.75</v>
       </c>
       <c r="N2" t="n">
-        <v>6532</v>
+        <v>6676.25</v>
       </c>
       <c r="O2" t="n">
-        <v>6590.5</v>
-      </c>
-      <c r="P2" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="Q2" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="R2" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+        <v>6711.75</v>
+      </c>
+      <c r="P2" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q2" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R2" s="6" t="n">
+        <v/>
       </c>
       <c r="S2" s="7" t="inlineStr">
         <is>
-          <t>↑C</t>
+          <t>↑</t>
         </is>
       </c>
       <c r="T2" s="8" t="inlineStr">
         <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U2" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="U2" s="8" t="n">
+        <v/>
       </c>
       <c r="V2" s="8" t="n">
         <v/>
@@ -717,59 +709,55 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X2" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="X2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2025-09-08</t>
+          <t>2025-09-15</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>6483.75</v>
+        <v>6588.25</v>
       </c>
       <c r="C3" t="n">
-        <v>6606</v>
+        <v>6662</v>
       </c>
       <c r="D3" t="n">
-        <v>6480.25</v>
+        <v>6554</v>
       </c>
       <c r="E3" t="n">
-        <v>6588.25</v>
+        <v>6658.77</v>
       </c>
       <c r="F3" t="n">
-        <v>98.5</v>
+        <v>70.52</v>
       </c>
       <c r="G3" s="5" t="n">
-        <v>0.0152</v>
+        <v>0.0107</v>
       </c>
       <c r="H3" t="n">
-        <v>125.75</v>
+        <v>108</v>
       </c>
       <c r="I3" t="n">
-        <v>6201.75</v>
+        <v>6354.5</v>
       </c>
       <c r="J3" t="n">
-        <v>6336.25</v>
+        <v>6485.06</v>
       </c>
       <c r="K3" t="n">
-        <v>6404.75</v>
+        <v>6525.38</v>
       </c>
       <c r="L3" t="n">
-        <v>6473.25</v>
+        <v>6565.69</v>
       </c>
       <c r="M3" t="n">
-        <v>6574.75</v>
+        <v>6651.12</v>
       </c>
       <c r="N3" t="n">
-        <v>6676.25</v>
+        <v>6736.56</v>
       </c>
       <c r="O3" t="n">
-        <v>6711.75</v>
+        <v>6731.75</v>
       </c>
       <c r="P3" s="6" t="n">
         <v/>
@@ -806,50 +794,50 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2025-09-15</t>
+          <t>2025-09-22</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>6588.25</v>
+        <v>6716</v>
       </c>
       <c r="C4" t="n">
-        <v>6662</v>
+        <v>6756.75</v>
       </c>
       <c r="D4" t="n">
-        <v>6554</v>
+        <v>6624.25</v>
       </c>
       <c r="E4" t="n">
-        <v>6658.77</v>
+        <v>6696.5</v>
       </c>
       <c r="F4" t="n">
-        <v>70.52</v>
+        <v>37.73</v>
       </c>
       <c r="G4" s="5" t="n">
-        <v>0.0107</v>
+        <v>0.0057</v>
       </c>
       <c r="H4" t="n">
-        <v>108</v>
+        <v>132.5</v>
       </c>
       <c r="I4" t="n">
-        <v>6354.5</v>
+        <v>6446</v>
       </c>
       <c r="J4" t="n">
-        <v>6485.06</v>
+        <v>6576.16</v>
       </c>
       <c r="K4" t="n">
-        <v>6525.38</v>
+        <v>6604.77</v>
       </c>
       <c r="L4" t="n">
-        <v>6565.69</v>
+        <v>6633.39</v>
       </c>
       <c r="M4" t="n">
-        <v>6651.12</v>
+        <v>6712.77</v>
       </c>
       <c r="N4" t="n">
-        <v>6736.56</v>
+        <v>6792.16</v>
       </c>
       <c r="O4" t="n">
-        <v>6731.75</v>
+        <v>6770</v>
       </c>
       <c r="P4" s="6" t="n">
         <v/>
@@ -886,50 +874,50 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2025-09-22</t>
+          <t>2025-09-29</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>6716</v>
+        <v>6697</v>
       </c>
       <c r="C5" t="n">
-        <v>6756.75</v>
+        <v>6800</v>
       </c>
       <c r="D5" t="n">
-        <v>6624.25</v>
+        <v>6680</v>
       </c>
       <c r="E5" t="n">
-        <v>6696.5</v>
+        <v>6764</v>
       </c>
       <c r="F5" t="n">
-        <v>37.73</v>
+        <v>67.5</v>
       </c>
       <c r="G5" s="5" t="n">
-        <v>0.0057</v>
+        <v>0.0101</v>
       </c>
       <c r="H5" t="n">
-        <v>132.5</v>
+        <v>120</v>
       </c>
       <c r="I5" t="n">
-        <v>6446</v>
+        <v>6491.75</v>
       </c>
       <c r="J5" t="n">
-        <v>6576.16</v>
+        <v>6567</v>
       </c>
       <c r="K5" t="n">
-        <v>6604.77</v>
+        <v>6630.25</v>
       </c>
       <c r="L5" t="n">
-        <v>6633.39</v>
+        <v>6693.5</v>
       </c>
       <c r="M5" t="n">
-        <v>6712.77</v>
+        <v>6762.75</v>
       </c>
       <c r="N5" t="n">
-        <v>6792.16</v>
+        <v>6832</v>
       </c>
       <c r="O5" t="n">
-        <v>6770</v>
+        <v>6889.25</v>
       </c>
       <c r="P5" s="6" t="n">
         <v/>
@@ -966,154 +954,158 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2025-09-29</t>
+          <t>2025-10-06</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>6697</v>
+        <v>6768</v>
       </c>
       <c r="C6" t="n">
-        <v>6800</v>
+        <v>6812.25</v>
       </c>
       <c r="D6" t="n">
-        <v>6680</v>
+        <v>6540.25</v>
       </c>
       <c r="E6" t="n">
-        <v>6764</v>
+        <v>6595.25</v>
       </c>
       <c r="F6" t="n">
-        <v>67.5</v>
+        <v>-168.75</v>
       </c>
       <c r="G6" s="5" t="n">
-        <v>0.0101</v>
+        <v>-0.0249</v>
       </c>
       <c r="H6" t="n">
-        <v>120</v>
+        <v>272</v>
       </c>
       <c r="I6" t="n">
-        <v>6491.75</v>
+        <v>6560</v>
       </c>
       <c r="J6" t="n">
-        <v>6567</v>
+        <v>6656</v>
       </c>
       <c r="K6" t="n">
-        <v>6630.25</v>
+        <v>6704</v>
       </c>
       <c r="L6" t="n">
-        <v>6693.5</v>
+        <v>6752</v>
       </c>
       <c r="M6" t="n">
-        <v>6762.75</v>
+        <v>6824</v>
       </c>
       <c r="N6" t="n">
-        <v>6832</v>
+        <v>6896</v>
       </c>
       <c r="O6" t="n">
-        <v>6889.25</v>
-      </c>
-      <c r="P6" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q6" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R6" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S6" s="7" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T6" s="8" t="inlineStr">
+        <v>6920</v>
+      </c>
+      <c r="P6" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
+      <c r="Q6" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="R6" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S6" s="10" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T6" s="8" t="n">
+        <v/>
+      </c>
       <c r="U6" s="8" t="n">
         <v/>
       </c>
       <c r="V6" s="8" t="n">
         <v/>
       </c>
-      <c r="W6" s="9" t="inlineStr">
-        <is>
-          <t>多方</t>
-        </is>
-      </c>
-      <c r="X6" t="inlineStr"/>
+      <c r="W6" s="11" t="inlineStr">
+        <is>
+          <t>空方</t>
+        </is>
+      </c>
+      <c r="X6" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2025-10-06</t>
+          <t>2025-10-13</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>6768</v>
+        <v>6632</v>
       </c>
       <c r="C7" t="n">
-        <v>6812.25</v>
+        <v>6766.75</v>
       </c>
       <c r="D7" t="n">
-        <v>6540.25</v>
+        <v>6571.25</v>
       </c>
       <c r="E7" t="n">
-        <v>6595.25</v>
+        <v>6702.5</v>
       </c>
       <c r="F7" t="n">
-        <v>-168.75</v>
+        <v>107.25</v>
       </c>
       <c r="G7" s="5" t="n">
-        <v>-0.0249</v>
+        <v>0.0163</v>
       </c>
       <c r="H7" t="n">
-        <v>272</v>
+        <v>195.5</v>
       </c>
       <c r="I7" t="n">
-        <v>6560</v>
+        <v>6268.25</v>
       </c>
       <c r="J7" t="n">
-        <v>6656</v>
+        <v>6282.75</v>
       </c>
       <c r="K7" t="n">
-        <v>6704</v>
+        <v>6459.25</v>
       </c>
       <c r="L7" t="n">
-        <v>6752</v>
+        <v>6635.75</v>
       </c>
       <c r="M7" t="n">
-        <v>6824</v>
+        <v>6731.25</v>
       </c>
       <c r="N7" t="n">
-        <v>6896</v>
+        <v>6826.75</v>
       </c>
       <c r="O7" t="n">
-        <v>6920</v>
-      </c>
-      <c r="P7" s="6" t="inlineStr">
+        <v>7084.25</v>
+      </c>
+      <c r="P7" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q7" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R7" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S7" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T7" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="Q7" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="R7" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S7" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T7" s="8" t="n">
-        <v/>
-      </c>
       <c r="U7" s="8" t="n">
         <v/>
       </c>
@@ -1127,57 +1119,57 @@
       </c>
       <c r="X7" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2025-10-13</t>
+          <t>2025-10-20</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>6632</v>
+        <v>6721</v>
       </c>
       <c r="C8" t="n">
-        <v>6766.75</v>
+        <v>6841.25</v>
       </c>
       <c r="D8" t="n">
-        <v>6571.25</v>
+        <v>6690.75</v>
       </c>
       <c r="E8" t="n">
-        <v>6702.5</v>
+        <v>6827</v>
       </c>
       <c r="F8" t="n">
-        <v>107.25</v>
+        <v>124.5</v>
       </c>
       <c r="G8" s="5" t="n">
-        <v>0.0163</v>
+        <v>0.0186</v>
       </c>
       <c r="H8" t="n">
-        <v>195.5</v>
+        <v>150.5</v>
       </c>
       <c r="I8" t="n">
-        <v>6268.25</v>
+        <v>6375.75</v>
       </c>
       <c r="J8" t="n">
-        <v>6282.75</v>
+        <v>6523.75</v>
       </c>
       <c r="K8" t="n">
-        <v>6459.25</v>
+        <v>6604.75</v>
       </c>
       <c r="L8" t="n">
-        <v>6635.75</v>
+        <v>6685.75</v>
       </c>
       <c r="M8" t="n">
-        <v>6731.25</v>
+        <v>6800.25</v>
       </c>
       <c r="N8" t="n">
-        <v>6826.75</v>
+        <v>6914.75</v>
       </c>
       <c r="O8" t="n">
-        <v>7084.25</v>
+        <v>6962.25</v>
       </c>
       <c r="P8" s="6" t="n">
         <v/>
@@ -1211,57 +1203,57 @@
       </c>
       <c r="X8" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2025-10-20</t>
+          <t>2025-10-27</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>6721</v>
+        <v>6881</v>
       </c>
       <c r="C9" t="n">
-        <v>6841.25</v>
+        <v>6953.75</v>
       </c>
       <c r="D9" t="n">
-        <v>6690.75</v>
+        <v>6843.5</v>
       </c>
       <c r="E9" t="n">
-        <v>6827</v>
+        <v>6874</v>
       </c>
       <c r="F9" t="n">
-        <v>124.5</v>
+        <v>47</v>
       </c>
       <c r="G9" s="5" t="n">
-        <v>0.0186</v>
+        <v>0.0069</v>
       </c>
       <c r="H9" t="n">
-        <v>150.5</v>
+        <v>110.25</v>
       </c>
       <c r="I9" t="n">
-        <v>6375.75</v>
+        <v>6540.25</v>
       </c>
       <c r="J9" t="n">
-        <v>6523.75</v>
+        <v>6707</v>
       </c>
       <c r="K9" t="n">
-        <v>6604.75</v>
+        <v>6751.75</v>
       </c>
       <c r="L9" t="n">
-        <v>6685.75</v>
+        <v>6796.5</v>
       </c>
       <c r="M9" t="n">
-        <v>6800.25</v>
+        <v>6902.25</v>
       </c>
       <c r="N9" t="n">
-        <v>6914.75</v>
+        <v>7008</v>
       </c>
       <c r="O9" t="n">
-        <v>6962.25</v>
+        <v>6991.75</v>
       </c>
       <c r="P9" s="6" t="n">
         <v/>
@@ -1302,70 +1294,74 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2025-10-27</t>
+          <t>2025-11-03</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>6881</v>
+        <v>6878</v>
       </c>
       <c r="C10" t="n">
-        <v>6953.75</v>
+        <v>6909.5</v>
       </c>
       <c r="D10" t="n">
-        <v>6843.5</v>
+        <v>6655.5</v>
       </c>
       <c r="E10" t="n">
-        <v>6874</v>
+        <v>6753.75</v>
       </c>
       <c r="F10" t="n">
-        <v>47</v>
+        <v>-120.25</v>
       </c>
       <c r="G10" s="5" t="n">
-        <v>0.0069</v>
+        <v>-0.0175</v>
       </c>
       <c r="H10" t="n">
-        <v>110.25</v>
+        <v>254</v>
       </c>
       <c r="I10" t="n">
-        <v>6540.25</v>
+        <v>6733.25</v>
       </c>
       <c r="J10" t="n">
-        <v>6707</v>
+        <v>6751.44</v>
       </c>
       <c r="K10" t="n">
-        <v>6751.75</v>
+        <v>6818.88</v>
       </c>
       <c r="L10" t="n">
-        <v>6796.5</v>
+        <v>6886.31</v>
       </c>
       <c r="M10" t="n">
-        <v>6902.25</v>
+        <v>6929.12</v>
       </c>
       <c r="N10" t="n">
-        <v>7008</v>
+        <v>6971.94</v>
       </c>
       <c r="O10" t="n">
-        <v>6991.75</v>
-      </c>
-      <c r="P10" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q10" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R10" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S10" s="7" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T10" s="8" t="inlineStr">
+        <v>7064</v>
+      </c>
+      <c r="P10" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="Q10" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
+      <c r="R10" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S10" s="10" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T10" s="8" t="n">
+        <v/>
+      </c>
       <c r="U10" s="8" t="n">
         <v/>
       </c>
@@ -1377,83 +1373,75 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X10" t="inlineStr">
-        <is>
-          <t>強警訊</t>
-        </is>
-      </c>
+      <c r="X10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2025-11-03</t>
+          <t>2025-11-10</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>6878</v>
+        <v>6788</v>
       </c>
       <c r="C11" t="n">
-        <v>6909.5</v>
+        <v>6900.5</v>
       </c>
       <c r="D11" t="n">
-        <v>6655.5</v>
+        <v>6670.5</v>
       </c>
       <c r="E11" t="n">
-        <v>6753.75</v>
+        <v>6755.25</v>
       </c>
       <c r="F11" t="n">
-        <v>-120.25</v>
+        <v>1.5</v>
       </c>
       <c r="G11" s="5" t="n">
-        <v>-0.0175</v>
+        <v>0.0002</v>
       </c>
       <c r="H11" t="n">
-        <v>254</v>
+        <v>230</v>
       </c>
       <c r="I11" t="n">
-        <v>6733.25</v>
+        <v>6401.5</v>
       </c>
       <c r="J11" t="n">
-        <v>6751.44</v>
+        <v>6485.38</v>
       </c>
       <c r="K11" t="n">
-        <v>6818.88</v>
+        <v>6626.75</v>
       </c>
       <c r="L11" t="n">
-        <v>6886.31</v>
+        <v>6768.12</v>
       </c>
       <c r="M11" t="n">
-        <v>6929.12</v>
+        <v>6880.75</v>
       </c>
       <c r="N11" t="n">
-        <v>6971.94</v>
+        <v>6993.38</v>
       </c>
       <c r="O11" t="n">
-        <v>7064</v>
-      </c>
-      <c r="P11" s="6" t="inlineStr">
+        <v>7163.5</v>
+      </c>
+      <c r="P11" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q11" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R11" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S11" s="10" t="inlineStr">
+        <is>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T11" s="8" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="Q11" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="R11" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S11" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T11" s="8" t="n">
-        <v/>
-      </c>
       <c r="U11" s="8" t="n">
         <v/>
       </c>
@@ -1465,55 +1453,59 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X11" t="inlineStr"/>
+      <c r="X11" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2025-11-10</t>
+          <t>2025-11-17</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>6788</v>
+        <v>6764.75</v>
       </c>
       <c r="C12" t="n">
-        <v>6900.5</v>
+        <v>6801.5</v>
       </c>
       <c r="D12" t="n">
-        <v>6670.5</v>
+        <v>6525</v>
       </c>
       <c r="E12" t="n">
-        <v>6755.25</v>
+        <v>6620.25</v>
       </c>
       <c r="F12" t="n">
-        <v>1.5</v>
+        <v>-135</v>
       </c>
       <c r="G12" s="5" t="n">
-        <v>0.0002</v>
+        <v>-0.02</v>
       </c>
       <c r="H12" t="n">
-        <v>230</v>
+        <v>276.5</v>
       </c>
       <c r="I12" t="n">
-        <v>6401.5</v>
+        <v>6440.5</v>
       </c>
       <c r="J12" t="n">
-        <v>6485.38</v>
+        <v>6510.12</v>
       </c>
       <c r="K12" t="n">
-        <v>6626.75</v>
+        <v>6640.25</v>
       </c>
       <c r="L12" t="n">
-        <v>6768.12</v>
+        <v>6770.38</v>
       </c>
       <c r="M12" t="n">
-        <v>6880.75</v>
+        <v>6870.25</v>
       </c>
       <c r="N12" t="n">
-        <v>6993.38</v>
+        <v>6970.12</v>
       </c>
       <c r="O12" t="n">
-        <v>7163.5</v>
+        <v>7130.5</v>
       </c>
       <c r="P12" s="6" t="n">
         <v/>
@@ -1521,18 +1513,18 @@
       <c r="Q12" s="6" t="n">
         <v/>
       </c>
-      <c r="R12" s="6" t="n">
-        <v/>
+      <c r="R12" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="S12" s="10" t="inlineStr">
         <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T12" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T12" s="8" t="n">
+        <v/>
       </c>
       <c r="U12" s="8" t="n">
         <v/>
@@ -1545,59 +1537,55 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X12" t="inlineStr">
-        <is>
-          <t>中警訊</t>
-        </is>
-      </c>
+      <c r="X12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2025-11-17</t>
+          <t>2025-11-24</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>6764.75</v>
+        <v>6654.75</v>
       </c>
       <c r="C13" t="n">
-        <v>6801.5</v>
+        <v>6863.75</v>
       </c>
       <c r="D13" t="n">
-        <v>6525</v>
+        <v>6625</v>
       </c>
       <c r="E13" t="n">
-        <v>6620.25</v>
+        <v>6859.5</v>
       </c>
       <c r="F13" t="n">
-        <v>-135</v>
+        <v>239.25</v>
       </c>
       <c r="G13" s="5" t="n">
-        <v>-0.02</v>
+        <v>0.0361</v>
       </c>
       <c r="H13" t="n">
-        <v>276.5</v>
+        <v>238.75</v>
       </c>
       <c r="I13" t="n">
-        <v>6440.5</v>
+        <v>6248.5</v>
       </c>
       <c r="J13" t="n">
-        <v>6510.12</v>
+        <v>6322.25</v>
       </c>
       <c r="K13" t="n">
-        <v>6640.25</v>
+        <v>6482</v>
       </c>
       <c r="L13" t="n">
-        <v>6770.38</v>
+        <v>6641.75</v>
       </c>
       <c r="M13" t="n">
-        <v>6870.25</v>
+        <v>6758.5</v>
       </c>
       <c r="N13" t="n">
-        <v>6970.12</v>
+        <v>6875.25</v>
       </c>
       <c r="O13" t="n">
-        <v>7130.5</v>
+        <v>7078</v>
       </c>
       <c r="P13" s="6" t="n">
         <v/>
@@ -1605,22 +1593,24 @@
       <c r="Q13" s="6" t="n">
         <v/>
       </c>
-      <c r="R13" s="6" t="inlineStr">
+      <c r="R13" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S13" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T13" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U13" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="S13" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T13" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U13" s="8" t="n">
-        <v/>
-      </c>
       <c r="V13" s="8" t="n">
         <v/>
       </c>
@@ -1629,55 +1619,59 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X13" t="inlineStr"/>
+      <c r="X13" t="inlineStr">
+        <is>
+          <t>強警訊</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2025-11-24</t>
+          <t>2025-12-01</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>6654.75</v>
+        <v>6854.75</v>
       </c>
       <c r="C14" t="n">
-        <v>6863.75</v>
+        <v>6905</v>
       </c>
       <c r="D14" t="n">
-        <v>6625</v>
+        <v>6802</v>
       </c>
       <c r="E14" t="n">
-        <v>6859.5</v>
+        <v>6878.25</v>
       </c>
       <c r="F14" t="n">
-        <v>239.25</v>
+        <v>18.75</v>
       </c>
       <c r="G14" s="5" t="n">
-        <v>0.0361</v>
+        <v>0.0027</v>
       </c>
       <c r="H14" t="n">
-        <v>238.75</v>
+        <v>103</v>
       </c>
       <c r="I14" t="n">
-        <v>6248.5</v>
+        <v>6386.25</v>
       </c>
       <c r="J14" t="n">
-        <v>6322.25</v>
+        <v>6678.31</v>
       </c>
       <c r="K14" t="n">
-        <v>6482</v>
+        <v>6740.12</v>
       </c>
       <c r="L14" t="n">
-        <v>6641.75</v>
+        <v>6801.94</v>
       </c>
       <c r="M14" t="n">
-        <v>6758.5</v>
+        <v>6978.88</v>
       </c>
       <c r="N14" t="n">
-        <v>6875.25</v>
+        <v>7155.81</v>
       </c>
       <c r="O14" t="n">
-        <v>7078</v>
+        <v>7102.5</v>
       </c>
       <c r="P14" s="6" t="n">
         <v/>
@@ -1690,18 +1684,14 @@
       </c>
       <c r="S14" s="7" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T14" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U14" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T14" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U14" s="8" t="n">
+        <v/>
       </c>
       <c r="V14" s="8" t="n">
         <v/>
@@ -1720,50 +1710,50 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2025-12-01</t>
+          <t>2025-12-08</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>6854.75</v>
+        <v>6883</v>
       </c>
       <c r="C15" t="n">
-        <v>6905</v>
+        <v>6928.75</v>
       </c>
       <c r="D15" t="n">
-        <v>6802</v>
+        <v>6805</v>
       </c>
       <c r="E15" t="n">
-        <v>6878.25</v>
+        <v>6830.75</v>
       </c>
       <c r="F15" t="n">
-        <v>18.75</v>
+        <v>-47.5</v>
       </c>
       <c r="G15" s="5" t="n">
-        <v>0.0027</v>
+        <v>-0.0069</v>
       </c>
       <c r="H15" t="n">
-        <v>103</v>
+        <v>123.75</v>
       </c>
       <c r="I15" t="n">
-        <v>6386.25</v>
+        <v>6699</v>
       </c>
       <c r="J15" t="n">
-        <v>6678.31</v>
+        <v>6787.62</v>
       </c>
       <c r="K15" t="n">
-        <v>6740.12</v>
+        <v>6826.75</v>
       </c>
       <c r="L15" t="n">
-        <v>6801.94</v>
+        <v>6865.88</v>
       </c>
       <c r="M15" t="n">
-        <v>6978.88</v>
+        <v>6929.75</v>
       </c>
       <c r="N15" t="n">
-        <v>7155.81</v>
+        <v>6993.62</v>
       </c>
       <c r="O15" t="n">
-        <v>7102.5</v>
+        <v>7008</v>
       </c>
       <c r="P15" s="6" t="n">
         <v/>
@@ -1771,12 +1761,14 @@
       <c r="Q15" s="6" t="n">
         <v/>
       </c>
-      <c r="R15" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S15" s="7" t="inlineStr">
-        <is>
-          <t>↑C</t>
+      <c r="R15" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="S15" s="10" t="inlineStr">
+        <is>
+          <t>↓</t>
         </is>
       </c>
       <c r="T15" s="8" t="n">
@@ -1795,57 +1787,57 @@
       </c>
       <c r="X15" t="inlineStr">
         <is>
-          <t>強警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2025-12-08</t>
+          <t>2025-12-15</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>6883</v>
+        <v>6831</v>
       </c>
       <c r="C16" t="n">
-        <v>6928.75</v>
+        <v>6872.5</v>
       </c>
       <c r="D16" t="n">
-        <v>6805</v>
+        <v>6720.25</v>
       </c>
       <c r="E16" t="n">
-        <v>6830.75</v>
+        <v>6796.54</v>
       </c>
       <c r="F16" t="n">
-        <v>-47.5</v>
+        <v>-34.21</v>
       </c>
       <c r="G16" s="5" t="n">
-        <v>-0.0069</v>
+        <v>-0.005</v>
       </c>
       <c r="H16" t="n">
-        <v>123.75</v>
+        <v>152.25</v>
       </c>
       <c r="I16" t="n">
-        <v>6699</v>
+        <v>6681.25</v>
       </c>
       <c r="J16" t="n">
-        <v>6787.62</v>
+        <v>6688.94</v>
       </c>
       <c r="K16" t="n">
-        <v>6826.75</v>
+        <v>6768.88</v>
       </c>
       <c r="L16" t="n">
-        <v>6865.88</v>
+        <v>6848.81</v>
       </c>
       <c r="M16" t="n">
-        <v>6929.75</v>
+        <v>6892.62</v>
       </c>
       <c r="N16" t="n">
-        <v>6993.62</v>
+        <v>6936.44</v>
       </c>
       <c r="O16" t="n">
-        <v>7008</v>
+        <v>7052.5</v>
       </c>
       <c r="P16" s="6" t="n">
         <v/>
@@ -1877,59 +1869,55 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X16" t="inlineStr">
-        <is>
-          <t>中警訊</t>
-        </is>
-      </c>
+      <c r="X16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2025-12-15</t>
+          <t>2025-12-22</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>6831</v>
+        <v>6906.25</v>
       </c>
       <c r="C17" t="n">
-        <v>6872.5</v>
+        <v>6994</v>
       </c>
       <c r="D17" t="n">
-        <v>6720.25</v>
+        <v>6900.5</v>
       </c>
       <c r="E17" t="n">
-        <v>6796.54</v>
+        <v>6979.25</v>
       </c>
       <c r="F17" t="n">
-        <v>-34.21</v>
+        <v>182.71</v>
       </c>
       <c r="G17" s="5" t="n">
-        <v>-0.005</v>
+        <v>0.0269</v>
       </c>
       <c r="H17" t="n">
-        <v>152.25</v>
+        <v>93.5</v>
       </c>
       <c r="I17" t="n">
-        <v>6681.25</v>
+        <v>6568</v>
       </c>
       <c r="J17" t="n">
-        <v>6688.94</v>
+        <v>6644.37</v>
       </c>
       <c r="K17" t="n">
-        <v>6768.88</v>
+        <v>6720.42</v>
       </c>
       <c r="L17" t="n">
-        <v>6848.81</v>
+        <v>6796.46</v>
       </c>
       <c r="M17" t="n">
-        <v>6892.62</v>
+        <v>6872.67</v>
       </c>
       <c r="N17" t="n">
-        <v>6936.44</v>
+        <v>6948.87</v>
       </c>
       <c r="O17" t="n">
-        <v>7052.5</v>
+        <v>7024.75</v>
       </c>
       <c r="P17" s="6" t="n">
         <v/>
@@ -1937,28 +1925,30 @@
       <c r="Q17" s="6" t="n">
         <v/>
       </c>
-      <c r="R17" s="6" t="inlineStr">
+      <c r="R17" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S17" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T17" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U17" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="S17" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T17" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U17" s="8" t="n">
-        <v/>
-      </c>
       <c r="V17" s="8" t="n">
         <v/>
       </c>
-      <c r="W17" s="11" t="inlineStr">
-        <is>
-          <t>空方</t>
+      <c r="W17" s="9" t="inlineStr">
+        <is>
+          <t>多方</t>
         </is>
       </c>
       <c r="X17" t="inlineStr"/>
@@ -1966,81 +1956,81 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2025-12-22</t>
+          <t>2025-12-29</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>6906.25</v>
+        <v>6980.5</v>
       </c>
       <c r="C18" t="n">
-        <v>6994</v>
+        <v>6984.75</v>
       </c>
       <c r="D18" t="n">
+        <v>6866.75</v>
+      </c>
+      <c r="E18" t="n">
         <v>6900.5</v>
       </c>
-      <c r="E18" t="n">
-        <v>6979.25</v>
-      </c>
       <c r="F18" t="n">
-        <v>182.71</v>
+        <v>-78.75</v>
       </c>
       <c r="G18" s="5" t="n">
-        <v>0.0269</v>
+        <v>-0.0113</v>
       </c>
       <c r="H18" t="n">
-        <v>93.5</v>
+        <v>118</v>
       </c>
       <c r="I18" t="n">
-        <v>6568</v>
+        <v>6807</v>
       </c>
       <c r="J18" t="n">
-        <v>6644.37</v>
+        <v>6901.75</v>
       </c>
       <c r="K18" t="n">
-        <v>6720.42</v>
+        <v>6932.5</v>
       </c>
       <c r="L18" t="n">
-        <v>6796.46</v>
+        <v>6963.25</v>
       </c>
       <c r="M18" t="n">
-        <v>6872.67</v>
+        <v>7026</v>
       </c>
       <c r="N18" t="n">
-        <v>6948.87</v>
+        <v>7088.75</v>
       </c>
       <c r="O18" t="n">
-        <v>7024.75</v>
+        <v>7087.5</v>
       </c>
       <c r="P18" s="6" t="n">
         <v/>
       </c>
-      <c r="Q18" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R18" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S18" s="7" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T18" s="8" t="inlineStr">
+      <c r="Q18" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="R18" s="6" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="U18" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+      <c r="S18" s="10" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T18" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U18" s="8" t="n">
+        <v/>
       </c>
       <c r="V18" s="8" t="n">
         <v/>
       </c>
-      <c r="W18" s="9" t="inlineStr">
-        <is>
-          <t>多方</t>
+      <c r="W18" s="11" t="inlineStr">
+        <is>
+          <t>空方</t>
         </is>
       </c>
       <c r="X18" t="inlineStr"/>
@@ -2048,75 +2038,75 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2025-12-29</t>
+          <t>2026-01-05</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>6980.5</v>
+        <v>6911.5</v>
       </c>
       <c r="C19" t="n">
-        <v>6984.75</v>
+        <v>7017.5</v>
       </c>
       <c r="D19" t="n">
-        <v>6866.75</v>
+        <v>6899.5</v>
       </c>
       <c r="E19" t="n">
-        <v>6900.5</v>
+        <v>7005</v>
       </c>
       <c r="F19" t="n">
-        <v>-78.75</v>
+        <v>104.5</v>
       </c>
       <c r="G19" s="5" t="n">
-        <v>-0.0113</v>
+        <v>0.0151</v>
       </c>
       <c r="H19" t="n">
         <v>118</v>
       </c>
       <c r="I19" t="n">
-        <v>6807</v>
+        <v>6748.75</v>
       </c>
       <c r="J19" t="n">
-        <v>6901.75</v>
+        <v>6769.88</v>
       </c>
       <c r="K19" t="n">
-        <v>6932.5</v>
+        <v>6841.5</v>
       </c>
       <c r="L19" t="n">
-        <v>6963.25</v>
+        <v>6913.12</v>
       </c>
       <c r="M19" t="n">
-        <v>7026</v>
+        <v>6959.5</v>
       </c>
       <c r="N19" t="n">
-        <v>7088.75</v>
+        <v>7005.88</v>
       </c>
       <c r="O19" t="n">
-        <v>7087.5</v>
+        <v>7102.75</v>
       </c>
       <c r="P19" s="6" t="n">
         <v/>
       </c>
-      <c r="Q19" s="6" t="inlineStr">
+      <c r="Q19" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R19" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S19" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T19" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U19" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="R19" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S19" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T19" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U19" s="8" t="n">
-        <v/>
-      </c>
       <c r="V19" s="8" t="n">
         <v/>
       </c>
@@ -2125,55 +2115,59 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X19" t="inlineStr"/>
+      <c r="X19" t="inlineStr">
+        <is>
+          <t>強警訊</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2026-01-05</t>
+          <t>2026-01-12</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>6911.5</v>
+        <v>7007</v>
       </c>
       <c r="C20" t="n">
-        <v>7017.5</v>
+        <v>7036.25</v>
       </c>
       <c r="D20" t="n">
-        <v>6899.5</v>
+        <v>6923.25</v>
       </c>
       <c r="E20" t="n">
-        <v>7005</v>
+        <v>6976.75</v>
       </c>
       <c r="F20" t="n">
-        <v>104.5</v>
+        <v>-28.25</v>
       </c>
       <c r="G20" s="5" t="n">
-        <v>0.0151</v>
+        <v>-0.004</v>
       </c>
       <c r="H20" t="n">
-        <v>118</v>
+        <v>113</v>
       </c>
       <c r="I20" t="n">
-        <v>6748.75</v>
+        <v>6781.5</v>
       </c>
       <c r="J20" t="n">
-        <v>6769.88</v>
+        <v>6910.25</v>
       </c>
       <c r="K20" t="n">
-        <v>6841.5</v>
+        <v>6946</v>
       </c>
       <c r="L20" t="n">
-        <v>6913.12</v>
+        <v>6981.75</v>
       </c>
       <c r="M20" t="n">
-        <v>6959.5</v>
+        <v>7064</v>
       </c>
       <c r="N20" t="n">
-        <v>7005.88</v>
+        <v>7146.25</v>
       </c>
       <c r="O20" t="n">
-        <v>7102.75</v>
+        <v>7135.5</v>
       </c>
       <c r="P20" s="6" t="n">
         <v/>
@@ -2181,23 +2175,21 @@
       <c r="Q20" s="6" t="n">
         <v/>
       </c>
-      <c r="R20" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S20" s="7" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T20" s="8" t="inlineStr">
+      <c r="R20" s="6" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="U20" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+      <c r="S20" s="10" t="inlineStr">
+        <is>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T20" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U20" s="8" t="n">
+        <v/>
       </c>
       <c r="V20" s="8" t="n">
         <v/>
@@ -2209,72 +2201,74 @@
       </c>
       <c r="X20" t="inlineStr">
         <is>
-          <t>強警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-01-12</t>
+          <t>2026-01-19</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>7007</v>
+        <v>6918.25</v>
       </c>
       <c r="C21" t="n">
-        <v>7036.25</v>
+        <v>6969</v>
       </c>
       <c r="D21" t="n">
-        <v>6923.25</v>
+        <v>6814.5</v>
       </c>
       <c r="E21" t="n">
-        <v>6976.75</v>
+        <v>6945.75</v>
       </c>
       <c r="F21" t="n">
-        <v>-28.25</v>
+        <v>-31</v>
       </c>
       <c r="G21" s="5" t="n">
-        <v>-0.004</v>
+        <v>-0.0044</v>
       </c>
       <c r="H21" t="n">
-        <v>113</v>
+        <v>154.5</v>
       </c>
       <c r="I21" t="n">
-        <v>6781.5</v>
+        <v>6810.25</v>
       </c>
       <c r="J21" t="n">
-        <v>6910.25</v>
+        <v>6862.25</v>
       </c>
       <c r="K21" t="n">
-        <v>6946</v>
+        <v>6920.25</v>
       </c>
       <c r="L21" t="n">
-        <v>6981.75</v>
+        <v>6978.25</v>
       </c>
       <c r="M21" t="n">
-        <v>7064</v>
+        <v>7033.25</v>
       </c>
       <c r="N21" t="n">
-        <v>7146.25</v>
+        <v>7088.25</v>
       </c>
       <c r="O21" t="n">
-        <v>7135.5</v>
+        <v>7149.25</v>
       </c>
       <c r="P21" s="6" t="n">
         <v/>
       </c>
-      <c r="Q21" s="6" t="n">
-        <v/>
+      <c r="Q21" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="R21" s="6" t="inlineStr">
         <is>
-          <t>✓</t>
+          <t>△C</t>
         </is>
       </c>
       <c r="S21" s="10" t="inlineStr">
         <is>
-          <t>↓C</t>
+          <t>↓</t>
         </is>
       </c>
       <c r="T21" s="8" t="n">
@@ -2291,81 +2285,75 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X21" t="inlineStr">
-        <is>
-          <t>中警訊</t>
-        </is>
-      </c>
+      <c r="X21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2026-01-19</t>
+          <t>2026-01-26</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>6918.25</v>
+        <v>6904</v>
       </c>
       <c r="C22" t="n">
-        <v>6969</v>
+        <v>7043</v>
       </c>
       <c r="D22" t="n">
-        <v>6814.5</v>
+        <v>6879</v>
       </c>
       <c r="E22" t="n">
-        <v>6945.75</v>
+        <v>6965.75</v>
       </c>
       <c r="F22" t="n">
-        <v>-31</v>
+        <v>20</v>
       </c>
       <c r="G22" s="5" t="n">
-        <v>-0.0044</v>
+        <v>0.0029</v>
       </c>
       <c r="H22" t="n">
-        <v>154.5</v>
+        <v>164</v>
       </c>
       <c r="I22" t="n">
-        <v>6810.25</v>
+        <v>6660</v>
       </c>
       <c r="J22" t="n">
-        <v>6862.25</v>
+        <v>6818.25</v>
       </c>
       <c r="K22" t="n">
-        <v>6920.25</v>
+        <v>6868.5</v>
       </c>
       <c r="L22" t="n">
-        <v>6978.25</v>
+        <v>6918.75</v>
       </c>
       <c r="M22" t="n">
-        <v>7033.25</v>
+        <v>7023</v>
       </c>
       <c r="N22" t="n">
-        <v>7088.25</v>
+        <v>7127.25</v>
       </c>
       <c r="O22" t="n">
-        <v>7149.25</v>
+        <v>7123.5</v>
       </c>
       <c r="P22" s="6" t="n">
         <v/>
       </c>
-      <c r="Q22" s="6" t="inlineStr">
+      <c r="Q22" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R22" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S22" s="7" t="inlineStr">
+        <is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T22" s="8" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="R22" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="S22" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T22" s="8" t="n">
-        <v/>
-      </c>
       <c r="U22" s="8" t="n">
         <v/>
       </c>
@@ -2377,75 +2365,81 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X22" t="inlineStr"/>
+      <c r="X22" t="inlineStr">
+        <is>
+          <t>強警訊</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-01-26</t>
+          <t>2026-02-02</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>6904</v>
+        <v>6938.5</v>
       </c>
       <c r="C23" t="n">
-        <v>7043</v>
+        <v>7027.25</v>
       </c>
       <c r="D23" t="n">
-        <v>6879</v>
+        <v>6751.5</v>
       </c>
       <c r="E23" t="n">
-        <v>6965.75</v>
+        <v>6952.75</v>
       </c>
       <c r="F23" t="n">
-        <v>20</v>
+        <v>-13</v>
       </c>
       <c r="G23" s="5" t="n">
-        <v>0.0029</v>
+        <v>-0.0019</v>
       </c>
       <c r="H23" t="n">
-        <v>164</v>
+        <v>275.75</v>
       </c>
       <c r="I23" t="n">
-        <v>6660</v>
+        <v>6715</v>
       </c>
       <c r="J23" t="n">
-        <v>6818.25</v>
+        <v>6804.12</v>
       </c>
       <c r="K23" t="n">
-        <v>6868.5</v>
+        <v>6883.75</v>
       </c>
       <c r="L23" t="n">
-        <v>6918.75</v>
+        <v>6963.38</v>
       </c>
       <c r="M23" t="n">
-        <v>7023</v>
+        <v>7047.75</v>
       </c>
       <c r="N23" t="n">
-        <v>7127.25</v>
+        <v>7132.12</v>
       </c>
       <c r="O23" t="n">
-        <v>7123.5</v>
+        <v>7207</v>
       </c>
       <c r="P23" s="6" t="n">
         <v/>
       </c>
-      <c r="Q23" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R23" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S23" s="7" t="inlineStr">
-        <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T23" s="8" t="inlineStr">
+      <c r="Q23" s="6" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
+      <c r="R23" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S23" s="10" t="inlineStr">
+        <is>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T23" s="8" t="n">
+        <v/>
+      </c>
       <c r="U23" s="8" t="n">
         <v/>
       </c>
@@ -2457,76 +2451,70 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X23" t="inlineStr">
-        <is>
-          <t>強警訊</t>
-        </is>
-      </c>
+      <c r="X23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2026-02-02</t>
+          <t>2026-02-09</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>6938.5</v>
+        <v>6960.25</v>
       </c>
       <c r="C24" t="n">
-        <v>7027.25</v>
+        <v>7011.5</v>
       </c>
       <c r="D24" t="n">
-        <v>6751.5</v>
+        <v>6808.75</v>
       </c>
       <c r="E24" t="n">
-        <v>6952.75</v>
+        <v>6850.5</v>
       </c>
       <c r="F24" t="n">
-        <v>-13</v>
+        <v>-102.25</v>
       </c>
       <c r="G24" s="5" t="n">
-        <v>-0.0019</v>
+        <v>-0.0147</v>
       </c>
       <c r="H24" t="n">
-        <v>275.75</v>
+        <v>202.75</v>
       </c>
       <c r="I24" t="n">
-        <v>6715</v>
+        <v>6475.75</v>
       </c>
       <c r="J24" t="n">
-        <v>6804.12</v>
+        <v>6708.69</v>
       </c>
       <c r="K24" t="n">
-        <v>6883.75</v>
+        <v>6814.88</v>
       </c>
       <c r="L24" t="n">
-        <v>6963.38</v>
+        <v>6921.06</v>
       </c>
       <c r="M24" t="n">
-        <v>7047.75</v>
+        <v>7090.62</v>
       </c>
       <c r="N24" t="n">
-        <v>7132.12</v>
+        <v>7260.19</v>
       </c>
       <c r="O24" t="n">
-        <v>7207</v>
+        <v>7303</v>
       </c>
       <c r="P24" s="6" t="n">
         <v/>
       </c>
-      <c r="Q24" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="Q24" s="6" t="n">
+        <v/>
       </c>
       <c r="R24" s="6" t="inlineStr">
         <is>
-          <t>✓</t>
+          <t>△C</t>
         </is>
       </c>
       <c r="S24" s="10" t="inlineStr">
         <is>
-          <t>↓C</t>
+          <t>↓</t>
         </is>
       </c>
       <c r="T24" s="8" t="n">
@@ -2543,55 +2531,59 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X24" t="inlineStr"/>
+      <c r="X24" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-02-09</t>
+          <t>2026-02-16</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>6960.25</v>
+        <v>6852.5</v>
       </c>
       <c r="C25" t="n">
-        <v>7011.5</v>
+        <v>6931.5</v>
       </c>
       <c r="D25" t="n">
-        <v>6808.75</v>
+        <v>6791</v>
       </c>
       <c r="E25" t="n">
-        <v>6850.5</v>
+        <v>6923.25</v>
       </c>
       <c r="F25" t="n">
-        <v>-102.25</v>
+        <v>72.75</v>
       </c>
       <c r="G25" s="5" t="n">
-        <v>-0.0147</v>
+        <v>0.0106</v>
       </c>
       <c r="H25" t="n">
-        <v>202.75</v>
+        <v>140.5</v>
       </c>
       <c r="I25" t="n">
-        <v>6475.75</v>
+        <v>6606</v>
       </c>
       <c r="J25" t="n">
-        <v>6708.69</v>
+        <v>6617.94</v>
       </c>
       <c r="K25" t="n">
-        <v>6814.88</v>
+        <v>6749.12</v>
       </c>
       <c r="L25" t="n">
-        <v>6921.06</v>
+        <v>6880.31</v>
       </c>
       <c r="M25" t="n">
-        <v>7090.62</v>
+        <v>6951.88</v>
       </c>
       <c r="N25" t="n">
-        <v>7260.19</v>
+        <v>7023.44</v>
       </c>
       <c r="O25" t="n">
-        <v>7303</v>
+        <v>7214.25</v>
       </c>
       <c r="P25" s="6" t="n">
         <v/>
@@ -2599,18 +2591,18 @@
       <c r="Q25" s="6" t="n">
         <v/>
       </c>
-      <c r="R25" s="6" t="inlineStr">
+      <c r="R25" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S25" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T25" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
-      </c>
-      <c r="S25" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T25" s="8" t="n">
-        <v/>
       </c>
       <c r="U25" s="8" t="n">
         <v/>
@@ -2632,50 +2624,50 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2026-02-16</t>
+          <t>2026-02-23</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>6852.5</v>
+        <v>6918</v>
       </c>
       <c r="C26" t="n">
-        <v>6931.5</v>
+        <v>6983.75</v>
       </c>
       <c r="D26" t="n">
-        <v>6791</v>
+        <v>6828.5</v>
       </c>
       <c r="E26" t="n">
-        <v>6923.25</v>
+        <v>6889</v>
       </c>
       <c r="F26" t="n">
-        <v>72.75</v>
+        <v>-34.25</v>
       </c>
       <c r="G26" s="5" t="n">
-        <v>0.0106</v>
+        <v>-0.0049</v>
       </c>
       <c r="H26" t="n">
-        <v>140.5</v>
+        <v>155.25</v>
       </c>
       <c r="I26" t="n">
-        <v>6606</v>
+        <v>6650.5</v>
       </c>
       <c r="J26" t="n">
-        <v>6617.94</v>
+        <v>6813.75</v>
       </c>
       <c r="K26" t="n">
-        <v>6749.12</v>
+        <v>6853</v>
       </c>
       <c r="L26" t="n">
-        <v>6880.31</v>
+        <v>6892.25</v>
       </c>
       <c r="M26" t="n">
-        <v>6951.88</v>
+        <v>6993.5</v>
       </c>
       <c r="N26" t="n">
-        <v>7023.44</v>
+        <v>7094.75</v>
       </c>
       <c r="O26" t="n">
-        <v>7214.25</v>
+        <v>7072</v>
       </c>
       <c r="P26" s="6" t="n">
         <v/>
@@ -2683,18 +2675,18 @@
       <c r="Q26" s="6" t="n">
         <v/>
       </c>
-      <c r="R26" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S26" s="7" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T26" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+      <c r="R26" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S26" s="10" t="inlineStr">
+        <is>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T26" s="8" t="n">
+        <v/>
       </c>
       <c r="U26" s="8" t="n">
         <v/>
@@ -2709,63 +2701,65 @@
       </c>
       <c r="X26" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-02-23</t>
+          <t>2026-03-02</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>6918</v>
+        <v>6820</v>
       </c>
       <c r="C27" t="n">
-        <v>6983.75</v>
+        <v>6911.25</v>
       </c>
       <c r="D27" t="n">
-        <v>6828.5</v>
+        <v>6715.75</v>
       </c>
       <c r="E27" t="n">
-        <v>6889</v>
+        <v>6743.75</v>
       </c>
       <c r="F27" t="n">
-        <v>-34.25</v>
+        <v>-145.25</v>
       </c>
       <c r="G27" s="5" t="n">
-        <v>-0.0049</v>
+        <v>-0.0211</v>
       </c>
       <c r="H27" t="n">
-        <v>155.25</v>
+        <v>195.5</v>
       </c>
       <c r="I27" t="n">
-        <v>6650.5</v>
+        <v>6673.25</v>
       </c>
       <c r="J27" t="n">
-        <v>6813.75</v>
+        <v>6725.19</v>
       </c>
       <c r="K27" t="n">
-        <v>6853</v>
+        <v>6811.38</v>
       </c>
       <c r="L27" t="n">
-        <v>6892.25</v>
+        <v>6897.56</v>
       </c>
       <c r="M27" t="n">
-        <v>6993.5</v>
+        <v>6966.62</v>
       </c>
       <c r="N27" t="n">
-        <v>7094.75</v>
+        <v>7035.69</v>
       </c>
       <c r="O27" t="n">
-        <v>7072</v>
+        <v>7139</v>
       </c>
       <c r="P27" s="6" t="n">
         <v/>
       </c>
-      <c r="Q27" s="6" t="n">
-        <v/>
+      <c r="Q27" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="R27" s="6" t="inlineStr">
         <is>
@@ -2774,7 +2768,7 @@
       </c>
       <c r="S27" s="10" t="inlineStr">
         <is>
-          <t>↓C</t>
+          <t>↓</t>
         </is>
       </c>
       <c r="T27" s="8" t="n">
@@ -2791,80 +2785,76 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X27" t="inlineStr">
-        <is>
-          <t>中警訊</t>
-        </is>
-      </c>
+      <c r="X27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-09</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>6820</v>
+        <v>6685.5</v>
       </c>
       <c r="C28" t="n">
-        <v>6911.25</v>
+        <v>6852</v>
       </c>
       <c r="D28" t="n">
-        <v>6715.75</v>
+        <v>6584.5</v>
       </c>
       <c r="E28" t="n">
-        <v>6743.75</v>
+        <v>6636</v>
       </c>
       <c r="F28" t="n">
-        <v>-145.25</v>
+        <v>-107.75</v>
       </c>
       <c r="G28" s="5" t="n">
-        <v>-0.0211</v>
+        <v>-0.016</v>
       </c>
       <c r="H28" t="n">
-        <v>195.5</v>
+        <v>267.5</v>
       </c>
       <c r="I28" t="n">
-        <v>6673.25</v>
+        <v>6520.25</v>
       </c>
       <c r="J28" t="n">
-        <v>6725.19</v>
+        <v>6513.38</v>
       </c>
       <c r="K28" t="n">
-        <v>6811.38</v>
+        <v>6646</v>
       </c>
       <c r="L28" t="n">
-        <v>6897.56</v>
+        <v>6778.62</v>
       </c>
       <c r="M28" t="n">
-        <v>6966.62</v>
+        <v>6841.5</v>
       </c>
       <c r="N28" t="n">
-        <v>7035.69</v>
+        <v>6904.38</v>
       </c>
       <c r="O28" t="n">
-        <v>7139</v>
+        <v>7106.75</v>
       </c>
       <c r="P28" s="6" t="n">
         <v/>
       </c>
-      <c r="Q28" s="6" t="inlineStr">
+      <c r="Q28" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R28" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="R28" s="6" t="inlineStr">
+      <c r="S28" s="10" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T28" s="8" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
-      </c>
-      <c r="S28" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T28" s="8" t="n">
-        <v/>
       </c>
       <c r="U28" s="8" t="n">
         <v/>
@@ -2882,50 +2872,50 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-03-16</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>6685.5</v>
+        <v>6608.5</v>
       </c>
       <c r="C29" t="n">
-        <v>6852</v>
+        <v>6762.25</v>
       </c>
       <c r="D29" t="n">
-        <v>6584.5</v>
+        <v>6558</v>
       </c>
       <c r="E29" t="n">
-        <v>6636</v>
+        <v>6594.63</v>
       </c>
       <c r="F29" t="n">
-        <v>-107.75</v>
+        <v>-41.37</v>
       </c>
       <c r="G29" s="5" t="n">
-        <v>-0.016</v>
+        <v>-0.0062</v>
       </c>
       <c r="H29" t="n">
-        <v>267.5</v>
+        <v>204.25</v>
       </c>
       <c r="I29" t="n">
-        <v>6520.25</v>
+        <v>6317</v>
       </c>
       <c r="J29" t="n">
-        <v>6513.38</v>
+        <v>6327.38</v>
       </c>
       <c r="K29" t="n">
-        <v>6646</v>
+        <v>6502.25</v>
       </c>
       <c r="L29" t="n">
-        <v>6778.62</v>
+        <v>6677.12</v>
       </c>
       <c r="M29" t="n">
-        <v>6841.5</v>
+        <v>6769.75</v>
       </c>
       <c r="N29" t="n">
-        <v>6904.38</v>
+        <v>6862.38</v>
       </c>
       <c r="O29" t="n">
-        <v>7106.75</v>
+        <v>7119.5</v>
       </c>
       <c r="P29" s="6" t="n">
         <v/>
@@ -2933,20 +2923,16 @@
       <c r="Q29" s="6" t="n">
         <v/>
       </c>
-      <c r="R29" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+      <c r="R29" s="6" t="n">
+        <v/>
       </c>
       <c r="S29" s="10" t="inlineStr">
         <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T29" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T29" s="8" t="n">
+        <v/>
       </c>
       <c r="U29" s="8" t="n">
         <v/>
@@ -2964,67 +2950,73 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-23</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>6608.5</v>
+        <v>6510</v>
       </c>
       <c r="C30" t="n">
-        <v>6762.25</v>
+        <v>6748</v>
       </c>
       <c r="D30" t="n">
-        <v>6558</v>
+        <v>6389</v>
       </c>
       <c r="E30" t="n">
-        <v>6594.63</v>
+        <v>6412.25</v>
       </c>
       <c r="F30" t="n">
-        <v>-41.37</v>
+        <v>-182.38</v>
       </c>
       <c r="G30" s="5" t="n">
-        <v>-0.0062</v>
+        <v>-0.0277</v>
       </c>
       <c r="H30" t="n">
-        <v>204.25</v>
+        <v>359</v>
       </c>
       <c r="I30" t="n">
-        <v>6317</v>
+        <v>6353.75</v>
       </c>
       <c r="J30" t="n">
-        <v>6327.38</v>
+        <v>6357.63</v>
       </c>
       <c r="K30" t="n">
-        <v>6502.25</v>
+        <v>6492.5</v>
       </c>
       <c r="L30" t="n">
-        <v>6677.12</v>
+        <v>6627.38</v>
       </c>
       <c r="M30" t="n">
-        <v>6769.75</v>
+        <v>6696.75</v>
       </c>
       <c r="N30" t="n">
-        <v>6862.38</v>
+        <v>6766.13</v>
       </c>
       <c r="O30" t="n">
-        <v>7119.5</v>
+        <v>6966.5</v>
       </c>
       <c r="P30" s="6" t="n">
         <v/>
       </c>
-      <c r="Q30" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R30" s="6" t="n">
-        <v/>
+      <c r="Q30" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="R30" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S30" s="10" t="inlineStr">
         <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T30" s="8" t="n">
-        <v/>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T30" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="U30" s="8" t="n">
         <v/>
@@ -3042,74 +3034,70 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026-03-23</t>
+          <t>2026-03-30</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>6510</v>
+        <v>6380</v>
       </c>
       <c r="C31" t="n">
-        <v>6748</v>
+        <v>6653.75</v>
       </c>
       <c r="D31" t="n">
-        <v>6389</v>
+        <v>6353.25</v>
       </c>
       <c r="E31" t="n">
-        <v>6412.25</v>
+        <v>6603.75</v>
       </c>
       <c r="F31" t="n">
-        <v>-182.38</v>
+        <v>191.5</v>
       </c>
       <c r="G31" s="5" t="n">
-        <v>-0.0277</v>
+        <v>0.0299</v>
       </c>
       <c r="H31" t="n">
-        <v>359</v>
+        <v>300.5</v>
       </c>
       <c r="I31" t="n">
-        <v>6353.75</v>
+        <v>6030</v>
       </c>
       <c r="J31" t="n">
-        <v>6357.63</v>
+        <v>5975.12</v>
       </c>
       <c r="K31" t="n">
-        <v>6492.5</v>
+        <v>6232.75</v>
       </c>
       <c r="L31" t="n">
-        <v>6627.38</v>
+        <v>6490.38</v>
       </c>
       <c r="M31" t="n">
-        <v>6696.75</v>
+        <v>6591.75</v>
       </c>
       <c r="N31" t="n">
-        <v>6766.13</v>
+        <v>6693.12</v>
       </c>
       <c r="O31" t="n">
-        <v>6966.5</v>
+        <v>7107</v>
       </c>
       <c r="P31" s="6" t="n">
         <v/>
       </c>
-      <c r="Q31" s="6" t="inlineStr">
+      <c r="Q31" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R31" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S31" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T31" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="R31" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S31" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T31" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
       <c r="U31" s="8" t="n">
         <v/>
       </c>
@@ -3121,55 +3109,59 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X31" t="inlineStr"/>
+      <c r="X31" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-04-06</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>6380</v>
+        <v>6590</v>
       </c>
       <c r="C32" t="n">
-        <v>6653.75</v>
+        <v>6888</v>
       </c>
       <c r="D32" t="n">
-        <v>6353.25</v>
+        <v>6567</v>
       </c>
       <c r="E32" t="n">
-        <v>6603.75</v>
+        <v>6855.25</v>
       </c>
       <c r="F32" t="n">
-        <v>191.5</v>
+        <v>251.5</v>
       </c>
       <c r="G32" s="5" t="n">
-        <v>0.0299</v>
+        <v>0.0381</v>
       </c>
       <c r="H32" t="n">
-        <v>300.5</v>
+        <v>321</v>
       </c>
       <c r="I32" t="n">
-        <v>6030</v>
+        <v>6052.75</v>
       </c>
       <c r="J32" t="n">
-        <v>5975.12</v>
+        <v>6353.38</v>
       </c>
       <c r="K32" t="n">
-        <v>6232.75</v>
+        <v>6453.5</v>
       </c>
       <c r="L32" t="n">
-        <v>6490.38</v>
+        <v>6553.62</v>
       </c>
       <c r="M32" t="n">
-        <v>6591.75</v>
+        <v>6754</v>
       </c>
       <c r="N32" t="n">
-        <v>6693.12</v>
+        <v>6954.38</v>
       </c>
       <c r="O32" t="n">
-        <v>7107</v>
+        <v>6954.25</v>
       </c>
       <c r="P32" s="6" t="n">
         <v/>
@@ -3187,15 +3179,17 @@
       </c>
       <c r="T32" s="8" t="inlineStr">
         <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U32" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V32" s="8" t="inlineStr">
+        <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="U32" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V32" s="8" t="n">
-        <v/>
-      </c>
       <c r="W32" s="11" t="inlineStr">
         <is>
           <t>空方</t>
@@ -3203,57 +3197,57 @@
       </c>
       <c r="X32" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2026-04-06</t>
+          <t>2026-04-13</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>6590</v>
+        <v>6780</v>
       </c>
       <c r="C33" t="n">
-        <v>6888</v>
+        <v>7185.75</v>
       </c>
       <c r="D33" t="n">
-        <v>6567</v>
+        <v>6767</v>
       </c>
       <c r="E33" t="n">
-        <v>6855.25</v>
+        <v>7161.5</v>
       </c>
       <c r="F33" t="n">
-        <v>251.5</v>
+        <v>306.25</v>
       </c>
       <c r="G33" s="5" t="n">
-        <v>0.0381</v>
+        <v>0.0447</v>
       </c>
       <c r="H33" t="n">
-        <v>321</v>
+        <v>418.75</v>
       </c>
       <c r="I33" t="n">
-        <v>6052.75</v>
+        <v>6246</v>
       </c>
       <c r="J33" t="n">
-        <v>6353.38</v>
+        <v>6598.12</v>
       </c>
       <c r="K33" t="n">
-        <v>6453.5</v>
+        <v>6694.75</v>
       </c>
       <c r="L33" t="n">
-        <v>6553.62</v>
+        <v>6791.38</v>
       </c>
       <c r="M33" t="n">
-        <v>6754</v>
+        <v>7015.75</v>
       </c>
       <c r="N33" t="n">
-        <v>6954.38</v>
+        <v>7240.12</v>
       </c>
       <c r="O33" t="n">
-        <v>6954.25</v>
+        <v>7209</v>
       </c>
       <c r="P33" s="6" t="n">
         <v/>
@@ -3296,50 +3290,50 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2026-04-13</t>
+          <t>2026-04-20</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>6780</v>
+        <v>7102.5</v>
       </c>
       <c r="C34" t="n">
-        <v>7185.75</v>
+        <v>7200.5</v>
       </c>
       <c r="D34" t="n">
-        <v>6767</v>
+        <v>7079.25</v>
       </c>
       <c r="E34" t="n">
-        <v>7161.5</v>
+        <v>7194.75</v>
       </c>
       <c r="F34" t="n">
-        <v>306.25</v>
+        <v>33.25</v>
       </c>
       <c r="G34" s="5" t="n">
-        <v>0.0447</v>
+        <v>0.0046</v>
       </c>
       <c r="H34" t="n">
-        <v>418.75</v>
+        <v>121.25</v>
       </c>
       <c r="I34" t="n">
-        <v>6246</v>
+        <v>6348.25</v>
       </c>
       <c r="J34" t="n">
-        <v>6598.12</v>
+        <v>6835.31</v>
       </c>
       <c r="K34" t="n">
-        <v>6694.75</v>
+        <v>6952.12</v>
       </c>
       <c r="L34" t="n">
-        <v>6791.38</v>
+        <v>7068.94</v>
       </c>
       <c r="M34" t="n">
-        <v>7015.75</v>
+        <v>7370.88</v>
       </c>
       <c r="N34" t="n">
-        <v>7240.12</v>
+        <v>7672.81</v>
       </c>
       <c r="O34" t="n">
-        <v>7209</v>
+        <v>7604.5</v>
       </c>
       <c r="P34" s="6" t="n">
         <v/>
@@ -3352,21 +3346,17 @@
       </c>
       <c r="S34" s="7" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T34" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T34" s="8" t="n">
+        <v/>
       </c>
       <c r="U34" s="8" t="n">
         <v/>
       </c>
-      <c r="V34" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+      <c r="V34" s="8" t="n">
+        <v/>
       </c>
       <c r="W34" s="11" t="inlineStr">
         <is>
@@ -3382,50 +3372,50 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
+          <t>2026-04-27</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>7102.5</v>
+        <v>7185</v>
       </c>
       <c r="C35" t="n">
-        <v>7200.5</v>
+        <v>7300.75</v>
       </c>
       <c r="D35" t="n">
-        <v>7079.25</v>
+        <v>7131.25</v>
       </c>
       <c r="E35" t="n">
-        <v>7194.75</v>
+        <v>7258</v>
       </c>
       <c r="F35" t="n">
-        <v>33.25</v>
+        <v>63.25</v>
       </c>
       <c r="G35" s="5" t="n">
-        <v>0.0046</v>
+        <v>0.008800000000000001</v>
       </c>
       <c r="H35" t="n">
-        <v>121.25</v>
+        <v>169.5</v>
       </c>
       <c r="I35" t="n">
-        <v>6348.25</v>
+        <v>6958</v>
       </c>
       <c r="J35" t="n">
-        <v>6835.31</v>
+        <v>7100.94</v>
       </c>
       <c r="K35" t="n">
-        <v>6952.12</v>
+        <v>7134.12</v>
       </c>
       <c r="L35" t="n">
-        <v>7068.94</v>
+        <v>7167.31</v>
       </c>
       <c r="M35" t="n">
-        <v>7370.88</v>
+        <v>7255.38</v>
       </c>
       <c r="N35" t="n">
-        <v>7672.81</v>
+        <v>7343.44</v>
       </c>
       <c r="O35" t="n">
-        <v>7604.5</v>
+        <v>7321.75</v>
       </c>
       <c r="P35" s="6" t="n">
         <v/>
@@ -3433,16 +3423,20 @@
       <c r="Q35" s="6" t="n">
         <v/>
       </c>
-      <c r="R35" s="6" t="n">
-        <v/>
+      <c r="R35" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S35" s="7" t="inlineStr">
         <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T35" s="8" t="n">
-        <v/>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T35" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="U35" s="8" t="n">
         <v/>
@@ -3464,50 +3458,50 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-05-04</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>7185</v>
+        <v>7276.25</v>
       </c>
       <c r="C36" t="n">
-        <v>7300.75</v>
+        <v>7427.75</v>
       </c>
       <c r="D36" t="n">
-        <v>7131.25</v>
+        <v>7199.5</v>
       </c>
       <c r="E36" t="n">
-        <v>7258</v>
+        <v>7419</v>
       </c>
       <c r="F36" t="n">
-        <v>63.25</v>
+        <v>161</v>
       </c>
       <c r="G36" s="5" t="n">
-        <v>0.008800000000000001</v>
+        <v>0.0222</v>
       </c>
       <c r="H36" t="n">
-        <v>169.5</v>
+        <v>228.25</v>
       </c>
       <c r="I36" t="n">
-        <v>6958</v>
+        <v>6961.75</v>
       </c>
       <c r="J36" t="n">
-        <v>7100.94</v>
+        <v>7109.5</v>
       </c>
       <c r="K36" t="n">
-        <v>7134.12</v>
+        <v>7173.25</v>
       </c>
       <c r="L36" t="n">
-        <v>7167.31</v>
+        <v>7237</v>
       </c>
       <c r="M36" t="n">
-        <v>7255.38</v>
+        <v>7342.75</v>
       </c>
       <c r="N36" t="n">
-        <v>7343.44</v>
+        <v>7448.5</v>
       </c>
       <c r="O36" t="n">
-        <v>7321.75</v>
+        <v>7470.25</v>
       </c>
       <c r="P36" s="6" t="n">
         <v/>
@@ -3515,23 +3509,23 @@
       <c r="Q36" s="6" t="n">
         <v/>
       </c>
-      <c r="R36" s="6" t="inlineStr">
+      <c r="R36" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S36" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T36" s="8" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="S36" s="7" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T36" s="8" t="inlineStr">
+      <c r="U36" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
-      </c>
-      <c r="U36" s="8" t="n">
-        <v/>
       </c>
       <c r="V36" s="8" t="n">
         <v/>
@@ -3550,50 +3544,50 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2026-05-04</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>7276.25</v>
+        <v>7403.5</v>
       </c>
       <c r="C37" t="n">
-        <v>7427.75</v>
+        <v>7540</v>
       </c>
       <c r="D37" t="n">
-        <v>7199.5</v>
+        <v>7363.25</v>
       </c>
       <c r="E37" t="n">
-        <v>7419</v>
+        <v>7432.25</v>
       </c>
       <c r="F37" t="n">
-        <v>161</v>
+        <v>13.25</v>
       </c>
       <c r="G37" s="5" t="n">
-        <v>0.0222</v>
+        <v>0.0018</v>
       </c>
       <c r="H37" t="n">
-        <v>228.25</v>
+        <v>176.75</v>
       </c>
       <c r="I37" t="n">
-        <v>6961.75</v>
+        <v>6971.25</v>
       </c>
       <c r="J37" t="n">
-        <v>7109.5</v>
+        <v>7243.44</v>
       </c>
       <c r="K37" t="n">
-        <v>7173.25</v>
+        <v>7304.88</v>
       </c>
       <c r="L37" t="n">
-        <v>7237</v>
+        <v>7366.31</v>
       </c>
       <c r="M37" t="n">
-        <v>7342.75</v>
+        <v>7533.12</v>
       </c>
       <c r="N37" t="n">
-        <v>7448.5</v>
+        <v>7699.94</v>
       </c>
       <c r="O37" t="n">
-        <v>7470.25</v>
+        <v>7656</v>
       </c>
       <c r="P37" s="6" t="n">
         <v/>
@@ -3606,7 +3600,7 @@
       </c>
       <c r="S37" s="7" t="inlineStr">
         <is>
-          <t>↑</t>
+          <t>↑C</t>
         </is>
       </c>
       <c r="T37" s="8" t="inlineStr">
@@ -3614,10 +3608,8 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="U37" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+      <c r="U37" s="8" t="n">
+        <v/>
       </c>
       <c r="V37" s="8" t="n">
         <v/>
@@ -3636,50 +3628,50 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-05-18</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>7403.5</v>
+        <v>7410</v>
       </c>
       <c r="C38" t="n">
-        <v>7540</v>
+        <v>7524</v>
       </c>
       <c r="D38" t="n">
-        <v>7363.25</v>
+        <v>7354.25</v>
       </c>
       <c r="E38" t="n">
-        <v>7432.25</v>
+        <v>7491</v>
       </c>
       <c r="F38" t="n">
-        <v>13.25</v>
+        <v>58.75</v>
       </c>
       <c r="G38" s="5" t="n">
-        <v>0.0018</v>
+        <v>0.007900000000000001</v>
       </c>
       <c r="H38" t="n">
-        <v>176.75</v>
+        <v>169.75</v>
       </c>
       <c r="I38" t="n">
-        <v>6971.25</v>
+        <v>7186.5</v>
       </c>
       <c r="J38" t="n">
-        <v>7243.44</v>
+        <v>7245.81</v>
       </c>
       <c r="K38" t="n">
-        <v>7304.88</v>
+        <v>7343.88</v>
       </c>
       <c r="L38" t="n">
-        <v>7366.31</v>
+        <v>7441.94</v>
       </c>
       <c r="M38" t="n">
-        <v>7533.12</v>
+        <v>7520.62</v>
       </c>
       <c r="N38" t="n">
-        <v>7699.94</v>
+        <v>7599.31</v>
       </c>
       <c r="O38" t="n">
-        <v>7656</v>
+        <v>7716.75</v>
       </c>
       <c r="P38" s="6" t="n">
         <v/>
@@ -3692,12 +3684,12 @@
       </c>
       <c r="S38" s="7" t="inlineStr">
         <is>
-          <t>↑C</t>
+          <t>↑</t>
         </is>
       </c>
       <c r="T38" s="8" t="inlineStr">
         <is>
-          <t>✓</t>
+          <t>△C</t>
         </is>
       </c>
       <c r="U38" s="8" t="n">
@@ -3713,57 +3705,57 @@
       </c>
       <c r="X38" t="inlineStr">
         <is>
-          <t>強警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-05-25</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>7410</v>
+        <v>7519</v>
       </c>
       <c r="C39" t="n">
-        <v>7524</v>
+        <v>7611.5</v>
       </c>
       <c r="D39" t="n">
-        <v>7354.25</v>
+        <v>7505.75</v>
       </c>
       <c r="E39" t="n">
-        <v>7491</v>
+        <v>7595.75</v>
       </c>
       <c r="F39" t="n">
-        <v>58.75</v>
+        <v>104.75</v>
       </c>
       <c r="G39" s="5" t="n">
-        <v>0.007900000000000001</v>
+        <v>0.014</v>
       </c>
       <c r="H39" t="n">
-        <v>169.75</v>
+        <v>105.75</v>
       </c>
       <c r="I39" t="n">
-        <v>7186.5</v>
+        <v>7184.5</v>
       </c>
       <c r="J39" t="n">
-        <v>7245.81</v>
+        <v>7347.19</v>
       </c>
       <c r="K39" t="n">
-        <v>7343.88</v>
+        <v>7406.12</v>
       </c>
       <c r="L39" t="n">
-        <v>7441.94</v>
+        <v>7465.06</v>
       </c>
       <c r="M39" t="n">
-        <v>7520.62</v>
+        <v>7575.88</v>
       </c>
       <c r="N39" t="n">
-        <v>7599.31</v>
+        <v>7686.69</v>
       </c>
       <c r="O39" t="n">
-        <v>7716.75</v>
+        <v>7693.75</v>
       </c>
       <c r="P39" s="6" t="n">
         <v/>
@@ -3797,77 +3789,81 @@
       </c>
       <c r="X39" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>2026-05-25</t>
+          <t>2026-06-01</t>
         </is>
       </c>
       <c r="B40" t="n">
-        <v>7519</v>
+        <v>7595</v>
       </c>
       <c r="C40" t="n">
-        <v>7611.5</v>
+        <v>7632.25</v>
       </c>
       <c r="D40" t="n">
-        <v>7505.75</v>
+        <v>7359</v>
       </c>
       <c r="E40" t="n">
-        <v>7595.75</v>
+        <v>7400.5</v>
       </c>
       <c r="F40" t="n">
-        <v>104.75</v>
+        <v>-195.25</v>
       </c>
       <c r="G40" s="5" t="n">
-        <v>0.014</v>
+        <v>-0.0257</v>
       </c>
       <c r="H40" t="n">
-        <v>105.75</v>
+        <v>273.25</v>
       </c>
       <c r="I40" t="n">
-        <v>7184.5</v>
+        <v>7400</v>
       </c>
       <c r="J40" t="n">
-        <v>7347.19</v>
+        <v>7508.56</v>
       </c>
       <c r="K40" t="n">
-        <v>7406.12</v>
+        <v>7542.88</v>
       </c>
       <c r="L40" t="n">
-        <v>7465.06</v>
+        <v>7577.19</v>
       </c>
       <c r="M40" t="n">
-        <v>7575.88</v>
+        <v>7648.62</v>
       </c>
       <c r="N40" t="n">
-        <v>7686.69</v>
+        <v>7720.06</v>
       </c>
       <c r="O40" t="n">
-        <v>7693.75</v>
-      </c>
-      <c r="P40" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q40" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R40" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S40" s="7" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T40" s="8" t="inlineStr">
+        <v>7717.25</v>
+      </c>
+      <c r="P40" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
+      <c r="Q40" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="R40" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S40" s="10" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T40" s="8" t="n">
+        <v/>
+      </c>
       <c r="U40" s="8" t="n">
         <v/>
       </c>
@@ -3881,76 +3877,72 @@
       </c>
       <c r="X40" t="inlineStr">
         <is>
-          <t>強警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-06-08</t>
         </is>
       </c>
       <c r="B41" t="n">
-        <v>7595</v>
+        <v>7368</v>
       </c>
       <c r="C41" t="n">
-        <v>7632.25</v>
+        <v>7491</v>
       </c>
       <c r="D41" t="n">
-        <v>7359</v>
+        <v>7232.25</v>
       </c>
       <c r="E41" t="n">
-        <v>7400.5</v>
+        <v>7435</v>
       </c>
       <c r="F41" t="n">
-        <v>-195.25</v>
+        <v>34.5</v>
       </c>
       <c r="G41" s="5" t="n">
-        <v>-0.0257</v>
+        <v>0.0047</v>
       </c>
       <c r="H41" t="n">
-        <v>273.25</v>
+        <v>258.75</v>
       </c>
       <c r="I41" t="n">
-        <v>7400</v>
+        <v>7085.75</v>
       </c>
       <c r="J41" t="n">
-        <v>7508.56</v>
+        <v>7079.69</v>
       </c>
       <c r="K41" t="n">
-        <v>7542.88</v>
+        <v>7263.88</v>
       </c>
       <c r="L41" t="n">
-        <v>7577.19</v>
+        <v>7448.06</v>
       </c>
       <c r="M41" t="n">
-        <v>7648.62</v>
+        <v>7537.12</v>
       </c>
       <c r="N41" t="n">
-        <v>7720.06</v>
+        <v>7626.19</v>
       </c>
       <c r="O41" t="n">
-        <v>7717.25</v>
-      </c>
-      <c r="P41" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="Q41" s="6" t="inlineStr">
+        <v>7905.5</v>
+      </c>
+      <c r="P41" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q41" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R41" s="6" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="R41" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
       <c r="S41" s="10" t="inlineStr">
         <is>
-          <t>↓</t>
+          <t>↓C</t>
         </is>
       </c>
       <c r="T41" s="8" t="n">
@@ -3976,50 +3968,50 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="B42" t="n">
-        <v>7368</v>
+        <v>7480</v>
       </c>
       <c r="C42" t="n">
-        <v>7491</v>
+        <v>7584.5</v>
       </c>
       <c r="D42" t="n">
-        <v>7232.25</v>
+        <v>7405</v>
       </c>
       <c r="E42" t="n">
-        <v>7435</v>
+        <v>7556.25</v>
       </c>
       <c r="F42" t="n">
-        <v>34.5</v>
+        <v>121.25</v>
       </c>
       <c r="G42" s="5" t="n">
-        <v>0.0047</v>
+        <v>0.0163</v>
       </c>
       <c r="H42" t="n">
-        <v>258.75</v>
+        <v>179.5</v>
       </c>
       <c r="I42" t="n">
-        <v>7085.75</v>
+        <v>6973.5</v>
       </c>
       <c r="J42" t="n">
-        <v>7079.69</v>
+        <v>7212.94</v>
       </c>
       <c r="K42" t="n">
-        <v>7263.88</v>
+        <v>7305.62</v>
       </c>
       <c r="L42" t="n">
-        <v>7448.06</v>
+        <v>7398.31</v>
       </c>
       <c r="M42" t="n">
-        <v>7537.12</v>
+        <v>7564.38</v>
       </c>
       <c r="N42" t="n">
-        <v>7626.19</v>
+        <v>7730.44</v>
       </c>
       <c r="O42" t="n">
-        <v>7905.5</v>
+        <v>7749.75</v>
       </c>
       <c r="P42" s="6" t="n">
         <v/>
@@ -4027,18 +4019,18 @@
       <c r="Q42" s="6" t="n">
         <v/>
       </c>
-      <c r="R42" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S42" s="10" t="inlineStr">
-        <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T42" s="8" t="n">
-        <v/>
+      <c r="R42" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S42" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T42" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="U42" s="8" t="n">
         <v/>
@@ -4053,77 +4045,79 @@
       </c>
       <c r="X42" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="B43" t="n">
-        <v>7480</v>
+        <v>7543.25</v>
       </c>
       <c r="C43" t="n">
-        <v>7584.5</v>
+        <v>7599.25</v>
       </c>
       <c r="D43" t="n">
-        <v>7405</v>
+        <v>7357.25</v>
       </c>
       <c r="E43" t="n">
-        <v>7556.25</v>
+        <v>7401.75</v>
       </c>
       <c r="F43" t="n">
-        <v>121.25</v>
+        <v>-154.5</v>
       </c>
       <c r="G43" s="5" t="n">
-        <v>0.0163</v>
+        <v>-0.0204</v>
       </c>
       <c r="H43" t="n">
-        <v>179.5</v>
+        <v>242</v>
       </c>
       <c r="I43" t="n">
-        <v>6973.5</v>
+        <v>7225.5</v>
       </c>
       <c r="J43" t="n">
-        <v>7212.94</v>
+        <v>7407.5</v>
       </c>
       <c r="K43" t="n">
-        <v>7305.62</v>
+        <v>7466.5</v>
       </c>
       <c r="L43" t="n">
-        <v>7398.31</v>
+        <v>7525.5</v>
       </c>
       <c r="M43" t="n">
-        <v>7564.38</v>
+        <v>7646</v>
       </c>
       <c r="N43" t="n">
-        <v>7730.44</v>
+        <v>7766.5</v>
       </c>
       <c r="O43" t="n">
-        <v>7749.75</v>
+        <v>7764</v>
       </c>
       <c r="P43" s="6" t="n">
         <v/>
       </c>
-      <c r="Q43" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R43" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S43" s="7" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T43" s="8" t="inlineStr">
+      <c r="Q43" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
+      <c r="R43" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S43" s="10" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T43" s="8" t="n">
+        <v/>
+      </c>
       <c r="U43" s="8" t="n">
         <v/>
       </c>
@@ -4137,79 +4131,77 @@
       </c>
       <c r="X43" t="inlineStr">
         <is>
-          <t>強警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="B44" t="n">
-        <v>7543.25</v>
+        <v>7398</v>
       </c>
       <c r="C44" t="n">
-        <v>7599.25</v>
+        <v>7593.75</v>
       </c>
       <c r="D44" t="n">
-        <v>7357.25</v>
+        <v>7398</v>
       </c>
       <c r="E44" t="n">
-        <v>7401.75</v>
+        <v>7557</v>
       </c>
       <c r="F44" t="n">
-        <v>-154.5</v>
+        <v>155.25</v>
       </c>
       <c r="G44" s="5" t="n">
-        <v>-0.0204</v>
+        <v>0.021</v>
       </c>
       <c r="H44" t="n">
-        <v>242</v>
+        <v>195.75</v>
       </c>
       <c r="I44" t="n">
-        <v>7225.5</v>
+        <v>7115.25</v>
       </c>
       <c r="J44" t="n">
-        <v>7407.5</v>
+        <v>7121.5</v>
       </c>
       <c r="K44" t="n">
-        <v>7466.5</v>
+        <v>7280.75</v>
       </c>
       <c r="L44" t="n">
-        <v>7525.5</v>
+        <v>7440</v>
       </c>
       <c r="M44" t="n">
-        <v>7646</v>
+        <v>7522.75</v>
       </c>
       <c r="N44" t="n">
-        <v>7766.5</v>
+        <v>7605.5</v>
       </c>
       <c r="O44" t="n">
-        <v>7764</v>
+        <v>7841.25</v>
       </c>
       <c r="P44" s="6" t="n">
         <v/>
       </c>
-      <c r="Q44" s="6" t="inlineStr">
+      <c r="Q44" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R44" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S44" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T44" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="R44" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S44" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T44" s="8" t="n">
-        <v/>
-      </c>
       <c r="U44" s="8" t="n">
         <v/>
       </c>
@@ -4223,57 +4215,57 @@
       </c>
       <c r="X44" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="B45" t="n">
-        <v>7398</v>
+        <v>7562.25</v>
       </c>
       <c r="C45" t="n">
-        <v>7593.75</v>
+        <v>7628.75</v>
       </c>
       <c r="D45" t="n">
-        <v>7398</v>
+        <v>7468.5</v>
       </c>
       <c r="E45" t="n">
-        <v>7557</v>
+        <v>7620.25</v>
       </c>
       <c r="F45" t="n">
-        <v>155.25</v>
+        <v>63.25</v>
       </c>
       <c r="G45" s="5" t="n">
-        <v>0.021</v>
+        <v>0.008399999999999999</v>
       </c>
       <c r="H45" t="n">
-        <v>195.75</v>
+        <v>160.25</v>
       </c>
       <c r="I45" t="n">
-        <v>7115.25</v>
+        <v>7202.25</v>
       </c>
       <c r="J45" t="n">
-        <v>7121.5</v>
+        <v>7391.81</v>
       </c>
       <c r="K45" t="n">
-        <v>7280.75</v>
+        <v>7459.12</v>
       </c>
       <c r="L45" t="n">
-        <v>7440</v>
+        <v>7526.44</v>
       </c>
       <c r="M45" t="n">
-        <v>7522.75</v>
+        <v>7654.88</v>
       </c>
       <c r="N45" t="n">
-        <v>7605.5</v>
+        <v>7783.31</v>
       </c>
       <c r="O45" t="n">
-        <v>7841.25</v>
+        <v>7789.5</v>
       </c>
       <c r="P45" s="6" t="n">
         <v/>
@@ -4307,77 +4299,79 @@
       </c>
       <c r="X45" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="B46" t="n">
-        <v>7562.25</v>
+        <v>7607</v>
       </c>
       <c r="C46" t="n">
-        <v>7628.75</v>
+        <v>7632</v>
       </c>
       <c r="D46" t="n">
-        <v>7468.5</v>
+        <v>7473</v>
       </c>
       <c r="E46" t="n">
-        <v>7620.25</v>
+        <v>7497.75</v>
       </c>
       <c r="F46" t="n">
-        <v>63.25</v>
+        <v>-122.5</v>
       </c>
       <c r="G46" s="5" t="n">
-        <v>0.008399999999999999</v>
+        <v>-0.0161</v>
       </c>
       <c r="H46" t="n">
-        <v>160.25</v>
+        <v>159</v>
       </c>
       <c r="I46" t="n">
-        <v>7202.25</v>
+        <v>7308.25</v>
       </c>
       <c r="J46" t="n">
-        <v>7391.81</v>
+        <v>7495.81</v>
       </c>
       <c r="K46" t="n">
-        <v>7459.12</v>
+        <v>7540.12</v>
       </c>
       <c r="L46" t="n">
-        <v>7526.44</v>
+        <v>7584.44</v>
       </c>
       <c r="M46" t="n">
-        <v>7654.88</v>
+        <v>7700.38</v>
       </c>
       <c r="N46" t="n">
-        <v>7783.31</v>
+        <v>7816.31</v>
       </c>
       <c r="O46" t="n">
-        <v>7789.5</v>
+        <v>7789</v>
       </c>
       <c r="P46" s="6" t="n">
         <v/>
       </c>
-      <c r="Q46" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R46" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S46" s="7" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T46" s="8" t="inlineStr">
+      <c r="Q46" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
+      <c r="R46" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S46" s="10" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T46" s="8" t="n">
+        <v/>
+      </c>
       <c r="U46" s="8" t="n">
         <v/>
       </c>
@@ -4391,71 +4385,69 @@
       </c>
       <c r="X46" t="inlineStr">
         <is>
-          <t>強警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="B47" t="n">
-        <v>7607</v>
+        <v>7485</v>
       </c>
       <c r="C47" t="n">
-        <v>7632</v>
+        <v>7563.5</v>
       </c>
       <c r="D47" t="n">
-        <v>7473</v>
+        <v>7411.75</v>
       </c>
       <c r="E47" t="n">
-        <v>7497.75</v>
+        <v>7447.5</v>
       </c>
       <c r="F47" t="n">
-        <v>-122.5</v>
+        <v>-50.25</v>
       </c>
       <c r="G47" s="5" t="n">
-        <v>-0.0161</v>
+        <v>-0.0067</v>
       </c>
       <c r="H47" t="n">
-        <v>159</v>
+        <v>151.75</v>
       </c>
       <c r="I47" t="n">
-        <v>7308.25</v>
+        <v>7314</v>
       </c>
       <c r="J47" t="n">
-        <v>7495.81</v>
+        <v>7311.38</v>
       </c>
       <c r="K47" t="n">
-        <v>7540.12</v>
+        <v>7418.25</v>
       </c>
       <c r="L47" t="n">
-        <v>7584.44</v>
+        <v>7525.12</v>
       </c>
       <c r="M47" t="n">
-        <v>7700.38</v>
+        <v>7577.25</v>
       </c>
       <c r="N47" t="n">
-        <v>7816.31</v>
+        <v>7629.38</v>
       </c>
       <c r="O47" t="n">
-        <v>7789</v>
+        <v>7791</v>
       </c>
       <c r="P47" s="6" t="n">
         <v/>
       </c>
-      <c r="Q47" s="6" t="inlineStr">
+      <c r="Q47" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R47" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="R47" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
       <c r="S47" s="10" t="inlineStr">
         <is>
           <t>↓</t>
@@ -4475,59 +4467,55 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X47" t="inlineStr">
-        <is>
-          <t>中警訊</t>
-        </is>
-      </c>
+      <c r="X47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="B48" t="n">
-        <v>7485</v>
+        <v>7490</v>
       </c>
       <c r="C48" t="n">
-        <v>7563.5</v>
+        <v>7541</v>
       </c>
       <c r="D48" t="n">
-        <v>7411.75</v>
+        <v>7324</v>
       </c>
       <c r="E48" t="n">
-        <v>7447.5</v>
+        <v>7519.25</v>
       </c>
       <c r="F48" t="n">
-        <v>-50.25</v>
+        <v>71.75</v>
       </c>
       <c r="G48" s="5" t="n">
-        <v>-0.0067</v>
+        <v>0.009599999999999999</v>
       </c>
       <c r="H48" t="n">
-        <v>151.75</v>
+        <v>217</v>
       </c>
       <c r="I48" t="n">
-        <v>7314</v>
+        <v>7260</v>
       </c>
       <c r="J48" t="n">
-        <v>7311.38</v>
+        <v>7275.69</v>
       </c>
       <c r="K48" t="n">
-        <v>7418.25</v>
+        <v>7371.62</v>
       </c>
       <c r="L48" t="n">
-        <v>7525.12</v>
+        <v>7467.56</v>
       </c>
       <c r="M48" t="n">
-        <v>7577.25</v>
+        <v>7523.38</v>
       </c>
       <c r="N48" t="n">
-        <v>7629.38</v>
+        <v>7579.19</v>
       </c>
       <c r="O48" t="n">
-        <v>7791</v>
+        <v>7715.25</v>
       </c>
       <c r="P48" s="6" t="n">
         <v/>
@@ -4537,17 +4525,19 @@
       </c>
       <c r="R48" s="6" t="inlineStr">
         <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S48" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T48" s="8" t="inlineStr">
+        <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="S48" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T48" s="8" t="n">
-        <v/>
-      </c>
       <c r="U48" s="8" t="n">
         <v/>
       </c>
@@ -4559,55 +4549,59 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X48" t="inlineStr"/>
+      <c r="X48" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="B49" t="n">
-        <v>7490</v>
+        <v>7550</v>
       </c>
       <c r="C49" t="n">
-        <v>7541</v>
+        <v>7820.25</v>
       </c>
       <c r="D49" t="n">
-        <v>7324</v>
+        <v>7542.75</v>
       </c>
       <c r="E49" t="n">
-        <v>7519.25</v>
+        <v>7779.75</v>
       </c>
       <c r="F49" t="n">
-        <v>71.75</v>
+        <v>260.5</v>
       </c>
       <c r="G49" s="5" t="n">
-        <v>0.009599999999999999</v>
+        <v>0.0346</v>
       </c>
       <c r="H49" t="n">
-        <v>217</v>
+        <v>277.5</v>
       </c>
       <c r="I49" t="n">
-        <v>7260</v>
+        <v>7107</v>
       </c>
       <c r="J49" t="n">
-        <v>7275.69</v>
+        <v>7345.62</v>
       </c>
       <c r="K49" t="n">
-        <v>7371.62</v>
+        <v>7410.75</v>
       </c>
       <c r="L49" t="n">
-        <v>7467.56</v>
+        <v>7475.88</v>
       </c>
       <c r="M49" t="n">
-        <v>7523.38</v>
+        <v>7627.75</v>
       </c>
       <c r="N49" t="n">
-        <v>7579.19</v>
+        <v>7779.62</v>
       </c>
       <c r="O49" t="n">
-        <v>7715.25</v>
+        <v>7758</v>
       </c>
       <c r="P49" s="6" t="n">
         <v/>
@@ -4615,85 +4609,83 @@
       <c r="Q49" s="6" t="n">
         <v/>
       </c>
-      <c r="R49" s="6" t="inlineStr">
+      <c r="R49" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S49" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T49" s="8" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="S49" s="7" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T49" s="8" t="inlineStr">
+      <c r="U49" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="U49" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V49" s="8" t="n">
-        <v/>
-      </c>
-      <c r="W49" s="11" t="inlineStr">
-        <is>
-          <t>空方</t>
-        </is>
-      </c>
-      <c r="X49" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="V49" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="W49" s="9" t="inlineStr">
+        <is>
+          <t>多方</t>
+        </is>
+      </c>
+      <c r="X49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="B50" t="n">
-        <v>7550</v>
+        <v>7776.75</v>
       </c>
       <c r="C50" t="n">
-        <v>7820.25</v>
+        <v>7838.5</v>
       </c>
       <c r="D50" t="n">
-        <v>7542.75</v>
+        <v>7738</v>
       </c>
       <c r="E50" t="n">
-        <v>7779.75</v>
+        <v>7805</v>
       </c>
       <c r="F50" t="n">
-        <v>260.5</v>
+        <v>25.25</v>
       </c>
       <c r="G50" s="5" t="n">
-        <v>0.0346</v>
+        <v>0.0032</v>
       </c>
       <c r="H50" t="n">
-        <v>277.5</v>
+        <v>100.5</v>
       </c>
       <c r="I50" t="n">
-        <v>7107</v>
+        <v>7265.25</v>
       </c>
       <c r="J50" t="n">
-        <v>7345.62</v>
+        <v>7551.38</v>
       </c>
       <c r="K50" t="n">
-        <v>7410.75</v>
+        <v>7641</v>
       </c>
       <c r="L50" t="n">
-        <v>7475.88</v>
+        <v>7730.62</v>
       </c>
       <c r="M50" t="n">
-        <v>7627.75</v>
+        <v>7918.5</v>
       </c>
       <c r="N50" t="n">
-        <v>7779.62</v>
+        <v>8106.38</v>
       </c>
       <c r="O50" t="n">
-        <v>7758</v>
+        <v>8097.75</v>
       </c>
       <c r="P50" s="6" t="n">
         <v/>
@@ -4706,23 +4698,17 @@
       </c>
       <c r="S50" s="7" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T50" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U50" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="V50" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T50" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U50" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V50" s="8" t="n">
+        <v/>
       </c>
       <c r="W50" s="9" t="inlineStr">
         <is>
@@ -4734,63 +4720,67 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="B51" t="n">
-        <v>7776.75</v>
+        <v>7809.25</v>
       </c>
       <c r="C51" t="n">
-        <v>7838.5</v>
+        <v>7824.5</v>
       </c>
       <c r="D51" t="n">
-        <v>7738</v>
+        <v>7657.75</v>
       </c>
       <c r="E51" t="n">
-        <v>7805</v>
+        <v>7691.25</v>
       </c>
       <c r="F51" t="n">
-        <v>25.25</v>
+        <v>-113.75</v>
       </c>
       <c r="G51" s="5" t="n">
-        <v>0.0032</v>
+        <v>-0.0146</v>
       </c>
       <c r="H51" t="n">
-        <v>100.5</v>
+        <v>166.75</v>
       </c>
       <c r="I51" t="n">
-        <v>7265.25</v>
+        <v>7637.5</v>
       </c>
       <c r="J51" t="n">
-        <v>7551.38</v>
+        <v>7712.88</v>
       </c>
       <c r="K51" t="n">
-        <v>7641</v>
+        <v>7754.75</v>
       </c>
       <c r="L51" t="n">
-        <v>7730.62</v>
+        <v>7796.62</v>
       </c>
       <c r="M51" t="n">
-        <v>7918.5</v>
+        <v>7855.25</v>
       </c>
       <c r="N51" t="n">
-        <v>8106.38</v>
+        <v>7913.88</v>
       </c>
       <c r="O51" t="n">
-        <v>8097.75</v>
+        <v>7939</v>
       </c>
       <c r="P51" s="6" t="n">
         <v/>
       </c>
-      <c r="Q51" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R51" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S51" s="7" t="inlineStr">
-        <is>
-          <t>↑C</t>
+      <c r="Q51" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="R51" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S51" s="10" t="inlineStr">
+        <is>
+          <t>↓</t>
         </is>
       </c>
       <c r="T51" s="8" t="n">
@@ -4802,9 +4792,9 @@
       <c r="V51" s="8" t="n">
         <v/>
       </c>
-      <c r="W51" s="9" t="inlineStr">
-        <is>
-          <t>多方</t>
+      <c r="W51" s="11" t="inlineStr">
+        <is>
+          <t>空方</t>
         </is>
       </c>
       <c r="X51" t="inlineStr"/>
@@ -4812,72 +4802,70 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="B52" t="n">
-        <v>7809.25</v>
+        <v>7693.5</v>
       </c>
       <c r="C52" t="n">
-        <v>7824.5</v>
+        <v>7782.5</v>
       </c>
       <c r="D52" t="n">
-        <v>7657.75</v>
+        <v>7655</v>
       </c>
       <c r="E52" t="n">
-        <v>7691.25</v>
+        <v>7722</v>
       </c>
       <c r="F52" t="n">
-        <v>-113.75</v>
+        <v>30.75</v>
       </c>
       <c r="G52" s="5" t="n">
-        <v>-0.0146</v>
+        <v>0.004</v>
       </c>
       <c r="H52" t="n">
-        <v>166.75</v>
+        <v>127.5</v>
       </c>
       <c r="I52" t="n">
-        <v>7637.5</v>
+        <v>7491</v>
       </c>
       <c r="J52" t="n">
-        <v>7712.88</v>
+        <v>7499.56</v>
       </c>
       <c r="K52" t="n">
-        <v>7754.75</v>
+        <v>7607.88</v>
       </c>
       <c r="L52" t="n">
-        <v>7796.62</v>
+        <v>7716.19</v>
       </c>
       <c r="M52" t="n">
-        <v>7855.25</v>
+        <v>7774.62</v>
       </c>
       <c r="N52" t="n">
-        <v>7913.88</v>
+        <v>7833.06</v>
       </c>
       <c r="O52" t="n">
-        <v>7939</v>
+        <v>7991.25</v>
       </c>
       <c r="P52" s="6" t="n">
         <v/>
       </c>
-      <c r="Q52" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="R52" s="6" t="inlineStr">
+      <c r="Q52" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R52" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S52" s="7" t="inlineStr">
+        <is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T52" s="8" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="S52" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T52" s="8" t="n">
-        <v/>
-      </c>
       <c r="U52" s="8" t="n">
         <v/>
       </c>
@@ -4889,55 +4877,59 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X52" t="inlineStr"/>
+      <c r="X52" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="B53" t="n">
-        <v>7693.5</v>
+        <v>7723.5</v>
       </c>
       <c r="C53" t="n">
-        <v>7782.5</v>
+        <v>7766.5</v>
       </c>
       <c r="D53" t="n">
-        <v>7655</v>
+        <v>7618.5</v>
       </c>
       <c r="E53" t="n">
         <v>7722</v>
       </c>
       <c r="F53" t="n">
-        <v>30.75</v>
+        <v>0</v>
       </c>
       <c r="G53" s="5" t="n">
-        <v>0.004</v>
+        <v>0</v>
       </c>
       <c r="H53" t="n">
-        <v>127.5</v>
+        <v>148</v>
       </c>
       <c r="I53" t="n">
-        <v>7491</v>
+        <v>7527.5</v>
       </c>
       <c r="J53" t="n">
-        <v>7499.56</v>
+        <v>7596.12</v>
       </c>
       <c r="K53" t="n">
-        <v>7607.88</v>
+        <v>7658.25</v>
       </c>
       <c r="L53" t="n">
-        <v>7716.19</v>
+        <v>7720.38</v>
       </c>
       <c r="M53" t="n">
-        <v>7774.62</v>
+        <v>7785.75</v>
       </c>
       <c r="N53" t="n">
-        <v>7833.06</v>
+        <v>7851.12</v>
       </c>
       <c r="O53" t="n">
-        <v>7991.25</v>
+        <v>7910</v>
       </c>
       <c r="P53" s="6" t="n">
         <v/>
@@ -4945,18 +4937,18 @@
       <c r="Q53" s="6" t="n">
         <v/>
       </c>
-      <c r="R53" s="6" t="n">
-        <v/>
+      <c r="R53" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S53" s="7" t="inlineStr">
         <is>
           <t>↑C</t>
         </is>
       </c>
-      <c r="T53" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="T53" s="8" t="n">
+        <v/>
       </c>
       <c r="U53" s="8" t="n">
         <v/>
@@ -4969,74 +4961,72 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X53" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="X53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="B54" t="n">
-        <v>7723.5</v>
+        <v>7715.5</v>
       </c>
       <c r="C54" t="n">
-        <v>7766.5</v>
+        <v>7728.5</v>
       </c>
       <c r="D54" t="n">
-        <v>7618.5</v>
+        <v>7585.5</v>
       </c>
       <c r="E54" t="n">
-        <v>7722</v>
+        <v>7659.5</v>
       </c>
       <c r="F54" t="n">
-        <v>0</v>
+        <v>-62.5</v>
       </c>
       <c r="G54" s="5" t="n">
-        <v>0</v>
+        <v>-0.0081</v>
       </c>
       <c r="H54" t="n">
-        <v>148</v>
+        <v>143</v>
       </c>
       <c r="I54" t="n">
-        <v>7527.5</v>
+        <v>7470.5</v>
       </c>
       <c r="J54" t="n">
-        <v>7596.12</v>
+        <v>7588.75</v>
       </c>
       <c r="K54" t="n">
-        <v>7658.25</v>
+        <v>7648</v>
       </c>
       <c r="L54" t="n">
-        <v>7720.38</v>
+        <v>7707.25</v>
       </c>
       <c r="M54" t="n">
-        <v>7785.75</v>
+        <v>7796</v>
       </c>
       <c r="N54" t="n">
-        <v>7851.12</v>
+        <v>7884.75</v>
       </c>
       <c r="O54" t="n">
-        <v>7910</v>
+        <v>7914.5</v>
       </c>
       <c r="P54" s="6" t="n">
         <v/>
       </c>
-      <c r="Q54" s="6" t="n">
-        <v/>
+      <c r="Q54" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="R54" s="6" t="inlineStr">
         <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S54" s="7" t="inlineStr">
-        <is>
-          <t>↑C</t>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="S54" s="10" t="inlineStr">
+        <is>
+          <t>↓</t>
         </is>
       </c>
       <c r="T54" s="8" t="n">
@@ -5058,50 +5048,50 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="B55" t="n">
-        <v>7715.5</v>
+        <v>7609.25</v>
       </c>
       <c r="C55" t="n">
-        <v>7728.5</v>
+        <v>7670.25</v>
       </c>
       <c r="D55" t="n">
-        <v>7585.5</v>
+        <v>7509.25</v>
       </c>
       <c r="E55" t="n">
-        <v>7659.5</v>
+        <v>7657.35</v>
       </c>
       <c r="F55" t="n">
-        <v>-62.5</v>
+        <v>-2.15</v>
       </c>
       <c r="G55" s="5" t="n">
-        <v>-0.0081</v>
+        <v>-0.0003</v>
       </c>
       <c r="H55" t="n">
-        <v>143</v>
+        <v>161</v>
       </c>
       <c r="I55" t="n">
-        <v>7470.5</v>
+        <v>7442.5</v>
       </c>
       <c r="J55" t="n">
-        <v>7588.75</v>
+        <v>7517.75</v>
       </c>
       <c r="K55" t="n">
-        <v>7648</v>
+        <v>7588</v>
       </c>
       <c r="L55" t="n">
-        <v>7707.25</v>
+        <v>7658.25</v>
       </c>
       <c r="M55" t="n">
-        <v>7796</v>
+        <v>7731</v>
       </c>
       <c r="N55" t="n">
-        <v>7884.75</v>
+        <v>7803.75</v>
       </c>
       <c r="O55" t="n">
-        <v>7914.5</v>
+        <v>7871.5</v>
       </c>
       <c r="P55" s="6" t="n">
         <v/>
@@ -5113,12 +5103,12 @@
       </c>
       <c r="R55" s="6" t="inlineStr">
         <is>
-          <t>△C</t>
+          <t>✓</t>
         </is>
       </c>
       <c r="S55" s="10" t="inlineStr">
         <is>
-          <t>↓</t>
+          <t>↓C</t>
         </is>
       </c>
       <c r="T55" s="8" t="n">
@@ -5140,250 +5130,170 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="B56" t="n">
-        <v>7609.25</v>
+        <v>7722</v>
       </c>
       <c r="C56" t="n">
-        <v>7670.25</v>
+        <v>7848.5</v>
       </c>
       <c r="D56" t="n">
-        <v>7509.25</v>
+        <v>7707.25</v>
       </c>
       <c r="E56" t="n">
-        <v>7657.35</v>
+        <v>7803.75</v>
       </c>
       <c r="F56" t="n">
-        <v>-2.15</v>
+        <v>146.4</v>
       </c>
       <c r="G56" s="5" t="n">
-        <v>-0.0003</v>
+        <v>0.0191</v>
       </c>
       <c r="H56" t="n">
-        <v>161</v>
+        <v>141.25</v>
       </c>
       <c r="I56" t="n">
-        <v>7442.5</v>
+        <v>7348.25</v>
       </c>
       <c r="J56" t="n">
-        <v>7517.75</v>
+        <v>7530.15</v>
       </c>
       <c r="K56" t="n">
-        <v>7588</v>
+        <v>7576.85</v>
       </c>
       <c r="L56" t="n">
-        <v>7658.25</v>
+        <v>7623.55</v>
       </c>
       <c r="M56" t="n">
-        <v>7731</v>
+        <v>7737.85</v>
       </c>
       <c r="N56" t="n">
-        <v>7803.75</v>
+        <v>7852.15</v>
       </c>
       <c r="O56" t="n">
-        <v>7871.5</v>
+        <v>7831.25</v>
       </c>
       <c r="P56" s="6" t="n">
         <v/>
       </c>
-      <c r="Q56" s="6" t="inlineStr">
+      <c r="Q56" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R56" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S56" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T56" s="8" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="R56" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S56" s="10" t="inlineStr">
-        <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T56" s="8" t="n">
-        <v/>
-      </c>
       <c r="U56" s="8" t="n">
         <v/>
       </c>
-      <c r="V56" s="8" t="n">
-        <v/>
+      <c r="V56" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="W56" s="11" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
       </c>
-      <c r="X56" t="inlineStr"/>
+      <c r="X56" t="inlineStr">
+        <is>
+          <t>強警訊</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="B57" t="n">
-        <v>7722</v>
+        <v>7796</v>
       </c>
       <c r="C57" t="n">
-        <v>7848.5</v>
+        <v>7810.25</v>
       </c>
       <c r="D57" t="n">
-        <v>7707.25</v>
+        <v>7672.75</v>
       </c>
       <c r="E57" t="n">
-        <v>7803.75</v>
+        <v>7777.25</v>
       </c>
       <c r="F57" t="n">
-        <v>146.4</v>
+        <v>-26.5</v>
       </c>
       <c r="G57" s="5" t="n">
-        <v>0.0191</v>
+        <v>-0.0034</v>
       </c>
       <c r="H57" t="n">
-        <v>141.25</v>
+        <v>137.5</v>
       </c>
       <c r="I57" t="n">
-        <v>7348.25</v>
+        <v>7566</v>
       </c>
       <c r="J57" t="n">
-        <v>7530.15</v>
+        <v>7675.44</v>
       </c>
       <c r="K57" t="n">
-        <v>7576.85</v>
+        <v>7733.12</v>
       </c>
       <c r="L57" t="n">
-        <v>7623.55</v>
+        <v>7790.81</v>
       </c>
       <c r="M57" t="n">
-        <v>7737.85</v>
+        <v>7874.38</v>
       </c>
       <c r="N57" t="n">
-        <v>7852.15</v>
+        <v>7957.94</v>
       </c>
       <c r="O57" t="n">
-        <v>7831.25</v>
+        <v>7989.75</v>
       </c>
       <c r="P57" s="6" t="n">
         <v/>
       </c>
-      <c r="Q57" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R57" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S57" s="7" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T57" s="8" t="inlineStr">
+      <c r="Q57" s="6" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
+      <c r="R57" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S57" s="10" t="inlineStr">
+        <is>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T57" s="8" t="n">
+        <v/>
+      </c>
       <c r="U57" s="8" t="n">
         <v/>
       </c>
-      <c r="V57" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+      <c r="V57" s="8" t="n">
+        <v/>
       </c>
       <c r="W57" s="11" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
       </c>
-      <c r="X57" t="inlineStr">
-        <is>
-          <t>強警訊</t>
-        </is>
-      </c>
-    </row>
-    <row r="58">
-      <c r="A58" t="inlineStr">
-        <is>
-          <t>2026-09-28</t>
-        </is>
-      </c>
-      <c r="B58" t="n">
-        <v>7796</v>
-      </c>
-      <c r="C58" t="n">
-        <v>7803</v>
-      </c>
-      <c r="D58" t="n">
-        <v>7705.5</v>
-      </c>
-      <c r="E58" t="n">
-        <v>7726</v>
-      </c>
-      <c r="F58" t="n">
-        <v>-77.75</v>
-      </c>
-      <c r="G58" s="5" t="n">
-        <v>-0.01</v>
-      </c>
-      <c r="H58" t="n">
-        <v>97.5</v>
-      </c>
-      <c r="I58" t="n">
-        <v>7566</v>
-      </c>
-      <c r="J58" t="n">
-        <v>7675.44</v>
-      </c>
-      <c r="K58" t="n">
-        <v>7733.12</v>
-      </c>
-      <c r="L58" t="n">
-        <v>7790.81</v>
-      </c>
-      <c r="M58" t="n">
-        <v>7874.38</v>
-      </c>
-      <c r="N58" t="n">
-        <v>7957.94</v>
-      </c>
-      <c r="O58" t="n">
-        <v>7989.75</v>
-      </c>
-      <c r="P58" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q58" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R58" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="S58" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T58" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U58" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V58" s="8" t="n">
-        <v/>
-      </c>
-      <c r="W58" s="11" t="inlineStr">
-        <is>
-          <t>空方</t>
-        </is>
-      </c>
-      <c r="X58" t="inlineStr"/>
+      <c r="X57" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/three_gate/analysis/ES_weekly.xlsx
+++ b/three_gate/analysis/ES_weekly.xlsx
@@ -480,7 +480,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X57"/>
+  <dimension ref="A1:X58"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -5295,6 +5295,90 @@
       </c>
       <c r="X57" t="inlineStr"/>
     </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="B58" t="n">
+        <v>7831.75</v>
+      </c>
+      <c r="C58" t="n">
+        <v>7836.25</v>
+      </c>
+      <c r="D58" t="n">
+        <v>7831.5</v>
+      </c>
+      <c r="E58" t="n">
+        <v>7834.25</v>
+      </c>
+      <c r="F58" t="n">
+        <v>57</v>
+      </c>
+      <c r="G58" s="5" t="n">
+        <v>0.0073</v>
+      </c>
+      <c r="H58" t="n">
+        <v>4.75</v>
+      </c>
+      <c r="I58" t="n">
+        <v>7535.25</v>
+      </c>
+      <c r="J58" t="n">
+        <v>7657.62</v>
+      </c>
+      <c r="K58" t="n">
+        <v>7708.5</v>
+      </c>
+      <c r="L58" t="n">
+        <v>7759.38</v>
+      </c>
+      <c r="M58" t="n">
+        <v>7846</v>
+      </c>
+      <c r="N58" t="n">
+        <v>7932.62</v>
+      </c>
+      <c r="O58" t="n">
+        <v>7947.75</v>
+      </c>
+      <c r="P58" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q58" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R58" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S58" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T58" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="U58" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V58" s="8" t="n">
+        <v/>
+      </c>
+      <c r="W58" s="11" t="inlineStr">
+        <is>
+          <t>空方</t>
+        </is>
+      </c>
+      <c r="X58" t="inlineStr">
+        <is>
+          <t>強警訊</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/three_gate/analysis/ES_weekly.xlsx
+++ b/three_gate/analysis/ES_weekly.xlsx
@@ -659,25 +659,25 @@
         <v>125.75</v>
       </c>
       <c r="I2" t="n">
-        <v>6201.75</v>
+        <v>6309.25</v>
       </c>
       <c r="J2" t="n">
-        <v>6336.25</v>
+        <v>6376.56</v>
       </c>
       <c r="K2" t="n">
-        <v>6404.75</v>
+        <v>6431.62</v>
       </c>
       <c r="L2" t="n">
-        <v>6473.25</v>
+        <v>6486.69</v>
       </c>
       <c r="M2" t="n">
-        <v>6574.75</v>
+        <v>6547.88</v>
       </c>
       <c r="N2" t="n">
-        <v>6676.25</v>
+        <v>6609.06</v>
       </c>
       <c r="O2" t="n">
-        <v>6711.75</v>
+        <v>6658</v>
       </c>
       <c r="P2" s="6" t="n">
         <v/>
@@ -695,11 +695,13 @@
       </c>
       <c r="T2" s="8" t="inlineStr">
         <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U2" s="8" t="inlineStr">
+        <is>
           <t>△C</t>
         </is>
-      </c>
-      <c r="U2" s="8" t="n">
-        <v/>
       </c>
       <c r="V2" s="8" t="n">
         <v/>
@@ -5302,25 +5304,25 @@
         </is>
       </c>
       <c r="B58" t="n">
-        <v>7831.75</v>
+        <v>7781.5</v>
       </c>
       <c r="C58" t="n">
-        <v>7836.25</v>
+        <v>7884.5</v>
       </c>
       <c r="D58" t="n">
-        <v>7831.5</v>
+        <v>7760.25</v>
       </c>
       <c r="E58" t="n">
-        <v>7834.25</v>
+        <v>7881</v>
       </c>
       <c r="F58" t="n">
-        <v>57</v>
+        <v>103.75</v>
       </c>
       <c r="G58" s="5" t="n">
-        <v>0.0073</v>
+        <v>0.0133</v>
       </c>
       <c r="H58" t="n">
-        <v>4.75</v>
+        <v>124.25</v>
       </c>
       <c r="I58" t="n">
         <v>7535.25</v>

--- a/three_gate/analysis/ES_weekly.xlsx
+++ b/three_gate/analysis/ES_weekly.xlsx
@@ -659,25 +659,25 @@
         <v>125.75</v>
       </c>
       <c r="I2" t="n">
-        <v>6309.25</v>
+        <v>6362.25</v>
       </c>
       <c r="J2" t="n">
-        <v>6376.56</v>
+        <v>6396.44</v>
       </c>
       <c r="K2" t="n">
-        <v>6431.62</v>
+        <v>6444.88</v>
       </c>
       <c r="L2" t="n">
-        <v>6486.69</v>
+        <v>6493.31</v>
       </c>
       <c r="M2" t="n">
-        <v>6547.88</v>
+        <v>6534.62</v>
       </c>
       <c r="N2" t="n">
-        <v>6609.06</v>
+        <v>6575.94</v>
       </c>
       <c r="O2" t="n">
-        <v>6658</v>
+        <v>6631.5</v>
       </c>
       <c r="P2" s="6" t="n">
         <v/>
@@ -5307,22 +5307,22 @@
         <v>7781.5</v>
       </c>
       <c r="C58" t="n">
-        <v>7884.5</v>
+        <v>7897.5</v>
       </c>
       <c r="D58" t="n">
         <v>7760.25</v>
       </c>
       <c r="E58" t="n">
-        <v>7881</v>
+        <v>7850</v>
       </c>
       <c r="F58" t="n">
-        <v>103.75</v>
+        <v>72.75</v>
       </c>
       <c r="G58" s="5" t="n">
-        <v>0.0133</v>
+        <v>0.0094</v>
       </c>
       <c r="H58" t="n">
-        <v>124.25</v>
+        <v>137.25</v>
       </c>
       <c r="I58" t="n">
         <v>7535.25</v>

--- a/three_gate/analysis/ES_weekly.xlsx
+++ b/three_gate/analysis/ES_weekly.xlsx
@@ -5313,13 +5313,13 @@
         <v>7760.25</v>
       </c>
       <c r="E58" t="n">
-        <v>7850</v>
+        <v>7851</v>
       </c>
       <c r="F58" t="n">
-        <v>72.75</v>
+        <v>73.75</v>
       </c>
       <c r="G58" s="5" t="n">
-        <v>0.0094</v>
+        <v>0.0095</v>
       </c>
       <c r="H58" t="n">
         <v>137.25</v>

--- a/three_gate/analysis/ES_weekly.xlsx
+++ b/three_gate/analysis/ES_weekly.xlsx
@@ -5313,13 +5313,13 @@
         <v>7760.25</v>
       </c>
       <c r="E58" t="n">
-        <v>7851</v>
+        <v>7832.25</v>
       </c>
       <c r="F58" t="n">
-        <v>73.75</v>
+        <v>55</v>
       </c>
       <c r="G58" s="5" t="n">
-        <v>0.0095</v>
+        <v>0.0071</v>
       </c>
       <c r="H58" t="n">
         <v>137.25</v>

--- a/three_gate/analysis/ES_weekly.xlsx
+++ b/three_gate/analysis/ES_weekly.xlsx
@@ -480,7 +480,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X58"/>
+  <dimension ref="A1:X57"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -634,50 +634,50 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2025-09-08</t>
+          <t>2025-09-15</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>6483.75</v>
+        <v>6588.25</v>
       </c>
       <c r="C2" t="n">
-        <v>6606</v>
+        <v>6662</v>
       </c>
       <c r="D2" t="n">
-        <v>6480.25</v>
+        <v>6554</v>
       </c>
       <c r="E2" t="n">
-        <v>6588.25</v>
+        <v>6658.77</v>
       </c>
       <c r="F2" t="n">
-        <v>98.5</v>
+        <v>70.52</v>
       </c>
       <c r="G2" s="5" t="n">
-        <v>0.0152</v>
+        <v>0.0107</v>
       </c>
       <c r="H2" t="n">
-        <v>125.75</v>
+        <v>108</v>
       </c>
       <c r="I2" t="n">
-        <v>6362.25</v>
+        <v>6354.5</v>
       </c>
       <c r="J2" t="n">
-        <v>6396.44</v>
+        <v>6485.06</v>
       </c>
       <c r="K2" t="n">
-        <v>6444.88</v>
+        <v>6525.38</v>
       </c>
       <c r="L2" t="n">
-        <v>6493.31</v>
+        <v>6565.69</v>
       </c>
       <c r="M2" t="n">
-        <v>6534.62</v>
+        <v>6651.12</v>
       </c>
       <c r="N2" t="n">
-        <v>6575.94</v>
+        <v>6736.56</v>
       </c>
       <c r="O2" t="n">
-        <v>6631.5</v>
+        <v>6731.75</v>
       </c>
       <c r="P2" s="6" t="n">
         <v/>
@@ -695,13 +695,11 @@
       </c>
       <c r="T2" s="8" t="inlineStr">
         <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U2" s="8" t="inlineStr">
-        <is>
           <t>△C</t>
         </is>
+      </c>
+      <c r="U2" s="8" t="n">
+        <v/>
       </c>
       <c r="V2" s="8" t="n">
         <v/>
@@ -716,50 +714,50 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2025-09-15</t>
+          <t>2025-09-22</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>6588.25</v>
+        <v>6716</v>
       </c>
       <c r="C3" t="n">
-        <v>6662</v>
+        <v>6756.75</v>
       </c>
       <c r="D3" t="n">
-        <v>6554</v>
+        <v>6624.25</v>
       </c>
       <c r="E3" t="n">
-        <v>6658.77</v>
+        <v>6696.5</v>
       </c>
       <c r="F3" t="n">
-        <v>70.52</v>
+        <v>37.73</v>
       </c>
       <c r="G3" s="5" t="n">
-        <v>0.0107</v>
+        <v>0.0057</v>
       </c>
       <c r="H3" t="n">
-        <v>108</v>
+        <v>132.5</v>
       </c>
       <c r="I3" t="n">
-        <v>6354.5</v>
+        <v>6446</v>
       </c>
       <c r="J3" t="n">
-        <v>6485.06</v>
+        <v>6576.16</v>
       </c>
       <c r="K3" t="n">
-        <v>6525.38</v>
+        <v>6604.77</v>
       </c>
       <c r="L3" t="n">
-        <v>6565.69</v>
+        <v>6633.39</v>
       </c>
       <c r="M3" t="n">
-        <v>6651.12</v>
+        <v>6712.77</v>
       </c>
       <c r="N3" t="n">
-        <v>6736.56</v>
+        <v>6792.16</v>
       </c>
       <c r="O3" t="n">
-        <v>6731.75</v>
+        <v>6770</v>
       </c>
       <c r="P3" s="6" t="n">
         <v/>
@@ -796,50 +794,50 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2025-09-22</t>
+          <t>2025-09-29</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>6716</v>
+        <v>6697</v>
       </c>
       <c r="C4" t="n">
-        <v>6756.75</v>
+        <v>6800</v>
       </c>
       <c r="D4" t="n">
-        <v>6624.25</v>
+        <v>6680</v>
       </c>
       <c r="E4" t="n">
-        <v>6696.5</v>
+        <v>6764</v>
       </c>
       <c r="F4" t="n">
-        <v>37.73</v>
+        <v>67.5</v>
       </c>
       <c r="G4" s="5" t="n">
-        <v>0.0057</v>
+        <v>0.0101</v>
       </c>
       <c r="H4" t="n">
-        <v>132.5</v>
+        <v>120</v>
       </c>
       <c r="I4" t="n">
-        <v>6446</v>
+        <v>6491.75</v>
       </c>
       <c r="J4" t="n">
-        <v>6576.16</v>
+        <v>6567</v>
       </c>
       <c r="K4" t="n">
-        <v>6604.77</v>
+        <v>6630.25</v>
       </c>
       <c r="L4" t="n">
-        <v>6633.39</v>
+        <v>6693.5</v>
       </c>
       <c r="M4" t="n">
-        <v>6712.77</v>
+        <v>6762.75</v>
       </c>
       <c r="N4" t="n">
-        <v>6792.16</v>
+        <v>6832</v>
       </c>
       <c r="O4" t="n">
-        <v>6770</v>
+        <v>6889.25</v>
       </c>
       <c r="P4" s="6" t="n">
         <v/>
@@ -876,154 +874,158 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2025-09-29</t>
+          <t>2025-10-06</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>6697</v>
+        <v>6768</v>
       </c>
       <c r="C5" t="n">
-        <v>6800</v>
+        <v>6812.25</v>
       </c>
       <c r="D5" t="n">
-        <v>6680</v>
+        <v>6540.25</v>
       </c>
       <c r="E5" t="n">
-        <v>6764</v>
+        <v>6595.25</v>
       </c>
       <c r="F5" t="n">
-        <v>67.5</v>
+        <v>-168.75</v>
       </c>
       <c r="G5" s="5" t="n">
-        <v>0.0101</v>
+        <v>-0.0249</v>
       </c>
       <c r="H5" t="n">
-        <v>120</v>
+        <v>272</v>
       </c>
       <c r="I5" t="n">
-        <v>6491.75</v>
+        <v>6560</v>
       </c>
       <c r="J5" t="n">
-        <v>6567</v>
+        <v>6656</v>
       </c>
       <c r="K5" t="n">
-        <v>6630.25</v>
+        <v>6704</v>
       </c>
       <c r="L5" t="n">
-        <v>6693.5</v>
+        <v>6752</v>
       </c>
       <c r="M5" t="n">
-        <v>6762.75</v>
+        <v>6824</v>
       </c>
       <c r="N5" t="n">
-        <v>6832</v>
+        <v>6896</v>
       </c>
       <c r="O5" t="n">
-        <v>6889.25</v>
-      </c>
-      <c r="P5" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q5" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R5" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S5" s="7" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T5" s="8" t="inlineStr">
+        <v>6920</v>
+      </c>
+      <c r="P5" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
+      <c r="Q5" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="R5" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S5" s="10" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T5" s="8" t="n">
+        <v/>
+      </c>
       <c r="U5" s="8" t="n">
         <v/>
       </c>
       <c r="V5" s="8" t="n">
         <v/>
       </c>
-      <c r="W5" s="9" t="inlineStr">
-        <is>
-          <t>多方</t>
-        </is>
-      </c>
-      <c r="X5" t="inlineStr"/>
+      <c r="W5" s="11" t="inlineStr">
+        <is>
+          <t>空方</t>
+        </is>
+      </c>
+      <c r="X5" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2025-10-06</t>
+          <t>2025-10-13</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>6768</v>
+        <v>6632</v>
       </c>
       <c r="C6" t="n">
-        <v>6812.25</v>
+        <v>6766.75</v>
       </c>
       <c r="D6" t="n">
-        <v>6540.25</v>
+        <v>6571.25</v>
       </c>
       <c r="E6" t="n">
-        <v>6595.25</v>
+        <v>6702.5</v>
       </c>
       <c r="F6" t="n">
-        <v>-168.75</v>
+        <v>107.25</v>
       </c>
       <c r="G6" s="5" t="n">
-        <v>-0.0249</v>
+        <v>0.0163</v>
       </c>
       <c r="H6" t="n">
-        <v>272</v>
+        <v>195.5</v>
       </c>
       <c r="I6" t="n">
-        <v>6560</v>
+        <v>6268.25</v>
       </c>
       <c r="J6" t="n">
-        <v>6656</v>
+        <v>6282.75</v>
       </c>
       <c r="K6" t="n">
-        <v>6704</v>
+        <v>6459.25</v>
       </c>
       <c r="L6" t="n">
-        <v>6752</v>
+        <v>6635.75</v>
       </c>
       <c r="M6" t="n">
-        <v>6824</v>
+        <v>6731.25</v>
       </c>
       <c r="N6" t="n">
-        <v>6896</v>
+        <v>6826.75</v>
       </c>
       <c r="O6" t="n">
-        <v>6920</v>
-      </c>
-      <c r="P6" s="6" t="inlineStr">
+        <v>7084.25</v>
+      </c>
+      <c r="P6" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q6" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R6" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S6" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T6" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="Q6" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="R6" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S6" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T6" s="8" t="n">
-        <v/>
-      </c>
       <c r="U6" s="8" t="n">
         <v/>
       </c>
@@ -1037,57 +1039,57 @@
       </c>
       <c r="X6" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2025-10-13</t>
+          <t>2025-10-20</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>6632</v>
+        <v>6721</v>
       </c>
       <c r="C7" t="n">
-        <v>6766.75</v>
+        <v>6841.25</v>
       </c>
       <c r="D7" t="n">
-        <v>6571.25</v>
+        <v>6690.75</v>
       </c>
       <c r="E7" t="n">
-        <v>6702.5</v>
+        <v>6827</v>
       </c>
       <c r="F7" t="n">
-        <v>107.25</v>
+        <v>124.5</v>
       </c>
       <c r="G7" s="5" t="n">
-        <v>0.0163</v>
+        <v>0.0186</v>
       </c>
       <c r="H7" t="n">
-        <v>195.5</v>
+        <v>150.5</v>
       </c>
       <c r="I7" t="n">
-        <v>6268.25</v>
+        <v>6375.75</v>
       </c>
       <c r="J7" t="n">
-        <v>6282.75</v>
+        <v>6523.75</v>
       </c>
       <c r="K7" t="n">
-        <v>6459.25</v>
+        <v>6604.75</v>
       </c>
       <c r="L7" t="n">
-        <v>6635.75</v>
+        <v>6685.75</v>
       </c>
       <c r="M7" t="n">
-        <v>6731.25</v>
+        <v>6800.25</v>
       </c>
       <c r="N7" t="n">
-        <v>6826.75</v>
+        <v>6914.75</v>
       </c>
       <c r="O7" t="n">
-        <v>7084.25</v>
+        <v>6962.25</v>
       </c>
       <c r="P7" s="6" t="n">
         <v/>
@@ -1121,57 +1123,57 @@
       </c>
       <c r="X7" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2025-10-20</t>
+          <t>2025-10-27</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>6721</v>
+        <v>6881</v>
       </c>
       <c r="C8" t="n">
-        <v>6841.25</v>
+        <v>6953.75</v>
       </c>
       <c r="D8" t="n">
-        <v>6690.75</v>
+        <v>6843.5</v>
       </c>
       <c r="E8" t="n">
-        <v>6827</v>
+        <v>6874</v>
       </c>
       <c r="F8" t="n">
-        <v>124.5</v>
+        <v>47</v>
       </c>
       <c r="G8" s="5" t="n">
-        <v>0.0186</v>
+        <v>0.0069</v>
       </c>
       <c r="H8" t="n">
-        <v>150.5</v>
+        <v>110.25</v>
       </c>
       <c r="I8" t="n">
-        <v>6375.75</v>
+        <v>6540.25</v>
       </c>
       <c r="J8" t="n">
-        <v>6523.75</v>
+        <v>6707</v>
       </c>
       <c r="K8" t="n">
-        <v>6604.75</v>
+        <v>6751.75</v>
       </c>
       <c r="L8" t="n">
-        <v>6685.75</v>
+        <v>6796.5</v>
       </c>
       <c r="M8" t="n">
-        <v>6800.25</v>
+        <v>6902.25</v>
       </c>
       <c r="N8" t="n">
-        <v>6914.75</v>
+        <v>7008</v>
       </c>
       <c r="O8" t="n">
-        <v>6962.25</v>
+        <v>6991.75</v>
       </c>
       <c r="P8" s="6" t="n">
         <v/>
@@ -1212,70 +1214,74 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2025-10-27</t>
+          <t>2025-11-03</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>6881</v>
+        <v>6878</v>
       </c>
       <c r="C9" t="n">
-        <v>6953.75</v>
+        <v>6909.5</v>
       </c>
       <c r="D9" t="n">
-        <v>6843.5</v>
+        <v>6655.5</v>
       </c>
       <c r="E9" t="n">
-        <v>6874</v>
+        <v>6753.75</v>
       </c>
       <c r="F9" t="n">
-        <v>47</v>
+        <v>-120.25</v>
       </c>
       <c r="G9" s="5" t="n">
-        <v>0.0069</v>
+        <v>-0.0175</v>
       </c>
       <c r="H9" t="n">
-        <v>110.25</v>
+        <v>254</v>
       </c>
       <c r="I9" t="n">
-        <v>6540.25</v>
+        <v>6733.25</v>
       </c>
       <c r="J9" t="n">
-        <v>6707</v>
+        <v>6751.44</v>
       </c>
       <c r="K9" t="n">
-        <v>6751.75</v>
+        <v>6818.88</v>
       </c>
       <c r="L9" t="n">
-        <v>6796.5</v>
+        <v>6886.31</v>
       </c>
       <c r="M9" t="n">
-        <v>6902.25</v>
+        <v>6929.12</v>
       </c>
       <c r="N9" t="n">
-        <v>7008</v>
+        <v>6971.94</v>
       </c>
       <c r="O9" t="n">
-        <v>6991.75</v>
-      </c>
-      <c r="P9" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q9" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R9" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S9" s="7" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T9" s="8" t="inlineStr">
+        <v>7064</v>
+      </c>
+      <c r="P9" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="Q9" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
+      <c r="R9" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S9" s="10" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T9" s="8" t="n">
+        <v/>
+      </c>
       <c r="U9" s="8" t="n">
         <v/>
       </c>
@@ -1287,83 +1293,75 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X9" t="inlineStr">
-        <is>
-          <t>強警訊</t>
-        </is>
-      </c>
+      <c r="X9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2025-11-03</t>
+          <t>2025-11-10</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>6878</v>
+        <v>6788</v>
       </c>
       <c r="C10" t="n">
-        <v>6909.5</v>
+        <v>6900.5</v>
       </c>
       <c r="D10" t="n">
-        <v>6655.5</v>
+        <v>6670.5</v>
       </c>
       <c r="E10" t="n">
-        <v>6753.75</v>
+        <v>6755.25</v>
       </c>
       <c r="F10" t="n">
-        <v>-120.25</v>
+        <v>1.5</v>
       </c>
       <c r="G10" s="5" t="n">
-        <v>-0.0175</v>
+        <v>0.0002</v>
       </c>
       <c r="H10" t="n">
-        <v>254</v>
+        <v>230</v>
       </c>
       <c r="I10" t="n">
-        <v>6733.25</v>
+        <v>6401.5</v>
       </c>
       <c r="J10" t="n">
-        <v>6751.44</v>
+        <v>6485.38</v>
       </c>
       <c r="K10" t="n">
-        <v>6818.88</v>
+        <v>6626.75</v>
       </c>
       <c r="L10" t="n">
-        <v>6886.31</v>
+        <v>6768.12</v>
       </c>
       <c r="M10" t="n">
-        <v>6929.12</v>
+        <v>6880.75</v>
       </c>
       <c r="N10" t="n">
-        <v>6971.94</v>
+        <v>6993.38</v>
       </c>
       <c r="O10" t="n">
-        <v>7064</v>
-      </c>
-      <c r="P10" s="6" t="inlineStr">
+        <v>7163.5</v>
+      </c>
+      <c r="P10" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q10" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R10" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S10" s="10" t="inlineStr">
+        <is>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T10" s="8" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="Q10" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="R10" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S10" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T10" s="8" t="n">
-        <v/>
-      </c>
       <c r="U10" s="8" t="n">
         <v/>
       </c>
@@ -1375,55 +1373,59 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X10" t="inlineStr"/>
+      <c r="X10" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2025-11-10</t>
+          <t>2025-11-17</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>6788</v>
+        <v>6764.75</v>
       </c>
       <c r="C11" t="n">
-        <v>6900.5</v>
+        <v>6801.5</v>
       </c>
       <c r="D11" t="n">
-        <v>6670.5</v>
+        <v>6525</v>
       </c>
       <c r="E11" t="n">
-        <v>6755.25</v>
+        <v>6620.25</v>
       </c>
       <c r="F11" t="n">
-        <v>1.5</v>
+        <v>-135</v>
       </c>
       <c r="G11" s="5" t="n">
-        <v>0.0002</v>
+        <v>-0.02</v>
       </c>
       <c r="H11" t="n">
-        <v>230</v>
+        <v>276.5</v>
       </c>
       <c r="I11" t="n">
-        <v>6401.5</v>
+        <v>6440.5</v>
       </c>
       <c r="J11" t="n">
-        <v>6485.38</v>
+        <v>6510.12</v>
       </c>
       <c r="K11" t="n">
-        <v>6626.75</v>
+        <v>6640.25</v>
       </c>
       <c r="L11" t="n">
-        <v>6768.12</v>
+        <v>6770.38</v>
       </c>
       <c r="M11" t="n">
-        <v>6880.75</v>
+        <v>6870.25</v>
       </c>
       <c r="N11" t="n">
-        <v>6993.38</v>
+        <v>6970.12</v>
       </c>
       <c r="O11" t="n">
-        <v>7163.5</v>
+        <v>7130.5</v>
       </c>
       <c r="P11" s="6" t="n">
         <v/>
@@ -1431,18 +1433,18 @@
       <c r="Q11" s="6" t="n">
         <v/>
       </c>
-      <c r="R11" s="6" t="n">
-        <v/>
+      <c r="R11" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="S11" s="10" t="inlineStr">
         <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T11" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T11" s="8" t="n">
+        <v/>
       </c>
       <c r="U11" s="8" t="n">
         <v/>
@@ -1455,59 +1457,55 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X11" t="inlineStr">
-        <is>
-          <t>中警訊</t>
-        </is>
-      </c>
+      <c r="X11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2025-11-17</t>
+          <t>2025-11-24</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>6764.75</v>
+        <v>6654.75</v>
       </c>
       <c r="C12" t="n">
-        <v>6801.5</v>
+        <v>6863.75</v>
       </c>
       <c r="D12" t="n">
-        <v>6525</v>
+        <v>6625</v>
       </c>
       <c r="E12" t="n">
-        <v>6620.25</v>
+        <v>6859.5</v>
       </c>
       <c r="F12" t="n">
-        <v>-135</v>
+        <v>239.25</v>
       </c>
       <c r="G12" s="5" t="n">
-        <v>-0.02</v>
+        <v>0.0361</v>
       </c>
       <c r="H12" t="n">
-        <v>276.5</v>
+        <v>238.75</v>
       </c>
       <c r="I12" t="n">
-        <v>6440.5</v>
+        <v>6248.5</v>
       </c>
       <c r="J12" t="n">
-        <v>6510.12</v>
+        <v>6322.25</v>
       </c>
       <c r="K12" t="n">
-        <v>6640.25</v>
+        <v>6482</v>
       </c>
       <c r="L12" t="n">
-        <v>6770.38</v>
+        <v>6641.75</v>
       </c>
       <c r="M12" t="n">
-        <v>6870.25</v>
+        <v>6758.5</v>
       </c>
       <c r="N12" t="n">
-        <v>6970.12</v>
+        <v>6875.25</v>
       </c>
       <c r="O12" t="n">
-        <v>7130.5</v>
+        <v>7078</v>
       </c>
       <c r="P12" s="6" t="n">
         <v/>
@@ -1515,22 +1513,24 @@
       <c r="Q12" s="6" t="n">
         <v/>
       </c>
-      <c r="R12" s="6" t="inlineStr">
+      <c r="R12" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S12" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T12" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U12" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="S12" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T12" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U12" s="8" t="n">
-        <v/>
-      </c>
       <c r="V12" s="8" t="n">
         <v/>
       </c>
@@ -1539,55 +1539,59 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X12" t="inlineStr"/>
+      <c r="X12" t="inlineStr">
+        <is>
+          <t>強警訊</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2025-11-24</t>
+          <t>2025-12-01</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>6654.75</v>
+        <v>6854.75</v>
       </c>
       <c r="C13" t="n">
-        <v>6863.75</v>
+        <v>6905</v>
       </c>
       <c r="D13" t="n">
-        <v>6625</v>
+        <v>6802</v>
       </c>
       <c r="E13" t="n">
-        <v>6859.5</v>
+        <v>6878.25</v>
       </c>
       <c r="F13" t="n">
-        <v>239.25</v>
+        <v>18.75</v>
       </c>
       <c r="G13" s="5" t="n">
-        <v>0.0361</v>
+        <v>0.0027</v>
       </c>
       <c r="H13" t="n">
-        <v>238.75</v>
+        <v>103</v>
       </c>
       <c r="I13" t="n">
-        <v>6248.5</v>
+        <v>6386.25</v>
       </c>
       <c r="J13" t="n">
-        <v>6322.25</v>
+        <v>6678.31</v>
       </c>
       <c r="K13" t="n">
-        <v>6482</v>
+        <v>6740.12</v>
       </c>
       <c r="L13" t="n">
-        <v>6641.75</v>
+        <v>6801.94</v>
       </c>
       <c r="M13" t="n">
-        <v>6758.5</v>
+        <v>6978.88</v>
       </c>
       <c r="N13" t="n">
-        <v>6875.25</v>
+        <v>7155.81</v>
       </c>
       <c r="O13" t="n">
-        <v>7078</v>
+        <v>7102.5</v>
       </c>
       <c r="P13" s="6" t="n">
         <v/>
@@ -1600,18 +1604,14 @@
       </c>
       <c r="S13" s="7" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T13" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U13" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T13" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U13" s="8" t="n">
+        <v/>
       </c>
       <c r="V13" s="8" t="n">
         <v/>
@@ -1630,50 +1630,50 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2025-12-01</t>
+          <t>2025-12-08</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>6854.75</v>
+        <v>6883</v>
       </c>
       <c r="C14" t="n">
-        <v>6905</v>
+        <v>6928.75</v>
       </c>
       <c r="D14" t="n">
-        <v>6802</v>
+        <v>6805</v>
       </c>
       <c r="E14" t="n">
-        <v>6878.25</v>
+        <v>6830.75</v>
       </c>
       <c r="F14" t="n">
-        <v>18.75</v>
+        <v>-47.5</v>
       </c>
       <c r="G14" s="5" t="n">
-        <v>0.0027</v>
+        <v>-0.0069</v>
       </c>
       <c r="H14" t="n">
-        <v>103</v>
+        <v>123.75</v>
       </c>
       <c r="I14" t="n">
-        <v>6386.25</v>
+        <v>6699</v>
       </c>
       <c r="J14" t="n">
-        <v>6678.31</v>
+        <v>6787.62</v>
       </c>
       <c r="K14" t="n">
-        <v>6740.12</v>
+        <v>6826.75</v>
       </c>
       <c r="L14" t="n">
-        <v>6801.94</v>
+        <v>6865.88</v>
       </c>
       <c r="M14" t="n">
-        <v>6978.88</v>
+        <v>6929.75</v>
       </c>
       <c r="N14" t="n">
-        <v>7155.81</v>
+        <v>6993.62</v>
       </c>
       <c r="O14" t="n">
-        <v>7102.5</v>
+        <v>7008</v>
       </c>
       <c r="P14" s="6" t="n">
         <v/>
@@ -1681,12 +1681,14 @@
       <c r="Q14" s="6" t="n">
         <v/>
       </c>
-      <c r="R14" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S14" s="7" t="inlineStr">
-        <is>
-          <t>↑C</t>
+      <c r="R14" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="S14" s="10" t="inlineStr">
+        <is>
+          <t>↓</t>
         </is>
       </c>
       <c r="T14" s="8" t="n">
@@ -1705,57 +1707,57 @@
       </c>
       <c r="X14" t="inlineStr">
         <is>
-          <t>強警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2025-12-08</t>
+          <t>2025-12-15</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>6883</v>
+        <v>6831</v>
       </c>
       <c r="C15" t="n">
-        <v>6928.75</v>
+        <v>6872.5</v>
       </c>
       <c r="D15" t="n">
-        <v>6805</v>
+        <v>6720.25</v>
       </c>
       <c r="E15" t="n">
-        <v>6830.75</v>
+        <v>6796.54</v>
       </c>
       <c r="F15" t="n">
-        <v>-47.5</v>
+        <v>-34.21</v>
       </c>
       <c r="G15" s="5" t="n">
-        <v>-0.0069</v>
+        <v>-0.005</v>
       </c>
       <c r="H15" t="n">
-        <v>123.75</v>
+        <v>152.25</v>
       </c>
       <c r="I15" t="n">
-        <v>6699</v>
+        <v>6681.25</v>
       </c>
       <c r="J15" t="n">
-        <v>6787.62</v>
+        <v>6688.94</v>
       </c>
       <c r="K15" t="n">
-        <v>6826.75</v>
+        <v>6768.88</v>
       </c>
       <c r="L15" t="n">
-        <v>6865.88</v>
+        <v>6848.81</v>
       </c>
       <c r="M15" t="n">
-        <v>6929.75</v>
+        <v>6892.62</v>
       </c>
       <c r="N15" t="n">
-        <v>6993.62</v>
+        <v>6936.44</v>
       </c>
       <c r="O15" t="n">
-        <v>7008</v>
+        <v>7052.5</v>
       </c>
       <c r="P15" s="6" t="n">
         <v/>
@@ -1787,59 +1789,55 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X15" t="inlineStr">
-        <is>
-          <t>中警訊</t>
-        </is>
-      </c>
+      <c r="X15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2025-12-15</t>
+          <t>2025-12-22</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>6831</v>
+        <v>6906.25</v>
       </c>
       <c r="C16" t="n">
-        <v>6872.5</v>
+        <v>6994</v>
       </c>
       <c r="D16" t="n">
-        <v>6720.25</v>
+        <v>6900.5</v>
       </c>
       <c r="E16" t="n">
-        <v>6796.54</v>
+        <v>6979.25</v>
       </c>
       <c r="F16" t="n">
-        <v>-34.21</v>
+        <v>182.71</v>
       </c>
       <c r="G16" s="5" t="n">
-        <v>-0.005</v>
+        <v>0.0269</v>
       </c>
       <c r="H16" t="n">
-        <v>152.25</v>
+        <v>93.5</v>
       </c>
       <c r="I16" t="n">
-        <v>6681.25</v>
+        <v>6568</v>
       </c>
       <c r="J16" t="n">
-        <v>6688.94</v>
+        <v>6644.37</v>
       </c>
       <c r="K16" t="n">
-        <v>6768.88</v>
+        <v>6720.42</v>
       </c>
       <c r="L16" t="n">
-        <v>6848.81</v>
+        <v>6796.46</v>
       </c>
       <c r="M16" t="n">
-        <v>6892.62</v>
+        <v>6872.67</v>
       </c>
       <c r="N16" t="n">
-        <v>6936.44</v>
+        <v>6948.87</v>
       </c>
       <c r="O16" t="n">
-        <v>7052.5</v>
+        <v>7024.75</v>
       </c>
       <c r="P16" s="6" t="n">
         <v/>
@@ -1847,28 +1845,30 @@
       <c r="Q16" s="6" t="n">
         <v/>
       </c>
-      <c r="R16" s="6" t="inlineStr">
+      <c r="R16" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S16" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T16" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U16" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="S16" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T16" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U16" s="8" t="n">
-        <v/>
-      </c>
       <c r="V16" s="8" t="n">
         <v/>
       </c>
-      <c r="W16" s="11" t="inlineStr">
-        <is>
-          <t>空方</t>
+      <c r="W16" s="9" t="inlineStr">
+        <is>
+          <t>多方</t>
         </is>
       </c>
       <c r="X16" t="inlineStr"/>
@@ -1876,81 +1876,81 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2025-12-22</t>
+          <t>2025-12-29</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>6906.25</v>
+        <v>6980.5</v>
       </c>
       <c r="C17" t="n">
-        <v>6994</v>
+        <v>6984.75</v>
       </c>
       <c r="D17" t="n">
+        <v>6866.75</v>
+      </c>
+      <c r="E17" t="n">
         <v>6900.5</v>
       </c>
-      <c r="E17" t="n">
-        <v>6979.25</v>
-      </c>
       <c r="F17" t="n">
-        <v>182.71</v>
+        <v>-78.75</v>
       </c>
       <c r="G17" s="5" t="n">
-        <v>0.0269</v>
+        <v>-0.0113</v>
       </c>
       <c r="H17" t="n">
-        <v>93.5</v>
+        <v>118</v>
       </c>
       <c r="I17" t="n">
-        <v>6568</v>
+        <v>6807</v>
       </c>
       <c r="J17" t="n">
-        <v>6644.37</v>
+        <v>6901.75</v>
       </c>
       <c r="K17" t="n">
-        <v>6720.42</v>
+        <v>6932.5</v>
       </c>
       <c r="L17" t="n">
-        <v>6796.46</v>
+        <v>6963.25</v>
       </c>
       <c r="M17" t="n">
-        <v>6872.67</v>
+        <v>7026</v>
       </c>
       <c r="N17" t="n">
-        <v>6948.87</v>
+        <v>7088.75</v>
       </c>
       <c r="O17" t="n">
-        <v>7024.75</v>
+        <v>7087.5</v>
       </c>
       <c r="P17" s="6" t="n">
         <v/>
       </c>
-      <c r="Q17" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R17" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S17" s="7" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T17" s="8" t="inlineStr">
+      <c r="Q17" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="R17" s="6" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="U17" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+      <c r="S17" s="10" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T17" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U17" s="8" t="n">
+        <v/>
       </c>
       <c r="V17" s="8" t="n">
         <v/>
       </c>
-      <c r="W17" s="9" t="inlineStr">
-        <is>
-          <t>多方</t>
+      <c r="W17" s="11" t="inlineStr">
+        <is>
+          <t>空方</t>
         </is>
       </c>
       <c r="X17" t="inlineStr"/>
@@ -1958,75 +1958,75 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2025-12-29</t>
+          <t>2026-01-05</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>6980.5</v>
+        <v>6911.5</v>
       </c>
       <c r="C18" t="n">
-        <v>6984.75</v>
+        <v>7017.5</v>
       </c>
       <c r="D18" t="n">
-        <v>6866.75</v>
+        <v>6899.5</v>
       </c>
       <c r="E18" t="n">
-        <v>6900.5</v>
+        <v>7005</v>
       </c>
       <c r="F18" t="n">
-        <v>-78.75</v>
+        <v>104.5</v>
       </c>
       <c r="G18" s="5" t="n">
-        <v>-0.0113</v>
+        <v>0.0151</v>
       </c>
       <c r="H18" t="n">
         <v>118</v>
       </c>
       <c r="I18" t="n">
-        <v>6807</v>
+        <v>6748.75</v>
       </c>
       <c r="J18" t="n">
-        <v>6901.75</v>
+        <v>6769.88</v>
       </c>
       <c r="K18" t="n">
-        <v>6932.5</v>
+        <v>6841.5</v>
       </c>
       <c r="L18" t="n">
-        <v>6963.25</v>
+        <v>6913.12</v>
       </c>
       <c r="M18" t="n">
-        <v>7026</v>
+        <v>6959.5</v>
       </c>
       <c r="N18" t="n">
-        <v>7088.75</v>
+        <v>7005.88</v>
       </c>
       <c r="O18" t="n">
-        <v>7087.5</v>
+        <v>7102.75</v>
       </c>
       <c r="P18" s="6" t="n">
         <v/>
       </c>
-      <c r="Q18" s="6" t="inlineStr">
+      <c r="Q18" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R18" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S18" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T18" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U18" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="R18" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S18" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T18" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U18" s="8" t="n">
-        <v/>
-      </c>
       <c r="V18" s="8" t="n">
         <v/>
       </c>
@@ -2035,55 +2035,59 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X18" t="inlineStr"/>
+      <c r="X18" t="inlineStr">
+        <is>
+          <t>強警訊</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-01-05</t>
+          <t>2026-01-12</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>6911.5</v>
+        <v>7007</v>
       </c>
       <c r="C19" t="n">
-        <v>7017.5</v>
+        <v>7036.25</v>
       </c>
       <c r="D19" t="n">
-        <v>6899.5</v>
+        <v>6923.25</v>
       </c>
       <c r="E19" t="n">
-        <v>7005</v>
+        <v>6976.75</v>
       </c>
       <c r="F19" t="n">
-        <v>104.5</v>
+        <v>-28.25</v>
       </c>
       <c r="G19" s="5" t="n">
-        <v>0.0151</v>
+        <v>-0.004</v>
       </c>
       <c r="H19" t="n">
-        <v>118</v>
+        <v>113</v>
       </c>
       <c r="I19" t="n">
-        <v>6748.75</v>
+        <v>6781.5</v>
       </c>
       <c r="J19" t="n">
-        <v>6769.88</v>
+        <v>6910.25</v>
       </c>
       <c r="K19" t="n">
-        <v>6841.5</v>
+        <v>6946</v>
       </c>
       <c r="L19" t="n">
-        <v>6913.12</v>
+        <v>6981.75</v>
       </c>
       <c r="M19" t="n">
-        <v>6959.5</v>
+        <v>7064</v>
       </c>
       <c r="N19" t="n">
-        <v>7005.88</v>
+        <v>7146.25</v>
       </c>
       <c r="O19" t="n">
-        <v>7102.75</v>
+        <v>7135.5</v>
       </c>
       <c r="P19" s="6" t="n">
         <v/>
@@ -2091,23 +2095,21 @@
       <c r="Q19" s="6" t="n">
         <v/>
       </c>
-      <c r="R19" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S19" s="7" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T19" s="8" t="inlineStr">
+      <c r="R19" s="6" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="U19" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+      <c r="S19" s="10" t="inlineStr">
+        <is>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T19" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U19" s="8" t="n">
+        <v/>
       </c>
       <c r="V19" s="8" t="n">
         <v/>
@@ -2119,72 +2121,74 @@
       </c>
       <c r="X19" t="inlineStr">
         <is>
-          <t>強警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2026-01-12</t>
+          <t>2026-01-19</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>7007</v>
+        <v>6918.25</v>
       </c>
       <c r="C20" t="n">
-        <v>7036.25</v>
+        <v>6969</v>
       </c>
       <c r="D20" t="n">
-        <v>6923.25</v>
+        <v>6814.5</v>
       </c>
       <c r="E20" t="n">
-        <v>6976.75</v>
+        <v>6945.75</v>
       </c>
       <c r="F20" t="n">
-        <v>-28.25</v>
+        <v>-31</v>
       </c>
       <c r="G20" s="5" t="n">
-        <v>-0.004</v>
+        <v>-0.0044</v>
       </c>
       <c r="H20" t="n">
-        <v>113</v>
+        <v>154.5</v>
       </c>
       <c r="I20" t="n">
-        <v>6781.5</v>
+        <v>6810.25</v>
       </c>
       <c r="J20" t="n">
-        <v>6910.25</v>
+        <v>6862.25</v>
       </c>
       <c r="K20" t="n">
-        <v>6946</v>
+        <v>6920.25</v>
       </c>
       <c r="L20" t="n">
-        <v>6981.75</v>
+        <v>6978.25</v>
       </c>
       <c r="M20" t="n">
-        <v>7064</v>
+        <v>7033.25</v>
       </c>
       <c r="N20" t="n">
-        <v>7146.25</v>
+        <v>7088.25</v>
       </c>
       <c r="O20" t="n">
-        <v>7135.5</v>
+        <v>7149.25</v>
       </c>
       <c r="P20" s="6" t="n">
         <v/>
       </c>
-      <c r="Q20" s="6" t="n">
-        <v/>
+      <c r="Q20" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="R20" s="6" t="inlineStr">
         <is>
-          <t>✓</t>
+          <t>△C</t>
         </is>
       </c>
       <c r="S20" s="10" t="inlineStr">
         <is>
-          <t>↓C</t>
+          <t>↓</t>
         </is>
       </c>
       <c r="T20" s="8" t="n">
@@ -2201,81 +2205,75 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X20" t="inlineStr">
-        <is>
-          <t>中警訊</t>
-        </is>
-      </c>
+      <c r="X20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-01-19</t>
+          <t>2026-01-26</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>6918.25</v>
+        <v>6904</v>
       </c>
       <c r="C21" t="n">
-        <v>6969</v>
+        <v>7043</v>
       </c>
       <c r="D21" t="n">
-        <v>6814.5</v>
+        <v>6879</v>
       </c>
       <c r="E21" t="n">
-        <v>6945.75</v>
+        <v>6965.75</v>
       </c>
       <c r="F21" t="n">
-        <v>-31</v>
+        <v>20</v>
       </c>
       <c r="G21" s="5" t="n">
-        <v>-0.0044</v>
+        <v>0.0029</v>
       </c>
       <c r="H21" t="n">
-        <v>154.5</v>
+        <v>164</v>
       </c>
       <c r="I21" t="n">
-        <v>6810.25</v>
+        <v>6660</v>
       </c>
       <c r="J21" t="n">
-        <v>6862.25</v>
+        <v>6818.25</v>
       </c>
       <c r="K21" t="n">
-        <v>6920.25</v>
+        <v>6868.5</v>
       </c>
       <c r="L21" t="n">
-        <v>6978.25</v>
+        <v>6918.75</v>
       </c>
       <c r="M21" t="n">
-        <v>7033.25</v>
+        <v>7023</v>
       </c>
       <c r="N21" t="n">
-        <v>7088.25</v>
+        <v>7127.25</v>
       </c>
       <c r="O21" t="n">
-        <v>7149.25</v>
+        <v>7123.5</v>
       </c>
       <c r="P21" s="6" t="n">
         <v/>
       </c>
-      <c r="Q21" s="6" t="inlineStr">
+      <c r="Q21" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R21" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S21" s="7" t="inlineStr">
+        <is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T21" s="8" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="R21" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="S21" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T21" s="8" t="n">
-        <v/>
-      </c>
       <c r="U21" s="8" t="n">
         <v/>
       </c>
@@ -2287,75 +2285,81 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X21" t="inlineStr"/>
+      <c r="X21" t="inlineStr">
+        <is>
+          <t>強警訊</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2026-01-26</t>
+          <t>2026-02-02</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>6904</v>
+        <v>6938.5</v>
       </c>
       <c r="C22" t="n">
-        <v>7043</v>
+        <v>7027.25</v>
       </c>
       <c r="D22" t="n">
-        <v>6879</v>
+        <v>6751.5</v>
       </c>
       <c r="E22" t="n">
-        <v>6965.75</v>
+        <v>6952.75</v>
       </c>
       <c r="F22" t="n">
-        <v>20</v>
+        <v>-13</v>
       </c>
       <c r="G22" s="5" t="n">
-        <v>0.0029</v>
+        <v>-0.0019</v>
       </c>
       <c r="H22" t="n">
-        <v>164</v>
+        <v>275.75</v>
       </c>
       <c r="I22" t="n">
-        <v>6660</v>
+        <v>6715</v>
       </c>
       <c r="J22" t="n">
-        <v>6818.25</v>
+        <v>6804.12</v>
       </c>
       <c r="K22" t="n">
-        <v>6868.5</v>
+        <v>6883.75</v>
       </c>
       <c r="L22" t="n">
-        <v>6918.75</v>
+        <v>6963.38</v>
       </c>
       <c r="M22" t="n">
-        <v>7023</v>
+        <v>7047.75</v>
       </c>
       <c r="N22" t="n">
-        <v>7127.25</v>
+        <v>7132.12</v>
       </c>
       <c r="O22" t="n">
-        <v>7123.5</v>
+        <v>7207</v>
       </c>
       <c r="P22" s="6" t="n">
         <v/>
       </c>
-      <c r="Q22" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R22" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S22" s="7" t="inlineStr">
-        <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T22" s="8" t="inlineStr">
+      <c r="Q22" s="6" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
+      <c r="R22" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S22" s="10" t="inlineStr">
+        <is>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T22" s="8" t="n">
+        <v/>
+      </c>
       <c r="U22" s="8" t="n">
         <v/>
       </c>
@@ -2367,76 +2371,70 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X22" t="inlineStr">
-        <is>
-          <t>強警訊</t>
-        </is>
-      </c>
+      <c r="X22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-02-02</t>
+          <t>2026-02-09</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>6938.5</v>
+        <v>6960.25</v>
       </c>
       <c r="C23" t="n">
-        <v>7027.25</v>
+        <v>7011.5</v>
       </c>
       <c r="D23" t="n">
-        <v>6751.5</v>
+        <v>6808.75</v>
       </c>
       <c r="E23" t="n">
-        <v>6952.75</v>
+        <v>6850.5</v>
       </c>
       <c r="F23" t="n">
-        <v>-13</v>
+        <v>-102.25</v>
       </c>
       <c r="G23" s="5" t="n">
-        <v>-0.0019</v>
+        <v>-0.0147</v>
       </c>
       <c r="H23" t="n">
-        <v>275.75</v>
+        <v>202.75</v>
       </c>
       <c r="I23" t="n">
-        <v>6715</v>
+        <v>6475.75</v>
       </c>
       <c r="J23" t="n">
-        <v>6804.12</v>
+        <v>6708.69</v>
       </c>
       <c r="K23" t="n">
-        <v>6883.75</v>
+        <v>6814.88</v>
       </c>
       <c r="L23" t="n">
-        <v>6963.38</v>
+        <v>6921.06</v>
       </c>
       <c r="M23" t="n">
-        <v>7047.75</v>
+        <v>7090.62</v>
       </c>
       <c r="N23" t="n">
-        <v>7132.12</v>
+        <v>7260.19</v>
       </c>
       <c r="O23" t="n">
-        <v>7207</v>
+        <v>7303</v>
       </c>
       <c r="P23" s="6" t="n">
         <v/>
       </c>
-      <c r="Q23" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="Q23" s="6" t="n">
+        <v/>
       </c>
       <c r="R23" s="6" t="inlineStr">
         <is>
-          <t>✓</t>
+          <t>△C</t>
         </is>
       </c>
       <c r="S23" s="10" t="inlineStr">
         <is>
-          <t>↓C</t>
+          <t>↓</t>
         </is>
       </c>
       <c r="T23" s="8" t="n">
@@ -2453,55 +2451,59 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X23" t="inlineStr"/>
+      <c r="X23" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2026-02-09</t>
+          <t>2026-02-16</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>6960.25</v>
+        <v>6852.5</v>
       </c>
       <c r="C24" t="n">
-        <v>7011.5</v>
+        <v>6931.5</v>
       </c>
       <c r="D24" t="n">
-        <v>6808.75</v>
+        <v>6791</v>
       </c>
       <c r="E24" t="n">
-        <v>6850.5</v>
+        <v>6923.25</v>
       </c>
       <c r="F24" t="n">
-        <v>-102.25</v>
+        <v>72.75</v>
       </c>
       <c r="G24" s="5" t="n">
-        <v>-0.0147</v>
+        <v>0.0106</v>
       </c>
       <c r="H24" t="n">
-        <v>202.75</v>
+        <v>140.5</v>
       </c>
       <c r="I24" t="n">
-        <v>6475.75</v>
+        <v>6606</v>
       </c>
       <c r="J24" t="n">
-        <v>6708.69</v>
+        <v>6617.94</v>
       </c>
       <c r="K24" t="n">
-        <v>6814.88</v>
+        <v>6749.12</v>
       </c>
       <c r="L24" t="n">
-        <v>6921.06</v>
+        <v>6880.31</v>
       </c>
       <c r="M24" t="n">
-        <v>7090.62</v>
+        <v>6951.88</v>
       </c>
       <c r="N24" t="n">
-        <v>7260.19</v>
+        <v>7023.44</v>
       </c>
       <c r="O24" t="n">
-        <v>7303</v>
+        <v>7214.25</v>
       </c>
       <c r="P24" s="6" t="n">
         <v/>
@@ -2509,18 +2511,18 @@
       <c r="Q24" s="6" t="n">
         <v/>
       </c>
-      <c r="R24" s="6" t="inlineStr">
+      <c r="R24" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S24" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T24" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
-      </c>
-      <c r="S24" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T24" s="8" t="n">
-        <v/>
       </c>
       <c r="U24" s="8" t="n">
         <v/>
@@ -2542,50 +2544,50 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-02-16</t>
+          <t>2026-02-23</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>6852.5</v>
+        <v>6918</v>
       </c>
       <c r="C25" t="n">
-        <v>6931.5</v>
+        <v>6983.75</v>
       </c>
       <c r="D25" t="n">
-        <v>6791</v>
+        <v>6828.5</v>
       </c>
       <c r="E25" t="n">
-        <v>6923.25</v>
+        <v>6889</v>
       </c>
       <c r="F25" t="n">
-        <v>72.75</v>
+        <v>-34.25</v>
       </c>
       <c r="G25" s="5" t="n">
-        <v>0.0106</v>
+        <v>-0.0049</v>
       </c>
       <c r="H25" t="n">
-        <v>140.5</v>
+        <v>155.25</v>
       </c>
       <c r="I25" t="n">
-        <v>6606</v>
+        <v>6650.5</v>
       </c>
       <c r="J25" t="n">
-        <v>6617.94</v>
+        <v>6813.75</v>
       </c>
       <c r="K25" t="n">
-        <v>6749.12</v>
+        <v>6853</v>
       </c>
       <c r="L25" t="n">
-        <v>6880.31</v>
+        <v>6892.25</v>
       </c>
       <c r="M25" t="n">
-        <v>6951.88</v>
+        <v>6993.5</v>
       </c>
       <c r="N25" t="n">
-        <v>7023.44</v>
+        <v>7094.75</v>
       </c>
       <c r="O25" t="n">
-        <v>7214.25</v>
+        <v>7072</v>
       </c>
       <c r="P25" s="6" t="n">
         <v/>
@@ -2593,18 +2595,18 @@
       <c r="Q25" s="6" t="n">
         <v/>
       </c>
-      <c r="R25" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S25" s="7" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T25" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+      <c r="R25" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S25" s="10" t="inlineStr">
+        <is>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T25" s="8" t="n">
+        <v/>
       </c>
       <c r="U25" s="8" t="n">
         <v/>
@@ -2619,63 +2621,65 @@
       </c>
       <c r="X25" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2026-02-23</t>
+          <t>2026-03-02</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>6918</v>
+        <v>6820</v>
       </c>
       <c r="C26" t="n">
-        <v>6983.75</v>
+        <v>6911.25</v>
       </c>
       <c r="D26" t="n">
-        <v>6828.5</v>
+        <v>6715.75</v>
       </c>
       <c r="E26" t="n">
-        <v>6889</v>
+        <v>6743.75</v>
       </c>
       <c r="F26" t="n">
-        <v>-34.25</v>
+        <v>-145.25</v>
       </c>
       <c r="G26" s="5" t="n">
-        <v>-0.0049</v>
+        <v>-0.0211</v>
       </c>
       <c r="H26" t="n">
-        <v>155.25</v>
+        <v>195.5</v>
       </c>
       <c r="I26" t="n">
-        <v>6650.5</v>
+        <v>6673.25</v>
       </c>
       <c r="J26" t="n">
-        <v>6813.75</v>
+        <v>6725.19</v>
       </c>
       <c r="K26" t="n">
-        <v>6853</v>
+        <v>6811.38</v>
       </c>
       <c r="L26" t="n">
-        <v>6892.25</v>
+        <v>6897.56</v>
       </c>
       <c r="M26" t="n">
-        <v>6993.5</v>
+        <v>6966.62</v>
       </c>
       <c r="N26" t="n">
-        <v>7094.75</v>
+        <v>7035.69</v>
       </c>
       <c r="O26" t="n">
-        <v>7072</v>
+        <v>7139</v>
       </c>
       <c r="P26" s="6" t="n">
         <v/>
       </c>
-      <c r="Q26" s="6" t="n">
-        <v/>
+      <c r="Q26" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="R26" s="6" t="inlineStr">
         <is>
@@ -2684,7 +2688,7 @@
       </c>
       <c r="S26" s="10" t="inlineStr">
         <is>
-          <t>↓C</t>
+          <t>↓</t>
         </is>
       </c>
       <c r="T26" s="8" t="n">
@@ -2701,80 +2705,76 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X26" t="inlineStr">
-        <is>
-          <t>中警訊</t>
-        </is>
-      </c>
+      <c r="X26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-09</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>6820</v>
+        <v>6685.5</v>
       </c>
       <c r="C27" t="n">
-        <v>6911.25</v>
+        <v>6852</v>
       </c>
       <c r="D27" t="n">
-        <v>6715.75</v>
+        <v>6584.5</v>
       </c>
       <c r="E27" t="n">
-        <v>6743.75</v>
+        <v>6636</v>
       </c>
       <c r="F27" t="n">
-        <v>-145.25</v>
+        <v>-107.75</v>
       </c>
       <c r="G27" s="5" t="n">
-        <v>-0.0211</v>
+        <v>-0.016</v>
       </c>
       <c r="H27" t="n">
-        <v>195.5</v>
+        <v>267.5</v>
       </c>
       <c r="I27" t="n">
-        <v>6673.25</v>
+        <v>6520.25</v>
       </c>
       <c r="J27" t="n">
-        <v>6725.19</v>
+        <v>6513.38</v>
       </c>
       <c r="K27" t="n">
-        <v>6811.38</v>
+        <v>6646</v>
       </c>
       <c r="L27" t="n">
-        <v>6897.56</v>
+        <v>6778.62</v>
       </c>
       <c r="M27" t="n">
-        <v>6966.62</v>
+        <v>6841.5</v>
       </c>
       <c r="N27" t="n">
-        <v>7035.69</v>
+        <v>6904.38</v>
       </c>
       <c r="O27" t="n">
-        <v>7139</v>
+        <v>7106.75</v>
       </c>
       <c r="P27" s="6" t="n">
         <v/>
       </c>
-      <c r="Q27" s="6" t="inlineStr">
+      <c r="Q27" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R27" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="R27" s="6" t="inlineStr">
+      <c r="S27" s="10" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T27" s="8" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
-      </c>
-      <c r="S27" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T27" s="8" t="n">
-        <v/>
       </c>
       <c r="U27" s="8" t="n">
         <v/>
@@ -2792,50 +2792,50 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-03-16</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>6685.5</v>
+        <v>6608.5</v>
       </c>
       <c r="C28" t="n">
-        <v>6852</v>
+        <v>6762.25</v>
       </c>
       <c r="D28" t="n">
-        <v>6584.5</v>
+        <v>6558</v>
       </c>
       <c r="E28" t="n">
-        <v>6636</v>
+        <v>6594.63</v>
       </c>
       <c r="F28" t="n">
-        <v>-107.75</v>
+        <v>-41.37</v>
       </c>
       <c r="G28" s="5" t="n">
-        <v>-0.016</v>
+        <v>-0.0062</v>
       </c>
       <c r="H28" t="n">
-        <v>267.5</v>
+        <v>204.25</v>
       </c>
       <c r="I28" t="n">
-        <v>6520.25</v>
+        <v>6317</v>
       </c>
       <c r="J28" t="n">
-        <v>6513.38</v>
+        <v>6327.38</v>
       </c>
       <c r="K28" t="n">
-        <v>6646</v>
+        <v>6502.25</v>
       </c>
       <c r="L28" t="n">
-        <v>6778.62</v>
+        <v>6677.12</v>
       </c>
       <c r="M28" t="n">
-        <v>6841.5</v>
+        <v>6769.75</v>
       </c>
       <c r="N28" t="n">
-        <v>6904.38</v>
+        <v>6862.38</v>
       </c>
       <c r="O28" t="n">
-        <v>7106.75</v>
+        <v>7119.5</v>
       </c>
       <c r="P28" s="6" t="n">
         <v/>
@@ -2843,20 +2843,16 @@
       <c r="Q28" s="6" t="n">
         <v/>
       </c>
-      <c r="R28" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+      <c r="R28" s="6" t="n">
+        <v/>
       </c>
       <c r="S28" s="10" t="inlineStr">
         <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T28" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T28" s="8" t="n">
+        <v/>
       </c>
       <c r="U28" s="8" t="n">
         <v/>
@@ -2874,67 +2870,73 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-23</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>6608.5</v>
+        <v>6510</v>
       </c>
       <c r="C29" t="n">
-        <v>6762.25</v>
+        <v>6748</v>
       </c>
       <c r="D29" t="n">
-        <v>6558</v>
+        <v>6389</v>
       </c>
       <c r="E29" t="n">
-        <v>6594.63</v>
+        <v>6412.25</v>
       </c>
       <c r="F29" t="n">
-        <v>-41.37</v>
+        <v>-182.38</v>
       </c>
       <c r="G29" s="5" t="n">
-        <v>-0.0062</v>
+        <v>-0.0277</v>
       </c>
       <c r="H29" t="n">
-        <v>204.25</v>
+        <v>359</v>
       </c>
       <c r="I29" t="n">
-        <v>6317</v>
+        <v>6353.75</v>
       </c>
       <c r="J29" t="n">
-        <v>6327.38</v>
+        <v>6357.63</v>
       </c>
       <c r="K29" t="n">
-        <v>6502.25</v>
+        <v>6492.5</v>
       </c>
       <c r="L29" t="n">
-        <v>6677.12</v>
+        <v>6627.38</v>
       </c>
       <c r="M29" t="n">
-        <v>6769.75</v>
+        <v>6696.75</v>
       </c>
       <c r="N29" t="n">
-        <v>6862.38</v>
+        <v>6766.13</v>
       </c>
       <c r="O29" t="n">
-        <v>7119.5</v>
+        <v>6966.5</v>
       </c>
       <c r="P29" s="6" t="n">
         <v/>
       </c>
-      <c r="Q29" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R29" s="6" t="n">
-        <v/>
+      <c r="Q29" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="R29" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S29" s="10" t="inlineStr">
         <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T29" s="8" t="n">
-        <v/>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T29" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="U29" s="8" t="n">
         <v/>
@@ -2952,74 +2954,70 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2026-03-23</t>
+          <t>2026-03-30</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>6510</v>
+        <v>6380</v>
       </c>
       <c r="C30" t="n">
-        <v>6748</v>
+        <v>6653.75</v>
       </c>
       <c r="D30" t="n">
-        <v>6389</v>
+        <v>6353.25</v>
       </c>
       <c r="E30" t="n">
-        <v>6412.25</v>
+        <v>6603.75</v>
       </c>
       <c r="F30" t="n">
-        <v>-182.38</v>
+        <v>191.5</v>
       </c>
       <c r="G30" s="5" t="n">
-        <v>-0.0277</v>
+        <v>0.0299</v>
       </c>
       <c r="H30" t="n">
-        <v>359</v>
+        <v>300.5</v>
       </c>
       <c r="I30" t="n">
-        <v>6353.75</v>
+        <v>6030</v>
       </c>
       <c r="J30" t="n">
-        <v>6357.63</v>
+        <v>5975.12</v>
       </c>
       <c r="K30" t="n">
-        <v>6492.5</v>
+        <v>6232.75</v>
       </c>
       <c r="L30" t="n">
-        <v>6627.38</v>
+        <v>6490.38</v>
       </c>
       <c r="M30" t="n">
-        <v>6696.75</v>
+        <v>6591.75</v>
       </c>
       <c r="N30" t="n">
-        <v>6766.13</v>
+        <v>6693.12</v>
       </c>
       <c r="O30" t="n">
-        <v>6966.5</v>
+        <v>7107</v>
       </c>
       <c r="P30" s="6" t="n">
         <v/>
       </c>
-      <c r="Q30" s="6" t="inlineStr">
+      <c r="Q30" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R30" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S30" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T30" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="R30" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S30" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T30" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
       <c r="U30" s="8" t="n">
         <v/>
       </c>
@@ -3031,55 +3029,59 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X30" t="inlineStr"/>
+      <c r="X30" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-04-06</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>6380</v>
+        <v>6590</v>
       </c>
       <c r="C31" t="n">
-        <v>6653.75</v>
+        <v>6888</v>
       </c>
       <c r="D31" t="n">
-        <v>6353.25</v>
+        <v>6567</v>
       </c>
       <c r="E31" t="n">
-        <v>6603.75</v>
+        <v>6855.25</v>
       </c>
       <c r="F31" t="n">
-        <v>191.5</v>
+        <v>251.5</v>
       </c>
       <c r="G31" s="5" t="n">
-        <v>0.0299</v>
+        <v>0.0381</v>
       </c>
       <c r="H31" t="n">
-        <v>300.5</v>
+        <v>321</v>
       </c>
       <c r="I31" t="n">
-        <v>6030</v>
+        <v>6052.75</v>
       </c>
       <c r="J31" t="n">
-        <v>5975.12</v>
+        <v>6353.38</v>
       </c>
       <c r="K31" t="n">
-        <v>6232.75</v>
+        <v>6453.5</v>
       </c>
       <c r="L31" t="n">
-        <v>6490.38</v>
+        <v>6553.62</v>
       </c>
       <c r="M31" t="n">
-        <v>6591.75</v>
+        <v>6754</v>
       </c>
       <c r="N31" t="n">
-        <v>6693.12</v>
+        <v>6954.38</v>
       </c>
       <c r="O31" t="n">
-        <v>7107</v>
+        <v>6954.25</v>
       </c>
       <c r="P31" s="6" t="n">
         <v/>
@@ -3097,15 +3099,17 @@
       </c>
       <c r="T31" s="8" t="inlineStr">
         <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U31" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V31" s="8" t="inlineStr">
+        <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="U31" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V31" s="8" t="n">
-        <v/>
-      </c>
       <c r="W31" s="11" t="inlineStr">
         <is>
           <t>空方</t>
@@ -3113,57 +3117,57 @@
       </c>
       <c r="X31" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2026-04-06</t>
+          <t>2026-04-13</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>6590</v>
+        <v>6780</v>
       </c>
       <c r="C32" t="n">
-        <v>6888</v>
+        <v>7185.75</v>
       </c>
       <c r="D32" t="n">
-        <v>6567</v>
+        <v>6767</v>
       </c>
       <c r="E32" t="n">
-        <v>6855.25</v>
+        <v>7161.5</v>
       </c>
       <c r="F32" t="n">
-        <v>251.5</v>
+        <v>306.25</v>
       </c>
       <c r="G32" s="5" t="n">
-        <v>0.0381</v>
+        <v>0.0447</v>
       </c>
       <c r="H32" t="n">
-        <v>321</v>
+        <v>418.75</v>
       </c>
       <c r="I32" t="n">
-        <v>6052.75</v>
+        <v>6246</v>
       </c>
       <c r="J32" t="n">
-        <v>6353.38</v>
+        <v>6598.12</v>
       </c>
       <c r="K32" t="n">
-        <v>6453.5</v>
+        <v>6694.75</v>
       </c>
       <c r="L32" t="n">
-        <v>6553.62</v>
+        <v>6791.38</v>
       </c>
       <c r="M32" t="n">
-        <v>6754</v>
+        <v>7015.75</v>
       </c>
       <c r="N32" t="n">
-        <v>6954.38</v>
+        <v>7240.12</v>
       </c>
       <c r="O32" t="n">
-        <v>6954.25</v>
+        <v>7209</v>
       </c>
       <c r="P32" s="6" t="n">
         <v/>
@@ -3206,50 +3210,50 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2026-04-13</t>
+          <t>2026-04-20</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>6780</v>
+        <v>7102.5</v>
       </c>
       <c r="C33" t="n">
-        <v>7185.75</v>
+        <v>7200.5</v>
       </c>
       <c r="D33" t="n">
-        <v>6767</v>
+        <v>7079.25</v>
       </c>
       <c r="E33" t="n">
-        <v>7161.5</v>
+        <v>7194.75</v>
       </c>
       <c r="F33" t="n">
-        <v>306.25</v>
+        <v>33.25</v>
       </c>
       <c r="G33" s="5" t="n">
-        <v>0.0447</v>
+        <v>0.0046</v>
       </c>
       <c r="H33" t="n">
-        <v>418.75</v>
+        <v>121.25</v>
       </c>
       <c r="I33" t="n">
-        <v>6246</v>
+        <v>6348.25</v>
       </c>
       <c r="J33" t="n">
-        <v>6598.12</v>
+        <v>6835.31</v>
       </c>
       <c r="K33" t="n">
-        <v>6694.75</v>
+        <v>6952.12</v>
       </c>
       <c r="L33" t="n">
-        <v>6791.38</v>
+        <v>7068.94</v>
       </c>
       <c r="M33" t="n">
-        <v>7015.75</v>
+        <v>7370.88</v>
       </c>
       <c r="N33" t="n">
-        <v>7240.12</v>
+        <v>7672.81</v>
       </c>
       <c r="O33" t="n">
-        <v>7209</v>
+        <v>7604.5</v>
       </c>
       <c r="P33" s="6" t="n">
         <v/>
@@ -3262,21 +3266,17 @@
       </c>
       <c r="S33" s="7" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T33" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T33" s="8" t="n">
+        <v/>
       </c>
       <c r="U33" s="8" t="n">
         <v/>
       </c>
-      <c r="V33" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+      <c r="V33" s="8" t="n">
+        <v/>
       </c>
       <c r="W33" s="11" t="inlineStr">
         <is>
@@ -3292,50 +3292,50 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
+          <t>2026-04-27</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>7102.5</v>
+        <v>7185</v>
       </c>
       <c r="C34" t="n">
-        <v>7200.5</v>
+        <v>7300.75</v>
       </c>
       <c r="D34" t="n">
-        <v>7079.25</v>
+        <v>7131.25</v>
       </c>
       <c r="E34" t="n">
-        <v>7194.75</v>
+        <v>7258</v>
       </c>
       <c r="F34" t="n">
-        <v>33.25</v>
+        <v>63.25</v>
       </c>
       <c r="G34" s="5" t="n">
-        <v>0.0046</v>
+        <v>0.008800000000000001</v>
       </c>
       <c r="H34" t="n">
-        <v>121.25</v>
+        <v>169.5</v>
       </c>
       <c r="I34" t="n">
-        <v>6348.25</v>
+        <v>6958</v>
       </c>
       <c r="J34" t="n">
-        <v>6835.31</v>
+        <v>7100.94</v>
       </c>
       <c r="K34" t="n">
-        <v>6952.12</v>
+        <v>7134.12</v>
       </c>
       <c r="L34" t="n">
-        <v>7068.94</v>
+        <v>7167.31</v>
       </c>
       <c r="M34" t="n">
-        <v>7370.88</v>
+        <v>7255.38</v>
       </c>
       <c r="N34" t="n">
-        <v>7672.81</v>
+        <v>7343.44</v>
       </c>
       <c r="O34" t="n">
-        <v>7604.5</v>
+        <v>7321.75</v>
       </c>
       <c r="P34" s="6" t="n">
         <v/>
@@ -3343,16 +3343,20 @@
       <c r="Q34" s="6" t="n">
         <v/>
       </c>
-      <c r="R34" s="6" t="n">
-        <v/>
+      <c r="R34" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S34" s="7" t="inlineStr">
         <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T34" s="8" t="n">
-        <v/>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T34" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="U34" s="8" t="n">
         <v/>
@@ -3374,50 +3378,50 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-05-04</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>7185</v>
+        <v>7276.25</v>
       </c>
       <c r="C35" t="n">
-        <v>7300.75</v>
+        <v>7427.75</v>
       </c>
       <c r="D35" t="n">
-        <v>7131.25</v>
+        <v>7199.5</v>
       </c>
       <c r="E35" t="n">
-        <v>7258</v>
+        <v>7419</v>
       </c>
       <c r="F35" t="n">
-        <v>63.25</v>
+        <v>161</v>
       </c>
       <c r="G35" s="5" t="n">
-        <v>0.008800000000000001</v>
+        <v>0.0222</v>
       </c>
       <c r="H35" t="n">
-        <v>169.5</v>
+        <v>228.25</v>
       </c>
       <c r="I35" t="n">
-        <v>6958</v>
+        <v>6961.75</v>
       </c>
       <c r="J35" t="n">
-        <v>7100.94</v>
+        <v>7109.5</v>
       </c>
       <c r="K35" t="n">
-        <v>7134.12</v>
+        <v>7173.25</v>
       </c>
       <c r="L35" t="n">
-        <v>7167.31</v>
+        <v>7237</v>
       </c>
       <c r="M35" t="n">
-        <v>7255.38</v>
+        <v>7342.75</v>
       </c>
       <c r="N35" t="n">
-        <v>7343.44</v>
+        <v>7448.5</v>
       </c>
       <c r="O35" t="n">
-        <v>7321.75</v>
+        <v>7470.25</v>
       </c>
       <c r="P35" s="6" t="n">
         <v/>
@@ -3425,23 +3429,23 @@
       <c r="Q35" s="6" t="n">
         <v/>
       </c>
-      <c r="R35" s="6" t="inlineStr">
+      <c r="R35" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S35" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T35" s="8" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="S35" s="7" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T35" s="8" t="inlineStr">
+      <c r="U35" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
-      </c>
-      <c r="U35" s="8" t="n">
-        <v/>
       </c>
       <c r="V35" s="8" t="n">
         <v/>
@@ -3460,50 +3464,50 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2026-05-04</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>7276.25</v>
+        <v>7403.5</v>
       </c>
       <c r="C36" t="n">
-        <v>7427.75</v>
+        <v>7540</v>
       </c>
       <c r="D36" t="n">
-        <v>7199.5</v>
+        <v>7363.25</v>
       </c>
       <c r="E36" t="n">
-        <v>7419</v>
+        <v>7432.25</v>
       </c>
       <c r="F36" t="n">
-        <v>161</v>
+        <v>13.25</v>
       </c>
       <c r="G36" s="5" t="n">
-        <v>0.0222</v>
+        <v>0.0018</v>
       </c>
       <c r="H36" t="n">
-        <v>228.25</v>
+        <v>176.75</v>
       </c>
       <c r="I36" t="n">
-        <v>6961.75</v>
+        <v>6971.25</v>
       </c>
       <c r="J36" t="n">
-        <v>7109.5</v>
+        <v>7243.44</v>
       </c>
       <c r="K36" t="n">
-        <v>7173.25</v>
+        <v>7304.88</v>
       </c>
       <c r="L36" t="n">
-        <v>7237</v>
+        <v>7366.31</v>
       </c>
       <c r="M36" t="n">
-        <v>7342.75</v>
+        <v>7533.12</v>
       </c>
       <c r="N36" t="n">
-        <v>7448.5</v>
+        <v>7699.94</v>
       </c>
       <c r="O36" t="n">
-        <v>7470.25</v>
+        <v>7656</v>
       </c>
       <c r="P36" s="6" t="n">
         <v/>
@@ -3516,7 +3520,7 @@
       </c>
       <c r="S36" s="7" t="inlineStr">
         <is>
-          <t>↑</t>
+          <t>↑C</t>
         </is>
       </c>
       <c r="T36" s="8" t="inlineStr">
@@ -3524,10 +3528,8 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="U36" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+      <c r="U36" s="8" t="n">
+        <v/>
       </c>
       <c r="V36" s="8" t="n">
         <v/>
@@ -3546,50 +3548,50 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-05-18</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>7403.5</v>
+        <v>7410</v>
       </c>
       <c r="C37" t="n">
-        <v>7540</v>
+        <v>7524</v>
       </c>
       <c r="D37" t="n">
-        <v>7363.25</v>
+        <v>7354.25</v>
       </c>
       <c r="E37" t="n">
-        <v>7432.25</v>
+        <v>7491</v>
       </c>
       <c r="F37" t="n">
-        <v>13.25</v>
+        <v>58.75</v>
       </c>
       <c r="G37" s="5" t="n">
-        <v>0.0018</v>
+        <v>0.007900000000000001</v>
       </c>
       <c r="H37" t="n">
-        <v>176.75</v>
+        <v>169.75</v>
       </c>
       <c r="I37" t="n">
-        <v>6971.25</v>
+        <v>7186.5</v>
       </c>
       <c r="J37" t="n">
-        <v>7243.44</v>
+        <v>7245.81</v>
       </c>
       <c r="K37" t="n">
-        <v>7304.88</v>
+        <v>7343.88</v>
       </c>
       <c r="L37" t="n">
-        <v>7366.31</v>
+        <v>7441.94</v>
       </c>
       <c r="M37" t="n">
-        <v>7533.12</v>
+        <v>7520.62</v>
       </c>
       <c r="N37" t="n">
-        <v>7699.94</v>
+        <v>7599.31</v>
       </c>
       <c r="O37" t="n">
-        <v>7656</v>
+        <v>7716.75</v>
       </c>
       <c r="P37" s="6" t="n">
         <v/>
@@ -3602,12 +3604,12 @@
       </c>
       <c r="S37" s="7" t="inlineStr">
         <is>
-          <t>↑C</t>
+          <t>↑</t>
         </is>
       </c>
       <c r="T37" s="8" t="inlineStr">
         <is>
-          <t>✓</t>
+          <t>△C</t>
         </is>
       </c>
       <c r="U37" s="8" t="n">
@@ -3623,57 +3625,57 @@
       </c>
       <c r="X37" t="inlineStr">
         <is>
-          <t>強警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-05-25</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>7410</v>
+        <v>7519</v>
       </c>
       <c r="C38" t="n">
-        <v>7524</v>
+        <v>7611.5</v>
       </c>
       <c r="D38" t="n">
-        <v>7354.25</v>
+        <v>7505.75</v>
       </c>
       <c r="E38" t="n">
-        <v>7491</v>
+        <v>7595.75</v>
       </c>
       <c r="F38" t="n">
-        <v>58.75</v>
+        <v>104.75</v>
       </c>
       <c r="G38" s="5" t="n">
-        <v>0.007900000000000001</v>
+        <v>0.014</v>
       </c>
       <c r="H38" t="n">
-        <v>169.75</v>
+        <v>105.75</v>
       </c>
       <c r="I38" t="n">
-        <v>7186.5</v>
+        <v>7184.5</v>
       </c>
       <c r="J38" t="n">
-        <v>7245.81</v>
+        <v>7347.19</v>
       </c>
       <c r="K38" t="n">
-        <v>7343.88</v>
+        <v>7406.12</v>
       </c>
       <c r="L38" t="n">
-        <v>7441.94</v>
+        <v>7465.06</v>
       </c>
       <c r="M38" t="n">
-        <v>7520.62</v>
+        <v>7575.88</v>
       </c>
       <c r="N38" t="n">
-        <v>7599.31</v>
+        <v>7686.69</v>
       </c>
       <c r="O38" t="n">
-        <v>7716.75</v>
+        <v>7693.75</v>
       </c>
       <c r="P38" s="6" t="n">
         <v/>
@@ -3707,77 +3709,81 @@
       </c>
       <c r="X38" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2026-05-25</t>
+          <t>2026-06-01</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>7519</v>
+        <v>7595</v>
       </c>
       <c r="C39" t="n">
-        <v>7611.5</v>
+        <v>7632.25</v>
       </c>
       <c r="D39" t="n">
-        <v>7505.75</v>
+        <v>7359</v>
       </c>
       <c r="E39" t="n">
-        <v>7595.75</v>
+        <v>7400.5</v>
       </c>
       <c r="F39" t="n">
-        <v>104.75</v>
+        <v>-195.25</v>
       </c>
       <c r="G39" s="5" t="n">
-        <v>0.014</v>
+        <v>-0.0257</v>
       </c>
       <c r="H39" t="n">
-        <v>105.75</v>
+        <v>273.25</v>
       </c>
       <c r="I39" t="n">
-        <v>7184.5</v>
+        <v>7400</v>
       </c>
       <c r="J39" t="n">
-        <v>7347.19</v>
+        <v>7508.56</v>
       </c>
       <c r="K39" t="n">
-        <v>7406.12</v>
+        <v>7542.88</v>
       </c>
       <c r="L39" t="n">
-        <v>7465.06</v>
+        <v>7577.19</v>
       </c>
       <c r="M39" t="n">
-        <v>7575.88</v>
+        <v>7648.62</v>
       </c>
       <c r="N39" t="n">
-        <v>7686.69</v>
+        <v>7720.06</v>
       </c>
       <c r="O39" t="n">
-        <v>7693.75</v>
-      </c>
-      <c r="P39" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q39" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R39" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S39" s="7" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T39" s="8" t="inlineStr">
+        <v>7717.25</v>
+      </c>
+      <c r="P39" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
+      <c r="Q39" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="R39" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S39" s="10" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T39" s="8" t="n">
+        <v/>
+      </c>
       <c r="U39" s="8" t="n">
         <v/>
       </c>
@@ -3791,76 +3797,72 @@
       </c>
       <c r="X39" t="inlineStr">
         <is>
-          <t>強警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-06-08</t>
         </is>
       </c>
       <c r="B40" t="n">
-        <v>7595</v>
+        <v>7368</v>
       </c>
       <c r="C40" t="n">
-        <v>7632.25</v>
+        <v>7491</v>
       </c>
       <c r="D40" t="n">
-        <v>7359</v>
+        <v>7232.25</v>
       </c>
       <c r="E40" t="n">
-        <v>7400.5</v>
+        <v>7435</v>
       </c>
       <c r="F40" t="n">
-        <v>-195.25</v>
+        <v>34.5</v>
       </c>
       <c r="G40" s="5" t="n">
-        <v>-0.0257</v>
+        <v>0.0047</v>
       </c>
       <c r="H40" t="n">
-        <v>273.25</v>
+        <v>258.75</v>
       </c>
       <c r="I40" t="n">
-        <v>7400</v>
+        <v>7085.75</v>
       </c>
       <c r="J40" t="n">
-        <v>7508.56</v>
+        <v>7079.69</v>
       </c>
       <c r="K40" t="n">
-        <v>7542.88</v>
+        <v>7263.88</v>
       </c>
       <c r="L40" t="n">
-        <v>7577.19</v>
+        <v>7448.06</v>
       </c>
       <c r="M40" t="n">
-        <v>7648.62</v>
+        <v>7537.12</v>
       </c>
       <c r="N40" t="n">
-        <v>7720.06</v>
+        <v>7626.19</v>
       </c>
       <c r="O40" t="n">
-        <v>7717.25</v>
-      </c>
-      <c r="P40" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="Q40" s="6" t="inlineStr">
+        <v>7905.5</v>
+      </c>
+      <c r="P40" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q40" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R40" s="6" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="R40" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
       <c r="S40" s="10" t="inlineStr">
         <is>
-          <t>↓</t>
+          <t>↓C</t>
         </is>
       </c>
       <c r="T40" s="8" t="n">
@@ -3886,50 +3888,50 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="B41" t="n">
-        <v>7368</v>
+        <v>7480</v>
       </c>
       <c r="C41" t="n">
-        <v>7491</v>
+        <v>7584.5</v>
       </c>
       <c r="D41" t="n">
-        <v>7232.25</v>
+        <v>7405</v>
       </c>
       <c r="E41" t="n">
-        <v>7435</v>
+        <v>7556.25</v>
       </c>
       <c r="F41" t="n">
-        <v>34.5</v>
+        <v>121.25</v>
       </c>
       <c r="G41" s="5" t="n">
-        <v>0.0047</v>
+        <v>0.0163</v>
       </c>
       <c r="H41" t="n">
-        <v>258.75</v>
+        <v>179.5</v>
       </c>
       <c r="I41" t="n">
-        <v>7085.75</v>
+        <v>6973.5</v>
       </c>
       <c r="J41" t="n">
-        <v>7079.69</v>
+        <v>7212.94</v>
       </c>
       <c r="K41" t="n">
-        <v>7263.88</v>
+        <v>7305.62</v>
       </c>
       <c r="L41" t="n">
-        <v>7448.06</v>
+        <v>7398.31</v>
       </c>
       <c r="M41" t="n">
-        <v>7537.12</v>
+        <v>7564.38</v>
       </c>
       <c r="N41" t="n">
-        <v>7626.19</v>
+        <v>7730.44</v>
       </c>
       <c r="O41" t="n">
-        <v>7905.5</v>
+        <v>7749.75</v>
       </c>
       <c r="P41" s="6" t="n">
         <v/>
@@ -3937,18 +3939,18 @@
       <c r="Q41" s="6" t="n">
         <v/>
       </c>
-      <c r="R41" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S41" s="10" t="inlineStr">
-        <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T41" s="8" t="n">
-        <v/>
+      <c r="R41" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S41" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T41" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="U41" s="8" t="n">
         <v/>
@@ -3963,77 +3965,79 @@
       </c>
       <c r="X41" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="B42" t="n">
-        <v>7480</v>
+        <v>7543.25</v>
       </c>
       <c r="C42" t="n">
-        <v>7584.5</v>
+        <v>7599.25</v>
       </c>
       <c r="D42" t="n">
-        <v>7405</v>
+        <v>7357.25</v>
       </c>
       <c r="E42" t="n">
-        <v>7556.25</v>
+        <v>7401.75</v>
       </c>
       <c r="F42" t="n">
-        <v>121.25</v>
+        <v>-154.5</v>
       </c>
       <c r="G42" s="5" t="n">
-        <v>0.0163</v>
+        <v>-0.0204</v>
       </c>
       <c r="H42" t="n">
-        <v>179.5</v>
+        <v>242</v>
       </c>
       <c r="I42" t="n">
-        <v>6973.5</v>
+        <v>7225.5</v>
       </c>
       <c r="J42" t="n">
-        <v>7212.94</v>
+        <v>7407.5</v>
       </c>
       <c r="K42" t="n">
-        <v>7305.62</v>
+        <v>7466.5</v>
       </c>
       <c r="L42" t="n">
-        <v>7398.31</v>
+        <v>7525.5</v>
       </c>
       <c r="M42" t="n">
-        <v>7564.38</v>
+        <v>7646</v>
       </c>
       <c r="N42" t="n">
-        <v>7730.44</v>
+        <v>7766.5</v>
       </c>
       <c r="O42" t="n">
-        <v>7749.75</v>
+        <v>7764</v>
       </c>
       <c r="P42" s="6" t="n">
         <v/>
       </c>
-      <c r="Q42" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R42" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S42" s="7" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T42" s="8" t="inlineStr">
+      <c r="Q42" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
+      <c r="R42" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S42" s="10" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T42" s="8" t="n">
+        <v/>
+      </c>
       <c r="U42" s="8" t="n">
         <v/>
       </c>
@@ -4047,79 +4051,77 @@
       </c>
       <c r="X42" t="inlineStr">
         <is>
-          <t>強警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="B43" t="n">
-        <v>7543.25</v>
+        <v>7398</v>
       </c>
       <c r="C43" t="n">
-        <v>7599.25</v>
+        <v>7593.75</v>
       </c>
       <c r="D43" t="n">
-        <v>7357.25</v>
+        <v>7398</v>
       </c>
       <c r="E43" t="n">
-        <v>7401.75</v>
+        <v>7557</v>
       </c>
       <c r="F43" t="n">
-        <v>-154.5</v>
+        <v>155.25</v>
       </c>
       <c r="G43" s="5" t="n">
-        <v>-0.0204</v>
+        <v>0.021</v>
       </c>
       <c r="H43" t="n">
-        <v>242</v>
+        <v>195.75</v>
       </c>
       <c r="I43" t="n">
-        <v>7225.5</v>
+        <v>7115.25</v>
       </c>
       <c r="J43" t="n">
-        <v>7407.5</v>
+        <v>7121.5</v>
       </c>
       <c r="K43" t="n">
-        <v>7466.5</v>
+        <v>7280.75</v>
       </c>
       <c r="L43" t="n">
-        <v>7525.5</v>
+        <v>7440</v>
       </c>
       <c r="M43" t="n">
-        <v>7646</v>
+        <v>7522.75</v>
       </c>
       <c r="N43" t="n">
-        <v>7766.5</v>
+        <v>7605.5</v>
       </c>
       <c r="O43" t="n">
-        <v>7764</v>
+        <v>7841.25</v>
       </c>
       <c r="P43" s="6" t="n">
         <v/>
       </c>
-      <c r="Q43" s="6" t="inlineStr">
+      <c r="Q43" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R43" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S43" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T43" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="R43" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S43" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T43" s="8" t="n">
-        <v/>
-      </c>
       <c r="U43" s="8" t="n">
         <v/>
       </c>
@@ -4133,57 +4135,57 @@
       </c>
       <c r="X43" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="B44" t="n">
-        <v>7398</v>
+        <v>7562.25</v>
       </c>
       <c r="C44" t="n">
-        <v>7593.75</v>
+        <v>7628.75</v>
       </c>
       <c r="D44" t="n">
-        <v>7398</v>
+        <v>7468.5</v>
       </c>
       <c r="E44" t="n">
-        <v>7557</v>
+        <v>7620.25</v>
       </c>
       <c r="F44" t="n">
-        <v>155.25</v>
+        <v>63.25</v>
       </c>
       <c r="G44" s="5" t="n">
-        <v>0.021</v>
+        <v>0.008399999999999999</v>
       </c>
       <c r="H44" t="n">
-        <v>195.75</v>
+        <v>160.25</v>
       </c>
       <c r="I44" t="n">
-        <v>7115.25</v>
+        <v>7202.25</v>
       </c>
       <c r="J44" t="n">
-        <v>7121.5</v>
+        <v>7391.81</v>
       </c>
       <c r="K44" t="n">
-        <v>7280.75</v>
+        <v>7459.12</v>
       </c>
       <c r="L44" t="n">
-        <v>7440</v>
+        <v>7526.44</v>
       </c>
       <c r="M44" t="n">
-        <v>7522.75</v>
+        <v>7654.88</v>
       </c>
       <c r="N44" t="n">
-        <v>7605.5</v>
+        <v>7783.31</v>
       </c>
       <c r="O44" t="n">
-        <v>7841.25</v>
+        <v>7789.5</v>
       </c>
       <c r="P44" s="6" t="n">
         <v/>
@@ -4217,77 +4219,79 @@
       </c>
       <c r="X44" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="B45" t="n">
-        <v>7562.25</v>
+        <v>7607</v>
       </c>
       <c r="C45" t="n">
-        <v>7628.75</v>
+        <v>7632</v>
       </c>
       <c r="D45" t="n">
-        <v>7468.5</v>
+        <v>7473</v>
       </c>
       <c r="E45" t="n">
-        <v>7620.25</v>
+        <v>7497.75</v>
       </c>
       <c r="F45" t="n">
-        <v>63.25</v>
+        <v>-122.5</v>
       </c>
       <c r="G45" s="5" t="n">
-        <v>0.008399999999999999</v>
+        <v>-0.0161</v>
       </c>
       <c r="H45" t="n">
-        <v>160.25</v>
+        <v>159</v>
       </c>
       <c r="I45" t="n">
-        <v>7202.25</v>
+        <v>7308.25</v>
       </c>
       <c r="J45" t="n">
-        <v>7391.81</v>
+        <v>7495.81</v>
       </c>
       <c r="K45" t="n">
-        <v>7459.12</v>
+        <v>7540.12</v>
       </c>
       <c r="L45" t="n">
-        <v>7526.44</v>
+        <v>7584.44</v>
       </c>
       <c r="M45" t="n">
-        <v>7654.88</v>
+        <v>7700.38</v>
       </c>
       <c r="N45" t="n">
-        <v>7783.31</v>
+        <v>7816.31</v>
       </c>
       <c r="O45" t="n">
-        <v>7789.5</v>
+        <v>7789</v>
       </c>
       <c r="P45" s="6" t="n">
         <v/>
       </c>
-      <c r="Q45" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R45" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S45" s="7" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T45" s="8" t="inlineStr">
+      <c r="Q45" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
+      <c r="R45" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S45" s="10" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T45" s="8" t="n">
+        <v/>
+      </c>
       <c r="U45" s="8" t="n">
         <v/>
       </c>
@@ -4301,71 +4305,69 @@
       </c>
       <c r="X45" t="inlineStr">
         <is>
-          <t>強警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="B46" t="n">
-        <v>7607</v>
+        <v>7485</v>
       </c>
       <c r="C46" t="n">
-        <v>7632</v>
+        <v>7563.5</v>
       </c>
       <c r="D46" t="n">
-        <v>7473</v>
+        <v>7411.75</v>
       </c>
       <c r="E46" t="n">
-        <v>7497.75</v>
+        <v>7447.5</v>
       </c>
       <c r="F46" t="n">
-        <v>-122.5</v>
+        <v>-50.25</v>
       </c>
       <c r="G46" s="5" t="n">
-        <v>-0.0161</v>
+        <v>-0.0067</v>
       </c>
       <c r="H46" t="n">
-        <v>159</v>
+        <v>151.75</v>
       </c>
       <c r="I46" t="n">
-        <v>7308.25</v>
+        <v>7314</v>
       </c>
       <c r="J46" t="n">
-        <v>7495.81</v>
+        <v>7311.38</v>
       </c>
       <c r="K46" t="n">
-        <v>7540.12</v>
+        <v>7418.25</v>
       </c>
       <c r="L46" t="n">
-        <v>7584.44</v>
+        <v>7525.12</v>
       </c>
       <c r="M46" t="n">
-        <v>7700.38</v>
+        <v>7577.25</v>
       </c>
       <c r="N46" t="n">
-        <v>7816.31</v>
+        <v>7629.38</v>
       </c>
       <c r="O46" t="n">
-        <v>7789</v>
+        <v>7791</v>
       </c>
       <c r="P46" s="6" t="n">
         <v/>
       </c>
-      <c r="Q46" s="6" t="inlineStr">
+      <c r="Q46" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R46" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="R46" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
       <c r="S46" s="10" t="inlineStr">
         <is>
           <t>↓</t>
@@ -4385,59 +4387,55 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X46" t="inlineStr">
-        <is>
-          <t>中警訊</t>
-        </is>
-      </c>
+      <c r="X46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="B47" t="n">
-        <v>7485</v>
+        <v>7490</v>
       </c>
       <c r="C47" t="n">
-        <v>7563.5</v>
+        <v>7541</v>
       </c>
       <c r="D47" t="n">
-        <v>7411.75</v>
+        <v>7324</v>
       </c>
       <c r="E47" t="n">
-        <v>7447.5</v>
+        <v>7519.25</v>
       </c>
       <c r="F47" t="n">
-        <v>-50.25</v>
+        <v>71.75</v>
       </c>
       <c r="G47" s="5" t="n">
-        <v>-0.0067</v>
+        <v>0.009599999999999999</v>
       </c>
       <c r="H47" t="n">
-        <v>151.75</v>
+        <v>217</v>
       </c>
       <c r="I47" t="n">
-        <v>7314</v>
+        <v>7260</v>
       </c>
       <c r="J47" t="n">
-        <v>7311.38</v>
+        <v>7275.69</v>
       </c>
       <c r="K47" t="n">
-        <v>7418.25</v>
+        <v>7371.62</v>
       </c>
       <c r="L47" t="n">
-        <v>7525.12</v>
+        <v>7467.56</v>
       </c>
       <c r="M47" t="n">
-        <v>7577.25</v>
+        <v>7523.38</v>
       </c>
       <c r="N47" t="n">
-        <v>7629.38</v>
+        <v>7579.19</v>
       </c>
       <c r="O47" t="n">
-        <v>7791</v>
+        <v>7715.25</v>
       </c>
       <c r="P47" s="6" t="n">
         <v/>
@@ -4447,17 +4445,19 @@
       </c>
       <c r="R47" s="6" t="inlineStr">
         <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S47" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T47" s="8" t="inlineStr">
+        <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="S47" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T47" s="8" t="n">
-        <v/>
-      </c>
       <c r="U47" s="8" t="n">
         <v/>
       </c>
@@ -4469,55 +4469,59 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X47" t="inlineStr"/>
+      <c r="X47" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="B48" t="n">
-        <v>7490</v>
+        <v>7550</v>
       </c>
       <c r="C48" t="n">
-        <v>7541</v>
+        <v>7820.25</v>
       </c>
       <c r="D48" t="n">
-        <v>7324</v>
+        <v>7542.75</v>
       </c>
       <c r="E48" t="n">
-        <v>7519.25</v>
+        <v>7779.75</v>
       </c>
       <c r="F48" t="n">
-        <v>71.75</v>
+        <v>260.5</v>
       </c>
       <c r="G48" s="5" t="n">
-        <v>0.009599999999999999</v>
+        <v>0.0346</v>
       </c>
       <c r="H48" t="n">
-        <v>217</v>
+        <v>277.5</v>
       </c>
       <c r="I48" t="n">
-        <v>7260</v>
+        <v>7107</v>
       </c>
       <c r="J48" t="n">
-        <v>7275.69</v>
+        <v>7345.62</v>
       </c>
       <c r="K48" t="n">
-        <v>7371.62</v>
+        <v>7410.75</v>
       </c>
       <c r="L48" t="n">
-        <v>7467.56</v>
+        <v>7475.88</v>
       </c>
       <c r="M48" t="n">
-        <v>7523.38</v>
+        <v>7627.75</v>
       </c>
       <c r="N48" t="n">
-        <v>7579.19</v>
+        <v>7779.62</v>
       </c>
       <c r="O48" t="n">
-        <v>7715.25</v>
+        <v>7758</v>
       </c>
       <c r="P48" s="6" t="n">
         <v/>
@@ -4525,85 +4529,83 @@
       <c r="Q48" s="6" t="n">
         <v/>
       </c>
-      <c r="R48" s="6" t="inlineStr">
+      <c r="R48" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S48" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T48" s="8" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="S48" s="7" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T48" s="8" t="inlineStr">
+      <c r="U48" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="U48" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V48" s="8" t="n">
-        <v/>
-      </c>
-      <c r="W48" s="11" t="inlineStr">
-        <is>
-          <t>空方</t>
-        </is>
-      </c>
-      <c r="X48" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="V48" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="W48" s="9" t="inlineStr">
+        <is>
+          <t>多方</t>
+        </is>
+      </c>
+      <c r="X48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="B49" t="n">
-        <v>7550</v>
+        <v>7776.75</v>
       </c>
       <c r="C49" t="n">
-        <v>7820.25</v>
+        <v>7838.5</v>
       </c>
       <c r="D49" t="n">
-        <v>7542.75</v>
+        <v>7738</v>
       </c>
       <c r="E49" t="n">
-        <v>7779.75</v>
+        <v>7805</v>
       </c>
       <c r="F49" t="n">
-        <v>260.5</v>
+        <v>25.25</v>
       </c>
       <c r="G49" s="5" t="n">
-        <v>0.0346</v>
+        <v>0.0032</v>
       </c>
       <c r="H49" t="n">
-        <v>277.5</v>
+        <v>100.5</v>
       </c>
       <c r="I49" t="n">
-        <v>7107</v>
+        <v>7265.25</v>
       </c>
       <c r="J49" t="n">
-        <v>7345.62</v>
+        <v>7551.38</v>
       </c>
       <c r="K49" t="n">
-        <v>7410.75</v>
+        <v>7641</v>
       </c>
       <c r="L49" t="n">
-        <v>7475.88</v>
+        <v>7730.62</v>
       </c>
       <c r="M49" t="n">
-        <v>7627.75</v>
+        <v>7918.5</v>
       </c>
       <c r="N49" t="n">
-        <v>7779.62</v>
+        <v>8106.38</v>
       </c>
       <c r="O49" t="n">
-        <v>7758</v>
+        <v>8097.75</v>
       </c>
       <c r="P49" s="6" t="n">
         <v/>
@@ -4616,23 +4618,17 @@
       </c>
       <c r="S49" s="7" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T49" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U49" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="V49" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T49" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U49" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V49" s="8" t="n">
+        <v/>
       </c>
       <c r="W49" s="9" t="inlineStr">
         <is>
@@ -4644,63 +4640,67 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="B50" t="n">
-        <v>7776.75</v>
+        <v>7809.25</v>
       </c>
       <c r="C50" t="n">
-        <v>7838.5</v>
+        <v>7824.5</v>
       </c>
       <c r="D50" t="n">
-        <v>7738</v>
+        <v>7657.75</v>
       </c>
       <c r="E50" t="n">
-        <v>7805</v>
+        <v>7691.25</v>
       </c>
       <c r="F50" t="n">
-        <v>25.25</v>
+        <v>-113.75</v>
       </c>
       <c r="G50" s="5" t="n">
-        <v>0.0032</v>
+        <v>-0.0146</v>
       </c>
       <c r="H50" t="n">
-        <v>100.5</v>
+        <v>166.75</v>
       </c>
       <c r="I50" t="n">
-        <v>7265.25</v>
+        <v>7637.5</v>
       </c>
       <c r="J50" t="n">
-        <v>7551.38</v>
+        <v>7712.88</v>
       </c>
       <c r="K50" t="n">
-        <v>7641</v>
+        <v>7754.75</v>
       </c>
       <c r="L50" t="n">
-        <v>7730.62</v>
+        <v>7796.62</v>
       </c>
       <c r="M50" t="n">
-        <v>7918.5</v>
+        <v>7855.25</v>
       </c>
       <c r="N50" t="n">
-        <v>8106.38</v>
+        <v>7913.88</v>
       </c>
       <c r="O50" t="n">
-        <v>8097.75</v>
+        <v>7939</v>
       </c>
       <c r="P50" s="6" t="n">
         <v/>
       </c>
-      <c r="Q50" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R50" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S50" s="7" t="inlineStr">
-        <is>
-          <t>↑C</t>
+      <c r="Q50" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="R50" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S50" s="10" t="inlineStr">
+        <is>
+          <t>↓</t>
         </is>
       </c>
       <c r="T50" s="8" t="n">
@@ -4712,9 +4712,9 @@
       <c r="V50" s="8" t="n">
         <v/>
       </c>
-      <c r="W50" s="9" t="inlineStr">
-        <is>
-          <t>多方</t>
+      <c r="W50" s="11" t="inlineStr">
+        <is>
+          <t>空方</t>
         </is>
       </c>
       <c r="X50" t="inlineStr"/>
@@ -4722,72 +4722,70 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="B51" t="n">
-        <v>7809.25</v>
+        <v>7693.5</v>
       </c>
       <c r="C51" t="n">
-        <v>7824.5</v>
+        <v>7782.5</v>
       </c>
       <c r="D51" t="n">
-        <v>7657.75</v>
+        <v>7655</v>
       </c>
       <c r="E51" t="n">
-        <v>7691.25</v>
+        <v>7722</v>
       </c>
       <c r="F51" t="n">
-        <v>-113.75</v>
+        <v>30.75</v>
       </c>
       <c r="G51" s="5" t="n">
-        <v>-0.0146</v>
+        <v>0.004</v>
       </c>
       <c r="H51" t="n">
-        <v>166.75</v>
+        <v>127.5</v>
       </c>
       <c r="I51" t="n">
-        <v>7637.5</v>
+        <v>7491</v>
       </c>
       <c r="J51" t="n">
-        <v>7712.88</v>
+        <v>7499.56</v>
       </c>
       <c r="K51" t="n">
-        <v>7754.75</v>
+        <v>7607.88</v>
       </c>
       <c r="L51" t="n">
-        <v>7796.62</v>
+        <v>7716.19</v>
       </c>
       <c r="M51" t="n">
-        <v>7855.25</v>
+        <v>7774.62</v>
       </c>
       <c r="N51" t="n">
-        <v>7913.88</v>
+        <v>7833.06</v>
       </c>
       <c r="O51" t="n">
-        <v>7939</v>
+        <v>7991.25</v>
       </c>
       <c r="P51" s="6" t="n">
         <v/>
       </c>
-      <c r="Q51" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="R51" s="6" t="inlineStr">
+      <c r="Q51" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R51" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S51" s="7" t="inlineStr">
+        <is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T51" s="8" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="S51" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T51" s="8" t="n">
-        <v/>
-      </c>
       <c r="U51" s="8" t="n">
         <v/>
       </c>
@@ -4799,55 +4797,59 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X51" t="inlineStr"/>
+      <c r="X51" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="B52" t="n">
-        <v>7693.5</v>
+        <v>7723.5</v>
       </c>
       <c r="C52" t="n">
-        <v>7782.5</v>
+        <v>7766.5</v>
       </c>
       <c r="D52" t="n">
-        <v>7655</v>
+        <v>7618.5</v>
       </c>
       <c r="E52" t="n">
         <v>7722</v>
       </c>
       <c r="F52" t="n">
-        <v>30.75</v>
+        <v>0</v>
       </c>
       <c r="G52" s="5" t="n">
-        <v>0.004</v>
+        <v>0</v>
       </c>
       <c r="H52" t="n">
-        <v>127.5</v>
+        <v>148</v>
       </c>
       <c r="I52" t="n">
-        <v>7491</v>
+        <v>7527.5</v>
       </c>
       <c r="J52" t="n">
-        <v>7499.56</v>
+        <v>7596.12</v>
       </c>
       <c r="K52" t="n">
-        <v>7607.88</v>
+        <v>7658.25</v>
       </c>
       <c r="L52" t="n">
-        <v>7716.19</v>
+        <v>7720.38</v>
       </c>
       <c r="M52" t="n">
-        <v>7774.62</v>
+        <v>7785.75</v>
       </c>
       <c r="N52" t="n">
-        <v>7833.06</v>
+        <v>7851.12</v>
       </c>
       <c r="O52" t="n">
-        <v>7991.25</v>
+        <v>7910</v>
       </c>
       <c r="P52" s="6" t="n">
         <v/>
@@ -4855,18 +4857,18 @@
       <c r="Q52" s="6" t="n">
         <v/>
       </c>
-      <c r="R52" s="6" t="n">
-        <v/>
+      <c r="R52" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S52" s="7" t="inlineStr">
         <is>
           <t>↑C</t>
         </is>
       </c>
-      <c r="T52" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="T52" s="8" t="n">
+        <v/>
       </c>
       <c r="U52" s="8" t="n">
         <v/>
@@ -4879,74 +4881,72 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X52" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="X52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="B53" t="n">
-        <v>7723.5</v>
+        <v>7715.5</v>
       </c>
       <c r="C53" t="n">
-        <v>7766.5</v>
+        <v>7728.5</v>
       </c>
       <c r="D53" t="n">
-        <v>7618.5</v>
+        <v>7585.5</v>
       </c>
       <c r="E53" t="n">
-        <v>7722</v>
+        <v>7659.5</v>
       </c>
       <c r="F53" t="n">
-        <v>0</v>
+        <v>-62.5</v>
       </c>
       <c r="G53" s="5" t="n">
-        <v>0</v>
+        <v>-0.0081</v>
       </c>
       <c r="H53" t="n">
-        <v>148</v>
+        <v>143</v>
       </c>
       <c r="I53" t="n">
-        <v>7527.5</v>
+        <v>7470.5</v>
       </c>
       <c r="J53" t="n">
-        <v>7596.12</v>
+        <v>7588.75</v>
       </c>
       <c r="K53" t="n">
-        <v>7658.25</v>
+        <v>7648</v>
       </c>
       <c r="L53" t="n">
-        <v>7720.38</v>
+        <v>7707.25</v>
       </c>
       <c r="M53" t="n">
-        <v>7785.75</v>
+        <v>7796</v>
       </c>
       <c r="N53" t="n">
-        <v>7851.12</v>
+        <v>7884.75</v>
       </c>
       <c r="O53" t="n">
-        <v>7910</v>
+        <v>7914.5</v>
       </c>
       <c r="P53" s="6" t="n">
         <v/>
       </c>
-      <c r="Q53" s="6" t="n">
-        <v/>
+      <c r="Q53" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="R53" s="6" t="inlineStr">
         <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S53" s="7" t="inlineStr">
-        <is>
-          <t>↑C</t>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="S53" s="10" t="inlineStr">
+        <is>
+          <t>↓</t>
         </is>
       </c>
       <c r="T53" s="8" t="n">
@@ -4968,50 +4968,50 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="B54" t="n">
-        <v>7715.5</v>
+        <v>7609.25</v>
       </c>
       <c r="C54" t="n">
-        <v>7728.5</v>
+        <v>7670.25</v>
       </c>
       <c r="D54" t="n">
-        <v>7585.5</v>
+        <v>7509.25</v>
       </c>
       <c r="E54" t="n">
-        <v>7659.5</v>
+        <v>7657.35</v>
       </c>
       <c r="F54" t="n">
-        <v>-62.5</v>
+        <v>-2.15</v>
       </c>
       <c r="G54" s="5" t="n">
-        <v>-0.0081</v>
+        <v>-0.0003</v>
       </c>
       <c r="H54" t="n">
-        <v>143</v>
+        <v>161</v>
       </c>
       <c r="I54" t="n">
-        <v>7470.5</v>
+        <v>7442.5</v>
       </c>
       <c r="J54" t="n">
-        <v>7588.75</v>
+        <v>7517.75</v>
       </c>
       <c r="K54" t="n">
-        <v>7648</v>
+        <v>7588</v>
       </c>
       <c r="L54" t="n">
-        <v>7707.25</v>
+        <v>7658.25</v>
       </c>
       <c r="M54" t="n">
-        <v>7796</v>
+        <v>7731</v>
       </c>
       <c r="N54" t="n">
-        <v>7884.75</v>
+        <v>7803.75</v>
       </c>
       <c r="O54" t="n">
-        <v>7914.5</v>
+        <v>7871.5</v>
       </c>
       <c r="P54" s="6" t="n">
         <v/>
@@ -5023,12 +5023,12 @@
       </c>
       <c r="R54" s="6" t="inlineStr">
         <is>
-          <t>△C</t>
+          <t>✓</t>
         </is>
       </c>
       <c r="S54" s="10" t="inlineStr">
         <is>
-          <t>↓</t>
+          <t>↓C</t>
         </is>
       </c>
       <c r="T54" s="8" t="n">
@@ -5050,239 +5050,237 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="B55" t="n">
-        <v>7609.25</v>
+        <v>7722</v>
       </c>
       <c r="C55" t="n">
-        <v>7670.25</v>
+        <v>7848.5</v>
       </c>
       <c r="D55" t="n">
-        <v>7509.25</v>
+        <v>7707.25</v>
       </c>
       <c r="E55" t="n">
-        <v>7657.35</v>
+        <v>7803.75</v>
       </c>
       <c r="F55" t="n">
-        <v>-2.15</v>
+        <v>146.4</v>
       </c>
       <c r="G55" s="5" t="n">
-        <v>-0.0003</v>
+        <v>0.0191</v>
       </c>
       <c r="H55" t="n">
-        <v>161</v>
+        <v>141.25</v>
       </c>
       <c r="I55" t="n">
-        <v>7442.5</v>
+        <v>7348.25</v>
       </c>
       <c r="J55" t="n">
-        <v>7517.75</v>
+        <v>7530.15</v>
       </c>
       <c r="K55" t="n">
-        <v>7588</v>
+        <v>7576.85</v>
       </c>
       <c r="L55" t="n">
-        <v>7658.25</v>
+        <v>7623.55</v>
       </c>
       <c r="M55" t="n">
-        <v>7731</v>
+        <v>7737.85</v>
       </c>
       <c r="N55" t="n">
-        <v>7803.75</v>
+        <v>7852.15</v>
       </c>
       <c r="O55" t="n">
-        <v>7871.5</v>
+        <v>7831.25</v>
       </c>
       <c r="P55" s="6" t="n">
         <v/>
       </c>
-      <c r="Q55" s="6" t="inlineStr">
+      <c r="Q55" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R55" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S55" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T55" s="8" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="R55" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S55" s="10" t="inlineStr">
-        <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T55" s="8" t="n">
-        <v/>
-      </c>
       <c r="U55" s="8" t="n">
         <v/>
       </c>
-      <c r="V55" s="8" t="n">
-        <v/>
+      <c r="V55" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="W55" s="11" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
       </c>
-      <c r="X55" t="inlineStr"/>
+      <c r="X55" t="inlineStr">
+        <is>
+          <t>強警訊</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="B56" t="n">
-        <v>7722</v>
+        <v>7796</v>
       </c>
       <c r="C56" t="n">
-        <v>7848.5</v>
+        <v>7810.25</v>
       </c>
       <c r="D56" t="n">
-        <v>7707.25</v>
+        <v>7672.75</v>
       </c>
       <c r="E56" t="n">
-        <v>7803.75</v>
+        <v>7777.25</v>
       </c>
       <c r="F56" t="n">
-        <v>146.4</v>
+        <v>-26.5</v>
       </c>
       <c r="G56" s="5" t="n">
-        <v>0.0191</v>
+        <v>-0.0034</v>
       </c>
       <c r="H56" t="n">
-        <v>141.25</v>
+        <v>137.5</v>
       </c>
       <c r="I56" t="n">
-        <v>7348.25</v>
+        <v>7566</v>
       </c>
       <c r="J56" t="n">
-        <v>7530.15</v>
+        <v>7675.44</v>
       </c>
       <c r="K56" t="n">
-        <v>7576.85</v>
+        <v>7733.12</v>
       </c>
       <c r="L56" t="n">
-        <v>7623.55</v>
+        <v>7790.81</v>
       </c>
       <c r="M56" t="n">
-        <v>7737.85</v>
+        <v>7874.38</v>
       </c>
       <c r="N56" t="n">
-        <v>7852.15</v>
+        <v>7957.94</v>
       </c>
       <c r="O56" t="n">
-        <v>7831.25</v>
+        <v>7989.75</v>
       </c>
       <c r="P56" s="6" t="n">
         <v/>
       </c>
-      <c r="Q56" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R56" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S56" s="7" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T56" s="8" t="inlineStr">
+      <c r="Q56" s="6" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
+      <c r="R56" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S56" s="10" t="inlineStr">
+        <is>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T56" s="8" t="n">
+        <v/>
+      </c>
       <c r="U56" s="8" t="n">
         <v/>
       </c>
-      <c r="V56" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+      <c r="V56" s="8" t="n">
+        <v/>
       </c>
       <c r="W56" s="11" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
       </c>
-      <c r="X56" t="inlineStr">
-        <is>
-          <t>強警訊</t>
-        </is>
-      </c>
+      <c r="X56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="B57" t="n">
-        <v>7796</v>
+        <v>7781.5</v>
       </c>
       <c r="C57" t="n">
-        <v>7810.25</v>
+        <v>7897.5</v>
       </c>
       <c r="D57" t="n">
-        <v>7672.75</v>
+        <v>7760.25</v>
       </c>
       <c r="E57" t="n">
-        <v>7777.25</v>
+        <v>7859.75</v>
       </c>
       <c r="F57" t="n">
-        <v>-26.5</v>
+        <v>82.5</v>
       </c>
       <c r="G57" s="5" t="n">
-        <v>-0.0034</v>
+        <v>0.0106</v>
       </c>
       <c r="H57" t="n">
-        <v>137.5</v>
+        <v>137.25</v>
       </c>
       <c r="I57" t="n">
-        <v>7566</v>
+        <v>7535.25</v>
       </c>
       <c r="J57" t="n">
-        <v>7675.44</v>
+        <v>7657.62</v>
       </c>
       <c r="K57" t="n">
-        <v>7733.12</v>
+        <v>7708.5</v>
       </c>
       <c r="L57" t="n">
-        <v>7790.81</v>
+        <v>7759.38</v>
       </c>
       <c r="M57" t="n">
-        <v>7874.38</v>
+        <v>7846</v>
       </c>
       <c r="N57" t="n">
-        <v>7957.94</v>
+        <v>7932.62</v>
       </c>
       <c r="O57" t="n">
-        <v>7989.75</v>
+        <v>7947.75</v>
       </c>
       <c r="P57" s="6" t="n">
         <v/>
       </c>
-      <c r="Q57" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="R57" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S57" s="10" t="inlineStr">
-        <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T57" s="8" t="n">
-        <v/>
+      <c r="Q57" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R57" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S57" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T57" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="U57" s="8" t="n">
         <v/>
@@ -5295,87 +5293,7 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X57" t="inlineStr"/>
-    </row>
-    <row r="58">
-      <c r="A58" t="inlineStr">
-        <is>
-          <t>2026-10-05</t>
-        </is>
-      </c>
-      <c r="B58" t="n">
-        <v>7781.5</v>
-      </c>
-      <c r="C58" t="n">
-        <v>7897.5</v>
-      </c>
-      <c r="D58" t="n">
-        <v>7760.25</v>
-      </c>
-      <c r="E58" t="n">
-        <v>7832.25</v>
-      </c>
-      <c r="F58" t="n">
-        <v>55</v>
-      </c>
-      <c r="G58" s="5" t="n">
-        <v>0.0071</v>
-      </c>
-      <c r="H58" t="n">
-        <v>137.25</v>
-      </c>
-      <c r="I58" t="n">
-        <v>7535.25</v>
-      </c>
-      <c r="J58" t="n">
-        <v>7657.62</v>
-      </c>
-      <c r="K58" t="n">
-        <v>7708.5</v>
-      </c>
-      <c r="L58" t="n">
-        <v>7759.38</v>
-      </c>
-      <c r="M58" t="n">
-        <v>7846</v>
-      </c>
-      <c r="N58" t="n">
-        <v>7932.62</v>
-      </c>
-      <c r="O58" t="n">
-        <v>7947.75</v>
-      </c>
-      <c r="P58" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q58" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R58" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S58" s="7" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T58" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="U58" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V58" s="8" t="n">
-        <v/>
-      </c>
-      <c r="W58" s="11" t="inlineStr">
-        <is>
-          <t>空方</t>
-        </is>
-      </c>
-      <c r="X58" t="inlineStr">
+      <c r="X57" t="inlineStr">
         <is>
           <t>強警訊</t>
         </is>

--- a/three_gate/analysis/ES_weekly.xlsx
+++ b/three_gate/analysis/ES_weekly.xlsx
@@ -5231,13 +5231,13 @@
         <v>7760.25</v>
       </c>
       <c r="E57" t="n">
-        <v>7859.75</v>
+        <v>7876.75</v>
       </c>
       <c r="F57" t="n">
-        <v>82.5</v>
+        <v>99.5</v>
       </c>
       <c r="G57" s="5" t="n">
-        <v>0.0106</v>
+        <v>0.0128</v>
       </c>
       <c r="H57" t="n">
         <v>137.25</v>

--- a/three_gate/analysis/ES_weekly.xlsx
+++ b/three_gate/analysis/ES_weekly.xlsx
@@ -5231,13 +5231,13 @@
         <v>7760.25</v>
       </c>
       <c r="E57" t="n">
-        <v>7876.75</v>
+        <v>7878.25</v>
       </c>
       <c r="F57" t="n">
-        <v>99.5</v>
+        <v>101</v>
       </c>
       <c r="G57" s="5" t="n">
-        <v>0.0128</v>
+        <v>0.013</v>
       </c>
       <c r="H57" t="n">
         <v>137.25</v>

--- a/three_gate/analysis/ES_weekly.xlsx
+++ b/three_gate/analysis/ES_weekly.xlsx
@@ -480,7 +480,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X57"/>
+  <dimension ref="A1:X58"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -659,25 +659,25 @@
         <v>108</v>
       </c>
       <c r="I2" t="n">
-        <v>6354.5</v>
+        <v>6372.5</v>
       </c>
       <c r="J2" t="n">
-        <v>6485.06</v>
+        <v>6491.81</v>
       </c>
       <c r="K2" t="n">
-        <v>6525.38</v>
+        <v>6529.88</v>
       </c>
       <c r="L2" t="n">
-        <v>6565.69</v>
+        <v>6567.94</v>
       </c>
       <c r="M2" t="n">
-        <v>6651.12</v>
+        <v>6646.62</v>
       </c>
       <c r="N2" t="n">
-        <v>6736.56</v>
+        <v>6725.31</v>
       </c>
       <c r="O2" t="n">
-        <v>6731.75</v>
+        <v>6722.75</v>
       </c>
       <c r="P2" s="6" t="n">
         <v/>
@@ -5231,13 +5231,13 @@
         <v>7760.25</v>
       </c>
       <c r="E57" t="n">
-        <v>7878.25</v>
+        <v>7859.75</v>
       </c>
       <c r="F57" t="n">
-        <v>101</v>
+        <v>82.5</v>
       </c>
       <c r="G57" s="5" t="n">
-        <v>0.013</v>
+        <v>0.0106</v>
       </c>
       <c r="H57" t="n">
         <v>137.25</v>
@@ -5296,6 +5296,88 @@
       <c r="X57" t="inlineStr">
         <is>
           <t>強警訊</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>2026-10-12</t>
+        </is>
+      </c>
+      <c r="B58" t="n">
+        <v>7873</v>
+      </c>
+      <c r="C58" t="n">
+        <v>7887</v>
+      </c>
+      <c r="D58" t="n">
+        <v>7846.25</v>
+      </c>
+      <c r="E58" t="n">
+        <v>7858</v>
+      </c>
+      <c r="F58" t="n">
+        <v>-1.75</v>
+      </c>
+      <c r="G58" s="5" t="n">
+        <v>-0.0002</v>
+      </c>
+      <c r="H58" t="n">
+        <v>40.75</v>
+      </c>
+      <c r="I58" t="n">
+        <v>7623</v>
+      </c>
+      <c r="J58" t="n">
+        <v>7737.94</v>
+      </c>
+      <c r="K58" t="n">
+        <v>7791.12</v>
+      </c>
+      <c r="L58" t="n">
+        <v>7844.31</v>
+      </c>
+      <c r="M58" t="n">
+        <v>7928.38</v>
+      </c>
+      <c r="N58" t="n">
+        <v>8012.44</v>
+      </c>
+      <c r="O58" t="n">
+        <v>8034.75</v>
+      </c>
+      <c r="P58" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q58" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R58" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S58" s="7" t="inlineStr">
+        <is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T58" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U58" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V58" s="8" t="n">
+        <v/>
+      </c>
+      <c r="W58" s="11" t="inlineStr">
+        <is>
+          <t>空方</t>
+        </is>
+      </c>
+      <c r="X58" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>

--- a/three_gate/analysis/ES_weekly.xlsx
+++ b/three_gate/analysis/ES_weekly.xlsx
@@ -659,25 +659,25 @@
         <v>108</v>
       </c>
       <c r="I2" t="n">
-        <v>6372.5</v>
+        <v>6439</v>
       </c>
       <c r="J2" t="n">
-        <v>6491.81</v>
+        <v>6516.75</v>
       </c>
       <c r="K2" t="n">
-        <v>6529.88</v>
+        <v>6546.5</v>
       </c>
       <c r="L2" t="n">
-        <v>6567.94</v>
+        <v>6576.25</v>
       </c>
       <c r="M2" t="n">
-        <v>6646.62</v>
+        <v>6630</v>
       </c>
       <c r="N2" t="n">
-        <v>6725.31</v>
+        <v>6683.75</v>
       </c>
       <c r="O2" t="n">
-        <v>6722.75</v>
+        <v>6689.5</v>
       </c>
       <c r="P2" s="6" t="n">
         <v/>
@@ -695,11 +695,13 @@
       </c>
       <c r="T2" s="8" t="inlineStr">
         <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U2" s="8" t="inlineStr">
+        <is>
           <t>△C</t>
         </is>
-      </c>
-      <c r="U2" s="8" t="n">
-        <v/>
       </c>
       <c r="V2" s="8" t="n">
         <v/>
@@ -5315,13 +5317,13 @@
         <v>7846.25</v>
       </c>
       <c r="E58" t="n">
-        <v>7858</v>
+        <v>7860.5</v>
       </c>
       <c r="F58" t="n">
-        <v>-1.75</v>
+        <v>0.75</v>
       </c>
       <c r="G58" s="5" t="n">
-        <v>-0.0002</v>
+        <v>0.0001</v>
       </c>
       <c r="H58" t="n">
         <v>40.75</v>
@@ -5377,7 +5379,7 @@
       </c>
       <c r="X58" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>

--- a/three_gate/analysis/ES_weekly.xlsx
+++ b/three_gate/analysis/ES_weekly.xlsx
@@ -659,25 +659,25 @@
         <v>108</v>
       </c>
       <c r="I2" t="n">
-        <v>6439</v>
+        <v>6465</v>
       </c>
       <c r="J2" t="n">
-        <v>6516.75</v>
+        <v>6526.5</v>
       </c>
       <c r="K2" t="n">
-        <v>6546.5</v>
+        <v>6553</v>
       </c>
       <c r="L2" t="n">
-        <v>6576.25</v>
+        <v>6579.5</v>
       </c>
       <c r="M2" t="n">
-        <v>6630</v>
+        <v>6623.5</v>
       </c>
       <c r="N2" t="n">
-        <v>6683.75</v>
+        <v>6667.5</v>
       </c>
       <c r="O2" t="n">
-        <v>6689.5</v>
+        <v>6676.5</v>
       </c>
       <c r="P2" s="6" t="n">
         <v/>
@@ -5314,19 +5314,19 @@
         <v>7887</v>
       </c>
       <c r="D58" t="n">
-        <v>7846.25</v>
+        <v>7740.75</v>
       </c>
       <c r="E58" t="n">
-        <v>7860.5</v>
+        <v>7748.75</v>
       </c>
       <c r="F58" t="n">
-        <v>0.75</v>
+        <v>-111</v>
       </c>
       <c r="G58" s="5" t="n">
-        <v>0.0001</v>
+        <v>-0.0141</v>
       </c>
       <c r="H58" t="n">
-        <v>40.75</v>
+        <v>146.25</v>
       </c>
       <c r="I58" t="n">
         <v>7623</v>
@@ -5352,15 +5352,19 @@
       <c r="P58" s="6" t="n">
         <v/>
       </c>
-      <c r="Q58" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R58" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S58" s="7" t="inlineStr">
-        <is>
-          <t>↑C</t>
+      <c r="Q58" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="R58" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S58" s="10" t="inlineStr">
+        <is>
+          <t>↓</t>
         </is>
       </c>
       <c r="T58" s="8" t="n">
@@ -5377,11 +5381,7 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X58" t="inlineStr">
-        <is>
-          <t>中警訊</t>
-        </is>
-      </c>
+      <c r="X58" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/three_gate/analysis/ES_weekly.xlsx
+++ b/three_gate/analysis/ES_weekly.xlsx
@@ -5317,13 +5317,13 @@
         <v>7740.75</v>
       </c>
       <c r="E58" t="n">
-        <v>7748.75</v>
+        <v>7745</v>
       </c>
       <c r="F58" t="n">
-        <v>-111</v>
+        <v>-114.75</v>
       </c>
       <c r="G58" s="5" t="n">
-        <v>-0.0141</v>
+        <v>-0.0146</v>
       </c>
       <c r="H58" t="n">
         <v>146.25</v>

--- a/three_gate/analysis/ES_weekly.xlsx
+++ b/three_gate/analysis/ES_weekly.xlsx
@@ -5317,13 +5317,13 @@
         <v>7740.75</v>
       </c>
       <c r="E58" t="n">
-        <v>7745</v>
+        <v>7746.5</v>
       </c>
       <c r="F58" t="n">
-        <v>-114.75</v>
+        <v>-113.25</v>
       </c>
       <c r="G58" s="5" t="n">
-        <v>-0.0146</v>
+        <v>-0.0144</v>
       </c>
       <c r="H58" t="n">
         <v>146.25</v>

--- a/three_gate/analysis/ES_weekly.xlsx
+++ b/three_gate/analysis/ES_weekly.xlsx
@@ -659,34 +659,38 @@
         <v>108</v>
       </c>
       <c r="I2" t="n">
-        <v>6465</v>
+        <v>6546</v>
       </c>
       <c r="J2" t="n">
-        <v>6526.5</v>
+        <v>6556.88</v>
       </c>
       <c r="K2" t="n">
-        <v>6553</v>
+        <v>6573.25</v>
       </c>
       <c r="L2" t="n">
-        <v>6579.5</v>
+        <v>6589.62</v>
       </c>
       <c r="M2" t="n">
-        <v>6623.5</v>
+        <v>6603.25</v>
       </c>
       <c r="N2" t="n">
-        <v>6667.5</v>
+        <v>6616.88</v>
       </c>
       <c r="O2" t="n">
-        <v>6676.5</v>
+        <v>6636</v>
       </c>
       <c r="P2" s="6" t="n">
         <v/>
       </c>
-      <c r="Q2" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R2" s="6" t="n">
-        <v/>
+      <c r="Q2" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="R2" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S2" s="7" t="inlineStr">
         <is>
@@ -700,18 +704,24 @@
       </c>
       <c r="U2" s="8" t="inlineStr">
         <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="V2" s="8" t="inlineStr">
+        <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="V2" s="8" t="n">
-        <v/>
-      </c>
       <c r="W2" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X2" t="inlineStr"/>
+      <c r="X2" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -5314,19 +5324,19 @@
         <v>7887</v>
       </c>
       <c r="D58" t="n">
-        <v>7740.75</v>
+        <v>7741</v>
       </c>
       <c r="E58" t="n">
-        <v>7746.5</v>
+        <v>7789</v>
       </c>
       <c r="F58" t="n">
-        <v>-113.25</v>
+        <v>-70.75</v>
       </c>
       <c r="G58" s="5" t="n">
-        <v>-0.0144</v>
+        <v>-0.008999999999999999</v>
       </c>
       <c r="H58" t="n">
-        <v>146.25</v>
+        <v>146</v>
       </c>
       <c r="I58" t="n">
         <v>7623</v>
@@ -5352,14 +5362,12 @@
       <c r="P58" s="6" t="n">
         <v/>
       </c>
-      <c r="Q58" s="6" t="inlineStr">
+      <c r="Q58" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R58" s="6" t="inlineStr">
         <is>
           <t>△C</t>
-        </is>
-      </c>
-      <c r="R58" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
         </is>
       </c>
       <c r="S58" s="10" t="inlineStr">

--- a/three_gate/analysis/ES_weekly.xlsx
+++ b/three_gate/analysis/ES_weekly.xlsx
@@ -480,7 +480,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X58"/>
+  <dimension ref="A1:X57"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -634,63 +634,59 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2025-09-15</t>
+          <t>2025-09-22</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>6588.25</v>
+        <v>6716</v>
       </c>
       <c r="C2" t="n">
-        <v>6662</v>
+        <v>6756.75</v>
       </c>
       <c r="D2" t="n">
-        <v>6554</v>
+        <v>6624.25</v>
       </c>
       <c r="E2" t="n">
-        <v>6658.77</v>
+        <v>6696.5</v>
       </c>
       <c r="F2" t="n">
-        <v>70.52</v>
+        <v>37.73</v>
       </c>
       <c r="G2" s="5" t="n">
-        <v>0.0107</v>
+        <v>0.0057</v>
       </c>
       <c r="H2" t="n">
-        <v>108</v>
+        <v>132.5</v>
       </c>
       <c r="I2" t="n">
-        <v>6546</v>
+        <v>6446</v>
       </c>
       <c r="J2" t="n">
-        <v>6556.88</v>
+        <v>6576.16</v>
       </c>
       <c r="K2" t="n">
-        <v>6573.25</v>
+        <v>6604.77</v>
       </c>
       <c r="L2" t="n">
-        <v>6589.62</v>
+        <v>6633.39</v>
       </c>
       <c r="M2" t="n">
-        <v>6603.25</v>
+        <v>6712.77</v>
       </c>
       <c r="N2" t="n">
-        <v>6616.88</v>
+        <v>6792.16</v>
       </c>
       <c r="O2" t="n">
-        <v>6636</v>
+        <v>6770</v>
       </c>
       <c r="P2" s="6" t="n">
         <v/>
       </c>
-      <c r="Q2" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="R2" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="Q2" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R2" s="6" t="n">
+        <v/>
       </c>
       <c r="S2" s="7" t="inlineStr">
         <is>
@@ -699,77 +695,69 @@
       </c>
       <c r="T2" s="8" t="inlineStr">
         <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U2" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="V2" s="8" t="inlineStr">
-        <is>
           <t>△C</t>
         </is>
       </c>
+      <c r="U2" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V2" s="8" t="n">
+        <v/>
+      </c>
       <c r="W2" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X2" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="X2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2025-09-22</t>
+          <t>2025-09-29</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>6716</v>
+        <v>6697</v>
       </c>
       <c r="C3" t="n">
-        <v>6756.75</v>
+        <v>6800</v>
       </c>
       <c r="D3" t="n">
-        <v>6624.25</v>
+        <v>6680</v>
       </c>
       <c r="E3" t="n">
-        <v>6696.5</v>
+        <v>6764</v>
       </c>
       <c r="F3" t="n">
-        <v>37.73</v>
+        <v>67.5</v>
       </c>
       <c r="G3" s="5" t="n">
-        <v>0.0057</v>
+        <v>0.0101</v>
       </c>
       <c r="H3" t="n">
-        <v>132.5</v>
+        <v>120</v>
       </c>
       <c r="I3" t="n">
-        <v>6446</v>
+        <v>6491.75</v>
       </c>
       <c r="J3" t="n">
-        <v>6576.16</v>
+        <v>6567</v>
       </c>
       <c r="K3" t="n">
-        <v>6604.77</v>
+        <v>6630.25</v>
       </c>
       <c r="L3" t="n">
-        <v>6633.39</v>
+        <v>6693.5</v>
       </c>
       <c r="M3" t="n">
-        <v>6712.77</v>
+        <v>6762.75</v>
       </c>
       <c r="N3" t="n">
-        <v>6792.16</v>
+        <v>6832</v>
       </c>
       <c r="O3" t="n">
-        <v>6770</v>
+        <v>6889.25</v>
       </c>
       <c r="P3" s="6" t="n">
         <v/>
@@ -806,154 +794,158 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2025-09-29</t>
+          <t>2025-10-06</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>6697</v>
+        <v>6768</v>
       </c>
       <c r="C4" t="n">
-        <v>6800</v>
+        <v>6812.25</v>
       </c>
       <c r="D4" t="n">
-        <v>6680</v>
+        <v>6540.25</v>
       </c>
       <c r="E4" t="n">
-        <v>6764</v>
+        <v>6595.25</v>
       </c>
       <c r="F4" t="n">
-        <v>67.5</v>
+        <v>-168.75</v>
       </c>
       <c r="G4" s="5" t="n">
-        <v>0.0101</v>
+        <v>-0.0249</v>
       </c>
       <c r="H4" t="n">
-        <v>120</v>
+        <v>272</v>
       </c>
       <c r="I4" t="n">
-        <v>6491.75</v>
+        <v>6560</v>
       </c>
       <c r="J4" t="n">
-        <v>6567</v>
+        <v>6656</v>
       </c>
       <c r="K4" t="n">
-        <v>6630.25</v>
+        <v>6704</v>
       </c>
       <c r="L4" t="n">
-        <v>6693.5</v>
+        <v>6752</v>
       </c>
       <c r="M4" t="n">
-        <v>6762.75</v>
+        <v>6824</v>
       </c>
       <c r="N4" t="n">
-        <v>6832</v>
+        <v>6896</v>
       </c>
       <c r="O4" t="n">
-        <v>6889.25</v>
-      </c>
-      <c r="P4" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q4" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R4" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S4" s="7" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T4" s="8" t="inlineStr">
+        <v>6920</v>
+      </c>
+      <c r="P4" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
+      <c r="Q4" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="R4" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S4" s="10" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T4" s="8" t="n">
+        <v/>
+      </c>
       <c r="U4" s="8" t="n">
         <v/>
       </c>
       <c r="V4" s="8" t="n">
         <v/>
       </c>
-      <c r="W4" s="9" t="inlineStr">
-        <is>
-          <t>多方</t>
-        </is>
-      </c>
-      <c r="X4" t="inlineStr"/>
+      <c r="W4" s="11" t="inlineStr">
+        <is>
+          <t>空方</t>
+        </is>
+      </c>
+      <c r="X4" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2025-10-06</t>
+          <t>2025-10-13</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>6768</v>
+        <v>6632</v>
       </c>
       <c r="C5" t="n">
-        <v>6812.25</v>
+        <v>6766.75</v>
       </c>
       <c r="D5" t="n">
-        <v>6540.25</v>
+        <v>6571.25</v>
       </c>
       <c r="E5" t="n">
-        <v>6595.25</v>
+        <v>6702.5</v>
       </c>
       <c r="F5" t="n">
-        <v>-168.75</v>
+        <v>107.25</v>
       </c>
       <c r="G5" s="5" t="n">
-        <v>-0.0249</v>
+        <v>0.0163</v>
       </c>
       <c r="H5" t="n">
-        <v>272</v>
+        <v>195.5</v>
       </c>
       <c r="I5" t="n">
-        <v>6560</v>
+        <v>6268.25</v>
       </c>
       <c r="J5" t="n">
-        <v>6656</v>
+        <v>6282.75</v>
       </c>
       <c r="K5" t="n">
-        <v>6704</v>
+        <v>6459.25</v>
       </c>
       <c r="L5" t="n">
-        <v>6752</v>
+        <v>6635.75</v>
       </c>
       <c r="M5" t="n">
-        <v>6824</v>
+        <v>6731.25</v>
       </c>
       <c r="N5" t="n">
-        <v>6896</v>
+        <v>6826.75</v>
       </c>
       <c r="O5" t="n">
-        <v>6920</v>
-      </c>
-      <c r="P5" s="6" t="inlineStr">
+        <v>7084.25</v>
+      </c>
+      <c r="P5" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q5" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R5" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S5" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T5" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="Q5" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="R5" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S5" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T5" s="8" t="n">
-        <v/>
-      </c>
       <c r="U5" s="8" t="n">
         <v/>
       </c>
@@ -967,57 +959,57 @@
       </c>
       <c r="X5" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2025-10-13</t>
+          <t>2025-10-20</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>6632</v>
+        <v>6721</v>
       </c>
       <c r="C6" t="n">
-        <v>6766.75</v>
+        <v>6841.25</v>
       </c>
       <c r="D6" t="n">
-        <v>6571.25</v>
+        <v>6690.75</v>
       </c>
       <c r="E6" t="n">
-        <v>6702.5</v>
+        <v>6827</v>
       </c>
       <c r="F6" t="n">
-        <v>107.25</v>
+        <v>124.5</v>
       </c>
       <c r="G6" s="5" t="n">
-        <v>0.0163</v>
+        <v>0.0186</v>
       </c>
       <c r="H6" t="n">
-        <v>195.5</v>
+        <v>150.5</v>
       </c>
       <c r="I6" t="n">
-        <v>6268.25</v>
+        <v>6375.75</v>
       </c>
       <c r="J6" t="n">
-        <v>6282.75</v>
+        <v>6523.75</v>
       </c>
       <c r="K6" t="n">
-        <v>6459.25</v>
+        <v>6604.75</v>
       </c>
       <c r="L6" t="n">
-        <v>6635.75</v>
+        <v>6685.75</v>
       </c>
       <c r="M6" t="n">
-        <v>6731.25</v>
+        <v>6800.25</v>
       </c>
       <c r="N6" t="n">
-        <v>6826.75</v>
+        <v>6914.75</v>
       </c>
       <c r="O6" t="n">
-        <v>7084.25</v>
+        <v>6962.25</v>
       </c>
       <c r="P6" s="6" t="n">
         <v/>
@@ -1051,57 +1043,57 @@
       </c>
       <c r="X6" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2025-10-20</t>
+          <t>2025-10-27</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>6721</v>
+        <v>6881</v>
       </c>
       <c r="C7" t="n">
-        <v>6841.25</v>
+        <v>6953.75</v>
       </c>
       <c r="D7" t="n">
-        <v>6690.75</v>
+        <v>6843.5</v>
       </c>
       <c r="E7" t="n">
-        <v>6827</v>
+        <v>6874</v>
       </c>
       <c r="F7" t="n">
-        <v>124.5</v>
+        <v>47</v>
       </c>
       <c r="G7" s="5" t="n">
-        <v>0.0186</v>
+        <v>0.0069</v>
       </c>
       <c r="H7" t="n">
-        <v>150.5</v>
+        <v>110.25</v>
       </c>
       <c r="I7" t="n">
-        <v>6375.75</v>
+        <v>6540.25</v>
       </c>
       <c r="J7" t="n">
-        <v>6523.75</v>
+        <v>6707</v>
       </c>
       <c r="K7" t="n">
-        <v>6604.75</v>
+        <v>6751.75</v>
       </c>
       <c r="L7" t="n">
-        <v>6685.75</v>
+        <v>6796.5</v>
       </c>
       <c r="M7" t="n">
-        <v>6800.25</v>
+        <v>6902.25</v>
       </c>
       <c r="N7" t="n">
-        <v>6914.75</v>
+        <v>7008</v>
       </c>
       <c r="O7" t="n">
-        <v>6962.25</v>
+        <v>6991.75</v>
       </c>
       <c r="P7" s="6" t="n">
         <v/>
@@ -1142,70 +1134,74 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2025-10-27</t>
+          <t>2025-11-03</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>6881</v>
+        <v>6878</v>
       </c>
       <c r="C8" t="n">
-        <v>6953.75</v>
+        <v>6909.5</v>
       </c>
       <c r="D8" t="n">
-        <v>6843.5</v>
+        <v>6655.5</v>
       </c>
       <c r="E8" t="n">
-        <v>6874</v>
+        <v>6753.75</v>
       </c>
       <c r="F8" t="n">
-        <v>47</v>
+        <v>-120.25</v>
       </c>
       <c r="G8" s="5" t="n">
-        <v>0.0069</v>
+        <v>-0.0175</v>
       </c>
       <c r="H8" t="n">
-        <v>110.25</v>
+        <v>254</v>
       </c>
       <c r="I8" t="n">
-        <v>6540.25</v>
+        <v>6733.25</v>
       </c>
       <c r="J8" t="n">
-        <v>6707</v>
+        <v>6751.44</v>
       </c>
       <c r="K8" t="n">
-        <v>6751.75</v>
+        <v>6818.88</v>
       </c>
       <c r="L8" t="n">
-        <v>6796.5</v>
+        <v>6886.31</v>
       </c>
       <c r="M8" t="n">
-        <v>6902.25</v>
+        <v>6929.12</v>
       </c>
       <c r="N8" t="n">
-        <v>7008</v>
+        <v>6971.94</v>
       </c>
       <c r="O8" t="n">
-        <v>6991.75</v>
-      </c>
-      <c r="P8" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q8" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R8" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S8" s="7" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T8" s="8" t="inlineStr">
+        <v>7064</v>
+      </c>
+      <c r="P8" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="Q8" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
+      <c r="R8" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S8" s="10" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T8" s="8" t="n">
+        <v/>
+      </c>
       <c r="U8" s="8" t="n">
         <v/>
       </c>
@@ -1217,83 +1213,75 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X8" t="inlineStr">
-        <is>
-          <t>強警訊</t>
-        </is>
-      </c>
+      <c r="X8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2025-11-03</t>
+          <t>2025-11-10</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>6878</v>
+        <v>6788</v>
       </c>
       <c r="C9" t="n">
-        <v>6909.5</v>
+        <v>6900.5</v>
       </c>
       <c r="D9" t="n">
-        <v>6655.5</v>
+        <v>6670.5</v>
       </c>
       <c r="E9" t="n">
-        <v>6753.75</v>
+        <v>6755.25</v>
       </c>
       <c r="F9" t="n">
-        <v>-120.25</v>
+        <v>1.5</v>
       </c>
       <c r="G9" s="5" t="n">
-        <v>-0.0175</v>
+        <v>0.0002</v>
       </c>
       <c r="H9" t="n">
-        <v>254</v>
+        <v>230</v>
       </c>
       <c r="I9" t="n">
-        <v>6733.25</v>
+        <v>6401.5</v>
       </c>
       <c r="J9" t="n">
-        <v>6751.44</v>
+        <v>6485.38</v>
       </c>
       <c r="K9" t="n">
-        <v>6818.88</v>
+        <v>6626.75</v>
       </c>
       <c r="L9" t="n">
-        <v>6886.31</v>
+        <v>6768.12</v>
       </c>
       <c r="M9" t="n">
-        <v>6929.12</v>
+        <v>6880.75</v>
       </c>
       <c r="N9" t="n">
-        <v>6971.94</v>
+        <v>6993.38</v>
       </c>
       <c r="O9" t="n">
-        <v>7064</v>
-      </c>
-      <c r="P9" s="6" t="inlineStr">
+        <v>7163.5</v>
+      </c>
+      <c r="P9" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q9" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R9" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S9" s="10" t="inlineStr">
+        <is>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T9" s="8" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="Q9" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="R9" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S9" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T9" s="8" t="n">
-        <v/>
-      </c>
       <c r="U9" s="8" t="n">
         <v/>
       </c>
@@ -1305,55 +1293,59 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X9" t="inlineStr"/>
+      <c r="X9" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2025-11-10</t>
+          <t>2025-11-17</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>6788</v>
+        <v>6764.75</v>
       </c>
       <c r="C10" t="n">
-        <v>6900.5</v>
+        <v>6801.5</v>
       </c>
       <c r="D10" t="n">
-        <v>6670.5</v>
+        <v>6525</v>
       </c>
       <c r="E10" t="n">
-        <v>6755.25</v>
+        <v>6620.25</v>
       </c>
       <c r="F10" t="n">
-        <v>1.5</v>
+        <v>-135</v>
       </c>
       <c r="G10" s="5" t="n">
-        <v>0.0002</v>
+        <v>-0.02</v>
       </c>
       <c r="H10" t="n">
-        <v>230</v>
+        <v>276.5</v>
       </c>
       <c r="I10" t="n">
-        <v>6401.5</v>
+        <v>6440.5</v>
       </c>
       <c r="J10" t="n">
-        <v>6485.38</v>
+        <v>6510.12</v>
       </c>
       <c r="K10" t="n">
-        <v>6626.75</v>
+        <v>6640.25</v>
       </c>
       <c r="L10" t="n">
-        <v>6768.12</v>
+        <v>6770.38</v>
       </c>
       <c r="M10" t="n">
-        <v>6880.75</v>
+        <v>6870.25</v>
       </c>
       <c r="N10" t="n">
-        <v>6993.38</v>
+        <v>6970.12</v>
       </c>
       <c r="O10" t="n">
-        <v>7163.5</v>
+        <v>7130.5</v>
       </c>
       <c r="P10" s="6" t="n">
         <v/>
@@ -1361,18 +1353,18 @@
       <c r="Q10" s="6" t="n">
         <v/>
       </c>
-      <c r="R10" s="6" t="n">
-        <v/>
+      <c r="R10" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="S10" s="10" t="inlineStr">
         <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T10" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T10" s="8" t="n">
+        <v/>
       </c>
       <c r="U10" s="8" t="n">
         <v/>
@@ -1385,59 +1377,55 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X10" t="inlineStr">
-        <is>
-          <t>中警訊</t>
-        </is>
-      </c>
+      <c r="X10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2025-11-17</t>
+          <t>2025-11-24</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>6764.75</v>
+        <v>6654.75</v>
       </c>
       <c r="C11" t="n">
-        <v>6801.5</v>
+        <v>6863.75</v>
       </c>
       <c r="D11" t="n">
-        <v>6525</v>
+        <v>6625</v>
       </c>
       <c r="E11" t="n">
-        <v>6620.25</v>
+        <v>6859.5</v>
       </c>
       <c r="F11" t="n">
-        <v>-135</v>
+        <v>239.25</v>
       </c>
       <c r="G11" s="5" t="n">
-        <v>-0.02</v>
+        <v>0.0361</v>
       </c>
       <c r="H11" t="n">
-        <v>276.5</v>
+        <v>238.75</v>
       </c>
       <c r="I11" t="n">
-        <v>6440.5</v>
+        <v>6248.5</v>
       </c>
       <c r="J11" t="n">
-        <v>6510.12</v>
+        <v>6322.25</v>
       </c>
       <c r="K11" t="n">
-        <v>6640.25</v>
+        <v>6482</v>
       </c>
       <c r="L11" t="n">
-        <v>6770.38</v>
+        <v>6641.75</v>
       </c>
       <c r="M11" t="n">
-        <v>6870.25</v>
+        <v>6758.5</v>
       </c>
       <c r="N11" t="n">
-        <v>6970.12</v>
+        <v>6875.25</v>
       </c>
       <c r="O11" t="n">
-        <v>7130.5</v>
+        <v>7078</v>
       </c>
       <c r="P11" s="6" t="n">
         <v/>
@@ -1445,22 +1433,24 @@
       <c r="Q11" s="6" t="n">
         <v/>
       </c>
-      <c r="R11" s="6" t="inlineStr">
+      <c r="R11" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S11" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T11" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U11" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="S11" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T11" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U11" s="8" t="n">
-        <v/>
-      </c>
       <c r="V11" s="8" t="n">
         <v/>
       </c>
@@ -1469,55 +1459,59 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X11" t="inlineStr"/>
+      <c r="X11" t="inlineStr">
+        <is>
+          <t>強警訊</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2025-11-24</t>
+          <t>2025-12-01</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>6654.75</v>
+        <v>6854.75</v>
       </c>
       <c r="C12" t="n">
-        <v>6863.75</v>
+        <v>6905</v>
       </c>
       <c r="D12" t="n">
-        <v>6625</v>
+        <v>6802</v>
       </c>
       <c r="E12" t="n">
-        <v>6859.5</v>
+        <v>6878.25</v>
       </c>
       <c r="F12" t="n">
-        <v>239.25</v>
+        <v>18.75</v>
       </c>
       <c r="G12" s="5" t="n">
-        <v>0.0361</v>
+        <v>0.0027</v>
       </c>
       <c r="H12" t="n">
-        <v>238.75</v>
+        <v>103</v>
       </c>
       <c r="I12" t="n">
-        <v>6248.5</v>
+        <v>6386.25</v>
       </c>
       <c r="J12" t="n">
-        <v>6322.25</v>
+        <v>6678.31</v>
       </c>
       <c r="K12" t="n">
-        <v>6482</v>
+        <v>6740.12</v>
       </c>
       <c r="L12" t="n">
-        <v>6641.75</v>
+        <v>6801.94</v>
       </c>
       <c r="M12" t="n">
-        <v>6758.5</v>
+        <v>6978.88</v>
       </c>
       <c r="N12" t="n">
-        <v>6875.25</v>
+        <v>7155.81</v>
       </c>
       <c r="O12" t="n">
-        <v>7078</v>
+        <v>7102.5</v>
       </c>
       <c r="P12" s="6" t="n">
         <v/>
@@ -1530,18 +1524,14 @@
       </c>
       <c r="S12" s="7" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T12" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U12" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T12" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U12" s="8" t="n">
+        <v/>
       </c>
       <c r="V12" s="8" t="n">
         <v/>
@@ -1560,50 +1550,50 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2025-12-01</t>
+          <t>2025-12-08</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>6854.75</v>
+        <v>6883</v>
       </c>
       <c r="C13" t="n">
-        <v>6905</v>
+        <v>6928.75</v>
       </c>
       <c r="D13" t="n">
-        <v>6802</v>
+        <v>6805</v>
       </c>
       <c r="E13" t="n">
-        <v>6878.25</v>
+        <v>6830.75</v>
       </c>
       <c r="F13" t="n">
-        <v>18.75</v>
+        <v>-47.5</v>
       </c>
       <c r="G13" s="5" t="n">
-        <v>0.0027</v>
+        <v>-0.0069</v>
       </c>
       <c r="H13" t="n">
-        <v>103</v>
+        <v>123.75</v>
       </c>
       <c r="I13" t="n">
-        <v>6386.25</v>
+        <v>6699</v>
       </c>
       <c r="J13" t="n">
-        <v>6678.31</v>
+        <v>6787.62</v>
       </c>
       <c r="K13" t="n">
-        <v>6740.12</v>
+        <v>6826.75</v>
       </c>
       <c r="L13" t="n">
-        <v>6801.94</v>
+        <v>6865.88</v>
       </c>
       <c r="M13" t="n">
-        <v>6978.88</v>
+        <v>6929.75</v>
       </c>
       <c r="N13" t="n">
-        <v>7155.81</v>
+        <v>6993.62</v>
       </c>
       <c r="O13" t="n">
-        <v>7102.5</v>
+        <v>7008</v>
       </c>
       <c r="P13" s="6" t="n">
         <v/>
@@ -1611,12 +1601,14 @@
       <c r="Q13" s="6" t="n">
         <v/>
       </c>
-      <c r="R13" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S13" s="7" t="inlineStr">
-        <is>
-          <t>↑C</t>
+      <c r="R13" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="S13" s="10" t="inlineStr">
+        <is>
+          <t>↓</t>
         </is>
       </c>
       <c r="T13" s="8" t="n">
@@ -1635,57 +1627,57 @@
       </c>
       <c r="X13" t="inlineStr">
         <is>
-          <t>強警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2025-12-08</t>
+          <t>2025-12-15</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>6883</v>
+        <v>6831</v>
       </c>
       <c r="C14" t="n">
-        <v>6928.75</v>
+        <v>6872.5</v>
       </c>
       <c r="D14" t="n">
-        <v>6805</v>
+        <v>6720.25</v>
       </c>
       <c r="E14" t="n">
-        <v>6830.75</v>
+        <v>6796.54</v>
       </c>
       <c r="F14" t="n">
-        <v>-47.5</v>
+        <v>-34.21</v>
       </c>
       <c r="G14" s="5" t="n">
-        <v>-0.0069</v>
+        <v>-0.005</v>
       </c>
       <c r="H14" t="n">
-        <v>123.75</v>
+        <v>152.25</v>
       </c>
       <c r="I14" t="n">
-        <v>6699</v>
+        <v>6681.25</v>
       </c>
       <c r="J14" t="n">
-        <v>6787.62</v>
+        <v>6688.94</v>
       </c>
       <c r="K14" t="n">
-        <v>6826.75</v>
+        <v>6768.88</v>
       </c>
       <c r="L14" t="n">
-        <v>6865.88</v>
+        <v>6848.81</v>
       </c>
       <c r="M14" t="n">
-        <v>6929.75</v>
+        <v>6892.62</v>
       </c>
       <c r="N14" t="n">
-        <v>6993.62</v>
+        <v>6936.44</v>
       </c>
       <c r="O14" t="n">
-        <v>7008</v>
+        <v>7052.5</v>
       </c>
       <c r="P14" s="6" t="n">
         <v/>
@@ -1717,59 +1709,55 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X14" t="inlineStr">
-        <is>
-          <t>中警訊</t>
-        </is>
-      </c>
+      <c r="X14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2025-12-15</t>
+          <t>2025-12-22</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>6831</v>
+        <v>6906.25</v>
       </c>
       <c r="C15" t="n">
-        <v>6872.5</v>
+        <v>6994</v>
       </c>
       <c r="D15" t="n">
-        <v>6720.25</v>
+        <v>6900.5</v>
       </c>
       <c r="E15" t="n">
-        <v>6796.54</v>
+        <v>6979.25</v>
       </c>
       <c r="F15" t="n">
-        <v>-34.21</v>
+        <v>182.71</v>
       </c>
       <c r="G15" s="5" t="n">
-        <v>-0.005</v>
+        <v>0.0269</v>
       </c>
       <c r="H15" t="n">
-        <v>152.25</v>
+        <v>93.5</v>
       </c>
       <c r="I15" t="n">
-        <v>6681.25</v>
+        <v>6568</v>
       </c>
       <c r="J15" t="n">
-        <v>6688.94</v>
+        <v>6644.37</v>
       </c>
       <c r="K15" t="n">
-        <v>6768.88</v>
+        <v>6720.42</v>
       </c>
       <c r="L15" t="n">
-        <v>6848.81</v>
+        <v>6796.46</v>
       </c>
       <c r="M15" t="n">
-        <v>6892.62</v>
+        <v>6872.67</v>
       </c>
       <c r="N15" t="n">
-        <v>6936.44</v>
+        <v>6948.87</v>
       </c>
       <c r="O15" t="n">
-        <v>7052.5</v>
+        <v>7024.75</v>
       </c>
       <c r="P15" s="6" t="n">
         <v/>
@@ -1777,28 +1765,30 @@
       <c r="Q15" s="6" t="n">
         <v/>
       </c>
-      <c r="R15" s="6" t="inlineStr">
+      <c r="R15" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S15" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T15" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U15" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="S15" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T15" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U15" s="8" t="n">
-        <v/>
-      </c>
       <c r="V15" s="8" t="n">
         <v/>
       </c>
-      <c r="W15" s="11" t="inlineStr">
-        <is>
-          <t>空方</t>
+      <c r="W15" s="9" t="inlineStr">
+        <is>
+          <t>多方</t>
         </is>
       </c>
       <c r="X15" t="inlineStr"/>
@@ -1806,81 +1796,81 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2025-12-22</t>
+          <t>2025-12-29</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>6906.25</v>
+        <v>6980.5</v>
       </c>
       <c r="C16" t="n">
-        <v>6994</v>
+        <v>6984.75</v>
       </c>
       <c r="D16" t="n">
+        <v>6866.75</v>
+      </c>
+      <c r="E16" t="n">
         <v>6900.5</v>
       </c>
-      <c r="E16" t="n">
-        <v>6979.25</v>
-      </c>
       <c r="F16" t="n">
-        <v>182.71</v>
+        <v>-78.75</v>
       </c>
       <c r="G16" s="5" t="n">
-        <v>0.0269</v>
+        <v>-0.0113</v>
       </c>
       <c r="H16" t="n">
-        <v>93.5</v>
+        <v>118</v>
       </c>
       <c r="I16" t="n">
-        <v>6568</v>
+        <v>6807</v>
       </c>
       <c r="J16" t="n">
-        <v>6644.37</v>
+        <v>6901.75</v>
       </c>
       <c r="K16" t="n">
-        <v>6720.42</v>
+        <v>6932.5</v>
       </c>
       <c r="L16" t="n">
-        <v>6796.46</v>
+        <v>6963.25</v>
       </c>
       <c r="M16" t="n">
-        <v>6872.67</v>
+        <v>7026</v>
       </c>
       <c r="N16" t="n">
-        <v>6948.87</v>
+        <v>7088.75</v>
       </c>
       <c r="O16" t="n">
-        <v>7024.75</v>
+        <v>7087.5</v>
       </c>
       <c r="P16" s="6" t="n">
         <v/>
       </c>
-      <c r="Q16" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R16" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S16" s="7" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T16" s="8" t="inlineStr">
+      <c r="Q16" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="R16" s="6" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="U16" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+      <c r="S16" s="10" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T16" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U16" s="8" t="n">
+        <v/>
       </c>
       <c r="V16" s="8" t="n">
         <v/>
       </c>
-      <c r="W16" s="9" t="inlineStr">
-        <is>
-          <t>多方</t>
+      <c r="W16" s="11" t="inlineStr">
+        <is>
+          <t>空方</t>
         </is>
       </c>
       <c r="X16" t="inlineStr"/>
@@ -1888,75 +1878,75 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2025-12-29</t>
+          <t>2026-01-05</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>6980.5</v>
+        <v>6911.5</v>
       </c>
       <c r="C17" t="n">
-        <v>6984.75</v>
+        <v>7017.5</v>
       </c>
       <c r="D17" t="n">
-        <v>6866.75</v>
+        <v>6899.5</v>
       </c>
       <c r="E17" t="n">
-        <v>6900.5</v>
+        <v>7005</v>
       </c>
       <c r="F17" t="n">
-        <v>-78.75</v>
+        <v>104.5</v>
       </c>
       <c r="G17" s="5" t="n">
-        <v>-0.0113</v>
+        <v>0.0151</v>
       </c>
       <c r="H17" t="n">
         <v>118</v>
       </c>
       <c r="I17" t="n">
-        <v>6807</v>
+        <v>6748.75</v>
       </c>
       <c r="J17" t="n">
-        <v>6901.75</v>
+        <v>6769.88</v>
       </c>
       <c r="K17" t="n">
-        <v>6932.5</v>
+        <v>6841.5</v>
       </c>
       <c r="L17" t="n">
-        <v>6963.25</v>
+        <v>6913.12</v>
       </c>
       <c r="M17" t="n">
-        <v>7026</v>
+        <v>6959.5</v>
       </c>
       <c r="N17" t="n">
-        <v>7088.75</v>
+        <v>7005.88</v>
       </c>
       <c r="O17" t="n">
-        <v>7087.5</v>
+        <v>7102.75</v>
       </c>
       <c r="P17" s="6" t="n">
         <v/>
       </c>
-      <c r="Q17" s="6" t="inlineStr">
+      <c r="Q17" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R17" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S17" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T17" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U17" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="R17" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S17" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T17" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U17" s="8" t="n">
-        <v/>
-      </c>
       <c r="V17" s="8" t="n">
         <v/>
       </c>
@@ -1965,55 +1955,59 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X17" t="inlineStr"/>
+      <c r="X17" t="inlineStr">
+        <is>
+          <t>強警訊</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2026-01-05</t>
+          <t>2026-01-12</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>6911.5</v>
+        <v>7007</v>
       </c>
       <c r="C18" t="n">
-        <v>7017.5</v>
+        <v>7036.25</v>
       </c>
       <c r="D18" t="n">
-        <v>6899.5</v>
+        <v>6923.25</v>
       </c>
       <c r="E18" t="n">
-        <v>7005</v>
+        <v>6976.75</v>
       </c>
       <c r="F18" t="n">
-        <v>104.5</v>
+        <v>-28.25</v>
       </c>
       <c r="G18" s="5" t="n">
-        <v>0.0151</v>
+        <v>-0.004</v>
       </c>
       <c r="H18" t="n">
-        <v>118</v>
+        <v>113</v>
       </c>
       <c r="I18" t="n">
-        <v>6748.75</v>
+        <v>6781.5</v>
       </c>
       <c r="J18" t="n">
-        <v>6769.88</v>
+        <v>6910.25</v>
       </c>
       <c r="K18" t="n">
-        <v>6841.5</v>
+        <v>6946</v>
       </c>
       <c r="L18" t="n">
-        <v>6913.12</v>
+        <v>6981.75</v>
       </c>
       <c r="M18" t="n">
-        <v>6959.5</v>
+        <v>7064</v>
       </c>
       <c r="N18" t="n">
-        <v>7005.88</v>
+        <v>7146.25</v>
       </c>
       <c r="O18" t="n">
-        <v>7102.75</v>
+        <v>7135.5</v>
       </c>
       <c r="P18" s="6" t="n">
         <v/>
@@ -2021,23 +2015,21 @@
       <c r="Q18" s="6" t="n">
         <v/>
       </c>
-      <c r="R18" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S18" s="7" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T18" s="8" t="inlineStr">
+      <c r="R18" s="6" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="U18" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+      <c r="S18" s="10" t="inlineStr">
+        <is>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T18" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U18" s="8" t="n">
+        <v/>
       </c>
       <c r="V18" s="8" t="n">
         <v/>
@@ -2049,72 +2041,74 @@
       </c>
       <c r="X18" t="inlineStr">
         <is>
-          <t>強警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-01-12</t>
+          <t>2026-01-19</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>7007</v>
+        <v>6918.25</v>
       </c>
       <c r="C19" t="n">
-        <v>7036.25</v>
+        <v>6969</v>
       </c>
       <c r="D19" t="n">
-        <v>6923.25</v>
+        <v>6814.5</v>
       </c>
       <c r="E19" t="n">
-        <v>6976.75</v>
+        <v>6945.75</v>
       </c>
       <c r="F19" t="n">
-        <v>-28.25</v>
+        <v>-31</v>
       </c>
       <c r="G19" s="5" t="n">
-        <v>-0.004</v>
+        <v>-0.0044</v>
       </c>
       <c r="H19" t="n">
-        <v>113</v>
+        <v>154.5</v>
       </c>
       <c r="I19" t="n">
-        <v>6781.5</v>
+        <v>6810.25</v>
       </c>
       <c r="J19" t="n">
-        <v>6910.25</v>
+        <v>6862.25</v>
       </c>
       <c r="K19" t="n">
-        <v>6946</v>
+        <v>6920.25</v>
       </c>
       <c r="L19" t="n">
-        <v>6981.75</v>
+        <v>6978.25</v>
       </c>
       <c r="M19" t="n">
-        <v>7064</v>
+        <v>7033.25</v>
       </c>
       <c r="N19" t="n">
-        <v>7146.25</v>
+        <v>7088.25</v>
       </c>
       <c r="O19" t="n">
-        <v>7135.5</v>
+        <v>7149.25</v>
       </c>
       <c r="P19" s="6" t="n">
         <v/>
       </c>
-      <c r="Q19" s="6" t="n">
-        <v/>
+      <c r="Q19" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="R19" s="6" t="inlineStr">
         <is>
-          <t>✓</t>
+          <t>△C</t>
         </is>
       </c>
       <c r="S19" s="10" t="inlineStr">
         <is>
-          <t>↓C</t>
+          <t>↓</t>
         </is>
       </c>
       <c r="T19" s="8" t="n">
@@ -2131,81 +2125,75 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X19" t="inlineStr">
-        <is>
-          <t>中警訊</t>
-        </is>
-      </c>
+      <c r="X19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2026-01-19</t>
+          <t>2026-01-26</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>6918.25</v>
+        <v>6904</v>
       </c>
       <c r="C20" t="n">
-        <v>6969</v>
+        <v>7043</v>
       </c>
       <c r="D20" t="n">
-        <v>6814.5</v>
+        <v>6879</v>
       </c>
       <c r="E20" t="n">
-        <v>6945.75</v>
+        <v>6965.75</v>
       </c>
       <c r="F20" t="n">
-        <v>-31</v>
+        <v>20</v>
       </c>
       <c r="G20" s="5" t="n">
-        <v>-0.0044</v>
+        <v>0.0029</v>
       </c>
       <c r="H20" t="n">
-        <v>154.5</v>
+        <v>164</v>
       </c>
       <c r="I20" t="n">
-        <v>6810.25</v>
+        <v>6660</v>
       </c>
       <c r="J20" t="n">
-        <v>6862.25</v>
+        <v>6818.25</v>
       </c>
       <c r="K20" t="n">
-        <v>6920.25</v>
+        <v>6868.5</v>
       </c>
       <c r="L20" t="n">
-        <v>6978.25</v>
+        <v>6918.75</v>
       </c>
       <c r="M20" t="n">
-        <v>7033.25</v>
+        <v>7023</v>
       </c>
       <c r="N20" t="n">
-        <v>7088.25</v>
+        <v>7127.25</v>
       </c>
       <c r="O20" t="n">
-        <v>7149.25</v>
+        <v>7123.5</v>
       </c>
       <c r="P20" s="6" t="n">
         <v/>
       </c>
-      <c r="Q20" s="6" t="inlineStr">
+      <c r="Q20" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R20" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S20" s="7" t="inlineStr">
+        <is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T20" s="8" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="R20" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="S20" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T20" s="8" t="n">
-        <v/>
-      </c>
       <c r="U20" s="8" t="n">
         <v/>
       </c>
@@ -2217,75 +2205,81 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X20" t="inlineStr"/>
+      <c r="X20" t="inlineStr">
+        <is>
+          <t>強警訊</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-01-26</t>
+          <t>2026-02-02</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>6904</v>
+        <v>6938.5</v>
       </c>
       <c r="C21" t="n">
-        <v>7043</v>
+        <v>7027.25</v>
       </c>
       <c r="D21" t="n">
-        <v>6879</v>
+        <v>6751.5</v>
       </c>
       <c r="E21" t="n">
-        <v>6965.75</v>
+        <v>6952.75</v>
       </c>
       <c r="F21" t="n">
-        <v>20</v>
+        <v>-13</v>
       </c>
       <c r="G21" s="5" t="n">
-        <v>0.0029</v>
+        <v>-0.0019</v>
       </c>
       <c r="H21" t="n">
-        <v>164</v>
+        <v>275.75</v>
       </c>
       <c r="I21" t="n">
-        <v>6660</v>
+        <v>6715</v>
       </c>
       <c r="J21" t="n">
-        <v>6818.25</v>
+        <v>6804.12</v>
       </c>
       <c r="K21" t="n">
-        <v>6868.5</v>
+        <v>6883.75</v>
       </c>
       <c r="L21" t="n">
-        <v>6918.75</v>
+        <v>6963.38</v>
       </c>
       <c r="M21" t="n">
-        <v>7023</v>
+        <v>7047.75</v>
       </c>
       <c r="N21" t="n">
-        <v>7127.25</v>
+        <v>7132.12</v>
       </c>
       <c r="O21" t="n">
-        <v>7123.5</v>
+        <v>7207</v>
       </c>
       <c r="P21" s="6" t="n">
         <v/>
       </c>
-      <c r="Q21" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R21" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S21" s="7" t="inlineStr">
-        <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T21" s="8" t="inlineStr">
+      <c r="Q21" s="6" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
+      <c r="R21" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S21" s="10" t="inlineStr">
+        <is>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T21" s="8" t="n">
+        <v/>
+      </c>
       <c r="U21" s="8" t="n">
         <v/>
       </c>
@@ -2297,76 +2291,70 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X21" t="inlineStr">
-        <is>
-          <t>強警訊</t>
-        </is>
-      </c>
+      <c r="X21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2026-02-02</t>
+          <t>2026-02-09</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>6938.5</v>
+        <v>6960.25</v>
       </c>
       <c r="C22" t="n">
-        <v>7027.25</v>
+        <v>7011.5</v>
       </c>
       <c r="D22" t="n">
-        <v>6751.5</v>
+        <v>6808.75</v>
       </c>
       <c r="E22" t="n">
-        <v>6952.75</v>
+        <v>6850.5</v>
       </c>
       <c r="F22" t="n">
-        <v>-13</v>
+        <v>-102.25</v>
       </c>
       <c r="G22" s="5" t="n">
-        <v>-0.0019</v>
+        <v>-0.0147</v>
       </c>
       <c r="H22" t="n">
-        <v>275.75</v>
+        <v>202.75</v>
       </c>
       <c r="I22" t="n">
-        <v>6715</v>
+        <v>6475.75</v>
       </c>
       <c r="J22" t="n">
-        <v>6804.12</v>
+        <v>6708.69</v>
       </c>
       <c r="K22" t="n">
-        <v>6883.75</v>
+        <v>6814.88</v>
       </c>
       <c r="L22" t="n">
-        <v>6963.38</v>
+        <v>6921.06</v>
       </c>
       <c r="M22" t="n">
-        <v>7047.75</v>
+        <v>7090.62</v>
       </c>
       <c r="N22" t="n">
-        <v>7132.12</v>
+        <v>7260.19</v>
       </c>
       <c r="O22" t="n">
-        <v>7207</v>
+        <v>7303</v>
       </c>
       <c r="P22" s="6" t="n">
         <v/>
       </c>
-      <c r="Q22" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="Q22" s="6" t="n">
+        <v/>
       </c>
       <c r="R22" s="6" t="inlineStr">
         <is>
-          <t>✓</t>
+          <t>△C</t>
         </is>
       </c>
       <c r="S22" s="10" t="inlineStr">
         <is>
-          <t>↓C</t>
+          <t>↓</t>
         </is>
       </c>
       <c r="T22" s="8" t="n">
@@ -2383,55 +2371,59 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X22" t="inlineStr"/>
+      <c r="X22" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-02-09</t>
+          <t>2026-02-16</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>6960.25</v>
+        <v>6852.5</v>
       </c>
       <c r="C23" t="n">
-        <v>7011.5</v>
+        <v>6931.5</v>
       </c>
       <c r="D23" t="n">
-        <v>6808.75</v>
+        <v>6791</v>
       </c>
       <c r="E23" t="n">
-        <v>6850.5</v>
+        <v>6923.25</v>
       </c>
       <c r="F23" t="n">
-        <v>-102.25</v>
+        <v>72.75</v>
       </c>
       <c r="G23" s="5" t="n">
-        <v>-0.0147</v>
+        <v>0.0106</v>
       </c>
       <c r="H23" t="n">
-        <v>202.75</v>
+        <v>140.5</v>
       </c>
       <c r="I23" t="n">
-        <v>6475.75</v>
+        <v>6606</v>
       </c>
       <c r="J23" t="n">
-        <v>6708.69</v>
+        <v>6617.94</v>
       </c>
       <c r="K23" t="n">
-        <v>6814.88</v>
+        <v>6749.12</v>
       </c>
       <c r="L23" t="n">
-        <v>6921.06</v>
+        <v>6880.31</v>
       </c>
       <c r="M23" t="n">
-        <v>7090.62</v>
+        <v>6951.88</v>
       </c>
       <c r="N23" t="n">
-        <v>7260.19</v>
+        <v>7023.44</v>
       </c>
       <c r="O23" t="n">
-        <v>7303</v>
+        <v>7214.25</v>
       </c>
       <c r="P23" s="6" t="n">
         <v/>
@@ -2439,18 +2431,18 @@
       <c r="Q23" s="6" t="n">
         <v/>
       </c>
-      <c r="R23" s="6" t="inlineStr">
+      <c r="R23" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S23" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T23" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
-      </c>
-      <c r="S23" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T23" s="8" t="n">
-        <v/>
       </c>
       <c r="U23" s="8" t="n">
         <v/>
@@ -2472,50 +2464,50 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2026-02-16</t>
+          <t>2026-02-23</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>6852.5</v>
+        <v>6918</v>
       </c>
       <c r="C24" t="n">
-        <v>6931.5</v>
+        <v>6983.75</v>
       </c>
       <c r="D24" t="n">
-        <v>6791</v>
+        <v>6828.5</v>
       </c>
       <c r="E24" t="n">
-        <v>6923.25</v>
+        <v>6889</v>
       </c>
       <c r="F24" t="n">
-        <v>72.75</v>
+        <v>-34.25</v>
       </c>
       <c r="G24" s="5" t="n">
-        <v>0.0106</v>
+        <v>-0.0049</v>
       </c>
       <c r="H24" t="n">
-        <v>140.5</v>
+        <v>155.25</v>
       </c>
       <c r="I24" t="n">
-        <v>6606</v>
+        <v>6650.5</v>
       </c>
       <c r="J24" t="n">
-        <v>6617.94</v>
+        <v>6813.75</v>
       </c>
       <c r="K24" t="n">
-        <v>6749.12</v>
+        <v>6853</v>
       </c>
       <c r="L24" t="n">
-        <v>6880.31</v>
+        <v>6892.25</v>
       </c>
       <c r="M24" t="n">
-        <v>6951.88</v>
+        <v>6993.5</v>
       </c>
       <c r="N24" t="n">
-        <v>7023.44</v>
+        <v>7094.75</v>
       </c>
       <c r="O24" t="n">
-        <v>7214.25</v>
+        <v>7072</v>
       </c>
       <c r="P24" s="6" t="n">
         <v/>
@@ -2523,18 +2515,18 @@
       <c r="Q24" s="6" t="n">
         <v/>
       </c>
-      <c r="R24" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S24" s="7" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T24" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+      <c r="R24" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S24" s="10" t="inlineStr">
+        <is>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T24" s="8" t="n">
+        <v/>
       </c>
       <c r="U24" s="8" t="n">
         <v/>
@@ -2549,63 +2541,65 @@
       </c>
       <c r="X24" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-02-23</t>
+          <t>2026-03-02</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>6918</v>
+        <v>6820</v>
       </c>
       <c r="C25" t="n">
-        <v>6983.75</v>
+        <v>6911.25</v>
       </c>
       <c r="D25" t="n">
-        <v>6828.5</v>
+        <v>6715.75</v>
       </c>
       <c r="E25" t="n">
-        <v>6889</v>
+        <v>6743.75</v>
       </c>
       <c r="F25" t="n">
-        <v>-34.25</v>
+        <v>-145.25</v>
       </c>
       <c r="G25" s="5" t="n">
-        <v>-0.0049</v>
+        <v>-0.0211</v>
       </c>
       <c r="H25" t="n">
-        <v>155.25</v>
+        <v>195.5</v>
       </c>
       <c r="I25" t="n">
-        <v>6650.5</v>
+        <v>6673.25</v>
       </c>
       <c r="J25" t="n">
-        <v>6813.75</v>
+        <v>6725.19</v>
       </c>
       <c r="K25" t="n">
-        <v>6853</v>
+        <v>6811.38</v>
       </c>
       <c r="L25" t="n">
-        <v>6892.25</v>
+        <v>6897.56</v>
       </c>
       <c r="M25" t="n">
-        <v>6993.5</v>
+        <v>6966.62</v>
       </c>
       <c r="N25" t="n">
-        <v>7094.75</v>
+        <v>7035.69</v>
       </c>
       <c r="O25" t="n">
-        <v>7072</v>
+        <v>7139</v>
       </c>
       <c r="P25" s="6" t="n">
         <v/>
       </c>
-      <c r="Q25" s="6" t="n">
-        <v/>
+      <c r="Q25" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="R25" s="6" t="inlineStr">
         <is>
@@ -2614,7 +2608,7 @@
       </c>
       <c r="S25" s="10" t="inlineStr">
         <is>
-          <t>↓C</t>
+          <t>↓</t>
         </is>
       </c>
       <c r="T25" s="8" t="n">
@@ -2631,80 +2625,76 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X25" t="inlineStr">
-        <is>
-          <t>中警訊</t>
-        </is>
-      </c>
+      <c r="X25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-09</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>6820</v>
+        <v>6685.5</v>
       </c>
       <c r="C26" t="n">
-        <v>6911.25</v>
+        <v>6852</v>
       </c>
       <c r="D26" t="n">
-        <v>6715.75</v>
+        <v>6584.5</v>
       </c>
       <c r="E26" t="n">
-        <v>6743.75</v>
+        <v>6636</v>
       </c>
       <c r="F26" t="n">
-        <v>-145.25</v>
+        <v>-107.75</v>
       </c>
       <c r="G26" s="5" t="n">
-        <v>-0.0211</v>
+        <v>-0.016</v>
       </c>
       <c r="H26" t="n">
-        <v>195.5</v>
+        <v>267.5</v>
       </c>
       <c r="I26" t="n">
-        <v>6673.25</v>
+        <v>6520.25</v>
       </c>
       <c r="J26" t="n">
-        <v>6725.19</v>
+        <v>6513.38</v>
       </c>
       <c r="K26" t="n">
-        <v>6811.38</v>
+        <v>6646</v>
       </c>
       <c r="L26" t="n">
-        <v>6897.56</v>
+        <v>6778.62</v>
       </c>
       <c r="M26" t="n">
-        <v>6966.62</v>
+        <v>6841.5</v>
       </c>
       <c r="N26" t="n">
-        <v>7035.69</v>
+        <v>6904.38</v>
       </c>
       <c r="O26" t="n">
-        <v>7139</v>
+        <v>7106.75</v>
       </c>
       <c r="P26" s="6" t="n">
         <v/>
       </c>
-      <c r="Q26" s="6" t="inlineStr">
+      <c r="Q26" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R26" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="R26" s="6" t="inlineStr">
+      <c r="S26" s="10" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T26" s="8" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
-      </c>
-      <c r="S26" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T26" s="8" t="n">
-        <v/>
       </c>
       <c r="U26" s="8" t="n">
         <v/>
@@ -2722,50 +2712,50 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-03-16</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>6685.5</v>
+        <v>6608.5</v>
       </c>
       <c r="C27" t="n">
-        <v>6852</v>
+        <v>6762.25</v>
       </c>
       <c r="D27" t="n">
-        <v>6584.5</v>
+        <v>6558</v>
       </c>
       <c r="E27" t="n">
-        <v>6636</v>
+        <v>6594.63</v>
       </c>
       <c r="F27" t="n">
-        <v>-107.75</v>
+        <v>-41.37</v>
       </c>
       <c r="G27" s="5" t="n">
-        <v>-0.016</v>
+        <v>-0.0062</v>
       </c>
       <c r="H27" t="n">
-        <v>267.5</v>
+        <v>204.25</v>
       </c>
       <c r="I27" t="n">
-        <v>6520.25</v>
+        <v>6317</v>
       </c>
       <c r="J27" t="n">
-        <v>6513.38</v>
+        <v>6327.38</v>
       </c>
       <c r="K27" t="n">
-        <v>6646</v>
+        <v>6502.25</v>
       </c>
       <c r="L27" t="n">
-        <v>6778.62</v>
+        <v>6677.12</v>
       </c>
       <c r="M27" t="n">
-        <v>6841.5</v>
+        <v>6769.75</v>
       </c>
       <c r="N27" t="n">
-        <v>6904.38</v>
+        <v>6862.38</v>
       </c>
       <c r="O27" t="n">
-        <v>7106.75</v>
+        <v>7119.5</v>
       </c>
       <c r="P27" s="6" t="n">
         <v/>
@@ -2773,20 +2763,16 @@
       <c r="Q27" s="6" t="n">
         <v/>
       </c>
-      <c r="R27" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+      <c r="R27" s="6" t="n">
+        <v/>
       </c>
       <c r="S27" s="10" t="inlineStr">
         <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T27" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T27" s="8" t="n">
+        <v/>
       </c>
       <c r="U27" s="8" t="n">
         <v/>
@@ -2804,67 +2790,73 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-23</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>6608.5</v>
+        <v>6510</v>
       </c>
       <c r="C28" t="n">
-        <v>6762.25</v>
+        <v>6748</v>
       </c>
       <c r="D28" t="n">
-        <v>6558</v>
+        <v>6389</v>
       </c>
       <c r="E28" t="n">
-        <v>6594.63</v>
+        <v>6412.25</v>
       </c>
       <c r="F28" t="n">
-        <v>-41.37</v>
+        <v>-182.38</v>
       </c>
       <c r="G28" s="5" t="n">
-        <v>-0.0062</v>
+        <v>-0.0277</v>
       </c>
       <c r="H28" t="n">
-        <v>204.25</v>
+        <v>359</v>
       </c>
       <c r="I28" t="n">
-        <v>6317</v>
+        <v>6353.75</v>
       </c>
       <c r="J28" t="n">
-        <v>6327.38</v>
+        <v>6357.63</v>
       </c>
       <c r="K28" t="n">
-        <v>6502.25</v>
+        <v>6492.5</v>
       </c>
       <c r="L28" t="n">
-        <v>6677.12</v>
+        <v>6627.38</v>
       </c>
       <c r="M28" t="n">
-        <v>6769.75</v>
+        <v>6696.75</v>
       </c>
       <c r="N28" t="n">
-        <v>6862.38</v>
+        <v>6766.13</v>
       </c>
       <c r="O28" t="n">
-        <v>7119.5</v>
+        <v>6966.5</v>
       </c>
       <c r="P28" s="6" t="n">
         <v/>
       </c>
-      <c r="Q28" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R28" s="6" t="n">
-        <v/>
+      <c r="Q28" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="R28" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S28" s="10" t="inlineStr">
         <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T28" s="8" t="n">
-        <v/>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T28" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="U28" s="8" t="n">
         <v/>
@@ -2882,74 +2874,70 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-03-23</t>
+          <t>2026-03-30</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>6510</v>
+        <v>6380</v>
       </c>
       <c r="C29" t="n">
-        <v>6748</v>
+        <v>6653.75</v>
       </c>
       <c r="D29" t="n">
-        <v>6389</v>
+        <v>6353.25</v>
       </c>
       <c r="E29" t="n">
-        <v>6412.25</v>
+        <v>6603.75</v>
       </c>
       <c r="F29" t="n">
-        <v>-182.38</v>
+        <v>191.5</v>
       </c>
       <c r="G29" s="5" t="n">
-        <v>-0.0277</v>
+        <v>0.0299</v>
       </c>
       <c r="H29" t="n">
-        <v>359</v>
+        <v>300.5</v>
       </c>
       <c r="I29" t="n">
-        <v>6353.75</v>
+        <v>6030</v>
       </c>
       <c r="J29" t="n">
-        <v>6357.63</v>
+        <v>5975.12</v>
       </c>
       <c r="K29" t="n">
-        <v>6492.5</v>
+        <v>6232.75</v>
       </c>
       <c r="L29" t="n">
-        <v>6627.38</v>
+        <v>6490.38</v>
       </c>
       <c r="M29" t="n">
-        <v>6696.75</v>
+        <v>6591.75</v>
       </c>
       <c r="N29" t="n">
-        <v>6766.13</v>
+        <v>6693.12</v>
       </c>
       <c r="O29" t="n">
-        <v>6966.5</v>
+        <v>7107</v>
       </c>
       <c r="P29" s="6" t="n">
         <v/>
       </c>
-      <c r="Q29" s="6" t="inlineStr">
+      <c r="Q29" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R29" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S29" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T29" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="R29" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S29" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T29" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
       <c r="U29" s="8" t="n">
         <v/>
       </c>
@@ -2961,55 +2949,59 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X29" t="inlineStr"/>
+      <c r="X29" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-04-06</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>6380</v>
+        <v>6590</v>
       </c>
       <c r="C30" t="n">
-        <v>6653.75</v>
+        <v>6888</v>
       </c>
       <c r="D30" t="n">
-        <v>6353.25</v>
+        <v>6567</v>
       </c>
       <c r="E30" t="n">
-        <v>6603.75</v>
+        <v>6855.25</v>
       </c>
       <c r="F30" t="n">
-        <v>191.5</v>
+        <v>251.5</v>
       </c>
       <c r="G30" s="5" t="n">
-        <v>0.0299</v>
+        <v>0.0381</v>
       </c>
       <c r="H30" t="n">
-        <v>300.5</v>
+        <v>321</v>
       </c>
       <c r="I30" t="n">
-        <v>6030</v>
+        <v>6052.75</v>
       </c>
       <c r="J30" t="n">
-        <v>5975.12</v>
+        <v>6353.38</v>
       </c>
       <c r="K30" t="n">
-        <v>6232.75</v>
+        <v>6453.5</v>
       </c>
       <c r="L30" t="n">
-        <v>6490.38</v>
+        <v>6553.62</v>
       </c>
       <c r="M30" t="n">
-        <v>6591.75</v>
+        <v>6754</v>
       </c>
       <c r="N30" t="n">
-        <v>6693.12</v>
+        <v>6954.38</v>
       </c>
       <c r="O30" t="n">
-        <v>7107</v>
+        <v>6954.25</v>
       </c>
       <c r="P30" s="6" t="n">
         <v/>
@@ -3027,15 +3019,17 @@
       </c>
       <c r="T30" s="8" t="inlineStr">
         <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U30" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V30" s="8" t="inlineStr">
+        <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="U30" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V30" s="8" t="n">
-        <v/>
-      </c>
       <c r="W30" s="11" t="inlineStr">
         <is>
           <t>空方</t>
@@ -3043,57 +3037,57 @@
       </c>
       <c r="X30" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026-04-06</t>
+          <t>2026-04-13</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>6590</v>
+        <v>6780</v>
       </c>
       <c r="C31" t="n">
-        <v>6888</v>
+        <v>7185.75</v>
       </c>
       <c r="D31" t="n">
-        <v>6567</v>
+        <v>6767</v>
       </c>
       <c r="E31" t="n">
-        <v>6855.25</v>
+        <v>7161.5</v>
       </c>
       <c r="F31" t="n">
-        <v>251.5</v>
+        <v>306.25</v>
       </c>
       <c r="G31" s="5" t="n">
-        <v>0.0381</v>
+        <v>0.0447</v>
       </c>
       <c r="H31" t="n">
-        <v>321</v>
+        <v>418.75</v>
       </c>
       <c r="I31" t="n">
-        <v>6052.75</v>
+        <v>6246</v>
       </c>
       <c r="J31" t="n">
-        <v>6353.38</v>
+        <v>6598.12</v>
       </c>
       <c r="K31" t="n">
-        <v>6453.5</v>
+        <v>6694.75</v>
       </c>
       <c r="L31" t="n">
-        <v>6553.62</v>
+        <v>6791.38</v>
       </c>
       <c r="M31" t="n">
-        <v>6754</v>
+        <v>7015.75</v>
       </c>
       <c r="N31" t="n">
-        <v>6954.38</v>
+        <v>7240.12</v>
       </c>
       <c r="O31" t="n">
-        <v>6954.25</v>
+        <v>7209</v>
       </c>
       <c r="P31" s="6" t="n">
         <v/>
@@ -3136,50 +3130,50 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2026-04-13</t>
+          <t>2026-04-20</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>6780</v>
+        <v>7102.5</v>
       </c>
       <c r="C32" t="n">
-        <v>7185.75</v>
+        <v>7200.5</v>
       </c>
       <c r="D32" t="n">
-        <v>6767</v>
+        <v>7079.25</v>
       </c>
       <c r="E32" t="n">
-        <v>7161.5</v>
+        <v>7194.75</v>
       </c>
       <c r="F32" t="n">
-        <v>306.25</v>
+        <v>33.25</v>
       </c>
       <c r="G32" s="5" t="n">
-        <v>0.0447</v>
+        <v>0.0046</v>
       </c>
       <c r="H32" t="n">
-        <v>418.75</v>
+        <v>121.25</v>
       </c>
       <c r="I32" t="n">
-        <v>6246</v>
+        <v>6348.25</v>
       </c>
       <c r="J32" t="n">
-        <v>6598.12</v>
+        <v>6835.31</v>
       </c>
       <c r="K32" t="n">
-        <v>6694.75</v>
+        <v>6952.12</v>
       </c>
       <c r="L32" t="n">
-        <v>6791.38</v>
+        <v>7068.94</v>
       </c>
       <c r="M32" t="n">
-        <v>7015.75</v>
+        <v>7370.88</v>
       </c>
       <c r="N32" t="n">
-        <v>7240.12</v>
+        <v>7672.81</v>
       </c>
       <c r="O32" t="n">
-        <v>7209</v>
+        <v>7604.5</v>
       </c>
       <c r="P32" s="6" t="n">
         <v/>
@@ -3192,21 +3186,17 @@
       </c>
       <c r="S32" s="7" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T32" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T32" s="8" t="n">
+        <v/>
       </c>
       <c r="U32" s="8" t="n">
         <v/>
       </c>
-      <c r="V32" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+      <c r="V32" s="8" t="n">
+        <v/>
       </c>
       <c r="W32" s="11" t="inlineStr">
         <is>
@@ -3222,50 +3212,50 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
+          <t>2026-04-27</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>7102.5</v>
+        <v>7185</v>
       </c>
       <c r="C33" t="n">
-        <v>7200.5</v>
+        <v>7300.75</v>
       </c>
       <c r="D33" t="n">
-        <v>7079.25</v>
+        <v>7131.25</v>
       </c>
       <c r="E33" t="n">
-        <v>7194.75</v>
+        <v>7258</v>
       </c>
       <c r="F33" t="n">
-        <v>33.25</v>
+        <v>63.25</v>
       </c>
       <c r="G33" s="5" t="n">
-        <v>0.0046</v>
+        <v>0.008800000000000001</v>
       </c>
       <c r="H33" t="n">
-        <v>121.25</v>
+        <v>169.5</v>
       </c>
       <c r="I33" t="n">
-        <v>6348.25</v>
+        <v>6958</v>
       </c>
       <c r="J33" t="n">
-        <v>6835.31</v>
+        <v>7100.94</v>
       </c>
       <c r="K33" t="n">
-        <v>6952.12</v>
+        <v>7134.12</v>
       </c>
       <c r="L33" t="n">
-        <v>7068.94</v>
+        <v>7167.31</v>
       </c>
       <c r="M33" t="n">
-        <v>7370.88</v>
+        <v>7255.38</v>
       </c>
       <c r="N33" t="n">
-        <v>7672.81</v>
+        <v>7343.44</v>
       </c>
       <c r="O33" t="n">
-        <v>7604.5</v>
+        <v>7321.75</v>
       </c>
       <c r="P33" s="6" t="n">
         <v/>
@@ -3273,16 +3263,20 @@
       <c r="Q33" s="6" t="n">
         <v/>
       </c>
-      <c r="R33" s="6" t="n">
-        <v/>
+      <c r="R33" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S33" s="7" t="inlineStr">
         <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T33" s="8" t="n">
-        <v/>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T33" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="U33" s="8" t="n">
         <v/>
@@ -3304,50 +3298,50 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-05-04</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>7185</v>
+        <v>7276.25</v>
       </c>
       <c r="C34" t="n">
-        <v>7300.75</v>
+        <v>7427.75</v>
       </c>
       <c r="D34" t="n">
-        <v>7131.25</v>
+        <v>7199.5</v>
       </c>
       <c r="E34" t="n">
-        <v>7258</v>
+        <v>7419</v>
       </c>
       <c r="F34" t="n">
-        <v>63.25</v>
+        <v>161</v>
       </c>
       <c r="G34" s="5" t="n">
-        <v>0.008800000000000001</v>
+        <v>0.0222</v>
       </c>
       <c r="H34" t="n">
-        <v>169.5</v>
+        <v>228.25</v>
       </c>
       <c r="I34" t="n">
-        <v>6958</v>
+        <v>6961.75</v>
       </c>
       <c r="J34" t="n">
-        <v>7100.94</v>
+        <v>7109.5</v>
       </c>
       <c r="K34" t="n">
-        <v>7134.12</v>
+        <v>7173.25</v>
       </c>
       <c r="L34" t="n">
-        <v>7167.31</v>
+        <v>7237</v>
       </c>
       <c r="M34" t="n">
-        <v>7255.38</v>
+        <v>7342.75</v>
       </c>
       <c r="N34" t="n">
-        <v>7343.44</v>
+        <v>7448.5</v>
       </c>
       <c r="O34" t="n">
-        <v>7321.75</v>
+        <v>7470.25</v>
       </c>
       <c r="P34" s="6" t="n">
         <v/>
@@ -3355,23 +3349,23 @@
       <c r="Q34" s="6" t="n">
         <v/>
       </c>
-      <c r="R34" s="6" t="inlineStr">
+      <c r="R34" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S34" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T34" s="8" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="S34" s="7" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T34" s="8" t="inlineStr">
+      <c r="U34" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
-      </c>
-      <c r="U34" s="8" t="n">
-        <v/>
       </c>
       <c r="V34" s="8" t="n">
         <v/>
@@ -3390,50 +3384,50 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2026-05-04</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>7276.25</v>
+        <v>7403.5</v>
       </c>
       <c r="C35" t="n">
-        <v>7427.75</v>
+        <v>7540</v>
       </c>
       <c r="D35" t="n">
-        <v>7199.5</v>
+        <v>7363.25</v>
       </c>
       <c r="E35" t="n">
-        <v>7419</v>
+        <v>7432.25</v>
       </c>
       <c r="F35" t="n">
-        <v>161</v>
+        <v>13.25</v>
       </c>
       <c r="G35" s="5" t="n">
-        <v>0.0222</v>
+        <v>0.0018</v>
       </c>
       <c r="H35" t="n">
-        <v>228.25</v>
+        <v>176.75</v>
       </c>
       <c r="I35" t="n">
-        <v>6961.75</v>
+        <v>6971.25</v>
       </c>
       <c r="J35" t="n">
-        <v>7109.5</v>
+        <v>7243.44</v>
       </c>
       <c r="K35" t="n">
-        <v>7173.25</v>
+        <v>7304.88</v>
       </c>
       <c r="L35" t="n">
-        <v>7237</v>
+        <v>7366.31</v>
       </c>
       <c r="M35" t="n">
-        <v>7342.75</v>
+        <v>7533.12</v>
       </c>
       <c r="N35" t="n">
-        <v>7448.5</v>
+        <v>7699.94</v>
       </c>
       <c r="O35" t="n">
-        <v>7470.25</v>
+        <v>7656</v>
       </c>
       <c r="P35" s="6" t="n">
         <v/>
@@ -3446,7 +3440,7 @@
       </c>
       <c r="S35" s="7" t="inlineStr">
         <is>
-          <t>↑</t>
+          <t>↑C</t>
         </is>
       </c>
       <c r="T35" s="8" t="inlineStr">
@@ -3454,10 +3448,8 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="U35" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+      <c r="U35" s="8" t="n">
+        <v/>
       </c>
       <c r="V35" s="8" t="n">
         <v/>
@@ -3476,50 +3468,50 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-05-18</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>7403.5</v>
+        <v>7410</v>
       </c>
       <c r="C36" t="n">
-        <v>7540</v>
+        <v>7524</v>
       </c>
       <c r="D36" t="n">
-        <v>7363.25</v>
+        <v>7354.25</v>
       </c>
       <c r="E36" t="n">
-        <v>7432.25</v>
+        <v>7491</v>
       </c>
       <c r="F36" t="n">
-        <v>13.25</v>
+        <v>58.75</v>
       </c>
       <c r="G36" s="5" t="n">
-        <v>0.0018</v>
+        <v>0.007900000000000001</v>
       </c>
       <c r="H36" t="n">
-        <v>176.75</v>
+        <v>169.75</v>
       </c>
       <c r="I36" t="n">
-        <v>6971.25</v>
+        <v>7186.5</v>
       </c>
       <c r="J36" t="n">
-        <v>7243.44</v>
+        <v>7245.81</v>
       </c>
       <c r="K36" t="n">
-        <v>7304.88</v>
+        <v>7343.88</v>
       </c>
       <c r="L36" t="n">
-        <v>7366.31</v>
+        <v>7441.94</v>
       </c>
       <c r="M36" t="n">
-        <v>7533.12</v>
+        <v>7520.62</v>
       </c>
       <c r="N36" t="n">
-        <v>7699.94</v>
+        <v>7599.31</v>
       </c>
       <c r="O36" t="n">
-        <v>7656</v>
+        <v>7716.75</v>
       </c>
       <c r="P36" s="6" t="n">
         <v/>
@@ -3532,12 +3524,12 @@
       </c>
       <c r="S36" s="7" t="inlineStr">
         <is>
-          <t>↑C</t>
+          <t>↑</t>
         </is>
       </c>
       <c r="T36" s="8" t="inlineStr">
         <is>
-          <t>✓</t>
+          <t>△C</t>
         </is>
       </c>
       <c r="U36" s="8" t="n">
@@ -3553,57 +3545,57 @@
       </c>
       <c r="X36" t="inlineStr">
         <is>
-          <t>強警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-05-25</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>7410</v>
+        <v>7519</v>
       </c>
       <c r="C37" t="n">
-        <v>7524</v>
+        <v>7611.5</v>
       </c>
       <c r="D37" t="n">
-        <v>7354.25</v>
+        <v>7505.75</v>
       </c>
       <c r="E37" t="n">
-        <v>7491</v>
+        <v>7595.75</v>
       </c>
       <c r="F37" t="n">
-        <v>58.75</v>
+        <v>104.75</v>
       </c>
       <c r="G37" s="5" t="n">
-        <v>0.007900000000000001</v>
+        <v>0.014</v>
       </c>
       <c r="H37" t="n">
-        <v>169.75</v>
+        <v>105.75</v>
       </c>
       <c r="I37" t="n">
-        <v>7186.5</v>
+        <v>7184.5</v>
       </c>
       <c r="J37" t="n">
-        <v>7245.81</v>
+        <v>7347.19</v>
       </c>
       <c r="K37" t="n">
-        <v>7343.88</v>
+        <v>7406.12</v>
       </c>
       <c r="L37" t="n">
-        <v>7441.94</v>
+        <v>7465.06</v>
       </c>
       <c r="M37" t="n">
-        <v>7520.62</v>
+        <v>7575.88</v>
       </c>
       <c r="N37" t="n">
-        <v>7599.31</v>
+        <v>7686.69</v>
       </c>
       <c r="O37" t="n">
-        <v>7716.75</v>
+        <v>7693.75</v>
       </c>
       <c r="P37" s="6" t="n">
         <v/>
@@ -3637,77 +3629,81 @@
       </c>
       <c r="X37" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>2026-05-25</t>
+          <t>2026-06-01</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>7519</v>
+        <v>7595</v>
       </c>
       <c r="C38" t="n">
-        <v>7611.5</v>
+        <v>7632.25</v>
       </c>
       <c r="D38" t="n">
-        <v>7505.75</v>
+        <v>7359</v>
       </c>
       <c r="E38" t="n">
-        <v>7595.75</v>
+        <v>7400.5</v>
       </c>
       <c r="F38" t="n">
-        <v>104.75</v>
+        <v>-195.25</v>
       </c>
       <c r="G38" s="5" t="n">
-        <v>0.014</v>
+        <v>-0.0257</v>
       </c>
       <c r="H38" t="n">
-        <v>105.75</v>
+        <v>273.25</v>
       </c>
       <c r="I38" t="n">
-        <v>7184.5</v>
+        <v>7400</v>
       </c>
       <c r="J38" t="n">
-        <v>7347.19</v>
+        <v>7508.56</v>
       </c>
       <c r="K38" t="n">
-        <v>7406.12</v>
+        <v>7542.88</v>
       </c>
       <c r="L38" t="n">
-        <v>7465.06</v>
+        <v>7577.19</v>
       </c>
       <c r="M38" t="n">
-        <v>7575.88</v>
+        <v>7648.62</v>
       </c>
       <c r="N38" t="n">
-        <v>7686.69</v>
+        <v>7720.06</v>
       </c>
       <c r="O38" t="n">
-        <v>7693.75</v>
-      </c>
-      <c r="P38" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q38" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R38" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S38" s="7" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T38" s="8" t="inlineStr">
+        <v>7717.25</v>
+      </c>
+      <c r="P38" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
+      <c r="Q38" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="R38" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S38" s="10" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T38" s="8" t="n">
+        <v/>
+      </c>
       <c r="U38" s="8" t="n">
         <v/>
       </c>
@@ -3721,76 +3717,72 @@
       </c>
       <c r="X38" t="inlineStr">
         <is>
-          <t>強警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-06-08</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>7595</v>
+        <v>7368</v>
       </c>
       <c r="C39" t="n">
-        <v>7632.25</v>
+        <v>7491</v>
       </c>
       <c r="D39" t="n">
-        <v>7359</v>
+        <v>7232.25</v>
       </c>
       <c r="E39" t="n">
-        <v>7400.5</v>
+        <v>7435</v>
       </c>
       <c r="F39" t="n">
-        <v>-195.25</v>
+        <v>34.5</v>
       </c>
       <c r="G39" s="5" t="n">
-        <v>-0.0257</v>
+        <v>0.0047</v>
       </c>
       <c r="H39" t="n">
-        <v>273.25</v>
+        <v>258.75</v>
       </c>
       <c r="I39" t="n">
-        <v>7400</v>
+        <v>7085.75</v>
       </c>
       <c r="J39" t="n">
-        <v>7508.56</v>
+        <v>7079.69</v>
       </c>
       <c r="K39" t="n">
-        <v>7542.88</v>
+        <v>7263.88</v>
       </c>
       <c r="L39" t="n">
-        <v>7577.19</v>
+        <v>7448.06</v>
       </c>
       <c r="M39" t="n">
-        <v>7648.62</v>
+        <v>7537.12</v>
       </c>
       <c r="N39" t="n">
-        <v>7720.06</v>
+        <v>7626.19</v>
       </c>
       <c r="O39" t="n">
-        <v>7717.25</v>
-      </c>
-      <c r="P39" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="Q39" s="6" t="inlineStr">
+        <v>7905.5</v>
+      </c>
+      <c r="P39" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q39" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R39" s="6" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="R39" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
       <c r="S39" s="10" t="inlineStr">
         <is>
-          <t>↓</t>
+          <t>↓C</t>
         </is>
       </c>
       <c r="T39" s="8" t="n">
@@ -3816,50 +3808,50 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="B40" t="n">
-        <v>7368</v>
+        <v>7480</v>
       </c>
       <c r="C40" t="n">
-        <v>7491</v>
+        <v>7584.5</v>
       </c>
       <c r="D40" t="n">
-        <v>7232.25</v>
+        <v>7405</v>
       </c>
       <c r="E40" t="n">
-        <v>7435</v>
+        <v>7556.25</v>
       </c>
       <c r="F40" t="n">
-        <v>34.5</v>
+        <v>121.25</v>
       </c>
       <c r="G40" s="5" t="n">
-        <v>0.0047</v>
+        <v>0.0163</v>
       </c>
       <c r="H40" t="n">
-        <v>258.75</v>
+        <v>179.5</v>
       </c>
       <c r="I40" t="n">
-        <v>7085.75</v>
+        <v>6973.5</v>
       </c>
       <c r="J40" t="n">
-        <v>7079.69</v>
+        <v>7212.94</v>
       </c>
       <c r="K40" t="n">
-        <v>7263.88</v>
+        <v>7305.62</v>
       </c>
       <c r="L40" t="n">
-        <v>7448.06</v>
+        <v>7398.31</v>
       </c>
       <c r="M40" t="n">
-        <v>7537.12</v>
+        <v>7564.38</v>
       </c>
       <c r="N40" t="n">
-        <v>7626.19</v>
+        <v>7730.44</v>
       </c>
       <c r="O40" t="n">
-        <v>7905.5</v>
+        <v>7749.75</v>
       </c>
       <c r="P40" s="6" t="n">
         <v/>
@@ -3867,18 +3859,18 @@
       <c r="Q40" s="6" t="n">
         <v/>
       </c>
-      <c r="R40" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S40" s="10" t="inlineStr">
-        <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T40" s="8" t="n">
-        <v/>
+      <c r="R40" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S40" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T40" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="U40" s="8" t="n">
         <v/>
@@ -3893,77 +3885,79 @@
       </c>
       <c r="X40" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="B41" t="n">
-        <v>7480</v>
+        <v>7543.25</v>
       </c>
       <c r="C41" t="n">
-        <v>7584.5</v>
+        <v>7599.25</v>
       </c>
       <c r="D41" t="n">
-        <v>7405</v>
+        <v>7357.25</v>
       </c>
       <c r="E41" t="n">
-        <v>7556.25</v>
+        <v>7401.75</v>
       </c>
       <c r="F41" t="n">
-        <v>121.25</v>
+        <v>-154.5</v>
       </c>
       <c r="G41" s="5" t="n">
-        <v>0.0163</v>
+        <v>-0.0204</v>
       </c>
       <c r="H41" t="n">
-        <v>179.5</v>
+        <v>242</v>
       </c>
       <c r="I41" t="n">
-        <v>6973.5</v>
+        <v>7225.5</v>
       </c>
       <c r="J41" t="n">
-        <v>7212.94</v>
+        <v>7407.5</v>
       </c>
       <c r="K41" t="n">
-        <v>7305.62</v>
+        <v>7466.5</v>
       </c>
       <c r="L41" t="n">
-        <v>7398.31</v>
+        <v>7525.5</v>
       </c>
       <c r="M41" t="n">
-        <v>7564.38</v>
+        <v>7646</v>
       </c>
       <c r="N41" t="n">
-        <v>7730.44</v>
+        <v>7766.5</v>
       </c>
       <c r="O41" t="n">
-        <v>7749.75</v>
+        <v>7764</v>
       </c>
       <c r="P41" s="6" t="n">
         <v/>
       </c>
-      <c r="Q41" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R41" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S41" s="7" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T41" s="8" t="inlineStr">
+      <c r="Q41" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
+      <c r="R41" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S41" s="10" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T41" s="8" t="n">
+        <v/>
+      </c>
       <c r="U41" s="8" t="n">
         <v/>
       </c>
@@ -3977,79 +3971,77 @@
       </c>
       <c r="X41" t="inlineStr">
         <is>
-          <t>強警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="B42" t="n">
-        <v>7543.25</v>
+        <v>7398</v>
       </c>
       <c r="C42" t="n">
-        <v>7599.25</v>
+        <v>7593.75</v>
       </c>
       <c r="D42" t="n">
-        <v>7357.25</v>
+        <v>7398</v>
       </c>
       <c r="E42" t="n">
-        <v>7401.75</v>
+        <v>7557</v>
       </c>
       <c r="F42" t="n">
-        <v>-154.5</v>
+        <v>155.25</v>
       </c>
       <c r="G42" s="5" t="n">
-        <v>-0.0204</v>
+        <v>0.021</v>
       </c>
       <c r="H42" t="n">
-        <v>242</v>
+        <v>195.75</v>
       </c>
       <c r="I42" t="n">
-        <v>7225.5</v>
+        <v>7115.25</v>
       </c>
       <c r="J42" t="n">
-        <v>7407.5</v>
+        <v>7121.5</v>
       </c>
       <c r="K42" t="n">
-        <v>7466.5</v>
+        <v>7280.75</v>
       </c>
       <c r="L42" t="n">
-        <v>7525.5</v>
+        <v>7440</v>
       </c>
       <c r="M42" t="n">
-        <v>7646</v>
+        <v>7522.75</v>
       </c>
       <c r="N42" t="n">
-        <v>7766.5</v>
+        <v>7605.5</v>
       </c>
       <c r="O42" t="n">
-        <v>7764</v>
+        <v>7841.25</v>
       </c>
       <c r="P42" s="6" t="n">
         <v/>
       </c>
-      <c r="Q42" s="6" t="inlineStr">
+      <c r="Q42" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R42" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S42" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T42" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="R42" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S42" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T42" s="8" t="n">
-        <v/>
-      </c>
       <c r="U42" s="8" t="n">
         <v/>
       </c>
@@ -4063,57 +4055,57 @@
       </c>
       <c r="X42" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="B43" t="n">
-        <v>7398</v>
+        <v>7562.25</v>
       </c>
       <c r="C43" t="n">
-        <v>7593.75</v>
+        <v>7628.75</v>
       </c>
       <c r="D43" t="n">
-        <v>7398</v>
+        <v>7468.5</v>
       </c>
       <c r="E43" t="n">
-        <v>7557</v>
+        <v>7620.25</v>
       </c>
       <c r="F43" t="n">
-        <v>155.25</v>
+        <v>63.25</v>
       </c>
       <c r="G43" s="5" t="n">
-        <v>0.021</v>
+        <v>0.008399999999999999</v>
       </c>
       <c r="H43" t="n">
-        <v>195.75</v>
+        <v>160.25</v>
       </c>
       <c r="I43" t="n">
-        <v>7115.25</v>
+        <v>7202.25</v>
       </c>
       <c r="J43" t="n">
-        <v>7121.5</v>
+        <v>7391.81</v>
       </c>
       <c r="K43" t="n">
-        <v>7280.75</v>
+        <v>7459.12</v>
       </c>
       <c r="L43" t="n">
-        <v>7440</v>
+        <v>7526.44</v>
       </c>
       <c r="M43" t="n">
-        <v>7522.75</v>
+        <v>7654.88</v>
       </c>
       <c r="N43" t="n">
-        <v>7605.5</v>
+        <v>7783.31</v>
       </c>
       <c r="O43" t="n">
-        <v>7841.25</v>
+        <v>7789.5</v>
       </c>
       <c r="P43" s="6" t="n">
         <v/>
@@ -4147,77 +4139,79 @@
       </c>
       <c r="X43" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="B44" t="n">
-        <v>7562.25</v>
+        <v>7607</v>
       </c>
       <c r="C44" t="n">
-        <v>7628.75</v>
+        <v>7632</v>
       </c>
       <c r="D44" t="n">
-        <v>7468.5</v>
+        <v>7473</v>
       </c>
       <c r="E44" t="n">
-        <v>7620.25</v>
+        <v>7497.75</v>
       </c>
       <c r="F44" t="n">
-        <v>63.25</v>
+        <v>-122.5</v>
       </c>
       <c r="G44" s="5" t="n">
-        <v>0.008399999999999999</v>
+        <v>-0.0161</v>
       </c>
       <c r="H44" t="n">
-        <v>160.25</v>
+        <v>159</v>
       </c>
       <c r="I44" t="n">
-        <v>7202.25</v>
+        <v>7308.25</v>
       </c>
       <c r="J44" t="n">
-        <v>7391.81</v>
+        <v>7495.81</v>
       </c>
       <c r="K44" t="n">
-        <v>7459.12</v>
+        <v>7540.12</v>
       </c>
       <c r="L44" t="n">
-        <v>7526.44</v>
+        <v>7584.44</v>
       </c>
       <c r="M44" t="n">
-        <v>7654.88</v>
+        <v>7700.38</v>
       </c>
       <c r="N44" t="n">
-        <v>7783.31</v>
+        <v>7816.31</v>
       </c>
       <c r="O44" t="n">
-        <v>7789.5</v>
+        <v>7789</v>
       </c>
       <c r="P44" s="6" t="n">
         <v/>
       </c>
-      <c r="Q44" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R44" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S44" s="7" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T44" s="8" t="inlineStr">
+      <c r="Q44" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
+      <c r="R44" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S44" s="10" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T44" s="8" t="n">
+        <v/>
+      </c>
       <c r="U44" s="8" t="n">
         <v/>
       </c>
@@ -4231,71 +4225,69 @@
       </c>
       <c r="X44" t="inlineStr">
         <is>
-          <t>強警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="B45" t="n">
-        <v>7607</v>
+        <v>7485</v>
       </c>
       <c r="C45" t="n">
-        <v>7632</v>
+        <v>7563.5</v>
       </c>
       <c r="D45" t="n">
-        <v>7473</v>
+        <v>7411.75</v>
       </c>
       <c r="E45" t="n">
-        <v>7497.75</v>
+        <v>7447.5</v>
       </c>
       <c r="F45" t="n">
-        <v>-122.5</v>
+        <v>-50.25</v>
       </c>
       <c r="G45" s="5" t="n">
-        <v>-0.0161</v>
+        <v>-0.0067</v>
       </c>
       <c r="H45" t="n">
-        <v>159</v>
+        <v>151.75</v>
       </c>
       <c r="I45" t="n">
-        <v>7308.25</v>
+        <v>7314</v>
       </c>
       <c r="J45" t="n">
-        <v>7495.81</v>
+        <v>7311.38</v>
       </c>
       <c r="K45" t="n">
-        <v>7540.12</v>
+        <v>7418.25</v>
       </c>
       <c r="L45" t="n">
-        <v>7584.44</v>
+        <v>7525.12</v>
       </c>
       <c r="M45" t="n">
-        <v>7700.38</v>
+        <v>7577.25</v>
       </c>
       <c r="N45" t="n">
-        <v>7816.31</v>
+        <v>7629.38</v>
       </c>
       <c r="O45" t="n">
-        <v>7789</v>
+        <v>7791</v>
       </c>
       <c r="P45" s="6" t="n">
         <v/>
       </c>
-      <c r="Q45" s="6" t="inlineStr">
+      <c r="Q45" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R45" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="R45" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
       <c r="S45" s="10" t="inlineStr">
         <is>
           <t>↓</t>
@@ -4315,59 +4307,55 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X45" t="inlineStr">
-        <is>
-          <t>中警訊</t>
-        </is>
-      </c>
+      <c r="X45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="B46" t="n">
-        <v>7485</v>
+        <v>7490</v>
       </c>
       <c r="C46" t="n">
-        <v>7563.5</v>
+        <v>7541</v>
       </c>
       <c r="D46" t="n">
-        <v>7411.75</v>
+        <v>7324</v>
       </c>
       <c r="E46" t="n">
-        <v>7447.5</v>
+        <v>7519.25</v>
       </c>
       <c r="F46" t="n">
-        <v>-50.25</v>
+        <v>71.75</v>
       </c>
       <c r="G46" s="5" t="n">
-        <v>-0.0067</v>
+        <v>0.009599999999999999</v>
       </c>
       <c r="H46" t="n">
-        <v>151.75</v>
+        <v>217</v>
       </c>
       <c r="I46" t="n">
-        <v>7314</v>
+        <v>7260</v>
       </c>
       <c r="J46" t="n">
-        <v>7311.38</v>
+        <v>7275.69</v>
       </c>
       <c r="K46" t="n">
-        <v>7418.25</v>
+        <v>7371.62</v>
       </c>
       <c r="L46" t="n">
-        <v>7525.12</v>
+        <v>7467.56</v>
       </c>
       <c r="M46" t="n">
-        <v>7577.25</v>
+        <v>7523.38</v>
       </c>
       <c r="N46" t="n">
-        <v>7629.38</v>
+        <v>7579.19</v>
       </c>
       <c r="O46" t="n">
-        <v>7791</v>
+        <v>7715.25</v>
       </c>
       <c r="P46" s="6" t="n">
         <v/>
@@ -4377,17 +4365,19 @@
       </c>
       <c r="R46" s="6" t="inlineStr">
         <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S46" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T46" s="8" t="inlineStr">
+        <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="S46" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T46" s="8" t="n">
-        <v/>
-      </c>
       <c r="U46" s="8" t="n">
         <v/>
       </c>
@@ -4399,55 +4389,59 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X46" t="inlineStr"/>
+      <c r="X46" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="B47" t="n">
-        <v>7490</v>
+        <v>7550</v>
       </c>
       <c r="C47" t="n">
-        <v>7541</v>
+        <v>7820.25</v>
       </c>
       <c r="D47" t="n">
-        <v>7324</v>
+        <v>7542.75</v>
       </c>
       <c r="E47" t="n">
-        <v>7519.25</v>
+        <v>7779.75</v>
       </c>
       <c r="F47" t="n">
-        <v>71.75</v>
+        <v>260.5</v>
       </c>
       <c r="G47" s="5" t="n">
-        <v>0.009599999999999999</v>
+        <v>0.0346</v>
       </c>
       <c r="H47" t="n">
-        <v>217</v>
+        <v>277.5</v>
       </c>
       <c r="I47" t="n">
-        <v>7260</v>
+        <v>7107</v>
       </c>
       <c r="J47" t="n">
-        <v>7275.69</v>
+        <v>7345.62</v>
       </c>
       <c r="K47" t="n">
-        <v>7371.62</v>
+        <v>7410.75</v>
       </c>
       <c r="L47" t="n">
-        <v>7467.56</v>
+        <v>7475.88</v>
       </c>
       <c r="M47" t="n">
-        <v>7523.38</v>
+        <v>7627.75</v>
       </c>
       <c r="N47" t="n">
-        <v>7579.19</v>
+        <v>7779.62</v>
       </c>
       <c r="O47" t="n">
-        <v>7715.25</v>
+        <v>7758</v>
       </c>
       <c r="P47" s="6" t="n">
         <v/>
@@ -4455,85 +4449,83 @@
       <c r="Q47" s="6" t="n">
         <v/>
       </c>
-      <c r="R47" s="6" t="inlineStr">
+      <c r="R47" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S47" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T47" s="8" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="S47" s="7" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T47" s="8" t="inlineStr">
+      <c r="U47" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="U47" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V47" s="8" t="n">
-        <v/>
-      </c>
-      <c r="W47" s="11" t="inlineStr">
-        <is>
-          <t>空方</t>
-        </is>
-      </c>
-      <c r="X47" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="V47" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="W47" s="9" t="inlineStr">
+        <is>
+          <t>多方</t>
+        </is>
+      </c>
+      <c r="X47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="B48" t="n">
-        <v>7550</v>
+        <v>7776.75</v>
       </c>
       <c r="C48" t="n">
-        <v>7820.25</v>
+        <v>7838.5</v>
       </c>
       <c r="D48" t="n">
-        <v>7542.75</v>
+        <v>7738</v>
       </c>
       <c r="E48" t="n">
-        <v>7779.75</v>
+        <v>7805</v>
       </c>
       <c r="F48" t="n">
-        <v>260.5</v>
+        <v>25.25</v>
       </c>
       <c r="G48" s="5" t="n">
-        <v>0.0346</v>
+        <v>0.0032</v>
       </c>
       <c r="H48" t="n">
-        <v>277.5</v>
+        <v>100.5</v>
       </c>
       <c r="I48" t="n">
-        <v>7107</v>
+        <v>7265.25</v>
       </c>
       <c r="J48" t="n">
-        <v>7345.62</v>
+        <v>7551.38</v>
       </c>
       <c r="K48" t="n">
-        <v>7410.75</v>
+        <v>7641</v>
       </c>
       <c r="L48" t="n">
-        <v>7475.88</v>
+        <v>7730.62</v>
       </c>
       <c r="M48" t="n">
-        <v>7627.75</v>
+        <v>7918.5</v>
       </c>
       <c r="N48" t="n">
-        <v>7779.62</v>
+        <v>8106.38</v>
       </c>
       <c r="O48" t="n">
-        <v>7758</v>
+        <v>8097.75</v>
       </c>
       <c r="P48" s="6" t="n">
         <v/>
@@ -4546,23 +4538,17 @@
       </c>
       <c r="S48" s="7" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T48" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U48" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="V48" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T48" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U48" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V48" s="8" t="n">
+        <v/>
       </c>
       <c r="W48" s="9" t="inlineStr">
         <is>
@@ -4574,63 +4560,67 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="B49" t="n">
-        <v>7776.75</v>
+        <v>7809.25</v>
       </c>
       <c r="C49" t="n">
-        <v>7838.5</v>
+        <v>7824.5</v>
       </c>
       <c r="D49" t="n">
-        <v>7738</v>
+        <v>7657.75</v>
       </c>
       <c r="E49" t="n">
-        <v>7805</v>
+        <v>7691.25</v>
       </c>
       <c r="F49" t="n">
-        <v>25.25</v>
+        <v>-113.75</v>
       </c>
       <c r="G49" s="5" t="n">
-        <v>0.0032</v>
+        <v>-0.0146</v>
       </c>
       <c r="H49" t="n">
-        <v>100.5</v>
+        <v>166.75</v>
       </c>
       <c r="I49" t="n">
-        <v>7265.25</v>
+        <v>7637.5</v>
       </c>
       <c r="J49" t="n">
-        <v>7551.38</v>
+        <v>7712.88</v>
       </c>
       <c r="K49" t="n">
-        <v>7641</v>
+        <v>7754.75</v>
       </c>
       <c r="L49" t="n">
-        <v>7730.62</v>
+        <v>7796.62</v>
       </c>
       <c r="M49" t="n">
-        <v>7918.5</v>
+        <v>7855.25</v>
       </c>
       <c r="N49" t="n">
-        <v>8106.38</v>
+        <v>7913.88</v>
       </c>
       <c r="O49" t="n">
-        <v>8097.75</v>
+        <v>7939</v>
       </c>
       <c r="P49" s="6" t="n">
         <v/>
       </c>
-      <c r="Q49" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R49" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S49" s="7" t="inlineStr">
-        <is>
-          <t>↑C</t>
+      <c r="Q49" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="R49" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S49" s="10" t="inlineStr">
+        <is>
+          <t>↓</t>
         </is>
       </c>
       <c r="T49" s="8" t="n">
@@ -4642,9 +4632,9 @@
       <c r="V49" s="8" t="n">
         <v/>
       </c>
-      <c r="W49" s="9" t="inlineStr">
-        <is>
-          <t>多方</t>
+      <c r="W49" s="11" t="inlineStr">
+        <is>
+          <t>空方</t>
         </is>
       </c>
       <c r="X49" t="inlineStr"/>
@@ -4652,72 +4642,70 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="B50" t="n">
-        <v>7809.25</v>
+        <v>7693.5</v>
       </c>
       <c r="C50" t="n">
-        <v>7824.5</v>
+        <v>7782.5</v>
       </c>
       <c r="D50" t="n">
-        <v>7657.75</v>
+        <v>7655</v>
       </c>
       <c r="E50" t="n">
-        <v>7691.25</v>
+        <v>7722</v>
       </c>
       <c r="F50" t="n">
-        <v>-113.75</v>
+        <v>30.75</v>
       </c>
       <c r="G50" s="5" t="n">
-        <v>-0.0146</v>
+        <v>0.004</v>
       </c>
       <c r="H50" t="n">
-        <v>166.75</v>
+        <v>127.5</v>
       </c>
       <c r="I50" t="n">
-        <v>7637.5</v>
+        <v>7491</v>
       </c>
       <c r="J50" t="n">
-        <v>7712.88</v>
+        <v>7499.56</v>
       </c>
       <c r="K50" t="n">
-        <v>7754.75</v>
+        <v>7607.88</v>
       </c>
       <c r="L50" t="n">
-        <v>7796.62</v>
+        <v>7716.19</v>
       </c>
       <c r="M50" t="n">
-        <v>7855.25</v>
+        <v>7774.62</v>
       </c>
       <c r="N50" t="n">
-        <v>7913.88</v>
+        <v>7833.06</v>
       </c>
       <c r="O50" t="n">
-        <v>7939</v>
+        <v>7991.25</v>
       </c>
       <c r="P50" s="6" t="n">
         <v/>
       </c>
-      <c r="Q50" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="R50" s="6" t="inlineStr">
+      <c r="Q50" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R50" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S50" s="7" t="inlineStr">
+        <is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T50" s="8" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="S50" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T50" s="8" t="n">
-        <v/>
-      </c>
       <c r="U50" s="8" t="n">
         <v/>
       </c>
@@ -4729,55 +4717,59 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X50" t="inlineStr"/>
+      <c r="X50" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="B51" t="n">
-        <v>7693.5</v>
+        <v>7723.5</v>
       </c>
       <c r="C51" t="n">
-        <v>7782.5</v>
+        <v>7766.5</v>
       </c>
       <c r="D51" t="n">
-        <v>7655</v>
+        <v>7618.5</v>
       </c>
       <c r="E51" t="n">
         <v>7722</v>
       </c>
       <c r="F51" t="n">
-        <v>30.75</v>
+        <v>0</v>
       </c>
       <c r="G51" s="5" t="n">
-        <v>0.004</v>
+        <v>0</v>
       </c>
       <c r="H51" t="n">
-        <v>127.5</v>
+        <v>148</v>
       </c>
       <c r="I51" t="n">
-        <v>7491</v>
+        <v>7527.5</v>
       </c>
       <c r="J51" t="n">
-        <v>7499.56</v>
+        <v>7596.12</v>
       </c>
       <c r="K51" t="n">
-        <v>7607.88</v>
+        <v>7658.25</v>
       </c>
       <c r="L51" t="n">
-        <v>7716.19</v>
+        <v>7720.38</v>
       </c>
       <c r="M51" t="n">
-        <v>7774.62</v>
+        <v>7785.75</v>
       </c>
       <c r="N51" t="n">
-        <v>7833.06</v>
+        <v>7851.12</v>
       </c>
       <c r="O51" t="n">
-        <v>7991.25</v>
+        <v>7910</v>
       </c>
       <c r="P51" s="6" t="n">
         <v/>
@@ -4785,18 +4777,18 @@
       <c r="Q51" s="6" t="n">
         <v/>
       </c>
-      <c r="R51" s="6" t="n">
-        <v/>
+      <c r="R51" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S51" s="7" t="inlineStr">
         <is>
           <t>↑C</t>
         </is>
       </c>
-      <c r="T51" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="T51" s="8" t="n">
+        <v/>
       </c>
       <c r="U51" s="8" t="n">
         <v/>
@@ -4809,74 +4801,72 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X51" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="X51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="B52" t="n">
-        <v>7723.5</v>
+        <v>7715.5</v>
       </c>
       <c r="C52" t="n">
-        <v>7766.5</v>
+        <v>7728.5</v>
       </c>
       <c r="D52" t="n">
-        <v>7618.5</v>
+        <v>7585.5</v>
       </c>
       <c r="E52" t="n">
-        <v>7722</v>
+        <v>7659.5</v>
       </c>
       <c r="F52" t="n">
-        <v>0</v>
+        <v>-62.5</v>
       </c>
       <c r="G52" s="5" t="n">
-        <v>0</v>
+        <v>-0.0081</v>
       </c>
       <c r="H52" t="n">
-        <v>148</v>
+        <v>143</v>
       </c>
       <c r="I52" t="n">
-        <v>7527.5</v>
+        <v>7470.5</v>
       </c>
       <c r="J52" t="n">
-        <v>7596.12</v>
+        <v>7588.75</v>
       </c>
       <c r="K52" t="n">
-        <v>7658.25</v>
+        <v>7648</v>
       </c>
       <c r="L52" t="n">
-        <v>7720.38</v>
+        <v>7707.25</v>
       </c>
       <c r="M52" t="n">
-        <v>7785.75</v>
+        <v>7796</v>
       </c>
       <c r="N52" t="n">
-        <v>7851.12</v>
+        <v>7884.75</v>
       </c>
       <c r="O52" t="n">
-        <v>7910</v>
+        <v>7914.5</v>
       </c>
       <c r="P52" s="6" t="n">
         <v/>
       </c>
-      <c r="Q52" s="6" t="n">
-        <v/>
+      <c r="Q52" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="R52" s="6" t="inlineStr">
         <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S52" s="7" t="inlineStr">
-        <is>
-          <t>↑C</t>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="S52" s="10" t="inlineStr">
+        <is>
+          <t>↓</t>
         </is>
       </c>
       <c r="T52" s="8" t="n">
@@ -4898,50 +4888,50 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="B53" t="n">
-        <v>7715.5</v>
+        <v>7609.25</v>
       </c>
       <c r="C53" t="n">
-        <v>7728.5</v>
+        <v>7670.25</v>
       </c>
       <c r="D53" t="n">
-        <v>7585.5</v>
+        <v>7509.25</v>
       </c>
       <c r="E53" t="n">
-        <v>7659.5</v>
+        <v>7657.35</v>
       </c>
       <c r="F53" t="n">
-        <v>-62.5</v>
+        <v>-2.15</v>
       </c>
       <c r="G53" s="5" t="n">
-        <v>-0.0081</v>
+        <v>-0.0003</v>
       </c>
       <c r="H53" t="n">
-        <v>143</v>
+        <v>161</v>
       </c>
       <c r="I53" t="n">
-        <v>7470.5</v>
+        <v>7442.5</v>
       </c>
       <c r="J53" t="n">
-        <v>7588.75</v>
+        <v>7517.75</v>
       </c>
       <c r="K53" t="n">
-        <v>7648</v>
+        <v>7588</v>
       </c>
       <c r="L53" t="n">
-        <v>7707.25</v>
+        <v>7658.25</v>
       </c>
       <c r="M53" t="n">
-        <v>7796</v>
+        <v>7731</v>
       </c>
       <c r="N53" t="n">
-        <v>7884.75</v>
+        <v>7803.75</v>
       </c>
       <c r="O53" t="n">
-        <v>7914.5</v>
+        <v>7871.5</v>
       </c>
       <c r="P53" s="6" t="n">
         <v/>
@@ -4953,12 +4943,12 @@
       </c>
       <c r="R53" s="6" t="inlineStr">
         <is>
-          <t>△C</t>
+          <t>✓</t>
         </is>
       </c>
       <c r="S53" s="10" t="inlineStr">
         <is>
-          <t>↓</t>
+          <t>↓C</t>
         </is>
       </c>
       <c r="T53" s="8" t="n">
@@ -4980,239 +4970,237 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="B54" t="n">
-        <v>7609.25</v>
+        <v>7722</v>
       </c>
       <c r="C54" t="n">
-        <v>7670.25</v>
+        <v>7848.5</v>
       </c>
       <c r="D54" t="n">
-        <v>7509.25</v>
+        <v>7707.25</v>
       </c>
       <c r="E54" t="n">
-        <v>7657.35</v>
+        <v>7803.75</v>
       </c>
       <c r="F54" t="n">
-        <v>-2.15</v>
+        <v>146.4</v>
       </c>
       <c r="G54" s="5" t="n">
-        <v>-0.0003</v>
+        <v>0.0191</v>
       </c>
       <c r="H54" t="n">
-        <v>161</v>
+        <v>141.25</v>
       </c>
       <c r="I54" t="n">
-        <v>7442.5</v>
+        <v>7348.25</v>
       </c>
       <c r="J54" t="n">
-        <v>7517.75</v>
+        <v>7530.15</v>
       </c>
       <c r="K54" t="n">
-        <v>7588</v>
+        <v>7576.85</v>
       </c>
       <c r="L54" t="n">
-        <v>7658.25</v>
+        <v>7623.55</v>
       </c>
       <c r="M54" t="n">
-        <v>7731</v>
+        <v>7737.85</v>
       </c>
       <c r="N54" t="n">
-        <v>7803.75</v>
+        <v>7852.15</v>
       </c>
       <c r="O54" t="n">
-        <v>7871.5</v>
+        <v>7831.25</v>
       </c>
       <c r="P54" s="6" t="n">
         <v/>
       </c>
-      <c r="Q54" s="6" t="inlineStr">
+      <c r="Q54" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R54" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S54" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T54" s="8" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="R54" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S54" s="10" t="inlineStr">
-        <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T54" s="8" t="n">
-        <v/>
-      </c>
       <c r="U54" s="8" t="n">
         <v/>
       </c>
-      <c r="V54" s="8" t="n">
-        <v/>
+      <c r="V54" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="W54" s="11" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
       </c>
-      <c r="X54" t="inlineStr"/>
+      <c r="X54" t="inlineStr">
+        <is>
+          <t>強警訊</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="B55" t="n">
-        <v>7722</v>
+        <v>7796</v>
       </c>
       <c r="C55" t="n">
-        <v>7848.5</v>
+        <v>7810.25</v>
       </c>
       <c r="D55" t="n">
-        <v>7707.25</v>
+        <v>7672.75</v>
       </c>
       <c r="E55" t="n">
-        <v>7803.75</v>
+        <v>7777.25</v>
       </c>
       <c r="F55" t="n">
-        <v>146.4</v>
+        <v>-26.5</v>
       </c>
       <c r="G55" s="5" t="n">
-        <v>0.0191</v>
+        <v>-0.0034</v>
       </c>
       <c r="H55" t="n">
-        <v>141.25</v>
+        <v>137.5</v>
       </c>
       <c r="I55" t="n">
-        <v>7348.25</v>
+        <v>7566</v>
       </c>
       <c r="J55" t="n">
-        <v>7530.15</v>
+        <v>7675.44</v>
       </c>
       <c r="K55" t="n">
-        <v>7576.85</v>
+        <v>7733.12</v>
       </c>
       <c r="L55" t="n">
-        <v>7623.55</v>
+        <v>7790.81</v>
       </c>
       <c r="M55" t="n">
-        <v>7737.85</v>
+        <v>7874.38</v>
       </c>
       <c r="N55" t="n">
-        <v>7852.15</v>
+        <v>7957.94</v>
       </c>
       <c r="O55" t="n">
-        <v>7831.25</v>
+        <v>7989.75</v>
       </c>
       <c r="P55" s="6" t="n">
         <v/>
       </c>
-      <c r="Q55" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R55" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S55" s="7" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T55" s="8" t="inlineStr">
+      <c r="Q55" s="6" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
+      <c r="R55" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S55" s="10" t="inlineStr">
+        <is>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T55" s="8" t="n">
+        <v/>
+      </c>
       <c r="U55" s="8" t="n">
         <v/>
       </c>
-      <c r="V55" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+      <c r="V55" s="8" t="n">
+        <v/>
       </c>
       <c r="W55" s="11" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
       </c>
-      <c r="X55" t="inlineStr">
-        <is>
-          <t>強警訊</t>
-        </is>
-      </c>
+      <c r="X55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="B56" t="n">
-        <v>7796</v>
+        <v>7781.5</v>
       </c>
       <c r="C56" t="n">
-        <v>7810.25</v>
+        <v>7897.5</v>
       </c>
       <c r="D56" t="n">
-        <v>7672.75</v>
+        <v>7760.25</v>
       </c>
       <c r="E56" t="n">
-        <v>7777.25</v>
+        <v>7859.75</v>
       </c>
       <c r="F56" t="n">
-        <v>-26.5</v>
+        <v>82.5</v>
       </c>
       <c r="G56" s="5" t="n">
-        <v>-0.0034</v>
+        <v>0.0106</v>
       </c>
       <c r="H56" t="n">
-        <v>137.5</v>
+        <v>137.25</v>
       </c>
       <c r="I56" t="n">
-        <v>7566</v>
+        <v>7535.25</v>
       </c>
       <c r="J56" t="n">
-        <v>7675.44</v>
+        <v>7657.62</v>
       </c>
       <c r="K56" t="n">
-        <v>7733.12</v>
+        <v>7708.5</v>
       </c>
       <c r="L56" t="n">
-        <v>7790.81</v>
+        <v>7759.38</v>
       </c>
       <c r="M56" t="n">
-        <v>7874.38</v>
+        <v>7846</v>
       </c>
       <c r="N56" t="n">
-        <v>7957.94</v>
+        <v>7932.62</v>
       </c>
       <c r="O56" t="n">
-        <v>7989.75</v>
+        <v>7947.75</v>
       </c>
       <c r="P56" s="6" t="n">
         <v/>
       </c>
-      <c r="Q56" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="R56" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S56" s="10" t="inlineStr">
-        <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T56" s="8" t="n">
-        <v/>
+      <c r="Q56" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R56" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S56" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T56" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="U56" s="8" t="n">
         <v/>
@@ -5225,75 +5213,81 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X56" t="inlineStr"/>
+      <c r="X56" t="inlineStr">
+        <is>
+          <t>強警訊</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="B57" t="n">
-        <v>7781.5</v>
+        <v>7873</v>
       </c>
       <c r="C57" t="n">
-        <v>7897.5</v>
+        <v>7887</v>
       </c>
       <c r="D57" t="n">
-        <v>7760.25</v>
+        <v>7676</v>
       </c>
       <c r="E57" t="n">
-        <v>7859.75</v>
+        <v>7703</v>
       </c>
       <c r="F57" t="n">
-        <v>82.5</v>
+        <v>-156.75</v>
       </c>
       <c r="G57" s="5" t="n">
-        <v>0.0106</v>
+        <v>-0.0199</v>
       </c>
       <c r="H57" t="n">
-        <v>137.25</v>
+        <v>211</v>
       </c>
       <c r="I57" t="n">
-        <v>7535.25</v>
+        <v>7623</v>
       </c>
       <c r="J57" t="n">
-        <v>7657.62</v>
+        <v>7737.94</v>
       </c>
       <c r="K57" t="n">
-        <v>7708.5</v>
+        <v>7791.12</v>
       </c>
       <c r="L57" t="n">
-        <v>7759.38</v>
+        <v>7844.31</v>
       </c>
       <c r="M57" t="n">
-        <v>7846</v>
+        <v>7928.38</v>
       </c>
       <c r="N57" t="n">
-        <v>7932.62</v>
+        <v>8012.44</v>
       </c>
       <c r="O57" t="n">
-        <v>7947.75</v>
+        <v>8034.75</v>
       </c>
       <c r="P57" s="6" t="n">
         <v/>
       </c>
-      <c r="Q57" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R57" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S57" s="7" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T57" s="8" t="inlineStr">
+      <c r="Q57" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
+      <c r="R57" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S57" s="10" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T57" s="8" t="n">
+        <v/>
+      </c>
       <c r="U57" s="8" t="n">
         <v/>
       </c>
@@ -5305,91 +5299,7 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X57" t="inlineStr">
-        <is>
-          <t>強警訊</t>
-        </is>
-      </c>
-    </row>
-    <row r="58">
-      <c r="A58" t="inlineStr">
-        <is>
-          <t>2026-10-12</t>
-        </is>
-      </c>
-      <c r="B58" t="n">
-        <v>7873</v>
-      </c>
-      <c r="C58" t="n">
-        <v>7887</v>
-      </c>
-      <c r="D58" t="n">
-        <v>7741</v>
-      </c>
-      <c r="E58" t="n">
-        <v>7789</v>
-      </c>
-      <c r="F58" t="n">
-        <v>-70.75</v>
-      </c>
-      <c r="G58" s="5" t="n">
-        <v>-0.008999999999999999</v>
-      </c>
-      <c r="H58" t="n">
-        <v>146</v>
-      </c>
-      <c r="I58" t="n">
-        <v>7623</v>
-      </c>
-      <c r="J58" t="n">
-        <v>7737.94</v>
-      </c>
-      <c r="K58" t="n">
-        <v>7791.12</v>
-      </c>
-      <c r="L58" t="n">
-        <v>7844.31</v>
-      </c>
-      <c r="M58" t="n">
-        <v>7928.38</v>
-      </c>
-      <c r="N58" t="n">
-        <v>8012.44</v>
-      </c>
-      <c r="O58" t="n">
-        <v>8034.75</v>
-      </c>
-      <c r="P58" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q58" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R58" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="S58" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T58" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U58" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V58" s="8" t="n">
-        <v/>
-      </c>
-      <c r="W58" s="11" t="inlineStr">
-        <is>
-          <t>空方</t>
-        </is>
-      </c>
-      <c r="X58" t="inlineStr"/>
+      <c r="X57" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/three_gate/analysis/ES_weekly.xlsx
+++ b/three_gate/analysis/ES_weekly.xlsx
@@ -5235,13 +5235,13 @@
         <v>7676</v>
       </c>
       <c r="E57" t="n">
-        <v>7703</v>
+        <v>7704.25</v>
       </c>
       <c r="F57" t="n">
-        <v>-156.75</v>
+        <v>-155.5</v>
       </c>
       <c r="G57" s="5" t="n">
-        <v>-0.0199</v>
+        <v>-0.0198</v>
       </c>
       <c r="H57" t="n">
         <v>211</v>

--- a/three_gate/analysis/ES_weekly.xlsx
+++ b/three_gate/analysis/ES_weekly.xlsx
@@ -5235,13 +5235,13 @@
         <v>7676</v>
       </c>
       <c r="E57" t="n">
-        <v>7704.25</v>
+        <v>7734.25</v>
       </c>
       <c r="F57" t="n">
-        <v>-155.5</v>
+        <v>-125.5</v>
       </c>
       <c r="G57" s="5" t="n">
-        <v>-0.0198</v>
+        <v>-0.016</v>
       </c>
       <c r="H57" t="n">
         <v>211</v>

--- a/three_gate/analysis/ES_weekly.xlsx
+++ b/three_gate/analysis/ES_weekly.xlsx
@@ -5235,13 +5235,13 @@
         <v>7676</v>
       </c>
       <c r="E57" t="n">
-        <v>7734.25</v>
+        <v>7744</v>
       </c>
       <c r="F57" t="n">
-        <v>-125.5</v>
+        <v>-115.75</v>
       </c>
       <c r="G57" s="5" t="n">
-        <v>-0.016</v>
+        <v>-0.0147</v>
       </c>
       <c r="H57" t="n">
         <v>211</v>

--- a/three_gate/analysis/ES_weekly.xlsx
+++ b/three_gate/analysis/ES_weekly.xlsx
@@ -86,7 +86,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -115,6 +115,9 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -480,7 +483,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X57"/>
+  <dimension ref="A1:X58"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -5235,13 +5238,13 @@
         <v>7676</v>
       </c>
       <c r="E57" t="n">
-        <v>7744</v>
+        <v>7704.25</v>
       </c>
       <c r="F57" t="n">
-        <v>-115.75</v>
+        <v>-155.5</v>
       </c>
       <c r="G57" s="5" t="n">
-        <v>-0.0147</v>
+        <v>-0.0198</v>
       </c>
       <c r="H57" t="n">
         <v>211</v>
@@ -5300,6 +5303,90 @@
         </is>
       </c>
       <c r="X57" t="inlineStr"/>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>2026-10-19</t>
+        </is>
+      </c>
+      <c r="B58" t="n">
+        <v>7740.75</v>
+      </c>
+      <c r="C58" t="n">
+        <v>7748.25</v>
+      </c>
+      <c r="D58" t="n">
+        <v>7725.25</v>
+      </c>
+      <c r="E58" t="n">
+        <v/>
+      </c>
+      <c r="F58" t="n">
+        <v/>
+      </c>
+      <c r="G58" s="5" t="n">
+        <v/>
+      </c>
+      <c r="H58" t="n">
+        <v>23</v>
+      </c>
+      <c r="I58" t="n">
+        <v>7465</v>
+      </c>
+      <c r="J58" t="n">
+        <v>7454.62</v>
+      </c>
+      <c r="K58" t="n">
+        <v>7598.75</v>
+      </c>
+      <c r="L58" t="n">
+        <v>7742.88</v>
+      </c>
+      <c r="M58" t="n">
+        <v>7809.75</v>
+      </c>
+      <c r="N58" t="n">
+        <v>7876.62</v>
+      </c>
+      <c r="O58" t="n">
+        <v>8098</v>
+      </c>
+      <c r="P58" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="Q58" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R58" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S58" s="12" t="inlineStr">
+        <is>
+          <t>=</t>
+        </is>
+      </c>
+      <c r="T58" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U58" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V58" s="8" t="n">
+        <v/>
+      </c>
+      <c r="W58" s="11" t="inlineStr">
+        <is>
+          <t>空方</t>
+        </is>
+      </c>
+      <c r="X58" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/three_gate/analysis/ES_weekly.xlsx
+++ b/three_gate/analysis/ES_weekly.xlsx
@@ -5317,7 +5317,7 @@
         <v>7748.25</v>
       </c>
       <c r="D58" t="n">
-        <v>7725.25</v>
+        <v>7724</v>
       </c>
       <c r="E58" t="n">
         <v/>
@@ -5329,7 +5329,7 @@
         <v/>
       </c>
       <c r="H58" t="n">
-        <v>23</v>
+        <v>24.25</v>
       </c>
       <c r="I58" t="n">
         <v>7465</v>

--- a/three_gate/analysis/ES_weekly.xlsx
+++ b/three_gate/analysis/ES_weekly.xlsx
@@ -86,7 +86,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="13">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -115,9 +115,6 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -5311,25 +5308,25 @@
         </is>
       </c>
       <c r="B58" t="n">
-        <v>7740.75</v>
+        <v>7679.5</v>
       </c>
       <c r="C58" t="n">
-        <v>7748.25</v>
+        <v>7793</v>
       </c>
       <c r="D58" t="n">
-        <v>7724</v>
+        <v>7677</v>
       </c>
       <c r="E58" t="n">
-        <v/>
+        <v>7770</v>
       </c>
       <c r="F58" t="n">
-        <v/>
+        <v>65.75</v>
       </c>
       <c r="G58" s="5" t="n">
-        <v/>
+        <v>0.008500000000000001</v>
       </c>
       <c r="H58" t="n">
-        <v>24.25</v>
+        <v>116</v>
       </c>
       <c r="I58" t="n">
         <v>7465</v>
@@ -5352,10 +5349,8 @@
       <c r="O58" t="n">
         <v>8098</v>
       </c>
-      <c r="P58" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+      <c r="P58" s="6" t="n">
+        <v/>
       </c>
       <c r="Q58" s="6" t="n">
         <v/>
@@ -5363,9 +5358,9 @@
       <c r="R58" s="6" t="n">
         <v/>
       </c>
-      <c r="S58" s="12" t="inlineStr">
-        <is>
-          <t>=</t>
+      <c r="S58" s="7" t="inlineStr">
+        <is>
+          <t>↑C</t>
         </is>
       </c>
       <c r="T58" s="8" t="n">
@@ -5384,7 +5379,7 @@
       </c>
       <c r="X58" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>

--- a/three_gate/analysis/ES_weekly.xlsx
+++ b/three_gate/analysis/ES_weekly.xlsx
@@ -659,25 +659,25 @@
         <v>132.5</v>
       </c>
       <c r="I2" t="n">
-        <v>6446</v>
+        <v>6549.5</v>
       </c>
       <c r="J2" t="n">
-        <v>6576.16</v>
+        <v>6614.97</v>
       </c>
       <c r="K2" t="n">
-        <v>6604.77</v>
+        <v>6630.65</v>
       </c>
       <c r="L2" t="n">
-        <v>6633.39</v>
+        <v>6646.32</v>
       </c>
       <c r="M2" t="n">
-        <v>6712.77</v>
+        <v>6686.9</v>
       </c>
       <c r="N2" t="n">
-        <v>6792.16</v>
+        <v>6727.47</v>
       </c>
       <c r="O2" t="n">
-        <v>6770</v>
+        <v>6718.25</v>
       </c>
       <c r="P2" s="6" t="n">
         <v/>
@@ -685,8 +685,10 @@
       <c r="Q2" s="6" t="n">
         <v/>
       </c>
-      <c r="R2" s="6" t="n">
-        <v/>
+      <c r="R2" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S2" s="7" t="inlineStr">
         <is>
@@ -698,11 +700,15 @@
           <t>△C</t>
         </is>
       </c>
-      <c r="U2" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V2" s="8" t="n">
-        <v/>
+      <c r="U2" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="V2" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="W2" s="9" t="inlineStr">
         <is>
@@ -5311,22 +5317,22 @@
         <v>7679.5</v>
       </c>
       <c r="C58" t="n">
-        <v>7793</v>
+        <v>7798.75</v>
       </c>
       <c r="D58" t="n">
         <v>7677</v>
       </c>
       <c r="E58" t="n">
-        <v>7770</v>
+        <v>7768</v>
       </c>
       <c r="F58" t="n">
-        <v>65.75</v>
+        <v>63.75</v>
       </c>
       <c r="G58" s="5" t="n">
-        <v>0.008500000000000001</v>
+        <v>0.0083</v>
       </c>
       <c r="H58" t="n">
-        <v>116</v>
+        <v>121.75</v>
       </c>
       <c r="I58" t="n">
         <v>7465</v>

--- a/three_gate/analysis/ES_weekly.xlsx
+++ b/three_gate/analysis/ES_weekly.xlsx
@@ -5317,22 +5317,22 @@
         <v>7679.5</v>
       </c>
       <c r="C58" t="n">
-        <v>7798.75</v>
+        <v>7812.25</v>
       </c>
       <c r="D58" t="n">
         <v>7677</v>
       </c>
       <c r="E58" t="n">
-        <v>7768</v>
+        <v>7755.5</v>
       </c>
       <c r="F58" t="n">
-        <v>63.75</v>
+        <v>51.25</v>
       </c>
       <c r="G58" s="5" t="n">
-        <v>0.0083</v>
+        <v>0.0067</v>
       </c>
       <c r="H58" t="n">
-        <v>121.75</v>
+        <v>135.25</v>
       </c>
       <c r="I58" t="n">
         <v>7465</v>
@@ -5369,8 +5369,10 @@
           <t>↑C</t>
         </is>
       </c>
-      <c r="T58" s="8" t="n">
-        <v/>
+      <c r="T58" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="U58" s="8" t="n">
         <v/>

--- a/three_gate/analysis/ES_weekly.xlsx
+++ b/three_gate/analysis/ES_weekly.xlsx
@@ -659,31 +659,33 @@
         <v>132.5</v>
       </c>
       <c r="I2" t="n">
-        <v>6549.5</v>
+        <v>6584.75</v>
       </c>
       <c r="J2" t="n">
-        <v>6614.97</v>
+        <v>6629.28</v>
       </c>
       <c r="K2" t="n">
-        <v>6630.65</v>
+        <v>6639.77</v>
       </c>
       <c r="L2" t="n">
-        <v>6646.32</v>
+        <v>6650.26</v>
       </c>
       <c r="M2" t="n">
-        <v>6686.9</v>
+        <v>6677.77</v>
       </c>
       <c r="N2" t="n">
-        <v>6727.47</v>
+        <v>6705.28</v>
       </c>
       <c r="O2" t="n">
-        <v>6718.25</v>
+        <v>6698.75</v>
       </c>
       <c r="P2" s="6" t="n">
         <v/>
       </c>
-      <c r="Q2" s="6" t="n">
-        <v/>
+      <c r="Q2" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="R2" s="6" t="inlineStr">
         <is>
@@ -697,17 +699,17 @@
       </c>
       <c r="T2" s="8" t="inlineStr">
         <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U2" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="V2" s="8" t="inlineStr">
+        <is>
           <t>△C</t>
-        </is>
-      </c>
-      <c r="U2" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="V2" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
         </is>
       </c>
       <c r="W2" s="9" t="inlineStr">
@@ -5323,13 +5325,13 @@
         <v>7677</v>
       </c>
       <c r="E58" t="n">
-        <v>7755.5</v>
+        <v>7699.5</v>
       </c>
       <c r="F58" t="n">
-        <v>51.25</v>
+        <v>-4.75</v>
       </c>
       <c r="G58" s="5" t="n">
-        <v>0.0067</v>
+        <v>-0.0005999999999999999</v>
       </c>
       <c r="H58" t="n">
         <v>135.25</v>
@@ -5364,9 +5366,9 @@
       <c r="R58" s="6" t="n">
         <v/>
       </c>
-      <c r="S58" s="7" t="inlineStr">
-        <is>
-          <t>↑C</t>
+      <c r="S58" s="10" t="inlineStr">
+        <is>
+          <t>↓C</t>
         </is>
       </c>
       <c r="T58" s="8" t="inlineStr">
@@ -5387,7 +5389,7 @@
       </c>
       <c r="X58" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>

--- a/three_gate/analysis/ES_weekly.xlsx
+++ b/three_gate/analysis/ES_weekly.xlsx
@@ -480,7 +480,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X58"/>
+  <dimension ref="A1:X57"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -634,63 +634,59 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2025-09-22</t>
+          <t>2025-09-29</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>6716</v>
+        <v>6697</v>
       </c>
       <c r="C2" t="n">
-        <v>6756.75</v>
+        <v>6800</v>
       </c>
       <c r="D2" t="n">
-        <v>6624.25</v>
+        <v>6680</v>
       </c>
       <c r="E2" t="n">
-        <v>6696.5</v>
+        <v>6764</v>
       </c>
       <c r="F2" t="n">
-        <v>37.73</v>
+        <v>67.5</v>
       </c>
       <c r="G2" s="5" t="n">
-        <v>0.0057</v>
+        <v>0.0101</v>
       </c>
       <c r="H2" t="n">
-        <v>132.5</v>
+        <v>120</v>
       </c>
       <c r="I2" t="n">
-        <v>6584.75</v>
+        <v>6491.75</v>
       </c>
       <c r="J2" t="n">
-        <v>6629.28</v>
+        <v>6567</v>
       </c>
       <c r="K2" t="n">
-        <v>6639.77</v>
+        <v>6630.25</v>
       </c>
       <c r="L2" t="n">
-        <v>6650.26</v>
+        <v>6693.5</v>
       </c>
       <c r="M2" t="n">
-        <v>6677.77</v>
+        <v>6762.75</v>
       </c>
       <c r="N2" t="n">
-        <v>6705.28</v>
+        <v>6832</v>
       </c>
       <c r="O2" t="n">
-        <v>6698.75</v>
+        <v>6889.25</v>
       </c>
       <c r="P2" s="6" t="n">
         <v/>
       </c>
-      <c r="Q2" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="R2" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="Q2" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R2" s="6" t="n">
+        <v/>
       </c>
       <c r="S2" s="7" t="inlineStr">
         <is>
@@ -699,18 +695,14 @@
       </c>
       <c r="T2" s="8" t="inlineStr">
         <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U2" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="V2" s="8" t="inlineStr">
-        <is>
           <t>△C</t>
         </is>
+      </c>
+      <c r="U2" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V2" s="8" t="n">
+        <v/>
       </c>
       <c r="W2" s="9" t="inlineStr">
         <is>
@@ -722,154 +714,158 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2025-09-29</t>
+          <t>2025-10-06</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>6697</v>
+        <v>6768</v>
       </c>
       <c r="C3" t="n">
-        <v>6800</v>
+        <v>6812.25</v>
       </c>
       <c r="D3" t="n">
-        <v>6680</v>
+        <v>6540.25</v>
       </c>
       <c r="E3" t="n">
-        <v>6764</v>
+        <v>6595.25</v>
       </c>
       <c r="F3" t="n">
-        <v>67.5</v>
+        <v>-168.75</v>
       </c>
       <c r="G3" s="5" t="n">
-        <v>0.0101</v>
+        <v>-0.0249</v>
       </c>
       <c r="H3" t="n">
-        <v>120</v>
+        <v>272</v>
       </c>
       <c r="I3" t="n">
-        <v>6491.75</v>
+        <v>6560</v>
       </c>
       <c r="J3" t="n">
-        <v>6567</v>
+        <v>6656</v>
       </c>
       <c r="K3" t="n">
-        <v>6630.25</v>
+        <v>6704</v>
       </c>
       <c r="L3" t="n">
-        <v>6693.5</v>
+        <v>6752</v>
       </c>
       <c r="M3" t="n">
-        <v>6762.75</v>
+        <v>6824</v>
       </c>
       <c r="N3" t="n">
-        <v>6832</v>
+        <v>6896</v>
       </c>
       <c r="O3" t="n">
-        <v>6889.25</v>
-      </c>
-      <c r="P3" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q3" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R3" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S3" s="7" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T3" s="8" t="inlineStr">
+        <v>6920</v>
+      </c>
+      <c r="P3" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
+      <c r="Q3" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="R3" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S3" s="10" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T3" s="8" t="n">
+        <v/>
+      </c>
       <c r="U3" s="8" t="n">
         <v/>
       </c>
       <c r="V3" s="8" t="n">
         <v/>
       </c>
-      <c r="W3" s="9" t="inlineStr">
-        <is>
-          <t>多方</t>
-        </is>
-      </c>
-      <c r="X3" t="inlineStr"/>
+      <c r="W3" s="11" t="inlineStr">
+        <is>
+          <t>空方</t>
+        </is>
+      </c>
+      <c r="X3" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2025-10-06</t>
+          <t>2025-10-13</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>6768</v>
+        <v>6632</v>
       </c>
       <c r="C4" t="n">
-        <v>6812.25</v>
+        <v>6766.75</v>
       </c>
       <c r="D4" t="n">
-        <v>6540.25</v>
+        <v>6571.25</v>
       </c>
       <c r="E4" t="n">
-        <v>6595.25</v>
+        <v>6702.5</v>
       </c>
       <c r="F4" t="n">
-        <v>-168.75</v>
+        <v>107.25</v>
       </c>
       <c r="G4" s="5" t="n">
-        <v>-0.0249</v>
+        <v>0.0163</v>
       </c>
       <c r="H4" t="n">
-        <v>272</v>
+        <v>195.5</v>
       </c>
       <c r="I4" t="n">
-        <v>6560</v>
+        <v>6268.25</v>
       </c>
       <c r="J4" t="n">
-        <v>6656</v>
+        <v>6282.75</v>
       </c>
       <c r="K4" t="n">
-        <v>6704</v>
+        <v>6459.25</v>
       </c>
       <c r="L4" t="n">
-        <v>6752</v>
+        <v>6635.75</v>
       </c>
       <c r="M4" t="n">
-        <v>6824</v>
+        <v>6731.25</v>
       </c>
       <c r="N4" t="n">
-        <v>6896</v>
+        <v>6826.75</v>
       </c>
       <c r="O4" t="n">
-        <v>6920</v>
-      </c>
-      <c r="P4" s="6" t="inlineStr">
+        <v>7084.25</v>
+      </c>
+      <c r="P4" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q4" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R4" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S4" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T4" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="Q4" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="R4" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S4" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T4" s="8" t="n">
-        <v/>
-      </c>
       <c r="U4" s="8" t="n">
         <v/>
       </c>
@@ -883,57 +879,57 @@
       </c>
       <c r="X4" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2025-10-13</t>
+          <t>2025-10-20</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>6632</v>
+        <v>6721</v>
       </c>
       <c r="C5" t="n">
-        <v>6766.75</v>
+        <v>6841.25</v>
       </c>
       <c r="D5" t="n">
-        <v>6571.25</v>
+        <v>6690.75</v>
       </c>
       <c r="E5" t="n">
-        <v>6702.5</v>
+        <v>6827</v>
       </c>
       <c r="F5" t="n">
-        <v>107.25</v>
+        <v>124.5</v>
       </c>
       <c r="G5" s="5" t="n">
-        <v>0.0163</v>
+        <v>0.0186</v>
       </c>
       <c r="H5" t="n">
-        <v>195.5</v>
+        <v>150.5</v>
       </c>
       <c r="I5" t="n">
-        <v>6268.25</v>
+        <v>6375.75</v>
       </c>
       <c r="J5" t="n">
-        <v>6282.75</v>
+        <v>6523.75</v>
       </c>
       <c r="K5" t="n">
-        <v>6459.25</v>
+        <v>6604.75</v>
       </c>
       <c r="L5" t="n">
-        <v>6635.75</v>
+        <v>6685.75</v>
       </c>
       <c r="M5" t="n">
-        <v>6731.25</v>
+        <v>6800.25</v>
       </c>
       <c r="N5" t="n">
-        <v>6826.75</v>
+        <v>6914.75</v>
       </c>
       <c r="O5" t="n">
-        <v>7084.25</v>
+        <v>6962.25</v>
       </c>
       <c r="P5" s="6" t="n">
         <v/>
@@ -967,57 +963,57 @@
       </c>
       <c r="X5" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2025-10-20</t>
+          <t>2025-10-27</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>6721</v>
+        <v>6881</v>
       </c>
       <c r="C6" t="n">
-        <v>6841.25</v>
+        <v>6953.75</v>
       </c>
       <c r="D6" t="n">
-        <v>6690.75</v>
+        <v>6843.5</v>
       </c>
       <c r="E6" t="n">
-        <v>6827</v>
+        <v>6874</v>
       </c>
       <c r="F6" t="n">
-        <v>124.5</v>
+        <v>47</v>
       </c>
       <c r="G6" s="5" t="n">
-        <v>0.0186</v>
+        <v>0.0069</v>
       </c>
       <c r="H6" t="n">
-        <v>150.5</v>
+        <v>110.25</v>
       </c>
       <c r="I6" t="n">
-        <v>6375.75</v>
+        <v>6540.25</v>
       </c>
       <c r="J6" t="n">
-        <v>6523.75</v>
+        <v>6707</v>
       </c>
       <c r="K6" t="n">
-        <v>6604.75</v>
+        <v>6751.75</v>
       </c>
       <c r="L6" t="n">
-        <v>6685.75</v>
+        <v>6796.5</v>
       </c>
       <c r="M6" t="n">
-        <v>6800.25</v>
+        <v>6902.25</v>
       </c>
       <c r="N6" t="n">
-        <v>6914.75</v>
+        <v>7008</v>
       </c>
       <c r="O6" t="n">
-        <v>6962.25</v>
+        <v>6991.75</v>
       </c>
       <c r="P6" s="6" t="n">
         <v/>
@@ -1058,70 +1054,74 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2025-10-27</t>
+          <t>2025-11-03</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>6881</v>
+        <v>6878</v>
       </c>
       <c r="C7" t="n">
-        <v>6953.75</v>
+        <v>6909.5</v>
       </c>
       <c r="D7" t="n">
-        <v>6843.5</v>
+        <v>6655.5</v>
       </c>
       <c r="E7" t="n">
-        <v>6874</v>
+        <v>6753.75</v>
       </c>
       <c r="F7" t="n">
-        <v>47</v>
+        <v>-120.25</v>
       </c>
       <c r="G7" s="5" t="n">
-        <v>0.0069</v>
+        <v>-0.0175</v>
       </c>
       <c r="H7" t="n">
-        <v>110.25</v>
+        <v>254</v>
       </c>
       <c r="I7" t="n">
-        <v>6540.25</v>
+        <v>6733.25</v>
       </c>
       <c r="J7" t="n">
-        <v>6707</v>
+        <v>6751.44</v>
       </c>
       <c r="K7" t="n">
-        <v>6751.75</v>
+        <v>6818.88</v>
       </c>
       <c r="L7" t="n">
-        <v>6796.5</v>
+        <v>6886.31</v>
       </c>
       <c r="M7" t="n">
-        <v>6902.25</v>
+        <v>6929.12</v>
       </c>
       <c r="N7" t="n">
-        <v>7008</v>
+        <v>6971.94</v>
       </c>
       <c r="O7" t="n">
-        <v>6991.75</v>
-      </c>
-      <c r="P7" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q7" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R7" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S7" s="7" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T7" s="8" t="inlineStr">
+        <v>7064</v>
+      </c>
+      <c r="P7" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="Q7" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
+      <c r="R7" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S7" s="10" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T7" s="8" t="n">
+        <v/>
+      </c>
       <c r="U7" s="8" t="n">
         <v/>
       </c>
@@ -1133,83 +1133,75 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X7" t="inlineStr">
-        <is>
-          <t>強警訊</t>
-        </is>
-      </c>
+      <c r="X7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2025-11-03</t>
+          <t>2025-11-10</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>6878</v>
+        <v>6788</v>
       </c>
       <c r="C8" t="n">
-        <v>6909.5</v>
+        <v>6900.5</v>
       </c>
       <c r="D8" t="n">
-        <v>6655.5</v>
+        <v>6670.5</v>
       </c>
       <c r="E8" t="n">
-        <v>6753.75</v>
+        <v>6755.25</v>
       </c>
       <c r="F8" t="n">
-        <v>-120.25</v>
+        <v>1.5</v>
       </c>
       <c r="G8" s="5" t="n">
-        <v>-0.0175</v>
+        <v>0.0002</v>
       </c>
       <c r="H8" t="n">
-        <v>254</v>
+        <v>230</v>
       </c>
       <c r="I8" t="n">
-        <v>6733.25</v>
+        <v>6401.5</v>
       </c>
       <c r="J8" t="n">
-        <v>6751.44</v>
+        <v>6485.38</v>
       </c>
       <c r="K8" t="n">
-        <v>6818.88</v>
+        <v>6626.75</v>
       </c>
       <c r="L8" t="n">
-        <v>6886.31</v>
+        <v>6768.12</v>
       </c>
       <c r="M8" t="n">
-        <v>6929.12</v>
+        <v>6880.75</v>
       </c>
       <c r="N8" t="n">
-        <v>6971.94</v>
+        <v>6993.38</v>
       </c>
       <c r="O8" t="n">
-        <v>7064</v>
-      </c>
-      <c r="P8" s="6" t="inlineStr">
+        <v>7163.5</v>
+      </c>
+      <c r="P8" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q8" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R8" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S8" s="10" t="inlineStr">
+        <is>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T8" s="8" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="Q8" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="R8" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S8" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T8" s="8" t="n">
-        <v/>
-      </c>
       <c r="U8" s="8" t="n">
         <v/>
       </c>
@@ -1221,55 +1213,59 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X8" t="inlineStr"/>
+      <c r="X8" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2025-11-10</t>
+          <t>2025-11-17</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>6788</v>
+        <v>6764.75</v>
       </c>
       <c r="C9" t="n">
-        <v>6900.5</v>
+        <v>6801.5</v>
       </c>
       <c r="D9" t="n">
-        <v>6670.5</v>
+        <v>6525</v>
       </c>
       <c r="E9" t="n">
-        <v>6755.25</v>
+        <v>6620.25</v>
       </c>
       <c r="F9" t="n">
-        <v>1.5</v>
+        <v>-135</v>
       </c>
       <c r="G9" s="5" t="n">
-        <v>0.0002</v>
+        <v>-0.02</v>
       </c>
       <c r="H9" t="n">
-        <v>230</v>
+        <v>276.5</v>
       </c>
       <c r="I9" t="n">
-        <v>6401.5</v>
+        <v>6440.5</v>
       </c>
       <c r="J9" t="n">
-        <v>6485.38</v>
+        <v>6510.12</v>
       </c>
       <c r="K9" t="n">
-        <v>6626.75</v>
+        <v>6640.25</v>
       </c>
       <c r="L9" t="n">
-        <v>6768.12</v>
+        <v>6770.38</v>
       </c>
       <c r="M9" t="n">
-        <v>6880.75</v>
+        <v>6870.25</v>
       </c>
       <c r="N9" t="n">
-        <v>6993.38</v>
+        <v>6970.12</v>
       </c>
       <c r="O9" t="n">
-        <v>7163.5</v>
+        <v>7130.5</v>
       </c>
       <c r="P9" s="6" t="n">
         <v/>
@@ -1277,18 +1273,18 @@
       <c r="Q9" s="6" t="n">
         <v/>
       </c>
-      <c r="R9" s="6" t="n">
-        <v/>
+      <c r="R9" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="S9" s="10" t="inlineStr">
         <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T9" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T9" s="8" t="n">
+        <v/>
       </c>
       <c r="U9" s="8" t="n">
         <v/>
@@ -1301,59 +1297,55 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X9" t="inlineStr">
-        <is>
-          <t>中警訊</t>
-        </is>
-      </c>
+      <c r="X9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2025-11-17</t>
+          <t>2025-11-24</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>6764.75</v>
+        <v>6654.75</v>
       </c>
       <c r="C10" t="n">
-        <v>6801.5</v>
+        <v>6863.75</v>
       </c>
       <c r="D10" t="n">
-        <v>6525</v>
+        <v>6625</v>
       </c>
       <c r="E10" t="n">
-        <v>6620.25</v>
+        <v>6859.5</v>
       </c>
       <c r="F10" t="n">
-        <v>-135</v>
+        <v>239.25</v>
       </c>
       <c r="G10" s="5" t="n">
-        <v>-0.02</v>
+        <v>0.0361</v>
       </c>
       <c r="H10" t="n">
-        <v>276.5</v>
+        <v>238.75</v>
       </c>
       <c r="I10" t="n">
-        <v>6440.5</v>
+        <v>6248.5</v>
       </c>
       <c r="J10" t="n">
-        <v>6510.12</v>
+        <v>6322.25</v>
       </c>
       <c r="K10" t="n">
-        <v>6640.25</v>
+        <v>6482</v>
       </c>
       <c r="L10" t="n">
-        <v>6770.38</v>
+        <v>6641.75</v>
       </c>
       <c r="M10" t="n">
-        <v>6870.25</v>
+        <v>6758.5</v>
       </c>
       <c r="N10" t="n">
-        <v>6970.12</v>
+        <v>6875.25</v>
       </c>
       <c r="O10" t="n">
-        <v>7130.5</v>
+        <v>7078</v>
       </c>
       <c r="P10" s="6" t="n">
         <v/>
@@ -1361,22 +1353,24 @@
       <c r="Q10" s="6" t="n">
         <v/>
       </c>
-      <c r="R10" s="6" t="inlineStr">
+      <c r="R10" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S10" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T10" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U10" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="S10" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T10" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U10" s="8" t="n">
-        <v/>
-      </c>
       <c r="V10" s="8" t="n">
         <v/>
       </c>
@@ -1385,55 +1379,59 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X10" t="inlineStr"/>
+      <c r="X10" t="inlineStr">
+        <is>
+          <t>強警訊</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2025-11-24</t>
+          <t>2025-12-01</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>6654.75</v>
+        <v>6854.75</v>
       </c>
       <c r="C11" t="n">
-        <v>6863.75</v>
+        <v>6905</v>
       </c>
       <c r="D11" t="n">
-        <v>6625</v>
+        <v>6802</v>
       </c>
       <c r="E11" t="n">
-        <v>6859.5</v>
+        <v>6878.25</v>
       </c>
       <c r="F11" t="n">
-        <v>239.25</v>
+        <v>18.75</v>
       </c>
       <c r="G11" s="5" t="n">
-        <v>0.0361</v>
+        <v>0.0027</v>
       </c>
       <c r="H11" t="n">
-        <v>238.75</v>
+        <v>103</v>
       </c>
       <c r="I11" t="n">
-        <v>6248.5</v>
+        <v>6386.25</v>
       </c>
       <c r="J11" t="n">
-        <v>6322.25</v>
+        <v>6678.31</v>
       </c>
       <c r="K11" t="n">
-        <v>6482</v>
+        <v>6740.12</v>
       </c>
       <c r="L11" t="n">
-        <v>6641.75</v>
+        <v>6801.94</v>
       </c>
       <c r="M11" t="n">
-        <v>6758.5</v>
+        <v>6978.88</v>
       </c>
       <c r="N11" t="n">
-        <v>6875.25</v>
+        <v>7155.81</v>
       </c>
       <c r="O11" t="n">
-        <v>7078</v>
+        <v>7102.5</v>
       </c>
       <c r="P11" s="6" t="n">
         <v/>
@@ -1446,18 +1444,14 @@
       </c>
       <c r="S11" s="7" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T11" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U11" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T11" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U11" s="8" t="n">
+        <v/>
       </c>
       <c r="V11" s="8" t="n">
         <v/>
@@ -1476,50 +1470,50 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2025-12-01</t>
+          <t>2025-12-08</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>6854.75</v>
+        <v>6883</v>
       </c>
       <c r="C12" t="n">
-        <v>6905</v>
+        <v>6928.75</v>
       </c>
       <c r="D12" t="n">
-        <v>6802</v>
+        <v>6805</v>
       </c>
       <c r="E12" t="n">
-        <v>6878.25</v>
+        <v>6830.75</v>
       </c>
       <c r="F12" t="n">
-        <v>18.75</v>
+        <v>-47.5</v>
       </c>
       <c r="G12" s="5" t="n">
-        <v>0.0027</v>
+        <v>-0.0069</v>
       </c>
       <c r="H12" t="n">
-        <v>103</v>
+        <v>123.75</v>
       </c>
       <c r="I12" t="n">
-        <v>6386.25</v>
+        <v>6699</v>
       </c>
       <c r="J12" t="n">
-        <v>6678.31</v>
+        <v>6787.62</v>
       </c>
       <c r="K12" t="n">
-        <v>6740.12</v>
+        <v>6826.75</v>
       </c>
       <c r="L12" t="n">
-        <v>6801.94</v>
+        <v>6865.88</v>
       </c>
       <c r="M12" t="n">
-        <v>6978.88</v>
+        <v>6929.75</v>
       </c>
       <c r="N12" t="n">
-        <v>7155.81</v>
+        <v>6993.62</v>
       </c>
       <c r="O12" t="n">
-        <v>7102.5</v>
+        <v>7008</v>
       </c>
       <c r="P12" s="6" t="n">
         <v/>
@@ -1527,12 +1521,14 @@
       <c r="Q12" s="6" t="n">
         <v/>
       </c>
-      <c r="R12" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S12" s="7" t="inlineStr">
-        <is>
-          <t>↑C</t>
+      <c r="R12" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="S12" s="10" t="inlineStr">
+        <is>
+          <t>↓</t>
         </is>
       </c>
       <c r="T12" s="8" t="n">
@@ -1551,57 +1547,57 @@
       </c>
       <c r="X12" t="inlineStr">
         <is>
-          <t>強警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2025-12-08</t>
+          <t>2025-12-15</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>6883</v>
+        <v>6831</v>
       </c>
       <c r="C13" t="n">
-        <v>6928.75</v>
+        <v>6872.5</v>
       </c>
       <c r="D13" t="n">
-        <v>6805</v>
+        <v>6720.25</v>
       </c>
       <c r="E13" t="n">
-        <v>6830.75</v>
+        <v>6796.54</v>
       </c>
       <c r="F13" t="n">
-        <v>-47.5</v>
+        <v>-34.21</v>
       </c>
       <c r="G13" s="5" t="n">
-        <v>-0.0069</v>
+        <v>-0.005</v>
       </c>
       <c r="H13" t="n">
-        <v>123.75</v>
+        <v>152.25</v>
       </c>
       <c r="I13" t="n">
-        <v>6699</v>
+        <v>6681.25</v>
       </c>
       <c r="J13" t="n">
-        <v>6787.62</v>
+        <v>6688.94</v>
       </c>
       <c r="K13" t="n">
-        <v>6826.75</v>
+        <v>6768.88</v>
       </c>
       <c r="L13" t="n">
-        <v>6865.88</v>
+        <v>6848.81</v>
       </c>
       <c r="M13" t="n">
-        <v>6929.75</v>
+        <v>6892.62</v>
       </c>
       <c r="N13" t="n">
-        <v>6993.62</v>
+        <v>6936.44</v>
       </c>
       <c r="O13" t="n">
-        <v>7008</v>
+        <v>7052.5</v>
       </c>
       <c r="P13" s="6" t="n">
         <v/>
@@ -1633,59 +1629,55 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X13" t="inlineStr">
-        <is>
-          <t>中警訊</t>
-        </is>
-      </c>
+      <c r="X13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2025-12-15</t>
+          <t>2025-12-22</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>6831</v>
+        <v>6906.25</v>
       </c>
       <c r="C14" t="n">
-        <v>6872.5</v>
+        <v>6994</v>
       </c>
       <c r="D14" t="n">
-        <v>6720.25</v>
+        <v>6900.5</v>
       </c>
       <c r="E14" t="n">
-        <v>6796.54</v>
+        <v>6979.25</v>
       </c>
       <c r="F14" t="n">
-        <v>-34.21</v>
+        <v>182.71</v>
       </c>
       <c r="G14" s="5" t="n">
-        <v>-0.005</v>
+        <v>0.0269</v>
       </c>
       <c r="H14" t="n">
-        <v>152.25</v>
+        <v>93.5</v>
       </c>
       <c r="I14" t="n">
-        <v>6681.25</v>
+        <v>6568</v>
       </c>
       <c r="J14" t="n">
-        <v>6688.94</v>
+        <v>6644.37</v>
       </c>
       <c r="K14" t="n">
-        <v>6768.88</v>
+        <v>6720.42</v>
       </c>
       <c r="L14" t="n">
-        <v>6848.81</v>
+        <v>6796.46</v>
       </c>
       <c r="M14" t="n">
-        <v>6892.62</v>
+        <v>6872.67</v>
       </c>
       <c r="N14" t="n">
-        <v>6936.44</v>
+        <v>6948.87</v>
       </c>
       <c r="O14" t="n">
-        <v>7052.5</v>
+        <v>7024.75</v>
       </c>
       <c r="P14" s="6" t="n">
         <v/>
@@ -1693,28 +1685,30 @@
       <c r="Q14" s="6" t="n">
         <v/>
       </c>
-      <c r="R14" s="6" t="inlineStr">
+      <c r="R14" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S14" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T14" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U14" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="S14" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T14" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U14" s="8" t="n">
-        <v/>
-      </c>
       <c r="V14" s="8" t="n">
         <v/>
       </c>
-      <c r="W14" s="11" t="inlineStr">
-        <is>
-          <t>空方</t>
+      <c r="W14" s="9" t="inlineStr">
+        <is>
+          <t>多方</t>
         </is>
       </c>
       <c r="X14" t="inlineStr"/>
@@ -1722,81 +1716,81 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2025-12-22</t>
+          <t>2025-12-29</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>6906.25</v>
+        <v>6980.5</v>
       </c>
       <c r="C15" t="n">
-        <v>6994</v>
+        <v>6984.75</v>
       </c>
       <c r="D15" t="n">
+        <v>6866.75</v>
+      </c>
+      <c r="E15" t="n">
         <v>6900.5</v>
       </c>
-      <c r="E15" t="n">
-        <v>6979.25</v>
-      </c>
       <c r="F15" t="n">
-        <v>182.71</v>
+        <v>-78.75</v>
       </c>
       <c r="G15" s="5" t="n">
-        <v>0.0269</v>
+        <v>-0.0113</v>
       </c>
       <c r="H15" t="n">
-        <v>93.5</v>
+        <v>118</v>
       </c>
       <c r="I15" t="n">
-        <v>6568</v>
+        <v>6807</v>
       </c>
       <c r="J15" t="n">
-        <v>6644.37</v>
+        <v>6901.75</v>
       </c>
       <c r="K15" t="n">
-        <v>6720.42</v>
+        <v>6932.5</v>
       </c>
       <c r="L15" t="n">
-        <v>6796.46</v>
+        <v>6963.25</v>
       </c>
       <c r="M15" t="n">
-        <v>6872.67</v>
+        <v>7026</v>
       </c>
       <c r="N15" t="n">
-        <v>6948.87</v>
+        <v>7088.75</v>
       </c>
       <c r="O15" t="n">
-        <v>7024.75</v>
+        <v>7087.5</v>
       </c>
       <c r="P15" s="6" t="n">
         <v/>
       </c>
-      <c r="Q15" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R15" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S15" s="7" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T15" s="8" t="inlineStr">
+      <c r="Q15" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="R15" s="6" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="U15" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+      <c r="S15" s="10" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T15" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U15" s="8" t="n">
+        <v/>
       </c>
       <c r="V15" s="8" t="n">
         <v/>
       </c>
-      <c r="W15" s="9" t="inlineStr">
-        <is>
-          <t>多方</t>
+      <c r="W15" s="11" t="inlineStr">
+        <is>
+          <t>空方</t>
         </is>
       </c>
       <c r="X15" t="inlineStr"/>
@@ -1804,75 +1798,75 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2025-12-29</t>
+          <t>2026-01-05</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>6980.5</v>
+        <v>6911.5</v>
       </c>
       <c r="C16" t="n">
-        <v>6984.75</v>
+        <v>7017.5</v>
       </c>
       <c r="D16" t="n">
-        <v>6866.75</v>
+        <v>6899.5</v>
       </c>
       <c r="E16" t="n">
-        <v>6900.5</v>
+        <v>7005</v>
       </c>
       <c r="F16" t="n">
-        <v>-78.75</v>
+        <v>104.5</v>
       </c>
       <c r="G16" s="5" t="n">
-        <v>-0.0113</v>
+        <v>0.0151</v>
       </c>
       <c r="H16" t="n">
         <v>118</v>
       </c>
       <c r="I16" t="n">
-        <v>6807</v>
+        <v>6748.75</v>
       </c>
       <c r="J16" t="n">
-        <v>6901.75</v>
+        <v>6769.88</v>
       </c>
       <c r="K16" t="n">
-        <v>6932.5</v>
+        <v>6841.5</v>
       </c>
       <c r="L16" t="n">
-        <v>6963.25</v>
+        <v>6913.12</v>
       </c>
       <c r="M16" t="n">
-        <v>7026</v>
+        <v>6959.5</v>
       </c>
       <c r="N16" t="n">
-        <v>7088.75</v>
+        <v>7005.88</v>
       </c>
       <c r="O16" t="n">
-        <v>7087.5</v>
+        <v>7102.75</v>
       </c>
       <c r="P16" s="6" t="n">
         <v/>
       </c>
-      <c r="Q16" s="6" t="inlineStr">
+      <c r="Q16" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R16" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S16" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T16" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U16" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="R16" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S16" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T16" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U16" s="8" t="n">
-        <v/>
-      </c>
       <c r="V16" s="8" t="n">
         <v/>
       </c>
@@ -1881,55 +1875,59 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X16" t="inlineStr"/>
+      <c r="X16" t="inlineStr">
+        <is>
+          <t>強警訊</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-01-05</t>
+          <t>2026-01-12</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>6911.5</v>
+        <v>7007</v>
       </c>
       <c r="C17" t="n">
-        <v>7017.5</v>
+        <v>7036.25</v>
       </c>
       <c r="D17" t="n">
-        <v>6899.5</v>
+        <v>6923.25</v>
       </c>
       <c r="E17" t="n">
-        <v>7005</v>
+        <v>6976.75</v>
       </c>
       <c r="F17" t="n">
-        <v>104.5</v>
+        <v>-28.25</v>
       </c>
       <c r="G17" s="5" t="n">
-        <v>0.0151</v>
+        <v>-0.004</v>
       </c>
       <c r="H17" t="n">
-        <v>118</v>
+        <v>113</v>
       </c>
       <c r="I17" t="n">
-        <v>6748.75</v>
+        <v>6781.5</v>
       </c>
       <c r="J17" t="n">
-        <v>6769.88</v>
+        <v>6910.25</v>
       </c>
       <c r="K17" t="n">
-        <v>6841.5</v>
+        <v>6946</v>
       </c>
       <c r="L17" t="n">
-        <v>6913.12</v>
+        <v>6981.75</v>
       </c>
       <c r="M17" t="n">
-        <v>6959.5</v>
+        <v>7064</v>
       </c>
       <c r="N17" t="n">
-        <v>7005.88</v>
+        <v>7146.25</v>
       </c>
       <c r="O17" t="n">
-        <v>7102.75</v>
+        <v>7135.5</v>
       </c>
       <c r="P17" s="6" t="n">
         <v/>
@@ -1937,23 +1935,21 @@
       <c r="Q17" s="6" t="n">
         <v/>
       </c>
-      <c r="R17" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S17" s="7" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T17" s="8" t="inlineStr">
+      <c r="R17" s="6" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="U17" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+      <c r="S17" s="10" t="inlineStr">
+        <is>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T17" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U17" s="8" t="n">
+        <v/>
       </c>
       <c r="V17" s="8" t="n">
         <v/>
@@ -1965,72 +1961,74 @@
       </c>
       <c r="X17" t="inlineStr">
         <is>
-          <t>強警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2026-01-12</t>
+          <t>2026-01-19</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>7007</v>
+        <v>6918.25</v>
       </c>
       <c r="C18" t="n">
-        <v>7036.25</v>
+        <v>6969</v>
       </c>
       <c r="D18" t="n">
-        <v>6923.25</v>
+        <v>6814.5</v>
       </c>
       <c r="E18" t="n">
-        <v>6976.75</v>
+        <v>6945.75</v>
       </c>
       <c r="F18" t="n">
-        <v>-28.25</v>
+        <v>-31</v>
       </c>
       <c r="G18" s="5" t="n">
-        <v>-0.004</v>
+        <v>-0.0044</v>
       </c>
       <c r="H18" t="n">
-        <v>113</v>
+        <v>154.5</v>
       </c>
       <c r="I18" t="n">
-        <v>6781.5</v>
+        <v>6810.25</v>
       </c>
       <c r="J18" t="n">
-        <v>6910.25</v>
+        <v>6862.25</v>
       </c>
       <c r="K18" t="n">
-        <v>6946</v>
+        <v>6920.25</v>
       </c>
       <c r="L18" t="n">
-        <v>6981.75</v>
+        <v>6978.25</v>
       </c>
       <c r="M18" t="n">
-        <v>7064</v>
+        <v>7033.25</v>
       </c>
       <c r="N18" t="n">
-        <v>7146.25</v>
+        <v>7088.25</v>
       </c>
       <c r="O18" t="n">
-        <v>7135.5</v>
+        <v>7149.25</v>
       </c>
       <c r="P18" s="6" t="n">
         <v/>
       </c>
-      <c r="Q18" s="6" t="n">
-        <v/>
+      <c r="Q18" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="R18" s="6" t="inlineStr">
         <is>
-          <t>✓</t>
+          <t>△C</t>
         </is>
       </c>
       <c r="S18" s="10" t="inlineStr">
         <is>
-          <t>↓C</t>
+          <t>↓</t>
         </is>
       </c>
       <c r="T18" s="8" t="n">
@@ -2047,81 +2045,75 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X18" t="inlineStr">
-        <is>
-          <t>中警訊</t>
-        </is>
-      </c>
+      <c r="X18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-01-19</t>
+          <t>2026-01-26</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>6918.25</v>
+        <v>6904</v>
       </c>
       <c r="C19" t="n">
-        <v>6969</v>
+        <v>7043</v>
       </c>
       <c r="D19" t="n">
-        <v>6814.5</v>
+        <v>6879</v>
       </c>
       <c r="E19" t="n">
-        <v>6945.75</v>
+        <v>6965.75</v>
       </c>
       <c r="F19" t="n">
-        <v>-31</v>
+        <v>20</v>
       </c>
       <c r="G19" s="5" t="n">
-        <v>-0.0044</v>
+        <v>0.0029</v>
       </c>
       <c r="H19" t="n">
-        <v>154.5</v>
+        <v>164</v>
       </c>
       <c r="I19" t="n">
-        <v>6810.25</v>
+        <v>6660</v>
       </c>
       <c r="J19" t="n">
-        <v>6862.25</v>
+        <v>6818.25</v>
       </c>
       <c r="K19" t="n">
-        <v>6920.25</v>
+        <v>6868.5</v>
       </c>
       <c r="L19" t="n">
-        <v>6978.25</v>
+        <v>6918.75</v>
       </c>
       <c r="M19" t="n">
-        <v>7033.25</v>
+        <v>7023</v>
       </c>
       <c r="N19" t="n">
-        <v>7088.25</v>
+        <v>7127.25</v>
       </c>
       <c r="O19" t="n">
-        <v>7149.25</v>
+        <v>7123.5</v>
       </c>
       <c r="P19" s="6" t="n">
         <v/>
       </c>
-      <c r="Q19" s="6" t="inlineStr">
+      <c r="Q19" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R19" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S19" s="7" t="inlineStr">
+        <is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T19" s="8" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="R19" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="S19" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T19" s="8" t="n">
-        <v/>
-      </c>
       <c r="U19" s="8" t="n">
         <v/>
       </c>
@@ -2133,75 +2125,81 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X19" t="inlineStr"/>
+      <c r="X19" t="inlineStr">
+        <is>
+          <t>強警訊</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2026-01-26</t>
+          <t>2026-02-02</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>6904</v>
+        <v>6938.5</v>
       </c>
       <c r="C20" t="n">
-        <v>7043</v>
+        <v>7027.25</v>
       </c>
       <c r="D20" t="n">
-        <v>6879</v>
+        <v>6751.5</v>
       </c>
       <c r="E20" t="n">
-        <v>6965.75</v>
+        <v>6952.75</v>
       </c>
       <c r="F20" t="n">
-        <v>20</v>
+        <v>-13</v>
       </c>
       <c r="G20" s="5" t="n">
-        <v>0.0029</v>
+        <v>-0.0019</v>
       </c>
       <c r="H20" t="n">
-        <v>164</v>
+        <v>275.75</v>
       </c>
       <c r="I20" t="n">
-        <v>6660</v>
+        <v>6715</v>
       </c>
       <c r="J20" t="n">
-        <v>6818.25</v>
+        <v>6804.12</v>
       </c>
       <c r="K20" t="n">
-        <v>6868.5</v>
+        <v>6883.75</v>
       </c>
       <c r="L20" t="n">
-        <v>6918.75</v>
+        <v>6963.38</v>
       </c>
       <c r="M20" t="n">
-        <v>7023</v>
+        <v>7047.75</v>
       </c>
       <c r="N20" t="n">
-        <v>7127.25</v>
+        <v>7132.12</v>
       </c>
       <c r="O20" t="n">
-        <v>7123.5</v>
+        <v>7207</v>
       </c>
       <c r="P20" s="6" t="n">
         <v/>
       </c>
-      <c r="Q20" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R20" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S20" s="7" t="inlineStr">
-        <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T20" s="8" t="inlineStr">
+      <c r="Q20" s="6" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
+      <c r="R20" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S20" s="10" t="inlineStr">
+        <is>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T20" s="8" t="n">
+        <v/>
+      </c>
       <c r="U20" s="8" t="n">
         <v/>
       </c>
@@ -2213,76 +2211,70 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X20" t="inlineStr">
-        <is>
-          <t>強警訊</t>
-        </is>
-      </c>
+      <c r="X20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-02-02</t>
+          <t>2026-02-09</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>6938.5</v>
+        <v>6960.25</v>
       </c>
       <c r="C21" t="n">
-        <v>7027.25</v>
+        <v>7011.5</v>
       </c>
       <c r="D21" t="n">
-        <v>6751.5</v>
+        <v>6808.75</v>
       </c>
       <c r="E21" t="n">
-        <v>6952.75</v>
+        <v>6850.5</v>
       </c>
       <c r="F21" t="n">
-        <v>-13</v>
+        <v>-102.25</v>
       </c>
       <c r="G21" s="5" t="n">
-        <v>-0.0019</v>
+        <v>-0.0147</v>
       </c>
       <c r="H21" t="n">
-        <v>275.75</v>
+        <v>202.75</v>
       </c>
       <c r="I21" t="n">
-        <v>6715</v>
+        <v>6475.75</v>
       </c>
       <c r="J21" t="n">
-        <v>6804.12</v>
+        <v>6708.69</v>
       </c>
       <c r="K21" t="n">
-        <v>6883.75</v>
+        <v>6814.88</v>
       </c>
       <c r="L21" t="n">
-        <v>6963.38</v>
+        <v>6921.06</v>
       </c>
       <c r="M21" t="n">
-        <v>7047.75</v>
+        <v>7090.62</v>
       </c>
       <c r="N21" t="n">
-        <v>7132.12</v>
+        <v>7260.19</v>
       </c>
       <c r="O21" t="n">
-        <v>7207</v>
+        <v>7303</v>
       </c>
       <c r="P21" s="6" t="n">
         <v/>
       </c>
-      <c r="Q21" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="Q21" s="6" t="n">
+        <v/>
       </c>
       <c r="R21" s="6" t="inlineStr">
         <is>
-          <t>✓</t>
+          <t>△C</t>
         </is>
       </c>
       <c r="S21" s="10" t="inlineStr">
         <is>
-          <t>↓C</t>
+          <t>↓</t>
         </is>
       </c>
       <c r="T21" s="8" t="n">
@@ -2299,55 +2291,59 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X21" t="inlineStr"/>
+      <c r="X21" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2026-02-09</t>
+          <t>2026-02-16</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>6960.25</v>
+        <v>6852.5</v>
       </c>
       <c r="C22" t="n">
-        <v>7011.5</v>
+        <v>6931.5</v>
       </c>
       <c r="D22" t="n">
-        <v>6808.75</v>
+        <v>6791</v>
       </c>
       <c r="E22" t="n">
-        <v>6850.5</v>
+        <v>6923.25</v>
       </c>
       <c r="F22" t="n">
-        <v>-102.25</v>
+        <v>72.75</v>
       </c>
       <c r="G22" s="5" t="n">
-        <v>-0.0147</v>
+        <v>0.0106</v>
       </c>
       <c r="H22" t="n">
-        <v>202.75</v>
+        <v>140.5</v>
       </c>
       <c r="I22" t="n">
-        <v>6475.75</v>
+        <v>6606</v>
       </c>
       <c r="J22" t="n">
-        <v>6708.69</v>
+        <v>6617.94</v>
       </c>
       <c r="K22" t="n">
-        <v>6814.88</v>
+        <v>6749.12</v>
       </c>
       <c r="L22" t="n">
-        <v>6921.06</v>
+        <v>6880.31</v>
       </c>
       <c r="M22" t="n">
-        <v>7090.62</v>
+        <v>6951.88</v>
       </c>
       <c r="N22" t="n">
-        <v>7260.19</v>
+        <v>7023.44</v>
       </c>
       <c r="O22" t="n">
-        <v>7303</v>
+        <v>7214.25</v>
       </c>
       <c r="P22" s="6" t="n">
         <v/>
@@ -2355,18 +2351,18 @@
       <c r="Q22" s="6" t="n">
         <v/>
       </c>
-      <c r="R22" s="6" t="inlineStr">
+      <c r="R22" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S22" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T22" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
-      </c>
-      <c r="S22" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T22" s="8" t="n">
-        <v/>
       </c>
       <c r="U22" s="8" t="n">
         <v/>
@@ -2388,50 +2384,50 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-02-16</t>
+          <t>2026-02-23</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>6852.5</v>
+        <v>6918</v>
       </c>
       <c r="C23" t="n">
-        <v>6931.5</v>
+        <v>6983.75</v>
       </c>
       <c r="D23" t="n">
-        <v>6791</v>
+        <v>6828.5</v>
       </c>
       <c r="E23" t="n">
-        <v>6923.25</v>
+        <v>6889</v>
       </c>
       <c r="F23" t="n">
-        <v>72.75</v>
+        <v>-34.25</v>
       </c>
       <c r="G23" s="5" t="n">
-        <v>0.0106</v>
+        <v>-0.0049</v>
       </c>
       <c r="H23" t="n">
-        <v>140.5</v>
+        <v>155.25</v>
       </c>
       <c r="I23" t="n">
-        <v>6606</v>
+        <v>6650.5</v>
       </c>
       <c r="J23" t="n">
-        <v>6617.94</v>
+        <v>6813.75</v>
       </c>
       <c r="K23" t="n">
-        <v>6749.12</v>
+        <v>6853</v>
       </c>
       <c r="L23" t="n">
-        <v>6880.31</v>
+        <v>6892.25</v>
       </c>
       <c r="M23" t="n">
-        <v>6951.88</v>
+        <v>6993.5</v>
       </c>
       <c r="N23" t="n">
-        <v>7023.44</v>
+        <v>7094.75</v>
       </c>
       <c r="O23" t="n">
-        <v>7214.25</v>
+        <v>7072</v>
       </c>
       <c r="P23" s="6" t="n">
         <v/>
@@ -2439,18 +2435,18 @@
       <c r="Q23" s="6" t="n">
         <v/>
       </c>
-      <c r="R23" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S23" s="7" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T23" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+      <c r="R23" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S23" s="10" t="inlineStr">
+        <is>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T23" s="8" t="n">
+        <v/>
       </c>
       <c r="U23" s="8" t="n">
         <v/>
@@ -2465,63 +2461,65 @@
       </c>
       <c r="X23" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2026-02-23</t>
+          <t>2026-03-02</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>6918</v>
+        <v>6820</v>
       </c>
       <c r="C24" t="n">
-        <v>6983.75</v>
+        <v>6911.25</v>
       </c>
       <c r="D24" t="n">
-        <v>6828.5</v>
+        <v>6715.75</v>
       </c>
       <c r="E24" t="n">
-        <v>6889</v>
+        <v>6743.75</v>
       </c>
       <c r="F24" t="n">
-        <v>-34.25</v>
+        <v>-145.25</v>
       </c>
       <c r="G24" s="5" t="n">
-        <v>-0.0049</v>
+        <v>-0.0211</v>
       </c>
       <c r="H24" t="n">
-        <v>155.25</v>
+        <v>195.5</v>
       </c>
       <c r="I24" t="n">
-        <v>6650.5</v>
+        <v>6673.25</v>
       </c>
       <c r="J24" t="n">
-        <v>6813.75</v>
+        <v>6725.19</v>
       </c>
       <c r="K24" t="n">
-        <v>6853</v>
+        <v>6811.38</v>
       </c>
       <c r="L24" t="n">
-        <v>6892.25</v>
+        <v>6897.56</v>
       </c>
       <c r="M24" t="n">
-        <v>6993.5</v>
+        <v>6966.62</v>
       </c>
       <c r="N24" t="n">
-        <v>7094.75</v>
+        <v>7035.69</v>
       </c>
       <c r="O24" t="n">
-        <v>7072</v>
+        <v>7139</v>
       </c>
       <c r="P24" s="6" t="n">
         <v/>
       </c>
-      <c r="Q24" s="6" t="n">
-        <v/>
+      <c r="Q24" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="R24" s="6" t="inlineStr">
         <is>
@@ -2530,7 +2528,7 @@
       </c>
       <c r="S24" s="10" t="inlineStr">
         <is>
-          <t>↓C</t>
+          <t>↓</t>
         </is>
       </c>
       <c r="T24" s="8" t="n">
@@ -2547,80 +2545,76 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X24" t="inlineStr">
-        <is>
-          <t>中警訊</t>
-        </is>
-      </c>
+      <c r="X24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-09</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>6820</v>
+        <v>6685.5</v>
       </c>
       <c r="C25" t="n">
-        <v>6911.25</v>
+        <v>6852</v>
       </c>
       <c r="D25" t="n">
-        <v>6715.75</v>
+        <v>6584.5</v>
       </c>
       <c r="E25" t="n">
-        <v>6743.75</v>
+        <v>6636</v>
       </c>
       <c r="F25" t="n">
-        <v>-145.25</v>
+        <v>-107.75</v>
       </c>
       <c r="G25" s="5" t="n">
-        <v>-0.0211</v>
+        <v>-0.016</v>
       </c>
       <c r="H25" t="n">
-        <v>195.5</v>
+        <v>267.5</v>
       </c>
       <c r="I25" t="n">
-        <v>6673.25</v>
+        <v>6520.25</v>
       </c>
       <c r="J25" t="n">
-        <v>6725.19</v>
+        <v>6513.38</v>
       </c>
       <c r="K25" t="n">
-        <v>6811.38</v>
+        <v>6646</v>
       </c>
       <c r="L25" t="n">
-        <v>6897.56</v>
+        <v>6778.62</v>
       </c>
       <c r="M25" t="n">
-        <v>6966.62</v>
+        <v>6841.5</v>
       </c>
       <c r="N25" t="n">
-        <v>7035.69</v>
+        <v>6904.38</v>
       </c>
       <c r="O25" t="n">
-        <v>7139</v>
+        <v>7106.75</v>
       </c>
       <c r="P25" s="6" t="n">
         <v/>
       </c>
-      <c r="Q25" s="6" t="inlineStr">
+      <c r="Q25" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R25" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="R25" s="6" t="inlineStr">
+      <c r="S25" s="10" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T25" s="8" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
-      </c>
-      <c r="S25" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T25" s="8" t="n">
-        <v/>
       </c>
       <c r="U25" s="8" t="n">
         <v/>
@@ -2638,50 +2632,50 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-03-16</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>6685.5</v>
+        <v>6608.5</v>
       </c>
       <c r="C26" t="n">
-        <v>6852</v>
+        <v>6762.25</v>
       </c>
       <c r="D26" t="n">
-        <v>6584.5</v>
+        <v>6558</v>
       </c>
       <c r="E26" t="n">
-        <v>6636</v>
+        <v>6594.63</v>
       </c>
       <c r="F26" t="n">
-        <v>-107.75</v>
+        <v>-41.37</v>
       </c>
       <c r="G26" s="5" t="n">
-        <v>-0.016</v>
+        <v>-0.0062</v>
       </c>
       <c r="H26" t="n">
-        <v>267.5</v>
+        <v>204.25</v>
       </c>
       <c r="I26" t="n">
-        <v>6520.25</v>
+        <v>6317</v>
       </c>
       <c r="J26" t="n">
-        <v>6513.38</v>
+        <v>6327.38</v>
       </c>
       <c r="K26" t="n">
-        <v>6646</v>
+        <v>6502.25</v>
       </c>
       <c r="L26" t="n">
-        <v>6778.62</v>
+        <v>6677.12</v>
       </c>
       <c r="M26" t="n">
-        <v>6841.5</v>
+        <v>6769.75</v>
       </c>
       <c r="N26" t="n">
-        <v>6904.38</v>
+        <v>6862.38</v>
       </c>
       <c r="O26" t="n">
-        <v>7106.75</v>
+        <v>7119.5</v>
       </c>
       <c r="P26" s="6" t="n">
         <v/>
@@ -2689,20 +2683,16 @@
       <c r="Q26" s="6" t="n">
         <v/>
       </c>
-      <c r="R26" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+      <c r="R26" s="6" t="n">
+        <v/>
       </c>
       <c r="S26" s="10" t="inlineStr">
         <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T26" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T26" s="8" t="n">
+        <v/>
       </c>
       <c r="U26" s="8" t="n">
         <v/>
@@ -2720,67 +2710,73 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-23</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>6608.5</v>
+        <v>6510</v>
       </c>
       <c r="C27" t="n">
-        <v>6762.25</v>
+        <v>6748</v>
       </c>
       <c r="D27" t="n">
-        <v>6558</v>
+        <v>6389</v>
       </c>
       <c r="E27" t="n">
-        <v>6594.63</v>
+        <v>6412.25</v>
       </c>
       <c r="F27" t="n">
-        <v>-41.37</v>
+        <v>-182.38</v>
       </c>
       <c r="G27" s="5" t="n">
-        <v>-0.0062</v>
+        <v>-0.0277</v>
       </c>
       <c r="H27" t="n">
-        <v>204.25</v>
+        <v>359</v>
       </c>
       <c r="I27" t="n">
-        <v>6317</v>
+        <v>6353.75</v>
       </c>
       <c r="J27" t="n">
-        <v>6327.38</v>
+        <v>6357.63</v>
       </c>
       <c r="K27" t="n">
-        <v>6502.25</v>
+        <v>6492.5</v>
       </c>
       <c r="L27" t="n">
-        <v>6677.12</v>
+        <v>6627.38</v>
       </c>
       <c r="M27" t="n">
-        <v>6769.75</v>
+        <v>6696.75</v>
       </c>
       <c r="N27" t="n">
-        <v>6862.38</v>
+        <v>6766.13</v>
       </c>
       <c r="O27" t="n">
-        <v>7119.5</v>
+        <v>6966.5</v>
       </c>
       <c r="P27" s="6" t="n">
         <v/>
       </c>
-      <c r="Q27" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R27" s="6" t="n">
-        <v/>
+      <c r="Q27" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="R27" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S27" s="10" t="inlineStr">
         <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T27" s="8" t="n">
-        <v/>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T27" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="U27" s="8" t="n">
         <v/>
@@ -2798,74 +2794,70 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2026-03-23</t>
+          <t>2026-03-30</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>6510</v>
+        <v>6380</v>
       </c>
       <c r="C28" t="n">
-        <v>6748</v>
+        <v>6653.75</v>
       </c>
       <c r="D28" t="n">
-        <v>6389</v>
+        <v>6353.25</v>
       </c>
       <c r="E28" t="n">
-        <v>6412.25</v>
+        <v>6603.75</v>
       </c>
       <c r="F28" t="n">
-        <v>-182.38</v>
+        <v>191.5</v>
       </c>
       <c r="G28" s="5" t="n">
-        <v>-0.0277</v>
+        <v>0.0299</v>
       </c>
       <c r="H28" t="n">
-        <v>359</v>
+        <v>300.5</v>
       </c>
       <c r="I28" t="n">
-        <v>6353.75</v>
+        <v>6030</v>
       </c>
       <c r="J28" t="n">
-        <v>6357.63</v>
+        <v>5975.12</v>
       </c>
       <c r="K28" t="n">
-        <v>6492.5</v>
+        <v>6232.75</v>
       </c>
       <c r="L28" t="n">
-        <v>6627.38</v>
+        <v>6490.38</v>
       </c>
       <c r="M28" t="n">
-        <v>6696.75</v>
+        <v>6591.75</v>
       </c>
       <c r="N28" t="n">
-        <v>6766.13</v>
+        <v>6693.12</v>
       </c>
       <c r="O28" t="n">
-        <v>6966.5</v>
+        <v>7107</v>
       </c>
       <c r="P28" s="6" t="n">
         <v/>
       </c>
-      <c r="Q28" s="6" t="inlineStr">
+      <c r="Q28" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R28" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S28" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T28" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="R28" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S28" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T28" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
       <c r="U28" s="8" t="n">
         <v/>
       </c>
@@ -2877,55 +2869,59 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X28" t="inlineStr"/>
+      <c r="X28" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-04-06</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>6380</v>
+        <v>6590</v>
       </c>
       <c r="C29" t="n">
-        <v>6653.75</v>
+        <v>6888</v>
       </c>
       <c r="D29" t="n">
-        <v>6353.25</v>
+        <v>6567</v>
       </c>
       <c r="E29" t="n">
-        <v>6603.75</v>
+        <v>6855.25</v>
       </c>
       <c r="F29" t="n">
-        <v>191.5</v>
+        <v>251.5</v>
       </c>
       <c r="G29" s="5" t="n">
-        <v>0.0299</v>
+        <v>0.0381</v>
       </c>
       <c r="H29" t="n">
-        <v>300.5</v>
+        <v>321</v>
       </c>
       <c r="I29" t="n">
-        <v>6030</v>
+        <v>6052.75</v>
       </c>
       <c r="J29" t="n">
-        <v>5975.12</v>
+        <v>6353.38</v>
       </c>
       <c r="K29" t="n">
-        <v>6232.75</v>
+        <v>6453.5</v>
       </c>
       <c r="L29" t="n">
-        <v>6490.38</v>
+        <v>6553.62</v>
       </c>
       <c r="M29" t="n">
-        <v>6591.75</v>
+        <v>6754</v>
       </c>
       <c r="N29" t="n">
-        <v>6693.12</v>
+        <v>6954.38</v>
       </c>
       <c r="O29" t="n">
-        <v>7107</v>
+        <v>6954.25</v>
       </c>
       <c r="P29" s="6" t="n">
         <v/>
@@ -2943,15 +2939,17 @@
       </c>
       <c r="T29" s="8" t="inlineStr">
         <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U29" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V29" s="8" t="inlineStr">
+        <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="U29" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V29" s="8" t="n">
-        <v/>
-      </c>
       <c r="W29" s="11" t="inlineStr">
         <is>
           <t>空方</t>
@@ -2959,57 +2957,57 @@
       </c>
       <c r="X29" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2026-04-06</t>
+          <t>2026-04-13</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>6590</v>
+        <v>6780</v>
       </c>
       <c r="C30" t="n">
-        <v>6888</v>
+        <v>7185.75</v>
       </c>
       <c r="D30" t="n">
-        <v>6567</v>
+        <v>6767</v>
       </c>
       <c r="E30" t="n">
-        <v>6855.25</v>
+        <v>7161.5</v>
       </c>
       <c r="F30" t="n">
-        <v>251.5</v>
+        <v>306.25</v>
       </c>
       <c r="G30" s="5" t="n">
-        <v>0.0381</v>
+        <v>0.0447</v>
       </c>
       <c r="H30" t="n">
-        <v>321</v>
+        <v>418.75</v>
       </c>
       <c r="I30" t="n">
-        <v>6052.75</v>
+        <v>6246</v>
       </c>
       <c r="J30" t="n">
-        <v>6353.38</v>
+        <v>6598.12</v>
       </c>
       <c r="K30" t="n">
-        <v>6453.5</v>
+        <v>6694.75</v>
       </c>
       <c r="L30" t="n">
-        <v>6553.62</v>
+        <v>6791.38</v>
       </c>
       <c r="M30" t="n">
-        <v>6754</v>
+        <v>7015.75</v>
       </c>
       <c r="N30" t="n">
-        <v>6954.38</v>
+        <v>7240.12</v>
       </c>
       <c r="O30" t="n">
-        <v>6954.25</v>
+        <v>7209</v>
       </c>
       <c r="P30" s="6" t="n">
         <v/>
@@ -3052,50 +3050,50 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026-04-13</t>
+          <t>2026-04-20</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>6780</v>
+        <v>7102.5</v>
       </c>
       <c r="C31" t="n">
-        <v>7185.75</v>
+        <v>7200.5</v>
       </c>
       <c r="D31" t="n">
-        <v>6767</v>
+        <v>7079.25</v>
       </c>
       <c r="E31" t="n">
-        <v>7161.5</v>
+        <v>7194.75</v>
       </c>
       <c r="F31" t="n">
-        <v>306.25</v>
+        <v>33.25</v>
       </c>
       <c r="G31" s="5" t="n">
-        <v>0.0447</v>
+        <v>0.0046</v>
       </c>
       <c r="H31" t="n">
-        <v>418.75</v>
+        <v>121.25</v>
       </c>
       <c r="I31" t="n">
-        <v>6246</v>
+        <v>6348.25</v>
       </c>
       <c r="J31" t="n">
-        <v>6598.12</v>
+        <v>6835.31</v>
       </c>
       <c r="K31" t="n">
-        <v>6694.75</v>
+        <v>6952.12</v>
       </c>
       <c r="L31" t="n">
-        <v>6791.38</v>
+        <v>7068.94</v>
       </c>
       <c r="M31" t="n">
-        <v>7015.75</v>
+        <v>7370.88</v>
       </c>
       <c r="N31" t="n">
-        <v>7240.12</v>
+        <v>7672.81</v>
       </c>
       <c r="O31" t="n">
-        <v>7209</v>
+        <v>7604.5</v>
       </c>
       <c r="P31" s="6" t="n">
         <v/>
@@ -3108,21 +3106,17 @@
       </c>
       <c r="S31" s="7" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T31" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T31" s="8" t="n">
+        <v/>
       </c>
       <c r="U31" s="8" t="n">
         <v/>
       </c>
-      <c r="V31" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+      <c r="V31" s="8" t="n">
+        <v/>
       </c>
       <c r="W31" s="11" t="inlineStr">
         <is>
@@ -3138,50 +3132,50 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
+          <t>2026-04-27</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>7102.5</v>
+        <v>7185</v>
       </c>
       <c r="C32" t="n">
-        <v>7200.5</v>
+        <v>7300.75</v>
       </c>
       <c r="D32" t="n">
-        <v>7079.25</v>
+        <v>7131.25</v>
       </c>
       <c r="E32" t="n">
-        <v>7194.75</v>
+        <v>7258</v>
       </c>
       <c r="F32" t="n">
-        <v>33.25</v>
+        <v>63.25</v>
       </c>
       <c r="G32" s="5" t="n">
-        <v>0.0046</v>
+        <v>0.008800000000000001</v>
       </c>
       <c r="H32" t="n">
-        <v>121.25</v>
+        <v>169.5</v>
       </c>
       <c r="I32" t="n">
-        <v>6348.25</v>
+        <v>6958</v>
       </c>
       <c r="J32" t="n">
-        <v>6835.31</v>
+        <v>7100.94</v>
       </c>
       <c r="K32" t="n">
-        <v>6952.12</v>
+        <v>7134.12</v>
       </c>
       <c r="L32" t="n">
-        <v>7068.94</v>
+        <v>7167.31</v>
       </c>
       <c r="M32" t="n">
-        <v>7370.88</v>
+        <v>7255.38</v>
       </c>
       <c r="N32" t="n">
-        <v>7672.81</v>
+        <v>7343.44</v>
       </c>
       <c r="O32" t="n">
-        <v>7604.5</v>
+        <v>7321.75</v>
       </c>
       <c r="P32" s="6" t="n">
         <v/>
@@ -3189,16 +3183,20 @@
       <c r="Q32" s="6" t="n">
         <v/>
       </c>
-      <c r="R32" s="6" t="n">
-        <v/>
+      <c r="R32" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S32" s="7" t="inlineStr">
         <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T32" s="8" t="n">
-        <v/>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T32" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="U32" s="8" t="n">
         <v/>
@@ -3220,50 +3218,50 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-05-04</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>7185</v>
+        <v>7276.25</v>
       </c>
       <c r="C33" t="n">
-        <v>7300.75</v>
+        <v>7427.75</v>
       </c>
       <c r="D33" t="n">
-        <v>7131.25</v>
+        <v>7199.5</v>
       </c>
       <c r="E33" t="n">
-        <v>7258</v>
+        <v>7419</v>
       </c>
       <c r="F33" t="n">
-        <v>63.25</v>
+        <v>161</v>
       </c>
       <c r="G33" s="5" t="n">
-        <v>0.008800000000000001</v>
+        <v>0.0222</v>
       </c>
       <c r="H33" t="n">
-        <v>169.5</v>
+        <v>228.25</v>
       </c>
       <c r="I33" t="n">
-        <v>6958</v>
+        <v>6961.75</v>
       </c>
       <c r="J33" t="n">
-        <v>7100.94</v>
+        <v>7109.5</v>
       </c>
       <c r="K33" t="n">
-        <v>7134.12</v>
+        <v>7173.25</v>
       </c>
       <c r="L33" t="n">
-        <v>7167.31</v>
+        <v>7237</v>
       </c>
       <c r="M33" t="n">
-        <v>7255.38</v>
+        <v>7342.75</v>
       </c>
       <c r="N33" t="n">
-        <v>7343.44</v>
+        <v>7448.5</v>
       </c>
       <c r="O33" t="n">
-        <v>7321.75</v>
+        <v>7470.25</v>
       </c>
       <c r="P33" s="6" t="n">
         <v/>
@@ -3271,23 +3269,23 @@
       <c r="Q33" s="6" t="n">
         <v/>
       </c>
-      <c r="R33" s="6" t="inlineStr">
+      <c r="R33" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S33" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T33" s="8" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="S33" s="7" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T33" s="8" t="inlineStr">
+      <c r="U33" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
-      </c>
-      <c r="U33" s="8" t="n">
-        <v/>
       </c>
       <c r="V33" s="8" t="n">
         <v/>
@@ -3306,50 +3304,50 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2026-05-04</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>7276.25</v>
+        <v>7403.5</v>
       </c>
       <c r="C34" t="n">
-        <v>7427.75</v>
+        <v>7540</v>
       </c>
       <c r="D34" t="n">
-        <v>7199.5</v>
+        <v>7363.25</v>
       </c>
       <c r="E34" t="n">
-        <v>7419</v>
+        <v>7432.25</v>
       </c>
       <c r="F34" t="n">
-        <v>161</v>
+        <v>13.25</v>
       </c>
       <c r="G34" s="5" t="n">
-        <v>0.0222</v>
+        <v>0.0018</v>
       </c>
       <c r="H34" t="n">
-        <v>228.25</v>
+        <v>176.75</v>
       </c>
       <c r="I34" t="n">
-        <v>6961.75</v>
+        <v>6971.25</v>
       </c>
       <c r="J34" t="n">
-        <v>7109.5</v>
+        <v>7243.44</v>
       </c>
       <c r="K34" t="n">
-        <v>7173.25</v>
+        <v>7304.88</v>
       </c>
       <c r="L34" t="n">
-        <v>7237</v>
+        <v>7366.31</v>
       </c>
       <c r="M34" t="n">
-        <v>7342.75</v>
+        <v>7533.12</v>
       </c>
       <c r="N34" t="n">
-        <v>7448.5</v>
+        <v>7699.94</v>
       </c>
       <c r="O34" t="n">
-        <v>7470.25</v>
+        <v>7656</v>
       </c>
       <c r="P34" s="6" t="n">
         <v/>
@@ -3362,7 +3360,7 @@
       </c>
       <c r="S34" s="7" t="inlineStr">
         <is>
-          <t>↑</t>
+          <t>↑C</t>
         </is>
       </c>
       <c r="T34" s="8" t="inlineStr">
@@ -3370,10 +3368,8 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="U34" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+      <c r="U34" s="8" t="n">
+        <v/>
       </c>
       <c r="V34" s="8" t="n">
         <v/>
@@ -3392,50 +3388,50 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-05-18</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>7403.5</v>
+        <v>7410</v>
       </c>
       <c r="C35" t="n">
-        <v>7540</v>
+        <v>7524</v>
       </c>
       <c r="D35" t="n">
-        <v>7363.25</v>
+        <v>7354.25</v>
       </c>
       <c r="E35" t="n">
-        <v>7432.25</v>
+        <v>7491</v>
       </c>
       <c r="F35" t="n">
-        <v>13.25</v>
+        <v>58.75</v>
       </c>
       <c r="G35" s="5" t="n">
-        <v>0.0018</v>
+        <v>0.007900000000000001</v>
       </c>
       <c r="H35" t="n">
-        <v>176.75</v>
+        <v>169.75</v>
       </c>
       <c r="I35" t="n">
-        <v>6971.25</v>
+        <v>7186.5</v>
       </c>
       <c r="J35" t="n">
-        <v>7243.44</v>
+        <v>7245.81</v>
       </c>
       <c r="K35" t="n">
-        <v>7304.88</v>
+        <v>7343.88</v>
       </c>
       <c r="L35" t="n">
-        <v>7366.31</v>
+        <v>7441.94</v>
       </c>
       <c r="M35" t="n">
-        <v>7533.12</v>
+        <v>7520.62</v>
       </c>
       <c r="N35" t="n">
-        <v>7699.94</v>
+        <v>7599.31</v>
       </c>
       <c r="O35" t="n">
-        <v>7656</v>
+        <v>7716.75</v>
       </c>
       <c r="P35" s="6" t="n">
         <v/>
@@ -3448,12 +3444,12 @@
       </c>
       <c r="S35" s="7" t="inlineStr">
         <is>
-          <t>↑C</t>
+          <t>↑</t>
         </is>
       </c>
       <c r="T35" s="8" t="inlineStr">
         <is>
-          <t>✓</t>
+          <t>△C</t>
         </is>
       </c>
       <c r="U35" s="8" t="n">
@@ -3469,57 +3465,57 @@
       </c>
       <c r="X35" t="inlineStr">
         <is>
-          <t>強警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-05-25</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>7410</v>
+        <v>7519</v>
       </c>
       <c r="C36" t="n">
-        <v>7524</v>
+        <v>7611.5</v>
       </c>
       <c r="D36" t="n">
-        <v>7354.25</v>
+        <v>7505.75</v>
       </c>
       <c r="E36" t="n">
-        <v>7491</v>
+        <v>7595.75</v>
       </c>
       <c r="F36" t="n">
-        <v>58.75</v>
+        <v>104.75</v>
       </c>
       <c r="G36" s="5" t="n">
-        <v>0.007900000000000001</v>
+        <v>0.014</v>
       </c>
       <c r="H36" t="n">
-        <v>169.75</v>
+        <v>105.75</v>
       </c>
       <c r="I36" t="n">
-        <v>7186.5</v>
+        <v>7184.5</v>
       </c>
       <c r="J36" t="n">
-        <v>7245.81</v>
+        <v>7347.19</v>
       </c>
       <c r="K36" t="n">
-        <v>7343.88</v>
+        <v>7406.12</v>
       </c>
       <c r="L36" t="n">
-        <v>7441.94</v>
+        <v>7465.06</v>
       </c>
       <c r="M36" t="n">
-        <v>7520.62</v>
+        <v>7575.88</v>
       </c>
       <c r="N36" t="n">
-        <v>7599.31</v>
+        <v>7686.69</v>
       </c>
       <c r="O36" t="n">
-        <v>7716.75</v>
+        <v>7693.75</v>
       </c>
       <c r="P36" s="6" t="n">
         <v/>
@@ -3553,77 +3549,81 @@
       </c>
       <c r="X36" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2026-05-25</t>
+          <t>2026-06-01</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>7519</v>
+        <v>7595</v>
       </c>
       <c r="C37" t="n">
-        <v>7611.5</v>
+        <v>7632.25</v>
       </c>
       <c r="D37" t="n">
-        <v>7505.75</v>
+        <v>7359</v>
       </c>
       <c r="E37" t="n">
-        <v>7595.75</v>
+        <v>7400.5</v>
       </c>
       <c r="F37" t="n">
-        <v>104.75</v>
+        <v>-195.25</v>
       </c>
       <c r="G37" s="5" t="n">
-        <v>0.014</v>
+        <v>-0.0257</v>
       </c>
       <c r="H37" t="n">
-        <v>105.75</v>
+        <v>273.25</v>
       </c>
       <c r="I37" t="n">
-        <v>7184.5</v>
+        <v>7400</v>
       </c>
       <c r="J37" t="n">
-        <v>7347.19</v>
+        <v>7508.56</v>
       </c>
       <c r="K37" t="n">
-        <v>7406.12</v>
+        <v>7542.88</v>
       </c>
       <c r="L37" t="n">
-        <v>7465.06</v>
+        <v>7577.19</v>
       </c>
       <c r="M37" t="n">
-        <v>7575.88</v>
+        <v>7648.62</v>
       </c>
       <c r="N37" t="n">
-        <v>7686.69</v>
+        <v>7720.06</v>
       </c>
       <c r="O37" t="n">
-        <v>7693.75</v>
-      </c>
-      <c r="P37" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q37" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R37" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S37" s="7" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T37" s="8" t="inlineStr">
+        <v>7717.25</v>
+      </c>
+      <c r="P37" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
+      <c r="Q37" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="R37" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S37" s="10" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T37" s="8" t="n">
+        <v/>
+      </c>
       <c r="U37" s="8" t="n">
         <v/>
       </c>
@@ -3637,76 +3637,72 @@
       </c>
       <c r="X37" t="inlineStr">
         <is>
-          <t>強警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-06-08</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>7595</v>
+        <v>7368</v>
       </c>
       <c r="C38" t="n">
-        <v>7632.25</v>
+        <v>7491</v>
       </c>
       <c r="D38" t="n">
-        <v>7359</v>
+        <v>7232.25</v>
       </c>
       <c r="E38" t="n">
-        <v>7400.5</v>
+        <v>7435</v>
       </c>
       <c r="F38" t="n">
-        <v>-195.25</v>
+        <v>34.5</v>
       </c>
       <c r="G38" s="5" t="n">
-        <v>-0.0257</v>
+        <v>0.0047</v>
       </c>
       <c r="H38" t="n">
-        <v>273.25</v>
+        <v>258.75</v>
       </c>
       <c r="I38" t="n">
-        <v>7400</v>
+        <v>7085.75</v>
       </c>
       <c r="J38" t="n">
-        <v>7508.56</v>
+        <v>7079.69</v>
       </c>
       <c r="K38" t="n">
-        <v>7542.88</v>
+        <v>7263.88</v>
       </c>
       <c r="L38" t="n">
-        <v>7577.19</v>
+        <v>7448.06</v>
       </c>
       <c r="M38" t="n">
-        <v>7648.62</v>
+        <v>7537.12</v>
       </c>
       <c r="N38" t="n">
-        <v>7720.06</v>
+        <v>7626.19</v>
       </c>
       <c r="O38" t="n">
-        <v>7717.25</v>
-      </c>
-      <c r="P38" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="Q38" s="6" t="inlineStr">
+        <v>7905.5</v>
+      </c>
+      <c r="P38" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q38" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R38" s="6" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="R38" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
       <c r="S38" s="10" t="inlineStr">
         <is>
-          <t>↓</t>
+          <t>↓C</t>
         </is>
       </c>
       <c r="T38" s="8" t="n">
@@ -3732,50 +3728,50 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>7368</v>
+        <v>7480</v>
       </c>
       <c r="C39" t="n">
-        <v>7491</v>
+        <v>7584.5</v>
       </c>
       <c r="D39" t="n">
-        <v>7232.25</v>
+        <v>7405</v>
       </c>
       <c r="E39" t="n">
-        <v>7435</v>
+        <v>7556.25</v>
       </c>
       <c r="F39" t="n">
-        <v>34.5</v>
+        <v>121.25</v>
       </c>
       <c r="G39" s="5" t="n">
-        <v>0.0047</v>
+        <v>0.0163</v>
       </c>
       <c r="H39" t="n">
-        <v>258.75</v>
+        <v>179.5</v>
       </c>
       <c r="I39" t="n">
-        <v>7085.75</v>
+        <v>6973.5</v>
       </c>
       <c r="J39" t="n">
-        <v>7079.69</v>
+        <v>7212.94</v>
       </c>
       <c r="K39" t="n">
-        <v>7263.88</v>
+        <v>7305.62</v>
       </c>
       <c r="L39" t="n">
-        <v>7448.06</v>
+        <v>7398.31</v>
       </c>
       <c r="M39" t="n">
-        <v>7537.12</v>
+        <v>7564.38</v>
       </c>
       <c r="N39" t="n">
-        <v>7626.19</v>
+        <v>7730.44</v>
       </c>
       <c r="O39" t="n">
-        <v>7905.5</v>
+        <v>7749.75</v>
       </c>
       <c r="P39" s="6" t="n">
         <v/>
@@ -3783,18 +3779,18 @@
       <c r="Q39" s="6" t="n">
         <v/>
       </c>
-      <c r="R39" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S39" s="10" t="inlineStr">
-        <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T39" s="8" t="n">
-        <v/>
+      <c r="R39" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S39" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T39" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="U39" s="8" t="n">
         <v/>
@@ -3809,77 +3805,79 @@
       </c>
       <c r="X39" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="B40" t="n">
-        <v>7480</v>
+        <v>7543.25</v>
       </c>
       <c r="C40" t="n">
-        <v>7584.5</v>
+        <v>7599.25</v>
       </c>
       <c r="D40" t="n">
-        <v>7405</v>
+        <v>7357.25</v>
       </c>
       <c r="E40" t="n">
-        <v>7556.25</v>
+        <v>7401.75</v>
       </c>
       <c r="F40" t="n">
-        <v>121.25</v>
+        <v>-154.5</v>
       </c>
       <c r="G40" s="5" t="n">
-        <v>0.0163</v>
+        <v>-0.0204</v>
       </c>
       <c r="H40" t="n">
-        <v>179.5</v>
+        <v>242</v>
       </c>
       <c r="I40" t="n">
-        <v>6973.5</v>
+        <v>7225.5</v>
       </c>
       <c r="J40" t="n">
-        <v>7212.94</v>
+        <v>7407.5</v>
       </c>
       <c r="K40" t="n">
-        <v>7305.62</v>
+        <v>7466.5</v>
       </c>
       <c r="L40" t="n">
-        <v>7398.31</v>
+        <v>7525.5</v>
       </c>
       <c r="M40" t="n">
-        <v>7564.38</v>
+        <v>7646</v>
       </c>
       <c r="N40" t="n">
-        <v>7730.44</v>
+        <v>7766.5</v>
       </c>
       <c r="O40" t="n">
-        <v>7749.75</v>
+        <v>7764</v>
       </c>
       <c r="P40" s="6" t="n">
         <v/>
       </c>
-      <c r="Q40" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R40" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S40" s="7" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T40" s="8" t="inlineStr">
+      <c r="Q40" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
+      <c r="R40" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S40" s="10" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T40" s="8" t="n">
+        <v/>
+      </c>
       <c r="U40" s="8" t="n">
         <v/>
       </c>
@@ -3893,79 +3891,77 @@
       </c>
       <c r="X40" t="inlineStr">
         <is>
-          <t>強警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="B41" t="n">
-        <v>7543.25</v>
+        <v>7398</v>
       </c>
       <c r="C41" t="n">
-        <v>7599.25</v>
+        <v>7593.75</v>
       </c>
       <c r="D41" t="n">
-        <v>7357.25</v>
+        <v>7398</v>
       </c>
       <c r="E41" t="n">
-        <v>7401.75</v>
+        <v>7557</v>
       </c>
       <c r="F41" t="n">
-        <v>-154.5</v>
+        <v>155.25</v>
       </c>
       <c r="G41" s="5" t="n">
-        <v>-0.0204</v>
+        <v>0.021</v>
       </c>
       <c r="H41" t="n">
-        <v>242</v>
+        <v>195.75</v>
       </c>
       <c r="I41" t="n">
-        <v>7225.5</v>
+        <v>7115.25</v>
       </c>
       <c r="J41" t="n">
-        <v>7407.5</v>
+        <v>7121.5</v>
       </c>
       <c r="K41" t="n">
-        <v>7466.5</v>
+        <v>7280.75</v>
       </c>
       <c r="L41" t="n">
-        <v>7525.5</v>
+        <v>7440</v>
       </c>
       <c r="M41" t="n">
-        <v>7646</v>
+        <v>7522.75</v>
       </c>
       <c r="N41" t="n">
-        <v>7766.5</v>
+        <v>7605.5</v>
       </c>
       <c r="O41" t="n">
-        <v>7764</v>
+        <v>7841.25</v>
       </c>
       <c r="P41" s="6" t="n">
         <v/>
       </c>
-      <c r="Q41" s="6" t="inlineStr">
+      <c r="Q41" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R41" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S41" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T41" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="R41" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S41" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T41" s="8" t="n">
-        <v/>
-      </c>
       <c r="U41" s="8" t="n">
         <v/>
       </c>
@@ -3979,57 +3975,57 @@
       </c>
       <c r="X41" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="B42" t="n">
-        <v>7398</v>
+        <v>7562.25</v>
       </c>
       <c r="C42" t="n">
-        <v>7593.75</v>
+        <v>7628.75</v>
       </c>
       <c r="D42" t="n">
-        <v>7398</v>
+        <v>7468.5</v>
       </c>
       <c r="E42" t="n">
-        <v>7557</v>
+        <v>7620.25</v>
       </c>
       <c r="F42" t="n">
-        <v>155.25</v>
+        <v>63.25</v>
       </c>
       <c r="G42" s="5" t="n">
-        <v>0.021</v>
+        <v>0.008399999999999999</v>
       </c>
       <c r="H42" t="n">
-        <v>195.75</v>
+        <v>160.25</v>
       </c>
       <c r="I42" t="n">
-        <v>7115.25</v>
+        <v>7202.25</v>
       </c>
       <c r="J42" t="n">
-        <v>7121.5</v>
+        <v>7391.81</v>
       </c>
       <c r="K42" t="n">
-        <v>7280.75</v>
+        <v>7459.12</v>
       </c>
       <c r="L42" t="n">
-        <v>7440</v>
+        <v>7526.44</v>
       </c>
       <c r="M42" t="n">
-        <v>7522.75</v>
+        <v>7654.88</v>
       </c>
       <c r="N42" t="n">
-        <v>7605.5</v>
+        <v>7783.31</v>
       </c>
       <c r="O42" t="n">
-        <v>7841.25</v>
+        <v>7789.5</v>
       </c>
       <c r="P42" s="6" t="n">
         <v/>
@@ -4063,77 +4059,79 @@
       </c>
       <c r="X42" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="B43" t="n">
-        <v>7562.25</v>
+        <v>7607</v>
       </c>
       <c r="C43" t="n">
-        <v>7628.75</v>
+        <v>7632</v>
       </c>
       <c r="D43" t="n">
-        <v>7468.5</v>
+        <v>7473</v>
       </c>
       <c r="E43" t="n">
-        <v>7620.25</v>
+        <v>7497.75</v>
       </c>
       <c r="F43" t="n">
-        <v>63.25</v>
+        <v>-122.5</v>
       </c>
       <c r="G43" s="5" t="n">
-        <v>0.008399999999999999</v>
+        <v>-0.0161</v>
       </c>
       <c r="H43" t="n">
-        <v>160.25</v>
+        <v>159</v>
       </c>
       <c r="I43" t="n">
-        <v>7202.25</v>
+        <v>7308.25</v>
       </c>
       <c r="J43" t="n">
-        <v>7391.81</v>
+        <v>7495.81</v>
       </c>
       <c r="K43" t="n">
-        <v>7459.12</v>
+        <v>7540.12</v>
       </c>
       <c r="L43" t="n">
-        <v>7526.44</v>
+        <v>7584.44</v>
       </c>
       <c r="M43" t="n">
-        <v>7654.88</v>
+        <v>7700.38</v>
       </c>
       <c r="N43" t="n">
-        <v>7783.31</v>
+        <v>7816.31</v>
       </c>
       <c r="O43" t="n">
-        <v>7789.5</v>
+        <v>7789</v>
       </c>
       <c r="P43" s="6" t="n">
         <v/>
       </c>
-      <c r="Q43" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R43" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S43" s="7" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T43" s="8" t="inlineStr">
+      <c r="Q43" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
+      <c r="R43" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S43" s="10" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T43" s="8" t="n">
+        <v/>
+      </c>
       <c r="U43" s="8" t="n">
         <v/>
       </c>
@@ -4147,71 +4145,69 @@
       </c>
       <c r="X43" t="inlineStr">
         <is>
-          <t>強警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="B44" t="n">
-        <v>7607</v>
+        <v>7485</v>
       </c>
       <c r="C44" t="n">
-        <v>7632</v>
+        <v>7563.5</v>
       </c>
       <c r="D44" t="n">
-        <v>7473</v>
+        <v>7411.75</v>
       </c>
       <c r="E44" t="n">
-        <v>7497.75</v>
+        <v>7447.5</v>
       </c>
       <c r="F44" t="n">
-        <v>-122.5</v>
+        <v>-50.25</v>
       </c>
       <c r="G44" s="5" t="n">
-        <v>-0.0161</v>
+        <v>-0.0067</v>
       </c>
       <c r="H44" t="n">
-        <v>159</v>
+        <v>151.75</v>
       </c>
       <c r="I44" t="n">
-        <v>7308.25</v>
+        <v>7314</v>
       </c>
       <c r="J44" t="n">
-        <v>7495.81</v>
+        <v>7311.38</v>
       </c>
       <c r="K44" t="n">
-        <v>7540.12</v>
+        <v>7418.25</v>
       </c>
       <c r="L44" t="n">
-        <v>7584.44</v>
+        <v>7525.12</v>
       </c>
       <c r="M44" t="n">
-        <v>7700.38</v>
+        <v>7577.25</v>
       </c>
       <c r="N44" t="n">
-        <v>7816.31</v>
+        <v>7629.38</v>
       </c>
       <c r="O44" t="n">
-        <v>7789</v>
+        <v>7791</v>
       </c>
       <c r="P44" s="6" t="n">
         <v/>
       </c>
-      <c r="Q44" s="6" t="inlineStr">
+      <c r="Q44" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R44" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="R44" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
       <c r="S44" s="10" t="inlineStr">
         <is>
           <t>↓</t>
@@ -4231,59 +4227,55 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X44" t="inlineStr">
-        <is>
-          <t>中警訊</t>
-        </is>
-      </c>
+      <c r="X44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="B45" t="n">
-        <v>7485</v>
+        <v>7490</v>
       </c>
       <c r="C45" t="n">
-        <v>7563.5</v>
+        <v>7541</v>
       </c>
       <c r="D45" t="n">
-        <v>7411.75</v>
+        <v>7324</v>
       </c>
       <c r="E45" t="n">
-        <v>7447.5</v>
+        <v>7519.25</v>
       </c>
       <c r="F45" t="n">
-        <v>-50.25</v>
+        <v>71.75</v>
       </c>
       <c r="G45" s="5" t="n">
-        <v>-0.0067</v>
+        <v>0.009599999999999999</v>
       </c>
       <c r="H45" t="n">
-        <v>151.75</v>
+        <v>217</v>
       </c>
       <c r="I45" t="n">
-        <v>7314</v>
+        <v>7260</v>
       </c>
       <c r="J45" t="n">
-        <v>7311.38</v>
+        <v>7275.69</v>
       </c>
       <c r="K45" t="n">
-        <v>7418.25</v>
+        <v>7371.62</v>
       </c>
       <c r="L45" t="n">
-        <v>7525.12</v>
+        <v>7467.56</v>
       </c>
       <c r="M45" t="n">
-        <v>7577.25</v>
+        <v>7523.38</v>
       </c>
       <c r="N45" t="n">
-        <v>7629.38</v>
+        <v>7579.19</v>
       </c>
       <c r="O45" t="n">
-        <v>7791</v>
+        <v>7715.25</v>
       </c>
       <c r="P45" s="6" t="n">
         <v/>
@@ -4293,17 +4285,19 @@
       </c>
       <c r="R45" s="6" t="inlineStr">
         <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S45" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T45" s="8" t="inlineStr">
+        <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="S45" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T45" s="8" t="n">
-        <v/>
-      </c>
       <c r="U45" s="8" t="n">
         <v/>
       </c>
@@ -4315,55 +4309,59 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X45" t="inlineStr"/>
+      <c r="X45" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="B46" t="n">
-        <v>7490</v>
+        <v>7550</v>
       </c>
       <c r="C46" t="n">
-        <v>7541</v>
+        <v>7820.25</v>
       </c>
       <c r="D46" t="n">
-        <v>7324</v>
+        <v>7542.75</v>
       </c>
       <c r="E46" t="n">
-        <v>7519.25</v>
+        <v>7779.75</v>
       </c>
       <c r="F46" t="n">
-        <v>71.75</v>
+        <v>260.5</v>
       </c>
       <c r="G46" s="5" t="n">
-        <v>0.009599999999999999</v>
+        <v>0.0346</v>
       </c>
       <c r="H46" t="n">
-        <v>217</v>
+        <v>277.5</v>
       </c>
       <c r="I46" t="n">
-        <v>7260</v>
+        <v>7107</v>
       </c>
       <c r="J46" t="n">
-        <v>7275.69</v>
+        <v>7345.62</v>
       </c>
       <c r="K46" t="n">
-        <v>7371.62</v>
+        <v>7410.75</v>
       </c>
       <c r="L46" t="n">
-        <v>7467.56</v>
+        <v>7475.88</v>
       </c>
       <c r="M46" t="n">
-        <v>7523.38</v>
+        <v>7627.75</v>
       </c>
       <c r="N46" t="n">
-        <v>7579.19</v>
+        <v>7779.62</v>
       </c>
       <c r="O46" t="n">
-        <v>7715.25</v>
+        <v>7758</v>
       </c>
       <c r="P46" s="6" t="n">
         <v/>
@@ -4371,85 +4369,83 @@
       <c r="Q46" s="6" t="n">
         <v/>
       </c>
-      <c r="R46" s="6" t="inlineStr">
+      <c r="R46" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S46" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T46" s="8" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="S46" s="7" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T46" s="8" t="inlineStr">
+      <c r="U46" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="U46" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V46" s="8" t="n">
-        <v/>
-      </c>
-      <c r="W46" s="11" t="inlineStr">
-        <is>
-          <t>空方</t>
-        </is>
-      </c>
-      <c r="X46" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="V46" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="W46" s="9" t="inlineStr">
+        <is>
+          <t>多方</t>
+        </is>
+      </c>
+      <c r="X46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="B47" t="n">
-        <v>7550</v>
+        <v>7776.75</v>
       </c>
       <c r="C47" t="n">
-        <v>7820.25</v>
+        <v>7838.5</v>
       </c>
       <c r="D47" t="n">
-        <v>7542.75</v>
+        <v>7738</v>
       </c>
       <c r="E47" t="n">
-        <v>7779.75</v>
+        <v>7805</v>
       </c>
       <c r="F47" t="n">
-        <v>260.5</v>
+        <v>25.25</v>
       </c>
       <c r="G47" s="5" t="n">
-        <v>0.0346</v>
+        <v>0.0032</v>
       </c>
       <c r="H47" t="n">
-        <v>277.5</v>
+        <v>100.5</v>
       </c>
       <c r="I47" t="n">
-        <v>7107</v>
+        <v>7265.25</v>
       </c>
       <c r="J47" t="n">
-        <v>7345.62</v>
+        <v>7551.38</v>
       </c>
       <c r="K47" t="n">
-        <v>7410.75</v>
+        <v>7641</v>
       </c>
       <c r="L47" t="n">
-        <v>7475.88</v>
+        <v>7730.62</v>
       </c>
       <c r="M47" t="n">
-        <v>7627.75</v>
+        <v>7918.5</v>
       </c>
       <c r="N47" t="n">
-        <v>7779.62</v>
+        <v>8106.38</v>
       </c>
       <c r="O47" t="n">
-        <v>7758</v>
+        <v>8097.75</v>
       </c>
       <c r="P47" s="6" t="n">
         <v/>
@@ -4462,23 +4458,17 @@
       </c>
       <c r="S47" s="7" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T47" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U47" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="V47" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T47" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U47" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V47" s="8" t="n">
+        <v/>
       </c>
       <c r="W47" s="9" t="inlineStr">
         <is>
@@ -4490,63 +4480,67 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="B48" t="n">
-        <v>7776.75</v>
+        <v>7809.25</v>
       </c>
       <c r="C48" t="n">
-        <v>7838.5</v>
+        <v>7824.5</v>
       </c>
       <c r="D48" t="n">
-        <v>7738</v>
+        <v>7657.75</v>
       </c>
       <c r="E48" t="n">
-        <v>7805</v>
+        <v>7691.25</v>
       </c>
       <c r="F48" t="n">
-        <v>25.25</v>
+        <v>-113.75</v>
       </c>
       <c r="G48" s="5" t="n">
-        <v>0.0032</v>
+        <v>-0.0146</v>
       </c>
       <c r="H48" t="n">
-        <v>100.5</v>
+        <v>166.75</v>
       </c>
       <c r="I48" t="n">
-        <v>7265.25</v>
+        <v>7637.5</v>
       </c>
       <c r="J48" t="n">
-        <v>7551.38</v>
+        <v>7712.88</v>
       </c>
       <c r="K48" t="n">
-        <v>7641</v>
+        <v>7754.75</v>
       </c>
       <c r="L48" t="n">
-        <v>7730.62</v>
+        <v>7796.62</v>
       </c>
       <c r="M48" t="n">
-        <v>7918.5</v>
+        <v>7855.25</v>
       </c>
       <c r="N48" t="n">
-        <v>8106.38</v>
+        <v>7913.88</v>
       </c>
       <c r="O48" t="n">
-        <v>8097.75</v>
+        <v>7939</v>
       </c>
       <c r="P48" s="6" t="n">
         <v/>
       </c>
-      <c r="Q48" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R48" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S48" s="7" t="inlineStr">
-        <is>
-          <t>↑C</t>
+      <c r="Q48" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="R48" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S48" s="10" t="inlineStr">
+        <is>
+          <t>↓</t>
         </is>
       </c>
       <c r="T48" s="8" t="n">
@@ -4558,9 +4552,9 @@
       <c r="V48" s="8" t="n">
         <v/>
       </c>
-      <c r="W48" s="9" t="inlineStr">
-        <is>
-          <t>多方</t>
+      <c r="W48" s="11" t="inlineStr">
+        <is>
+          <t>空方</t>
         </is>
       </c>
       <c r="X48" t="inlineStr"/>
@@ -4568,72 +4562,70 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="B49" t="n">
-        <v>7809.25</v>
+        <v>7693.5</v>
       </c>
       <c r="C49" t="n">
-        <v>7824.5</v>
+        <v>7782.5</v>
       </c>
       <c r="D49" t="n">
-        <v>7657.75</v>
+        <v>7655</v>
       </c>
       <c r="E49" t="n">
-        <v>7691.25</v>
+        <v>7722</v>
       </c>
       <c r="F49" t="n">
-        <v>-113.75</v>
+        <v>30.75</v>
       </c>
       <c r="G49" s="5" t="n">
-        <v>-0.0146</v>
+        <v>0.004</v>
       </c>
       <c r="H49" t="n">
-        <v>166.75</v>
+        <v>127.5</v>
       </c>
       <c r="I49" t="n">
-        <v>7637.5</v>
+        <v>7491</v>
       </c>
       <c r="J49" t="n">
-        <v>7712.88</v>
+        <v>7499.56</v>
       </c>
       <c r="K49" t="n">
-        <v>7754.75</v>
+        <v>7607.88</v>
       </c>
       <c r="L49" t="n">
-        <v>7796.62</v>
+        <v>7716.19</v>
       </c>
       <c r="M49" t="n">
-        <v>7855.25</v>
+        <v>7774.62</v>
       </c>
       <c r="N49" t="n">
-        <v>7913.88</v>
+        <v>7833.06</v>
       </c>
       <c r="O49" t="n">
-        <v>7939</v>
+        <v>7991.25</v>
       </c>
       <c r="P49" s="6" t="n">
         <v/>
       </c>
-      <c r="Q49" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="R49" s="6" t="inlineStr">
+      <c r="Q49" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R49" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S49" s="7" t="inlineStr">
+        <is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T49" s="8" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="S49" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T49" s="8" t="n">
-        <v/>
-      </c>
       <c r="U49" s="8" t="n">
         <v/>
       </c>
@@ -4645,55 +4637,59 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X49" t="inlineStr"/>
+      <c r="X49" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="B50" t="n">
-        <v>7693.5</v>
+        <v>7723.5</v>
       </c>
       <c r="C50" t="n">
-        <v>7782.5</v>
+        <v>7766.5</v>
       </c>
       <c r="D50" t="n">
-        <v>7655</v>
+        <v>7618.5</v>
       </c>
       <c r="E50" t="n">
         <v>7722</v>
       </c>
       <c r="F50" t="n">
-        <v>30.75</v>
+        <v>0</v>
       </c>
       <c r="G50" s="5" t="n">
-        <v>0.004</v>
+        <v>0</v>
       </c>
       <c r="H50" t="n">
-        <v>127.5</v>
+        <v>148</v>
       </c>
       <c r="I50" t="n">
-        <v>7491</v>
+        <v>7527.5</v>
       </c>
       <c r="J50" t="n">
-        <v>7499.56</v>
+        <v>7596.12</v>
       </c>
       <c r="K50" t="n">
-        <v>7607.88</v>
+        <v>7658.25</v>
       </c>
       <c r="L50" t="n">
-        <v>7716.19</v>
+        <v>7720.38</v>
       </c>
       <c r="M50" t="n">
-        <v>7774.62</v>
+        <v>7785.75</v>
       </c>
       <c r="N50" t="n">
-        <v>7833.06</v>
+        <v>7851.12</v>
       </c>
       <c r="O50" t="n">
-        <v>7991.25</v>
+        <v>7910</v>
       </c>
       <c r="P50" s="6" t="n">
         <v/>
@@ -4701,18 +4697,18 @@
       <c r="Q50" s="6" t="n">
         <v/>
       </c>
-      <c r="R50" s="6" t="n">
-        <v/>
+      <c r="R50" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S50" s="7" t="inlineStr">
         <is>
           <t>↑C</t>
         </is>
       </c>
-      <c r="T50" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="T50" s="8" t="n">
+        <v/>
       </c>
       <c r="U50" s="8" t="n">
         <v/>
@@ -4725,74 +4721,72 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X50" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="X50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="B51" t="n">
-        <v>7723.5</v>
+        <v>7715.5</v>
       </c>
       <c r="C51" t="n">
-        <v>7766.5</v>
+        <v>7728.5</v>
       </c>
       <c r="D51" t="n">
-        <v>7618.5</v>
+        <v>7585.5</v>
       </c>
       <c r="E51" t="n">
-        <v>7722</v>
+        <v>7659.5</v>
       </c>
       <c r="F51" t="n">
-        <v>0</v>
+        <v>-62.5</v>
       </c>
       <c r="G51" s="5" t="n">
-        <v>0</v>
+        <v>-0.0081</v>
       </c>
       <c r="H51" t="n">
-        <v>148</v>
+        <v>143</v>
       </c>
       <c r="I51" t="n">
-        <v>7527.5</v>
+        <v>7470.5</v>
       </c>
       <c r="J51" t="n">
-        <v>7596.12</v>
+        <v>7588.75</v>
       </c>
       <c r="K51" t="n">
-        <v>7658.25</v>
+        <v>7648</v>
       </c>
       <c r="L51" t="n">
-        <v>7720.38</v>
+        <v>7707.25</v>
       </c>
       <c r="M51" t="n">
-        <v>7785.75</v>
+        <v>7796</v>
       </c>
       <c r="N51" t="n">
-        <v>7851.12</v>
+        <v>7884.75</v>
       </c>
       <c r="O51" t="n">
-        <v>7910</v>
+        <v>7914.5</v>
       </c>
       <c r="P51" s="6" t="n">
         <v/>
       </c>
-      <c r="Q51" s="6" t="n">
-        <v/>
+      <c r="Q51" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="R51" s="6" t="inlineStr">
         <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S51" s="7" t="inlineStr">
-        <is>
-          <t>↑C</t>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="S51" s="10" t="inlineStr">
+        <is>
+          <t>↓</t>
         </is>
       </c>
       <c r="T51" s="8" t="n">
@@ -4814,50 +4808,50 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="B52" t="n">
-        <v>7715.5</v>
+        <v>7609.25</v>
       </c>
       <c r="C52" t="n">
-        <v>7728.5</v>
+        <v>7670.25</v>
       </c>
       <c r="D52" t="n">
-        <v>7585.5</v>
+        <v>7509.25</v>
       </c>
       <c r="E52" t="n">
-        <v>7659.5</v>
+        <v>7657.35</v>
       </c>
       <c r="F52" t="n">
-        <v>-62.5</v>
+        <v>-2.15</v>
       </c>
       <c r="G52" s="5" t="n">
-        <v>-0.0081</v>
+        <v>-0.0003</v>
       </c>
       <c r="H52" t="n">
-        <v>143</v>
+        <v>161</v>
       </c>
       <c r="I52" t="n">
-        <v>7470.5</v>
+        <v>7442.5</v>
       </c>
       <c r="J52" t="n">
-        <v>7588.75</v>
+        <v>7517.75</v>
       </c>
       <c r="K52" t="n">
-        <v>7648</v>
+        <v>7588</v>
       </c>
       <c r="L52" t="n">
-        <v>7707.25</v>
+        <v>7658.25</v>
       </c>
       <c r="M52" t="n">
-        <v>7796</v>
+        <v>7731</v>
       </c>
       <c r="N52" t="n">
-        <v>7884.75</v>
+        <v>7803.75</v>
       </c>
       <c r="O52" t="n">
-        <v>7914.5</v>
+        <v>7871.5</v>
       </c>
       <c r="P52" s="6" t="n">
         <v/>
@@ -4869,12 +4863,12 @@
       </c>
       <c r="R52" s="6" t="inlineStr">
         <is>
-          <t>△C</t>
+          <t>✓</t>
         </is>
       </c>
       <c r="S52" s="10" t="inlineStr">
         <is>
-          <t>↓</t>
+          <t>↓C</t>
         </is>
       </c>
       <c r="T52" s="8" t="n">
@@ -4896,239 +4890,237 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="B53" t="n">
-        <v>7609.25</v>
+        <v>7722</v>
       </c>
       <c r="C53" t="n">
-        <v>7670.25</v>
+        <v>7848.5</v>
       </c>
       <c r="D53" t="n">
-        <v>7509.25</v>
+        <v>7707.25</v>
       </c>
       <c r="E53" t="n">
-        <v>7657.35</v>
+        <v>7803.75</v>
       </c>
       <c r="F53" t="n">
-        <v>-2.15</v>
+        <v>146.4</v>
       </c>
       <c r="G53" s="5" t="n">
-        <v>-0.0003</v>
+        <v>0.0191</v>
       </c>
       <c r="H53" t="n">
-        <v>161</v>
+        <v>141.25</v>
       </c>
       <c r="I53" t="n">
-        <v>7442.5</v>
+        <v>7348.25</v>
       </c>
       <c r="J53" t="n">
-        <v>7517.75</v>
+        <v>7530.15</v>
       </c>
       <c r="K53" t="n">
-        <v>7588</v>
+        <v>7576.85</v>
       </c>
       <c r="L53" t="n">
-        <v>7658.25</v>
+        <v>7623.55</v>
       </c>
       <c r="M53" t="n">
-        <v>7731</v>
+        <v>7737.85</v>
       </c>
       <c r="N53" t="n">
-        <v>7803.75</v>
+        <v>7852.15</v>
       </c>
       <c r="O53" t="n">
-        <v>7871.5</v>
+        <v>7831.25</v>
       </c>
       <c r="P53" s="6" t="n">
         <v/>
       </c>
-      <c r="Q53" s="6" t="inlineStr">
+      <c r="Q53" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R53" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S53" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T53" s="8" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="R53" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S53" s="10" t="inlineStr">
-        <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T53" s="8" t="n">
-        <v/>
-      </c>
       <c r="U53" s="8" t="n">
         <v/>
       </c>
-      <c r="V53" s="8" t="n">
-        <v/>
+      <c r="V53" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="W53" s="11" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
       </c>
-      <c r="X53" t="inlineStr"/>
+      <c r="X53" t="inlineStr">
+        <is>
+          <t>強警訊</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="B54" t="n">
-        <v>7722</v>
+        <v>7796</v>
       </c>
       <c r="C54" t="n">
-        <v>7848.5</v>
+        <v>7810.25</v>
       </c>
       <c r="D54" t="n">
-        <v>7707.25</v>
+        <v>7672.75</v>
       </c>
       <c r="E54" t="n">
-        <v>7803.75</v>
+        <v>7777.25</v>
       </c>
       <c r="F54" t="n">
-        <v>146.4</v>
+        <v>-26.5</v>
       </c>
       <c r="G54" s="5" t="n">
-        <v>0.0191</v>
+        <v>-0.0034</v>
       </c>
       <c r="H54" t="n">
-        <v>141.25</v>
+        <v>137.5</v>
       </c>
       <c r="I54" t="n">
-        <v>7348.25</v>
+        <v>7566</v>
       </c>
       <c r="J54" t="n">
-        <v>7530.15</v>
+        <v>7675.44</v>
       </c>
       <c r="K54" t="n">
-        <v>7576.85</v>
+        <v>7733.12</v>
       </c>
       <c r="L54" t="n">
-        <v>7623.55</v>
+        <v>7790.81</v>
       </c>
       <c r="M54" t="n">
-        <v>7737.85</v>
+        <v>7874.38</v>
       </c>
       <c r="N54" t="n">
-        <v>7852.15</v>
+        <v>7957.94</v>
       </c>
       <c r="O54" t="n">
-        <v>7831.25</v>
+        <v>7989.75</v>
       </c>
       <c r="P54" s="6" t="n">
         <v/>
       </c>
-      <c r="Q54" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R54" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S54" s="7" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T54" s="8" t="inlineStr">
+      <c r="Q54" s="6" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
+      <c r="R54" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S54" s="10" t="inlineStr">
+        <is>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T54" s="8" t="n">
+        <v/>
+      </c>
       <c r="U54" s="8" t="n">
         <v/>
       </c>
-      <c r="V54" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+      <c r="V54" s="8" t="n">
+        <v/>
       </c>
       <c r="W54" s="11" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
       </c>
-      <c r="X54" t="inlineStr">
-        <is>
-          <t>強警訊</t>
-        </is>
-      </c>
+      <c r="X54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="B55" t="n">
-        <v>7796</v>
+        <v>7781.5</v>
       </c>
       <c r="C55" t="n">
-        <v>7810.25</v>
+        <v>7897.5</v>
       </c>
       <c r="D55" t="n">
-        <v>7672.75</v>
+        <v>7760.25</v>
       </c>
       <c r="E55" t="n">
-        <v>7777.25</v>
+        <v>7859.75</v>
       </c>
       <c r="F55" t="n">
-        <v>-26.5</v>
+        <v>82.5</v>
       </c>
       <c r="G55" s="5" t="n">
-        <v>-0.0034</v>
+        <v>0.0106</v>
       </c>
       <c r="H55" t="n">
-        <v>137.5</v>
+        <v>137.25</v>
       </c>
       <c r="I55" t="n">
-        <v>7566</v>
+        <v>7535.25</v>
       </c>
       <c r="J55" t="n">
-        <v>7675.44</v>
+        <v>7657.62</v>
       </c>
       <c r="K55" t="n">
-        <v>7733.12</v>
+        <v>7708.5</v>
       </c>
       <c r="L55" t="n">
-        <v>7790.81</v>
+        <v>7759.38</v>
       </c>
       <c r="M55" t="n">
-        <v>7874.38</v>
+        <v>7846</v>
       </c>
       <c r="N55" t="n">
-        <v>7957.94</v>
+        <v>7932.62</v>
       </c>
       <c r="O55" t="n">
-        <v>7989.75</v>
+        <v>7947.75</v>
       </c>
       <c r="P55" s="6" t="n">
         <v/>
       </c>
-      <c r="Q55" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="R55" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S55" s="10" t="inlineStr">
-        <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T55" s="8" t="n">
-        <v/>
+      <c r="Q55" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R55" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S55" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T55" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="U55" s="8" t="n">
         <v/>
@@ -5141,75 +5133,81 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X55" t="inlineStr"/>
+      <c r="X55" t="inlineStr">
+        <is>
+          <t>強警訊</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="B56" t="n">
-        <v>7781.5</v>
+        <v>7873</v>
       </c>
       <c r="C56" t="n">
-        <v>7897.5</v>
+        <v>7887</v>
       </c>
       <c r="D56" t="n">
-        <v>7760.25</v>
+        <v>7676</v>
       </c>
       <c r="E56" t="n">
-        <v>7859.75</v>
+        <v>7704.25</v>
       </c>
       <c r="F56" t="n">
-        <v>82.5</v>
+        <v>-155.5</v>
       </c>
       <c r="G56" s="5" t="n">
-        <v>0.0106</v>
+        <v>-0.0198</v>
       </c>
       <c r="H56" t="n">
-        <v>137.25</v>
+        <v>211</v>
       </c>
       <c r="I56" t="n">
-        <v>7535.25</v>
+        <v>7623</v>
       </c>
       <c r="J56" t="n">
-        <v>7657.62</v>
+        <v>7737.94</v>
       </c>
       <c r="K56" t="n">
-        <v>7708.5</v>
+        <v>7791.12</v>
       </c>
       <c r="L56" t="n">
-        <v>7759.38</v>
+        <v>7844.31</v>
       </c>
       <c r="M56" t="n">
-        <v>7846</v>
+        <v>7928.38</v>
       </c>
       <c r="N56" t="n">
-        <v>7932.62</v>
+        <v>8012.44</v>
       </c>
       <c r="O56" t="n">
-        <v>7947.75</v>
+        <v>8034.75</v>
       </c>
       <c r="P56" s="6" t="n">
         <v/>
       </c>
-      <c r="Q56" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R56" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S56" s="7" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T56" s="8" t="inlineStr">
+      <c r="Q56" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
+      <c r="R56" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S56" s="10" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T56" s="8" t="n">
+        <v/>
+      </c>
       <c r="U56" s="8" t="n">
         <v/>
       </c>
@@ -5221,81 +5219,75 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X56" t="inlineStr">
-        <is>
-          <t>強警訊</t>
-        </is>
-      </c>
+      <c r="X56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="B57" t="n">
-        <v>7873</v>
+        <v>7679.5</v>
       </c>
       <c r="C57" t="n">
-        <v>7887</v>
+        <v>7812.25</v>
       </c>
       <c r="D57" t="n">
-        <v>7676</v>
+        <v>7648.5</v>
       </c>
       <c r="E57" t="n">
-        <v>7704.25</v>
+        <v>7672.5</v>
       </c>
       <c r="F57" t="n">
-        <v>-155.5</v>
+        <v>-31.75</v>
       </c>
       <c r="G57" s="5" t="n">
-        <v>-0.0198</v>
+        <v>-0.0041</v>
       </c>
       <c r="H57" t="n">
-        <v>211</v>
+        <v>163.75</v>
       </c>
       <c r="I57" t="n">
-        <v>7623</v>
+        <v>7465</v>
       </c>
       <c r="J57" t="n">
-        <v>7737.94</v>
+        <v>7454.62</v>
       </c>
       <c r="K57" t="n">
-        <v>7791.12</v>
+        <v>7598.75</v>
       </c>
       <c r="L57" t="n">
-        <v>7844.31</v>
+        <v>7742.88</v>
       </c>
       <c r="M57" t="n">
-        <v>7928.38</v>
+        <v>7809.75</v>
       </c>
       <c r="N57" t="n">
-        <v>8012.44</v>
+        <v>7876.62</v>
       </c>
       <c r="O57" t="n">
-        <v>8034.75</v>
+        <v>8098</v>
       </c>
       <c r="P57" s="6" t="n">
         <v/>
       </c>
-      <c r="Q57" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="R57" s="6" t="inlineStr">
+      <c r="Q57" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R57" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S57" s="10" t="inlineStr">
+        <is>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T57" s="8" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="S57" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T57" s="8" t="n">
-        <v/>
-      </c>
       <c r="U57" s="8" t="n">
         <v/>
       </c>
@@ -5308,90 +5300,6 @@
         </is>
       </c>
       <c r="X57" t="inlineStr"/>
-    </row>
-    <row r="58">
-      <c r="A58" t="inlineStr">
-        <is>
-          <t>2026-10-19</t>
-        </is>
-      </c>
-      <c r="B58" t="n">
-        <v>7679.5</v>
-      </c>
-      <c r="C58" t="n">
-        <v>7812.25</v>
-      </c>
-      <c r="D58" t="n">
-        <v>7677</v>
-      </c>
-      <c r="E58" t="n">
-        <v>7699.5</v>
-      </c>
-      <c r="F58" t="n">
-        <v>-4.75</v>
-      </c>
-      <c r="G58" s="5" t="n">
-        <v>-0.0005999999999999999</v>
-      </c>
-      <c r="H58" t="n">
-        <v>135.25</v>
-      </c>
-      <c r="I58" t="n">
-        <v>7465</v>
-      </c>
-      <c r="J58" t="n">
-        <v>7454.62</v>
-      </c>
-      <c r="K58" t="n">
-        <v>7598.75</v>
-      </c>
-      <c r="L58" t="n">
-        <v>7742.88</v>
-      </c>
-      <c r="M58" t="n">
-        <v>7809.75</v>
-      </c>
-      <c r="N58" t="n">
-        <v>7876.62</v>
-      </c>
-      <c r="O58" t="n">
-        <v>8098</v>
-      </c>
-      <c r="P58" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q58" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R58" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S58" s="10" t="inlineStr">
-        <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T58" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U58" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V58" s="8" t="n">
-        <v/>
-      </c>
-      <c r="W58" s="11" t="inlineStr">
-        <is>
-          <t>空方</t>
-        </is>
-      </c>
-      <c r="X58" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/three_gate/analysis/ES_weekly.xlsx
+++ b/three_gate/analysis/ES_weekly.xlsx
@@ -5237,13 +5237,13 @@
         <v>7648.5</v>
       </c>
       <c r="E57" t="n">
-        <v>7672.5</v>
+        <v>7663</v>
       </c>
       <c r="F57" t="n">
-        <v>-31.75</v>
+        <v>-41.25</v>
       </c>
       <c r="G57" s="5" t="n">
-        <v>-0.0041</v>
+        <v>-0.0054</v>
       </c>
       <c r="H57" t="n">
         <v>163.75</v>
@@ -5275,12 +5275,14 @@
       <c r="Q57" s="6" t="n">
         <v/>
       </c>
-      <c r="R57" s="6" t="n">
-        <v/>
+      <c r="R57" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="S57" s="10" t="inlineStr">
         <is>
-          <t>↓C</t>
+          <t>↓</t>
         </is>
       </c>
       <c r="T57" s="8" t="inlineStr">

--- a/three_gate/analysis/ES_weekly.xlsx
+++ b/three_gate/analysis/ES_weekly.xlsx
@@ -86,7 +86,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -115,6 +115,9 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -480,7 +483,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X57"/>
+  <dimension ref="A1:X58"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -659,25 +662,25 @@
         <v>120</v>
       </c>
       <c r="I2" t="n">
-        <v>6491.75</v>
+        <v>6492</v>
       </c>
       <c r="J2" t="n">
-        <v>6567</v>
+        <v>6567.31</v>
       </c>
       <c r="K2" t="n">
-        <v>6630.25</v>
+        <v>6630.38</v>
       </c>
       <c r="L2" t="n">
-        <v>6693.5</v>
+        <v>6693.44</v>
       </c>
       <c r="M2" t="n">
-        <v>6762.75</v>
+        <v>6762.62</v>
       </c>
       <c r="N2" t="n">
-        <v>6832</v>
+        <v>6831.81</v>
       </c>
       <c r="O2" t="n">
-        <v>6889.25</v>
+        <v>6888.75</v>
       </c>
       <c r="P2" s="6" t="n">
         <v/>
@@ -5237,13 +5240,13 @@
         <v>7648.5</v>
       </c>
       <c r="E57" t="n">
-        <v>7663</v>
+        <v>7659.75</v>
       </c>
       <c r="F57" t="n">
-        <v>-41.25</v>
+        <v>-44.5</v>
       </c>
       <c r="G57" s="5" t="n">
-        <v>-0.0054</v>
+        <v>-0.0058</v>
       </c>
       <c r="H57" t="n">
         <v>163.75</v>
@@ -5302,6 +5305,90 @@
         </is>
       </c>
       <c r="X57" t="inlineStr"/>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>2026-10-26</t>
+        </is>
+      </c>
+      <c r="B58" t="n">
+        <v>7715</v>
+      </c>
+      <c r="C58" t="n">
+        <v>7731</v>
+      </c>
+      <c r="D58" t="n">
+        <v>7702.75</v>
+      </c>
+      <c r="E58" t="n">
+        <v/>
+      </c>
+      <c r="F58" t="n">
+        <v/>
+      </c>
+      <c r="G58" s="5" t="n">
+        <v/>
+      </c>
+      <c r="H58" t="n">
+        <v>28.25</v>
+      </c>
+      <c r="I58" t="n">
+        <v>7484.75</v>
+      </c>
+      <c r="J58" t="n">
+        <v>7460.69</v>
+      </c>
+      <c r="K58" t="n">
+        <v>7577.88</v>
+      </c>
+      <c r="L58" t="n">
+        <v>7695.06</v>
+      </c>
+      <c r="M58" t="n">
+        <v>7741.62</v>
+      </c>
+      <c r="N58" t="n">
+        <v>7788.19</v>
+      </c>
+      <c r="O58" t="n">
+        <v>7976</v>
+      </c>
+      <c r="P58" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="Q58" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R58" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S58" s="12" t="inlineStr">
+        <is>
+          <t>=</t>
+        </is>
+      </c>
+      <c r="T58" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U58" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V58" s="8" t="n">
+        <v/>
+      </c>
+      <c r="W58" s="11" t="inlineStr">
+        <is>
+          <t>空方</t>
+        </is>
+      </c>
+      <c r="X58" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/three_gate/analysis/ES_weekly.xlsx
+++ b/three_gate/analysis/ES_weekly.xlsx
@@ -86,7 +86,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="13">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -115,9 +115,6 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -662,25 +659,25 @@
         <v>120</v>
       </c>
       <c r="I2" t="n">
-        <v>6492</v>
+        <v>6519.75</v>
       </c>
       <c r="J2" t="n">
-        <v>6567.31</v>
+        <v>6602</v>
       </c>
       <c r="K2" t="n">
-        <v>6630.38</v>
+        <v>6644.25</v>
       </c>
       <c r="L2" t="n">
-        <v>6693.44</v>
+        <v>6686.5</v>
       </c>
       <c r="M2" t="n">
-        <v>6762.62</v>
+        <v>6748.75</v>
       </c>
       <c r="N2" t="n">
-        <v>6831.81</v>
+        <v>6811</v>
       </c>
       <c r="O2" t="n">
-        <v>6888.75</v>
+        <v>6833.25</v>
       </c>
       <c r="P2" s="6" t="n">
         <v/>
@@ -5313,25 +5310,25 @@
         </is>
       </c>
       <c r="B58" t="n">
-        <v>7715</v>
+        <v>7690</v>
       </c>
       <c r="C58" t="n">
-        <v>7731</v>
+        <v>7772.75</v>
       </c>
       <c r="D58" t="n">
-        <v>7702.75</v>
+        <v>7651.75</v>
       </c>
       <c r="E58" t="n">
-        <v/>
+        <v>7757.75</v>
       </c>
       <c r="F58" t="n">
-        <v/>
+        <v>98</v>
       </c>
       <c r="G58" s="5" t="n">
-        <v/>
+        <v>0.0128</v>
       </c>
       <c r="H58" t="n">
-        <v>28.25</v>
+        <v>121</v>
       </c>
       <c r="I58" t="n">
         <v>7484.75</v>
@@ -5354,25 +5351,25 @@
       <c r="O58" t="n">
         <v>7976</v>
       </c>
-      <c r="P58" s="6" t="inlineStr">
+      <c r="P58" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q58" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R58" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S58" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T58" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="Q58" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R58" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S58" s="12" t="inlineStr">
-        <is>
-          <t>=</t>
-        </is>
-      </c>
-      <c r="T58" s="8" t="n">
-        <v/>
-      </c>
       <c r="U58" s="8" t="n">
         <v/>
       </c>
@@ -5386,7 +5383,7 @@
       </c>
       <c r="X58" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>

--- a/three_gate/analysis/ES_weekly.xlsx
+++ b/three_gate/analysis/ES_weekly.xlsx
@@ -659,25 +659,25 @@
         <v>120</v>
       </c>
       <c r="I2" t="n">
-        <v>6519.75</v>
+        <v>6543.25</v>
       </c>
       <c r="J2" t="n">
-        <v>6602</v>
+        <v>6631.38</v>
       </c>
       <c r="K2" t="n">
-        <v>6644.25</v>
+        <v>6656</v>
       </c>
       <c r="L2" t="n">
-        <v>6686.5</v>
+        <v>6680.62</v>
       </c>
       <c r="M2" t="n">
-        <v>6748.75</v>
+        <v>6737</v>
       </c>
       <c r="N2" t="n">
-        <v>6811</v>
+        <v>6793.38</v>
       </c>
       <c r="O2" t="n">
-        <v>6833.25</v>
+        <v>6786.25</v>
       </c>
       <c r="P2" s="6" t="n">
         <v/>
@@ -695,14 +695,18 @@
       </c>
       <c r="T2" s="8" t="inlineStr">
         <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U2" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="V2" s="8" t="inlineStr">
+        <is>
           <t>△C</t>
         </is>
-      </c>
-      <c r="U2" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V2" s="8" t="n">
-        <v/>
       </c>
       <c r="W2" s="9" t="inlineStr">
         <is>
@@ -5313,22 +5317,22 @@
         <v>7690</v>
       </c>
       <c r="C58" t="n">
-        <v>7772.75</v>
+        <v>7819.5</v>
       </c>
       <c r="D58" t="n">
         <v>7651.75</v>
       </c>
       <c r="E58" t="n">
-        <v>7757.75</v>
+        <v>7748.25</v>
       </c>
       <c r="F58" t="n">
-        <v>98</v>
+        <v>88.5</v>
       </c>
       <c r="G58" s="5" t="n">
-        <v>0.0128</v>
+        <v>0.0116</v>
       </c>
       <c r="H58" t="n">
-        <v>121</v>
+        <v>167.75</v>
       </c>
       <c r="I58" t="n">
         <v>7484.75</v>
@@ -5370,8 +5374,10 @@
           <t>△C</t>
         </is>
       </c>
-      <c r="U58" s="8" t="n">
-        <v/>
+      <c r="U58" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="V58" s="8" t="n">
         <v/>
@@ -5383,7 +5389,7 @@
       </c>
       <c r="X58" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>

--- a/three_gate/analysis/ES_weekly.xlsx
+++ b/three_gate/analysis/ES_weekly.xlsx
@@ -659,25 +659,25 @@
         <v>120</v>
       </c>
       <c r="I2" t="n">
-        <v>6543.25</v>
+        <v>6602.75</v>
       </c>
       <c r="J2" t="n">
-        <v>6631.38</v>
+        <v>6655</v>
       </c>
       <c r="K2" t="n">
-        <v>6656</v>
+        <v>6671.25</v>
       </c>
       <c r="L2" t="n">
-        <v>6680.62</v>
+        <v>6687.5</v>
       </c>
       <c r="M2" t="n">
-        <v>6737</v>
+        <v>6721.75</v>
       </c>
       <c r="N2" t="n">
-        <v>6793.38</v>
+        <v>6756</v>
       </c>
       <c r="O2" t="n">
-        <v>6786.25</v>
+        <v>6754.25</v>
       </c>
       <c r="P2" s="6" t="n">
         <v/>
@@ -700,12 +700,12 @@
       </c>
       <c r="U2" s="8" t="inlineStr">
         <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="V2" s="8" t="inlineStr">
+        <is>
           <t>✓</t>
-        </is>
-      </c>
-      <c r="V2" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
         </is>
       </c>
       <c r="W2" s="9" t="inlineStr">
@@ -5323,13 +5323,13 @@
         <v>7651.75</v>
       </c>
       <c r="E58" t="n">
-        <v>7748.25</v>
+        <v>7672</v>
       </c>
       <c r="F58" t="n">
-        <v>88.5</v>
+        <v>12.25</v>
       </c>
       <c r="G58" s="5" t="n">
-        <v>0.0116</v>
+        <v>0.0016</v>
       </c>
       <c r="H58" t="n">
         <v>167.75</v>
@@ -5364,14 +5364,14 @@
       <c r="R58" s="6" t="n">
         <v/>
       </c>
-      <c r="S58" s="7" t="inlineStr">
-        <is>
-          <t>↑</t>
+      <c r="S58" s="10" t="inlineStr">
+        <is>
+          <t>↓C</t>
         </is>
       </c>
       <c r="T58" s="8" t="inlineStr">
         <is>
-          <t>△C</t>
+          <t>✓</t>
         </is>
       </c>
       <c r="U58" s="8" t="inlineStr">

--- a/three_gate/analysis/ES_weekly.xlsx
+++ b/three_gate/analysis/ES_weekly.xlsx
@@ -104,17 +104,17 @@
     <xf numFmtId="0" fontId="2" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -480,7 +480,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X58"/>
+  <dimension ref="A1:X57"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -634,222 +634,222 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2025-09-29</t>
+          <t>2025-10-06</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>6697</v>
+        <v>6768</v>
       </c>
       <c r="C2" t="n">
-        <v>6800</v>
+        <v>6812.25</v>
       </c>
       <c r="D2" t="n">
-        <v>6680</v>
+        <v>6540.25</v>
       </c>
       <c r="E2" t="n">
-        <v>6764</v>
+        <v>6595.25</v>
       </c>
       <c r="F2" t="n">
-        <v>67.5</v>
+        <v>-168.75</v>
       </c>
       <c r="G2" s="5" t="n">
-        <v>0.0101</v>
+        <v>-0.0249</v>
       </c>
       <c r="H2" t="n">
-        <v>120</v>
+        <v>272</v>
       </c>
       <c r="I2" t="n">
-        <v>6602.75</v>
+        <v>6560</v>
       </c>
       <c r="J2" t="n">
-        <v>6655</v>
+        <v>6656</v>
       </c>
       <c r="K2" t="n">
-        <v>6671.25</v>
+        <v>6704</v>
       </c>
       <c r="L2" t="n">
-        <v>6687.5</v>
+        <v>6752</v>
       </c>
       <c r="M2" t="n">
-        <v>6721.75</v>
+        <v>6824</v>
       </c>
       <c r="N2" t="n">
-        <v>6756</v>
+        <v>6896</v>
       </c>
       <c r="O2" t="n">
-        <v>6754.25</v>
-      </c>
-      <c r="P2" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q2" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R2" s="6" t="n">
-        <v/>
+        <v>6920</v>
+      </c>
+      <c r="P2" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="Q2" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="R2" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S2" s="7" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T2" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U2" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="V2" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T2" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U2" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V2" s="8" t="n">
+        <v/>
       </c>
       <c r="W2" s="9" t="inlineStr">
         <is>
-          <t>多方</t>
-        </is>
-      </c>
-      <c r="X2" t="inlineStr"/>
+          <t>空方</t>
+        </is>
+      </c>
+      <c r="X2" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2025-10-06</t>
+          <t>2025-10-13</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>6768</v>
+        <v>6632</v>
       </c>
       <c r="C3" t="n">
-        <v>6812.25</v>
+        <v>6766.75</v>
       </c>
       <c r="D3" t="n">
-        <v>6540.25</v>
+        <v>6571.25</v>
       </c>
       <c r="E3" t="n">
-        <v>6595.25</v>
+        <v>6702.5</v>
       </c>
       <c r="F3" t="n">
-        <v>-168.75</v>
+        <v>107.25</v>
       </c>
       <c r="G3" s="5" t="n">
-        <v>-0.0249</v>
+        <v>0.0163</v>
       </c>
       <c r="H3" t="n">
-        <v>272</v>
+        <v>195.5</v>
       </c>
       <c r="I3" t="n">
-        <v>6560</v>
+        <v>6268.25</v>
       </c>
       <c r="J3" t="n">
-        <v>6656</v>
+        <v>6282.75</v>
       </c>
       <c r="K3" t="n">
-        <v>6704</v>
+        <v>6459.25</v>
       </c>
       <c r="L3" t="n">
-        <v>6752</v>
+        <v>6635.75</v>
       </c>
       <c r="M3" t="n">
-        <v>6824</v>
+        <v>6731.25</v>
       </c>
       <c r="N3" t="n">
-        <v>6896</v>
+        <v>6826.75</v>
       </c>
       <c r="O3" t="n">
-        <v>6920</v>
-      </c>
-      <c r="P3" s="6" t="inlineStr">
+        <v>7084.25</v>
+      </c>
+      <c r="P3" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q3" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R3" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S3" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T3" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="Q3" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="R3" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S3" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T3" s="8" t="n">
-        <v/>
-      </c>
       <c r="U3" s="8" t="n">
         <v/>
       </c>
       <c r="V3" s="8" t="n">
         <v/>
       </c>
-      <c r="W3" s="11" t="inlineStr">
+      <c r="W3" s="9" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2025-10-13</t>
+          <t>2025-10-20</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>6632</v>
+        <v>6721</v>
       </c>
       <c r="C4" t="n">
-        <v>6766.75</v>
+        <v>6841.25</v>
       </c>
       <c r="D4" t="n">
-        <v>6571.25</v>
+        <v>6690.75</v>
       </c>
       <c r="E4" t="n">
-        <v>6702.5</v>
+        <v>6827</v>
       </c>
       <c r="F4" t="n">
-        <v>107.25</v>
+        <v>124.5</v>
       </c>
       <c r="G4" s="5" t="n">
-        <v>0.0163</v>
+        <v>0.0186</v>
       </c>
       <c r="H4" t="n">
-        <v>195.5</v>
+        <v>150.5</v>
       </c>
       <c r="I4" t="n">
-        <v>6268.25</v>
+        <v>6375.75</v>
       </c>
       <c r="J4" t="n">
-        <v>6282.75</v>
+        <v>6523.75</v>
       </c>
       <c r="K4" t="n">
-        <v>6459.25</v>
+        <v>6604.75</v>
       </c>
       <c r="L4" t="n">
-        <v>6635.75</v>
+        <v>6685.75</v>
       </c>
       <c r="M4" t="n">
-        <v>6731.25</v>
+        <v>6800.25</v>
       </c>
       <c r="N4" t="n">
-        <v>6826.75</v>
+        <v>6914.75</v>
       </c>
       <c r="O4" t="n">
-        <v>7084.25</v>
+        <v>6962.25</v>
       </c>
       <c r="P4" s="6" t="n">
         <v/>
@@ -860,7 +860,7 @@
       <c r="R4" s="6" t="n">
         <v/>
       </c>
-      <c r="S4" s="7" t="inlineStr">
+      <c r="S4" s="10" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
@@ -876,64 +876,64 @@
       <c r="V4" s="8" t="n">
         <v/>
       </c>
-      <c r="W4" s="11" t="inlineStr">
+      <c r="W4" s="9" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
       </c>
       <c r="X4" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2025-10-20</t>
+          <t>2025-10-27</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>6721</v>
+        <v>6881</v>
       </c>
       <c r="C5" t="n">
-        <v>6841.25</v>
+        <v>6953.75</v>
       </c>
       <c r="D5" t="n">
-        <v>6690.75</v>
+        <v>6843.5</v>
       </c>
       <c r="E5" t="n">
-        <v>6827</v>
+        <v>6874</v>
       </c>
       <c r="F5" t="n">
-        <v>124.5</v>
+        <v>47</v>
       </c>
       <c r="G5" s="5" t="n">
-        <v>0.0186</v>
+        <v>0.0069</v>
       </c>
       <c r="H5" t="n">
-        <v>150.5</v>
+        <v>110.25</v>
       </c>
       <c r="I5" t="n">
-        <v>6375.75</v>
+        <v>6540.25</v>
       </c>
       <c r="J5" t="n">
-        <v>6523.75</v>
+        <v>6707</v>
       </c>
       <c r="K5" t="n">
-        <v>6604.75</v>
+        <v>6751.75</v>
       </c>
       <c r="L5" t="n">
-        <v>6685.75</v>
+        <v>6796.5</v>
       </c>
       <c r="M5" t="n">
-        <v>6800.25</v>
+        <v>6902.25</v>
       </c>
       <c r="N5" t="n">
-        <v>6914.75</v>
+        <v>7008</v>
       </c>
       <c r="O5" t="n">
-        <v>6962.25</v>
+        <v>6991.75</v>
       </c>
       <c r="P5" s="6" t="n">
         <v/>
@@ -944,7 +944,7 @@
       <c r="R5" s="6" t="n">
         <v/>
       </c>
-      <c r="S5" s="7" t="inlineStr">
+      <c r="S5" s="10" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
@@ -960,7 +960,7 @@
       <c r="V5" s="8" t="n">
         <v/>
       </c>
-      <c r="W5" s="11" t="inlineStr">
+      <c r="W5" s="9" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
@@ -974,69 +974,73 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2025-10-27</t>
+          <t>2025-11-03</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>6881</v>
+        <v>6878</v>
       </c>
       <c r="C6" t="n">
-        <v>6953.75</v>
+        <v>6909.5</v>
       </c>
       <c r="D6" t="n">
-        <v>6843.5</v>
+        <v>6655.5</v>
       </c>
       <c r="E6" t="n">
-        <v>6874</v>
+        <v>6753.75</v>
       </c>
       <c r="F6" t="n">
-        <v>47</v>
+        <v>-120.25</v>
       </c>
       <c r="G6" s="5" t="n">
-        <v>0.0069</v>
+        <v>-0.0175</v>
       </c>
       <c r="H6" t="n">
-        <v>110.25</v>
+        <v>254</v>
       </c>
       <c r="I6" t="n">
-        <v>6540.25</v>
+        <v>6733.25</v>
       </c>
       <c r="J6" t="n">
-        <v>6707</v>
+        <v>6751.44</v>
       </c>
       <c r="K6" t="n">
-        <v>6751.75</v>
+        <v>6818.88</v>
       </c>
       <c r="L6" t="n">
-        <v>6796.5</v>
+        <v>6886.31</v>
       </c>
       <c r="M6" t="n">
-        <v>6902.25</v>
+        <v>6929.12</v>
       </c>
       <c r="N6" t="n">
-        <v>7008</v>
+        <v>6971.94</v>
       </c>
       <c r="O6" t="n">
-        <v>6991.75</v>
-      </c>
-      <c r="P6" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q6" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R6" s="6" t="n">
-        <v/>
+        <v>7064</v>
+      </c>
+      <c r="P6" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="Q6" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="R6" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S6" s="7" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T6" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T6" s="8" t="n">
+        <v/>
       </c>
       <c r="U6" s="8" t="n">
         <v/>
@@ -1044,148 +1048,144 @@
       <c r="V6" s="8" t="n">
         <v/>
       </c>
-      <c r="W6" s="11" t="inlineStr">
+      <c r="W6" s="9" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
       </c>
-      <c r="X6" t="inlineStr">
-        <is>
-          <t>強警訊</t>
-        </is>
-      </c>
+      <c r="X6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2025-11-03</t>
+          <t>2025-11-10</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>6878</v>
+        <v>6788</v>
       </c>
       <c r="C7" t="n">
-        <v>6909.5</v>
+        <v>6900.5</v>
       </c>
       <c r="D7" t="n">
-        <v>6655.5</v>
+        <v>6670.5</v>
       </c>
       <c r="E7" t="n">
-        <v>6753.75</v>
+        <v>6755.25</v>
       </c>
       <c r="F7" t="n">
-        <v>-120.25</v>
+        <v>1.5</v>
       </c>
       <c r="G7" s="5" t="n">
-        <v>-0.0175</v>
+        <v>0.0002</v>
       </c>
       <c r="H7" t="n">
-        <v>254</v>
+        <v>230</v>
       </c>
       <c r="I7" t="n">
-        <v>6733.25</v>
+        <v>6401.5</v>
       </c>
       <c r="J7" t="n">
-        <v>6751.44</v>
+        <v>6485.38</v>
       </c>
       <c r="K7" t="n">
-        <v>6818.88</v>
+        <v>6626.75</v>
       </c>
       <c r="L7" t="n">
-        <v>6886.31</v>
+        <v>6768.12</v>
       </c>
       <c r="M7" t="n">
-        <v>6929.12</v>
+        <v>6880.75</v>
       </c>
       <c r="N7" t="n">
-        <v>6971.94</v>
+        <v>6993.38</v>
       </c>
       <c r="O7" t="n">
-        <v>7064</v>
-      </c>
-      <c r="P7" s="6" t="inlineStr">
+        <v>7163.5</v>
+      </c>
+      <c r="P7" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q7" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R7" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S7" s="7" t="inlineStr">
+        <is>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T7" s="8" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="Q7" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="R7" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S7" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T7" s="8" t="n">
-        <v/>
-      </c>
       <c r="U7" s="8" t="n">
         <v/>
       </c>
       <c r="V7" s="8" t="n">
         <v/>
       </c>
-      <c r="W7" s="11" t="inlineStr">
+      <c r="W7" s="9" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
       </c>
-      <c r="X7" t="inlineStr"/>
+      <c r="X7" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2025-11-10</t>
+          <t>2025-11-17</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>6788</v>
+        <v>6764.75</v>
       </c>
       <c r="C8" t="n">
-        <v>6900.5</v>
+        <v>6801.5</v>
       </c>
       <c r="D8" t="n">
-        <v>6670.5</v>
+        <v>6525</v>
       </c>
       <c r="E8" t="n">
-        <v>6755.25</v>
+        <v>6620.25</v>
       </c>
       <c r="F8" t="n">
-        <v>1.5</v>
+        <v>-135</v>
       </c>
       <c r="G8" s="5" t="n">
-        <v>0.0002</v>
+        <v>-0.02</v>
       </c>
       <c r="H8" t="n">
-        <v>230</v>
+        <v>276.5</v>
       </c>
       <c r="I8" t="n">
-        <v>6401.5</v>
+        <v>6440.5</v>
       </c>
       <c r="J8" t="n">
-        <v>6485.38</v>
+        <v>6510.12</v>
       </c>
       <c r="K8" t="n">
-        <v>6626.75</v>
+        <v>6640.25</v>
       </c>
       <c r="L8" t="n">
-        <v>6768.12</v>
+        <v>6770.38</v>
       </c>
       <c r="M8" t="n">
-        <v>6880.75</v>
+        <v>6870.25</v>
       </c>
       <c r="N8" t="n">
-        <v>6993.38</v>
+        <v>6970.12</v>
       </c>
       <c r="O8" t="n">
-        <v>7163.5</v>
+        <v>7130.5</v>
       </c>
       <c r="P8" s="6" t="n">
         <v/>
@@ -1193,18 +1193,18 @@
       <c r="Q8" s="6" t="n">
         <v/>
       </c>
-      <c r="R8" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S8" s="10" t="inlineStr">
-        <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T8" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="R8" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="S8" s="7" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T8" s="8" t="n">
+        <v/>
       </c>
       <c r="U8" s="8" t="n">
         <v/>
@@ -1212,64 +1212,60 @@
       <c r="V8" s="8" t="n">
         <v/>
       </c>
-      <c r="W8" s="11" t="inlineStr">
+      <c r="W8" s="9" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
       </c>
-      <c r="X8" t="inlineStr">
-        <is>
-          <t>中警訊</t>
-        </is>
-      </c>
+      <c r="X8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2025-11-17</t>
+          <t>2025-11-24</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>6764.75</v>
+        <v>6654.75</v>
       </c>
       <c r="C9" t="n">
-        <v>6801.5</v>
+        <v>6863.75</v>
       </c>
       <c r="D9" t="n">
-        <v>6525</v>
+        <v>6625</v>
       </c>
       <c r="E9" t="n">
-        <v>6620.25</v>
+        <v>6859.5</v>
       </c>
       <c r="F9" t="n">
-        <v>-135</v>
+        <v>239.25</v>
       </c>
       <c r="G9" s="5" t="n">
-        <v>-0.02</v>
+        <v>0.0361</v>
       </c>
       <c r="H9" t="n">
-        <v>276.5</v>
+        <v>238.75</v>
       </c>
       <c r="I9" t="n">
-        <v>6440.5</v>
+        <v>6248.5</v>
       </c>
       <c r="J9" t="n">
-        <v>6510.12</v>
+        <v>6322.25</v>
       </c>
       <c r="K9" t="n">
-        <v>6640.25</v>
+        <v>6482</v>
       </c>
       <c r="L9" t="n">
-        <v>6770.38</v>
+        <v>6641.75</v>
       </c>
       <c r="M9" t="n">
-        <v>6870.25</v>
+        <v>6758.5</v>
       </c>
       <c r="N9" t="n">
-        <v>6970.12</v>
+        <v>6875.25</v>
       </c>
       <c r="O9" t="n">
-        <v>7130.5</v>
+        <v>7078</v>
       </c>
       <c r="P9" s="6" t="n">
         <v/>
@@ -1277,79 +1273,85 @@
       <c r="Q9" s="6" t="n">
         <v/>
       </c>
-      <c r="R9" s="6" t="inlineStr">
+      <c r="R9" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S9" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T9" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U9" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="S9" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T9" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U9" s="8" t="n">
-        <v/>
-      </c>
       <c r="V9" s="8" t="n">
         <v/>
       </c>
-      <c r="W9" s="11" t="inlineStr">
+      <c r="W9" s="9" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
       </c>
-      <c r="X9" t="inlineStr"/>
+      <c r="X9" t="inlineStr">
+        <is>
+          <t>強警訊</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2025-11-24</t>
+          <t>2025-12-01</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>6654.75</v>
+        <v>6854.75</v>
       </c>
       <c r="C10" t="n">
-        <v>6863.75</v>
+        <v>6905</v>
       </c>
       <c r="D10" t="n">
-        <v>6625</v>
+        <v>6802</v>
       </c>
       <c r="E10" t="n">
-        <v>6859.5</v>
+        <v>6878.25</v>
       </c>
       <c r="F10" t="n">
-        <v>239.25</v>
+        <v>18.75</v>
       </c>
       <c r="G10" s="5" t="n">
-        <v>0.0361</v>
+        <v>0.0027</v>
       </c>
       <c r="H10" t="n">
-        <v>238.75</v>
+        <v>103</v>
       </c>
       <c r="I10" t="n">
-        <v>6248.5</v>
+        <v>6386.25</v>
       </c>
       <c r="J10" t="n">
-        <v>6322.25</v>
+        <v>6678.31</v>
       </c>
       <c r="K10" t="n">
-        <v>6482</v>
+        <v>6740.12</v>
       </c>
       <c r="L10" t="n">
-        <v>6641.75</v>
+        <v>6801.94</v>
       </c>
       <c r="M10" t="n">
-        <v>6758.5</v>
+        <v>6978.88</v>
       </c>
       <c r="N10" t="n">
-        <v>6875.25</v>
+        <v>7155.81</v>
       </c>
       <c r="O10" t="n">
-        <v>7078</v>
+        <v>7102.5</v>
       </c>
       <c r="P10" s="6" t="n">
         <v/>
@@ -1360,25 +1362,21 @@
       <c r="R10" s="6" t="n">
         <v/>
       </c>
-      <c r="S10" s="7" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T10" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U10" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+      <c r="S10" s="10" t="inlineStr">
+        <is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T10" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U10" s="8" t="n">
+        <v/>
       </c>
       <c r="V10" s="8" t="n">
         <v/>
       </c>
-      <c r="W10" s="11" t="inlineStr">
+      <c r="W10" s="9" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
@@ -1392,50 +1390,50 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2025-12-01</t>
+          <t>2025-12-08</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>6854.75</v>
+        <v>6883</v>
       </c>
       <c r="C11" t="n">
-        <v>6905</v>
+        <v>6928.75</v>
       </c>
       <c r="D11" t="n">
-        <v>6802</v>
+        <v>6805</v>
       </c>
       <c r="E11" t="n">
-        <v>6878.25</v>
+        <v>6830.75</v>
       </c>
       <c r="F11" t="n">
-        <v>18.75</v>
+        <v>-47.5</v>
       </c>
       <c r="G11" s="5" t="n">
-        <v>0.0027</v>
+        <v>-0.0069</v>
       </c>
       <c r="H11" t="n">
-        <v>103</v>
+        <v>123.75</v>
       </c>
       <c r="I11" t="n">
-        <v>6386.25</v>
+        <v>6699</v>
       </c>
       <c r="J11" t="n">
-        <v>6678.31</v>
+        <v>6787.62</v>
       </c>
       <c r="K11" t="n">
-        <v>6740.12</v>
+        <v>6826.75</v>
       </c>
       <c r="L11" t="n">
-        <v>6801.94</v>
+        <v>6865.88</v>
       </c>
       <c r="M11" t="n">
-        <v>6978.88</v>
+        <v>6929.75</v>
       </c>
       <c r="N11" t="n">
-        <v>7155.81</v>
+        <v>6993.62</v>
       </c>
       <c r="O11" t="n">
-        <v>7102.5</v>
+        <v>7008</v>
       </c>
       <c r="P11" s="6" t="n">
         <v/>
@@ -1443,12 +1441,14 @@
       <c r="Q11" s="6" t="n">
         <v/>
       </c>
-      <c r="R11" s="6" t="n">
-        <v/>
+      <c r="R11" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="S11" s="7" t="inlineStr">
         <is>
-          <t>↑C</t>
+          <t>↓</t>
         </is>
       </c>
       <c r="T11" s="8" t="n">
@@ -1460,64 +1460,64 @@
       <c r="V11" s="8" t="n">
         <v/>
       </c>
-      <c r="W11" s="11" t="inlineStr">
+      <c r="W11" s="9" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
       </c>
       <c r="X11" t="inlineStr">
         <is>
-          <t>強警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2025-12-08</t>
+          <t>2025-12-15</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>6883</v>
+        <v>6831</v>
       </c>
       <c r="C12" t="n">
-        <v>6928.75</v>
+        <v>6872.5</v>
       </c>
       <c r="D12" t="n">
-        <v>6805</v>
+        <v>6720.25</v>
       </c>
       <c r="E12" t="n">
-        <v>6830.75</v>
+        <v>6796.54</v>
       </c>
       <c r="F12" t="n">
-        <v>-47.5</v>
+        <v>-34.21</v>
       </c>
       <c r="G12" s="5" t="n">
-        <v>-0.0069</v>
+        <v>-0.005</v>
       </c>
       <c r="H12" t="n">
-        <v>123.75</v>
+        <v>152.25</v>
       </c>
       <c r="I12" t="n">
-        <v>6699</v>
+        <v>6681.25</v>
       </c>
       <c r="J12" t="n">
-        <v>6787.62</v>
+        <v>6688.94</v>
       </c>
       <c r="K12" t="n">
-        <v>6826.75</v>
+        <v>6768.88</v>
       </c>
       <c r="L12" t="n">
-        <v>6865.88</v>
+        <v>6848.81</v>
       </c>
       <c r="M12" t="n">
-        <v>6929.75</v>
+        <v>6892.62</v>
       </c>
       <c r="N12" t="n">
-        <v>6993.62</v>
+        <v>6936.44</v>
       </c>
       <c r="O12" t="n">
-        <v>7008</v>
+        <v>7052.5</v>
       </c>
       <c r="P12" s="6" t="n">
         <v/>
@@ -1530,7 +1530,7 @@
           <t>△C</t>
         </is>
       </c>
-      <c r="S12" s="10" t="inlineStr">
+      <c r="S12" s="7" t="inlineStr">
         <is>
           <t>↓</t>
         </is>
@@ -1544,64 +1544,60 @@
       <c r="V12" s="8" t="n">
         <v/>
       </c>
-      <c r="W12" s="11" t="inlineStr">
+      <c r="W12" s="9" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
       </c>
-      <c r="X12" t="inlineStr">
-        <is>
-          <t>中警訊</t>
-        </is>
-      </c>
+      <c r="X12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2025-12-15</t>
+          <t>2025-12-22</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>6831</v>
+        <v>6906.25</v>
       </c>
       <c r="C13" t="n">
-        <v>6872.5</v>
+        <v>6994</v>
       </c>
       <c r="D13" t="n">
-        <v>6720.25</v>
+        <v>6900.5</v>
       </c>
       <c r="E13" t="n">
-        <v>6796.54</v>
+        <v>6979.25</v>
       </c>
       <c r="F13" t="n">
-        <v>-34.21</v>
+        <v>182.71</v>
       </c>
       <c r="G13" s="5" t="n">
-        <v>-0.005</v>
+        <v>0.0269</v>
       </c>
       <c r="H13" t="n">
-        <v>152.25</v>
+        <v>93.5</v>
       </c>
       <c r="I13" t="n">
-        <v>6681.25</v>
+        <v>6568</v>
       </c>
       <c r="J13" t="n">
-        <v>6688.94</v>
+        <v>6644.37</v>
       </c>
       <c r="K13" t="n">
-        <v>6768.88</v>
+        <v>6720.42</v>
       </c>
       <c r="L13" t="n">
-        <v>6848.81</v>
+        <v>6796.46</v>
       </c>
       <c r="M13" t="n">
-        <v>6892.62</v>
+        <v>6872.67</v>
       </c>
       <c r="N13" t="n">
-        <v>6936.44</v>
+        <v>6948.87</v>
       </c>
       <c r="O13" t="n">
-        <v>7052.5</v>
+        <v>7024.75</v>
       </c>
       <c r="P13" s="6" t="n">
         <v/>
@@ -1609,28 +1605,30 @@
       <c r="Q13" s="6" t="n">
         <v/>
       </c>
-      <c r="R13" s="6" t="inlineStr">
+      <c r="R13" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S13" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T13" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U13" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="S13" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T13" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U13" s="8" t="n">
-        <v/>
-      </c>
       <c r="V13" s="8" t="n">
         <v/>
       </c>
       <c r="W13" s="11" t="inlineStr">
         <is>
-          <t>空方</t>
+          <t>多方</t>
         </is>
       </c>
       <c r="X13" t="inlineStr"/>
@@ -1638,81 +1636,81 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2025-12-22</t>
+          <t>2025-12-29</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>6906.25</v>
+        <v>6980.5</v>
       </c>
       <c r="C14" t="n">
-        <v>6994</v>
+        <v>6984.75</v>
       </c>
       <c r="D14" t="n">
+        <v>6866.75</v>
+      </c>
+      <c r="E14" t="n">
         <v>6900.5</v>
       </c>
-      <c r="E14" t="n">
-        <v>6979.25</v>
-      </c>
       <c r="F14" t="n">
-        <v>182.71</v>
+        <v>-78.75</v>
       </c>
       <c r="G14" s="5" t="n">
-        <v>0.0269</v>
+        <v>-0.0113</v>
       </c>
       <c r="H14" t="n">
-        <v>93.5</v>
+        <v>118</v>
       </c>
       <c r="I14" t="n">
-        <v>6568</v>
+        <v>6807</v>
       </c>
       <c r="J14" t="n">
-        <v>6644.37</v>
+        <v>6901.75</v>
       </c>
       <c r="K14" t="n">
-        <v>6720.42</v>
+        <v>6932.5</v>
       </c>
       <c r="L14" t="n">
-        <v>6796.46</v>
+        <v>6963.25</v>
       </c>
       <c r="M14" t="n">
-        <v>6872.67</v>
+        <v>7026</v>
       </c>
       <c r="N14" t="n">
-        <v>6948.87</v>
+        <v>7088.75</v>
       </c>
       <c r="O14" t="n">
-        <v>7024.75</v>
+        <v>7087.5</v>
       </c>
       <c r="P14" s="6" t="n">
         <v/>
       </c>
-      <c r="Q14" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R14" s="6" t="n">
-        <v/>
+      <c r="Q14" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="R14" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S14" s="7" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T14" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U14" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T14" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U14" s="8" t="n">
+        <v/>
       </c>
       <c r="V14" s="8" t="n">
         <v/>
       </c>
       <c r="W14" s="9" t="inlineStr">
         <is>
-          <t>多方</t>
+          <t>空方</t>
         </is>
       </c>
       <c r="X14" t="inlineStr"/>
@@ -1720,132 +1718,136 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2025-12-29</t>
+          <t>2026-01-05</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>6980.5</v>
+        <v>6911.5</v>
       </c>
       <c r="C15" t="n">
-        <v>6984.75</v>
+        <v>7017.5</v>
       </c>
       <c r="D15" t="n">
-        <v>6866.75</v>
+        <v>6899.5</v>
       </c>
       <c r="E15" t="n">
-        <v>6900.5</v>
+        <v>7005</v>
       </c>
       <c r="F15" t="n">
-        <v>-78.75</v>
+        <v>104.5</v>
       </c>
       <c r="G15" s="5" t="n">
-        <v>-0.0113</v>
+        <v>0.0151</v>
       </c>
       <c r="H15" t="n">
         <v>118</v>
       </c>
       <c r="I15" t="n">
-        <v>6807</v>
+        <v>6748.75</v>
       </c>
       <c r="J15" t="n">
-        <v>6901.75</v>
+        <v>6769.88</v>
       </c>
       <c r="K15" t="n">
-        <v>6932.5</v>
+        <v>6841.5</v>
       </c>
       <c r="L15" t="n">
-        <v>6963.25</v>
+        <v>6913.12</v>
       </c>
       <c r="M15" t="n">
-        <v>7026</v>
+        <v>6959.5</v>
       </c>
       <c r="N15" t="n">
-        <v>7088.75</v>
+        <v>7005.88</v>
       </c>
       <c r="O15" t="n">
-        <v>7087.5</v>
+        <v>7102.75</v>
       </c>
       <c r="P15" s="6" t="n">
         <v/>
       </c>
-      <c r="Q15" s="6" t="inlineStr">
+      <c r="Q15" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R15" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S15" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T15" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U15" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="R15" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S15" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T15" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U15" s="8" t="n">
-        <v/>
-      </c>
       <c r="V15" s="8" t="n">
         <v/>
       </c>
-      <c r="W15" s="11" t="inlineStr">
+      <c r="W15" s="9" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
       </c>
-      <c r="X15" t="inlineStr"/>
+      <c r="X15" t="inlineStr">
+        <is>
+          <t>強警訊</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2026-01-05</t>
+          <t>2026-01-12</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>6911.5</v>
+        <v>7007</v>
       </c>
       <c r="C16" t="n">
-        <v>7017.5</v>
+        <v>7036.25</v>
       </c>
       <c r="D16" t="n">
-        <v>6899.5</v>
+        <v>6923.25</v>
       </c>
       <c r="E16" t="n">
-        <v>7005</v>
+        <v>6976.75</v>
       </c>
       <c r="F16" t="n">
-        <v>104.5</v>
+        <v>-28.25</v>
       </c>
       <c r="G16" s="5" t="n">
-        <v>0.0151</v>
+        <v>-0.004</v>
       </c>
       <c r="H16" t="n">
-        <v>118</v>
+        <v>113</v>
       </c>
       <c r="I16" t="n">
-        <v>6748.75</v>
+        <v>6781.5</v>
       </c>
       <c r="J16" t="n">
-        <v>6769.88</v>
+        <v>6910.25</v>
       </c>
       <c r="K16" t="n">
-        <v>6841.5</v>
+        <v>6946</v>
       </c>
       <c r="L16" t="n">
-        <v>6913.12</v>
+        <v>6981.75</v>
       </c>
       <c r="M16" t="n">
-        <v>6959.5</v>
+        <v>7064</v>
       </c>
       <c r="N16" t="n">
-        <v>7005.88</v>
+        <v>7146.25</v>
       </c>
       <c r="O16" t="n">
-        <v>7102.75</v>
+        <v>7135.5</v>
       </c>
       <c r="P16" s="6" t="n">
         <v/>
@@ -1853,100 +1855,100 @@
       <c r="Q16" s="6" t="n">
         <v/>
       </c>
-      <c r="R16" s="6" t="n">
-        <v/>
+      <c r="R16" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S16" s="7" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T16" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U16" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T16" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U16" s="8" t="n">
+        <v/>
       </c>
       <c r="V16" s="8" t="n">
         <v/>
       </c>
-      <c r="W16" s="11" t="inlineStr">
+      <c r="W16" s="9" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
       </c>
       <c r="X16" t="inlineStr">
         <is>
-          <t>強警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-01-12</t>
+          <t>2026-01-19</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>7007</v>
+        <v>6918.25</v>
       </c>
       <c r="C17" t="n">
-        <v>7036.25</v>
+        <v>6969</v>
       </c>
       <c r="D17" t="n">
-        <v>6923.25</v>
+        <v>6814.5</v>
       </c>
       <c r="E17" t="n">
-        <v>6976.75</v>
+        <v>6945.75</v>
       </c>
       <c r="F17" t="n">
-        <v>-28.25</v>
+        <v>-31</v>
       </c>
       <c r="G17" s="5" t="n">
-        <v>-0.004</v>
+        <v>-0.0044</v>
       </c>
       <c r="H17" t="n">
-        <v>113</v>
+        <v>154.5</v>
       </c>
       <c r="I17" t="n">
-        <v>6781.5</v>
+        <v>6810.25</v>
       </c>
       <c r="J17" t="n">
-        <v>6910.25</v>
+        <v>6862.25</v>
       </c>
       <c r="K17" t="n">
-        <v>6946</v>
+        <v>6920.25</v>
       </c>
       <c r="L17" t="n">
-        <v>6981.75</v>
+        <v>6978.25</v>
       </c>
       <c r="M17" t="n">
-        <v>7064</v>
+        <v>7033.25</v>
       </c>
       <c r="N17" t="n">
-        <v>7146.25</v>
+        <v>7088.25</v>
       </c>
       <c r="O17" t="n">
-        <v>7135.5</v>
+        <v>7149.25</v>
       </c>
       <c r="P17" s="6" t="n">
         <v/>
       </c>
-      <c r="Q17" s="6" t="n">
-        <v/>
+      <c r="Q17" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="R17" s="6" t="inlineStr">
         <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S17" s="10" t="inlineStr">
-        <is>
-          <t>↓C</t>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="S17" s="7" t="inlineStr">
+        <is>
+          <t>↓</t>
         </is>
       </c>
       <c r="T17" s="8" t="n">
@@ -1958,165 +1960,165 @@
       <c r="V17" s="8" t="n">
         <v/>
       </c>
-      <c r="W17" s="11" t="inlineStr">
+      <c r="W17" s="9" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
       </c>
-      <c r="X17" t="inlineStr">
-        <is>
-          <t>中警訊</t>
-        </is>
-      </c>
+      <c r="X17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2026-01-19</t>
+          <t>2026-01-26</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>6918.25</v>
+        <v>6904</v>
       </c>
       <c r="C18" t="n">
-        <v>6969</v>
+        <v>7043</v>
       </c>
       <c r="D18" t="n">
-        <v>6814.5</v>
+        <v>6879</v>
       </c>
       <c r="E18" t="n">
-        <v>6945.75</v>
+        <v>6965.75</v>
       </c>
       <c r="F18" t="n">
-        <v>-31</v>
+        <v>20</v>
       </c>
       <c r="G18" s="5" t="n">
-        <v>-0.0044</v>
+        <v>0.0029</v>
       </c>
       <c r="H18" t="n">
-        <v>154.5</v>
+        <v>164</v>
       </c>
       <c r="I18" t="n">
-        <v>6810.25</v>
+        <v>6660</v>
       </c>
       <c r="J18" t="n">
-        <v>6862.25</v>
+        <v>6818.25</v>
       </c>
       <c r="K18" t="n">
-        <v>6920.25</v>
+        <v>6868.5</v>
       </c>
       <c r="L18" t="n">
-        <v>6978.25</v>
+        <v>6918.75</v>
       </c>
       <c r="M18" t="n">
-        <v>7033.25</v>
+        <v>7023</v>
       </c>
       <c r="N18" t="n">
-        <v>7088.25</v>
+        <v>7127.25</v>
       </c>
       <c r="O18" t="n">
-        <v>7149.25</v>
+        <v>7123.5</v>
       </c>
       <c r="P18" s="6" t="n">
         <v/>
       </c>
-      <c r="Q18" s="6" t="inlineStr">
+      <c r="Q18" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R18" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S18" s="10" t="inlineStr">
+        <is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T18" s="8" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="R18" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="S18" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T18" s="8" t="n">
-        <v/>
-      </c>
       <c r="U18" s="8" t="n">
         <v/>
       </c>
       <c r="V18" s="8" t="n">
         <v/>
       </c>
-      <c r="W18" s="11" t="inlineStr">
+      <c r="W18" s="9" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
       </c>
-      <c r="X18" t="inlineStr"/>
+      <c r="X18" t="inlineStr">
+        <is>
+          <t>強警訊</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-01-26</t>
+          <t>2026-02-02</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>6904</v>
+        <v>6938.5</v>
       </c>
       <c r="C19" t="n">
-        <v>7043</v>
+        <v>7027.25</v>
       </c>
       <c r="D19" t="n">
-        <v>6879</v>
+        <v>6751.5</v>
       </c>
       <c r="E19" t="n">
-        <v>6965.75</v>
+        <v>6952.75</v>
       </c>
       <c r="F19" t="n">
-        <v>20</v>
+        <v>-13</v>
       </c>
       <c r="G19" s="5" t="n">
-        <v>0.0029</v>
+        <v>-0.0019</v>
       </c>
       <c r="H19" t="n">
-        <v>164</v>
+        <v>275.75</v>
       </c>
       <c r="I19" t="n">
-        <v>6660</v>
+        <v>6715</v>
       </c>
       <c r="J19" t="n">
-        <v>6818.25</v>
+        <v>6804.12</v>
       </c>
       <c r="K19" t="n">
-        <v>6868.5</v>
+        <v>6883.75</v>
       </c>
       <c r="L19" t="n">
-        <v>6918.75</v>
+        <v>6963.38</v>
       </c>
       <c r="M19" t="n">
-        <v>7023</v>
+        <v>7047.75</v>
       </c>
       <c r="N19" t="n">
-        <v>7127.25</v>
+        <v>7132.12</v>
       </c>
       <c r="O19" t="n">
-        <v>7123.5</v>
+        <v>7207</v>
       </c>
       <c r="P19" s="6" t="n">
         <v/>
       </c>
-      <c r="Q19" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R19" s="6" t="n">
-        <v/>
+      <c r="Q19" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="R19" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S19" s="7" t="inlineStr">
         <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T19" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T19" s="8" t="n">
+        <v/>
       </c>
       <c r="U19" s="8" t="n">
         <v/>
@@ -2124,81 +2126,75 @@
       <c r="V19" s="8" t="n">
         <v/>
       </c>
-      <c r="W19" s="11" t="inlineStr">
+      <c r="W19" s="9" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
       </c>
-      <c r="X19" t="inlineStr">
-        <is>
-          <t>強警訊</t>
-        </is>
-      </c>
+      <c r="X19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2026-02-02</t>
+          <t>2026-02-09</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>6938.5</v>
+        <v>6960.25</v>
       </c>
       <c r="C20" t="n">
-        <v>7027.25</v>
+        <v>7011.5</v>
       </c>
       <c r="D20" t="n">
-        <v>6751.5</v>
+        <v>6808.75</v>
       </c>
       <c r="E20" t="n">
-        <v>6952.75</v>
+        <v>6850.5</v>
       </c>
       <c r="F20" t="n">
-        <v>-13</v>
+        <v>-102.25</v>
       </c>
       <c r="G20" s="5" t="n">
-        <v>-0.0019</v>
+        <v>-0.0147</v>
       </c>
       <c r="H20" t="n">
-        <v>275.75</v>
+        <v>202.75</v>
       </c>
       <c r="I20" t="n">
-        <v>6715</v>
+        <v>6475.75</v>
       </c>
       <c r="J20" t="n">
-        <v>6804.12</v>
+        <v>6708.69</v>
       </c>
       <c r="K20" t="n">
-        <v>6883.75</v>
+        <v>6814.88</v>
       </c>
       <c r="L20" t="n">
-        <v>6963.38</v>
+        <v>6921.06</v>
       </c>
       <c r="M20" t="n">
-        <v>7047.75</v>
+        <v>7090.62</v>
       </c>
       <c r="N20" t="n">
-        <v>7132.12</v>
+        <v>7260.19</v>
       </c>
       <c r="O20" t="n">
-        <v>7207</v>
+        <v>7303</v>
       </c>
       <c r="P20" s="6" t="n">
         <v/>
       </c>
-      <c r="Q20" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="Q20" s="6" t="n">
+        <v/>
       </c>
       <c r="R20" s="6" t="inlineStr">
         <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S20" s="10" t="inlineStr">
-        <is>
-          <t>↓C</t>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="S20" s="7" t="inlineStr">
+        <is>
+          <t>↓</t>
         </is>
       </c>
       <c r="T20" s="8" t="n">
@@ -2210,60 +2206,64 @@
       <c r="V20" s="8" t="n">
         <v/>
       </c>
-      <c r="W20" s="11" t="inlineStr">
+      <c r="W20" s="9" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
       </c>
-      <c r="X20" t="inlineStr"/>
+      <c r="X20" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-02-09</t>
+          <t>2026-02-16</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>6960.25</v>
+        <v>6852.5</v>
       </c>
       <c r="C21" t="n">
-        <v>7011.5</v>
+        <v>6931.5</v>
       </c>
       <c r="D21" t="n">
-        <v>6808.75</v>
+        <v>6791</v>
       </c>
       <c r="E21" t="n">
-        <v>6850.5</v>
+        <v>6923.25</v>
       </c>
       <c r="F21" t="n">
-        <v>-102.25</v>
+        <v>72.75</v>
       </c>
       <c r="G21" s="5" t="n">
-        <v>-0.0147</v>
+        <v>0.0106</v>
       </c>
       <c r="H21" t="n">
-        <v>202.75</v>
+        <v>140.5</v>
       </c>
       <c r="I21" t="n">
-        <v>6475.75</v>
+        <v>6606</v>
       </c>
       <c r="J21" t="n">
-        <v>6708.69</v>
+        <v>6617.94</v>
       </c>
       <c r="K21" t="n">
-        <v>6814.88</v>
+        <v>6749.12</v>
       </c>
       <c r="L21" t="n">
-        <v>6921.06</v>
+        <v>6880.31</v>
       </c>
       <c r="M21" t="n">
-        <v>7090.62</v>
+        <v>6951.88</v>
       </c>
       <c r="N21" t="n">
-        <v>7260.19</v>
+        <v>7023.44</v>
       </c>
       <c r="O21" t="n">
-        <v>7303</v>
+        <v>7214.25</v>
       </c>
       <c r="P21" s="6" t="n">
         <v/>
@@ -2271,26 +2271,26 @@
       <c r="Q21" s="6" t="n">
         <v/>
       </c>
-      <c r="R21" s="6" t="inlineStr">
+      <c r="R21" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S21" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T21" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="S21" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T21" s="8" t="n">
-        <v/>
-      </c>
       <c r="U21" s="8" t="n">
         <v/>
       </c>
       <c r="V21" s="8" t="n">
         <v/>
       </c>
-      <c r="W21" s="11" t="inlineStr">
+      <c r="W21" s="9" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
@@ -2304,50 +2304,50 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2026-02-16</t>
+          <t>2026-02-23</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>6852.5</v>
+        <v>6918</v>
       </c>
       <c r="C22" t="n">
-        <v>6931.5</v>
+        <v>6983.75</v>
       </c>
       <c r="D22" t="n">
-        <v>6791</v>
+        <v>6828.5</v>
       </c>
       <c r="E22" t="n">
-        <v>6923.25</v>
+        <v>6889</v>
       </c>
       <c r="F22" t="n">
-        <v>72.75</v>
+        <v>-34.25</v>
       </c>
       <c r="G22" s="5" t="n">
-        <v>0.0106</v>
+        <v>-0.0049</v>
       </c>
       <c r="H22" t="n">
-        <v>140.5</v>
+        <v>155.25</v>
       </c>
       <c r="I22" t="n">
-        <v>6606</v>
+        <v>6650.5</v>
       </c>
       <c r="J22" t="n">
-        <v>6617.94</v>
+        <v>6813.75</v>
       </c>
       <c r="K22" t="n">
-        <v>6749.12</v>
+        <v>6853</v>
       </c>
       <c r="L22" t="n">
-        <v>6880.31</v>
+        <v>6892.25</v>
       </c>
       <c r="M22" t="n">
-        <v>6951.88</v>
+        <v>6993.5</v>
       </c>
       <c r="N22" t="n">
-        <v>7023.44</v>
+        <v>7094.75</v>
       </c>
       <c r="O22" t="n">
-        <v>7214.25</v>
+        <v>7072</v>
       </c>
       <c r="P22" s="6" t="n">
         <v/>
@@ -2355,18 +2355,18 @@
       <c r="Q22" s="6" t="n">
         <v/>
       </c>
-      <c r="R22" s="6" t="n">
-        <v/>
+      <c r="R22" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S22" s="7" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T22" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T22" s="8" t="n">
+        <v/>
       </c>
       <c r="U22" s="8" t="n">
         <v/>
@@ -2374,79 +2374,81 @@
       <c r="V22" s="8" t="n">
         <v/>
       </c>
-      <c r="W22" s="11" t="inlineStr">
+      <c r="W22" s="9" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
       </c>
       <c r="X22" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-02-23</t>
+          <t>2026-03-02</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>6918</v>
+        <v>6820</v>
       </c>
       <c r="C23" t="n">
-        <v>6983.75</v>
+        <v>6911.25</v>
       </c>
       <c r="D23" t="n">
-        <v>6828.5</v>
+        <v>6715.75</v>
       </c>
       <c r="E23" t="n">
-        <v>6889</v>
+        <v>6743.75</v>
       </c>
       <c r="F23" t="n">
-        <v>-34.25</v>
+        <v>-145.25</v>
       </c>
       <c r="G23" s="5" t="n">
-        <v>-0.0049</v>
+        <v>-0.0211</v>
       </c>
       <c r="H23" t="n">
-        <v>155.25</v>
+        <v>195.5</v>
       </c>
       <c r="I23" t="n">
-        <v>6650.5</v>
+        <v>6673.25</v>
       </c>
       <c r="J23" t="n">
-        <v>6813.75</v>
+        <v>6725.19</v>
       </c>
       <c r="K23" t="n">
-        <v>6853</v>
+        <v>6811.38</v>
       </c>
       <c r="L23" t="n">
-        <v>6892.25</v>
+        <v>6897.56</v>
       </c>
       <c r="M23" t="n">
-        <v>6993.5</v>
+        <v>6966.62</v>
       </c>
       <c r="N23" t="n">
-        <v>7094.75</v>
+        <v>7035.69</v>
       </c>
       <c r="O23" t="n">
-        <v>7072</v>
+        <v>7139</v>
       </c>
       <c r="P23" s="6" t="n">
         <v/>
       </c>
-      <c r="Q23" s="6" t="n">
-        <v/>
+      <c r="Q23" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="R23" s="6" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="S23" s="10" t="inlineStr">
-        <is>
-          <t>↓C</t>
+      <c r="S23" s="7" t="inlineStr">
+        <is>
+          <t>↓</t>
         </is>
       </c>
       <c r="T23" s="8" t="n">
@@ -2458,93 +2460,89 @@
       <c r="V23" s="8" t="n">
         <v/>
       </c>
-      <c r="W23" s="11" t="inlineStr">
+      <c r="W23" s="9" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
       </c>
-      <c r="X23" t="inlineStr">
-        <is>
-          <t>中警訊</t>
-        </is>
-      </c>
+      <c r="X23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-09</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>6820</v>
+        <v>6685.5</v>
       </c>
       <c r="C24" t="n">
-        <v>6911.25</v>
+        <v>6852</v>
       </c>
       <c r="D24" t="n">
-        <v>6715.75</v>
+        <v>6584.5</v>
       </c>
       <c r="E24" t="n">
-        <v>6743.75</v>
+        <v>6636</v>
       </c>
       <c r="F24" t="n">
-        <v>-145.25</v>
+        <v>-107.75</v>
       </c>
       <c r="G24" s="5" t="n">
-        <v>-0.0211</v>
+        <v>-0.016</v>
       </c>
       <c r="H24" t="n">
-        <v>195.5</v>
+        <v>267.5</v>
       </c>
       <c r="I24" t="n">
-        <v>6673.25</v>
+        <v>6520.25</v>
       </c>
       <c r="J24" t="n">
-        <v>6725.19</v>
+        <v>6513.38</v>
       </c>
       <c r="K24" t="n">
-        <v>6811.38</v>
+        <v>6646</v>
       </c>
       <c r="L24" t="n">
-        <v>6897.56</v>
+        <v>6778.62</v>
       </c>
       <c r="M24" t="n">
-        <v>6966.62</v>
+        <v>6841.5</v>
       </c>
       <c r="N24" t="n">
-        <v>7035.69</v>
+        <v>6904.38</v>
       </c>
       <c r="O24" t="n">
-        <v>7139</v>
+        <v>7106.75</v>
       </c>
       <c r="P24" s="6" t="n">
         <v/>
       </c>
-      <c r="Q24" s="6" t="inlineStr">
+      <c r="Q24" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R24" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="R24" s="6" t="inlineStr">
+      <c r="S24" s="7" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T24" s="8" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="S24" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T24" s="8" t="n">
-        <v/>
-      </c>
       <c r="U24" s="8" t="n">
         <v/>
       </c>
       <c r="V24" s="8" t="n">
         <v/>
       </c>
-      <c r="W24" s="11" t="inlineStr">
+      <c r="W24" s="9" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
@@ -2554,50 +2552,50 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-03-16</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>6685.5</v>
+        <v>6608.5</v>
       </c>
       <c r="C25" t="n">
-        <v>6852</v>
+        <v>6762.25</v>
       </c>
       <c r="D25" t="n">
-        <v>6584.5</v>
+        <v>6558</v>
       </c>
       <c r="E25" t="n">
-        <v>6636</v>
+        <v>6594.63</v>
       </c>
       <c r="F25" t="n">
-        <v>-107.75</v>
+        <v>-41.37</v>
       </c>
       <c r="G25" s="5" t="n">
-        <v>-0.016</v>
+        <v>-0.0062</v>
       </c>
       <c r="H25" t="n">
-        <v>267.5</v>
+        <v>204.25</v>
       </c>
       <c r="I25" t="n">
-        <v>6520.25</v>
+        <v>6317</v>
       </c>
       <c r="J25" t="n">
-        <v>6513.38</v>
+        <v>6327.38</v>
       </c>
       <c r="K25" t="n">
-        <v>6646</v>
+        <v>6502.25</v>
       </c>
       <c r="L25" t="n">
-        <v>6778.62</v>
+        <v>6677.12</v>
       </c>
       <c r="M25" t="n">
-        <v>6841.5</v>
+        <v>6769.75</v>
       </c>
       <c r="N25" t="n">
-        <v>6904.38</v>
+        <v>6862.38</v>
       </c>
       <c r="O25" t="n">
-        <v>7106.75</v>
+        <v>7119.5</v>
       </c>
       <c r="P25" s="6" t="n">
         <v/>
@@ -2605,20 +2603,16 @@
       <c r="Q25" s="6" t="n">
         <v/>
       </c>
-      <c r="R25" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="S25" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T25" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="R25" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S25" s="7" t="inlineStr">
+        <is>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T25" s="8" t="n">
+        <v/>
       </c>
       <c r="U25" s="8" t="n">
         <v/>
@@ -2626,7 +2620,7 @@
       <c r="V25" s="8" t="n">
         <v/>
       </c>
-      <c r="W25" s="11" t="inlineStr">
+      <c r="W25" s="9" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
@@ -2636,67 +2630,73 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-23</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>6608.5</v>
+        <v>6510</v>
       </c>
       <c r="C26" t="n">
-        <v>6762.25</v>
+        <v>6748</v>
       </c>
       <c r="D26" t="n">
-        <v>6558</v>
+        <v>6389</v>
       </c>
       <c r="E26" t="n">
-        <v>6594.63</v>
+        <v>6412.25</v>
       </c>
       <c r="F26" t="n">
-        <v>-41.37</v>
+        <v>-182.38</v>
       </c>
       <c r="G26" s="5" t="n">
-        <v>-0.0062</v>
+        <v>-0.0277</v>
       </c>
       <c r="H26" t="n">
-        <v>204.25</v>
+        <v>359</v>
       </c>
       <c r="I26" t="n">
-        <v>6317</v>
+        <v>6353.75</v>
       </c>
       <c r="J26" t="n">
-        <v>6327.38</v>
+        <v>6357.63</v>
       </c>
       <c r="K26" t="n">
-        <v>6502.25</v>
+        <v>6492.5</v>
       </c>
       <c r="L26" t="n">
-        <v>6677.12</v>
+        <v>6627.38</v>
       </c>
       <c r="M26" t="n">
-        <v>6769.75</v>
+        <v>6696.75</v>
       </c>
       <c r="N26" t="n">
-        <v>6862.38</v>
+        <v>6766.13</v>
       </c>
       <c r="O26" t="n">
-        <v>7119.5</v>
+        <v>6966.5</v>
       </c>
       <c r="P26" s="6" t="n">
         <v/>
       </c>
-      <c r="Q26" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R26" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S26" s="10" t="inlineStr">
-        <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T26" s="8" t="n">
-        <v/>
+      <c r="Q26" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="R26" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S26" s="7" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T26" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="U26" s="8" t="n">
         <v/>
@@ -2704,7 +2704,7 @@
       <c r="V26" s="8" t="n">
         <v/>
       </c>
-      <c r="W26" s="11" t="inlineStr">
+      <c r="W26" s="9" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
@@ -2714,134 +2714,134 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-03-23</t>
+          <t>2026-03-30</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>6510</v>
+        <v>6380</v>
       </c>
       <c r="C27" t="n">
-        <v>6748</v>
+        <v>6653.75</v>
       </c>
       <c r="D27" t="n">
-        <v>6389</v>
+        <v>6353.25</v>
       </c>
       <c r="E27" t="n">
-        <v>6412.25</v>
+        <v>6603.75</v>
       </c>
       <c r="F27" t="n">
-        <v>-182.38</v>
+        <v>191.5</v>
       </c>
       <c r="G27" s="5" t="n">
-        <v>-0.0277</v>
+        <v>0.0299</v>
       </c>
       <c r="H27" t="n">
-        <v>359</v>
+        <v>300.5</v>
       </c>
       <c r="I27" t="n">
-        <v>6353.75</v>
+        <v>6030</v>
       </c>
       <c r="J27" t="n">
-        <v>6357.63</v>
+        <v>5975.12</v>
       </c>
       <c r="K27" t="n">
-        <v>6492.5</v>
+        <v>6232.75</v>
       </c>
       <c r="L27" t="n">
-        <v>6627.38</v>
+        <v>6490.38</v>
       </c>
       <c r="M27" t="n">
-        <v>6696.75</v>
+        <v>6591.75</v>
       </c>
       <c r="N27" t="n">
-        <v>6766.13</v>
+        <v>6693.12</v>
       </c>
       <c r="O27" t="n">
-        <v>6966.5</v>
+        <v>7107</v>
       </c>
       <c r="P27" s="6" t="n">
         <v/>
       </c>
-      <c r="Q27" s="6" t="inlineStr">
+      <c r="Q27" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R27" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S27" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T27" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="R27" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S27" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T27" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
       <c r="U27" s="8" t="n">
         <v/>
       </c>
       <c r="V27" s="8" t="n">
         <v/>
       </c>
-      <c r="W27" s="11" t="inlineStr">
+      <c r="W27" s="9" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
       </c>
-      <c r="X27" t="inlineStr"/>
+      <c r="X27" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-04-06</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>6380</v>
+        <v>6590</v>
       </c>
       <c r="C28" t="n">
-        <v>6653.75</v>
+        <v>6888</v>
       </c>
       <c r="D28" t="n">
-        <v>6353.25</v>
+        <v>6567</v>
       </c>
       <c r="E28" t="n">
-        <v>6603.75</v>
+        <v>6855.25</v>
       </c>
       <c r="F28" t="n">
-        <v>191.5</v>
+        <v>251.5</v>
       </c>
       <c r="G28" s="5" t="n">
-        <v>0.0299</v>
+        <v>0.0381</v>
       </c>
       <c r="H28" t="n">
-        <v>300.5</v>
+        <v>321</v>
       </c>
       <c r="I28" t="n">
-        <v>6030</v>
+        <v>6052.75</v>
       </c>
       <c r="J28" t="n">
-        <v>5975.12</v>
+        <v>6353.38</v>
       </c>
       <c r="K28" t="n">
-        <v>6232.75</v>
+        <v>6453.5</v>
       </c>
       <c r="L28" t="n">
-        <v>6490.38</v>
+        <v>6553.62</v>
       </c>
       <c r="M28" t="n">
-        <v>6591.75</v>
+        <v>6754</v>
       </c>
       <c r="N28" t="n">
-        <v>6693.12</v>
+        <v>6954.38</v>
       </c>
       <c r="O28" t="n">
-        <v>7107</v>
+        <v>6954.25</v>
       </c>
       <c r="P28" s="6" t="n">
         <v/>
@@ -2852,80 +2852,82 @@
       <c r="R28" s="6" t="n">
         <v/>
       </c>
-      <c r="S28" s="7" t="inlineStr">
+      <c r="S28" s="10" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
       </c>
       <c r="T28" s="8" t="inlineStr">
         <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U28" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V28" s="8" t="inlineStr">
+        <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="U28" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V28" s="8" t="n">
-        <v/>
-      </c>
-      <c r="W28" s="11" t="inlineStr">
+      <c r="W28" s="9" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
       </c>
       <c r="X28" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-04-06</t>
+          <t>2026-04-13</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>6590</v>
+        <v>6780</v>
       </c>
       <c r="C29" t="n">
-        <v>6888</v>
+        <v>7185.75</v>
       </c>
       <c r="D29" t="n">
-        <v>6567</v>
+        <v>6767</v>
       </c>
       <c r="E29" t="n">
-        <v>6855.25</v>
+        <v>7161.5</v>
       </c>
       <c r="F29" t="n">
-        <v>251.5</v>
+        <v>306.25</v>
       </c>
       <c r="G29" s="5" t="n">
-        <v>0.0381</v>
+        <v>0.0447</v>
       </c>
       <c r="H29" t="n">
-        <v>321</v>
+        <v>418.75</v>
       </c>
       <c r="I29" t="n">
-        <v>6052.75</v>
+        <v>6246</v>
       </c>
       <c r="J29" t="n">
-        <v>6353.38</v>
+        <v>6598.12</v>
       </c>
       <c r="K29" t="n">
-        <v>6453.5</v>
+        <v>6694.75</v>
       </c>
       <c r="L29" t="n">
-        <v>6553.62</v>
+        <v>6791.38</v>
       </c>
       <c r="M29" t="n">
-        <v>6754</v>
+        <v>7015.75</v>
       </c>
       <c r="N29" t="n">
-        <v>6954.38</v>
+        <v>7240.12</v>
       </c>
       <c r="O29" t="n">
-        <v>6954.25</v>
+        <v>7209</v>
       </c>
       <c r="P29" s="6" t="n">
         <v/>
@@ -2936,7 +2938,7 @@
       <c r="R29" s="6" t="n">
         <v/>
       </c>
-      <c r="S29" s="7" t="inlineStr">
+      <c r="S29" s="10" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
@@ -2954,7 +2956,7 @@
           <t>△C</t>
         </is>
       </c>
-      <c r="W29" s="11" t="inlineStr">
+      <c r="W29" s="9" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
@@ -2968,50 +2970,50 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2026-04-13</t>
+          <t>2026-04-20</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>6780</v>
+        <v>7102.5</v>
       </c>
       <c r="C30" t="n">
-        <v>7185.75</v>
+        <v>7200.5</v>
       </c>
       <c r="D30" t="n">
-        <v>6767</v>
+        <v>7079.25</v>
       </c>
       <c r="E30" t="n">
-        <v>7161.5</v>
+        <v>7194.75</v>
       </c>
       <c r="F30" t="n">
-        <v>306.25</v>
+        <v>33.25</v>
       </c>
       <c r="G30" s="5" t="n">
-        <v>0.0447</v>
+        <v>0.0046</v>
       </c>
       <c r="H30" t="n">
-        <v>418.75</v>
+        <v>121.25</v>
       </c>
       <c r="I30" t="n">
-        <v>6246</v>
+        <v>6348.25</v>
       </c>
       <c r="J30" t="n">
-        <v>6598.12</v>
+        <v>6835.31</v>
       </c>
       <c r="K30" t="n">
-        <v>6694.75</v>
+        <v>6952.12</v>
       </c>
       <c r="L30" t="n">
-        <v>6791.38</v>
+        <v>7068.94</v>
       </c>
       <c r="M30" t="n">
-        <v>7015.75</v>
+        <v>7370.88</v>
       </c>
       <c r="N30" t="n">
-        <v>7240.12</v>
+        <v>7672.81</v>
       </c>
       <c r="O30" t="n">
-        <v>7209</v>
+        <v>7604.5</v>
       </c>
       <c r="P30" s="6" t="n">
         <v/>
@@ -3022,25 +3024,21 @@
       <c r="R30" s="6" t="n">
         <v/>
       </c>
-      <c r="S30" s="7" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T30" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="S30" s="10" t="inlineStr">
+        <is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T30" s="8" t="n">
+        <v/>
       </c>
       <c r="U30" s="8" t="n">
         <v/>
       </c>
-      <c r="V30" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="W30" s="11" t="inlineStr">
+      <c r="V30" s="8" t="n">
+        <v/>
+      </c>
+      <c r="W30" s="9" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
@@ -3054,50 +3052,50 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
+          <t>2026-04-27</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>7102.5</v>
+        <v>7185</v>
       </c>
       <c r="C31" t="n">
-        <v>7200.5</v>
+        <v>7300.75</v>
       </c>
       <c r="D31" t="n">
-        <v>7079.25</v>
+        <v>7131.25</v>
       </c>
       <c r="E31" t="n">
-        <v>7194.75</v>
+        <v>7258</v>
       </c>
       <c r="F31" t="n">
-        <v>33.25</v>
+        <v>63.25</v>
       </c>
       <c r="G31" s="5" t="n">
-        <v>0.0046</v>
+        <v>0.008800000000000001</v>
       </c>
       <c r="H31" t="n">
-        <v>121.25</v>
+        <v>169.5</v>
       </c>
       <c r="I31" t="n">
-        <v>6348.25</v>
+        <v>6958</v>
       </c>
       <c r="J31" t="n">
-        <v>6835.31</v>
+        <v>7100.94</v>
       </c>
       <c r="K31" t="n">
-        <v>6952.12</v>
+        <v>7134.12</v>
       </c>
       <c r="L31" t="n">
-        <v>7068.94</v>
+        <v>7167.31</v>
       </c>
       <c r="M31" t="n">
-        <v>7370.88</v>
+        <v>7255.38</v>
       </c>
       <c r="N31" t="n">
-        <v>7672.81</v>
+        <v>7343.44</v>
       </c>
       <c r="O31" t="n">
-        <v>7604.5</v>
+        <v>7321.75</v>
       </c>
       <c r="P31" s="6" t="n">
         <v/>
@@ -3105,16 +3103,20 @@
       <c r="Q31" s="6" t="n">
         <v/>
       </c>
-      <c r="R31" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S31" s="7" t="inlineStr">
-        <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T31" s="8" t="n">
-        <v/>
+      <c r="R31" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S31" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T31" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="U31" s="8" t="n">
         <v/>
@@ -3122,7 +3124,7 @@
       <c r="V31" s="8" t="n">
         <v/>
       </c>
-      <c r="W31" s="11" t="inlineStr">
+      <c r="W31" s="9" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
@@ -3136,50 +3138,50 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-05-04</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>7185</v>
+        <v>7276.25</v>
       </c>
       <c r="C32" t="n">
-        <v>7300.75</v>
+        <v>7427.75</v>
       </c>
       <c r="D32" t="n">
-        <v>7131.25</v>
+        <v>7199.5</v>
       </c>
       <c r="E32" t="n">
-        <v>7258</v>
+        <v>7419</v>
       </c>
       <c r="F32" t="n">
-        <v>63.25</v>
+        <v>161</v>
       </c>
       <c r="G32" s="5" t="n">
-        <v>0.008800000000000001</v>
+        <v>0.0222</v>
       </c>
       <c r="H32" t="n">
-        <v>169.5</v>
+        <v>228.25</v>
       </c>
       <c r="I32" t="n">
-        <v>6958</v>
+        <v>6961.75</v>
       </c>
       <c r="J32" t="n">
-        <v>7100.94</v>
+        <v>7109.5</v>
       </c>
       <c r="K32" t="n">
-        <v>7134.12</v>
+        <v>7173.25</v>
       </c>
       <c r="L32" t="n">
-        <v>7167.31</v>
+        <v>7237</v>
       </c>
       <c r="M32" t="n">
-        <v>7255.38</v>
+        <v>7342.75</v>
       </c>
       <c r="N32" t="n">
-        <v>7343.44</v>
+        <v>7448.5</v>
       </c>
       <c r="O32" t="n">
-        <v>7321.75</v>
+        <v>7470.25</v>
       </c>
       <c r="P32" s="6" t="n">
         <v/>
@@ -3187,28 +3189,28 @@
       <c r="Q32" s="6" t="n">
         <v/>
       </c>
-      <c r="R32" s="6" t="inlineStr">
+      <c r="R32" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S32" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T32" s="8" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="S32" s="7" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T32" s="8" t="inlineStr">
+      <c r="U32" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="U32" s="8" t="n">
-        <v/>
-      </c>
       <c r="V32" s="8" t="n">
         <v/>
       </c>
-      <c r="W32" s="11" t="inlineStr">
+      <c r="W32" s="9" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
@@ -3222,50 +3224,50 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2026-05-04</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>7276.25</v>
+        <v>7403.5</v>
       </c>
       <c r="C33" t="n">
-        <v>7427.75</v>
+        <v>7540</v>
       </c>
       <c r="D33" t="n">
-        <v>7199.5</v>
+        <v>7363.25</v>
       </c>
       <c r="E33" t="n">
-        <v>7419</v>
+        <v>7432.25</v>
       </c>
       <c r="F33" t="n">
-        <v>161</v>
+        <v>13.25</v>
       </c>
       <c r="G33" s="5" t="n">
-        <v>0.0222</v>
+        <v>0.0018</v>
       </c>
       <c r="H33" t="n">
-        <v>228.25</v>
+        <v>176.75</v>
       </c>
       <c r="I33" t="n">
-        <v>6961.75</v>
+        <v>6971.25</v>
       </c>
       <c r="J33" t="n">
-        <v>7109.5</v>
+        <v>7243.44</v>
       </c>
       <c r="K33" t="n">
-        <v>7173.25</v>
+        <v>7304.88</v>
       </c>
       <c r="L33" t="n">
-        <v>7237</v>
+        <v>7366.31</v>
       </c>
       <c r="M33" t="n">
-        <v>7342.75</v>
+        <v>7533.12</v>
       </c>
       <c r="N33" t="n">
-        <v>7448.5</v>
+        <v>7699.94</v>
       </c>
       <c r="O33" t="n">
-        <v>7470.25</v>
+        <v>7656</v>
       </c>
       <c r="P33" s="6" t="n">
         <v/>
@@ -3276,9 +3278,9 @@
       <c r="R33" s="6" t="n">
         <v/>
       </c>
-      <c r="S33" s="7" t="inlineStr">
-        <is>
-          <t>↑</t>
+      <c r="S33" s="10" t="inlineStr">
+        <is>
+          <t>↑C</t>
         </is>
       </c>
       <c r="T33" s="8" t="inlineStr">
@@ -3286,15 +3288,13 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="U33" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+      <c r="U33" s="8" t="n">
+        <v/>
       </c>
       <c r="V33" s="8" t="n">
         <v/>
       </c>
-      <c r="W33" s="11" t="inlineStr">
+      <c r="W33" s="9" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
@@ -3308,50 +3308,50 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-05-18</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>7403.5</v>
+        <v>7410</v>
       </c>
       <c r="C34" t="n">
-        <v>7540</v>
+        <v>7524</v>
       </c>
       <c r="D34" t="n">
-        <v>7363.25</v>
+        <v>7354.25</v>
       </c>
       <c r="E34" t="n">
-        <v>7432.25</v>
+        <v>7491</v>
       </c>
       <c r="F34" t="n">
-        <v>13.25</v>
+        <v>58.75</v>
       </c>
       <c r="G34" s="5" t="n">
-        <v>0.0018</v>
+        <v>0.007900000000000001</v>
       </c>
       <c r="H34" t="n">
-        <v>176.75</v>
+        <v>169.75</v>
       </c>
       <c r="I34" t="n">
-        <v>6971.25</v>
+        <v>7186.5</v>
       </c>
       <c r="J34" t="n">
-        <v>7243.44</v>
+        <v>7245.81</v>
       </c>
       <c r="K34" t="n">
-        <v>7304.88</v>
+        <v>7343.88</v>
       </c>
       <c r="L34" t="n">
-        <v>7366.31</v>
+        <v>7441.94</v>
       </c>
       <c r="M34" t="n">
-        <v>7533.12</v>
+        <v>7520.62</v>
       </c>
       <c r="N34" t="n">
-        <v>7699.94</v>
+        <v>7599.31</v>
       </c>
       <c r="O34" t="n">
-        <v>7656</v>
+        <v>7716.75</v>
       </c>
       <c r="P34" s="6" t="n">
         <v/>
@@ -3362,14 +3362,14 @@
       <c r="R34" s="6" t="n">
         <v/>
       </c>
-      <c r="S34" s="7" t="inlineStr">
-        <is>
-          <t>↑C</t>
+      <c r="S34" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
         </is>
       </c>
       <c r="T34" s="8" t="inlineStr">
         <is>
-          <t>✓</t>
+          <t>△C</t>
         </is>
       </c>
       <c r="U34" s="8" t="n">
@@ -3378,64 +3378,64 @@
       <c r="V34" s="8" t="n">
         <v/>
       </c>
-      <c r="W34" s="11" t="inlineStr">
+      <c r="W34" s="9" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
       </c>
       <c r="X34" t="inlineStr">
         <is>
-          <t>強警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-05-25</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>7410</v>
+        <v>7519</v>
       </c>
       <c r="C35" t="n">
-        <v>7524</v>
+        <v>7611.5</v>
       </c>
       <c r="D35" t="n">
-        <v>7354.25</v>
+        <v>7505.75</v>
       </c>
       <c r="E35" t="n">
-        <v>7491</v>
+        <v>7595.75</v>
       </c>
       <c r="F35" t="n">
-        <v>58.75</v>
+        <v>104.75</v>
       </c>
       <c r="G35" s="5" t="n">
-        <v>0.007900000000000001</v>
+        <v>0.014</v>
       </c>
       <c r="H35" t="n">
-        <v>169.75</v>
+        <v>105.75</v>
       </c>
       <c r="I35" t="n">
-        <v>7186.5</v>
+        <v>7184.5</v>
       </c>
       <c r="J35" t="n">
-        <v>7245.81</v>
+        <v>7347.19</v>
       </c>
       <c r="K35" t="n">
-        <v>7343.88</v>
+        <v>7406.12</v>
       </c>
       <c r="L35" t="n">
-        <v>7441.94</v>
+        <v>7465.06</v>
       </c>
       <c r="M35" t="n">
-        <v>7520.62</v>
+        <v>7575.88</v>
       </c>
       <c r="N35" t="n">
-        <v>7599.31</v>
+        <v>7686.69</v>
       </c>
       <c r="O35" t="n">
-        <v>7716.75</v>
+        <v>7693.75</v>
       </c>
       <c r="P35" s="6" t="n">
         <v/>
@@ -3446,7 +3446,7 @@
       <c r="R35" s="6" t="n">
         <v/>
       </c>
-      <c r="S35" s="7" t="inlineStr">
+      <c r="S35" s="10" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
@@ -3462,83 +3462,87 @@
       <c r="V35" s="8" t="n">
         <v/>
       </c>
-      <c r="W35" s="11" t="inlineStr">
+      <c r="W35" s="9" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
       </c>
       <c r="X35" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2026-05-25</t>
+          <t>2026-06-01</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>7519</v>
+        <v>7595</v>
       </c>
       <c r="C36" t="n">
-        <v>7611.5</v>
+        <v>7632.25</v>
       </c>
       <c r="D36" t="n">
-        <v>7505.75</v>
+        <v>7359</v>
       </c>
       <c r="E36" t="n">
-        <v>7595.75</v>
+        <v>7400.5</v>
       </c>
       <c r="F36" t="n">
-        <v>104.75</v>
+        <v>-195.25</v>
       </c>
       <c r="G36" s="5" t="n">
-        <v>0.014</v>
+        <v>-0.0257</v>
       </c>
       <c r="H36" t="n">
-        <v>105.75</v>
+        <v>273.25</v>
       </c>
       <c r="I36" t="n">
-        <v>7184.5</v>
+        <v>7400</v>
       </c>
       <c r="J36" t="n">
-        <v>7347.19</v>
+        <v>7508.56</v>
       </c>
       <c r="K36" t="n">
-        <v>7406.12</v>
+        <v>7542.88</v>
       </c>
       <c r="L36" t="n">
-        <v>7465.06</v>
+        <v>7577.19</v>
       </c>
       <c r="M36" t="n">
-        <v>7575.88</v>
+        <v>7648.62</v>
       </c>
       <c r="N36" t="n">
-        <v>7686.69</v>
+        <v>7720.06</v>
       </c>
       <c r="O36" t="n">
-        <v>7693.75</v>
-      </c>
-      <c r="P36" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q36" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R36" s="6" t="n">
-        <v/>
+        <v>7717.25</v>
+      </c>
+      <c r="P36" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="Q36" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="R36" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S36" s="7" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T36" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T36" s="8" t="n">
+        <v/>
       </c>
       <c r="U36" s="8" t="n">
         <v/>
@@ -3546,83 +3550,79 @@
       <c r="V36" s="8" t="n">
         <v/>
       </c>
-      <c r="W36" s="11" t="inlineStr">
+      <c r="W36" s="9" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
       </c>
       <c r="X36" t="inlineStr">
         <is>
-          <t>強警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-06-08</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>7595</v>
+        <v>7368</v>
       </c>
       <c r="C37" t="n">
-        <v>7632.25</v>
+        <v>7491</v>
       </c>
       <c r="D37" t="n">
-        <v>7359</v>
+        <v>7232.25</v>
       </c>
       <c r="E37" t="n">
-        <v>7400.5</v>
+        <v>7435</v>
       </c>
       <c r="F37" t="n">
-        <v>-195.25</v>
+        <v>34.5</v>
       </c>
       <c r="G37" s="5" t="n">
-        <v>-0.0257</v>
+        <v>0.0047</v>
       </c>
       <c r="H37" t="n">
-        <v>273.25</v>
+        <v>258.75</v>
       </c>
       <c r="I37" t="n">
-        <v>7400</v>
+        <v>7085.75</v>
       </c>
       <c r="J37" t="n">
-        <v>7508.56</v>
+        <v>7079.69</v>
       </c>
       <c r="K37" t="n">
-        <v>7542.88</v>
+        <v>7263.88</v>
       </c>
       <c r="L37" t="n">
-        <v>7577.19</v>
+        <v>7448.06</v>
       </c>
       <c r="M37" t="n">
-        <v>7648.62</v>
+        <v>7537.12</v>
       </c>
       <c r="N37" t="n">
-        <v>7720.06</v>
+        <v>7626.19</v>
       </c>
       <c r="O37" t="n">
-        <v>7717.25</v>
-      </c>
-      <c r="P37" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="Q37" s="6" t="inlineStr">
+        <v>7905.5</v>
+      </c>
+      <c r="P37" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q37" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R37" s="6" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="R37" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S37" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
+      <c r="S37" s="7" t="inlineStr">
+        <is>
+          <t>↓C</t>
         </is>
       </c>
       <c r="T37" s="8" t="n">
@@ -3634,7 +3634,7 @@
       <c r="V37" s="8" t="n">
         <v/>
       </c>
-      <c r="W37" s="11" t="inlineStr">
+      <c r="W37" s="9" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
@@ -3648,50 +3648,50 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>7368</v>
+        <v>7480</v>
       </c>
       <c r="C38" t="n">
-        <v>7491</v>
+        <v>7584.5</v>
       </c>
       <c r="D38" t="n">
-        <v>7232.25</v>
+        <v>7405</v>
       </c>
       <c r="E38" t="n">
-        <v>7435</v>
+        <v>7556.25</v>
       </c>
       <c r="F38" t="n">
-        <v>34.5</v>
+        <v>121.25</v>
       </c>
       <c r="G38" s="5" t="n">
-        <v>0.0047</v>
+        <v>0.0163</v>
       </c>
       <c r="H38" t="n">
-        <v>258.75</v>
+        <v>179.5</v>
       </c>
       <c r="I38" t="n">
-        <v>7085.75</v>
+        <v>6973.5</v>
       </c>
       <c r="J38" t="n">
-        <v>7079.69</v>
+        <v>7212.94</v>
       </c>
       <c r="K38" t="n">
-        <v>7263.88</v>
+        <v>7305.62</v>
       </c>
       <c r="L38" t="n">
-        <v>7448.06</v>
+        <v>7398.31</v>
       </c>
       <c r="M38" t="n">
-        <v>7537.12</v>
+        <v>7564.38</v>
       </c>
       <c r="N38" t="n">
-        <v>7626.19</v>
+        <v>7730.44</v>
       </c>
       <c r="O38" t="n">
-        <v>7905.5</v>
+        <v>7749.75</v>
       </c>
       <c r="P38" s="6" t="n">
         <v/>
@@ -3699,18 +3699,18 @@
       <c r="Q38" s="6" t="n">
         <v/>
       </c>
-      <c r="R38" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="R38" s="6" t="n">
+        <v/>
       </c>
       <c r="S38" s="10" t="inlineStr">
         <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T38" s="8" t="n">
-        <v/>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T38" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="U38" s="8" t="n">
         <v/>
@@ -3718,83 +3718,85 @@
       <c r="V38" s="8" t="n">
         <v/>
       </c>
-      <c r="W38" s="11" t="inlineStr">
+      <c r="W38" s="9" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
       </c>
       <c r="X38" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>7480</v>
+        <v>7543.25</v>
       </c>
       <c r="C39" t="n">
-        <v>7584.5</v>
+        <v>7599.25</v>
       </c>
       <c r="D39" t="n">
-        <v>7405</v>
+        <v>7357.25</v>
       </c>
       <c r="E39" t="n">
-        <v>7556.25</v>
+        <v>7401.75</v>
       </c>
       <c r="F39" t="n">
-        <v>121.25</v>
+        <v>-154.5</v>
       </c>
       <c r="G39" s="5" t="n">
-        <v>0.0163</v>
+        <v>-0.0204</v>
       </c>
       <c r="H39" t="n">
-        <v>179.5</v>
+        <v>242</v>
       </c>
       <c r="I39" t="n">
-        <v>6973.5</v>
+        <v>7225.5</v>
       </c>
       <c r="J39" t="n">
-        <v>7212.94</v>
+        <v>7407.5</v>
       </c>
       <c r="K39" t="n">
-        <v>7305.62</v>
+        <v>7466.5</v>
       </c>
       <c r="L39" t="n">
-        <v>7398.31</v>
+        <v>7525.5</v>
       </c>
       <c r="M39" t="n">
-        <v>7564.38</v>
+        <v>7646</v>
       </c>
       <c r="N39" t="n">
-        <v>7730.44</v>
+        <v>7766.5</v>
       </c>
       <c r="O39" t="n">
-        <v>7749.75</v>
+        <v>7764</v>
       </c>
       <c r="P39" s="6" t="n">
         <v/>
       </c>
-      <c r="Q39" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R39" s="6" t="n">
-        <v/>
+      <c r="Q39" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="R39" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S39" s="7" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T39" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T39" s="8" t="n">
+        <v/>
       </c>
       <c r="U39" s="8" t="n">
         <v/>
@@ -3802,150 +3804,148 @@
       <c r="V39" s="8" t="n">
         <v/>
       </c>
-      <c r="W39" s="11" t="inlineStr">
+      <c r="W39" s="9" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
       </c>
       <c r="X39" t="inlineStr">
         <is>
-          <t>強警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="B40" t="n">
-        <v>7543.25</v>
+        <v>7398</v>
       </c>
       <c r="C40" t="n">
-        <v>7599.25</v>
+        <v>7593.75</v>
       </c>
       <c r="D40" t="n">
-        <v>7357.25</v>
+        <v>7398</v>
       </c>
       <c r="E40" t="n">
-        <v>7401.75</v>
+        <v>7557</v>
       </c>
       <c r="F40" t="n">
-        <v>-154.5</v>
+        <v>155.25</v>
       </c>
       <c r="G40" s="5" t="n">
-        <v>-0.0204</v>
+        <v>0.021</v>
       </c>
       <c r="H40" t="n">
-        <v>242</v>
+        <v>195.75</v>
       </c>
       <c r="I40" t="n">
-        <v>7225.5</v>
+        <v>7115.25</v>
       </c>
       <c r="J40" t="n">
-        <v>7407.5</v>
+        <v>7121.5</v>
       </c>
       <c r="K40" t="n">
-        <v>7466.5</v>
+        <v>7280.75</v>
       </c>
       <c r="L40" t="n">
-        <v>7525.5</v>
+        <v>7440</v>
       </c>
       <c r="M40" t="n">
-        <v>7646</v>
+        <v>7522.75</v>
       </c>
       <c r="N40" t="n">
-        <v>7766.5</v>
+        <v>7605.5</v>
       </c>
       <c r="O40" t="n">
-        <v>7764</v>
+        <v>7841.25</v>
       </c>
       <c r="P40" s="6" t="n">
         <v/>
       </c>
-      <c r="Q40" s="6" t="inlineStr">
+      <c r="Q40" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R40" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S40" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T40" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="R40" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S40" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T40" s="8" t="n">
-        <v/>
-      </c>
       <c r="U40" s="8" t="n">
         <v/>
       </c>
       <c r="V40" s="8" t="n">
         <v/>
       </c>
-      <c r="W40" s="11" t="inlineStr">
+      <c r="W40" s="9" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
       </c>
       <c r="X40" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="B41" t="n">
-        <v>7398</v>
+        <v>7562.25</v>
       </c>
       <c r="C41" t="n">
-        <v>7593.75</v>
+        <v>7628.75</v>
       </c>
       <c r="D41" t="n">
-        <v>7398</v>
+        <v>7468.5</v>
       </c>
       <c r="E41" t="n">
-        <v>7557</v>
+        <v>7620.25</v>
       </c>
       <c r="F41" t="n">
-        <v>155.25</v>
+        <v>63.25</v>
       </c>
       <c r="G41" s="5" t="n">
-        <v>0.021</v>
+        <v>0.008399999999999999</v>
       </c>
       <c r="H41" t="n">
-        <v>195.75</v>
+        <v>160.25</v>
       </c>
       <c r="I41" t="n">
-        <v>7115.25</v>
+        <v>7202.25</v>
       </c>
       <c r="J41" t="n">
-        <v>7121.5</v>
+        <v>7391.81</v>
       </c>
       <c r="K41" t="n">
-        <v>7280.75</v>
+        <v>7459.12</v>
       </c>
       <c r="L41" t="n">
-        <v>7440</v>
+        <v>7526.44</v>
       </c>
       <c r="M41" t="n">
-        <v>7522.75</v>
+        <v>7654.88</v>
       </c>
       <c r="N41" t="n">
-        <v>7605.5</v>
+        <v>7783.31</v>
       </c>
       <c r="O41" t="n">
-        <v>7841.25</v>
+        <v>7789.5</v>
       </c>
       <c r="P41" s="6" t="n">
         <v/>
@@ -3956,7 +3956,7 @@
       <c r="R41" s="6" t="n">
         <v/>
       </c>
-      <c r="S41" s="7" t="inlineStr">
+      <c r="S41" s="10" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
@@ -3972,83 +3972,85 @@
       <c r="V41" s="8" t="n">
         <v/>
       </c>
-      <c r="W41" s="11" t="inlineStr">
+      <c r="W41" s="9" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
       </c>
       <c r="X41" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="B42" t="n">
-        <v>7562.25</v>
+        <v>7607</v>
       </c>
       <c r="C42" t="n">
-        <v>7628.75</v>
+        <v>7632</v>
       </c>
       <c r="D42" t="n">
-        <v>7468.5</v>
+        <v>7473</v>
       </c>
       <c r="E42" t="n">
-        <v>7620.25</v>
+        <v>7497.75</v>
       </c>
       <c r="F42" t="n">
-        <v>63.25</v>
+        <v>-122.5</v>
       </c>
       <c r="G42" s="5" t="n">
-        <v>0.008399999999999999</v>
+        <v>-0.0161</v>
       </c>
       <c r="H42" t="n">
-        <v>160.25</v>
+        <v>159</v>
       </c>
       <c r="I42" t="n">
-        <v>7202.25</v>
+        <v>7308.25</v>
       </c>
       <c r="J42" t="n">
-        <v>7391.81</v>
+        <v>7495.81</v>
       </c>
       <c r="K42" t="n">
-        <v>7459.12</v>
+        <v>7540.12</v>
       </c>
       <c r="L42" t="n">
-        <v>7526.44</v>
+        <v>7584.44</v>
       </c>
       <c r="M42" t="n">
-        <v>7654.88</v>
+        <v>7700.38</v>
       </c>
       <c r="N42" t="n">
-        <v>7783.31</v>
+        <v>7816.31</v>
       </c>
       <c r="O42" t="n">
-        <v>7789.5</v>
+        <v>7789</v>
       </c>
       <c r="P42" s="6" t="n">
         <v/>
       </c>
-      <c r="Q42" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R42" s="6" t="n">
-        <v/>
+      <c r="Q42" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="R42" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S42" s="7" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T42" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T42" s="8" t="n">
+        <v/>
       </c>
       <c r="U42" s="8" t="n">
         <v/>
@@ -4056,79 +4058,77 @@
       <c r="V42" s="8" t="n">
         <v/>
       </c>
-      <c r="W42" s="11" t="inlineStr">
+      <c r="W42" s="9" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
       </c>
       <c r="X42" t="inlineStr">
         <is>
-          <t>強警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="B43" t="n">
-        <v>7607</v>
+        <v>7485</v>
       </c>
       <c r="C43" t="n">
-        <v>7632</v>
+        <v>7563.5</v>
       </c>
       <c r="D43" t="n">
-        <v>7473</v>
+        <v>7411.75</v>
       </c>
       <c r="E43" t="n">
-        <v>7497.75</v>
+        <v>7447.5</v>
       </c>
       <c r="F43" t="n">
-        <v>-122.5</v>
+        <v>-50.25</v>
       </c>
       <c r="G43" s="5" t="n">
-        <v>-0.0161</v>
+        <v>-0.0067</v>
       </c>
       <c r="H43" t="n">
-        <v>159</v>
+        <v>151.75</v>
       </c>
       <c r="I43" t="n">
-        <v>7308.25</v>
+        <v>7314</v>
       </c>
       <c r="J43" t="n">
-        <v>7495.81</v>
+        <v>7311.38</v>
       </c>
       <c r="K43" t="n">
-        <v>7540.12</v>
+        <v>7418.25</v>
       </c>
       <c r="L43" t="n">
-        <v>7584.44</v>
+        <v>7525.12</v>
       </c>
       <c r="M43" t="n">
-        <v>7700.38</v>
+        <v>7577.25</v>
       </c>
       <c r="N43" t="n">
-        <v>7816.31</v>
+        <v>7629.38</v>
       </c>
       <c r="O43" t="n">
-        <v>7789</v>
+        <v>7791</v>
       </c>
       <c r="P43" s="6" t="n">
         <v/>
       </c>
-      <c r="Q43" s="6" t="inlineStr">
+      <c r="Q43" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R43" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="R43" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S43" s="10" t="inlineStr">
+      <c r="S43" s="7" t="inlineStr">
         <is>
           <t>↓</t>
         </is>
@@ -4142,64 +4142,60 @@
       <c r="V43" s="8" t="n">
         <v/>
       </c>
-      <c r="W43" s="11" t="inlineStr">
+      <c r="W43" s="9" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
       </c>
-      <c r="X43" t="inlineStr">
-        <is>
-          <t>中警訊</t>
-        </is>
-      </c>
+      <c r="X43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="B44" t="n">
-        <v>7485</v>
+        <v>7490</v>
       </c>
       <c r="C44" t="n">
-        <v>7563.5</v>
+        <v>7541</v>
       </c>
       <c r="D44" t="n">
-        <v>7411.75</v>
+        <v>7324</v>
       </c>
       <c r="E44" t="n">
-        <v>7447.5</v>
+        <v>7519.25</v>
       </c>
       <c r="F44" t="n">
-        <v>-50.25</v>
+        <v>71.75</v>
       </c>
       <c r="G44" s="5" t="n">
-        <v>-0.0067</v>
+        <v>0.009599999999999999</v>
       </c>
       <c r="H44" t="n">
-        <v>151.75</v>
+        <v>217</v>
       </c>
       <c r="I44" t="n">
-        <v>7314</v>
+        <v>7260</v>
       </c>
       <c r="J44" t="n">
-        <v>7311.38</v>
+        <v>7275.69</v>
       </c>
       <c r="K44" t="n">
-        <v>7418.25</v>
+        <v>7371.62</v>
       </c>
       <c r="L44" t="n">
-        <v>7525.12</v>
+        <v>7467.56</v>
       </c>
       <c r="M44" t="n">
-        <v>7577.25</v>
+        <v>7523.38</v>
       </c>
       <c r="N44" t="n">
-        <v>7629.38</v>
+        <v>7579.19</v>
       </c>
       <c r="O44" t="n">
-        <v>7791</v>
+        <v>7715.25</v>
       </c>
       <c r="P44" s="6" t="n">
         <v/>
@@ -4209,77 +4205,83 @@
       </c>
       <c r="R44" s="6" t="inlineStr">
         <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S44" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T44" s="8" t="inlineStr">
+        <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="S44" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T44" s="8" t="n">
-        <v/>
-      </c>
       <c r="U44" s="8" t="n">
         <v/>
       </c>
       <c r="V44" s="8" t="n">
         <v/>
       </c>
-      <c r="W44" s="11" t="inlineStr">
+      <c r="W44" s="9" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
       </c>
-      <c r="X44" t="inlineStr"/>
+      <c r="X44" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="B45" t="n">
-        <v>7490</v>
+        <v>7550</v>
       </c>
       <c r="C45" t="n">
-        <v>7541</v>
+        <v>7820.25</v>
       </c>
       <c r="D45" t="n">
-        <v>7324</v>
+        <v>7542.75</v>
       </c>
       <c r="E45" t="n">
-        <v>7519.25</v>
+        <v>7779.75</v>
       </c>
       <c r="F45" t="n">
-        <v>71.75</v>
+        <v>260.5</v>
       </c>
       <c r="G45" s="5" t="n">
-        <v>0.009599999999999999</v>
+        <v>0.0346</v>
       </c>
       <c r="H45" t="n">
-        <v>217</v>
+        <v>277.5</v>
       </c>
       <c r="I45" t="n">
-        <v>7260</v>
+        <v>7107</v>
       </c>
       <c r="J45" t="n">
-        <v>7275.69</v>
+        <v>7345.62</v>
       </c>
       <c r="K45" t="n">
-        <v>7371.62</v>
+        <v>7410.75</v>
       </c>
       <c r="L45" t="n">
-        <v>7467.56</v>
+        <v>7475.88</v>
       </c>
       <c r="M45" t="n">
-        <v>7523.38</v>
+        <v>7627.75</v>
       </c>
       <c r="N45" t="n">
-        <v>7579.19</v>
+        <v>7779.62</v>
       </c>
       <c r="O45" t="n">
-        <v>7715.25</v>
+        <v>7758</v>
       </c>
       <c r="P45" s="6" t="n">
         <v/>
@@ -4287,85 +4289,83 @@
       <c r="Q45" s="6" t="n">
         <v/>
       </c>
-      <c r="R45" s="6" t="inlineStr">
+      <c r="R45" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S45" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T45" s="8" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="S45" s="7" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T45" s="8" t="inlineStr">
+      <c r="U45" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="U45" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V45" s="8" t="n">
-        <v/>
+      <c r="V45" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="W45" s="11" t="inlineStr">
         <is>
-          <t>空方</t>
-        </is>
-      </c>
-      <c r="X45" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+          <t>多方</t>
+        </is>
+      </c>
+      <c r="X45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="B46" t="n">
-        <v>7550</v>
+        <v>7776.75</v>
       </c>
       <c r="C46" t="n">
-        <v>7820.25</v>
+        <v>7838.5</v>
       </c>
       <c r="D46" t="n">
-        <v>7542.75</v>
+        <v>7738</v>
       </c>
       <c r="E46" t="n">
-        <v>7779.75</v>
+        <v>7805</v>
       </c>
       <c r="F46" t="n">
-        <v>260.5</v>
+        <v>25.25</v>
       </c>
       <c r="G46" s="5" t="n">
-        <v>0.0346</v>
+        <v>0.0032</v>
       </c>
       <c r="H46" t="n">
-        <v>277.5</v>
+        <v>100.5</v>
       </c>
       <c r="I46" t="n">
-        <v>7107</v>
+        <v>7265.25</v>
       </c>
       <c r="J46" t="n">
-        <v>7345.62</v>
+        <v>7551.38</v>
       </c>
       <c r="K46" t="n">
-        <v>7410.75</v>
+        <v>7641</v>
       </c>
       <c r="L46" t="n">
-        <v>7475.88</v>
+        <v>7730.62</v>
       </c>
       <c r="M46" t="n">
-        <v>7627.75</v>
+        <v>7918.5</v>
       </c>
       <c r="N46" t="n">
-        <v>7779.62</v>
+        <v>8106.38</v>
       </c>
       <c r="O46" t="n">
-        <v>7758</v>
+        <v>8097.75</v>
       </c>
       <c r="P46" s="6" t="n">
         <v/>
@@ -4376,27 +4376,21 @@
       <c r="R46" s="6" t="n">
         <v/>
       </c>
-      <c r="S46" s="7" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T46" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U46" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="V46" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="W46" s="9" t="inlineStr">
+      <c r="S46" s="10" t="inlineStr">
+        <is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T46" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U46" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V46" s="8" t="n">
+        <v/>
+      </c>
+      <c r="W46" s="11" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
@@ -4406,63 +4400,67 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="B47" t="n">
-        <v>7776.75</v>
+        <v>7809.25</v>
       </c>
       <c r="C47" t="n">
-        <v>7838.5</v>
+        <v>7824.5</v>
       </c>
       <c r="D47" t="n">
-        <v>7738</v>
+        <v>7657.75</v>
       </c>
       <c r="E47" t="n">
-        <v>7805</v>
+        <v>7691.25</v>
       </c>
       <c r="F47" t="n">
-        <v>25.25</v>
+        <v>-113.75</v>
       </c>
       <c r="G47" s="5" t="n">
-        <v>0.0032</v>
+        <v>-0.0146</v>
       </c>
       <c r="H47" t="n">
-        <v>100.5</v>
+        <v>166.75</v>
       </c>
       <c r="I47" t="n">
-        <v>7265.25</v>
+        <v>7637.5</v>
       </c>
       <c r="J47" t="n">
-        <v>7551.38</v>
+        <v>7712.88</v>
       </c>
       <c r="K47" t="n">
-        <v>7641</v>
+        <v>7754.75</v>
       </c>
       <c r="L47" t="n">
-        <v>7730.62</v>
+        <v>7796.62</v>
       </c>
       <c r="M47" t="n">
-        <v>7918.5</v>
+        <v>7855.25</v>
       </c>
       <c r="N47" t="n">
-        <v>8106.38</v>
+        <v>7913.88</v>
       </c>
       <c r="O47" t="n">
-        <v>8097.75</v>
+        <v>7939</v>
       </c>
       <c r="P47" s="6" t="n">
         <v/>
       </c>
-      <c r="Q47" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R47" s="6" t="n">
-        <v/>
+      <c r="Q47" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="R47" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S47" s="7" t="inlineStr">
         <is>
-          <t>↑C</t>
+          <t>↓</t>
         </is>
       </c>
       <c r="T47" s="8" t="n">
@@ -4476,7 +4474,7 @@
       </c>
       <c r="W47" s="9" t="inlineStr">
         <is>
-          <t>多方</t>
+          <t>空方</t>
         </is>
       </c>
       <c r="X47" t="inlineStr"/>
@@ -4484,132 +4482,134 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="B48" t="n">
-        <v>7809.25</v>
+        <v>7693.5</v>
       </c>
       <c r="C48" t="n">
-        <v>7824.5</v>
+        <v>7782.5</v>
       </c>
       <c r="D48" t="n">
-        <v>7657.75</v>
+        <v>7655</v>
       </c>
       <c r="E48" t="n">
-        <v>7691.25</v>
+        <v>7722</v>
       </c>
       <c r="F48" t="n">
-        <v>-113.75</v>
+        <v>30.75</v>
       </c>
       <c r="G48" s="5" t="n">
-        <v>-0.0146</v>
+        <v>0.004</v>
       </c>
       <c r="H48" t="n">
-        <v>166.75</v>
+        <v>127.5</v>
       </c>
       <c r="I48" t="n">
-        <v>7637.5</v>
+        <v>7491</v>
       </c>
       <c r="J48" t="n">
-        <v>7712.88</v>
+        <v>7499.56</v>
       </c>
       <c r="K48" t="n">
-        <v>7754.75</v>
+        <v>7607.88</v>
       </c>
       <c r="L48" t="n">
-        <v>7796.62</v>
+        <v>7716.19</v>
       </c>
       <c r="M48" t="n">
-        <v>7855.25</v>
+        <v>7774.62</v>
       </c>
       <c r="N48" t="n">
-        <v>7913.88</v>
+        <v>7833.06</v>
       </c>
       <c r="O48" t="n">
-        <v>7939</v>
+        <v>7991.25</v>
       </c>
       <c r="P48" s="6" t="n">
         <v/>
       </c>
-      <c r="Q48" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="R48" s="6" t="inlineStr">
+      <c r="Q48" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R48" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S48" s="10" t="inlineStr">
+        <is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T48" s="8" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="S48" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T48" s="8" t="n">
-        <v/>
-      </c>
       <c r="U48" s="8" t="n">
         <v/>
       </c>
       <c r="V48" s="8" t="n">
         <v/>
       </c>
-      <c r="W48" s="11" t="inlineStr">
+      <c r="W48" s="9" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
       </c>
-      <c r="X48" t="inlineStr"/>
+      <c r="X48" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="B49" t="n">
-        <v>7693.5</v>
+        <v>7723.5</v>
       </c>
       <c r="C49" t="n">
-        <v>7782.5</v>
+        <v>7766.5</v>
       </c>
       <c r="D49" t="n">
-        <v>7655</v>
+        <v>7618.5</v>
       </c>
       <c r="E49" t="n">
         <v>7722</v>
       </c>
       <c r="F49" t="n">
-        <v>30.75</v>
+        <v>0</v>
       </c>
       <c r="G49" s="5" t="n">
-        <v>0.004</v>
+        <v>0</v>
       </c>
       <c r="H49" t="n">
-        <v>127.5</v>
+        <v>148</v>
       </c>
       <c r="I49" t="n">
-        <v>7491</v>
+        <v>7527.5</v>
       </c>
       <c r="J49" t="n">
-        <v>7499.56</v>
+        <v>7596.12</v>
       </c>
       <c r="K49" t="n">
-        <v>7607.88</v>
+        <v>7658.25</v>
       </c>
       <c r="L49" t="n">
-        <v>7716.19</v>
+        <v>7720.38</v>
       </c>
       <c r="M49" t="n">
-        <v>7774.62</v>
+        <v>7785.75</v>
       </c>
       <c r="N49" t="n">
-        <v>7833.06</v>
+        <v>7851.12</v>
       </c>
       <c r="O49" t="n">
-        <v>7991.25</v>
+        <v>7910</v>
       </c>
       <c r="P49" s="6" t="n">
         <v/>
@@ -4617,18 +4617,18 @@
       <c r="Q49" s="6" t="n">
         <v/>
       </c>
-      <c r="R49" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S49" s="7" t="inlineStr">
+      <c r="R49" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S49" s="10" t="inlineStr">
         <is>
           <t>↑C</t>
         </is>
       </c>
-      <c r="T49" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="T49" s="8" t="n">
+        <v/>
       </c>
       <c r="U49" s="8" t="n">
         <v/>
@@ -4636,79 +4636,77 @@
       <c r="V49" s="8" t="n">
         <v/>
       </c>
-      <c r="W49" s="11" t="inlineStr">
+      <c r="W49" s="9" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
       </c>
-      <c r="X49" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="X49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="B50" t="n">
-        <v>7723.5</v>
+        <v>7715.5</v>
       </c>
       <c r="C50" t="n">
-        <v>7766.5</v>
+        <v>7728.5</v>
       </c>
       <c r="D50" t="n">
-        <v>7618.5</v>
+        <v>7585.5</v>
       </c>
       <c r="E50" t="n">
-        <v>7722</v>
+        <v>7659.5</v>
       </c>
       <c r="F50" t="n">
-        <v>0</v>
+        <v>-62.5</v>
       </c>
       <c r="G50" s="5" t="n">
-        <v>0</v>
+        <v>-0.0081</v>
       </c>
       <c r="H50" t="n">
-        <v>148</v>
+        <v>143</v>
       </c>
       <c r="I50" t="n">
-        <v>7527.5</v>
+        <v>7470.5</v>
       </c>
       <c r="J50" t="n">
-        <v>7596.12</v>
+        <v>7588.75</v>
       </c>
       <c r="K50" t="n">
-        <v>7658.25</v>
+        <v>7648</v>
       </c>
       <c r="L50" t="n">
-        <v>7720.38</v>
+        <v>7707.25</v>
       </c>
       <c r="M50" t="n">
-        <v>7785.75</v>
+        <v>7796</v>
       </c>
       <c r="N50" t="n">
-        <v>7851.12</v>
+        <v>7884.75</v>
       </c>
       <c r="O50" t="n">
-        <v>7910</v>
+        <v>7914.5</v>
       </c>
       <c r="P50" s="6" t="n">
         <v/>
       </c>
-      <c r="Q50" s="6" t="n">
-        <v/>
+      <c r="Q50" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="R50" s="6" t="inlineStr">
         <is>
-          <t>✓</t>
+          <t>△C</t>
         </is>
       </c>
       <c r="S50" s="7" t="inlineStr">
         <is>
-          <t>↑C</t>
+          <t>↓</t>
         </is>
       </c>
       <c r="T50" s="8" t="n">
@@ -4720,7 +4718,7 @@
       <c r="V50" s="8" t="n">
         <v/>
       </c>
-      <c r="W50" s="11" t="inlineStr">
+      <c r="W50" s="9" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
@@ -4730,50 +4728,50 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="B51" t="n">
-        <v>7715.5</v>
+        <v>7609.25</v>
       </c>
       <c r="C51" t="n">
-        <v>7728.5</v>
+        <v>7670.25</v>
       </c>
       <c r="D51" t="n">
-        <v>7585.5</v>
+        <v>7509.25</v>
       </c>
       <c r="E51" t="n">
-        <v>7659.5</v>
+        <v>7657.35</v>
       </c>
       <c r="F51" t="n">
-        <v>-62.5</v>
+        <v>-2.15</v>
       </c>
       <c r="G51" s="5" t="n">
-        <v>-0.0081</v>
+        <v>-0.0003</v>
       </c>
       <c r="H51" t="n">
-        <v>143</v>
+        <v>161</v>
       </c>
       <c r="I51" t="n">
-        <v>7470.5</v>
+        <v>7442.5</v>
       </c>
       <c r="J51" t="n">
-        <v>7588.75</v>
+        <v>7517.75</v>
       </c>
       <c r="K51" t="n">
-        <v>7648</v>
+        <v>7588</v>
       </c>
       <c r="L51" t="n">
-        <v>7707.25</v>
+        <v>7658.25</v>
       </c>
       <c r="M51" t="n">
-        <v>7796</v>
+        <v>7731</v>
       </c>
       <c r="N51" t="n">
-        <v>7884.75</v>
+        <v>7803.75</v>
       </c>
       <c r="O51" t="n">
-        <v>7914.5</v>
+        <v>7871.5</v>
       </c>
       <c r="P51" s="6" t="n">
         <v/>
@@ -4785,12 +4783,12 @@
       </c>
       <c r="R51" s="6" t="inlineStr">
         <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="S51" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S51" s="7" t="inlineStr">
+        <is>
+          <t>↓C</t>
         </is>
       </c>
       <c r="T51" s="8" t="n">
@@ -4802,7 +4800,7 @@
       <c r="V51" s="8" t="n">
         <v/>
       </c>
-      <c r="W51" s="11" t="inlineStr">
+      <c r="W51" s="9" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
@@ -4812,239 +4810,237 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="B52" t="n">
-        <v>7609.25</v>
+        <v>7722</v>
       </c>
       <c r="C52" t="n">
-        <v>7670.25</v>
+        <v>7848.5</v>
       </c>
       <c r="D52" t="n">
-        <v>7509.25</v>
+        <v>7707.25</v>
       </c>
       <c r="E52" t="n">
-        <v>7657.35</v>
+        <v>7803.75</v>
       </c>
       <c r="F52" t="n">
-        <v>-2.15</v>
+        <v>146.4</v>
       </c>
       <c r="G52" s="5" t="n">
-        <v>-0.0003</v>
+        <v>0.0191</v>
       </c>
       <c r="H52" t="n">
-        <v>161</v>
+        <v>141.25</v>
       </c>
       <c r="I52" t="n">
-        <v>7442.5</v>
+        <v>7348.25</v>
       </c>
       <c r="J52" t="n">
-        <v>7517.75</v>
+        <v>7530.15</v>
       </c>
       <c r="K52" t="n">
-        <v>7588</v>
+        <v>7576.85</v>
       </c>
       <c r="L52" t="n">
-        <v>7658.25</v>
+        <v>7623.55</v>
       </c>
       <c r="M52" t="n">
-        <v>7731</v>
+        <v>7737.85</v>
       </c>
       <c r="N52" t="n">
-        <v>7803.75</v>
+        <v>7852.15</v>
       </c>
       <c r="O52" t="n">
-        <v>7871.5</v>
+        <v>7831.25</v>
       </c>
       <c r="P52" s="6" t="n">
         <v/>
       </c>
-      <c r="Q52" s="6" t="inlineStr">
+      <c r="Q52" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R52" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S52" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T52" s="8" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="R52" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S52" s="10" t="inlineStr">
-        <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T52" s="8" t="n">
-        <v/>
-      </c>
       <c r="U52" s="8" t="n">
         <v/>
       </c>
-      <c r="V52" s="8" t="n">
-        <v/>
-      </c>
-      <c r="W52" s="11" t="inlineStr">
+      <c r="V52" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="W52" s="9" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
       </c>
-      <c r="X52" t="inlineStr"/>
+      <c r="X52" t="inlineStr">
+        <is>
+          <t>強警訊</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="B53" t="n">
-        <v>7722</v>
+        <v>7796</v>
       </c>
       <c r="C53" t="n">
-        <v>7848.5</v>
+        <v>7810.25</v>
       </c>
       <c r="D53" t="n">
-        <v>7707.25</v>
+        <v>7672.75</v>
       </c>
       <c r="E53" t="n">
-        <v>7803.75</v>
+        <v>7777.25</v>
       </c>
       <c r="F53" t="n">
-        <v>146.4</v>
+        <v>-26.5</v>
       </c>
       <c r="G53" s="5" t="n">
-        <v>0.0191</v>
+        <v>-0.0034</v>
       </c>
       <c r="H53" t="n">
-        <v>141.25</v>
+        <v>137.5</v>
       </c>
       <c r="I53" t="n">
-        <v>7348.25</v>
+        <v>7566</v>
       </c>
       <c r="J53" t="n">
-        <v>7530.15</v>
+        <v>7675.44</v>
       </c>
       <c r="K53" t="n">
-        <v>7576.85</v>
+        <v>7733.12</v>
       </c>
       <c r="L53" t="n">
-        <v>7623.55</v>
+        <v>7790.81</v>
       </c>
       <c r="M53" t="n">
-        <v>7737.85</v>
+        <v>7874.38</v>
       </c>
       <c r="N53" t="n">
-        <v>7852.15</v>
+        <v>7957.94</v>
       </c>
       <c r="O53" t="n">
-        <v>7831.25</v>
+        <v>7989.75</v>
       </c>
       <c r="P53" s="6" t="n">
         <v/>
       </c>
-      <c r="Q53" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R53" s="6" t="n">
-        <v/>
+      <c r="Q53" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="R53" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S53" s="7" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T53" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T53" s="8" t="n">
+        <v/>
       </c>
       <c r="U53" s="8" t="n">
         <v/>
       </c>
-      <c r="V53" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="W53" s="11" t="inlineStr">
+      <c r="V53" s="8" t="n">
+        <v/>
+      </c>
+      <c r="W53" s="9" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
       </c>
-      <c r="X53" t="inlineStr">
-        <is>
-          <t>強警訊</t>
-        </is>
-      </c>
+      <c r="X53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="B54" t="n">
-        <v>7796</v>
+        <v>7781.5</v>
       </c>
       <c r="C54" t="n">
-        <v>7810.25</v>
+        <v>7897.5</v>
       </c>
       <c r="D54" t="n">
-        <v>7672.75</v>
+        <v>7760.25</v>
       </c>
       <c r="E54" t="n">
-        <v>7777.25</v>
+        <v>7859.75</v>
       </c>
       <c r="F54" t="n">
-        <v>-26.5</v>
+        <v>82.5</v>
       </c>
       <c r="G54" s="5" t="n">
-        <v>-0.0034</v>
+        <v>0.0106</v>
       </c>
       <c r="H54" t="n">
-        <v>137.5</v>
+        <v>137.25</v>
       </c>
       <c r="I54" t="n">
-        <v>7566</v>
+        <v>7535.25</v>
       </c>
       <c r="J54" t="n">
-        <v>7675.44</v>
+        <v>7657.62</v>
       </c>
       <c r="K54" t="n">
-        <v>7733.12</v>
+        <v>7708.5</v>
       </c>
       <c r="L54" t="n">
-        <v>7790.81</v>
+        <v>7759.38</v>
       </c>
       <c r="M54" t="n">
-        <v>7874.38</v>
+        <v>7846</v>
       </c>
       <c r="N54" t="n">
-        <v>7957.94</v>
+        <v>7932.62</v>
       </c>
       <c r="O54" t="n">
-        <v>7989.75</v>
+        <v>7947.75</v>
       </c>
       <c r="P54" s="6" t="n">
         <v/>
       </c>
-      <c r="Q54" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="R54" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="Q54" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R54" s="6" t="n">
+        <v/>
       </c>
       <c r="S54" s="10" t="inlineStr">
         <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T54" s="8" t="n">
-        <v/>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T54" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="U54" s="8" t="n">
         <v/>
@@ -5052,79 +5048,85 @@
       <c r="V54" s="8" t="n">
         <v/>
       </c>
-      <c r="W54" s="11" t="inlineStr">
+      <c r="W54" s="9" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
       </c>
-      <c r="X54" t="inlineStr"/>
+      <c r="X54" t="inlineStr">
+        <is>
+          <t>強警訊</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="B55" t="n">
-        <v>7781.5</v>
+        <v>7873</v>
       </c>
       <c r="C55" t="n">
-        <v>7897.5</v>
+        <v>7887</v>
       </c>
       <c r="D55" t="n">
-        <v>7760.25</v>
+        <v>7676</v>
       </c>
       <c r="E55" t="n">
-        <v>7859.75</v>
+        <v>7704.25</v>
       </c>
       <c r="F55" t="n">
-        <v>82.5</v>
+        <v>-155.5</v>
       </c>
       <c r="G55" s="5" t="n">
-        <v>0.0106</v>
+        <v>-0.0198</v>
       </c>
       <c r="H55" t="n">
-        <v>137.25</v>
+        <v>211</v>
       </c>
       <c r="I55" t="n">
-        <v>7535.25</v>
+        <v>7623</v>
       </c>
       <c r="J55" t="n">
-        <v>7657.62</v>
+        <v>7737.94</v>
       </c>
       <c r="K55" t="n">
-        <v>7708.5</v>
+        <v>7791.12</v>
       </c>
       <c r="L55" t="n">
-        <v>7759.38</v>
+        <v>7844.31</v>
       </c>
       <c r="M55" t="n">
-        <v>7846</v>
+        <v>7928.38</v>
       </c>
       <c r="N55" t="n">
-        <v>7932.62</v>
+        <v>8012.44</v>
       </c>
       <c r="O55" t="n">
-        <v>7947.75</v>
+        <v>8034.75</v>
       </c>
       <c r="P55" s="6" t="n">
         <v/>
       </c>
-      <c r="Q55" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R55" s="6" t="n">
-        <v/>
+      <c r="Q55" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="R55" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S55" s="7" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T55" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T55" s="8" t="n">
+        <v/>
       </c>
       <c r="U55" s="8" t="n">
         <v/>
@@ -5132,93 +5134,89 @@
       <c r="V55" s="8" t="n">
         <v/>
       </c>
-      <c r="W55" s="11" t="inlineStr">
+      <c r="W55" s="9" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
       </c>
-      <c r="X55" t="inlineStr">
-        <is>
-          <t>強警訊</t>
-        </is>
-      </c>
+      <c r="X55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="B56" t="n">
-        <v>7873</v>
+        <v>7679.5</v>
       </c>
       <c r="C56" t="n">
-        <v>7887</v>
+        <v>7812.25</v>
       </c>
       <c r="D56" t="n">
-        <v>7676</v>
+        <v>7648.5</v>
       </c>
       <c r="E56" t="n">
-        <v>7704.25</v>
+        <v>7659.75</v>
       </c>
       <c r="F56" t="n">
-        <v>-155.5</v>
+        <v>-44.5</v>
       </c>
       <c r="G56" s="5" t="n">
-        <v>-0.0198</v>
+        <v>-0.0058</v>
       </c>
       <c r="H56" t="n">
-        <v>211</v>
+        <v>163.75</v>
       </c>
       <c r="I56" t="n">
-        <v>7623</v>
+        <v>7465</v>
       </c>
       <c r="J56" t="n">
-        <v>7737.94</v>
+        <v>7454.62</v>
       </c>
       <c r="K56" t="n">
-        <v>7791.12</v>
+        <v>7598.75</v>
       </c>
       <c r="L56" t="n">
-        <v>7844.31</v>
+        <v>7742.88</v>
       </c>
       <c r="M56" t="n">
-        <v>7928.38</v>
+        <v>7809.75</v>
       </c>
       <c r="N56" t="n">
-        <v>8012.44</v>
+        <v>7876.62</v>
       </c>
       <c r="O56" t="n">
-        <v>8034.75</v>
+        <v>8098</v>
       </c>
       <c r="P56" s="6" t="n">
         <v/>
       </c>
-      <c r="Q56" s="6" t="inlineStr">
+      <c r="Q56" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R56" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="R56" s="6" t="inlineStr">
+      <c r="S56" s="7" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T56" s="8" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="S56" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T56" s="8" t="n">
-        <v/>
-      </c>
       <c r="U56" s="8" t="n">
         <v/>
       </c>
       <c r="V56" s="8" t="n">
         <v/>
       </c>
-      <c r="W56" s="11" t="inlineStr">
+      <c r="W56" s="9" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
@@ -5228,50 +5226,50 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="B57" t="n">
-        <v>7679.5</v>
+        <v>7690</v>
       </c>
       <c r="C57" t="n">
-        <v>7812.25</v>
+        <v>7819.5</v>
       </c>
       <c r="D57" t="n">
-        <v>7648.5</v>
+        <v>7558.25</v>
       </c>
       <c r="E57" t="n">
-        <v>7659.75</v>
+        <v>7614.5</v>
       </c>
       <c r="F57" t="n">
-        <v>-44.5</v>
+        <v>-45.25</v>
       </c>
       <c r="G57" s="5" t="n">
-        <v>-0.0058</v>
+        <v>-0.0059</v>
       </c>
       <c r="H57" t="n">
-        <v>163.75</v>
+        <v>261.25</v>
       </c>
       <c r="I57" t="n">
-        <v>7465</v>
+        <v>7484.75</v>
       </c>
       <c r="J57" t="n">
-        <v>7454.62</v>
+        <v>7460.69</v>
       </c>
       <c r="K57" t="n">
-        <v>7598.75</v>
+        <v>7577.88</v>
       </c>
       <c r="L57" t="n">
-        <v>7742.88</v>
+        <v>7695.06</v>
       </c>
       <c r="M57" t="n">
-        <v>7809.75</v>
+        <v>7741.62</v>
       </c>
       <c r="N57" t="n">
-        <v>7876.62</v>
+        <v>7788.19</v>
       </c>
       <c r="O57" t="n">
-        <v>8098</v>
+        <v>7976</v>
       </c>
       <c r="P57" s="6" t="n">
         <v/>
@@ -5284,7 +5282,7 @@
           <t>△C</t>
         </is>
       </c>
-      <c r="S57" s="10" t="inlineStr">
+      <c r="S57" s="7" t="inlineStr">
         <is>
           <t>↓</t>
         </is>
@@ -5294,102 +5292,22 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="U57" s="8" t="n">
-        <v/>
+      <c r="U57" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="V57" s="8" t="n">
         <v/>
       </c>
-      <c r="W57" s="11" t="inlineStr">
+      <c r="W57" s="9" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
       </c>
-      <c r="X57" t="inlineStr"/>
-    </row>
-    <row r="58">
-      <c r="A58" t="inlineStr">
-        <is>
-          <t>2026-10-26</t>
-        </is>
-      </c>
-      <c r="B58" t="n">
-        <v>7690</v>
-      </c>
-      <c r="C58" t="n">
-        <v>7819.5</v>
-      </c>
-      <c r="D58" t="n">
-        <v>7651.75</v>
-      </c>
-      <c r="E58" t="n">
-        <v>7672</v>
-      </c>
-      <c r="F58" t="n">
-        <v>12.25</v>
-      </c>
-      <c r="G58" s="5" t="n">
-        <v>0.0016</v>
-      </c>
-      <c r="H58" t="n">
-        <v>167.75</v>
-      </c>
-      <c r="I58" t="n">
-        <v>7484.75</v>
-      </c>
-      <c r="J58" t="n">
-        <v>7460.69</v>
-      </c>
-      <c r="K58" t="n">
-        <v>7577.88</v>
-      </c>
-      <c r="L58" t="n">
-        <v>7695.06</v>
-      </c>
-      <c r="M58" t="n">
-        <v>7741.62</v>
-      </c>
-      <c r="N58" t="n">
-        <v>7788.19</v>
-      </c>
-      <c r="O58" t="n">
-        <v>7976</v>
-      </c>
-      <c r="P58" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q58" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R58" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S58" s="10" t="inlineStr">
-        <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T58" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U58" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="V58" s="8" t="n">
-        <v/>
-      </c>
-      <c r="W58" s="11" t="inlineStr">
-        <is>
-          <t>空方</t>
-        </is>
-      </c>
-      <c r="X58" t="inlineStr">
-        <is>
-          <t>強警訊</t>
+      <c r="X57" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
